--- a/NYC_2026_Planificador.xlsx
+++ b/NYC_2026_Planificador.xlsx
@@ -16994,7 +16994,7 @@
         <v>2</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H156" s="13">
         <f>IF(AND(F156=2,G156=2),"AMBOS",IF(AND(F156=2,G156&lt;2),"solo JP",IF(AND(F156&lt;2,G156=2),"solo Thais","-")))</f>

--- a/NYC_2026_Planificador.xlsx
+++ b/NYC_2026_Planificador.xlsx
@@ -18315,7 +18315,7 @@
       </c>
       <c r="S169" s="17" t="inlineStr">
         <is>
-          <t>Día 3 · lun 31/8, Día 7 · vie 4/9</t>
+          <t>Día 3 · lun 31/8</t>
         </is>
       </c>
       <c r="T169" s="18" t="inlineStr">
@@ -23035,7 +23035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I181"/>
+  <dimension ref="A1:I180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -26110,7 +26110,7 @@
     <row r="126" ht="32" customHeight="1">
       <c r="A126" s="34" t="inlineStr">
         <is>
-          <t>Salieron el West Village, Washington Square y el Whitney; entraron el High Line, THE VESSEL (al pie del arranque, $10 y 45 min), la Morgan (hoy GRATIS 17-20) y SUMMIT — que se movió AL ATARDECER por el pedido de ustedes: entrada 18:10, luz plena, la puesta ~19:21 multiplicada por los espejos de Kusama (es EL lugar de la ciudad para ese momento) y la noche encendida hasta las 20:15. EL PAGO, dicho honesto: la Morgan se hace en una hora entrando 17:00 en punto, y la cena de hoy es un bocado rápido — por eso el almuerzo en Chelsea Market es EL fuerte del día.</t>
+          <t>Salieron el West Village, Washington Square y el Whitney; entraron el High Line, THE VESSEL (al pie del arranque, $10 y 45 min), la Morgan (hoy GRATIS 17-20) y SUMMIT — que se movió AL ATARDECER por el pedido de ustedes: entrada 18:10, luz plena, la puesta ~19:21 multiplicada por los espejos de Kusama (es EL lugar de la ciudad para ese momento) y la noche encendida hasta las 20:15. EL PAGO, dicho honesto: la Morgan se hace en una hora entrando 17:00 en punto, y la cena de hoy es un bocado rápido — por eso el almuerzo en Chelsea Market es EL fuerte del día. SALIÓ GRAND CENTRAL: estaba a las 16:20 con el argumento de que JP ya lo vio el lunes y Thais no — pero ella lo tiene en 0, así que eran 40 minutos para alguien que no lo quiere. Sin esa parada tampoco hace falta cortar Chelsea a las 15:50: se sale 16:25 derecho a la Morgan y la tarde de galerías y almuerzo gana una hora larga.</t>
         </is>
       </c>
     </row>
@@ -26305,7 +26305,7 @@
       </c>
       <c r="C133" s="37" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="D133" s="38" t="inlineStr">
@@ -26315,7 +26315,7 @@
       </c>
       <c r="E133" s="39" t="inlineStr">
         <is>
-          <t>Almuerzo en Chelsea Market — COMER FUERTE: es la comida grande del día, la cena de hoy es un bocado rápido entre el SUMMIT y el Vanguard. Los Tacos No.1 o Very Fresh Noodles.</t>
+          <t>Almuerzo en Chelsea Market — COMER FUERTE: es la comida grande del día, la cena de hoy es un bocado rápido entre el SUMMIT y el Vanguard. Los Tacos No.1 o Very Fresh Noodles. Ahora hay casi DOS HORAS: sin apuro, y si quedaron galerías de Chelsea sin ver, se vuelve.</t>
         </is>
       </c>
       <c r="F133" s="37" t="inlineStr">
@@ -26335,12 +26335,12 @@
       <c r="A134" s="35" t="n"/>
       <c r="B134" s="36" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="C134" s="37" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D134" s="38" t="inlineStr">
@@ -26350,7 +26350,7 @@
       </c>
       <c r="E134" s="39" t="inlineStr">
         <is>
-          <t>A Grand Central SIN desandar: L desde 14 St-8 Av hasta Union Sq y 4/5 exprés hasta Grand Central (~20 min puerta a puerta). Volver caminando a Hudson Yards sería 1,9 km al revés.</t>
+          <t>A la Morgan: L desde 14 St-8 Av hasta Union Sq y 6 hasta 33 St, o A/C/E hasta 34 St-Penn y siete cuadras a pie (~30 min). Salir 16:25 deja margen para entrar 17:00 EN PUNTO.</t>
         </is>
       </c>
       <c r="F134" s="37" t="inlineStr"/>
@@ -26360,124 +26360,116 @@
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="35" t="n"/>
-      <c r="B135" s="36" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="C135" s="37" t="inlineStr">
+      <c r="B135" s="42" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D135" s="38" t="inlineStr">
+      <c r="C135" s="43" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D135" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E135" s="39" t="inlineStr">
-        <is>
-          <t>Grand Central PARA THAIS: el techo celeste, la Whispering Gallery y el mercado — JP ya lo vio el lunes, ella no, y está literalmente abajo del SUMMIT.</t>
-        </is>
-      </c>
-      <c r="F135" s="37" t="inlineStr">
-        <is>
-          <t>Grand Central Terminal</t>
+      <c r="E135" s="45" t="inlineStr">
+        <is>
+          <t>★ MORGAN LIBRARY — GRATIS los viernes 17-20h: entrar 17:00 EN PUNTO y hacerla en una hora — la biblioteca son tres salas gloriosas (estanterías de nogal, la Biblia de Gutenberg): alcanza. RESERVA OBLIGATORIA, se libera el viernes 28 de agosto. Está a 8 min a pie de One Vanderbilt.</t>
+        </is>
+      </c>
+      <c r="F135" s="43" t="inlineStr">
+        <is>
+          <t>The Morgan Library &amp; Museum</t>
         </is>
       </c>
       <c r="G135" s="40" t="inlineStr"/>
       <c r="H135" s="41" t="inlineStr"/>
       <c r="I135" s="41" t="inlineStr"/>
     </row>
-    <row r="136" ht="30" customHeight="1">
+    <row r="136" ht="16" customHeight="1">
       <c r="A136" s="35" t="n"/>
-      <c r="B136" s="42" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C136" s="43" t="inlineStr">
+      <c r="B136" s="36" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D136" s="44" t="inlineStr">
+      <c r="C136" s="37" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D136" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E136" s="45" t="inlineStr">
-        <is>
-          <t>★ MORGAN LIBRARY — GRATIS los viernes 17-20h: entrar 17:00 EN PUNTO y hacerla en una hora — la biblioteca son tres salas gloriosas (estanterías de nogal, la Biblia de Gutenberg): alcanza. RESERVA OBLIGATORIA, se libera el viernes 28 de agosto. Está a 8 min a pie de One Vanderbilt.</t>
-        </is>
-      </c>
-      <c r="F136" s="43" t="inlineStr">
-        <is>
-          <t>The Morgan Library &amp; Museum</t>
-        </is>
-      </c>
-      <c r="G136" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~9 min a pie · 0.7 km · estimado</t>
-        </is>
-      </c>
+      <c r="E136" s="39" t="inlineStr">
+        <is>
+          <t>Caminar las seis cuadras de la Morgan a One Vanderbilt (~8-10 min).</t>
+        </is>
+      </c>
+      <c r="F136" s="37" t="inlineStr"/>
+      <c r="G136" s="40" t="inlineStr"/>
       <c r="H136" s="41" t="inlineStr"/>
       <c r="I136" s="41" t="inlineStr"/>
     </row>
-    <row r="137" ht="16" customHeight="1">
+    <row r="137" ht="30" customHeight="1">
       <c r="A137" s="35" t="n"/>
-      <c r="B137" s="36" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C137" s="37" t="inlineStr">
+      <c r="B137" s="42" t="inlineStr">
         <is>
           <t>18:10</t>
         </is>
       </c>
-      <c r="D137" s="38" t="inlineStr">
+      <c r="C137" s="43" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="D137" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E137" s="39" t="inlineStr">
-        <is>
-          <t>Caminar de vuelta las seis cuadras a One Vanderbilt (~8-10 min).</t>
-        </is>
-      </c>
-      <c r="F137" s="37" t="inlineStr"/>
+      <c r="E137" s="45" t="inlineStr">
+        <is>
+          <t>★★ SUMMIT ONE VANDERBILT — EL ARCO COMPLETO: entrada 18:10 con luz, el atardecer ~19:21 multiplicado por los espejos infinitos de Kusama, y la noche encendida hasta ~20:15. Ticket ATARDECER $57-63 — es la franja que primero se agota: reservar YA. NO está en ningún pase.</t>
+        </is>
+      </c>
+      <c r="F137" s="43" t="inlineStr">
+        <is>
+          <t>SUMMIT One Vanderbilt</t>
+        </is>
+      </c>
       <c r="G137" s="40" t="inlineStr"/>
       <c r="H137" s="41" t="inlineStr"/>
       <c r="I137" s="41" t="inlineStr"/>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="35" t="n"/>
-      <c r="B138" s="42" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="C138" s="43" t="inlineStr">
+      <c r="B138" s="36" t="inlineStr">
         <is>
           <t>20:20</t>
         </is>
       </c>
-      <c r="D138" s="44" t="inlineStr">
+      <c r="C138" s="37" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="D138" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E138" s="45" t="inlineStr">
-        <is>
-          <t>★★ SUMMIT ONE VANDERBILT — EL ARCO COMPLETO: entrada 18:10 con luz, el atardecer ~19:21 multiplicado por los espejos infinitos de Kusama, y la noche encendida hasta ~20:15. Ticket ATARDECER $57-63 — es la franja que primero se agota: reservar YA. NO está en ningún pase.</t>
-        </is>
-      </c>
-      <c r="F138" s="43" t="inlineStr">
-        <is>
-          <t>SUMMIT One Vanderbilt</t>
-        </is>
-      </c>
+      <c r="E138" s="39" t="inlineStr">
+        <is>
+          <t>Bajar AL VILLAGE PRIMERO y cenar allá: 4/5/6 o 7 hasta 14 St-Union Sq y 1 hasta Christopher St (~25 min). Cenar cerca de Grand Central y bajar después llega justo; hacerlo al revés deja margen.</t>
+        </is>
+      </c>
+      <c r="F138" s="37" t="inlineStr"/>
       <c r="G138" s="40" t="inlineStr"/>
       <c r="H138" s="41" t="inlineStr"/>
       <c r="I138" s="41" t="inlineStr"/>
@@ -26486,12 +26478,12 @@
       <c r="A139" s="35" t="n"/>
       <c r="B139" s="36" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="C139" s="37" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="D139" s="38" t="inlineStr">
@@ -26501,7 +26493,7 @@
       </c>
       <c r="E139" s="39" t="inlineStr">
         <is>
-          <t>Bajar AL VILLAGE PRIMERO y cenar allá: 4/5/6 o 7 hasta 14 St-Union Sq y 1 hasta Christopher St (~25 min). Cenar cerca de Grand Central y bajar después llega justo; hacerlo al revés deja margen.</t>
+          <t>Cena en el West Village, a cinco minutos del club. El Vanguard NO sirve NADA de comida (lo dicen así: 'ni un maní') y no se permite entrar comida: lo que no cenen ahora, no se cena. 40 minutos alcanzan.</t>
         </is>
       </c>
       <c r="F139" s="37" t="inlineStr"/>
@@ -26513,12 +26505,12 @@
       <c r="A140" s="35" t="n"/>
       <c r="B140" s="36" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C140" s="37" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D140" s="38" t="inlineStr">
@@ -26528,7 +26520,7 @@
       </c>
       <c r="E140" s="39" t="inlineStr">
         <is>
-          <t>Cena en el West Village, a cinco minutos del club. El Vanguard NO sirve NADA de comida (lo dicen así: 'ni un maní') y no se permite entrar comida: lo que no cenen ahora, no se cena. 40 minutos alcanzan.</t>
+          <t>EN LA PUERTA DEL VANGUARD a las 21:30 EN PUNTO: el acomodo del segundo set arranca a esa hora y los asientos son POR ORDEN DE LLEGADA — la entrada es General Admission, no numerada. Con 123 asientos, los diez minutos de diferencia son estar frente al piano o contra la columna. El ticket lo dice: el acomodo tardío, con entrada o sin ella, queda a criterio del encargado.</t>
         </is>
       </c>
       <c r="F140" s="37" t="inlineStr"/>
@@ -26538,199 +26530,199 @@
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="35" t="n"/>
-      <c r="B141" s="36" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C141" s="37" t="inlineStr">
+      <c r="B141" s="42" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="D141" s="38" t="inlineStr">
+      <c r="C141" s="43" t="inlineStr"/>
+      <c r="D141" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E141" s="39" t="inlineStr">
-        <is>
-          <t>EN LA PUERTA DEL VANGUARD a las 21:30 EN PUNTO: el acomodo del segundo set arranca a esa hora y los asientos son POR ORDEN DE LLEGADA — la entrada es General Admission, no numerada. Con 123 asientos, los diez minutos de diferencia son estar frente al piano o contra la columna. El ticket lo dice: el acomodo tardío, con entrada o sin ella, queda a criterio del encargado.</t>
-        </is>
-      </c>
-      <c r="F141" s="37" t="inlineStr"/>
+      <c r="E141" s="45" t="inlineStr">
+        <is>
+          <t>★★ VILLAGE VANGUARD — JOHN PATITUCCI TRIO con Chris Potter y Brian Blade, SET DE LAS 22:00. Movido acá desde el martes para que vayan LOS DOS (pedido de Juan). El sótano triangular de 1935, 123 asientos, la acústica que grabó a Coltrane. ✔ ENTRADAS COMPRADAS el 26/8: 2 × General Admission $45 (#18741454 y #18741456), a nombre de Juan Pablo Garicoïts. Falta solo el mínimo de UNA CONSUMICIÓN por cabeza en la mesa (vale gaseosa, jugo o agua) — se paga ahí, aceptan tarjeta.</t>
+        </is>
+      </c>
+      <c r="F141" s="43" t="inlineStr">
+        <is>
+          <t>Village Vanguard</t>
+        </is>
+      </c>
       <c r="G141" s="40" t="inlineStr"/>
       <c r="H141" s="41" t="inlineStr"/>
       <c r="I141" s="41" t="inlineStr"/>
     </row>
-    <row r="142" ht="30" customHeight="1">
-      <c r="A142" s="35" t="n"/>
-      <c r="B142" s="42" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C142" s="43" t="inlineStr"/>
-      <c r="D142" s="44" t="inlineStr">
+    <row r="142" ht="32" customHeight="1">
+      <c r="A142" s="46" t="inlineStr">
+        <is>
+          <t>ALTERNATIVA / OJO:  EL CANJE DE ESTA NOCHE: para meter el Vanguard con Thais, SALIÓ BILL'S PLACE. No hay otra noche donde entre (Bill Saxton toca solo viernes y sábado, y el sábado está tomado por Peter Luger + el play + el Café Wha). Con las entradas ya compradas y sin cambios ni transferencias, el canje quedó CERRADO: Bill's Place sale del viaje. // El Whitney es gratis hoy de 17 a 22h, pero choca con la Morgan y ustedes lo bajaron a 'quizás' mientras que la Morgan quedó en 2. Si igual lo prefieren, el ticket gratis es OBLIGATORIO y el Whitney ahora cierra los martes. SI ALGO SALIERA MAL con el acomodo (llegar tarde y que no haya lugar): Mezzrow o Smalls quedan a cuatro cuadras ($25 con bebida, Smalls tiene jam de madrugada los viernes desde la 1:00), o el Blue Note — el 4 y 5 de septiembre toca Chief Adjuah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="22" customHeight="1">
+      <c r="A144" s="33" t="inlineStr">
+        <is>
+          <t>DÍA 8 · Sábado 05/09 · Brooklyn, Peter Luger, un PLAY y Café Wha hasta la madrugada  —  base: The Beacon  ·  Ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="32" customHeight="1">
+      <c r="A145" s="34" t="inlineStr">
+        <is>
+          <t>La gran noche del viaje, rearmada a pedido: el musical SALIÓ y entraron un PLAY de Broadway a las 19:30 y el CAFÉ WHA a las 23:45 — el sótano del Village donde debutaron Dylan y Hendrix, con reserva gratis ya pedida por Eventbrite. La cena temprana en Peter Luger (17:00) ahora existe exactamente para esto: porterhouse → telón → medianoche de soul y funk. Frankel's sigue afuera (a un porterhouse no se llega con un pastrami encima) y Westlight sigue opcional. ⚠️ La noche termina ~1:15-1:30: el domingo no tiene NADA fijo hasta las 16:00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="30" customHeight="1">
+      <c r="A146" s="35" t="n"/>
+      <c r="B146" s="36" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="C146" s="37" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D146" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E142" s="45" t="inlineStr">
-        <is>
-          <t>★★ VILLAGE VANGUARD — JOHN PATITUCCI TRIO con Chris Potter y Brian Blade, SET DE LAS 22:00. Movido acá desde el martes para que vayan LOS DOS (pedido de Juan). El sótano triangular de 1935, 123 asientos, la acústica que grabó a Coltrane. ✔ ENTRADAS COMPRADAS el 26/8: 2 × General Admission $45 (#18741454 y #18741456), a nombre de Juan Pablo Garicoïts. Falta solo el mínimo de UNA CONSUMICIÓN por cabeza en la mesa (vale gaseosa, jugo o agua) — se paga ahí, aceptan tarjeta.</t>
-        </is>
-      </c>
-      <c r="F142" s="43" t="inlineStr">
-        <is>
-          <t>Village Vanguard</t>
-        </is>
-      </c>
-      <c r="G142" s="40" t="inlineStr"/>
-      <c r="H142" s="41" t="inlineStr"/>
-      <c r="I142" s="41" t="inlineStr"/>
-    </row>
-    <row r="143" ht="32" customHeight="1">
-      <c r="A143" s="46" t="inlineStr">
-        <is>
-          <t>ALTERNATIVA / OJO:  EL CANJE DE ESTA NOCHE: para meter el Vanguard con Thais, SALIÓ BILL'S PLACE. No hay otra noche donde entre (Bill Saxton toca solo viernes y sábado, y el sábado está tomado por Peter Luger + el play + el Café Wha). Con las entradas ya compradas y sin cambios ni transferencias, el canje quedó CERRADO: Bill's Place sale del viaje. // El Whitney es gratis hoy de 17 a 22h, pero choca con la Morgan y ustedes lo bajaron a 'quizás' mientras que la Morgan quedó en 2. Si igual lo prefieren, el ticket gratis es OBLIGATORIO y el Whitney ahora cierra los martes. SI ALGO SALIERA MAL con el acomodo (llegar tarde y que no haya lugar): Mezzrow o Smalls quedan a cuatro cuadras ($25 con bebida, Smalls tiene jam de madrugada los viernes desde la 1:00), o el Blue Note — el 4 y 5 de septiembre toca Chief Adjuah.</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="22" customHeight="1">
-      <c r="A145" s="33" t="inlineStr">
-        <is>
-          <t>DÍA 8 · Sábado 05/09 · Brooklyn, Peter Luger, un PLAY y Café Wha hasta la madrugada  —  base: The Beacon  ·  Ambos</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="32" customHeight="1">
-      <c r="A146" s="34" t="inlineStr">
-        <is>
-          <t>La gran noche del viaje, rearmada a pedido: el musical SALIÓ y entraron un PLAY de Broadway a las 19:30 y el CAFÉ WHA a las 23:45 — el sótano del Village donde debutaron Dylan y Hendrix, con reserva gratis ya pedida por Eventbrite. La cena temprana en Peter Luger (17:00) ahora existe exactamente para esto: porterhouse → telón → medianoche de soul y funk. Frankel's sigue afuera (a un porterhouse no se llega con un pastrami encima) y Westlight sigue opcional. ⚠️ La noche termina ~1:15-1:30: el domingo no tiene NADA fijo hasta las 16:00.</t>
-        </is>
-      </c>
+      <c r="E146" s="39" t="inlineStr">
+        <is>
+          <t>Salir 8:15: 1/2/3 desde 72 St + transbordo a A/C hasta High St son ~40-45 min REALES. Llegar temprano a DUMBO es la diferencia entre la foto y la cola de fotos.</t>
+        </is>
+      </c>
+      <c r="F146" s="37" t="inlineStr"/>
+      <c r="G146" s="40" t="inlineStr"/>
+      <c r="H146" s="41" t="inlineStr"/>
+      <c r="I146" s="41" t="inlineStr"/>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="35" t="n"/>
-      <c r="B147" s="36" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="C147" s="37" t="inlineStr">
+      <c r="B147" s="42" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D147" s="38" t="inlineStr">
+      <c r="C147" s="43" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D147" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E147" s="39" t="inlineStr">
-        <is>
-          <t>Salir 8:15: 1/2/3 desde 72 St + transbordo a A/C hasta High St son ~40-45 min REALES. Llegar temprano a DUMBO es la diferencia entre la foto y la cola de fotos.</t>
-        </is>
-      </c>
-      <c r="F147" s="37" t="inlineStr"/>
+      <c r="E147" s="45" t="inlineStr">
+        <is>
+          <t>★ Brooklyn Bridge Park y DUMBO — muelles reconvertidos con el skyline de Lower Manhattan de frente, y la foto del Manhattan Bridge encuadrado en Washington y Water.</t>
+        </is>
+      </c>
+      <c r="F147" s="43" t="inlineStr">
+        <is>
+          <t>Brooklyn Bridge Park</t>
+        </is>
+      </c>
       <c r="G147" s="40" t="inlineStr"/>
       <c r="H147" s="41" t="inlineStr"/>
       <c r="I147" s="41" t="inlineStr"/>
     </row>
-    <row r="148" ht="30" customHeight="1">
+    <row r="148" ht="16" customHeight="1">
       <c r="A148" s="35" t="n"/>
-      <c r="B148" s="42" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="C148" s="43" t="inlineStr">
+      <c r="B148" s="36" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="D148" s="44" t="inlineStr">
+      <c r="C148" s="37" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="D148" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E148" s="45" t="inlineStr">
-        <is>
-          <t>★ Brooklyn Bridge Park y DUMBO — muelles reconvertidos con el skyline de Lower Manhattan de frente, y la foto del Manhattan Bridge encuadrado en Washington y Water.</t>
-        </is>
-      </c>
-      <c r="F148" s="43" t="inlineStr">
-        <is>
-          <t>Brooklyn Bridge Park</t>
-        </is>
-      </c>
-      <c r="G148" s="40" t="inlineStr"/>
+      <c r="E148" s="39" t="inlineStr">
+        <is>
+          <t>Brooklyn Heights Promenade — la postal clásica del skyline sobre el BQE.</t>
+        </is>
+      </c>
+      <c r="F148" s="37" t="inlineStr">
+        <is>
+          <t>Brooklyn Heights Promenade</t>
+        </is>
+      </c>
+      <c r="G148" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~8 min a pie · 0.6 km · estimado</t>
+        </is>
+      </c>
       <c r="H148" s="41" t="inlineStr"/>
       <c r="I148" s="41" t="inlineStr"/>
     </row>
-    <row r="149" ht="16" customHeight="1">
+    <row r="149" ht="30" customHeight="1">
       <c r="A149" s="35" t="n"/>
-      <c r="B149" s="36" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="C149" s="37" t="inlineStr">
+      <c r="B149" s="42" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="D149" s="38" t="inlineStr">
+      <c r="C149" s="43" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="D149" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E149" s="39" t="inlineStr">
-        <is>
-          <t>Brooklyn Heights Promenade — la postal clásica del skyline sobre el BQE.</t>
-        </is>
-      </c>
-      <c r="F149" s="37" t="inlineStr">
-        <is>
-          <t>Brooklyn Heights Promenade</t>
-        </is>
-      </c>
-      <c r="G149" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~8 min a pie · 0.6 km · estimado</t>
-        </is>
-      </c>
+      <c r="E149" s="45" t="inlineStr">
+        <is>
+          <t>★ NEW YORK TRANSIT MUSEUM — una estación de subte clausurada de 1936 con 20 vagones históricos en las vías originales; se puede subir a todos. $10. Cierra lunes y martes, así que hoy es el día.</t>
+        </is>
+      </c>
+      <c r="F149" s="43" t="inlineStr">
+        <is>
+          <t>New York Transit Museum</t>
+        </is>
+      </c>
+      <c r="G149" s="40" t="inlineStr"/>
       <c r="H149" s="41" t="inlineStr"/>
       <c r="I149" s="41" t="inlineStr"/>
     </row>
-    <row r="150" ht="30" customHeight="1">
+    <row r="150" ht="16" customHeight="1">
       <c r="A150" s="35" t="n"/>
-      <c r="B150" s="42" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="C150" s="43" t="inlineStr">
+      <c r="B150" s="36" t="inlineStr">
         <is>
           <t>12:45</t>
         </is>
       </c>
-      <c r="D150" s="44" t="inlineStr">
+      <c r="C150" s="37" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="D150" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E150" s="45" t="inlineStr">
-        <is>
-          <t>★ NEW YORK TRANSIT MUSEUM — una estación de subte clausurada de 1936 con 20 vagones históricos en las vías originales; se puede subir a todos. $10. Cierra lunes y martes, así que hoy es el día.</t>
-        </is>
-      </c>
-      <c r="F150" s="43" t="inlineStr">
-        <is>
-          <t>New York Transit Museum</t>
-        </is>
-      </c>
+      <c r="E150" s="39" t="inlineStr">
+        <is>
+          <t>Almuerzo en Downtown Brooklyn.</t>
+        </is>
+      </c>
+      <c r="F150" s="37" t="inlineStr"/>
       <c r="G150" s="40" t="inlineStr"/>
       <c r="H150" s="41" t="inlineStr"/>
       <c r="I150" s="41" t="inlineStr"/>
@@ -26739,12 +26731,12 @@
       <c r="A151" s="35" t="n"/>
       <c r="B151" s="36" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C151" s="37" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="D151" s="38" t="inlineStr">
@@ -26754,7 +26746,7 @@
       </c>
       <c r="E151" s="39" t="inlineStr">
         <is>
-          <t>Almuerzo en Downtown Brooklyn.</t>
+          <t>Subte a Williamsburg.</t>
         </is>
       </c>
       <c r="F151" s="37" t="inlineStr"/>
@@ -26762,74 +26754,74 @@
       <c r="H151" s="41" t="inlineStr"/>
       <c r="I151" s="41" t="inlineStr"/>
     </row>
-    <row r="152" ht="16" customHeight="1">
+    <row r="152" ht="30" customHeight="1">
       <c r="A152" s="35" t="n"/>
-      <c r="B152" s="36" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="C152" s="37" t="inlineStr">
+      <c r="B152" s="42" t="inlineStr">
         <is>
           <t>14:15</t>
         </is>
       </c>
-      <c r="D152" s="38" t="inlineStr">
+      <c r="C152" s="43" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="D152" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E152" s="39" t="inlineStr">
-        <is>
-          <t>Subte a Williamsburg.</t>
-        </is>
-      </c>
-      <c r="F152" s="37" t="inlineStr"/>
+      <c r="E152" s="45" t="inlineStr">
+        <is>
+          <t>★ Domino Park — ex refinería de azúcar; el paseo elevado pasa entre la maquinaria industrial conservada, con el Williamsburg Bridge y Midtown enfrente.</t>
+        </is>
+      </c>
+      <c r="F152" s="43" t="inlineStr">
+        <is>
+          <t>Domino Park</t>
+        </is>
+      </c>
       <c r="G152" s="40" t="inlineStr"/>
       <c r="H152" s="41" t="inlineStr"/>
       <c r="I152" s="41" t="inlineStr"/>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="35" t="n"/>
-      <c r="B153" s="42" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="C153" s="43" t="inlineStr">
+      <c r="B153" s="36" t="inlineStr">
         <is>
           <t>15:15</t>
         </is>
       </c>
-      <c r="D153" s="44" t="inlineStr">
+      <c r="C153" s="37" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="D153" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E153" s="45" t="inlineStr">
-        <is>
-          <t>★ Domino Park — ex refinería de azúcar; el paseo elevado pasa entre la maquinaria industrial conservada, con el Williamsburg Bridge y Midtown enfrente.</t>
-        </is>
-      </c>
-      <c r="F153" s="43" t="inlineStr">
-        <is>
-          <t>Domino Park</t>
-        </is>
-      </c>
+      <c r="E153" s="39" t="inlineStr">
+        <is>
+          <t>Paseo por Williamsburg: Bedford Ave, disquerías y vintage. OPCIONAL si quieren la panorámica: Westlight (piso 22, sin cover, un trago) — lo bajaron a 'quizás', así que es prescindible. NO comer nada: lo que viene lo merece.</t>
+        </is>
+      </c>
+      <c r="F153" s="37" t="inlineStr"/>
       <c r="G153" s="40" t="inlineStr"/>
       <c r="H153" s="41" t="inlineStr"/>
       <c r="I153" s="41" t="inlineStr"/>
     </row>
-    <row r="154" ht="30" customHeight="1">
+    <row r="154" ht="16" customHeight="1">
       <c r="A154" s="35" t="n"/>
       <c r="B154" s="36" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C154" s="37" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D154" s="38" t="inlineStr">
@@ -26839,7 +26831,7 @@
       </c>
       <c r="E154" s="39" t="inlineStr">
         <is>
-          <t>Paseo por Williamsburg: Bedford Ave, disquerías y vintage. OPCIONAL si quieren la panorámica: Westlight (piso 22, sin cover, un trago) — lo bajaron a 'quizás', así que es prescindible. NO comer nada: lo que viene lo merece.</t>
+          <t>Caminar por Bedford/Driggs hasta el pie del Williamsburg Bridge (~15 min).</t>
         </is>
       </c>
       <c r="F154" s="37" t="inlineStr"/>
@@ -26847,132 +26839,132 @@
       <c r="H154" s="41" t="inlineStr"/>
       <c r="I154" s="41" t="inlineStr"/>
     </row>
-    <row r="155" ht="16" customHeight="1">
+    <row r="155" ht="30" customHeight="1">
       <c r="A155" s="35" t="n"/>
-      <c r="B155" s="36" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="C155" s="37" t="inlineStr">
+      <c r="B155" s="42" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D155" s="38" t="inlineStr">
+      <c r="C155" s="43" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="D155" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E155" s="39" t="inlineStr">
-        <is>
-          <t>Caminar por Bedford/Driggs hasta el pie del Williamsburg Bridge (~15 min).</t>
-        </is>
-      </c>
-      <c r="F155" s="37" t="inlineStr"/>
+      <c r="E155" s="45" t="inlineStr">
+        <is>
+          <t>★★ PETER LUGER (178 Broadway) — el porterhouse for two de 1887, dry-aged en el sótano, con la tocineta gruesa de entrada. ~$160-200 los dos con sides y propina. ⚠️ SIN TARJETAS DE CRÉDITO: efectivo, débito US o cheque — llevar cash. Cena temprana a propósito: el teatro espera. RESERVA EN RESY YA.</t>
+        </is>
+      </c>
+      <c r="F155" s="43" t="inlineStr">
+        <is>
+          <t>Peter Luger Steak House</t>
+        </is>
+      </c>
       <c r="G155" s="40" t="inlineStr"/>
       <c r="H155" s="41" t="inlineStr"/>
       <c r="I155" s="41" t="inlineStr"/>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="35" t="n"/>
-      <c r="B156" s="42" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C156" s="43" t="inlineStr">
+      <c r="B156" s="36" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="D156" s="44" t="inlineStr">
+      <c r="C156" s="37" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="D156" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E156" s="45" t="inlineStr">
-        <is>
-          <t>★★ PETER LUGER (178 Broadway) — el porterhouse for two de 1887, dry-aged en el sótano, con la tocineta gruesa de entrada. ~$160-200 los dos con sides y propina. ⚠️ SIN TARJETAS DE CRÉDITO: efectivo, débito US o cheque — llevar cash. Cena temprana a propósito: el teatro espera. RESERVA EN RESY YA.</t>
-        </is>
-      </c>
-      <c r="F156" s="43" t="inlineStr">
-        <is>
-          <t>Peter Luger Steak House</t>
-        </is>
-      </c>
+      <c r="E156" s="39" t="inlineStr">
+        <is>
+          <t>A la zona de teatros: subte J desde Marcy Av hasta Essex St y F hasta 42 St-Bryant Park (~35 min con transbordo), o directamente Uber al teatro (~20-25 min, $25-35 — un sábado a la noche el puente puede estar cargado).</t>
+        </is>
+      </c>
+      <c r="F156" s="37" t="inlineStr"/>
       <c r="G156" s="40" t="inlineStr"/>
       <c r="H156" s="41" t="inlineStr"/>
       <c r="I156" s="41" t="inlineStr"/>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="35" t="n"/>
-      <c r="B157" s="36" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="C157" s="37" t="inlineStr">
+      <c r="B157" s="42" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D157" s="38" t="inlineStr">
+      <c r="C157" s="43" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="D157" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E157" s="39" t="inlineStr">
-        <is>
-          <t>A la zona de teatros: subte J desde Marcy Av hasta Essex St y F hasta 42 St-Bryant Park (~35 min con transbordo), o directamente Uber al teatro (~20-25 min, $25-35 — un sábado a la noche el puente puede estar cargado).</t>
-        </is>
-      </c>
-      <c r="F157" s="37" t="inlineStr"/>
+      <c r="E157" s="45" t="inlineStr">
+        <is>
+          <t>★★ PLAY DE BROADWAY — mi recomendación: STRANGER THINGS: THE FIRST SHADOW (Marquis, desde ~$76): la maquinaria escénica que ganó el Tony — para quien viene de Mercer Labs, el mismo músculo llevado al teatro. Alternativas esa semana: Harry Potter and the Cursed Child, Paranormal Activity, The Imaginary Invalid. COMPRA FIRME esta semana y verificar el horario real de la función (19:00/19:30/20:00): tiene que terminar ~22:00 para lo que sigue.</t>
+        </is>
+      </c>
+      <c r="F157" s="43" t="inlineStr">
+        <is>
+          <t>Stranger Things: The First Shadow (play)</t>
+        </is>
+      </c>
       <c r="G157" s="40" t="inlineStr"/>
       <c r="H157" s="41" t="inlineStr"/>
       <c r="I157" s="41" t="inlineStr"/>
     </row>
-    <row r="158" ht="30" customHeight="1">
+    <row r="158" ht="16" customHeight="1">
       <c r="A158" s="35" t="n"/>
-      <c r="B158" s="42" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C158" s="43" t="inlineStr">
+      <c r="B158" s="36" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="D158" s="44" t="inlineStr">
+      <c r="C158" s="37" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="D158" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E158" s="45" t="inlineStr">
-        <is>
-          <t>★★ PLAY DE BROADWAY — mi recomendación: STRANGER THINGS: THE FIRST SHADOW (Marquis, desde ~$76): la maquinaria escénica que ganó el Tony — para quien viene de Mercer Labs, el mismo músculo llevado al teatro. Alternativas esa semana: Harry Potter and the Cursed Child, Paranormal Activity, The Imaginary Invalid. COMPRA FIRME esta semana y verificar el horario real de la función (19:00/19:30/20:00): tiene que terminar ~22:00 para lo que sigue.</t>
-        </is>
-      </c>
-      <c r="F158" s="43" t="inlineStr">
-        <is>
-          <t>Stranger Things: The First Shadow (play)</t>
-        </is>
-      </c>
+      <c r="E158" s="39" t="inlineStr">
+        <is>
+          <t>Subte 1 desde Times Sq hasta Christopher St (~15 min) y caminar al corazón del Village.</t>
+        </is>
+      </c>
+      <c r="F158" s="37" t="inlineStr"/>
       <c r="G158" s="40" t="inlineStr"/>
       <c r="H158" s="41" t="inlineStr"/>
       <c r="I158" s="41" t="inlineStr"/>
     </row>
-    <row r="159" ht="16" customHeight="1">
+    <row r="159" ht="30" customHeight="1">
       <c r="A159" s="35" t="n"/>
       <c r="B159" s="36" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C159" s="37" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D159" s="38" t="inlineStr">
@@ -26982,7 +26974,7 @@
       </c>
       <c r="E159" s="39" t="inlineStr">
         <is>
-          <t>Subte 1 desde Times Sq hasta Christopher St (~15 min) y caminar al corazón del Village.</t>
+          <t>Paseo sin apuro por Bleecker y MacDougal — la esquina folk de los 60s de noche, un café o un trago corto. El único objetivo real: estar en la puerta del Wha a las 23:10.</t>
         </is>
       </c>
       <c r="F159" s="37" t="inlineStr"/>
@@ -26992,102 +26984,106 @@
     </row>
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="35" t="n"/>
-      <c r="B160" s="36" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C160" s="37" t="inlineStr">
+      <c r="B160" s="42" t="inlineStr">
         <is>
           <t>23:15</t>
         </is>
       </c>
-      <c r="D160" s="38" t="inlineStr">
+      <c r="C160" s="43" t="inlineStr"/>
+      <c r="D160" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E160" s="39" t="inlineStr">
-        <is>
-          <t>Paseo sin apuro por Bleecker y MacDougal — la esquina folk de los 60s de noche, un café o un trago corto. El único objetivo real: estar en la puerta del Wha a las 23:10.</t>
-        </is>
-      </c>
-      <c r="F160" s="37" t="inlineStr"/>
+      <c r="E160" s="45" t="inlineStr">
+        <is>
+          <t>★★ CAFÉ WHA — LLEGAR 23:10-23:15: la reserva de Eventbrite NO garantiza admisión y a las 23:30 EN PUNTO liberan los asientos vacíos al standby. TODOS los de la reserva presentes. Set 2 de la house band 23:45-~1:15: soul y funk a máquina en el sótano donde debutaron Dylan, Hendrix y Springsteen. $20 por cabeza van a la cuenta + consumo. Vuelta: subte 1 Christopher St → 72 St (~25 min) o taxi.</t>
+        </is>
+      </c>
+      <c r="F160" s="43" t="inlineStr">
+        <is>
+          <t>Cafe Wha?</t>
+        </is>
+      </c>
       <c r="G160" s="40" t="inlineStr"/>
       <c r="H160" s="41" t="inlineStr"/>
       <c r="I160" s="41" t="inlineStr"/>
     </row>
-    <row r="161" ht="30" customHeight="1">
-      <c r="A161" s="35" t="n"/>
-      <c r="B161" s="42" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C161" s="43" t="inlineStr"/>
-      <c r="D161" s="44" t="inlineStr">
+    <row r="161" ht="32" customHeight="1">
+      <c r="A161" s="46" t="inlineStr">
+        <is>
+          <t>ALTERNATIVA / OJO:  SOBRE PETER LUGER: la mesa de las 17:00 es la realista — y ahora es la única que funciona: el play manda. PLAN B si no hay mesa: correr Peter Luger al ALMUERZO del mismo día (12:45). // SI EL CANSANCIO GANA A LAS 22:00: el Café Wha es la pieza sacrificable — la reserva es gratis y no penaliza no ir; el play, pagado, no. // Sigue afuera: Bar LunÀtico y Barbès (Bed-Stuy/Park Slope), sin noche posible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="22" customHeight="1">
+      <c r="A163" s="33" t="inlineStr">
+        <is>
+          <t>DÍA 9 · Domingo 06/09 · Checkout, Central Park, Roosevelt Island y vuelo  —  base: The Beacon (checkout) → EWR  ·  Ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="32" customHeight="1">
+      <c r="A164" s="34" t="inlineStr">
+        <is>
+          <t>El día arranca con el CHECKOUT de The Beacon: hacerlo temprano y dejar las valijas en el bell desk libera el día entero. El vuelo sale 23:40, así que hay margen — pero es el domingo del fin de semana largo de Labor Day, la noche de mayor tráfico del año, y EWR va a estar cargado. Por eso todo queda dentro del eje Central Park - Upper East Side, a diez minutos de subte del hotel, y se sale con 2h45 de anticipación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="30" customHeight="1">
+      <c r="A165" s="35" t="n"/>
+      <c r="B165" s="36" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C165" s="37" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="D165" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E161" s="45" t="inlineStr">
-        <is>
-          <t>★★ CAFÉ WHA — LLEGAR 23:10-23:15: la reserva de Eventbrite NO garantiza admisión y a las 23:30 EN PUNTO liberan los asientos vacíos al standby. TODOS los de la reserva presentes. Set 2 de la house band 23:45-~1:15: soul y funk a máquina en el sótano donde debutaron Dylan, Hendrix y Springsteen. $20 por cabeza van a la cuenta + consumo. Vuelta: subte 1 Christopher St → 72 St (~25 min) o taxi.</t>
-        </is>
-      </c>
-      <c r="F161" s="43" t="inlineStr">
-        <is>
-          <t>Cafe Wha?</t>
-        </is>
-      </c>
-      <c r="G161" s="40" t="inlineStr"/>
-      <c r="H161" s="41" t="inlineStr"/>
-      <c r="I161" s="41" t="inlineStr"/>
-    </row>
-    <row r="162" ht="32" customHeight="1">
-      <c r="A162" s="46" t="inlineStr">
-        <is>
-          <t>ALTERNATIVA / OJO:  SOBRE PETER LUGER: la mesa de las 17:00 es la realista — y ahora es la única que funciona: el play manda. PLAN B si no hay mesa: correr Peter Luger al ALMUERZO del mismo día (12:45). // SI EL CANSANCIO GANA A LAS 22:00: el Café Wha es la pieza sacrificable — la reserva es gratis y no penaliza no ir; el play, pagado, no. // Sigue afuera: Bar LunÀtico y Barbès (Bed-Stuy/Park Slope), sin noche posible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="22" customHeight="1">
-      <c r="A164" s="33" t="inlineStr">
-        <is>
-          <t>DÍA 9 · Domingo 06/09 · Checkout, Central Park, Roosevelt Island y vuelo  —  base: The Beacon (checkout) → EWR  ·  Ambos</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="32" customHeight="1">
-      <c r="A165" s="34" t="inlineStr">
-        <is>
-          <t>El día arranca con el CHECKOUT de The Beacon: hacerlo temprano y dejar las valijas en el bell desk libera el día entero. El vuelo sale 23:40, así que hay margen — pero es el domingo del fin de semana largo de Labor Day, la noche de mayor tráfico del año, y EWR va a estar cargado. Por eso todo queda dentro del eje Central Park - Upper East Side, a diez minutos de subte del hotel, y se sale con 2h45 de anticipación.</t>
-        </is>
-      </c>
+      <c r="E165" s="39" t="inlineStr">
+        <is>
+          <t>Desayuno SIN despertador temprano: anoche terminó ~1:30 en el Village y lo único con hora fija hoy es el Guggenheim a las 16:00. Dormir un poco más está permitido.</t>
+        </is>
+      </c>
+      <c r="F165" s="37" t="inlineStr"/>
+      <c r="G165" s="40" t="inlineStr"/>
+      <c r="H165" s="41" t="inlineStr"/>
+      <c r="I165" s="41" t="inlineStr"/>
     </row>
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="35" t="n"/>
-      <c r="B166" s="36" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="C166" s="37" t="inlineStr">
+      <c r="B166" s="42" t="inlineStr">
         <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="D166" s="38" t="inlineStr">
+      <c r="C166" s="43" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="D166" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E166" s="39" t="inlineStr">
-        <is>
-          <t>Desayuno SIN despertador temprano: anoche terminó ~1:30 en el Village y lo único con hora fija hoy es el Guggenheim a las 16:00. Dormir un poco más está permitido.</t>
-        </is>
-      </c>
-      <c r="F166" s="37" t="inlineStr"/>
+      <c r="E166" s="45" t="inlineStr">
+        <is>
+          <t>★ CHECKOUT de The Beacon y dejar las valijas en el bell desk. El checkout formal suele ser 11:00-12:00, pero hacerlo antes libera el día.</t>
+        </is>
+      </c>
+      <c r="F166" s="43" t="inlineStr">
+        <is>
+          <t>Hotel The Beacon (3-6 sep)</t>
+        </is>
+      </c>
       <c r="G166" s="40" t="inlineStr"/>
       <c r="H166" s="41" t="inlineStr"/>
       <c r="I166" s="41" t="inlineStr"/>
@@ -27096,12 +27092,12 @@
       <c r="A167" s="35" t="n"/>
       <c r="B167" s="42" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C167" s="43" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="D167" s="44" t="inlineStr">
@@ -27111,63 +27107,59 @@
       </c>
       <c r="E167" s="45" t="inlineStr">
         <is>
-          <t>★ CHECKOUT de The Beacon y dejar las valijas en el bell desk. El checkout formal suele ser 11:00-12:00, pero hacerlo antes libera el día.</t>
+          <t>★ CENTRAL PARK cruzando de oeste a este: Bethesda Terrace, el Ramble, Bow Bridge. Se entra por la 72 desde Broadway, a tres cuadras del hotel.</t>
         </is>
       </c>
       <c r="F167" s="43" t="inlineStr">
         <is>
-          <t>Hotel The Beacon (3-6 sep)</t>
-        </is>
-      </c>
-      <c r="G167" s="40" t="inlineStr"/>
+          <t>Central Park</t>
+        </is>
+      </c>
+      <c r="G167" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~20 min a pie (1.5 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H167" s="41" t="inlineStr"/>
       <c r="I167" s="41" t="inlineStr"/>
     </row>
-    <row r="168" ht="30" customHeight="1">
+    <row r="168" ht="16" customHeight="1">
       <c r="A168" s="35" t="n"/>
-      <c r="B168" s="42" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="C168" s="43" t="inlineStr">
+      <c r="B168" s="36" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="D168" s="44" t="inlineStr">
+      <c r="C168" s="37" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="D168" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E168" s="45" t="inlineStr">
-        <is>
-          <t>★ CENTRAL PARK cruzando de oeste a este: Bethesda Terrace, el Ramble, Bow Bridge. Se entra por la 72 desde Broadway, a tres cuadras del hotel.</t>
-        </is>
-      </c>
-      <c r="F168" s="43" t="inlineStr">
-        <is>
-          <t>Central Park</t>
-        </is>
-      </c>
-      <c r="G168" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~20 min a pie (1.5 km) o 🚇 ~15 min · estimado</t>
-        </is>
-      </c>
+      <c r="E168" s="39" t="inlineStr">
+        <is>
+          <t>Almuerzo en el Upper East Side, saliendo del parque por la Quinta.</t>
+        </is>
+      </c>
+      <c r="F168" s="37" t="inlineStr"/>
+      <c r="G168" s="40" t="inlineStr"/>
       <c r="H168" s="41" t="inlineStr"/>
       <c r="I168" s="41" t="inlineStr"/>
     </row>
-    <row r="169" ht="16" customHeight="1">
+    <row r="169" ht="30" customHeight="1">
       <c r="A169" s="35" t="n"/>
       <c r="B169" s="36" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C169" s="37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="D169" s="38" t="inlineStr">
@@ -27177,7 +27169,7 @@
       </c>
       <c r="E169" s="39" t="inlineStr">
         <is>
-          <t>Almuerzo en el Upper East Side, saliendo del parque por la Quinta.</t>
+          <t>Bajar a 59 St y 2ª Av: subte 6 desde 68 St-Hunter College (el 4/5 exprés NO para ahí), o caminando por la Quinta si el día está lindo.</t>
         </is>
       </c>
       <c r="F169" s="37" t="inlineStr"/>
@@ -27187,56 +27179,60 @@
     </row>
     <row r="170" ht="30" customHeight="1">
       <c r="A170" s="35" t="n"/>
-      <c r="B170" s="36" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C170" s="37" t="inlineStr">
+      <c r="B170" s="42" t="inlineStr">
         <is>
           <t>13:50</t>
         </is>
       </c>
-      <c r="D170" s="38" t="inlineStr">
+      <c r="C170" s="43" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="D170" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E170" s="39" t="inlineStr">
-        <is>
-          <t>Bajar a 59 St y 2ª Av: subte 6 desde 68 St-Hunter College (el 4/5 exprés NO para ahí), o caminando por la Quinta si el día está lindo.</t>
-        </is>
-      </c>
-      <c r="F170" s="37" t="inlineStr"/>
+      <c r="E170" s="45" t="inlineStr">
+        <is>
+          <t>★ ROOSEVELT ISLAND TRAMWAY ($3, OMNY) — cruza el East River a 76 metros de altura con el Queensboro Bridge al lado. Es la vista de $50 por el precio de un viaje de subte.</t>
+        </is>
+      </c>
+      <c r="F170" s="43" t="inlineStr">
+        <is>
+          <t>Roosevelt Island Tramway</t>
+        </is>
+      </c>
       <c r="G170" s="40" t="inlineStr"/>
       <c r="H170" s="41" t="inlineStr"/>
       <c r="I170" s="41" t="inlineStr"/>
     </row>
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="35" t="n"/>
-      <c r="B171" s="42" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="C171" s="43" t="inlineStr">
+      <c r="B171" s="36" t="inlineStr">
         <is>
           <t>14:25</t>
         </is>
       </c>
-      <c r="D171" s="44" t="inlineStr">
+      <c r="C171" s="37" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="D171" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E171" s="45" t="inlineStr">
-        <is>
-          <t>★ ROOSEVELT ISLAND TRAMWAY ($3, OMNY) — cruza el East River a 76 metros de altura con el Queensboro Bridge al lado. Es la vista de $50 por el precio de un viaje de subte.</t>
-        </is>
-      </c>
-      <c r="F171" s="43" t="inlineStr">
-        <is>
-          <t>Roosevelt Island Tramway</t>
+      <c r="E171" s="39" t="inlineStr">
+        <is>
+          <t>FDR Four Freedoms Park — del teleférico son ~20 min a pie por el borde del río. La última obra de Louis Kahn: granito, plátanos y una sala abierta al río apuntando a Manhattan. Gratis y vacía. Se pasa por las ruinas del Smallpox Hospital.</t>
+        </is>
+      </c>
+      <c r="F171" s="37" t="inlineStr">
+        <is>
+          <t>FDR Four Freedoms Park</t>
         </is>
       </c>
       <c r="G171" s="40" t="inlineStr"/>
@@ -27247,12 +27243,12 @@
       <c r="A172" s="35" t="n"/>
       <c r="B172" s="36" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="C172" s="37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D172" s="38" t="inlineStr">
@@ -27262,70 +27258,70 @@
       </c>
       <c r="E172" s="39" t="inlineStr">
         <is>
-          <t>FDR Four Freedoms Park — del teleférico son ~20 min a pie por el borde del río. La última obra de Louis Kahn: granito, plátanos y una sala abierta al río apuntando a Manhattan. Gratis y vacía. Se pasa por las ruinas del Smallpox Hospital.</t>
-        </is>
-      </c>
-      <c r="F172" s="37" t="inlineStr">
-        <is>
-          <t>FDR Four Freedoms Park</t>
-        </is>
-      </c>
+          <t>SALIR 15:05 (no más tarde): caminata al teleférico + cruce + subte 4/5/6 de 59 St a 86 St suman ~50 min, y la ventana pay-what-you-wish del Guggenheim arranca 16:00 y el museo cierra 17:30 — llegar puntuales ES la visita.</t>
+        </is>
+      </c>
+      <c r="F172" s="37" t="inlineStr"/>
       <c r="G172" s="40" t="inlineStr"/>
       <c r="H172" s="41" t="inlineStr"/>
       <c r="I172" s="41" t="inlineStr"/>
     </row>
     <row r="173" ht="30" customHeight="1">
       <c r="A173" s="35" t="n"/>
-      <c r="B173" s="36" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="C173" s="37" t="inlineStr">
+      <c r="B173" s="42" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D173" s="38" t="inlineStr">
+      <c r="C173" s="43" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="D173" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E173" s="39" t="inlineStr">
-        <is>
-          <t>SALIR 15:05 (no más tarde): caminata al teleférico + cruce + subte 4/5/6 de 59 St a 86 St suman ~50 min, y la ventana pay-what-you-wish del Guggenheim arranca 16:00 y el museo cierra 17:30 — llegar puntuales ES la visita.</t>
-        </is>
-      </c>
-      <c r="F173" s="37" t="inlineStr"/>
+      <c r="E173" s="45" t="inlineStr">
+        <is>
+          <t>★ GUGGENHEIM — pay-what-you-wish domingos 16:00-17:30 (sugerido $10, mínimo $1). El edificio de Frank Lloyd Wright vale la visita solo: se sube en ascensor y se baja caminando la rampa. ⚠️ LLAMAR ANTES: la rotonda estaría en montaje hasta el 18 de septiembre y el pay-what-you-wish no está confirmado en fuente oficial.</t>
+        </is>
+      </c>
+      <c r="F173" s="43" t="inlineStr">
+        <is>
+          <t>Guggenheim</t>
+        </is>
+      </c>
       <c r="G173" s="40" t="inlineStr"/>
       <c r="H173" s="41" t="inlineStr"/>
       <c r="I173" s="41" t="inlineStr"/>
     </row>
-    <row r="174" ht="30" customHeight="1">
+    <row r="174" ht="16" customHeight="1">
       <c r="A174" s="35" t="n"/>
-      <c r="B174" s="42" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C174" s="43" t="inlineStr">
+      <c r="B174" s="36" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="D174" s="44" t="inlineStr">
+      <c r="C174" s="37" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D174" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E174" s="45" t="inlineStr">
-        <is>
-          <t>★ GUGGENHEIM — pay-what-you-wish domingos 16:00-17:30 (sugerido $10, mínimo $1). El edificio de Frank Lloyd Wright vale la visita solo: se sube en ascensor y se baja caminando la rampa. ⚠️ LLAMAR ANTES: la rotonda estaría en montaje hasta el 18 de septiembre y el pay-what-you-wish no está confirmado en fuente oficial.</t>
-        </is>
-      </c>
-      <c r="F174" s="43" t="inlineStr">
-        <is>
-          <t>Guggenheim</t>
+      <c r="E174" s="39" t="inlineStr">
+        <is>
+          <t>Volver caminando por Central Park hasta el hotel (~25 min) o subte 86 St → 1 a 79 St.</t>
+        </is>
+      </c>
+      <c r="F174" s="37" t="inlineStr">
+        <is>
+          <t>Hotel The Beacon (3-6 sep)</t>
         </is>
       </c>
       <c r="G174" s="40" t="inlineStr"/>
@@ -27336,12 +27332,12 @@
       <c r="A175" s="35" t="n"/>
       <c r="B175" s="36" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C175" s="37" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="D175" s="38" t="inlineStr">
@@ -27351,14 +27347,10 @@
       </c>
       <c r="E175" s="39" t="inlineStr">
         <is>
-          <t>Volver caminando por Central Park hasta el hotel (~25 min) o subte 86 St → 1 a 79 St.</t>
-        </is>
-      </c>
-      <c r="F175" s="37" t="inlineStr">
-        <is>
-          <t>Hotel The Beacon (3-6 sep)</t>
-        </is>
-      </c>
+          <t>Retirar las valijas del bell desk. Cena tranquila cerca del hotel: es la última.</t>
+        </is>
+      </c>
+      <c r="F175" s="37" t="inlineStr"/>
       <c r="G175" s="40" t="inlineStr"/>
       <c r="H175" s="41" t="inlineStr"/>
       <c r="I175" s="41" t="inlineStr"/>
@@ -27367,12 +27359,12 @@
       <c r="A176" s="35" t="n"/>
       <c r="B176" s="36" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="C176" s="37" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="D176" s="38" t="inlineStr">
@@ -27382,7 +27374,7 @@
       </c>
       <c r="E176" s="39" t="inlineStr">
         <is>
-          <t>Retirar las valijas del bell desk. Cena tranquila cerca del hotel: es la última.</t>
+          <t>Salir de The Beacon. Subte 1/2/3 desde 72 St hasta 34 St-Penn Station: ~10 min, $3.</t>
         </is>
       </c>
       <c r="F176" s="37" t="inlineStr"/>
@@ -27390,16 +27382,16 @@
       <c r="H176" s="41" t="inlineStr"/>
       <c r="I176" s="41" t="inlineStr"/>
     </row>
-    <row r="177" ht="16" customHeight="1">
+    <row r="177" ht="30" customHeight="1">
       <c r="A177" s="35" t="n"/>
       <c r="B177" s="36" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="C177" s="37" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="D177" s="38" t="inlineStr">
@@ -27409,7 +27401,7 @@
       </c>
       <c r="E177" s="39" t="inlineStr">
         <is>
-          <t>Salir de The Beacon. Subte 1/2/3 desde 72 St hasta 34 St-Penn Station: ~10 min, $3.</t>
+          <t>NJ Transit Penn Station → EWR, llega 20:38. $17,25 (incluye el AirTrain). VERIFICAR el horario dominical en njtransit.com unos días antes.</t>
         </is>
       </c>
       <c r="F177" s="37" t="inlineStr"/>
@@ -27417,16 +27409,16 @@
       <c r="H177" s="41" t="inlineStr"/>
       <c r="I177" s="41" t="inlineStr"/>
     </row>
-    <row r="178" ht="30" customHeight="1">
+    <row r="178" ht="16" customHeight="1">
       <c r="A178" s="35" t="n"/>
       <c r="B178" s="36" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="C178" s="37" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="D178" s="38" t="inlineStr">
@@ -27436,7 +27428,7 @@
       </c>
       <c r="E178" s="39" t="inlineStr">
         <is>
-          <t>NJ Transit Penn Station → EWR, llega 20:38. $17,25 (incluye el AirTrain). VERIFICAR el horario dominical en njtransit.com unos días antes.</t>
+          <t>AirTrain hasta la terminal: 10-15 min.</t>
         </is>
       </c>
       <c r="F178" s="37" t="inlineStr"/>
@@ -27444,18 +27436,14 @@
       <c r="H178" s="41" t="inlineStr"/>
       <c r="I178" s="41" t="inlineStr"/>
     </row>
-    <row r="179" ht="16" customHeight="1">
+    <row r="179" ht="30" customHeight="1">
       <c r="A179" s="35" t="n"/>
       <c r="B179" s="36" t="inlineStr">
         <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C179" s="37" t="inlineStr">
-        <is>
           <t>20:55</t>
         </is>
       </c>
+      <c r="C179" s="37" t="inlineStr"/>
       <c r="D179" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -27463,7 +27451,7 @@
       </c>
       <c r="E179" s="39" t="inlineStr">
         <is>
-          <t>AirTrain hasta la terminal: 10-15 min.</t>
+          <t>En terminal. Faltan 2h45 para el vuelo de las 23:40 — correcto para un internacional en el domingo de Labor Day, que es la noche de más tráfico del año en EWR.</t>
         </is>
       </c>
       <c r="F179" s="37" t="inlineStr"/>
@@ -27471,31 +27459,8 @@
       <c r="H179" s="41" t="inlineStr"/>
       <c r="I179" s="41" t="inlineStr"/>
     </row>
-    <row r="180" ht="30" customHeight="1">
-      <c r="A180" s="35" t="n"/>
-      <c r="B180" s="36" t="inlineStr">
-        <is>
-          <t>20:55</t>
-        </is>
-      </c>
-      <c r="C180" s="37" t="inlineStr"/>
-      <c r="D180" s="38" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="E180" s="39" t="inlineStr">
-        <is>
-          <t>En terminal. Faltan 2h45 para el vuelo de las 23:40 — correcto para un internacional en el domingo de Labor Day, que es la noche de más tráfico del año en EWR.</t>
-        </is>
-      </c>
-      <c r="F180" s="37" t="inlineStr"/>
-      <c r="G180" s="40" t="inlineStr"/>
-      <c r="H180" s="41" t="inlineStr"/>
-      <c r="I180" s="41" t="inlineStr"/>
-    </row>
-    <row r="181" ht="32" customHeight="1">
-      <c r="A181" s="46" t="inlineStr">
+    <row r="180" ht="32" customHeight="1">
+      <c r="A180" s="46" t="inlineStr">
         <is>
           <t>ALTERNATIVA / OJO:  COLCHÓN: si algo se atrasa, el tren siguiente sale 20:55 y llega a EWR 21:16, o sea terminal ~21:35 y 2h05 antes del vuelo. Es el último que yo tomaría. // Si prefieren un último día sin moverse, salteen el teleférico y estiren Central Park hasta el Guggenheim: el parque solo da para toda la mañana y la tarde. Y si el Guggenheim tiene la rotonda cerrada, el Whitney abre los domingos. Lo que NO conviene hoy es meter algo nuevo y grande.</t>
         </is>
@@ -27510,31 +27475,31 @@
     <mergeCell ref="A46:I46"/>
     <mergeCell ref="A27:I27"/>
     <mergeCell ref="A145:I145"/>
+    <mergeCell ref="A163:I163"/>
     <mergeCell ref="A101:I101"/>
     <mergeCell ref="A86:I86"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A85:I85"/>
-    <mergeCell ref="A181:I181"/>
     <mergeCell ref="A126:I126"/>
+    <mergeCell ref="A144:I144"/>
     <mergeCell ref="A125:I125"/>
-    <mergeCell ref="A165:I165"/>
+    <mergeCell ref="A180:I180"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A68:I68"/>
     <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A161:I161"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="A102:I102"/>
     <mergeCell ref="A67:I67"/>
     <mergeCell ref="A83:I83"/>
-    <mergeCell ref="A143:I143"/>
+    <mergeCell ref="A142:I142"/>
     <mergeCell ref="A123:I123"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A146:I146"/>
-    <mergeCell ref="A162:I162"/>
     <mergeCell ref="A6:I6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H182" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,Reservado,Confirmado,Descartado"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NYC_2026_Planificador.xlsx
+++ b/NYC_2026_Planificador.xlsx
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" s="13">
         <f>IF(AND(F6=2,G6=2),"AMBOS",IF(AND(F6=2,G6&lt;2),"solo JP",IF(AND(F6&lt;2,G6=2),"solo Thais","-")))</f>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>1</v>
@@ -3684,7 +3684,11 @@
           <t>otros</t>
         </is>
       </c>
-      <c r="V21" s="20" t="inlineStr"/>
+      <c r="V21" s="20" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="46" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
@@ -7965,7 +7969,11 @@
           <t>lista google</t>
         </is>
       </c>
-      <c r="V64" s="20" t="inlineStr"/>
+      <c r="V64" s="20" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="46" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
@@ -12627,10 +12635,10 @@
         </is>
       </c>
       <c r="F112" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" s="13">
         <f>IF(AND(F112=2,G112=2),"AMBOS",IF(AND(F112=2,G112&lt;2),"solo JP",IF(AND(F112&lt;2,G112=2),"solo Thais","-")))</f>
@@ -14900,10 +14908,10 @@
         </is>
       </c>
       <c r="F135" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H135" s="13">
         <f>IF(AND(F135=2,G135=2),"AMBOS",IF(AND(F135=2,G135&lt;2),"solo JP",IF(AND(F135&lt;2,G135=2),"solo Thais","-")))</f>
@@ -14999,10 +15007,10 @@
         </is>
       </c>
       <c r="F136" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H136" s="13">
         <f>IF(AND(F136=2,G136=2),"AMBOS",IF(AND(F136=2,G136&lt;2),"solo JP",IF(AND(F136&lt;2,G136=2),"solo Thais","-")))</f>
@@ -15502,10 +15510,10 @@
         </is>
       </c>
       <c r="F141" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H141" s="13">
         <f>IF(AND(F141=2,G141=2),"AMBOS",IF(AND(F141=2,G141&lt;2),"solo JP",IF(AND(F141&lt;2,G141=2),"solo Thais","-")))</f>
@@ -15700,10 +15708,10 @@
         </is>
       </c>
       <c r="F143" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H143" s="13">
         <f>IF(AND(F143=2,G143=2),"AMBOS",IF(AND(F143=2,G143&lt;2),"solo JP",IF(AND(F143&lt;2,G143=2),"solo Thais","-")))</f>
@@ -15799,10 +15807,10 @@
         </is>
       </c>
       <c r="F144" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H144" s="13">
         <f>IF(AND(F144=2,G144=2),"AMBOS",IF(AND(F144=2,G144&lt;2),"solo JP",IF(AND(F144&lt;2,G144=2),"solo Thais","-")))</f>
@@ -16067,7 +16075,11 @@
           <t>lista google</t>
         </is>
       </c>
-      <c r="V146" s="20" t="inlineStr"/>
+      <c r="V146" s="20" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="46" customHeight="1">
       <c r="A147" s="9" t="inlineStr">
@@ -16096,10 +16108,10 @@
         </is>
       </c>
       <c r="F147" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H147" s="13">
         <f>IF(AND(F147=2,G147=2),"AMBOS",IF(AND(F147=2,G147&lt;2),"solo JP",IF(AND(F147&lt;2,G147=2),"solo Thais","-")))</f>
@@ -16195,10 +16207,10 @@
         </is>
       </c>
       <c r="F148" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H148" s="13">
         <f>IF(AND(F148=2,G148=2),"AMBOS",IF(AND(F148=2,G148&lt;2),"solo JP",IF(AND(F148&lt;2,G148=2),"solo Thais","-")))</f>
@@ -16393,7 +16405,7 @@
         </is>
       </c>
       <c r="F150" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G150" s="12" t="n">
         <v>1</v>
@@ -16793,7 +16805,7 @@
         </is>
       </c>
       <c r="F154" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G154" s="12" t="n">
         <v>1</v>
@@ -17478,10 +17490,10 @@
         </is>
       </c>
       <c r="F161" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H161" s="13">
         <f>IF(AND(F161=2,G161=2),"AMBOS",IF(AND(F161=2,G161&lt;2),"solo JP",IF(AND(F161&lt;2,G161=2),"solo Thais","-")))</f>
@@ -17668,7 +17680,7 @@
         </is>
       </c>
       <c r="F163" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G163" s="12" t="n">
         <v>1</v>
@@ -17734,7 +17746,11 @@
           <t>lista google</t>
         </is>
       </c>
-      <c r="V163" s="20" t="inlineStr"/>
+      <c r="V163" s="20" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="46" customHeight="1">
       <c r="A164" s="9" t="inlineStr">
@@ -17961,7 +17977,7 @@
         </is>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G166" s="12" t="n">
         <v>1</v>
@@ -18662,7 +18678,7 @@
         </is>
       </c>
       <c r="F173" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G173" s="12" t="n">
         <v>1</v>
@@ -18757,7 +18773,7 @@
         </is>
       </c>
       <c r="F174" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G174" s="12" t="n">
         <v>1</v>
@@ -18955,7 +18971,7 @@
         </is>
       </c>
       <c r="F176" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G176" s="12" t="n">
         <v>1</v>
@@ -19453,7 +19469,7 @@
         <v>1</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H181" s="13">
         <f>IF(AND(F181=2,G181=2),"AMBOS",IF(AND(F181=2,G181&lt;2),"solo JP",IF(AND(F181&lt;2,G181=2),"solo Thais","-")))</f>
@@ -19747,7 +19763,7 @@
         </is>
       </c>
       <c r="F184" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G184" s="12" t="n">
         <v>0</v>
@@ -22230,10 +22246,10 @@
         </is>
       </c>
       <c r="F209" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G209" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H209" s="26">
         <f>IF(AND(F209=2,G209=2),"AMBOS",IF(AND(F209=2,G209&lt;2),"solo JP",IF(AND(F209&lt;2,G209=2),"solo Thais","-")))</f>

--- a/NYC_2026_Planificador.xlsx
+++ b/NYC_2026_Planificador.xlsx
@@ -20806,9 +20806,9 @@
         </is>
       </c>
       <c r="R193" s="16" t="inlineStr"/>
-      <c r="S193" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S193" s="17" t="inlineStr">
+        <is>
+          <t>Día 6 · jue 3/9</t>
         </is>
       </c>
       <c r="T193" s="18" t="inlineStr">
@@ -30318,7 +30318,7 @@
     <row r="102" ht="32" customHeight="1">
       <c r="A102" s="34" t="inlineStr">
         <is>
-          <t>La mañana y la primera tarde son el World Trade Center completo — memorial, museo y One World Observatory en una sola bajada. OJO: One World es EL MIRADOR DE DÍA a propósito — su vista es el puerto y el agua, que de noche es negra; los arcos de atardecer van en Top of the Rock (lunes) y SUMMIT (viernes). THAIS ESTÁ EN NYC CON SU EQUIPO este jueves y SE LIBERA A LAS 16:00: se encuentran por Manhattan y se van juntos al Museum of the Moving Image, que es GRATIS los jueves de 14 a 18 — estaba caído del plan y ustedes lo tienen 2/2: RECUPERADO. El día cierra con check-in, cena y Dizzy's. Siguen afuera MoMA PS1, Astoria y Gantry (no hay hueco), y el Staten Island Ferry pasó a la alternativa nocturna de hoy.</t>
+          <t>La mañana y la primera tarde son el World Trade Center completo — memorial, museo y One World Observatory en una sola bajada. OJO: One World es EL MIRADOR DE DÍA a propósito — su vista es el puerto y el agua, que de noche es negra; los arcos de atardecer van en Top of the Rock (lunes) y SUMMIT (viernes). THAIS ESTÁ EN NYC CON SU EQUIPO este jueves y SE LIBERA A LAS 16:00: se encuentran por Manhattan y se van juntos al Museum of the Moving Image, que es GRATIS los jueves de 14 a 18 — estaba caído del plan y ustedes lo tienen 2/2: RECUPERADO. El día cierra con check-in, cena y Dizzy's. Siguen afuera MoMA PS1, Astoria y Gantry (no hay hueco), y el Staten Island Ferry pasó a la alternativa nocturna de hoy. ENTRA STONE ST, que era imprescindible y no estaba en ningún día: el almuerzo se corre de Brookfield Place a la calle adoquinada, a 10 minutos del museo y 12 de One World. Se pagan 22 minutos de caminata y quedan 38 para comer — alcanza para un mediodía, aunque su mejor hora sea el after office de 5 a 8 y no la del almuerzo.</t>
         </is>
       </c>
     </row>
@@ -30542,11 +30542,19 @@
       </c>
       <c r="E110" s="39" t="inlineStr">
         <is>
-          <t>Almuerzo cruzando West St: Hudson Eats o Le District, en Brookfield Place, con el yate harbor de fondo.</t>
-        </is>
-      </c>
-      <c r="F110" s="37" t="inlineStr"/>
-      <c r="G110" s="40" t="inlineStr"/>
+          <t>★ ALMUERZO EN STONE ST — 10 min a pie desde el museo, hacia el sureste. Calle adoquinada peatonal de 1660, la traza holandesa que sobrevivió al fuego de 1835: mesas afuera, sin autos, entre edificios de piedra. Se come rápido y se sigue: One World es a las 13:45 y son 12 min de vuelta. Plan B si llueve o no hay mesa: Hudson Eats o Le District en Brookfield Place, cruzando West St.</t>
+        </is>
+      </c>
+      <c r="F110" s="37" t="inlineStr">
+        <is>
+          <t>Stone St</t>
+        </is>
+      </c>
+      <c r="G110" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~14 min a pie · 1.1 km · estimado</t>
+        </is>
+      </c>
       <c r="H110" s="41" t="inlineStr"/>
       <c r="I110" s="41" t="inlineStr"/>
     </row>
@@ -30579,7 +30587,7 @@
       </c>
       <c r="G111" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~4 min a pie · 0.2 km · estimado</t>
+          <t>🚶 ~20 min a pie (1.2 km) o 🚇 ~15 min · estimado</t>
         </is>
       </c>
       <c r="H111" s="41" t="inlineStr"/>

--- a/NYC_2026_Planificador.xlsx
+++ b/NYC_2026_Planificador.xlsx
@@ -27856,7 +27856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I180"/>
+  <dimension ref="A1:I181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="C171" s="37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D171" s="38" t="inlineStr">
@@ -32072,14 +32072,14 @@
       <c r="A172" s="35" t="n"/>
       <c r="B172" s="36" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C172" s="37" t="inlineStr">
+        <is>
           <t>15:05</t>
         </is>
       </c>
-      <c r="C172" s="37" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="D172" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -32087,7 +32087,7 @@
       </c>
       <c r="E172" s="39" t="inlineStr">
         <is>
-          <t>SALIR 15:05 (no más tarde): caminata al teleférico + cruce + subte 4/5/6 de 59 St a 86 St suman ~50 min, y la ventana pay-what-you-wish del Guggenheim arranca 16:00 y el museo cierra 17:30 — llegar puntuales ES la visita.</t>
+          <t>◇ LA DECISIÓN DEL DÍA, y se toma acá parado, antes de salir de la isla. Si al llamar al Guggenheim les dijeron que la rotonda está en montaje, el edificio —que es la mitad de la visita— no se ve, y conviene cambiarlo por MOMA PS1: el último imprescindible que queda afuera del viaje, GRATIS, abierto los domingos hasta las 18, y a 1,2 km de donde están parados. CÓMO: en vez de volver en teleférico, caminan a la estación del F que está EN Roosevelt Island, una parada hasta 21 St-Queensbridge y 15 min a pie (~25 min puerta a puerta). Entran 15:45, dos horas holgadas hasta las 17:45, y al hotel en el 7 o el E/M desde Court Sq (~45 min): llegan 18:30, justo para las valijas. NO toca el vuelo. Lo que se pierde: el Guggenheim y el cruce de vuelta en teleférico — el de ida ya lo hicieron a las 13:50.</t>
         </is>
       </c>
       <c r="F172" s="37" t="inlineStr"/>
@@ -32097,60 +32097,56 @@
     </row>
     <row r="173" ht="30" customHeight="1">
       <c r="A173" s="35" t="n"/>
-      <c r="B173" s="42" t="inlineStr">
+      <c r="B173" s="36" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="C173" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="C173" s="43" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="D173" s="44" t="inlineStr">
+      <c r="D173" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E173" s="45" t="inlineStr">
-        <is>
-          <t>★ GUGGENHEIM — pay-what-you-wish domingos 16:00-17:30 (sugerido $10, mínimo $1). El edificio de Frank Lloyd Wright vale la visita solo: se sube en ascensor y se baja caminando la rampa. ⚠️ LLAMAR ANTES: la rotonda estaría en montaje hasta el 18 de septiembre y el pay-what-you-wish no está confirmado en fuente oficial.</t>
-        </is>
-      </c>
-      <c r="F173" s="43" t="inlineStr">
-        <is>
-          <t>Guggenheim</t>
-        </is>
-      </c>
+      <c r="E173" s="39" t="inlineStr">
+        <is>
+          <t>SALIR 15:05 (no más tarde): caminata al teleférico + cruce + subte 4/5/6 de 59 St a 86 St suman ~50 min, y la ventana pay-what-you-wish del Guggenheim arranca 16:00 y el museo cierra 17:30 — llegar puntuales ES la visita.</t>
+        </is>
+      </c>
+      <c r="F173" s="37" t="inlineStr"/>
       <c r="G173" s="40" t="inlineStr"/>
       <c r="H173" s="41" t="inlineStr"/>
       <c r="I173" s="41" t="inlineStr"/>
     </row>
-    <row r="174" ht="16" customHeight="1">
+    <row r="174" ht="30" customHeight="1">
       <c r="A174" s="35" t="n"/>
-      <c r="B174" s="36" t="inlineStr">
+      <c r="B174" s="42" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C174" s="43" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="C174" s="37" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="D174" s="38" t="inlineStr">
+      <c r="D174" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E174" s="39" t="inlineStr">
-        <is>
-          <t>Volver caminando por Central Park hasta el hotel (~25 min) o subte 86 St → 1 a 79 St.</t>
-        </is>
-      </c>
-      <c r="F174" s="37" t="inlineStr">
-        <is>
-          <t>Hotel The Beacon (3-6 sep)</t>
+      <c r="E174" s="45" t="inlineStr">
+        <is>
+          <t>★ GUGGENHEIM — pay-what-you-wish domingos 16:00-17:30 (sugerido $10, mínimo $1). El edificio de Frank Lloyd Wright vale la visita solo: se sube en ascensor y se baja caminando la rampa. ⚠️ LLAMAR ANTES DE SALIR (guggenheim.org o +1 212-423-3500) y preguntar DOS cosas: si la rotonda está abierta —estaría en montaje hasta el 18 de septiembre— y si el pay-what-you-wish sigue en pie. Ninguna de las dos está confirmada en fuente oficial. SI LA ROTONDA ESTÁ CERRADA, el plan B ya está armado: ver el bloque de abajo.</t>
+        </is>
+      </c>
+      <c r="F174" s="43" t="inlineStr">
+        <is>
+          <t>Guggenheim</t>
         </is>
       </c>
       <c r="G174" s="40" t="inlineStr"/>
@@ -32161,14 +32157,14 @@
       <c r="A175" s="35" t="n"/>
       <c r="B175" s="36" t="inlineStr">
         <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="C175" s="37" t="inlineStr">
+        <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="C175" s="37" t="inlineStr">
-        <is>
-          <t>19:40</t>
-        </is>
-      </c>
       <c r="D175" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -32176,10 +32172,14 @@
       </c>
       <c r="E175" s="39" t="inlineStr">
         <is>
-          <t>Retirar las valijas del bell desk. Cena tranquila cerca del hotel: es la última.</t>
-        </is>
-      </c>
-      <c r="F175" s="37" t="inlineStr"/>
+          <t>Volver caminando por Central Park hasta el hotel (~25 min) o subte 86 St → 1 a 79 St.</t>
+        </is>
+      </c>
+      <c r="F175" s="37" t="inlineStr">
+        <is>
+          <t>Hotel The Beacon (3-6 sep)</t>
+        </is>
+      </c>
       <c r="G175" s="40" t="inlineStr"/>
       <c r="H175" s="41" t="inlineStr"/>
       <c r="I175" s="41" t="inlineStr"/>
@@ -32188,14 +32188,14 @@
       <c r="A176" s="35" t="n"/>
       <c r="B176" s="36" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C176" s="37" t="inlineStr">
+        <is>
           <t>19:40</t>
         </is>
       </c>
-      <c r="C176" s="37" t="inlineStr">
-        <is>
-          <t>20:14</t>
-        </is>
-      </c>
       <c r="D176" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -32203,7 +32203,7 @@
       </c>
       <c r="E176" s="39" t="inlineStr">
         <is>
-          <t>Salir de The Beacon. Subte 1/2/3 desde 72 St hasta 34 St-Penn Station: ~10 min, $3.</t>
+          <t>Retirar las valijas del bell desk. Cena tranquila cerca del hotel: es la última.</t>
         </is>
       </c>
       <c r="F176" s="37" t="inlineStr"/>
@@ -32211,18 +32211,18 @@
       <c r="H176" s="41" t="inlineStr"/>
       <c r="I176" s="41" t="inlineStr"/>
     </row>
-    <row r="177" ht="30" customHeight="1">
+    <row r="177" ht="16" customHeight="1">
       <c r="A177" s="35" t="n"/>
       <c r="B177" s="36" t="inlineStr">
         <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="C177" s="37" t="inlineStr">
+        <is>
           <t>20:14</t>
         </is>
       </c>
-      <c r="C177" s="37" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
       <c r="D177" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -32230,7 +32230,7 @@
       </c>
       <c r="E177" s="39" t="inlineStr">
         <is>
-          <t>NJ Transit Penn Station → EWR, llega 20:38. $17,25 (incluye el AirTrain). VERIFICAR el horario dominical en njtransit.com unos días antes.</t>
+          <t>Salir de The Beacon. Subte 1/2/3 desde 72 St hasta 34 St-Penn Station: ~10 min, $3.</t>
         </is>
       </c>
       <c r="F177" s="37" t="inlineStr"/>
@@ -32238,18 +32238,18 @@
       <c r="H177" s="41" t="inlineStr"/>
       <c r="I177" s="41" t="inlineStr"/>
     </row>
-    <row r="178" ht="16" customHeight="1">
+    <row r="178" ht="30" customHeight="1">
       <c r="A178" s="35" t="n"/>
       <c r="B178" s="36" t="inlineStr">
         <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="C178" s="37" t="inlineStr">
+        <is>
           <t>20:45</t>
         </is>
       </c>
-      <c r="C178" s="37" t="inlineStr">
-        <is>
-          <t>20:55</t>
-        </is>
-      </c>
       <c r="D178" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -32257,7 +32257,7 @@
       </c>
       <c r="E178" s="39" t="inlineStr">
         <is>
-          <t>AirTrain hasta la terminal: 10-15 min.</t>
+          <t>NJ Transit Penn Station → EWR, llega 20:38. $17,25 (incluye el AirTrain). VERIFICAR el horario dominical en njtransit.com unos días antes.</t>
         </is>
       </c>
       <c r="F178" s="37" t="inlineStr"/>
@@ -32265,14 +32265,18 @@
       <c r="H178" s="41" t="inlineStr"/>
       <c r="I178" s="41" t="inlineStr"/>
     </row>
-    <row r="179" ht="30" customHeight="1">
+    <row r="179" ht="16" customHeight="1">
       <c r="A179" s="35" t="n"/>
       <c r="B179" s="36" t="inlineStr">
         <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C179" s="37" t="inlineStr">
+        <is>
           <t>20:55</t>
         </is>
       </c>
-      <c r="C179" s="37" t="inlineStr"/>
       <c r="D179" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -32280,7 +32284,7 @@
       </c>
       <c r="E179" s="39" t="inlineStr">
         <is>
-          <t>En terminal. Faltan 2h45 para el vuelo de las 23:40 — correcto para un internacional en el domingo de Labor Day, que es la noche de más tráfico del año en EWR.</t>
+          <t>AirTrain hasta la terminal: 10-15 min.</t>
         </is>
       </c>
       <c r="F179" s="37" t="inlineStr"/>
@@ -32288,10 +32292,33 @@
       <c r="H179" s="41" t="inlineStr"/>
       <c r="I179" s="41" t="inlineStr"/>
     </row>
-    <row r="180" ht="32" customHeight="1">
-      <c r="A180" s="46" t="inlineStr">
-        <is>
-          <t>ALTERNATIVA / OJO:  COLCHÓN: si algo se atrasa, el tren siguiente sale 20:55 y llega a EWR 21:16, o sea terminal ~21:35 y 2h05 antes del vuelo. Es el último que yo tomaría. // Si prefieren un último día sin moverse, salteen el teleférico y estiren Central Park hasta el Guggenheim: el parque solo da para toda la mañana y la tarde. Y si el Guggenheim tiene la rotonda cerrada, el Whitney abre los domingos. Lo que NO conviene hoy es meter algo nuevo y grande.</t>
+    <row r="180" ht="30" customHeight="1">
+      <c r="A180" s="35" t="n"/>
+      <c r="B180" s="36" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="C180" s="37" t="inlineStr"/>
+      <c r="D180" s="38" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E180" s="39" t="inlineStr">
+        <is>
+          <t>En terminal. Faltan 2h45 para el vuelo de las 23:40 — correcto para un internacional en el domingo de Labor Day, que es la noche de más tráfico del año en EWR.</t>
+        </is>
+      </c>
+      <c r="F180" s="37" t="inlineStr"/>
+      <c r="G180" s="40" t="inlineStr"/>
+      <c r="H180" s="41" t="inlineStr"/>
+      <c r="I180" s="41" t="inlineStr"/>
+    </row>
+    <row r="181" ht="32" customHeight="1">
+      <c r="A181" s="46" t="inlineStr">
+        <is>
+          <t>ALTERNATIVA / OJO:  COLCHÓN: si algo se atrasa, el tren siguiente sale 20:55 y llega a EWR 21:16, o sea terminal ~21:35 y 2h05 antes del vuelo. Es el último que yo tomaría. // Si prefieren un último día sin moverse, salteen el teleférico y estiren Central Park hasta el Guggenheim: el parque solo da para toda la mañana y la tarde. Lo que NO conviene hoy es meter algo nuevo y grande. // LA DECISIÓN DEL DÍA, y se toma con una llamada: si la rotonda del Guggenheim está en montaje, el edificio —que es la mitad de la visita— no se ve, y ahí conviene cambiarlo por MOMA PS1, el último imprescindible que queda afuera del viaje. Es gratis, abre los domingos hasta las 18 y hoy pasan a 1,2 km. Los tiempos están calculados en el bloque de las 16:00 y no tocan el vuelo. Si la rotonda está abierta, el Guggenheim se queda: el edificio de Wright vale por sí solo. Tercera opción si ninguna convence: el Whitney también abre los domingos.</t>
         </is>
       </c>
     </row>
@@ -32310,10 +32337,10 @@
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A85:I85"/>
+    <mergeCell ref="A181:I181"/>
     <mergeCell ref="A126:I126"/>
     <mergeCell ref="A144:I144"/>
     <mergeCell ref="A125:I125"/>
-    <mergeCell ref="A180:I180"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A68:I68"/>
     <mergeCell ref="A28:I28"/>
@@ -32328,7 +32355,7 @@
     <mergeCell ref="A6:I6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H182" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,Reservado,Confirmado,Descartado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -34251,22 +34278,22 @@
       <c r="A16" s="41" t="inlineStr"/>
       <c r="B16" s="60" t="inlineStr">
         <is>
-          <t>Guggenheim — llamar para confirmar precio y estado de la rotonda</t>
+          <t>Guggenheim — llamar y preguntar DOS cosas: si la rotonda está abierta y si sigue el pay-what-you-wish</t>
         </is>
       </c>
       <c r="C16" s="59" t="inlineStr">
         <is>
-          <t>Antes de meterlo en el plan</t>
+          <t>La mañana del domingo 6, antes de salir del hotel</t>
         </is>
       </c>
       <c r="D16" s="59" t="inlineStr">
         <is>
-          <t>guggenheim.org / teléfono</t>
+          <t>guggenheim.org / +1 212-423-3500</t>
         </is>
       </c>
       <c r="E16" s="59" t="inlineStr">
         <is>
-          <t>La rotonda estaría en montaje hasta el 18 de septiembre, con entrada rebajada a ~$16. El pay-what-you-wish de martes y domingos 16-17:30 no lo pude confirmar en fuente oficial (el sitio bloquea la lectura). Si la rotonda está cerrada, el edificio —que es la razón para ir— se ve a medias.</t>
+          <t>Es la única decisión del último día y ahora tiene plan B armado. La rotonda estaría en montaje hasta el 18 de septiembre, con entrada rebajada a ~$16; el pay-what-you-wish de domingos 16-17:30 no lo pude confirmar en fuente oficial (el sitio bloquea la lectura). SI LA ROTONDA ESTÁ CERRADA: el edificio —que es la razón para ir— se ve a medias, y conviene cambiarlo por MoMA PS1, el último imprescindible que queda afuera del viaje. Es gratis, abre los domingos hasta las 18 y ese día pasan a 1,2 km. Los tiempos están en el bloque de las 15:00 del domingo y no tocan el vuelo.</t>
         </is>
       </c>
     </row>

--- a/NYC_2026_Planificador.xlsx
+++ b/NYC_2026_Planificador.xlsx
@@ -4956,9 +4956,9 @@
           <t>1071 5th Ave</t>
         </is>
       </c>
-      <c r="S32" s="17" t="inlineStr">
-        <is>
-          <t>Día 9 · dom 6/9</t>
+      <c r="S32" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="T32" s="18" t="inlineStr">
@@ -5261,9 +5261,9 @@
           <t>22-25 Jackson Ave, LIC</t>
         </is>
       </c>
-      <c r="S35" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S35" s="17" t="inlineStr">
+        <is>
+          <t>Día 9 · dom 6/9</t>
         </is>
       </c>
       <c r="T35" s="18" t="inlineStr">
@@ -32441,7 +32441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I181"/>
+  <dimension ref="A1:I182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -36433,14 +36433,14 @@
     <row r="163" ht="22" customHeight="1">
       <c r="A163" s="33" t="inlineStr">
         <is>
-          <t>DÍA 9 · Domingo 06/09 · Checkout, Central Park, Roosevelt Island y vuelo  —  base: The Beacon (checkout) → EWR  ·  Ambos</t>
+          <t>DÍA 9 · Domingo 06/09 · Checkout, Central Park, Roosevelt Island, MoMA PS1 y vuelo  —  base: The Beacon (checkout) → EWR  ·  Ambos</t>
         </is>
       </c>
     </row>
     <row r="164" ht="32" customHeight="1">
       <c r="A164" s="34" t="inlineStr">
         <is>
-          <t>El día arranca con el CHECKOUT de The Beacon: hacerlo temprano y dejar las valijas en el bell desk libera el día entero. El vuelo sale 23:40, así que hay margen — pero es el domingo del fin de semana largo de Labor Day, la noche de mayor tráfico del año, y EWR va a estar cargado. Por eso todo queda dentro del eje Central Park - Upper East Side, a diez minutos de subte del hotel, y se sale con 2h45 de anticipación.</t>
+          <t>El día arranca con el CHECKOUT de The Beacon: hacerlo temprano y dejar las valijas en el bell desk libera el día entero. El vuelo sale 23:40, así que hay margen — pero es el domingo del fin de semana largo de Labor Day, la noche de mayor tráfico del año, y EWR va a estar cargado. Por eso todo queda cerca y se sale con 2h45 de anticipación. EL CAMBIO DEL ÚLTIMO DÍA: entra MOMA PS1 y sale el Guggenheim. Se verificó el 27/8 que la rotonda del Guggenheim está cerrada hasta el 17/9 —no se camina la rampa, que es la razón para ir— y PS1 resultó ser gratis, abierto hasta las 18 los domingos, a 1,2 km de Roosevelt Island y con «Greater New York 2026» en pie hasta el 7/9. Era el último imprescindible que quedaba afuera del viaje. El Guggenheim queda escrito como alternativa por si cambian de idea.</t>
         </is>
       </c>
     </row>
@@ -36463,7 +36463,7 @@
       </c>
       <c r="E165" s="39" t="inlineStr">
         <is>
-          <t>Desayuno SIN despertador temprano: anoche terminó ~1:30 en el Village y lo único con hora fija hoy es el Guggenheim a las 16:00. Dormir un poco más está permitido.</t>
+          <t>Desayuno SIN despertador temprano: anoche terminó ~1:30 en el Village y lo único con hora fija hoy es el PS1, que cierra a las 18:00. Dormir un poco más está permitido.</t>
         </is>
       </c>
       <c r="F165" s="37" t="inlineStr"/>
@@ -36631,7 +36631,7 @@
       </c>
       <c r="C171" s="37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="D171" s="38" t="inlineStr">
@@ -36657,12 +36657,12 @@
       <c r="A172" s="35" t="n"/>
       <c r="B172" s="36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="C172" s="37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="D172" s="38" t="inlineStr">
@@ -36672,7 +36672,7 @@
       </c>
       <c r="E172" s="39" t="inlineStr">
         <is>
-          <t>◇ LA DECISIÓN DEL DÍA, y se toma acá parado, antes de salir de la isla. YA NO HACE FALTA LLAMAR: se verificó el 27/8 y la rotonda del Guggenheim está cerrada hasta el 17/9, así que el edificio —que es la mitad de la visita— se ve a medias. La alternativa es MOMA PS1 —ENTRADA GRATUITA para todos, verificado, y con «Greater New York 2026» en pie hasta el 7 de septiembre—: el último imprescindible que queda afuera del viaje, GRATIS, abierto los domingos hasta las 18, y a 1,2 km de donde están parados. CÓMO: en vez de volver en teleférico, caminan a la estación del F que está EN Roosevelt Island, una parada hasta 21 St-Queensbridge y 15 min a pie (~25 min puerta a puerta). Entran 15:45, dos horas holgadas hasta las 17:45, y al hotel en el 7 o el E/M desde Court Sq (~45 min): llegan 18:30, justo para las valijas. NO toca el vuelo. Lo que se pierde: el Guggenheim y el cruce de vuelta en teleférico — el de ida ya lo hicieron a las 13:50.</t>
+          <t>SALIR 15:05 de Four Freedoms Park y caminar 15 min al norte por el borde del río hasta la ESTACIÓN DEL F, que está en el medio de la isla (Main St y Roosevelt Island Bridge). Hoy NO se vuelve en teleférico: se cruza a Queens por abajo.</t>
         </is>
       </c>
       <c r="F172" s="37" t="inlineStr"/>
@@ -36684,12 +36684,12 @@
       <c r="A173" s="35" t="n"/>
       <c r="B173" s="36" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C173" s="37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="D173" s="38" t="inlineStr">
@@ -36699,7 +36699,7 @@
       </c>
       <c r="E173" s="39" t="inlineStr">
         <is>
-          <t>SALIR 15:05 (no más tarde): caminata al teleférico + cruce + subte 4/5/6 de 59 St a 86 St suman ~50 min, y la ventana pay-what-you-wish del Guggenheim arranca 16:00 y el museo cierra 17:30 — llegar puntuales ES la visita.</t>
+          <t>Subte F, UNA parada: Roosevelt Island → 21 St-Queensbridge (~4 min). Salir y caminar 12-15 min al sur por 21st St / Jackson Ave.</t>
         </is>
       </c>
       <c r="F173" s="37" t="inlineStr"/>
@@ -36711,7 +36711,7 @@
       <c r="A174" s="35" t="n"/>
       <c r="B174" s="42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C174" s="43" t="inlineStr">
@@ -36726,19 +36726,19 @@
       </c>
       <c r="E174" s="45" t="inlineStr">
         <is>
-          <t>★ GUGGENHEIM — ⚠️ VERIFICADO el 27/8 y la respuesta es la mala: LA ROTONDA ESTÁ CERRADA del 3/8 al 17/9 por el montaje de la muestra de Taryn Simon. No se puede caminar la rampa —la razón para venir— y avisan que puede haber ruido de obra; la espiral se mira desde abajo nomás. A cambio la entrada baja de $30 a $16, y sigue el pay-what-you-wish de los domingos 16:00-17:30. Lo que SÍ queda: Guggenheim Pop en las torres 4, 5 y 7 (Lichtenstein, Warhol, Oldenburg, Cattelan) y la colección Thannhauser. Con esto sobre la mesa, mirá el bloque de las 15:00: MoMA PS1 es la alternativa, y es el último imprescindible que falta.</t>
+          <t>★★ MOMA PS1 — el último imprescindible del viaje, y entra gratis. Escuela pública de 1892 reconvertida en el laboratorio del MoMA: lo que no se anima a mostrar en la Quinta Avenida. VERIFICADO el 27/8: ENTRADA GRATUITA para todos, abre domingos 12:00-18:00, y «Greater New York 2026» —la encuesta insignia de la casa, que se hace cada cinco años— sigue en pie hasta el 7 de septiembre, o sea que la agarran por un día. Más el Courtyard Commission de Precious Okoyomon al aire libre. Dos horas holgadas hasta las 17:45.</t>
         </is>
       </c>
       <c r="F174" s="43" t="inlineStr">
         <is>
-          <t>Guggenheim</t>
+          <t>MoMA PS1</t>
         </is>
       </c>
       <c r="G174" s="40" t="inlineStr"/>
       <c r="H174" s="41" t="inlineStr"/>
       <c r="I174" s="41" t="inlineStr"/>
     </row>
-    <row r="175" ht="16" customHeight="1">
+    <row r="175" ht="30" customHeight="1">
       <c r="A175" s="35" t="n"/>
       <c r="B175" s="36" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
       </c>
       <c r="C175" s="37" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D175" s="38" t="inlineStr">
@@ -36757,30 +36757,26 @@
       </c>
       <c r="E175" s="39" t="inlineStr">
         <is>
-          <t>Volver caminando por Central Park hasta el hotel (~25 min) o subte 86 St → 1 a 79 St.</t>
-        </is>
-      </c>
-      <c r="F175" s="37" t="inlineStr">
-        <is>
-          <t>Hotel The Beacon (3-6 sep)</t>
-        </is>
-      </c>
+          <t>Del PS1 al hotel: subte 7 desde Court Sq hasta Times Sq y 1/2/3 hasta 72 St, o E/M hasta 53 St (~45 min). Llegan 18:30, justo para las valijas. El vuelo no se toca.</t>
+        </is>
+      </c>
+      <c r="F175" s="37" t="inlineStr"/>
       <c r="G175" s="40" t="inlineStr"/>
       <c r="H175" s="41" t="inlineStr"/>
       <c r="I175" s="41" t="inlineStr"/>
     </row>
-    <row r="176" ht="16" customHeight="1">
+    <row r="176" ht="30" customHeight="1">
       <c r="A176" s="35" t="n"/>
       <c r="B176" s="36" t="inlineStr">
         <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="C176" s="37" t="inlineStr">
+        <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="C176" s="37" t="inlineStr">
-        <is>
-          <t>19:40</t>
-        </is>
-      </c>
       <c r="D176" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36788,7 +36784,7 @@
       </c>
       <c r="E176" s="39" t="inlineStr">
         <is>
-          <t>Retirar las valijas del bell desk. Cena tranquila cerca del hotel: es la última.</t>
+          <t>◇ SI PREFIEREN EL GUGGENHEIM, sigue estando y este bloque se ignora: pay-what-you-wish domingos 16:00-17:30 (mínimo $1) y entrada rebajada a $16 el resto del horario. ⚠️ PERO la rotonda está CERRADA del 3/8 al 17/9 por el montaje de Taryn Simon: no se camina la rampa —que es la razón para ir— y avisan que puede haber ruido de obra. Quedan las torres 4, 5 y 7 con «Guggenheim Pop» (Lichtenstein, Warhol, Oldenburg, Cattelan) y la colección Thannhauser. Para hacerlo: en vez de cruzar a Queens, teleférico de vuelta y subte 4/5/6 de 59 St a 86 St, y hay que salir del FDR Park 15:05 para entrar 16:00 — la ventana a voluntad va hasta las 17:30 y el museo cierra ahí.</t>
         </is>
       </c>
       <c r="F176" s="37" t="inlineStr"/>
@@ -36800,14 +36796,14 @@
       <c r="A177" s="35" t="n"/>
       <c r="B177" s="36" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C177" s="37" t="inlineStr">
+        <is>
           <t>19:40</t>
         </is>
       </c>
-      <c r="C177" s="37" t="inlineStr">
-        <is>
-          <t>20:14</t>
-        </is>
-      </c>
       <c r="D177" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36815,7 +36811,7 @@
       </c>
       <c r="E177" s="39" t="inlineStr">
         <is>
-          <t>Salir de The Beacon. Subte 1/2/3 desde 72 St hasta 34 St-Penn Station: ~10 min, $3.</t>
+          <t>Retirar las valijas del bell desk. Cena tranquila cerca del hotel: es la última.</t>
         </is>
       </c>
       <c r="F177" s="37" t="inlineStr"/>
@@ -36823,18 +36819,18 @@
       <c r="H177" s="41" t="inlineStr"/>
       <c r="I177" s="41" t="inlineStr"/>
     </row>
-    <row r="178" ht="30" customHeight="1">
+    <row r="178" ht="16" customHeight="1">
       <c r="A178" s="35" t="n"/>
       <c r="B178" s="36" t="inlineStr">
         <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="C178" s="37" t="inlineStr">
+        <is>
           <t>20:14</t>
         </is>
       </c>
-      <c r="C178" s="37" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
       <c r="D178" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36842,7 +36838,7 @@
       </c>
       <c r="E178" s="39" t="inlineStr">
         <is>
-          <t>NJ Transit Penn Station → EWR, llega 20:38. $17,25 (incluye el AirTrain). VERIFICAR el horario dominical en njtransit.com unos días antes.</t>
+          <t>Salir de The Beacon. Subte 1/2/3 desde 72 St hasta 34 St-Penn Station: ~10 min, $3.</t>
         </is>
       </c>
       <c r="F178" s="37" t="inlineStr"/>
@@ -36850,18 +36846,18 @@
       <c r="H178" s="41" t="inlineStr"/>
       <c r="I178" s="41" t="inlineStr"/>
     </row>
-    <row r="179" ht="16" customHeight="1">
+    <row r="179" ht="30" customHeight="1">
       <c r="A179" s="35" t="n"/>
       <c r="B179" s="36" t="inlineStr">
         <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="C179" s="37" t="inlineStr">
+        <is>
           <t>20:45</t>
         </is>
       </c>
-      <c r="C179" s="37" t="inlineStr">
-        <is>
-          <t>20:55</t>
-        </is>
-      </c>
       <c r="D179" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36869,7 +36865,7 @@
       </c>
       <c r="E179" s="39" t="inlineStr">
         <is>
-          <t>AirTrain hasta la terminal: 10-15 min.</t>
+          <t>NJ Transit Penn Station → EWR, llega 20:38. $17,25 (incluye el AirTrain). VERIFICAR el horario dominical en njtransit.com unos días antes.</t>
         </is>
       </c>
       <c r="F179" s="37" t="inlineStr"/>
@@ -36877,14 +36873,18 @@
       <c r="H179" s="41" t="inlineStr"/>
       <c r="I179" s="41" t="inlineStr"/>
     </row>
-    <row r="180" ht="30" customHeight="1">
+    <row r="180" ht="16" customHeight="1">
       <c r="A180" s="35" t="n"/>
       <c r="B180" s="36" t="inlineStr">
         <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C180" s="37" t="inlineStr">
+        <is>
           <t>20:55</t>
         </is>
       </c>
-      <c r="C180" s="37" t="inlineStr"/>
       <c r="D180" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36892,7 +36892,7 @@
       </c>
       <c r="E180" s="39" t="inlineStr">
         <is>
-          <t>En terminal. Faltan 2h45 para el vuelo de las 23:40 — correcto para un internacional en el domingo de Labor Day, que es la noche de más tráfico del año en EWR.</t>
+          <t>AirTrain hasta la terminal: 10-15 min.</t>
         </is>
       </c>
       <c r="F180" s="37" t="inlineStr"/>
@@ -36900,10 +36900,33 @@
       <c r="H180" s="41" t="inlineStr"/>
       <c r="I180" s="41" t="inlineStr"/>
     </row>
-    <row r="181" ht="32" customHeight="1">
-      <c r="A181" s="46" t="inlineStr">
-        <is>
-          <t>ALTERNATIVA / OJO:  COLCHÓN: si algo se atrasa, el tren siguiente sale 20:55 y llega a EWR 21:16, o sea terminal ~21:35 y 2h05 antes del vuelo. Es el último que yo tomaría. // Si prefieren un último día sin moverse, salteen el teleférico y estiren Central Park hasta el Guggenheim: el parque solo da para toda la mañana y la tarde. Lo que NO conviene hoy es meter algo nuevo y grande. // LO QUE SE PIERDEN POR EL VUELO, y duele: esta noche a las 20:00 el Met proyecta gratis en Lincoln Center «El Último Sueño de Frida y Diego» —la misma Frida de la muestra del MoMA del lunes— y ustedes salen del hotel 19:40 hacia Penn Station. Está a diez cuadras del Beacon. No hay forma de que entre sin poner en riesgo el vuelo. // LA DECISIÓN DEL DÍA, y se toma con una llamada: si la rotonda del Guggenheim está en montaje, el edificio —que es la mitad de la visita— no se ve, y ahí conviene cambiarlo por MOMA PS1, el último imprescindible que queda afuera del viaje. Es gratis, abre los domingos hasta las 18 y hoy pasan a 1,2 km. Los tiempos están calculados en el bloque de las 16:00 y no tocan el vuelo. Si la rotonda está abierta, el Guggenheim se queda: el edificio de Wright vale por sí solo. Tercera opción si ninguna convence: el Whitney también abre los domingos.</t>
+    <row r="181" ht="30" customHeight="1">
+      <c r="A181" s="35" t="n"/>
+      <c r="B181" s="36" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="C181" s="37" t="inlineStr"/>
+      <c r="D181" s="38" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E181" s="39" t="inlineStr">
+        <is>
+          <t>En terminal. Faltan 2h45 para el vuelo de las 23:40 — correcto para un internacional en el domingo de Labor Day, que es la noche de más tráfico del año en EWR.</t>
+        </is>
+      </c>
+      <c r="F181" s="37" t="inlineStr"/>
+      <c r="G181" s="40" t="inlineStr"/>
+      <c r="H181" s="41" t="inlineStr"/>
+      <c r="I181" s="41" t="inlineStr"/>
+    </row>
+    <row r="182" ht="32" customHeight="1">
+      <c r="A182" s="46" t="inlineStr">
+        <is>
+          <t>ALTERNATIVA / OJO:  COLCHÓN: si algo se atrasa, el tren siguiente sale 20:55 y llega a EWR 21:16, o sea terminal ~21:35 y 2h05 antes del vuelo. Es el último que yo tomaría. // Si prefieren un último día sin moverse, salteen el teleférico y estiren Central Park hasta el Guggenheim: el parque solo da para toda la mañana y la tarde. Lo que NO conviene hoy es meter algo nuevo y grande. // LO QUE SE PIERDEN POR EL VUELO, y duele: esta noche a las 20:00 el Met proyecta gratis en Lincoln Center «El Último Sueño de Frida y Diego» —la misma Frida de la muestra del MoMA del lunes— y ustedes salen del hotel 19:40 hacia Penn Station. Está a diez cuadras del Beacon. No hay forma de que entre sin poner en riesgo el vuelo. // SI QUIEREN VOLVER AL GUGGENHEIM en vez del PS1: está escrito en el bloque de las 18:20, con los tiempos hechos. Cuesta el último imprescindible del viaje y hay que aceptar que la rampa —la razón para ir— no se camina hasta el 17/9. Tercera opción si ninguna convence: el Whitney también abre los domingos.</t>
         </is>
       </c>
     </row>
@@ -36922,7 +36945,6 @@
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A85:I85"/>
-    <mergeCell ref="A181:I181"/>
     <mergeCell ref="A126:I126"/>
     <mergeCell ref="A144:I144"/>
     <mergeCell ref="A125:I125"/>
@@ -36935,12 +36957,13 @@
     <mergeCell ref="A67:I67"/>
     <mergeCell ref="A83:I83"/>
     <mergeCell ref="A142:I142"/>
+    <mergeCell ref="A182:I182"/>
     <mergeCell ref="A123:I123"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A6:I6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H184" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,Reservado,Confirmado,Descartado"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NYC_2026_Planificador.xlsx
+++ b/NYC_2026_Planificador.xlsx
@@ -32441,7 +32441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I182"/>
+  <dimension ref="A1:I183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -32526,7 +32526,7 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="34" t="inlineStr">
         <is>
-          <t>La reserva de Hudson VU (rooftop del propio Ink48) NO es modificable y exige estar en el hotel 19:20, así que el festival queda en la franja 16:30-18:30 — dos horas justas, con salida obligada 20-30 min antes del cierre. La tarde liberada la ocupa ARTHUR AVENUE, la Little Italy real del Bronx — los dos la marcaron 2 y no entraba en ningún día. Desde Harlem es un tiro de subte D (~20 min), y el sábado es EL día: el mercado cierra ~18h y los domingos no abre. Bogotá está a una hora de NYC: no hay jet lag, solo noche corta de avión. PEDIR EARLY CHECK-IN a Ink48 por mail.</t>
+          <t>La reserva de Hudson VU (rooftop del propio Ink48) NO es modificable y exige estar en el hotel 19:20, así que el festival queda en la franja 16:30-18:30 — dos horas justas, con salida obligada 20-30 min antes del cierre. La tarde liberada la ocupa ARTHUR AVENUE, la Little Italy real del Bronx — los dos la marcaron 2 y no entraba en ningún día. Desde Harlem es un tiro de subte D (~20 min), y el sábado es EL día: el mercado cierra ~18h y los domingos no abre. Bogotá está a una hora de NYC: no hay jet lag, solo noche corta de avión. PEDIR EARLY CHECK-IN a Ink48 por mail. CAMBIO EN LA LLEGADA: entra el UBER SHUTTLE en vez de AirTrain + NJ Transit + taxi. Para dos personas sale más barato —$41,40 contra $46-52— y sobre todo es UN solo transporte con las valijas en vez de tres, a las siete de la mañana y después de un vuelo nocturno. Lo que se paga: llegan al hotel ~9:10 en vez de ~8:20, y los shuttles salen cada 40-50 minutos mientras que el tren sale cada 10-15. Si migraciones se estira más de lo previsto, EL PLAN VIEJO SIGUE SIENDO MEJOR y está escrito en las alternativas del día.</t>
         </is>
       </c>
     </row>
@@ -32539,7 +32539,7 @@
       </c>
       <c r="C7" s="37" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="D7" s="38" t="inlineStr">
@@ -32561,12 +32561,12 @@
       <c r="A8" s="35" t="n"/>
       <c r="B8" s="36" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="D8" s="38" t="inlineStr">
@@ -32576,7 +32576,7 @@
       </c>
       <c r="E8" s="39" t="inlineStr">
         <is>
-          <t>AirTrain al Newark Airport Station (~10 min). Comprar el ticket en la app MyTix: a bordo cobran $5 extra.</t>
+          <t>Caminar a la zona de recogida del UBER SHUTTLE: Terminal B, Zona 5 — son ~6 min desde la puerta de llegadas. Pedirlo en la app apenas salgan de migraciones.</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr"/>
@@ -32584,16 +32584,16 @@
       <c r="H8" s="41" t="inlineStr"/>
       <c r="I8" s="41" t="inlineStr"/>
     </row>
-    <row r="9" ht="16" customHeight="1">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="35" t="n"/>
       <c r="B9" s="36" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="C9" s="37" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="D9" s="38" t="inlineStr">
@@ -32603,7 +32603,7 @@
       </c>
       <c r="E9" s="39" t="inlineStr">
         <is>
-          <t>NJ Transit EWR → New York Penn Station. $17,25 (incluye el fee del AirTrain). Llega 8:07.</t>
+          <t>★ UBER SHUTTLE EWR → THEATRE DISTRICT (50th St y 8th Ave). $20,70 POR PERSONA = $41,40 los dos, precio fijo y asiento reservado. Llega 8:54. UN SOLO transporte con las valijas, después de un vuelo nocturno: sin AirTrain, sin transbordo en Penn Station y sin taxi. Horarios del sábado desde Terminal B: 7:40 · 7:50 (a Port Authority) · 8:30 · 8:35.</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr"/>
@@ -32615,12 +32615,12 @@
       <c r="A10" s="35" t="n"/>
       <c r="B10" s="36" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="D10" s="38" t="inlineStr">
@@ -32630,14 +32630,10 @@
       </c>
       <c r="E10" s="39" t="inlineStr">
         <is>
-          <t>Taxi/Uber Penn Station → Ink48 ($12-18). Dejar valijas y, si consiguieron el early check-in, ducha y ropa limpia.</t>
-        </is>
-      </c>
-      <c r="F10" s="37" t="inlineStr">
-        <is>
-          <t>Hotel Ink48 (29-31 ago)</t>
-        </is>
-      </c>
+          <t>Bajar en Theatre District y caminar 13 min al Ink48 (50th y 8ª → 48th y 11ª, todo derecho por la 48). Con valijas es lo único que cuesta de esta opción.</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr"/>
       <c r="G10" s="40" t="inlineStr"/>
       <c r="H10" s="41" t="inlineStr"/>
       <c r="I10" s="41" t="inlineStr"/>
@@ -32646,12 +32642,12 @@
       <c r="A11" s="35" t="n"/>
       <c r="B11" s="36" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="C11" s="37" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="D11" s="38" t="inlineStr">
@@ -32661,26 +32657,30 @@
       </c>
       <c r="E11" s="39" t="inlineStr">
         <is>
-          <t>Desayuno rápido en Hell's Kitchen.</t>
-        </is>
-      </c>
-      <c r="F11" s="37" t="inlineStr"/>
+          <t>Ink48: dejar valijas y, si consiguieron el early check-in, ducha y ropa limpia.</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>Hotel Ink48 (29-31 ago)</t>
+        </is>
+      </c>
       <c r="G11" s="40" t="inlineStr"/>
       <c r="H11" s="41" t="inlineStr"/>
       <c r="I11" s="41" t="inlineStr"/>
     </row>
-    <row r="12" ht="16" customHeight="1">
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="35" t="n"/>
       <c r="B12" s="36" t="inlineStr">
         <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="C12" s="37" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="D12" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -32688,7 +32688,7 @@
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
-          <t>Subte A o D express desde 42 St hasta 125 St: 12 minutos y ya están en Harlem.</t>
+          <t>Desayuno RÁPIDO en Hell's Kitchen, sobre la 9ª o la 10ª. Hoy es rápido de verdad: el shuttle llega más tarde que el tren y el subte a Harlem sale 10:00.</t>
         </is>
       </c>
       <c r="F12" s="37" t="inlineStr"/>
@@ -32696,102 +32696,94 @@
       <c r="H12" s="41" t="inlineStr"/>
       <c r="I12" s="41" t="inlineStr"/>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="16" customHeight="1">
       <c r="A13" s="35" t="n"/>
-      <c r="B13" s="42" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="C13" s="43" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="D13" s="44" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E13" s="45" t="inlineStr">
-        <is>
-          <t>Caminata por Harlem: 125th St, Adam Clayton Powell Blvd y las brownstones del Mount Morris Park Historic District.</t>
-        </is>
-      </c>
-      <c r="F13" s="43" t="inlineStr">
-        <is>
-          <t>Harlem</t>
-        </is>
-      </c>
+      <c r="E13" s="39" t="inlineStr">
+        <is>
+          <t>Subte A o D express desde 42 St hasta 125 St: 12 minutos y ya están en Harlem.</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr"/>
       <c r="G13" s="40" t="inlineStr"/>
       <c r="H13" s="41" t="inlineStr"/>
       <c r="I13" s="41" t="inlineStr"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="35" t="n"/>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="C14" s="37" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="D14" s="38" t="inlineStr">
+      <c r="D14" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E14" s="39" t="inlineStr">
-        <is>
-          <t>Bo's Bagels (235 W 116th St) — bagel rápido, sin sentarse mucho: hoy el almuerzo fuerte es italiano en el Bronx.</t>
-        </is>
-      </c>
-      <c r="F14" s="37" t="inlineStr">
-        <is>
-          <t>Bo's Bagels</t>
-        </is>
-      </c>
-      <c r="G14" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~15 min a pie · 1.1 km · estimado</t>
-        </is>
-      </c>
+      <c r="E14" s="45" t="inlineStr">
+        <is>
+          <t>Caminata por Harlem: 125th St, Adam Clayton Powell Blvd y las brownstones del Mount Morris Park Historic District.</t>
+        </is>
+      </c>
+      <c r="F14" s="43" t="inlineStr">
+        <is>
+          <t>Harlem</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr"/>
       <c r="H14" s="41" t="inlineStr"/>
       <c r="I14" s="41" t="inlineStr"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="35" t="n"/>
-      <c r="B15" s="42" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="C15" s="43" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="D15" s="44" t="inlineStr">
+      <c r="D15" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E15" s="45" t="inlineStr">
-        <is>
-          <t>★ STUDIO MUSEUM IN HARLEM — reabrió en noviembre 2025 en el edificio nuevo de David Adjaye. La novedad arquitectónica y curatorial más relevante de la ciudad. Sugerido $16, gratis los domingos. QUÉ HAY AHORA (verificado 27/8): «Fade» en el 4º piso, que CIERRA EL 6 DE SEPTIEMBRE — o sea que esta es la única pasada posible — y «Dreams of This Future», la colección de Peggy Cooper Cafritz. ⚠️ La entrada es con HORARIO ASIGNADO: sacarla antes.</t>
-        </is>
-      </c>
-      <c r="F15" s="43" t="inlineStr">
-        <is>
-          <t>Studio Museum in Harlem</t>
+      <c r="E15" s="39" t="inlineStr">
+        <is>
+          <t>Bo's Bagels (235 W 116th St) — bagel rápido, sin sentarse mucho: hoy el almuerzo fuerte es italiano en el Bronx.</t>
+        </is>
+      </c>
+      <c r="F15" s="37" t="inlineStr">
+        <is>
+          <t>Bo's Bagels</t>
         </is>
       </c>
       <c r="G15" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~14 min a pie · 1.0 km · estimado</t>
+          <t>🚶 ~15 min a pie · 1.1 km · estimado</t>
         </is>
       </c>
       <c r="H15" s="41" t="inlineStr"/>
@@ -32799,159 +32791,167 @@
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="35" t="n"/>
-      <c r="B16" s="36" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="C16" s="37" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="D16" s="38" t="inlineStr">
+      <c r="D16" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E16" s="39" t="inlineStr">
-        <is>
-          <t>Subte D desde 125 St hasta Fordham Rd (~20 min). Alternativa: Metro-North desde Harlem-125th a Fordham, 12 minutos.</t>
-        </is>
-      </c>
-      <c r="F16" s="37" t="inlineStr"/>
-      <c r="G16" s="40" t="inlineStr"/>
+      <c r="E16" s="45" t="inlineStr">
+        <is>
+          <t>★ STUDIO MUSEUM IN HARLEM — reabrió en noviembre 2025 en el edificio nuevo de David Adjaye. La novedad arquitectónica y curatorial más relevante de la ciudad. Sugerido $16, gratis los domingos. QUÉ HAY AHORA (verificado 27/8): «Fade» en el 4º piso, que CIERRA EL 6 DE SEPTIEMBRE — o sea que esta es la única pasada posible — y «Dreams of This Future», la colección de Peggy Cooper Cafritz. ⚠️ La entrada es con HORARIO ASIGNADO: sacarla antes.</t>
+        </is>
+      </c>
+      <c r="F16" s="43" t="inlineStr">
+        <is>
+          <t>Studio Museum in Harlem</t>
+        </is>
+      </c>
+      <c r="G16" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~14 min a pie · 1.0 km · estimado</t>
+        </is>
+      </c>
       <c r="H16" s="41" t="inlineStr"/>
       <c r="I16" s="41" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="35" t="n"/>
-      <c r="B17" s="42" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="C17" s="43" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="D17" s="44" t="inlineStr">
+      <c r="D17" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E17" s="45" t="inlineStr">
-        <is>
-          <t>★★ ARTHUR AVENUE (Belmont) — la Little Italy real: carnicerías, panaderos de 1918 y el enclave albanés. Almuerzo: el sándwich de mozzarella fresca de Casa Della Mozzarella (E 187th St) y el Arthur Avenue Retail Market con Mike's Deli adentro. El mercado cierra ~18h y los DOMINGOS no abre: hoy es el único día del viaje que sirve.</t>
-        </is>
-      </c>
-      <c r="F17" s="43" t="inlineStr">
-        <is>
-          <t>Arthur Avenue (Belmont)</t>
-        </is>
-      </c>
+      <c r="E17" s="39" t="inlineStr">
+        <is>
+          <t>Subte D desde 125 St hasta Fordham Rd (~20 min). Alternativa: Metro-North desde Harlem-125th a Fordham, 12 minutos.</t>
+        </is>
+      </c>
+      <c r="F17" s="37" t="inlineStr"/>
       <c r="G17" s="40" t="inlineStr"/>
       <c r="H17" s="41" t="inlineStr"/>
       <c r="I17" s="41" t="inlineStr"/>
     </row>
-    <row r="18" ht="16" customHeight="1">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="35" t="n"/>
-      <c r="B18" s="36" t="inlineStr">
+      <c r="B18" s="42" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
         <is>
           <t>15:40</t>
         </is>
       </c>
-      <c r="C18" s="37" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="D18" s="38" t="inlineStr">
+      <c r="D18" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E18" s="39" t="inlineStr">
-        <is>
-          <t>Subte D desde Fordham Rd de vuelta a 125 St (~25 min) y caminar a Marcus Garvey Park.</t>
-        </is>
-      </c>
-      <c r="F18" s="37" t="inlineStr"/>
+      <c r="E18" s="45" t="inlineStr">
+        <is>
+          <t>★★ ARTHUR AVENUE (Belmont) — la Little Italy real: carnicerías, panaderos de 1918 y el enclave albanés. Almuerzo: el sándwich de mozzarella fresca de Casa Della Mozzarella (E 187th St) y el Arthur Avenue Retail Market con Mike's Deli adentro. El mercado cierra ~18h y los DOMINGOS no abre: hoy es el único día del viaje que sirve.</t>
+        </is>
+      </c>
+      <c r="F18" s="43" t="inlineStr">
+        <is>
+          <t>Arthur Avenue (Belmont)</t>
+        </is>
+      </c>
       <c r="G18" s="40" t="inlineStr"/>
       <c r="H18" s="41" t="inlineStr"/>
       <c r="I18" s="41" t="inlineStr"/>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="16" customHeight="1">
       <c r="A19" s="35" t="n"/>
-      <c r="B19" s="42" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="C19" s="43" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="D19" s="44" t="inlineStr">
+      <c r="D19" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E19" s="45" t="inlineStr">
-        <is>
-          <t>★★ CHARLIE PARKER JAZZ FESTIVAL — VERIFICADO el 27/8: la música va de 14:00 a 19:00 en Marcus Garvey Park, y el cartel es JOSHUA REDMAN de cierre, con Nat Adderley Jr., Catherine Russell, Nicole Glover y DJ Kultured Child. Ustedes entran 16:30 con la franja 16:30-18:30: la reserva de Hudson VU no es modificable y manda. ⚠️ SALIDA OBLIGADA 18:30 — Redman cierra, así que van a ver el arranque de su set y se pierden el final. Si quieren verlo entero hay que recortar Arthur Avenue y llegar al parque a las 15:30.</t>
-        </is>
-      </c>
-      <c r="F19" s="43" t="inlineStr">
-        <is>
-          <t>Charlie Parker Jazz Festival - Harlem</t>
-        </is>
-      </c>
+      <c r="E19" s="39" t="inlineStr">
+        <is>
+          <t>Subte D desde Fordham Rd de vuelta a 125 St (~25 min) y caminar a Marcus Garvey Park.</t>
+        </is>
+      </c>
+      <c r="F19" s="37" t="inlineStr"/>
       <c r="G19" s="40" t="inlineStr"/>
       <c r="H19" s="41" t="inlineStr"/>
       <c r="I19" s="41" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="35" t="n"/>
-      <c r="B20" s="36" t="inlineStr">
+      <c r="B20" s="42" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C20" s="43" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="C20" s="37" t="inlineStr">
-        <is>
-          <t>19:20</t>
-        </is>
-      </c>
-      <c r="D20" s="38" t="inlineStr">
+      <c r="D20" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E20" s="39" t="inlineStr">
-        <is>
-          <t>UBER desde Marcus Garvey Park al Ink48 (~20-25 min un sábado a la tarde, ~$25-30). Es lo que garantiza llegar 19:00-19:05. Plan B en subte: salir 18:10, 2/3 desde 125-Lenox hasta Times Sq y 15 min a pie — total ~45 min.</t>
-        </is>
-      </c>
-      <c r="F20" s="37" t="inlineStr"/>
+      <c r="E20" s="45" t="inlineStr">
+        <is>
+          <t>★★ CHARLIE PARKER JAZZ FESTIVAL — VERIFICADO el 27/8: la música va de 14:00 a 19:00 en Marcus Garvey Park, y el cartel es JOSHUA REDMAN de cierre, con Nat Adderley Jr., Catherine Russell, Nicole Glover y DJ Kultured Child. Ustedes entran 16:30 con la franja 16:30-18:30: la reserva de Hudson VU no es modificable y manda. ⚠️ SALIDA OBLIGADA 18:30 — Redman cierra, así que van a ver el arranque de su set y se pierden el final. Si quieren verlo entero hay que recortar Arthur Avenue y llegar al parque a las 15:30.</t>
+        </is>
+      </c>
+      <c r="F20" s="43" t="inlineStr">
+        <is>
+          <t>Charlie Parker Jazz Festival - Harlem</t>
+        </is>
+      </c>
       <c r="G20" s="40" t="inlineStr"/>
       <c r="H20" s="41" t="inlineStr"/>
       <c r="I20" s="41" t="inlineStr"/>
     </row>
-    <row r="21" ht="16" customHeight="1">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="35" t="n"/>
       <c r="B21" s="36" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C21" s="37" t="inlineStr">
+        <is>
           <t>19:20</t>
         </is>
       </c>
-      <c r="C21" s="37" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
       <c r="D21" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -32959,7 +32959,7 @@
       </c>
       <c r="E21" s="39" t="inlineStr">
         <is>
-          <t>EN EL HOTEL — margen para dejar cosas y subir.</t>
+          <t>UBER desde Marcus Garvey Park al Ink48 (~20-25 min un sábado a la tarde, ~$25-30). Es lo que garantiza llegar 19:00-19:05. Plan B en subte: salir 18:10, 2/3 desde 125-Lenox hasta Times Sq y 15 min a pie — total ~45 min.</t>
         </is>
       </c>
       <c r="F21" s="37" t="inlineStr"/>
@@ -32967,166 +32967,162 @@
       <c r="H21" s="41" t="inlineStr"/>
       <c r="I21" s="41" t="inlineStr"/>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="16" customHeight="1">
       <c r="A22" s="35" t="n"/>
-      <c r="B22" s="42" t="inlineStr">
+      <c r="B22" s="36" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="C22" s="37" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="C22" s="43" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="D22" s="44" t="inlineStr">
+      <c r="D22" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E22" s="45" t="inlineStr">
-        <is>
-          <t>★★ HUDSON VU — drinks y comida, RESERVA NO MODIFICABLE, en el rooftop de SU PROPIO hotel (Ink48). La mesa es de MÁXIMO 90 MINUTOS: cierran ~21:00. Pedir sin vueltas y disfrutar la vista — lo que sigue está a 8 cuadras.</t>
-        </is>
-      </c>
-      <c r="F22" s="43" t="inlineStr">
-        <is>
-          <t>Hotel Ink48 (29-31 ago)</t>
-        </is>
-      </c>
+      <c r="E22" s="39" t="inlineStr">
+        <is>
+          <t>EN EL HOTEL — margen para dejar cosas y subir.</t>
+        </is>
+      </c>
+      <c r="F22" s="37" t="inlineStr"/>
       <c r="G22" s="40" t="inlineStr"/>
       <c r="H22" s="41" t="inlineStr"/>
       <c r="I22" s="41" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="35" t="n"/>
-      <c r="B23" s="36" t="inlineStr">
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C23" s="37" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="D23" s="38" t="inlineStr">
+      <c r="D23" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E23" s="39" t="inlineStr">
-        <is>
-          <t>Caminata Ink48 → Birdland (315 W 44th): 8 cuadras, 10-12 min. Llegan ~21:15, justo para las puertas del set de las 21:30.</t>
-        </is>
-      </c>
-      <c r="F23" s="37" t="inlineStr"/>
+      <c r="E23" s="45" t="inlineStr">
+        <is>
+          <t>★★ HUDSON VU — drinks y comida, RESERVA NO MODIFICABLE, en el rooftop de SU PROPIO hotel (Ink48). La mesa es de MÁXIMO 90 MINUTOS: cierran ~21:00. Pedir sin vueltas y disfrutar la vista — lo que sigue está a 8 cuadras.</t>
+        </is>
+      </c>
+      <c r="F23" s="43" t="inlineStr">
+        <is>
+          <t>Hotel Ink48 (29-31 ago)</t>
+        </is>
+      </c>
       <c r="G23" s="40" t="inlineStr"/>
       <c r="H23" s="41" t="inlineStr"/>
       <c r="I23" s="41" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="35" t="n"/>
-      <c r="B24" s="42" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C24" s="43" t="inlineStr"/>
-      <c r="D24" s="44" t="inlineStr">
+      <c r="D24" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E24" s="45" t="inlineStr">
-        <is>
-          <t>★★ BIRDLAND — set de las 21:30: DAVID DEJESUS &amp; THE BOPTET, 'Celebrating Charlie Parker'. El 29/8 es el CUMPLEAÑOS de Bird y Birdland es el club que lleva su nombre: el día cierra en círculo — festival Charlie Parker de día, tributo a Parker de noche. RESERVAR en birdlandjazz.com (cartelera ya publicada). Si prefieren más tarde: Makoto Ozone Trio a las 22:30 en el mismo club. Y si el cansancio de un día que empezó 6 AM en un avión manda, saltearlo no es pecado.</t>
-        </is>
-      </c>
-      <c r="F24" s="43" t="inlineStr">
-        <is>
-          <t>Birdland</t>
-        </is>
-      </c>
+      <c r="E24" s="39" t="inlineStr">
+        <is>
+          <t>Caminata Ink48 → Birdland (315 W 44th): 8 cuadras, 10-12 min. Llegan ~21:15, justo para las puertas del set de las 21:30.</t>
+        </is>
+      </c>
+      <c r="F24" s="37" t="inlineStr"/>
       <c r="G24" s="40" t="inlineStr"/>
       <c r="H24" s="41" t="inlineStr"/>
       <c r="I24" s="41" t="inlineStr"/>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="46" t="inlineStr">
-        <is>
-          <t>ALTERNATIVA / OJO:  Si llegan fundidos del vuelo, ARTHUR AVENUE es lo primero que se cae: salteenla, descansen en el hotel 13-16h y lleguen al festival 16:30. El festival y la reserva de Hudson VU son lo irrenunciable del día. OJO: Bill's Place se movió al VIERNES 4/9 por esta reserva — el set del sábado ya no aplica. // Sobre agregar cosas AL LUNES con este recorte: el lunes ya está lleno de 8:45 a 22:48 con dos anclas fijas (Ford Foundation solo abre días hábiles y el 9/11 gratis es 17:30-19:00) — no hay hueco real. El tiempo que libera el festival es del SÁBADO, y Arthur Avenue era lo mejor que quedaba sin agendar de lo que marcaron los dos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="33" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="35" t="n"/>
+      <c r="B25" s="42" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C25" s="43" t="inlineStr"/>
+      <c r="D25" s="44" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E25" s="45" t="inlineStr">
+        <is>
+          <t>★★ BIRDLAND — set de las 21:30: DAVID DEJESUS &amp; THE BOPTET, 'Celebrating Charlie Parker'. El 29/8 es el CUMPLEAÑOS de Bird y Birdland es el club que lleva su nombre: el día cierra en círculo — festival Charlie Parker de día, tributo a Parker de noche. RESERVAR en birdlandjazz.com (cartelera ya publicada). Si prefieren más tarde: Makoto Ozone Trio a las 22:30 en el mismo club. Y si el cansancio de un día que empezó 6 AM en un avión manda, saltearlo no es pecado.</t>
+        </is>
+      </c>
+      <c r="F25" s="43" t="inlineStr">
+        <is>
+          <t>Birdland</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="inlineStr"/>
+      <c r="H25" s="41" t="inlineStr"/>
+      <c r="I25" s="41" t="inlineStr"/>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="46" t="inlineStr">
+        <is>
+          <t>ALTERNATIVA / OJO:  PLAN VIEJO, POR SI EL SHUTTLE NO SIRVE (y es el que conviene si salen tarde de migraciones): AirTrain hasta Newark Airport Station (~10 min, ticket en la app MyTix — a bordo cobran $5 extra) y NJ Transit hasta Penn Station, $17,25 por persona con el AirTrain incluido. Trenes del sábado desde EWR: 6:00, 6:07, 6:43, 7:04, 7:15, 7:25, 7:39 — o sea uno cada diez o quince minutos, que es la ventaja real. De Penn al hotel, taxi de $12-18. Llegan 8:15-8:30, casi una hora antes que con el shuttle. // Si llegan fundidos del vuelo, ARTHUR AVENUE es lo primero que se cae: salteenla, descansen en el hotel 13-16h y lleguen al festival 16:30. El festival y la reserva de Hudson VU son lo irrenunciable del día. OJO: Bill's Place se movió al VIERNES 4/9 por esta reserva — el set del sábado ya no aplica. // Sobre agregar cosas AL LUNES con este recorte: el lunes ya está lleno de 8:45 a 22:48 con dos anclas fijas (Ford Foundation solo abre días hábiles y el 9/11 gratis es 17:30-19:00) — no hay hueco real. El tiempo que libera el festival es del SÁBADO, y Arthur Avenue era lo mejor que quedaba sin agendar de lo que marcaron los dos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="33" t="inlineStr">
         <is>
           <t>DÍA 2 · Domingo 30/08 · Lower East Side, Chinatown y el Brooklyn Bridge a pie  —  base: Ink48  ·  Ambos</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="34" t="inlineStr">
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="34" t="inlineStr">
         <is>
           <t>SALIÓ el día 2 del festival Charlie Parker: los dos lo marcaron 0 en la app (ver dos días seguidos de festival no les cerró). La mañana del Lower East Side queda igual — el domingo sigue siendo el ÚNICO día que sirve para Eldridge Street, que cierra los sábados. La tarde liberada la ocupa el CRUCE DEL BROOKLYN BRIDGE A PIE, que no estaba en ningún día del viaje y desde Chinatown se arranca caminando: la entrada peatonal está en City Hall, a diez minutos de Mott St.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="35" t="n"/>
-      <c r="B29" s="36" t="inlineStr">
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="35" t="n"/>
+      <c r="B30" s="36" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="C29" s="37" t="inlineStr">
+      <c r="C30" s="37" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="D29" s="38" t="inlineStr">
+      <c r="D30" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E29" s="39" t="inlineStr">
+      <c r="E30" s="39" t="inlineStr">
         <is>
           <t>Desayuno rápido y subte F hasta 2 Av.</t>
         </is>
       </c>
-      <c r="F29" s="37" t="inlineStr"/>
-      <c r="G29" s="40" t="inlineStr"/>
-      <c r="H29" s="41" t="inlineStr"/>
-      <c r="I29" s="41" t="inlineStr"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="35" t="n"/>
-      <c r="B30" s="42" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="C30" s="43" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="D30" s="44" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="E30" s="45" t="inlineStr">
-        <is>
-          <t>★ Russ &amp; Daughters — appetizing store de 1914, cuarta generación de la misma familia. Salmón curado cortado a mano sobre bagel. El mostrador es mejor experiencia que el café de al lado.</t>
-        </is>
-      </c>
-      <c r="F30" s="43" t="inlineStr">
-        <is>
-          <t>Russ &amp; Daughters</t>
-        </is>
-      </c>
+      <c r="F30" s="37" t="inlineStr"/>
       <c r="G30" s="40" t="inlineStr"/>
       <c r="H30" s="41" t="inlineStr"/>
       <c r="I30" s="41" t="inlineStr"/>
@@ -33135,14 +33131,14 @@
       <c r="A31" s="35" t="n"/>
       <c r="B31" s="42" t="inlineStr">
         <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C31" s="43" t="inlineStr">
+        <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="C31" s="43" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="D31" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -33150,52 +33146,48 @@
       </c>
       <c r="E31" s="45" t="inlineStr">
         <is>
-          <t>★ Museum at Eldridge Street — sinagoga de 1887 restaurada por $20 millones, con un rosetón nuevo de Kiki Smith. Que hoy esté en el medio de Chinatown es la mitad del punto. CIERRA LOS SÁBADOS: hoy es el día.</t>
+          <t>★ Russ &amp; Daughters — appetizing store de 1914, cuarta generación de la misma familia. Salmón curado cortado a mano sobre bagel. El mostrador es mejor experiencia que el café de al lado.</t>
         </is>
       </c>
       <c r="F31" s="43" t="inlineStr">
         <is>
-          <t>Museum at Eldridge Street</t>
-        </is>
-      </c>
-      <c r="G31" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~20 min a pie (1.3 km) o 🚇 ~15 min · estimado</t>
-        </is>
-      </c>
+          <t>Russ &amp; Daughters</t>
+        </is>
+      </c>
+      <c r="G31" s="40" t="inlineStr"/>
       <c r="H31" s="41" t="inlineStr"/>
       <c r="I31" s="41" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="35" t="n"/>
-      <c r="B32" s="36" t="inlineStr">
+      <c r="B32" s="42" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C32" s="43" t="inlineStr">
         <is>
           <t>11:45</t>
         </is>
       </c>
-      <c r="C32" s="37" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="D32" s="38" t="inlineStr">
+      <c r="D32" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E32" s="39" t="inlineStr">
-        <is>
-          <t>Essex Market — mercado municipal desde 1940. Sigue teniendo carniceros y pescaderos de verdad, no solo puestos para turistas.</t>
-        </is>
-      </c>
-      <c r="F32" s="37" t="inlineStr">
-        <is>
-          <t>Essex Market</t>
+      <c r="E32" s="45" t="inlineStr">
+        <is>
+          <t>★ Museum at Eldridge Street — sinagoga de 1887 restaurada por $20 millones, con un rosetón nuevo de Kiki Smith. Que hoy esté en el medio de Chinatown es la mitad del punto. CIERRA LOS SÁBADOS: hoy es el día.</t>
+        </is>
+      </c>
+      <c r="F32" s="43" t="inlineStr">
+        <is>
+          <t>Museum at Eldridge Street</t>
         </is>
       </c>
       <c r="G32" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~11 min a pie · 0.8 km · estimado</t>
+          <t>🚶 ~20 min a pie (1.3 km) o 🚇 ~15 min · estimado</t>
         </is>
       </c>
       <c r="H32" s="41" t="inlineStr"/>
@@ -33205,14 +33197,14 @@
       <c r="A33" s="35" t="n"/>
       <c r="B33" s="36" t="inlineStr">
         <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C33" s="37" t="inlineStr">
+        <is>
           <t>12:45</t>
         </is>
       </c>
-      <c r="C33" s="37" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="D33" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -33220,15 +33212,19 @@
       </c>
       <c r="E33" s="39" t="inlineStr">
         <is>
-          <t>Caminata por el Lower East Side: Orchard, Ludlow, Rivington. Tres capas de inmigración en la misma cuadra.</t>
+          <t>Essex Market — mercado municipal desde 1940. Sigue teniendo carniceros y pescaderos de verdad, no solo puestos para turistas.</t>
         </is>
       </c>
       <c r="F33" s="37" t="inlineStr">
         <is>
-          <t>Lower East Side</t>
-        </is>
-      </c>
-      <c r="G33" s="40" t="inlineStr"/>
+          <t>Essex Market</t>
+        </is>
+      </c>
+      <c r="G33" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~11 min a pie · 0.8 km · estimado</t>
+        </is>
+      </c>
       <c r="H33" s="41" t="inlineStr"/>
       <c r="I33" s="41" t="inlineStr"/>
     </row>
@@ -33236,14 +33232,14 @@
       <c r="A34" s="35" t="n"/>
       <c r="B34" s="36" t="inlineStr">
         <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C34" s="37" t="inlineStr">
+        <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="C34" s="37" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="D34" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -33251,19 +33247,15 @@
       </c>
       <c r="E34" s="39" t="inlineStr">
         <is>
-          <t>Almuerzo en Chinatown: Mott St y las pescaderías de la calle. El paisaje urbano es el plato fuerte.</t>
+          <t>Caminata por el Lower East Side: Orchard, Ludlow, Rivington. Tres capas de inmigración en la misma cuadra.</t>
         </is>
       </c>
       <c r="F34" s="37" t="inlineStr">
         <is>
-          <t>Chinatown (Manhattan)</t>
-        </is>
-      </c>
-      <c r="G34" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~14 min a pie · 1.0 km · estimado</t>
-        </is>
-      </c>
+          <t>Lower East Side</t>
+        </is>
+      </c>
+      <c r="G34" s="40" t="inlineStr"/>
       <c r="H34" s="41" t="inlineStr"/>
       <c r="I34" s="41" t="inlineStr"/>
     </row>
@@ -33271,14 +33263,14 @@
       <c r="A35" s="35" t="n"/>
       <c r="B35" s="36" t="inlineStr">
         <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="C35" s="37" t="inlineStr">
+        <is>
           <t>14:15</t>
         </is>
       </c>
-      <c r="C35" s="37" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="D35" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -33286,84 +33278,88 @@
       </c>
       <c r="E35" s="39" t="inlineStr">
         <is>
-          <t>Columbus Park (tai chi y partidas de xiangqi) y Doyers Street, la cuadra torcida que era 'the Bloody Angle'. Diez minutos y de ahí se sale caminando hacia City Hall.</t>
-        </is>
-      </c>
-      <c r="F35" s="37" t="inlineStr"/>
-      <c r="G35" s="40" t="inlineStr"/>
+          <t>Almuerzo en Chinatown: Mott St y las pescaderías de la calle. El paisaje urbano es el plato fuerte.</t>
+        </is>
+      </c>
+      <c r="F35" s="37" t="inlineStr">
+        <is>
+          <t>Chinatown (Manhattan)</t>
+        </is>
+      </c>
+      <c r="G35" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~14 min a pie · 1.0 km · estimado</t>
+        </is>
+      </c>
       <c r="H35" s="41" t="inlineStr"/>
       <c r="I35" s="41" t="inlineStr"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="35" t="n"/>
-      <c r="B36" s="42" t="inlineStr">
+      <c r="B36" s="36" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="C36" s="37" t="inlineStr">
         <is>
           <t>14:45</t>
         </is>
       </c>
-      <c r="C36" s="43" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D36" s="44" t="inlineStr">
+      <c r="D36" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E36" s="45" t="inlineStr">
-        <is>
-          <t>★★ CRUZAR EL BROOKLYN BRIDGE A PIE — entrada peatonal frente a City Hall. 30-45 minutos hasta Brooklyn con paradas de foto: el skyline de Lower Manhattan de un lado y el Manhattan Bridge del otro. GRATIS y es una de las cosas que un first-timer no debería saltearse.</t>
-        </is>
-      </c>
-      <c r="F36" s="43" t="inlineStr"/>
+      <c r="E36" s="39" t="inlineStr">
+        <is>
+          <t>Columbus Park (tai chi y partidas de xiangqi) y Doyers Street, la cuadra torcida que era 'the Bloody Angle'. Diez minutos y de ahí se sale caminando hacia City Hall.</t>
+        </is>
+      </c>
+      <c r="F36" s="37" t="inlineStr"/>
       <c r="G36" s="40" t="inlineStr"/>
       <c r="H36" s="41" t="inlineStr"/>
       <c r="I36" s="41" t="inlineStr"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="35" t="n"/>
-      <c r="B37" s="36" t="inlineStr">
+      <c r="B37" s="42" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="C37" s="43" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="C37" s="37" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="D37" s="38" t="inlineStr">
+      <c r="D37" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E37" s="39" t="inlineStr">
-        <is>
-          <t>Bajar en DUMBO: la foto del Manhattan Bridge encuadrado en Washington St, el waterfront, y una parada en TIME OUT MARKET (está ahí mismo y JP lo marcó 2): un vermut con el skyline de frente. OJO: el sábado 5 vuelven de día — no repetir de más.</t>
-        </is>
-      </c>
-      <c r="F37" s="37" t="inlineStr">
-        <is>
-          <t>DUMBO</t>
-        </is>
-      </c>
+      <c r="E37" s="45" t="inlineStr">
+        <is>
+          <t>★★ CRUZAR EL BROOKLYN BRIDGE A PIE — entrada peatonal frente a City Hall. 30-45 minutos hasta Brooklyn con paradas de foto: el skyline de Lower Manhattan de un lado y el Manhattan Bridge del otro. GRATIS y es una de las cosas que un first-timer no debería saltearse.</t>
+        </is>
+      </c>
+      <c r="F37" s="43" t="inlineStr"/>
       <c r="G37" s="40" t="inlineStr"/>
       <c r="H37" s="41" t="inlineStr"/>
       <c r="I37" s="41" t="inlineStr"/>
     </row>
-    <row r="38" ht="16" customHeight="1">
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="35" t="n"/>
       <c r="B38" s="36" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C38" s="37" t="inlineStr">
+        <is>
           <t>17:05</t>
         </is>
       </c>
-      <c r="C38" s="37" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="D38" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -33371,135 +33367,131 @@
       </c>
       <c r="E38" s="39" t="inlineStr">
         <is>
-          <t>Subte A/C desde High St hasta Fulton St (2 paradas, ~10 min) y 5 min a pie hasta Dey St.</t>
-        </is>
-      </c>
-      <c r="F38" s="37" t="inlineStr"/>
+          <t>Bajar en DUMBO: la foto del Manhattan Bridge encuadrado en Washington St, el waterfront, y una parada en TIME OUT MARKET (está ahí mismo y JP lo marcó 2): un vermut con el skyline de frente. OJO: el sábado 5 vuelven de día — no repetir de más.</t>
+        </is>
+      </c>
+      <c r="F38" s="37" t="inlineStr">
+        <is>
+          <t>DUMBO</t>
+        </is>
+      </c>
       <c r="G38" s="40" t="inlineStr"/>
       <c r="H38" s="41" t="inlineStr"/>
       <c r="I38" s="41" t="inlineStr"/>
     </row>
-    <row r="39" ht="30" customHeight="1">
+    <row r="39" ht="16" customHeight="1">
       <c r="A39" s="35" t="n"/>
-      <c r="B39" s="42" t="inlineStr">
+      <c r="B39" s="36" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="C39" s="37" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="C39" s="43" t="inlineStr">
-        <is>
-          <t>18:50</t>
-        </is>
-      </c>
-      <c r="D39" s="44" t="inlineStr">
+      <c r="D39" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E39" s="45" t="inlineStr">
-        <is>
-          <t>★★ MERCER LABS (21 Dey St, frente al Oculus) — 15 salas inmersivas de arte y tecnología de Roy Nachum: proyecciones, sonido espacial, salas interactivas, a su ritmo. Hasta $57 según franja; TIMED TICKET por Fever, reservar el slot de 17:30 antes de viajar. Los domingos abre hasta las 22.</t>
-        </is>
-      </c>
-      <c r="F39" s="43" t="inlineStr">
-        <is>
-          <t>Mercer Labs — Museum of Art and Technology</t>
-        </is>
-      </c>
+      <c r="E39" s="39" t="inlineStr">
+        <is>
+          <t>Subte A/C desde High St hasta Fulton St (2 paradas, ~10 min) y 5 min a pie hasta Dey St.</t>
+        </is>
+      </c>
+      <c r="F39" s="37" t="inlineStr"/>
       <c r="G39" s="40" t="inlineStr"/>
       <c r="H39" s="41" t="inlineStr"/>
       <c r="I39" s="41" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="35" t="n"/>
-      <c r="B40" s="36" t="inlineStr">
+      <c r="B40" s="42" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C40" s="43" t="inlineStr">
         <is>
           <t>18:50</t>
         </is>
       </c>
-      <c r="C40" s="37" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="D40" s="38" t="inlineStr">
+      <c r="D40" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E40" s="39" t="inlineStr">
-        <is>
-          <t>Caminar a The Crown: 1,6 km derecho por Park Row hacia Bowery (~20 min) — o R/W City Hall → Canal St si llueve.</t>
-        </is>
-      </c>
-      <c r="F40" s="37" t="inlineStr"/>
+      <c r="E40" s="45" t="inlineStr">
+        <is>
+          <t>★★ MERCER LABS (21 Dey St, frente al Oculus) — 15 salas inmersivas de arte y tecnología de Roy Nachum: proyecciones, sonido espacial, salas interactivas, a su ritmo. Hasta $57 según franja; TIMED TICKET por Fever, reservar el slot de 17:30 antes de viajar. Los domingos abre hasta las 22.</t>
+        </is>
+      </c>
+      <c r="F40" s="43" t="inlineStr">
+        <is>
+          <t>Mercer Labs — Museum of Art and Technology</t>
+        </is>
+      </c>
       <c r="G40" s="40" t="inlineStr"/>
       <c r="H40" s="41" t="inlineStr"/>
       <c r="I40" s="41" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="35" t="n"/>
-      <c r="B41" s="42" t="inlineStr">
+      <c r="B41" s="36" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="C41" s="37" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="C41" s="43" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="D41" s="44" t="inlineStr">
+      <c r="D41" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E41" s="45" t="inlineStr">
-        <is>
-          <t>★ The Crown (50 Bowery, piso 21) — rooftop sin cover, EN EL ATARDECER (~19:27): el Manhattan Bridge que acaban de cruzar se enciende de frente mientras cae el sol. Es el ángulo que no da ningún observatorio pago — luz, atardecer y noche en un solo trago.</t>
-        </is>
-      </c>
-      <c r="F41" s="43" t="inlineStr">
-        <is>
-          <t>The Crown (50 Bowery)</t>
-        </is>
-      </c>
+      <c r="E41" s="39" t="inlineStr">
+        <is>
+          <t>Caminar a The Crown: 1,6 km derecho por Park Row hacia Bowery (~20 min) — o R/W City Hall → Canal St si llueve.</t>
+        </is>
+      </c>
+      <c r="F41" s="37" t="inlineStr"/>
       <c r="G41" s="40" t="inlineStr"/>
       <c r="H41" s="41" t="inlineStr"/>
       <c r="I41" s="41" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="35" t="n"/>
-      <c r="B42" s="36" t="inlineStr">
+      <c r="B42" s="42" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C42" s="43" t="inlineStr">
         <is>
           <t>20:45</t>
         </is>
       </c>
-      <c r="C42" s="37" t="inlineStr">
-        <is>
-          <t>22:15</t>
-        </is>
-      </c>
-      <c r="D42" s="38" t="inlineStr">
+      <c r="D42" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E42" s="39" t="inlineStr">
-        <is>
-          <t>Cena en el East Village / LES: Katz's abre hasta tarde (a esta hora la cola del domingo ya bajó).</t>
-        </is>
-      </c>
-      <c r="F42" s="37" t="inlineStr">
-        <is>
-          <t>Katz's Delicatessen</t>
-        </is>
-      </c>
-      <c r="G42" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~20 min a pie (1.3 km) o 🚇 ~15 min · estimado</t>
-        </is>
-      </c>
+      <c r="E42" s="45" t="inlineStr">
+        <is>
+          <t>★ The Crown (50 Bowery, piso 21) — rooftop sin cover, EN EL ATARDECER (~19:27): el Manhattan Bridge que acaban de cruzar se enciende de frente mientras cae el sol. Es el ángulo que no da ningún observatorio pago — luz, atardecer y noche en un solo trago.</t>
+        </is>
+      </c>
+      <c r="F42" s="43" t="inlineStr">
+        <is>
+          <t>The Crown (50 Bowery)</t>
+        </is>
+      </c>
+      <c r="G42" s="40" t="inlineStr"/>
       <c r="H42" s="41" t="inlineStr"/>
       <c r="I42" s="41" t="inlineStr"/>
     </row>
@@ -33507,10 +33499,14 @@
       <c r="A43" s="35" t="n"/>
       <c r="B43" s="36" t="inlineStr">
         <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C43" s="37" t="inlineStr">
+        <is>
           <t>22:15</t>
         </is>
       </c>
-      <c r="C43" s="37" t="inlineStr"/>
       <c r="D43" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -33518,113 +33514,117 @@
       </c>
       <c r="E43" s="39" t="inlineStr">
         <is>
-          <t>Opcional: Nublu (Avenue C) — jazz experimental y afrobeat hasta tarde. A 14 minutos A PIE de Katz's. Lo marcaron 2 los dos.</t>
+          <t>Cena en el East Village / LES: Katz's abre hasta tarde (a esta hora la cola del domingo ya bajó).</t>
         </is>
       </c>
       <c r="F43" s="37" t="inlineStr">
         <is>
-          <t>Nublu</t>
+          <t>Katz's Delicatessen</t>
         </is>
       </c>
       <c r="G43" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~14 min a pie · 1.1 km · estimado</t>
+          <t>🚶 ~20 min a pie (1.3 km) o 🚇 ~15 min · estimado</t>
         </is>
       </c>
       <c r="H43" s="41" t="inlineStr"/>
       <c r="I43" s="41" t="inlineStr"/>
     </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="46" t="inlineStr">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="35" t="n"/>
+      <c r="B44" s="36" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="C44" s="37" t="inlineStr"/>
+      <c r="D44" s="38" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E44" s="39" t="inlineStr">
+        <is>
+          <t>Opcional: Nublu (Avenue C) — jazz experimental y afrobeat hasta tarde. A 14 minutos A PIE de Katz's. Lo marcaron 2 los dos.</t>
+        </is>
+      </c>
+      <c r="F44" s="37" t="inlineStr">
+        <is>
+          <t>Nublu</t>
+        </is>
+      </c>
+      <c r="G44" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~14 min a pie · 1.1 km · estimado</t>
+        </is>
+      </c>
+      <c r="H44" s="41" t="inlineStr"/>
+      <c r="I44" s="41" t="inlineStr"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="46" t="inlineStr">
         <is>
           <t>ALTERNATIVA / OJO:  Si cambian de idea con el festival: Ravi Coltrane toca GRATIS en Tompkins Square de 15 a 19h, a cinco cuadras del almuerzo — pueden ir un rato y cruzar el puente otro día. Y ojo: hoy es la ÚLTIMA función de Moulin Rouge! en Broadway, si la quieren hay que decidir ya. // El cruce del puente conviene NO hacerlo más tarde: después de las 16h de un domingo de verano la pasarela se llena.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="33" t="inlineStr">
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="33" t="inlineStr">
         <is>
           <t>DÍA 3 · Lunes 31/08 · JP solo · Midtown total: MoMA, Top of the Rock y Birdland  —  base: Ink48 → JGStay SoHo (las valijas viajan con Thais)  ·  Solo JP</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="34" t="inlineStr">
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="34" t="inlineStr">
         <is>
           <t>⚠️ DÍA DE JP SOLO. Thais viaja temprano a New Jersey porque EMPIEZA A TRABAJAR — trabaja del 31 de agosto al 3 de septiembre y no participa de nada de NYC en esos días. Ella hace el checkout y se lleva las dos valijas, así que JP arranca libre y sin equipaje desde las 8. El lunes, que suele ser el peor día en NYC, acá es el mejor: el lobby del Chrysler y el Ford Foundation SOLO abren días hábiles, y Birdland tiene su programa de lunes. El MoMA y Top of the Rock encajan justo hoy porque Thais los marcó 0. El 9/11 se MOVIÓ al jueves para hacerlo completo (memorial + museo + One World Observatory en una sola bajada) — se paga la entrada que el lunes era gratis, pero el circuito queda entero y este día gana el observatorio con luz de tarde. CERRADOS hoy: Morgan, Noguchi, Brooklyn Museum, Studio Museum, Transit Museum. Y LA GRAN NOVEDAD: JP ya no duerme en New Jersey — la noche termina en el JGStay SoHo, y la vuelta nocturna a NJ quedó reducida a UNA sola (el miércoles).</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="35" t="n"/>
-      <c r="B48" s="36" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="C48" s="37" t="inlineStr">
-        <is>
-          <t>08:10</t>
-        </is>
-      </c>
-      <c r="D48" s="38" t="inlineStr">
-        <is>
-          <t>Thais</t>
-        </is>
-      </c>
-      <c r="E48" s="39" t="inlineStr">
-        <is>
-          <t>THAIS: checkout de Ink48 y tren temprano a New Jersey con LAS DOS valijas — hoy EMPIEZA A TRABAJAR. No participa de nada de este día. JP sale solo con su bolso de dos noches.</t>
-        </is>
-      </c>
-      <c r="F48" s="37" t="inlineStr">
-        <is>
-          <t>Hotel Ink48 (29-31 ago)</t>
-        </is>
-      </c>
-      <c r="G48" s="40" t="inlineStr"/>
-      <c r="H48" s="41" t="inlineStr"/>
-      <c r="I48" s="41" t="inlineStr"/>
-    </row>
-    <row r="49" ht="16" customHeight="1">
+    <row r="49" ht="30" customHeight="1">
       <c r="A49" s="35" t="n"/>
       <c r="B49" s="36" t="inlineStr">
         <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C49" s="37" t="inlineStr">
+        <is>
           <t>08:10</t>
         </is>
       </c>
-      <c r="C49" s="37" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
       <c r="D49" s="38" t="inlineStr">
         <is>
-          <t>Solo JP</t>
+          <t>Thais</t>
         </is>
       </c>
       <c r="E49" s="39" t="inlineStr">
         <is>
-          <t>JP: checkout y subte N/R/W desde 49 St derecho por Broadway hasta Canal St (~15 min).</t>
-        </is>
-      </c>
-      <c r="F49" s="37" t="inlineStr"/>
+          <t>THAIS: checkout de Ink48 y tren temprano a New Jersey con LAS DOS valijas — hoy EMPIEZA A TRABAJAR. No participa de nada de este día. JP sale solo con su bolso de dos noches.</t>
+        </is>
+      </c>
+      <c r="F49" s="37" t="inlineStr">
+        <is>
+          <t>Hotel Ink48 (29-31 ago)</t>
+        </is>
+      </c>
       <c r="G49" s="40" t="inlineStr"/>
       <c r="H49" s="41" t="inlineStr"/>
       <c r="I49" s="41" t="inlineStr"/>
     </row>
-    <row r="50" ht="30" customHeight="1">
+    <row r="50" ht="16" customHeight="1">
       <c r="A50" s="35" t="n"/>
       <c r="B50" s="36" t="inlineStr">
         <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="C50" s="37" t="inlineStr">
+        <is>
           <t>08:35</t>
         </is>
       </c>
-      <c r="C50" s="37" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="D50" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -33632,30 +33632,26 @@
       </c>
       <c r="E50" s="39" t="inlineStr">
         <is>
-          <t>Dejar el bolso en la CONSIGNA del JGSTAY SOHO (recepción 24 h; el check-in formal es a la tarde — confirmar la consigna por mensaje). Liviano el resto del día.</t>
-        </is>
-      </c>
-      <c r="F50" s="37" t="inlineStr">
-        <is>
-          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
-        </is>
-      </c>
+          <t>JP: checkout y subte N/R/W desde 49 St derecho por Broadway hasta Canal St (~15 min).</t>
+        </is>
+      </c>
+      <c r="F50" s="37" t="inlineStr"/>
       <c r="G50" s="40" t="inlineStr"/>
       <c r="H50" s="41" t="inlineStr"/>
       <c r="I50" s="41" t="inlineStr"/>
     </row>
-    <row r="51" ht="16" customHeight="1">
+    <row r="51" ht="30" customHeight="1">
       <c r="A51" s="35" t="n"/>
       <c r="B51" s="36" t="inlineStr">
         <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="C51" s="37" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="C51" s="37" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="D51" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -33663,26 +33659,30 @@
       </c>
       <c r="E51" s="39" t="inlineStr">
         <is>
-          <t>Subte 6 desde Canal St directo hasta Grand Central (~20 min).</t>
-        </is>
-      </c>
-      <c r="F51" s="37" t="inlineStr"/>
+          <t>Dejar el bolso en la CONSIGNA del JGSTAY SOHO (recepción 24 h; el check-in formal es a la tarde — confirmar la consigna por mensaje). Liviano el resto del día.</t>
+        </is>
+      </c>
+      <c r="F51" s="37" t="inlineStr">
+        <is>
+          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
+        </is>
+      </c>
       <c r="G51" s="40" t="inlineStr"/>
       <c r="H51" s="41" t="inlineStr"/>
       <c r="I51" s="41" t="inlineStr"/>
     </row>
-    <row r="52" ht="30" customHeight="1">
+    <row r="52" ht="16" customHeight="1">
       <c r="A52" s="35" t="n"/>
       <c r="B52" s="36" t="inlineStr">
         <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C52" s="37" t="inlineStr">
+        <is>
           <t>09:20</t>
         </is>
       </c>
-      <c r="C52" s="37" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="D52" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -33690,41 +33690,37 @@
       </c>
       <c r="E52" s="39" t="inlineStr">
         <is>
-          <t>Desayuno adentro de Grand Central, en el dining concourse o en el Grand Central Market — ya estás dentro del edificio que venís a ver.</t>
-        </is>
-      </c>
-      <c r="F52" s="37" t="inlineStr">
-        <is>
-          <t>Grand Central Terminal</t>
-        </is>
-      </c>
+          <t>Subte 6 desde Canal St directo hasta Grand Central (~20 min).</t>
+        </is>
+      </c>
+      <c r="F52" s="37" t="inlineStr"/>
       <c r="G52" s="40" t="inlineStr"/>
       <c r="H52" s="41" t="inlineStr"/>
       <c r="I52" s="41" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="35" t="n"/>
-      <c r="B53" s="42" t="inlineStr">
+      <c r="B53" s="36" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="C53" s="37" t="inlineStr">
         <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="C53" s="43" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="D53" s="44" t="inlineStr">
+      <c r="D53" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E53" s="45" t="inlineStr">
-        <is>
-          <t>Grand Central Terminal: el techo celeste pintado al revés y la Whispering Gallery frente al Oyster Bar.</t>
-        </is>
-      </c>
-      <c r="F53" s="43" t="inlineStr">
+      <c r="E53" s="39" t="inlineStr">
+        <is>
+          <t>Desayuno adentro de Grand Central, en el dining concourse o en el Grand Central Market — ya estás dentro del edificio que venís a ver.</t>
+        </is>
+      </c>
+      <c r="F53" s="37" t="inlineStr">
         <is>
           <t>Grand Central Terminal</t>
         </is>
@@ -33733,71 +33729,67 @@
       <c r="H53" s="41" t="inlineStr"/>
       <c r="I53" s="41" t="inlineStr"/>
     </row>
-    <row r="54" ht="16" customHeight="1">
+    <row r="54" ht="30" customHeight="1">
       <c r="A54" s="35" t="n"/>
-      <c r="B54" s="36" t="inlineStr">
+      <c r="B54" s="42" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="C54" s="43" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="C54" s="37" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="D54" s="38" t="inlineStr">
+      <c r="D54" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E54" s="39" t="inlineStr">
-        <is>
-          <t>Lobby del Chrysler Building — art déco puro. SOLO lun-vie 8-18h.</t>
-        </is>
-      </c>
-      <c r="F54" s="37" t="inlineStr">
-        <is>
-          <t>Lobby del Chrysler Building</t>
-        </is>
-      </c>
-      <c r="G54" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~4 min a pie · 0.2 km · estimado</t>
-        </is>
-      </c>
+      <c r="E54" s="45" t="inlineStr">
+        <is>
+          <t>Grand Central Terminal: el techo celeste pintado al revés y la Whispering Gallery frente al Oyster Bar.</t>
+        </is>
+      </c>
+      <c r="F54" s="43" t="inlineStr">
+        <is>
+          <t>Grand Central Terminal</t>
+        </is>
+      </c>
+      <c r="G54" s="40" t="inlineStr"/>
       <c r="H54" s="41" t="inlineStr"/>
       <c r="I54" s="41" t="inlineStr"/>
     </row>
-    <row r="55" ht="30" customHeight="1">
+    <row r="55" ht="16" customHeight="1">
       <c r="A55" s="35" t="n"/>
-      <c r="B55" s="42" t="inlineStr">
+      <c r="B55" s="36" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="C55" s="37" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="C55" s="43" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="D55" s="44" t="inlineStr">
+      <c r="D55" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E55" s="45" t="inlineStr">
-        <is>
-          <t>Ford Foundation Atrium — jardín de 12 pisos dentro de un edificio de oficinas. PREINSCRIPCIÓN online antes de las 17h de ayer. Solo se puede del 31/8 al 3/9.</t>
-        </is>
-      </c>
-      <c r="F55" s="43" t="inlineStr">
-        <is>
-          <t>Ford Foundation Atrium</t>
+      <c r="E55" s="39" t="inlineStr">
+        <is>
+          <t>Lobby del Chrysler Building — art déco puro. SOLO lun-vie 8-18h.</t>
+        </is>
+      </c>
+      <c r="F55" s="37" t="inlineStr">
+        <is>
+          <t>Lobby del Chrysler Building</t>
         </is>
       </c>
       <c r="G55" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~9 min a pie · 0.6 km · estimado</t>
+          <t>🚶 ~4 min a pie · 0.2 km · estimado</t>
         </is>
       </c>
       <c r="H55" s="41" t="inlineStr"/>
@@ -33805,51 +33797,51 @@
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="35" t="n"/>
-      <c r="B56" s="36" t="inlineStr">
+      <c r="B56" s="42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C56" s="43" t="inlineStr">
         <is>
           <t>11:55</t>
         </is>
       </c>
-      <c r="C56" s="37" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="D56" s="38" t="inlineStr">
+      <c r="D56" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E56" s="39" t="inlineStr">
-        <is>
-          <t>New York Public Library: Rose Main Reading Room — se ve perfecta por libre (los tours gratuitos son 11:00 y 14:00 y no coinciden con esta pasada; no hacen falta).</t>
-        </is>
-      </c>
-      <c r="F56" s="37" t="inlineStr">
-        <is>
-          <t>New York Public Library (Schwarzman)</t>
+      <c r="E56" s="45" t="inlineStr">
+        <is>
+          <t>Ford Foundation Atrium — jardín de 12 pisos dentro de un edificio de oficinas. PREINSCRIPCIÓN online antes de las 17h de ayer. Solo se puede del 31/8 al 3/9.</t>
+        </is>
+      </c>
+      <c r="F56" s="43" t="inlineStr">
+        <is>
+          <t>Ford Foundation Atrium</t>
         </is>
       </c>
       <c r="G56" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~20 min a pie (1.4 km) o 🚇 ~15 min · estimado</t>
+          <t>🚶 ~9 min a pie · 0.6 km · estimado</t>
         </is>
       </c>
       <c r="H56" s="41" t="inlineStr"/>
       <c r="I56" s="41" t="inlineStr"/>
     </row>
-    <row r="57" ht="16" customHeight="1">
+    <row r="57" ht="30" customHeight="1">
       <c r="A57" s="35" t="n"/>
       <c r="B57" s="36" t="inlineStr">
         <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="C57" s="37" t="inlineStr">
+        <is>
           <t>12:55</t>
         </is>
       </c>
-      <c r="C57" s="37" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="D57" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -33857,77 +33849,85 @@
       </c>
       <c r="E57" s="39" t="inlineStr">
         <is>
-          <t>Almuerzo cerca de Bryant Park.</t>
+          <t>New York Public Library: Rose Main Reading Room — se ve perfecta por libre (los tours gratuitos son 11:00 y 14:00 y no coinciden con esta pasada; no hacen falta).</t>
         </is>
       </c>
       <c r="F57" s="37" t="inlineStr">
         <is>
-          <t>Bryant Park</t>
-        </is>
-      </c>
-      <c r="G57" s="40" t="inlineStr"/>
+          <t>New York Public Library (Schwarzman)</t>
+        </is>
+      </c>
+      <c r="G57" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~20 min a pie (1.4 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H57" s="41" t="inlineStr"/>
       <c r="I57" s="41" t="inlineStr"/>
     </row>
-    <row r="58" ht="30" customHeight="1">
+    <row r="58" ht="16" customHeight="1">
       <c r="A58" s="35" t="n"/>
-      <c r="B58" s="42" t="inlineStr">
+      <c r="B58" s="36" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="C58" s="37" t="inlineStr">
         <is>
           <t>13:45</t>
         </is>
       </c>
-      <c r="C58" s="43" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="D58" s="44" t="inlineStr">
+      <c r="D58" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E58" s="45" t="inlineStr">
-        <is>
-          <t>★ MoMA — a cinco cuadras de la biblioteca. Van Gogh, Picasso, Rothko, Warhol. El cine está INCLUIDO en la entrada. QUÉ HAY AHORA (verificado 27/8): «Frida and Diego: The Last Dream» — seis pinturas de Frida y una docena de Rivera, montaje del escenógrafo de la ópera de Frida. Cierra el 12 de septiembre, seis días después de que se van. Y engancha con la ópera gratis del domingo 6 en Lincoln Center, que es esa misma obra.</t>
-        </is>
-      </c>
-      <c r="F58" s="43" t="inlineStr">
-        <is>
-          <t>MoMA</t>
-        </is>
-      </c>
-      <c r="G58" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~20 min a pie (1.3 km) o 🚇 ~15 min · estimado</t>
-        </is>
-      </c>
+      <c r="E58" s="39" t="inlineStr">
+        <is>
+          <t>Almuerzo cerca de Bryant Park.</t>
+        </is>
+      </c>
+      <c r="F58" s="37" t="inlineStr">
+        <is>
+          <t>Bryant Park</t>
+        </is>
+      </c>
+      <c r="G58" s="40" t="inlineStr"/>
       <c r="H58" s="41" t="inlineStr"/>
       <c r="I58" s="41" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="35" t="n"/>
-      <c r="B59" s="36" t="inlineStr">
+      <c r="B59" s="42" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="C59" s="43" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="C59" s="37" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="D59" s="38" t="inlineStr">
+      <c r="D59" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E59" s="39" t="inlineStr">
-        <is>
-          <t>Caminar cuatro cuadras: Rockefeller Center a nivel de calle — la plaza, Atlas y St. Patrick's enfrente, sobre la Quinta.</t>
-        </is>
-      </c>
-      <c r="F59" s="37" t="inlineStr"/>
-      <c r="G59" s="40" t="inlineStr"/>
+      <c r="E59" s="45" t="inlineStr">
+        <is>
+          <t>★ MoMA — a cinco cuadras de la biblioteca. Van Gogh, Picasso, Rothko, Warhol. El cine está INCLUIDO en la entrada. QUÉ HAY AHORA (verificado 27/8): «Frida and Diego: The Last Dream» — seis pinturas de Frida y una docena de Rivera, montaje del escenógrafo de la ópera de Frida. Cierra el 12 de septiembre, seis días después de que se van. Y engancha con la ópera gratis del domingo 6 en Lincoln Center, que es esa misma obra.</t>
+        </is>
+      </c>
+      <c r="F59" s="43" t="inlineStr">
+        <is>
+          <t>MoMA</t>
+        </is>
+      </c>
+      <c r="G59" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~20 min a pie (1.3 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H59" s="41" t="inlineStr"/>
       <c r="I59" s="41" t="inlineStr"/>
     </row>
@@ -33935,14 +33935,14 @@
       <c r="A60" s="35" t="n"/>
       <c r="B60" s="36" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C60" s="37" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="C60" s="37" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
       <c r="D60" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -33950,7 +33950,7 @@
       </c>
       <c r="E60" s="39" t="inlineStr">
         <is>
-          <t>Cena TEMPRANA en Midtown. Hoy se cena ANTES de subir: la noche está tomada por el arco del observatorio y Birdland. Las valijas viajan con Thais y el bolso ya espera en SoHo.</t>
+          <t>Caminar cuatro cuadras: Rockefeller Center a nivel de calle — la plaza, Atlas y St. Patrick's enfrente, sobre la Quinta.</t>
         </is>
       </c>
       <c r="F60" s="37" t="inlineStr"/>
@@ -33960,184 +33960,180 @@
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="35" t="n"/>
-      <c r="B61" s="42" t="inlineStr">
+      <c r="B61" s="36" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C61" s="37" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="C61" s="43" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="D61" s="44" t="inlineStr">
+      <c r="D61" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E61" s="45" t="inlineStr">
-        <is>
-          <t>★★ TOP OF THE ROCK — EL ARCO COMPLETO que pidieron: entrada 18:15 con luz plena, el atardecer ~19:28 desde arriba, y la ciudad encendiéndose hasta ~20:05. Es el ÚNICO observatorio con el Empire State dentro del encuadre y Central Park del otro lado. ⚠️ La franja de atardecer es la cara (~$57-65) y la que primero se agota: reservar YA. Thais lo marcó 0: es de hoy.</t>
-        </is>
-      </c>
-      <c r="F61" s="43" t="inlineStr">
-        <is>
-          <t>Top of the Rock</t>
-        </is>
-      </c>
+      <c r="E61" s="39" t="inlineStr">
+        <is>
+          <t>Cena TEMPRANA en Midtown. Hoy se cena ANTES de subir: la noche está tomada por el arco del observatorio y Birdland. Las valijas viajan con Thais y el bolso ya espera en SoHo.</t>
+        </is>
+      </c>
+      <c r="F61" s="37" t="inlineStr"/>
       <c r="G61" s="40" t="inlineStr"/>
       <c r="H61" s="41" t="inlineStr"/>
       <c r="I61" s="41" t="inlineStr"/>
     </row>
-    <row r="62" ht="16" customHeight="1">
+    <row r="62" ht="30" customHeight="1">
       <c r="A62" s="35" t="n"/>
-      <c r="B62" s="36" t="inlineStr">
+      <c r="B62" s="42" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="C62" s="43" t="inlineStr">
         <is>
           <t>20:10</t>
         </is>
       </c>
-      <c r="C62" s="37" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="D62" s="38" t="inlineStr">
+      <c r="D62" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E62" s="39" t="inlineStr">
-        <is>
-          <t>Caminar a Birdland: 12 minutos (50th y 6ª → 44th entre 8ª y 9ª).</t>
-        </is>
-      </c>
-      <c r="F62" s="37" t="inlineStr"/>
+      <c r="E62" s="45" t="inlineStr">
+        <is>
+          <t>★★ TOP OF THE ROCK — EL ARCO COMPLETO que pidieron: entrada 18:15 con luz plena, el atardecer ~19:28 desde arriba, y la ciudad encendiéndose hasta ~20:05. Es el ÚNICO observatorio con el Empire State dentro del encuadre y Central Park del otro lado. ⚠️ La franja de atardecer es la cara (~$57-65) y la que primero se agota: reservar YA. Thais lo marcó 0: es de hoy.</t>
+        </is>
+      </c>
+      <c r="F62" s="43" t="inlineStr">
+        <is>
+          <t>Top of the Rock</t>
+        </is>
+      </c>
       <c r="G62" s="40" t="inlineStr"/>
       <c r="H62" s="41" t="inlineStr"/>
       <c r="I62" s="41" t="inlineStr"/>
     </row>
-    <row r="63" ht="30" customHeight="1">
+    <row r="63" ht="16" customHeight="1">
       <c r="A63" s="35" t="n"/>
-      <c r="B63" s="42" t="inlineStr">
+      <c r="B63" s="36" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="C63" s="37" t="inlineStr">
         <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="C63" s="43" t="inlineStr">
-        <is>
-          <t>22:40</t>
-        </is>
-      </c>
-      <c r="D63" s="44" t="inlineStr">
+      <c r="D63" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E63" s="45" t="inlineStr">
-        <is>
-          <t>★ BIRDLAND: Vince Giordano &amp; the Nighthawks — jazz de los años 20 y 30 con instrumentos de época. Institución de los lunes, y el lunes Broadway está oscuro. Birdland está a 8 cuadras de Penn Station.</t>
-        </is>
-      </c>
-      <c r="F63" s="43" t="inlineStr">
-        <is>
-          <t>Birdland</t>
-        </is>
-      </c>
+      <c r="E63" s="39" t="inlineStr">
+        <is>
+          <t>Caminar a Birdland: 12 minutos (50th y 6ª → 44th entre 8ª y 9ª).</t>
+        </is>
+      </c>
+      <c r="F63" s="37" t="inlineStr"/>
       <c r="G63" s="40" t="inlineStr"/>
       <c r="H63" s="41" t="inlineStr"/>
       <c r="I63" s="41" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="35" t="n"/>
-      <c r="B64" s="36" t="inlineStr">
+      <c r="B64" s="42" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C64" s="43" t="inlineStr">
         <is>
           <t>22:40</t>
         </is>
       </c>
-      <c r="C64" s="37" t="inlineStr"/>
-      <c r="D64" s="38" t="inlineStr">
+      <c r="D64" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E64" s="39" t="inlineStr">
-        <is>
-          <t>Birdland ENTERO y sin mirar el reloj: ya NO hay tren que atrapar. Subte A/C/E desde 42 St-Port Authority hasta Canal St (~15 min) y check-in en el JGStay. La noche pasó de terminar 00:35 en New Jersey a ~23:30 en SoHo.</t>
-        </is>
-      </c>
-      <c r="F64" s="37" t="inlineStr">
-        <is>
-          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
+      <c r="E64" s="45" t="inlineStr">
+        <is>
+          <t>★ BIRDLAND: Vince Giordano &amp; the Nighthawks — jazz de los años 20 y 30 con instrumentos de época. Institución de los lunes, y el lunes Broadway está oscuro. Birdland está a 8 cuadras de Penn Station.</t>
+        </is>
+      </c>
+      <c r="F64" s="43" t="inlineStr">
+        <is>
+          <t>Birdland</t>
         </is>
       </c>
       <c r="G64" s="40" t="inlineStr"/>
       <c r="H64" s="41" t="inlineStr"/>
       <c r="I64" s="41" t="inlineStr"/>
     </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="46" t="inlineStr">
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="35" t="n"/>
+      <c r="B65" s="36" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="C65" s="37" t="inlineStr"/>
+      <c r="D65" s="38" t="inlineStr">
+        <is>
+          <t>Solo JP</t>
+        </is>
+      </c>
+      <c r="E65" s="39" t="inlineStr">
+        <is>
+          <t>Birdland ENTERO y sin mirar el reloj: ya NO hay tren que atrapar. Subte A/C/E desde 42 St-Port Authority hasta Canal St (~15 min) y check-in en el JGStay. La noche pasó de terminar 00:35 en New Jersey a ~23:30 en SoHo.</t>
+        </is>
+      </c>
+      <c r="F65" s="37" t="inlineStr">
+        <is>
+          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
+        </is>
+      </c>
+      <c r="G65" s="40" t="inlineStr"/>
+      <c r="H65" s="41" t="inlineStr"/>
+      <c r="I65" s="41" t="inlineStr"/>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="46" t="inlineStr">
         <is>
           <t>ALTERNATIVA / OJO:  SIN TREN, el lunes cambió de naturaleza: Birdland completo, sobremesa incluida. Si queda pila, el JGStay está a 15-20 min a pie del Village y Smalls tiene jam de lunes hasta tarde. Y si el día pesó, SoHo a las 23:30 es una hora y cinco más de sueño que el plan viejo.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="33" t="inlineStr">
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="33" t="inlineStr">
         <is>
           <t>DÍA 4 · Martes 01/09 · JP solo · el MET, The Cloisters y la noche del Village  —  base: JGStay SoHo  ·  Solo JP</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="34" t="inlineStr">
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="34" t="inlineStr">
         <is>
           <t>Thais marcó el MET y The Cloisters en 0, así que este es EL día para hacerlos — y el martes es de los pocos que sirven: cierran los miércoles. El mismo ticket de $30 cubre los dos museos el mismo día, así que The Cloisters sale gratis. Thais sigue trabajando en New Jersey, así que hoy también es día de JP solo. CERRADOS hoy: Whitney, Frick, Noguchi, Brooklyn Museum, 9/11, MoMA PS1, Transit Museum y Studio Museum — por eso el martes es día de MET, que abre.</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="35" t="n"/>
-      <c r="B69" s="36" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="C69" s="37" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="D69" s="38" t="inlineStr">
-        <is>
-          <t>Solo JP</t>
-        </is>
-      </c>
-      <c r="E69" s="39" t="inlineStr">
-        <is>
-          <t>Desayuno INCLUIDO en el JGStay (7-9 AM) — primera mañana del viaje sin tren ni madrugón: el MET abre 10:00 y Canal St está en la puerta.</t>
-        </is>
-      </c>
-      <c r="F69" s="37" t="inlineStr">
-        <is>
-          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
-        </is>
-      </c>
-      <c r="G69" s="40" t="inlineStr"/>
-      <c r="H69" s="41" t="inlineStr"/>
-      <c r="I69" s="41" t="inlineStr"/>
-    </row>
-    <row r="70" ht="16" customHeight="1">
+    <row r="70" ht="30" customHeight="1">
       <c r="A70" s="35" t="n"/>
       <c r="B70" s="36" t="inlineStr">
         <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="C70" s="37" t="inlineStr">
+        <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="C70" s="37" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="D70" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -34145,84 +34141,88 @@
       </c>
       <c r="E70" s="39" t="inlineStr">
         <is>
-          <t>Subte 6 directo desde Canal St hasta 86 St (~35 min): se llega justo a la apertura del MET.</t>
-        </is>
-      </c>
-      <c r="F70" s="37" t="inlineStr"/>
+          <t>Desayuno INCLUIDO en el JGStay (7-9 AM) — primera mañana del viaje sin tren ni madrugón: el MET abre 10:00 y Canal St está en la puerta.</t>
+        </is>
+      </c>
+      <c r="F70" s="37" t="inlineStr">
+        <is>
+          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
+        </is>
+      </c>
       <c r="G70" s="40" t="inlineStr"/>
       <c r="H70" s="41" t="inlineStr"/>
       <c r="I70" s="41" t="inlineStr"/>
     </row>
-    <row r="71" ht="30" customHeight="1">
+    <row r="71" ht="16" customHeight="1">
       <c r="A71" s="35" t="n"/>
-      <c r="B71" s="42" t="inlineStr">
+      <c r="B71" s="36" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="C71" s="37" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="C71" s="43" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="D71" s="44" t="inlineStr">
+      <c r="D71" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E71" s="45" t="inlineStr">
-        <is>
-          <t>★★ THE METROPOLITAN MUSEUM OF ART — es inagotable, así que elegí DOS alas y hacelas bien: egipcio + pintura europea, o armas y armaduras + arte islámico. $30 (el pay-what-you-wish es solo para residentes de NY y estudiantes de NY/NJ/CT). QUÉ HAY AHORA (verificado 27/8): «Musical Bodies» en la Galería 199 —130 objetos sobre instrumentos y cuerpo, la primera muestra grande del Met sobre el tema— y «Costume Art» en las galerías de moda nuevas. ⚠️ El CANTOR ROOF GARDEN, la terraza con vista a Central Park que recomiendan todas las guías, está CERRADO desde 2025 y reabre en 2030: no existe en este viaje.</t>
-        </is>
-      </c>
-      <c r="F71" s="43" t="inlineStr">
-        <is>
-          <t>The Metropolitan Museum of Art</t>
-        </is>
-      </c>
+      <c r="E71" s="39" t="inlineStr">
+        <is>
+          <t>Subte 6 directo desde Canal St hasta 86 St (~35 min): se llega justo a la apertura del MET.</t>
+        </is>
+      </c>
+      <c r="F71" s="37" t="inlineStr"/>
       <c r="G71" s="40" t="inlineStr"/>
       <c r="H71" s="41" t="inlineStr"/>
       <c r="I71" s="41" t="inlineStr"/>
     </row>
-    <row r="72" ht="16" customHeight="1">
+    <row r="72" ht="30" customHeight="1">
       <c r="A72" s="35" t="n"/>
-      <c r="B72" s="36" t="inlineStr">
+      <c r="B72" s="42" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C72" s="43" t="inlineStr">
         <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="C72" s="37" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="D72" s="38" t="inlineStr">
+      <c r="D72" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E72" s="39" t="inlineStr">
-        <is>
-          <t>Almuerzo RÁPIDO cerca del MET (30-40 min): hoy la tarde tiene museo con hora de cierre.</t>
-        </is>
-      </c>
-      <c r="F72" s="37" t="inlineStr"/>
+      <c r="E72" s="45" t="inlineStr">
+        <is>
+          <t>★★ THE METROPOLITAN MUSEUM OF ART — es inagotable, así que elegí DOS alas y hacelas bien: egipcio + pintura europea, o armas y armaduras + arte islámico. $30 (el pay-what-you-wish es solo para residentes de NY y estudiantes de NY/NJ/CT). QUÉ HAY AHORA (verificado 27/8): «Musical Bodies» en la Galería 199 —130 objetos sobre instrumentos y cuerpo, la primera muestra grande del Met sobre el tema— y «Costume Art» en las galerías de moda nuevas. ⚠️ El CANTOR ROOF GARDEN, la terraza con vista a Central Park que recomiendan todas las guías, está CERRADO desde 2025 y reabre en 2030: no existe en este viaje.</t>
+        </is>
+      </c>
+      <c r="F72" s="43" t="inlineStr">
+        <is>
+          <t>The Metropolitan Museum of Art</t>
+        </is>
+      </c>
       <c r="G72" s="40" t="inlineStr"/>
       <c r="H72" s="41" t="inlineStr"/>
       <c r="I72" s="41" t="inlineStr"/>
     </row>
-    <row r="73" ht="30" customHeight="1">
+    <row r="73" ht="16" customHeight="1">
       <c r="A73" s="35" t="n"/>
       <c r="B73" s="36" t="inlineStr">
         <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="C73" s="37" t="inlineStr">
+        <is>
           <t>13:50</t>
         </is>
       </c>
-      <c r="C73" s="37" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="D73" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="E73" s="39" t="inlineStr">
         <is>
-          <t>Al Cloisters: NO hay tren A en el lado este — la ruta real en subte es M86-SBS cruzando el parque + B/C hasta 168 St + A hasta 190 St (~55 min). El taxi/Uber directo (~25 min, $28-35) compra 40 minutos de museo: hoy se justifica.</t>
+          <t>Almuerzo RÁPIDO cerca del MET (30-40 min): hoy la tarde tiene museo con hora de cierre.</t>
         </is>
       </c>
       <c r="F73" s="37" t="inlineStr"/>
@@ -34240,82 +34240,74 @@
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="35" t="n"/>
-      <c r="B74" s="42" t="inlineStr">
+      <c r="B74" s="36" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="C74" s="37" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="C74" s="43" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D74" s="44" t="inlineStr">
+      <c r="D74" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E74" s="45" t="inlineStr">
-        <is>
-          <t>★ THE MET CLOISTERS — arte medieval en un edificio armado con claustros franceses reales, sobre un acantilado del Hudson. INCLUIDO en el ticket del MET del mismo día: guardá el sticker.</t>
-        </is>
-      </c>
-      <c r="F74" s="43" t="inlineStr">
-        <is>
-          <t>The Met Cloisters</t>
-        </is>
-      </c>
+      <c r="E74" s="39" t="inlineStr">
+        <is>
+          <t>Al Cloisters: NO hay tren A en el lado este — la ruta real en subte es M86-SBS cruzando el parque + B/C hasta 168 St + A hasta 190 St (~55 min). El taxi/Uber directo (~25 min, $28-35) compra 40 minutos de museo: hoy se justifica.</t>
+        </is>
+      </c>
+      <c r="F74" s="37" t="inlineStr"/>
       <c r="G74" s="40" t="inlineStr"/>
       <c r="H74" s="41" t="inlineStr"/>
       <c r="I74" s="41" t="inlineStr"/>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="35" t="n"/>
-      <c r="B75" s="36" t="inlineStr">
+      <c r="B75" s="42" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C75" s="43" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="C75" s="37" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="D75" s="38" t="inlineStr">
+      <c r="D75" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E75" s="39" t="inlineStr">
-        <is>
-          <t>Fort Tryon Park — el Hudson y los Palisades sin un solo edificio a la vista. Media hora honesta: el parque ya rodea al Cloisters, y la noche de hoy tiene tres paradas.</t>
-        </is>
-      </c>
-      <c r="F75" s="37" t="inlineStr">
-        <is>
-          <t>Fort Tryon Park</t>
-        </is>
-      </c>
-      <c r="G75" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~5 min a pie · 0.3 km · estimado</t>
-        </is>
-      </c>
+      <c r="E75" s="45" t="inlineStr">
+        <is>
+          <t>★ THE MET CLOISTERS — arte medieval en un edificio armado con claustros franceses reales, sobre un acantilado del Hudson. INCLUIDO en el ticket del MET del mismo día: guardá el sticker.</t>
+        </is>
+      </c>
+      <c r="F75" s="43" t="inlineStr">
+        <is>
+          <t>The Met Cloisters</t>
+        </is>
+      </c>
+      <c r="G75" s="40" t="inlineStr"/>
       <c r="H75" s="41" t="inlineStr"/>
       <c r="I75" s="41" t="inlineStr"/>
     </row>
-    <row r="76" ht="16" customHeight="1">
+    <row r="76" ht="30" customHeight="1">
       <c r="A76" s="35" t="n"/>
       <c r="B76" s="36" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C76" s="37" t="inlineStr">
+        <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="C76" s="37" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
       <c r="D76" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -34323,26 +34315,34 @@
       </c>
       <c r="E76" s="39" t="inlineStr">
         <is>
-          <t>Tren A desde 190 St directo hasta W 4 St-Washington Sq (~35 min).</t>
-        </is>
-      </c>
-      <c r="F76" s="37" t="inlineStr"/>
-      <c r="G76" s="40" t="inlineStr"/>
+          <t>Fort Tryon Park — el Hudson y los Palisades sin un solo edificio a la vista. Media hora honesta: el parque ya rodea al Cloisters, y la noche de hoy tiene tres paradas.</t>
+        </is>
+      </c>
+      <c r="F76" s="37" t="inlineStr">
+        <is>
+          <t>Fort Tryon Park</t>
+        </is>
+      </c>
+      <c r="G76" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~5 min a pie · 0.3 km · estimado</t>
+        </is>
+      </c>
       <c r="H76" s="41" t="inlineStr"/>
       <c r="I76" s="41" t="inlineStr"/>
     </row>
-    <row r="77" ht="30" customHeight="1">
+    <row r="77" ht="16" customHeight="1">
       <c r="A77" s="35" t="n"/>
       <c r="B77" s="36" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C77" s="37" t="inlineStr">
+        <is>
           <t>18:10</t>
         </is>
       </c>
-      <c r="C77" s="37" t="inlineStr">
-        <is>
-          <t>18:35</t>
-        </is>
-      </c>
       <c r="D77" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -34350,14 +34350,10 @@
       </c>
       <c r="E77" s="39" t="inlineStr">
         <is>
-          <t>Washington Square Park (JP lo marcó 2): el arco, los músicos y las mesas de ajedrez al caer la tarde. Veinte minutos.</t>
-        </is>
-      </c>
-      <c r="F77" s="37" t="inlineStr">
-        <is>
-          <t>Washington Square Park</t>
-        </is>
-      </c>
+          <t>Tren A desde 190 St directo hasta W 4 St-Washington Sq (~35 min).</t>
+        </is>
+      </c>
+      <c r="F77" s="37" t="inlineStr"/>
       <c r="G77" s="40" t="inlineStr"/>
       <c r="H77" s="41" t="inlineStr"/>
       <c r="I77" s="41" t="inlineStr"/>
@@ -34366,14 +34362,14 @@
       <c r="A78" s="35" t="n"/>
       <c r="B78" s="36" t="inlineStr">
         <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="C78" s="37" t="inlineStr">
+        <is>
           <t>18:35</t>
         </is>
       </c>
-      <c r="C78" s="37" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
       <c r="D78" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -34381,79 +34377,75 @@
       </c>
       <c r="E78" s="39" t="inlineStr">
         <is>
-          <t>Bajar MacDougal St — la cuadra folk de los 60s (Caffe Reggio, el viejo Gaslight) — hasta Houston: 8-10 min y es paseo, no traslado.</t>
-        </is>
-      </c>
-      <c r="F78" s="37" t="inlineStr"/>
+          <t>Washington Square Park (JP lo marcó 2): el arco, los músicos y las mesas de ajedrez al caer la tarde. Veinte minutos.</t>
+        </is>
+      </c>
+      <c r="F78" s="37" t="inlineStr">
+        <is>
+          <t>Washington Square Park</t>
+        </is>
+      </c>
       <c r="G78" s="40" t="inlineStr"/>
       <c r="H78" s="41" t="inlineStr"/>
       <c r="I78" s="41" t="inlineStr"/>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="35" t="n"/>
-      <c r="B79" s="42" t="inlineStr">
+      <c r="B79" s="36" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="C79" s="37" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="C79" s="43" t="inlineStr">
-        <is>
-          <t>19:40</t>
-        </is>
-      </c>
-      <c r="D79" s="44" t="inlineStr">
+      <c r="D79" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E79" s="45" t="inlineStr">
-        <is>
-          <t>★★ HAMBURGER AMERICA (155 W Houston St) — MUST de JP: el counter de George Motz, el historiador de la hamburguesa americana. Pedir la fried-onion burger estilo Oklahoma y mirar el griddle trabajar. ~$15-20. SIN RESERVAS, orden de llegada — un martes 18:45 la fila es manejable, y el counter rota rápido.</t>
-        </is>
-      </c>
-      <c r="F79" s="43" t="inlineStr">
-        <is>
-          <t>Hamburger America</t>
-        </is>
-      </c>
-      <c r="G79" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~10 min a pie · 0.8 km · estimado</t>
-        </is>
-      </c>
+      <c r="E79" s="39" t="inlineStr">
+        <is>
+          <t>Bajar MacDougal St — la cuadra folk de los 60s (Caffe Reggio, el viejo Gaslight) — hasta Houston: 8-10 min y es paseo, no traslado.</t>
+        </is>
+      </c>
+      <c r="F79" s="37" t="inlineStr"/>
+      <c r="G79" s="40" t="inlineStr"/>
       <c r="H79" s="41" t="inlineStr"/>
       <c r="I79" s="41" t="inlineStr"/>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="35" t="n"/>
-      <c r="B80" s="36" t="inlineStr">
+      <c r="B80" s="42" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C80" s="43" t="inlineStr">
         <is>
           <t>19:40</t>
         </is>
       </c>
-      <c r="C80" s="37" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="D80" s="38" t="inlineStr">
+      <c r="D80" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E80" s="39" t="inlineStr">
-        <is>
-          <t>Paseo por el West Village sin plan: Bleecker, Grove, Bedford. La única grilla rota de Manhattan, y de noche es cuando mejor está.</t>
-        </is>
-      </c>
-      <c r="F80" s="37" t="inlineStr">
-        <is>
-          <t>West Village</t>
+      <c r="E80" s="45" t="inlineStr">
+        <is>
+          <t>★★ HAMBURGER AMERICA (155 W Houston St) — MUST de JP: el counter de George Motz, el historiador de la hamburguesa americana. Pedir la fried-onion burger estilo Oklahoma y mirar el griddle trabajar. ~$15-20. SIN RESERVAS, orden de llegada — un martes 18:45 la fila es manejable, y el counter rota rápido.</t>
+        </is>
+      </c>
+      <c r="F80" s="43" t="inlineStr">
+        <is>
+          <t>Hamburger America</t>
         </is>
       </c>
       <c r="G80" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~11 min a pie · 0.8 km · estimado</t>
+          <t>🚶 ~10 min a pie · 0.8 km · estimado</t>
         </is>
       </c>
       <c r="H80" s="41" t="inlineStr"/>
@@ -34461,126 +34453,130 @@
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="35" t="n"/>
-      <c r="B81" s="42" t="inlineStr">
+      <c r="B81" s="36" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="C81" s="37" t="inlineStr">
         <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="C81" s="43" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="D81" s="44" t="inlineStr">
+      <c r="D81" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E81" s="45" t="inlineStr">
-        <is>
-          <t>★ SMALLS JAZZ CLUB (183 W 10th St) — sótano de 60 asientos, la escena real de Nueva York tocando para el barrio. $25 con un trago; la jam de madrugada es de las mejores de la ciudad. Se entra por orden de llegada: llegar 20:15 asegura lugar. Mezzrow está enfrente si Smalls está lleno.</t>
-        </is>
-      </c>
-      <c r="F81" s="43" t="inlineStr">
-        <is>
-          <t>Smalls Jazz Club</t>
-        </is>
-      </c>
-      <c r="G81" s="40" t="inlineStr"/>
+      <c r="E81" s="39" t="inlineStr">
+        <is>
+          <t>Paseo por el West Village sin plan: Bleecker, Grove, Bedford. La única grilla rota de Manhattan, y de noche es cuando mejor está.</t>
+        </is>
+      </c>
+      <c r="F81" s="37" t="inlineStr">
+        <is>
+          <t>West Village</t>
+        </is>
+      </c>
+      <c r="G81" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~11 min a pie · 0.8 km · estimado</t>
+        </is>
+      </c>
       <c r="H81" s="41" t="inlineStr"/>
       <c r="I81" s="41" t="inlineStr"/>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="35" t="n"/>
-      <c r="B82" s="36" t="inlineStr">
+      <c r="B82" s="42" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C82" s="43" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="C82" s="37" t="inlineStr"/>
-      <c r="D82" s="38" t="inlineStr">
+      <c r="D82" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E82" s="39" t="inlineStr">
-        <is>
-          <t>Caminar al JGStay: 20-25 min cruzando el Village y SoHo, que a esta hora es el mejor paseo del viaje. O subte 1 desde Christopher St a Canal.</t>
-        </is>
-      </c>
-      <c r="F82" s="37" t="inlineStr">
-        <is>
-          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
+      <c r="E82" s="45" t="inlineStr">
+        <is>
+          <t>★ SMALLS JAZZ CLUB (183 W 10th St) — sótano de 60 asientos, la escena real de Nueva York tocando para el barrio. $25 con un trago; la jam de madrugada es de las mejores de la ciudad. Se entra por orden de llegada: llegar 20:15 asegura lugar. Mezzrow está enfrente si Smalls está lleno.</t>
+        </is>
+      </c>
+      <c r="F82" s="43" t="inlineStr">
+        <is>
+          <t>Smalls Jazz Club</t>
         </is>
       </c>
       <c r="G82" s="40" t="inlineStr"/>
       <c r="H82" s="41" t="inlineStr"/>
       <c r="I82" s="41" t="inlineStr"/>
     </row>
-    <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="46" t="inlineStr">
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="35" t="n"/>
+      <c r="B83" s="36" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C83" s="37" t="inlineStr"/>
+      <c r="D83" s="38" t="inlineStr">
+        <is>
+          <t>Solo JP</t>
+        </is>
+      </c>
+      <c r="E83" s="39" t="inlineStr">
+        <is>
+          <t>Caminar al JGStay: 20-25 min cruzando el Village y SoHo, que a esta hora es el mejor paseo del viaje. O subte 1 desde Christopher St a Canal.</t>
+        </is>
+      </c>
+      <c r="F83" s="37" t="inlineStr">
+        <is>
+          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
+        </is>
+      </c>
+      <c r="G83" s="40" t="inlineStr"/>
+      <c r="H83" s="41" t="inlineStr"/>
+      <c r="I83" s="41" t="inlineStr"/>
+    </row>
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="46" t="inlineStr">
         <is>
           <t>ALTERNATIVA / OJO:  El MET y The Cloisters el mismo día son ~6 horas de museo. Si es demasiado: hacé solo el MET hasta las 15h y usá la tarde para Inwood Hill Park (el único bosque primario que queda en Manhattan, con cuevas de los Lenape), que está tres paradas más al norte. El Tenement Museum quedó afuera: los dos lo bajaron a 'quizás'.</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="33" t="inlineStr">
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="33" t="inlineStr">
         <is>
           <t>DÍA 5 · Miércoles 02/09 · JP solo · Historia Natural, Frick gratis y McBride en Central Park  —  base: JGStay SoHo → New Jersey (la ÚNICA vuelta nocturna)  ·  Solo JP</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="32" customHeight="1">
-      <c r="A86" s="34" t="inlineStr">
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="34" t="inlineStr">
         <is>
           <t>Thais trabaja en New Jersey hasta mañana, así que sigue siendo día de JP solo, y se aprovecha para lo que ella marcó 0: el Museo de Historia Natural y el Frick. El miércoles el Frick es pay-what-you-wish de 13:30 a 17:30, así que sale casi nada. Cierra el MET, pero hoy no hace falta: ya se hizo ayer. El teleférico a Roosevelt Island se fue al domingo: lo marcaron 2 los dos, así que corresponde a un día de a dos. ⚠️ OJO CON LA NOCHE: hoy es LA ÚNICA vuelta a New Jersey que quedó en el viaje (para volver mañana con las maletas), y mañana se madruga 5:45. Cenar TEMPRANO y no perder el tren de las 22:48.</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="35" t="n"/>
-      <c r="B87" s="36" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="C87" s="37" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="D87" s="38" t="inlineStr">
-        <is>
-          <t>Solo JP</t>
-        </is>
-      </c>
-      <c r="E87" s="39" t="inlineStr">
-        <is>
-          <t>Desayuno incluido en el JGStay y CHECKOUT: el bolso queda en la CONSIGNA — se retira a la tarde, en el hueco libre del día.</t>
-        </is>
-      </c>
-      <c r="F87" s="37" t="inlineStr">
-        <is>
-          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
-        </is>
-      </c>
-      <c r="G87" s="40" t="inlineStr"/>
-      <c r="H87" s="41" t="inlineStr"/>
-      <c r="I87" s="41" t="inlineStr"/>
-    </row>
-    <row r="88" ht="16" customHeight="1">
+    <row r="88" ht="30" customHeight="1">
       <c r="A88" s="35" t="n"/>
       <c r="B88" s="36" t="inlineStr">
         <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="C88" s="37" t="inlineStr">
+        <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="C88" s="37" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="D88" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -34588,135 +34584,135 @@
       </c>
       <c r="E88" s="39" t="inlineStr">
         <is>
-          <t>Subte A o C desde Canal St hasta 81 St-Museum of Natural History (~30 min).</t>
-        </is>
-      </c>
-      <c r="F88" s="37" t="inlineStr"/>
+          <t>Desayuno incluido en el JGStay y CHECKOUT: el bolso queda en la CONSIGNA — se retira a la tarde, en el hueco libre del día.</t>
+        </is>
+      </c>
+      <c r="F88" s="37" t="inlineStr">
+        <is>
+          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
+        </is>
+      </c>
       <c r="G88" s="40" t="inlineStr"/>
       <c r="H88" s="41" t="inlineStr"/>
       <c r="I88" s="41" t="inlineStr"/>
     </row>
-    <row r="89" ht="30" customHeight="1">
+    <row r="89" ht="16" customHeight="1">
       <c r="A89" s="35" t="n"/>
-      <c r="B89" s="42" t="inlineStr">
+      <c r="B89" s="36" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C89" s="37" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="C89" s="43" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="D89" s="44" t="inlineStr">
+      <c r="D89" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E89" s="45" t="inlineStr">
-        <is>
-          <t>★ AMERICAN MUSEUM OF NATURAL HISTORY — dinosaurios, la ballena azul y el Gilder Center nuevo de Studio Gang. $37. Thais lo marcó 0: es de hoy.</t>
-        </is>
-      </c>
-      <c r="F89" s="43" t="inlineStr">
-        <is>
-          <t>American Museum of Natural History</t>
-        </is>
-      </c>
+      <c r="E89" s="39" t="inlineStr">
+        <is>
+          <t>Subte A o C desde Canal St hasta 81 St-Museum of Natural History (~30 min).</t>
+        </is>
+      </c>
+      <c r="F89" s="37" t="inlineStr"/>
       <c r="G89" s="40" t="inlineStr"/>
       <c r="H89" s="41" t="inlineStr"/>
       <c r="I89" s="41" t="inlineStr"/>
     </row>
-    <row r="90" ht="16" customHeight="1">
+    <row r="90" ht="30" customHeight="1">
       <c r="A90" s="35" t="n"/>
-      <c r="B90" s="36" t="inlineStr">
+      <c r="B90" s="42" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C90" s="43" t="inlineStr">
         <is>
           <t>12:45</t>
         </is>
       </c>
-      <c r="C90" s="37" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="D90" s="38" t="inlineStr">
+      <c r="D90" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E90" s="39" t="inlineStr">
-        <is>
-          <t>Almuerzo y cruzar Central Park de oeste a este (20 min a pie).</t>
-        </is>
-      </c>
-      <c r="F90" s="37" t="inlineStr"/>
+      <c r="E90" s="45" t="inlineStr">
+        <is>
+          <t>★ AMERICAN MUSEUM OF NATURAL HISTORY — dinosaurios, la ballena azul y el Gilder Center nuevo de Studio Gang. $37. Thais lo marcó 0: es de hoy.</t>
+        </is>
+      </c>
+      <c r="F90" s="43" t="inlineStr">
+        <is>
+          <t>American Museum of Natural History</t>
+        </is>
+      </c>
       <c r="G90" s="40" t="inlineStr"/>
       <c r="H90" s="41" t="inlineStr"/>
       <c r="I90" s="41" t="inlineStr"/>
     </row>
-    <row r="91" ht="30" customHeight="1">
+    <row r="91" ht="16" customHeight="1">
       <c r="A91" s="35" t="n"/>
-      <c r="B91" s="42" t="inlineStr">
+      <c r="B91" s="36" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C91" s="37" t="inlineStr">
         <is>
           <t>13:45</t>
         </is>
       </c>
-      <c r="C91" s="43" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="D91" s="44" t="inlineStr">
+      <c r="D91" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E91" s="45" t="inlineStr">
-        <is>
-          <t>★ THE FRICK COLLECTION — pay-what-you-wish los miércoles 13:30-17:30, y ESA VENTANA ES TODA: fuera de ahí son $30. Vermeer, Rembrandt y Bellini colgados como en una casa, porque era una casa. Online el mínimo es $5 y CONVIENE RESERVAR: el cupo en puerta existe pero no está garantizado. Llegar 13:45 como está planeado deja las cuatro horas justas.</t>
-        </is>
-      </c>
-      <c r="F91" s="43" t="inlineStr">
-        <is>
-          <t>The Frick Collection</t>
-        </is>
-      </c>
-      <c r="G91" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~25 min a pie (1.6 km) o 🚇 ~15 min · estimado</t>
-        </is>
-      </c>
+      <c r="E91" s="39" t="inlineStr">
+        <is>
+          <t>Almuerzo y cruzar Central Park de oeste a este (20 min a pie).</t>
+        </is>
+      </c>
+      <c r="F91" s="37" t="inlineStr"/>
+      <c r="G91" s="40" t="inlineStr"/>
       <c r="H91" s="41" t="inlineStr"/>
       <c r="I91" s="41" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="35" t="n"/>
-      <c r="B92" s="36" t="inlineStr">
+      <c r="B92" s="42" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="C92" s="43" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="C92" s="37" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="D92" s="38" t="inlineStr">
+      <c r="D92" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E92" s="39" t="inlineStr">
-        <is>
-          <t>El hueco libre ahora tiene una función: subte 6 desde 68 St hasta Canal St, RETIRAR EL BOLSO de la consigna del JGStay, y 6 de vuelta hasta 68 St (~1h10 el circuito completo). El bolso viaja esta noche a New Jersey. La cena temprana de las 17:45 sigue en pie.</t>
-        </is>
-      </c>
-      <c r="F92" s="37" t="inlineStr">
-        <is>
-          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
-        </is>
-      </c>
-      <c r="G92" s="40" t="inlineStr"/>
+      <c r="E92" s="45" t="inlineStr">
+        <is>
+          <t>★ THE FRICK COLLECTION — pay-what-you-wish los miércoles 13:30-17:30, y ESA VENTANA ES TODA: fuera de ahí son $30. Vermeer, Rembrandt y Bellini colgados como en una casa, porque era una casa. Online el mínimo es $5 y CONVIENE RESERVAR: el cupo en puerta existe pero no está garantizado. Llegar 13:45 como está planeado deja las cuatro horas justas.</t>
+        </is>
+      </c>
+      <c r="F92" s="43" t="inlineStr">
+        <is>
+          <t>The Frick Collection</t>
+        </is>
+      </c>
+      <c r="G92" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~25 min a pie (1.6 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H92" s="41" t="inlineStr"/>
       <c r="I92" s="41" t="inlineStr"/>
     </row>
@@ -34724,14 +34720,14 @@
       <c r="A93" s="35" t="n"/>
       <c r="B93" s="36" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C93" s="37" t="inlineStr">
+        <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="C93" s="37" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
       <c r="D93" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -34739,26 +34735,30 @@
       </c>
       <c r="E93" s="39" t="inlineStr">
         <is>
-          <t>Subte 6 al sur. Cena TEMPRANA cerca de Central Park: hoy no hay cena tardía posible, el tren manda.</t>
-        </is>
-      </c>
-      <c r="F93" s="37" t="inlineStr"/>
+          <t>El hueco libre ahora tiene una función: subte 6 desde 68 St hasta Canal St, RETIRAR EL BOLSO de la consigna del JGStay, y 6 de vuelta hasta 68 St (~1h10 el circuito completo). El bolso viaja esta noche a New Jersey. La cena temprana de las 17:45 sigue en pie.</t>
+        </is>
+      </c>
+      <c r="F93" s="37" t="inlineStr">
+        <is>
+          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
+        </is>
+      </c>
       <c r="G93" s="40" t="inlineStr"/>
       <c r="H93" s="41" t="inlineStr"/>
       <c r="I93" s="41" t="inlineStr"/>
     </row>
-    <row r="94" ht="16" customHeight="1">
+    <row r="94" ht="30" customHeight="1">
       <c r="A94" s="35" t="n"/>
       <c r="B94" s="36" t="inlineStr">
         <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="C94" s="37" t="inlineStr">
+        <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="C94" s="37" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
       <c r="D94" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -34766,7 +34766,7 @@
       </c>
       <c r="E94" s="39" t="inlineStr">
         <is>
-          <t>Entrar a Rumsey Playfield. Puertas 18:00 y con este cartel se llena: cuanto antes, mejor lugar.</t>
+          <t>Subte 6 al sur. Cena TEMPRANA cerca de Central Park: hoy no hay cena tardía posible, el tren manda.</t>
         </is>
       </c>
       <c r="F94" s="37" t="inlineStr"/>
@@ -34774,60 +34774,60 @@
       <c r="H94" s="41" t="inlineStr"/>
       <c r="I94" s="41" t="inlineStr"/>
     </row>
-    <row r="95" ht="30" customHeight="1">
+    <row r="95" ht="16" customHeight="1">
       <c r="A95" s="35" t="n"/>
-      <c r="B95" s="42" t="inlineStr">
+      <c r="B95" s="36" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C95" s="37" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C95" s="43" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="D95" s="44" t="inlineStr">
+      <c r="D95" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E95" s="45" t="inlineStr">
-        <is>
-          <t>★★ SUMMERSTAGE: Christian McBride + SAMARA JOY + Mei Semones — Verve 70 aniversario y Getz/Gilberto. GRATIS, sin ticket, Rumsey Playfield, 19:00-22:00.</t>
-        </is>
-      </c>
-      <c r="F95" s="43" t="inlineStr">
-        <is>
-          <t>SummerStage: Christian McBride (gratis)</t>
-        </is>
-      </c>
+      <c r="E95" s="39" t="inlineStr">
+        <is>
+          <t>Entrar a Rumsey Playfield. Puertas 18:00 y con este cartel se llena: cuanto antes, mejor lugar.</t>
+        </is>
+      </c>
+      <c r="F95" s="37" t="inlineStr"/>
       <c r="G95" s="40" t="inlineStr"/>
       <c r="H95" s="41" t="inlineStr"/>
       <c r="I95" s="41" t="inlineStr"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="35" t="n"/>
-      <c r="B96" s="36" t="inlineStr">
+      <c r="B96" s="42" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C96" s="43" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C96" s="37" t="inlineStr">
-        <is>
-          <t>22:48</t>
-        </is>
-      </c>
-      <c r="D96" s="38" t="inlineStr">
+      <c r="D96" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E96" s="39" t="inlineStr">
-        <is>
-          <t>Salir del parque por la 72 y subte 1/2/3 hasta 34 St-Penn Station. Son 25-30 min puerta a puerta: llegás a Penn 22:25-22:30, con 18-23 min de colchón.</t>
-        </is>
-      </c>
-      <c r="F96" s="37" t="inlineStr"/>
+      <c r="E96" s="45" t="inlineStr">
+        <is>
+          <t>★★ SUMMERSTAGE: Christian McBride + SAMARA JOY + Mei Semones — Verve 70 aniversario y Getz/Gilberto. GRATIS, sin ticket, Rumsey Playfield, 19:00-22:00.</t>
+        </is>
+      </c>
+      <c r="F96" s="43" t="inlineStr">
+        <is>
+          <t>SummerStage: Christian McBride (gratis)</t>
+        </is>
+      </c>
       <c r="G96" s="40" t="inlineStr"/>
       <c r="H96" s="41" t="inlineStr"/>
       <c r="I96" s="41" t="inlineStr"/>
@@ -34836,14 +34836,14 @@
       <c r="A97" s="35" t="n"/>
       <c r="B97" s="36" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C97" s="37" t="inlineStr">
+        <is>
           <t>22:48</t>
         </is>
       </c>
-      <c r="C97" s="37" t="inlineStr">
-        <is>
-          <t>00:15</t>
-        </is>
-      </c>
       <c r="D97" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -34851,7 +34851,7 @@
       </c>
       <c r="E97" s="39" t="inlineStr">
         <is>
-          <t>NJ Transit DIRECTO Penn → Raritan (tren 5197), llega 00:04. $18,50. ⚠️ ES EL TREN CRÍTICO: si lo perdés, la próxima llegada a Raritan es 01:31.</t>
+          <t>Salir del parque por la 72 y subte 1/2/3 hasta 34 St-Penn Station. Son 25-30 min puerta a puerta: llegás a Penn 22:25-22:30, con 18-23 min de colchón.</t>
         </is>
       </c>
       <c r="F97" s="37" t="inlineStr"/>
@@ -34863,10 +34863,14 @@
       <c r="A98" s="35" t="n"/>
       <c r="B98" s="36" t="inlineStr">
         <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="C98" s="37" t="inlineStr">
+        <is>
           <t>00:15</t>
         </is>
       </c>
-      <c r="C98" s="37" t="inlineStr"/>
       <c r="D98" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -34874,82 +34878,74 @@
       </c>
       <c r="E98" s="39" t="inlineStr">
         <is>
-          <t>Uber Raritan → Residence Inn (pedirlo antes de subir al tren). Mañana: despertador 5:45 para el tren de las 6:55 con las maletas.</t>
-        </is>
-      </c>
-      <c r="F98" s="37" t="inlineStr">
-        <is>
-          <t>Residence Inn Branchburg (Thais 31/8-3/9 · JP solo la noche del 2)</t>
-        </is>
-      </c>
+          <t>NJ Transit DIRECTO Penn → Raritan (tren 5197), llega 00:04. $18,50. ⚠️ ES EL TREN CRÍTICO: si lo perdés, la próxima llegada a Raritan es 01:31.</t>
+        </is>
+      </c>
+      <c r="F98" s="37" t="inlineStr"/>
       <c r="G98" s="40" t="inlineStr"/>
       <c r="H98" s="41" t="inlineStr"/>
       <c r="I98" s="41" t="inlineStr"/>
     </row>
-    <row r="99" ht="32" customHeight="1">
-      <c r="A99" s="46" t="inlineStr">
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="35" t="n"/>
+      <c r="B99" s="36" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="C99" s="37" t="inlineStr"/>
+      <c r="D99" s="38" t="inlineStr">
+        <is>
+          <t>Solo JP</t>
+        </is>
+      </c>
+      <c r="E99" s="39" t="inlineStr">
+        <is>
+          <t>Uber Raritan → Residence Inn (pedirlo antes de subir al tren). Mañana: despertador 5:45 para el tren de las 6:55 con las maletas.</t>
+        </is>
+      </c>
+      <c r="F99" s="37" t="inlineStr">
+        <is>
+          <t>Residence Inn Branchburg (Thais 31/8-3/9 · JP solo la noche del 2)</t>
+        </is>
+      </c>
+      <c r="G99" s="40" t="inlineStr"/>
+      <c r="H99" s="41" t="inlineStr"/>
+      <c r="I99" s="41" t="inlineStr"/>
+    </row>
+    <row r="100" ht="32" customHeight="1">
+      <c r="A100" s="46" t="inlineStr">
         <is>
           <t>ALTERNATIVA / OJO:  Si el AMNH es demasiado museo dos días seguidos (ayer fueron el MET y The Cloisters), salteálo y usá la mañana para Inwood Hill Park o para caminar el Upper West Side sin plan. El Frick y el SummerStage son los dos anclas del día: uno es casi gratis solo hoy, el otro pasa una sola vez. // ⚠️ LA DECISIÓN DE LA NOCHE, con los horarios ya verificados: el directo de las 21:48 llega a Raritan 23:10 y al hotel ~23:30, o sea UNA HORA MÁS DE SUEÑO antes de un jueves que arranca 5:45 con maletas. Pero para tomarlo hay que salir del SummerStage a las 21:05 — el colchón es de 3 a 8 minutos, no hay margen — y te perdés el final de Christian McBride y Samara Joy, que es el plato fuerte y pasa una sola vez. Mi recomendación: quedate hasta el final y tomá el de las 22:48. La hora de sueño no convierte el jueves en un día fácil, y el show no se repite.</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="33" t="inlineStr">
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="33" t="inlineStr">
         <is>
           <t>DÍA 6 · Jueves 03/09 · Traslado + World Trade Center completo + ferry con Thais  —  base: New Jersey → The Beacon  ·  Solo JP</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="32" customHeight="1">
-      <c r="A102" s="34" t="inlineStr">
+    <row r="103" ht="32" customHeight="1">
+      <c r="A103" s="34" t="inlineStr">
         <is>
           <t>La mañana y la primera tarde son el World Trade Center completo — memorial, museo y One World Observatory en una sola bajada. OJO: One World es EL MIRADOR DE DÍA a propósito — su vista es el puerto y el agua, que de noche es negra; los arcos de atardecer van en Top of the Rock (lunes) y SUMMIT (viernes). THAIS ESTÁ EN NYC CON SU EQUIPO este jueves y SE LIBERA A LAS 16:00: se encuentran por Manhattan y se van juntos al Museum of the Moving Image, que es GRATIS los jueves de 14 a 18 — estaba caído del plan y ustedes lo tienen 2/2: RECUPERADO. El día cierra con check-in, cena y Dizzy's. Siguen afuera MoMA PS1, Astoria y Gantry (no hay hueco), y el Staten Island Ferry pasó a la alternativa nocturna de hoy. ENTRA STONE ST, que era imprescindible y no estaba en ningún día: el almuerzo se corre de Brookfield Place a la calle adoquinada, a 10 minutos del museo y 12 de One World. Se pagan 22 minutos de caminata y quedan 38 para comer — alcanza para un mediodía, aunque su mejor hora sea el after office de 5 a 8 y no la del almuerzo.</t>
         </is>
       </c>
-    </row>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="35" t="n"/>
-      <c r="B103" s="36" t="inlineStr">
-        <is>
-          <t>06:20</t>
-        </is>
-      </c>
-      <c r="C103" s="37" t="inlineStr">
-        <is>
-          <t>06:55</t>
-        </is>
-      </c>
-      <c r="D103" s="38" t="inlineStr">
-        <is>
-          <t>Solo JP</t>
-        </is>
-      </c>
-      <c r="E103" s="39" t="inlineStr">
-        <is>
-          <t>Uber desde el Residence Inn a la estación Raritan (~20 min, $14-20). PEDIRLO LA NOCHE ANTERIOR: Branchburg es semi-rural y a esa hora puede no haber autos.</t>
-        </is>
-      </c>
-      <c r="F103" s="37" t="inlineStr">
-        <is>
-          <t>Residence Inn Branchburg (Thais 31/8-3/9 · JP solo la noche del 2)</t>
-        </is>
-      </c>
-      <c r="G103" s="40" t="inlineStr"/>
-      <c r="H103" s="41" t="inlineStr"/>
-      <c r="I103" s="41" t="inlineStr"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="35" t="n"/>
       <c r="B104" s="36" t="inlineStr">
         <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="C104" s="37" t="inlineStr">
+        <is>
           <t>06:55</t>
         </is>
       </c>
-      <c r="C104" s="37" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
       <c r="D104" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -34957,26 +34953,30 @@
       </c>
       <c r="E104" s="39" t="inlineStr">
         <is>
-          <t>NJ Transit Raritan → NY Penn Station. Llega 8:20. $18,50. Con maletas, ir al vagón con espacio de equipaje.</t>
-        </is>
-      </c>
-      <c r="F104" s="37" t="inlineStr"/>
+          <t>Uber desde el Residence Inn a la estación Raritan (~20 min, $14-20). PEDIRLO LA NOCHE ANTERIOR: Branchburg es semi-rural y a esa hora puede no haber autos.</t>
+        </is>
+      </c>
+      <c r="F104" s="37" t="inlineStr">
+        <is>
+          <t>Residence Inn Branchburg (Thais 31/8-3/9 · JP solo la noche del 2)</t>
+        </is>
+      </c>
       <c r="G104" s="40" t="inlineStr"/>
       <c r="H104" s="41" t="inlineStr"/>
       <c r="I104" s="41" t="inlineStr"/>
     </row>
-    <row r="105" ht="16" customHeight="1">
+    <row r="105" ht="30" customHeight="1">
       <c r="A105" s="35" t="n"/>
       <c r="B105" s="36" t="inlineStr">
         <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="C105" s="37" t="inlineStr">
+        <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="C105" s="37" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
       <c r="D105" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -34984,7 +34984,7 @@
       </c>
       <c r="E105" s="39" t="inlineStr">
         <is>
-          <t>Subte 1/2/3 desde 34 St-Penn Station hasta 72 St. Diez minutos, directo.</t>
+          <t>NJ Transit Raritan → NY Penn Station. Llega 8:20. $18,50. Con maletas, ir al vagón con espacio de equipaje.</t>
         </is>
       </c>
       <c r="F105" s="37" t="inlineStr"/>
@@ -34992,87 +34992,87 @@
       <c r="H105" s="41" t="inlineStr"/>
       <c r="I105" s="41" t="inlineStr"/>
     </row>
-    <row r="106" ht="30" customHeight="1">
+    <row r="106" ht="16" customHeight="1">
       <c r="A106" s="35" t="n"/>
-      <c r="B106" s="42" t="inlineStr">
+      <c r="B106" s="36" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C106" s="37" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="C106" s="43" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="D106" s="44" t="inlineStr">
+      <c r="D106" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E106" s="45" t="inlineStr">
-        <is>
-          <t>★ THE BEACON — dejar las maletas en el bell desk. El check-in formal es a la tarde, con Thais, pero el equipaje se puede dejar desde temprano. Confirmalo por mail antes de viajar.</t>
-        </is>
-      </c>
-      <c r="F106" s="43" t="inlineStr">
-        <is>
-          <t>Hotel The Beacon (3-6 sep)</t>
-        </is>
-      </c>
+      <c r="E106" s="39" t="inlineStr">
+        <is>
+          <t>Subte 1/2/3 desde 34 St-Penn Station hasta 72 St. Diez minutos, directo.</t>
+        </is>
+      </c>
+      <c r="F106" s="37" t="inlineStr"/>
       <c r="G106" s="40" t="inlineStr"/>
       <c r="H106" s="41" t="inlineStr"/>
       <c r="I106" s="41" t="inlineStr"/>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="35" t="n"/>
-      <c r="B107" s="36" t="inlineStr">
+      <c r="B107" s="42" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="C107" s="43" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="C107" s="37" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="D107" s="38" t="inlineStr">
+      <c r="D107" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E107" s="39" t="inlineStr">
-        <is>
-          <t>Subte 1 directo desde 72 St hasta WTC Cortlandt (~30 min). Alternativa: 2/3 express hasta Chambers St y 5 min a pie.</t>
-        </is>
-      </c>
-      <c r="F107" s="37" t="inlineStr"/>
+      <c r="E107" s="45" t="inlineStr">
+        <is>
+          <t>★ THE BEACON — dejar las maletas en el bell desk. El check-in formal es a la tarde, con Thais, pero el equipaje se puede dejar desde temprano. Confirmalo por mail antes de viajar.</t>
+        </is>
+      </c>
+      <c r="F107" s="43" t="inlineStr">
+        <is>
+          <t>Hotel The Beacon (3-6 sep)</t>
+        </is>
+      </c>
       <c r="G107" s="40" t="inlineStr"/>
       <c r="H107" s="41" t="inlineStr"/>
       <c r="I107" s="41" t="inlineStr"/>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="35" t="n"/>
-      <c r="B108" s="42" t="inlineStr">
+      <c r="B108" s="36" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C108" s="37" t="inlineStr">
         <is>
           <t>09:50</t>
         </is>
       </c>
-      <c r="C108" s="43" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="D108" s="44" t="inlineStr">
+      <c r="D108" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E108" s="45" t="inlineStr">
-        <is>
-          <t>★ 9/11 MEMORIAL (la plaza) — las dos fuentes en las huellas de las torres y el Survivor Tree. Gratis, abierto desde las 8:00. Verlo ANTES del museo ordena la visita.</t>
-        </is>
-      </c>
-      <c r="F108" s="43" t="inlineStr"/>
+      <c r="E108" s="39" t="inlineStr">
+        <is>
+          <t>Subte 1 directo desde 72 St hasta WTC Cortlandt (~30 min). Alternativa: 2/3 express hasta Chambers St y 5 min a pie.</t>
+        </is>
+      </c>
+      <c r="F108" s="37" t="inlineStr"/>
       <c r="G108" s="40" t="inlineStr"/>
       <c r="H108" s="41" t="inlineStr"/>
       <c r="I108" s="41" t="inlineStr"/>
@@ -35081,14 +35081,14 @@
       <c r="A109" s="35" t="n"/>
       <c r="B109" s="42" t="inlineStr">
         <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="C109" s="43" t="inlineStr">
+        <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="C109" s="43" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="D109" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -35096,83 +35096,75 @@
       </c>
       <c r="E109" s="45" t="inlineStr">
         <is>
-          <t>★★ 9/11 MEMORIAL MUSEUM — $36, TIMED TICKET OBLIGATORIO comprado online antes (el museo no vende en puerta sin reserva). 2 horas largas; es duro y muy bien hecho. Thais lo marcó 0: por eso va en la mañana de JP solo.</t>
-        </is>
-      </c>
-      <c r="F109" s="43" t="inlineStr">
-        <is>
-          <t>9/11 Memorial Museum</t>
-        </is>
-      </c>
+          <t>★ 9/11 MEMORIAL (la plaza) — las dos fuentes en las huellas de las torres y el Survivor Tree. Gratis, abierto desde las 8:00. Verlo ANTES del museo ordena la visita.</t>
+        </is>
+      </c>
+      <c r="F109" s="43" t="inlineStr"/>
       <c r="G109" s="40" t="inlineStr"/>
       <c r="H109" s="41" t="inlineStr"/>
       <c r="I109" s="41" t="inlineStr"/>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="35" t="n"/>
-      <c r="B110" s="36" t="inlineStr">
+      <c r="B110" s="42" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C110" s="43" t="inlineStr">
         <is>
           <t>12:45</t>
         </is>
       </c>
-      <c r="C110" s="37" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="D110" s="38" t="inlineStr">
+      <c r="D110" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E110" s="39" t="inlineStr">
-        <is>
-          <t>★ ALMUERZO EN STONE ST — 10 min a pie desde el museo, hacia el sureste. Calle adoquinada peatonal de 1660, la traza holandesa que sobrevivió al fuego de 1835: mesas afuera, sin autos, entre edificios de piedra. Se come rápido y se sigue: One World es a las 13:45 y son 12 min de vuelta. Plan B si llueve o no hay mesa: Hudson Eats o Le District en Brookfield Place, cruzando West St.</t>
-        </is>
-      </c>
-      <c r="F110" s="37" t="inlineStr">
-        <is>
-          <t>Stone St</t>
-        </is>
-      </c>
-      <c r="G110" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~14 min a pie · 1.1 km · estimado</t>
-        </is>
-      </c>
+      <c r="E110" s="45" t="inlineStr">
+        <is>
+          <t>★★ 9/11 MEMORIAL MUSEUM — $36, TIMED TICKET OBLIGATORIO comprado online antes (el museo no vende en puerta sin reserva). 2 horas largas; es duro y muy bien hecho. Thais lo marcó 0: por eso va en la mañana de JP solo.</t>
+        </is>
+      </c>
+      <c r="F110" s="43" t="inlineStr">
+        <is>
+          <t>9/11 Memorial Museum</t>
+        </is>
+      </c>
+      <c r="G110" s="40" t="inlineStr"/>
       <c r="H110" s="41" t="inlineStr"/>
       <c r="I110" s="41" t="inlineStr"/>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="35" t="n"/>
-      <c r="B111" s="42" t="inlineStr">
+      <c r="B111" s="36" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C111" s="37" t="inlineStr">
         <is>
           <t>13:45</t>
         </is>
       </c>
-      <c r="C111" s="43" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="D111" s="44" t="inlineStr">
+      <c r="D111" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E111" s="45" t="inlineStr">
-        <is>
-          <t>★★ ONE WORLD OBSERVATORY — piso 102, el punto más alto del hemisferio occidental, con el puerto y Brooklyn dominando la vista. $44+fee, ventana de entrada de 15 min: sacar el timed ticket online. JP lo subió a 2 en la última pasada.</t>
-        </is>
-      </c>
-      <c r="F111" s="43" t="inlineStr">
-        <is>
-          <t>One World Observatory</t>
+      <c r="E111" s="39" t="inlineStr">
+        <is>
+          <t>★ ALMUERZO EN STONE ST — 10 min a pie desde el museo, hacia el sureste. Calle adoquinada peatonal de 1660, la traza holandesa que sobrevivió al fuego de 1835: mesas afuera, sin autos, entre edificios de piedra. Se come rápido y se sigue: One World es a las 13:45 y son 12 min de vuelta. Plan B si llueve o no hay mesa: Hudson Eats o Le District en Brookfield Place, cruzando West St.</t>
+        </is>
+      </c>
+      <c r="F111" s="37" t="inlineStr">
+        <is>
+          <t>Stone St</t>
         </is>
       </c>
       <c r="G111" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~20 min a pie (1.2 km) o 🚇 ~15 min · estimado</t>
+          <t>🚶 ~14 min a pie · 1.1 km · estimado</t>
         </is>
       </c>
       <c r="H111" s="41" t="inlineStr"/>
@@ -35180,34 +35172,34 @@
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="35" t="n"/>
-      <c r="B112" s="36" t="inlineStr">
+      <c r="B112" s="42" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="C112" s="43" t="inlineStr">
         <is>
           <t>15:15</t>
         </is>
       </c>
-      <c r="C112" s="37" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D112" s="38" t="inlineStr">
+      <c r="D112" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E112" s="39" t="inlineStr">
-        <is>
-          <t>El Oculus en un VISTAZO (5 min — ya estás ahí, y el tiempo no da para más) y R/W desde Cortlandt St hacia el norte.</t>
-        </is>
-      </c>
-      <c r="F112" s="37" t="inlineStr">
-        <is>
-          <t>Oculus / WTC Transportation Hub</t>
+      <c r="E112" s="45" t="inlineStr">
+        <is>
+          <t>★★ ONE WORLD OBSERVATORY — piso 102, el punto más alto del hemisferio occidental, con el puerto y Brooklyn dominando la vista. $44+fee, ventana de entrada de 15 min: sacar el timed ticket online. JP lo subió a 2 en la última pasada.</t>
+        </is>
+      </c>
+      <c r="F112" s="43" t="inlineStr">
+        <is>
+          <t>One World Observatory</t>
         </is>
       </c>
       <c r="G112" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~4 min a pie · 0.3 km · estimado</t>
+          <t>🚶 ~20 min a pie (1.2 km) o 🚇 ~15 min · estimado</t>
         </is>
       </c>
       <c r="H112" s="41" t="inlineStr"/>
@@ -35215,28 +35207,36 @@
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="35" t="n"/>
-      <c r="B113" s="42" t="inlineStr">
+      <c r="B113" s="36" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C113" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="C113" s="43" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="D113" s="44" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="E113" s="45" t="inlineStr">
-        <is>
-          <t>★ ENCUENTRO CON THAIS. Lo que MÁS rinde: verse DIRECTO en la puerta del MoMI a las 16:20 (36-01 35 Ave, N/W hasta 36 Av) — cada uno llega por su lado y el museo gana 10-15 min. Si prefieren encontrarse antes en Manhattan: Lexington Av-59 St 16:00 y N/W juntos (JP puede llegar 16:05-16:10 si el WTC se estiró: avisale que es ±10).</t>
-        </is>
-      </c>
-      <c r="F113" s="43" t="inlineStr"/>
-      <c r="G113" s="40" t="inlineStr"/>
+      <c r="D113" s="38" t="inlineStr">
+        <is>
+          <t>Solo JP</t>
+        </is>
+      </c>
+      <c r="E113" s="39" t="inlineStr">
+        <is>
+          <t>El Oculus en un VISTAZO (5 min — ya estás ahí, y el tiempo no da para más) y R/W desde Cortlandt St hacia el norte.</t>
+        </is>
+      </c>
+      <c r="F113" s="37" t="inlineStr">
+        <is>
+          <t>Oculus / WTC Transportation Hub</t>
+        </is>
+      </c>
+      <c r="G113" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~4 min a pie · 0.3 km · estimado</t>
+        </is>
+      </c>
       <c r="H113" s="41" t="inlineStr"/>
       <c r="I113" s="41" t="inlineStr"/>
     </row>
@@ -35244,14 +35244,14 @@
       <c r="A114" s="35" t="n"/>
       <c r="B114" s="42" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C114" s="43" t="inlineStr">
+        <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="C114" s="43" t="inlineStr">
-        <is>
-          <t>18:05</t>
-        </is>
-      </c>
       <c r="D114" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35259,46 +35259,46 @@
       </c>
       <c r="E114" s="45" t="inlineStr">
         <is>
-          <t>★★ MUSEUM OF THE MOVING IMAGE — GRATIS los jueves 14-18, sus únicas horas del jueves. RECUPERADO: había quedado afuera del plan y ustedes lo tienen 2/2. Una hora y media alcanza para Behind the Screen y los Muppets originales de Jim Henson. Cierra 18:00 EN PUNTO. (N/W hasta 36 Av + 8 min a pie.)</t>
-        </is>
-      </c>
-      <c r="F114" s="43" t="inlineStr">
-        <is>
-          <t>Museum of the Moving Image</t>
-        </is>
-      </c>
-      <c r="G114" s="40" t="inlineStr">
-        <is>
-          <t>🚇 ~40 min en subte · 11.5 km (a pie 155 min) · estimado</t>
-        </is>
-      </c>
+          <t>★ ENCUENTRO CON THAIS. Lo que MÁS rinde: verse DIRECTO en la puerta del MoMI a las 16:20 (36-01 35 Ave, N/W hasta 36 Av) — cada uno llega por su lado y el museo gana 10-15 min. Si prefieren encontrarse antes en Manhattan: Lexington Av-59 St 16:00 y N/W juntos (JP puede llegar 16:05-16:10 si el WTC se estiró: avisale que es ±10).</t>
+        </is>
+      </c>
+      <c r="F114" s="43" t="inlineStr"/>
+      <c r="G114" s="40" t="inlineStr"/>
       <c r="H114" s="41" t="inlineStr"/>
       <c r="I114" s="41" t="inlineStr"/>
     </row>
-    <row r="115" ht="16" customHeight="1">
+    <row r="115" ht="30" customHeight="1">
       <c r="A115" s="35" t="n"/>
-      <c r="B115" s="36" t="inlineStr">
+      <c r="B115" s="42" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C115" s="43" t="inlineStr">
         <is>
           <t>18:05</t>
         </is>
       </c>
-      <c r="C115" s="37" t="inlineStr">
-        <is>
-          <t>18:55</t>
-        </is>
-      </c>
-      <c r="D115" s="38" t="inlineStr">
+      <c r="D115" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E115" s="39" t="inlineStr">
-        <is>
-          <t>Subte N/W desde 36 Av hasta Times Sq y 1/2/3 hasta 72 St (~45 min).</t>
-        </is>
-      </c>
-      <c r="F115" s="37" t="inlineStr"/>
-      <c r="G115" s="40" t="inlineStr"/>
+      <c r="E115" s="45" t="inlineStr">
+        <is>
+          <t>★★ MUSEUM OF THE MOVING IMAGE — GRATIS los jueves 14-18, sus únicas horas del jueves. RECUPERADO: había quedado afuera del plan y ustedes lo tienen 2/2. Una hora y media alcanza para Behind the Screen y los Muppets originales de Jim Henson. Cierra 18:00 EN PUNTO. (N/W hasta 36 Av + 8 min a pie.)</t>
+        </is>
+      </c>
+      <c r="F115" s="43" t="inlineStr">
+        <is>
+          <t>Museum of the Moving Image</t>
+        </is>
+      </c>
+      <c r="G115" s="40" t="inlineStr">
+        <is>
+          <t>🚇 ~40 min en subte · 11.5 km (a pie 155 min) · estimado</t>
+        </is>
+      </c>
       <c r="H115" s="41" t="inlineStr"/>
       <c r="I115" s="41" t="inlineStr"/>
     </row>
@@ -35306,14 +35306,14 @@
       <c r="A116" s="35" t="n"/>
       <c r="B116" s="36" t="inlineStr">
         <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="C116" s="37" t="inlineStr">
+        <is>
           <t>18:55</t>
         </is>
       </c>
-      <c r="C116" s="37" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
       <c r="D116" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35321,30 +35321,26 @@
       </c>
       <c r="E116" s="39" t="inlineStr">
         <is>
-          <t>The Beacon: check-in formal y subir las maletas.</t>
-        </is>
-      </c>
-      <c r="F116" s="37" t="inlineStr">
-        <is>
-          <t>Hotel The Beacon (3-6 sep)</t>
-        </is>
-      </c>
+          <t>Subte N/W desde 36 Av hasta Times Sq y 1/2/3 hasta 72 St (~45 min).</t>
+        </is>
+      </c>
+      <c r="F116" s="37" t="inlineStr"/>
       <c r="G116" s="40" t="inlineStr"/>
       <c r="H116" s="41" t="inlineStr"/>
       <c r="I116" s="41" t="inlineStr"/>
     </row>
-    <row r="117" ht="30" customHeight="1">
+    <row r="117" ht="16" customHeight="1">
       <c r="A117" s="35" t="n"/>
       <c r="B117" s="36" t="inlineStr">
         <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="C117" s="37" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="C117" s="37" t="inlineStr">
-        <is>
-          <t>19:55</t>
-        </is>
-      </c>
       <c r="D117" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35352,130 +35348,134 @@
       </c>
       <c r="E117" s="39" t="inlineStr">
         <is>
-          <t>Cena RÁPIDA en el Upper West Side, bajando por Broadway o Columbus. Hoy se come temprano y liviano: la noche tiene tres paradas y todas valen.</t>
-        </is>
-      </c>
-      <c r="F117" s="37" t="inlineStr"/>
+          <t>The Beacon: check-in formal y subir las maletas.</t>
+        </is>
+      </c>
+      <c r="F117" s="37" t="inlineStr">
+        <is>
+          <t>Hotel The Beacon (3-6 sep)</t>
+        </is>
+      </c>
       <c r="G117" s="40" t="inlineStr"/>
       <c r="H117" s="41" t="inlineStr"/>
       <c r="I117" s="41" t="inlineStr"/>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="35" t="n"/>
-      <c r="B118" s="42" t="inlineStr">
+      <c r="B118" s="36" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C118" s="37" t="inlineStr">
         <is>
           <t>19:55</t>
         </is>
       </c>
-      <c r="C118" s="43" t="inlineStr">
-        <is>
-          <t>20:20</t>
-        </is>
-      </c>
-      <c r="D118" s="44" t="inlineStr">
+      <c r="D118" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E118" s="45" t="inlineStr">
-        <is>
-          <t>★ LINCOLN CENTER DE NOCHE (gratis, 20 min) — OJO, VERIFICADO el 27/8 y cambia lo que van a encontrar: esta noche la Josie Robertson Plaza NO está tranquila. El Met proyecta Tristan und Isolde (actos II y III) a las 20:00 en pantalla gigante, gratis y sin reserva, y despejan la plaza desde las 18:00 para armar 2.500 sillas. O sea: llegan justo cuando se está llenando. La fuente y los chandeliers siguen ahí, pero con multitud y pantalla. Puede ser mejor que el plan original —hay ambiente de estreno— o puede ser un quilombo: decidan en el momento. Si prefieren el Lincoln Center vacío, el espejo de agua con el Henry Moore está del lado norte, detrás del Vivian Beaumont, y ahí no hay nadie.</t>
-        </is>
-      </c>
-      <c r="F118" s="43" t="inlineStr">
-        <is>
-          <t>Lincoln Center (campus y plaza)</t>
-        </is>
-      </c>
-      <c r="G118" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~20 min a pie (1.3 km) o 🚇 ~15 min · estimado</t>
-        </is>
-      </c>
+      <c r="E118" s="39" t="inlineStr">
+        <is>
+          <t>Cena RÁPIDA en el Upper West Side, bajando por Broadway o Columbus. Hoy se come temprano y liviano: la noche tiene tres paradas y todas valen.</t>
+        </is>
+      </c>
+      <c r="F118" s="37" t="inlineStr"/>
+      <c r="G118" s="40" t="inlineStr"/>
       <c r="H118" s="41" t="inlineStr"/>
       <c r="I118" s="41" t="inlineStr"/>
     </row>
-    <row r="119" ht="16" customHeight="1">
+    <row r="119" ht="30" customHeight="1">
       <c r="A119" s="35" t="n"/>
-      <c r="B119" s="36" t="inlineStr">
+      <c r="B119" s="42" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="C119" s="43" t="inlineStr">
         <is>
           <t>20:20</t>
         </is>
       </c>
-      <c r="C119" s="37" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="D119" s="38" t="inlineStr">
+      <c r="D119" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E119" s="39" t="inlineStr">
-        <is>
-          <t>Caminar seis cuadras por Broadway hasta Columbus Circle (~8 min).</t>
-        </is>
-      </c>
-      <c r="F119" s="37" t="inlineStr"/>
-      <c r="G119" s="40" t="inlineStr"/>
+      <c r="E119" s="45" t="inlineStr">
+        <is>
+          <t>★ LINCOLN CENTER DE NOCHE (gratis, 20 min) — OJO, VERIFICADO el 27/8 y cambia lo que van a encontrar: esta noche la Josie Robertson Plaza NO está tranquila. El Met proyecta Tristan und Isolde (actos II y III) a las 20:00 en pantalla gigante, gratis y sin reserva, y despejan la plaza desde las 18:00 para armar 2.500 sillas. O sea: llegan justo cuando se está llenando. La fuente y los chandeliers siguen ahí, pero con multitud y pantalla. Puede ser mejor que el plan original —hay ambiente de estreno— o puede ser un quilombo: decidan en el momento. Si prefieren el Lincoln Center vacío, el espejo de agua con el Henry Moore está del lado norte, detrás del Vivian Beaumont, y ahí no hay nadie.</t>
+        </is>
+      </c>
+      <c r="F119" s="43" t="inlineStr">
+        <is>
+          <t>Lincoln Center (campus y plaza)</t>
+        </is>
+      </c>
+      <c r="G119" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~20 min a pie (1.3 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H119" s="41" t="inlineStr"/>
       <c r="I119" s="41" t="inlineStr"/>
     </row>
-    <row r="120" ht="30" customHeight="1">
+    <row r="120" ht="16" customHeight="1">
       <c r="A120" s="35" t="n"/>
-      <c r="B120" s="42" t="inlineStr">
+      <c r="B120" s="36" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="C120" s="37" t="inlineStr">
         <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="C120" s="43" t="inlineStr">
-        <is>
-          <t>20:55</t>
-        </is>
-      </c>
-      <c r="D120" s="44" t="inlineStr">
+      <c r="D120" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E120" s="45" t="inlineStr">
-        <is>
-          <t>★★ MO LOUNGE, PISO 35 DEL MANDARIN ORIENTAL (80 Columbus Circle) — el dato del amigo de Juan, con una corrección: es el piso 35, no el 60 (el hotel ocupa del 35 al 54). Ventanales de piso a techo sobre Central Park con la ciudad encendida abajo. Coctel ~$26-32, sin cover. RESERVAR por SevenRooms desde su web. Si prefieren algo más íntimo, en ese MISMO piso está The Bar (ex speakeasy The Office, 45 asientos, mar-sáb 17-1h).</t>
-        </is>
-      </c>
-      <c r="F120" s="43" t="inlineStr">
-        <is>
-          <t>MO Lounge — Mandarin Oriental (piso 35)</t>
-        </is>
-      </c>
+      <c r="E120" s="39" t="inlineStr">
+        <is>
+          <t>Caminar seis cuadras por Broadway hasta Columbus Circle (~8 min).</t>
+        </is>
+      </c>
+      <c r="F120" s="37" t="inlineStr"/>
       <c r="G120" s="40" t="inlineStr"/>
       <c r="H120" s="41" t="inlineStr"/>
       <c r="I120" s="41" t="inlineStr"/>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="35" t="n"/>
-      <c r="B121" s="36" t="inlineStr">
+      <c r="B121" s="42" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C121" s="43" t="inlineStr">
         <is>
           <t>20:55</t>
         </is>
       </c>
-      <c r="C121" s="37" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="D121" s="38" t="inlineStr">
+      <c r="D121" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E121" s="39" t="inlineStr">
-        <is>
-          <t>Bajar en ascensor: Dizzy's está EN EL MISMO EDIFICIO (10 Columbus Circle, piso 5). Cero calle, cero frío.</t>
-        </is>
-      </c>
-      <c r="F121" s="37" t="inlineStr"/>
+      <c r="E121" s="45" t="inlineStr">
+        <is>
+          <t>★★ MO LOUNGE, PISO 35 DEL MANDARIN ORIENTAL (80 Columbus Circle) — el dato del amigo de Juan, con una corrección: es el piso 35, no el 60 (el hotel ocupa del 35 al 54). Ventanales de piso a techo sobre Central Park con la ciudad encendida abajo. Coctel ~$26-32, sin cover. RESERVAR por SevenRooms desde su web. Si prefieren algo más íntimo, en ese MISMO piso está The Bar (ex speakeasy The Office, 45 asientos, mar-sáb 17-1h).</t>
+        </is>
+      </c>
+      <c r="F121" s="43" t="inlineStr">
+        <is>
+          <t>MO Lounge — Mandarin Oriental (piso 35)</t>
+        </is>
+      </c>
       <c r="G121" s="40" t="inlineStr"/>
       <c r="H121" s="41" t="inlineStr"/>
       <c r="I121" s="41" t="inlineStr"/>
@@ -35484,10 +35484,14 @@
       <c r="A122" s="35" t="n"/>
       <c r="B122" s="36" t="inlineStr">
         <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="C122" s="37" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C122" s="37" t="inlineStr"/>
       <c r="D122" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35495,78 +35499,74 @@
       </c>
       <c r="E122" s="39" t="inlineStr">
         <is>
-          <t>★ Dizzy's Club — ventanales sobre Central Park detrás del escenario, un piso abajo del cóctel. SEAMOS HONESTOS: JP lleva ~17 horas en pie con 5 de sueño. Decidan A LAS 20:00, arriba en el Mandarin: si están enteros, bajan; si no, se quedan con la vista y el trago, que ya es un cierre precioso. El set Late Night (~22:45) cuesta una fracción — variante para valientes.</t>
-        </is>
-      </c>
-      <c r="F122" s="37" t="inlineStr">
-        <is>
-          <t>Dizzy's Club (Jazz at Lincoln Center)</t>
-        </is>
-      </c>
+          <t>Bajar en ascensor: Dizzy's está EN EL MISMO EDIFICIO (10 Columbus Circle, piso 5). Cero calle, cero frío.</t>
+        </is>
+      </c>
+      <c r="F122" s="37" t="inlineStr"/>
       <c r="G122" s="40" t="inlineStr"/>
       <c r="H122" s="41" t="inlineStr"/>
       <c r="I122" s="41" t="inlineStr"/>
     </row>
-    <row r="123" ht="32" customHeight="1">
-      <c r="A123" s="46" t="inlineStr">
+    <row r="123" ht="30" customHeight="1">
+      <c r="A123" s="35" t="n"/>
+      <c r="B123" s="36" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C123" s="37" t="inlineStr"/>
+      <c r="D123" s="38" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E123" s="39" t="inlineStr">
+        <is>
+          <t>★ Dizzy's Club — ventanales sobre Central Park detrás del escenario, un piso abajo del cóctel. SEAMOS HONESTOS: JP lleva ~17 horas en pie con 5 de sueño. Decidan A LAS 20:00, arriba en el Mandarin: si están enteros, bajan; si no, se quedan con la vista y el trago, que ya es un cierre precioso. El set Late Night (~22:45) cuesta una fracción — variante para valientes.</t>
+        </is>
+      </c>
+      <c r="F123" s="37" t="inlineStr">
+        <is>
+          <t>Dizzy's Club (Jazz at Lincoln Center)</t>
+        </is>
+      </c>
+      <c r="G123" s="40" t="inlineStr"/>
+      <c r="H123" s="41" t="inlineStr"/>
+      <c r="I123" s="41" t="inlineStr"/>
+    </row>
+    <row r="124" ht="32" customHeight="1">
+      <c r="A124" s="46" t="inlineStr">
         <is>
           <t>ALTERNATIVA / OJO:  ⚠️ EL PROBLEMA DE LA NOCHE ANTERIOR: si JP viaja desde New Jersey el jueves, significa que durmió allá el miércoles — y el miércoles el SummerStage termina a las 22:00 en Central Park. Llegando a Penn ~22:25 se toma el directo de las 22:48, que deja en Raritan ~0:04, más Uber: llegada al hotel ~0:25 y despertador a las 5:45. Son cinco horas de sueño antes de un día completo. Tres salidas: (a) salir del SummerStage a las 21:15, después del set principal; (b) quedarse una noche más en el JGStay y que Thais lleve las maletas el jueves (implica tocar la reserva); (c) tomar el tren de las 7:13 en vez del de 6:55 y arrancar 20 minutos más tarde. Verificá los horarios exactos de la tarde-noche en njtransit.com: solo tengo confirmado el directo de las 22:48. // EL FERRY, SI LES DUELE (lo tienen 2/2): al salir del MoMI, W directo hasta Whitehall (~50 min), ferry ~19:15 — el atardecer (~19:22) de ida y la Estatua y el skyline ILUMINADOS de vuelta; check-in ~21:15, cena tarde cerca del hotel, y Dizzy's tiene set Late Night los jueves ~22:45 como consuelo. Es MÁS día: elíjanlo solo si llegan enteros. // Siguen afuera: MoMA PS1, Astoria y Gantry (sin hueco); ya habían salido Noguchi, Astoria Park y Socrates por interés bajo.</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="22" customHeight="1">
-      <c r="A125" s="33" t="inlineStr">
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="33" t="inlineStr">
         <is>
           <t>DÍA 7 · Viernes 04/09 · Vessel + High Line, SUMMIT al atardecer y el VANGUARD de a dos  —  base: The Beacon  ·  Ambos</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="32" customHeight="1">
-      <c r="A126" s="34" t="inlineStr">
+    <row r="127" ht="32" customHeight="1">
+      <c r="A127" s="34" t="inlineStr">
         <is>
           <t>Salieron el West Village, Washington Square y el Whitney; entraron el High Line, THE VESSEL (al pie del arranque, $10 y 45 min), la Morgan (hoy GRATIS 17-20) y SUMMIT — que se movió AL ATARDECER por el pedido de ustedes: entrada 18:10, luz plena, la puesta ~19:21 multiplicada por los espejos de Kusama (es EL lugar de la ciudad para ese momento) y la noche encendida hasta las 20:15. EL PAGO, dicho honesto: la Morgan se hace en una hora entrando 17:00 en punto, y la cena de hoy es un bocado rápido — por eso el almuerzo en Chelsea Market es EL fuerte del día. SALIÓ GRAND CENTRAL: estaba a las 16:20 con el argumento de que JP ya lo vio el lunes y Thais no — pero ella lo tiene en 0, así que eran 40 minutos para alguien que no lo quiere. Sin esa parada tampoco hace falta cortar Chelsea a las 15:50: se sale 16:25 derecho a la Morgan y la tarde de galerías y almuerzo gana una hora larga.</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="35" t="n"/>
-      <c r="B127" s="36" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="C127" s="37" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="D127" s="38" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="E127" s="39" t="inlineStr">
-        <is>
-          <t>Subte a Hudson Yards.</t>
-        </is>
-      </c>
-      <c r="F127" s="37" t="inlineStr"/>
-      <c r="G127" s="40" t="inlineStr"/>
-      <c r="H127" s="41" t="inlineStr"/>
-      <c r="I127" s="41" t="inlineStr"/>
-    </row>
-    <row r="128" ht="30" customHeight="1">
+    <row r="128" ht="16" customHeight="1">
       <c r="A128" s="35" t="n"/>
       <c r="B128" s="36" t="inlineStr">
         <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C128" s="37" t="inlineStr">
+        <is>
           <t>09:40</t>
         </is>
       </c>
-      <c r="C128" s="37" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="D128" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="E128" s="39" t="inlineStr">
         <is>
-          <t>La plaza de Hudson Yards mientras abre el Vessel: The Shops y el Shed desde afuera. Sacar el timed ticket de las 10:00 online antes.</t>
+          <t>Subte a Hudson Yards.</t>
         </is>
       </c>
       <c r="F128" s="37" t="inlineStr"/>
@@ -35584,31 +35584,27 @@
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="35" t="n"/>
-      <c r="B129" s="42" t="inlineStr">
+      <c r="B129" s="36" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="C129" s="37" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="C129" s="43" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="D129" s="44" t="inlineStr">
+      <c r="D129" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E129" s="45" t="inlineStr">
-        <is>
-          <t>★ THE VESSEL — la escalera infinita de Heatherwick: 154 tramos, 2.500 escalones, $10. Reabierto con redes; algunos tramos altos hacia el Hudson siguen cerrados, y hay ascensor cada 15 min. Subir es la única forma de entenderla. Si Thais prefiere no subir, la plaza está al pie.</t>
-        </is>
-      </c>
-      <c r="F129" s="43" t="inlineStr">
-        <is>
-          <t>The Vessel</t>
-        </is>
-      </c>
+      <c r="E129" s="39" t="inlineStr">
+        <is>
+          <t>La plaza de Hudson Yards mientras abre el Vessel: The Shops y el Shed desde afuera. Sacar el timed ticket de las 10:00 online antes.</t>
+        </is>
+      </c>
+      <c r="F129" s="37" t="inlineStr"/>
       <c r="G129" s="40" t="inlineStr"/>
       <c r="H129" s="41" t="inlineStr"/>
       <c r="I129" s="41" t="inlineStr"/>
@@ -35617,14 +35613,14 @@
       <c r="A130" s="35" t="n"/>
       <c r="B130" s="42" t="inlineStr">
         <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C130" s="43" t="inlineStr">
+        <is>
           <t>10:50</t>
         </is>
       </c>
-      <c r="C130" s="43" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="D130" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35632,52 +35628,48 @@
       </c>
       <c r="E130" s="45" t="inlineStr">
         <is>
-          <t>★ THE HIGH LINE completo, de norte a sur (2,3 km) — arranca ahí mismo, en 30th y 10ª. Vía ferroviaria elevada convertida en parque lineal. Incluye el Buda de arenisca de 9 metros de Tuan Andrew Nguyen.</t>
+          <t>★ THE VESSEL — la escalera infinita de Heatherwick: 154 tramos, 2.500 escalones, $10. Reabierto con redes; algunos tramos altos hacia el Hudson siguen cerrados, y hay ascensor cada 15 min. Subir es la única forma de entenderla. Si Thais prefiere no subir, la plaza está al pie.</t>
         </is>
       </c>
       <c r="F130" s="43" t="inlineStr">
         <is>
-          <t>The High Line</t>
-        </is>
-      </c>
-      <c r="G130" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~12 min a pie · 0.9 km · estimado</t>
-        </is>
-      </c>
+          <t>The Vessel</t>
+        </is>
+      </c>
+      <c r="G130" s="40" t="inlineStr"/>
       <c r="H130" s="41" t="inlineStr"/>
       <c r="I130" s="41" t="inlineStr"/>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="35" t="n"/>
-      <c r="B131" s="36" t="inlineStr">
+      <c r="B131" s="42" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="C131" s="43" t="inlineStr">
         <is>
           <t>12:20</t>
         </is>
       </c>
-      <c r="C131" s="37" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="D131" s="38" t="inlineStr">
+      <c r="D131" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E131" s="39" t="inlineStr">
-        <is>
-          <t>Little Island — el parque flotante de Heatherwick sobre 132 macetas de hormigón, al final del High Line. Gratis.</t>
-        </is>
-      </c>
-      <c r="F131" s="37" t="inlineStr">
-        <is>
-          <t>Little Island</t>
+      <c r="E131" s="45" t="inlineStr">
+        <is>
+          <t>★ THE HIGH LINE completo, de norte a sur (2,3 km) — arranca ahí mismo, en 30th y 10ª. Vía ferroviaria elevada convertida en parque lineal. Incluye el Buda de arenisca de 9 metros de Tuan Andrew Nguyen.</t>
+        </is>
+      </c>
+      <c r="F131" s="43" t="inlineStr">
+        <is>
+          <t>The High Line</t>
         </is>
       </c>
       <c r="G131" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~15 min a pie · 1.1 km · estimado</t>
+          <t>🚶 ~12 min a pie · 0.9 km · estimado</t>
         </is>
       </c>
       <c r="H131" s="41" t="inlineStr"/>
@@ -35685,63 +35677,63 @@
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="35" t="n"/>
-      <c r="B132" s="42" t="inlineStr">
+      <c r="B132" s="36" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="C132" s="37" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="C132" s="43" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="D132" s="44" t="inlineStr">
+      <c r="D132" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E132" s="45" t="inlineStr">
-        <is>
-          <t>Galerías de Chelsea COMPLETAS — W 19th a W 27th entre la 10ª y la 11ª, concentradas en W 24th y W 21st (Gagosian, Pace, Zwirner). Gratis, se entra y se sale. El recorte del Vessel se devolvió: SUMMIT pasó al atardecer y la tarde se estiró.</t>
-        </is>
-      </c>
-      <c r="F132" s="43" t="inlineStr"/>
-      <c r="G132" s="40" t="inlineStr"/>
+      <c r="E132" s="39" t="inlineStr">
+        <is>
+          <t>Little Island — el parque flotante de Heatherwick sobre 132 macetas de hormigón, al final del High Line. Gratis.</t>
+        </is>
+      </c>
+      <c r="F132" s="37" t="inlineStr">
+        <is>
+          <t>Little Island</t>
+        </is>
+      </c>
+      <c r="G132" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~15 min a pie · 1.1 km · estimado</t>
+        </is>
+      </c>
       <c r="H132" s="41" t="inlineStr"/>
       <c r="I132" s="41" t="inlineStr"/>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="35" t="n"/>
-      <c r="B133" s="36" t="inlineStr">
+      <c r="B133" s="42" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C133" s="43" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="C133" s="37" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="D133" s="38" t="inlineStr">
+      <c r="D133" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E133" s="39" t="inlineStr">
-        <is>
-          <t>Almuerzo en Chelsea Market — COMER FUERTE: es la comida grande del día, la cena de hoy es un bocado rápido entre el SUMMIT y el Vanguard. Los Tacos No.1 o Very Fresh Noodles. Ahora hay casi DOS HORAS: sin apuro, y si quedaron galerías de Chelsea sin ver, se vuelve.</t>
-        </is>
-      </c>
-      <c r="F133" s="37" t="inlineStr">
-        <is>
-          <t>Chelsea Market</t>
-        </is>
-      </c>
-      <c r="G133" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~7 min a pie · 0.5 km · estimado</t>
-        </is>
-      </c>
+      <c r="E133" s="45" t="inlineStr">
+        <is>
+          <t>Galerías de Chelsea COMPLETAS — W 19th a W 27th entre la 10ª y la 11ª, concentradas en W 24th y W 21st (Gagosian, Pace, Zwirner). Gratis, se entra y se sale. El recorte del Vessel se devolvió: SUMMIT pasó al atardecer y la tarde se estiró.</t>
+        </is>
+      </c>
+      <c r="F133" s="43" t="inlineStr"/>
+      <c r="G133" s="40" t="inlineStr"/>
       <c r="H133" s="41" t="inlineStr"/>
       <c r="I133" s="41" t="inlineStr"/>
     </row>
@@ -35749,14 +35741,14 @@
       <c r="A134" s="35" t="n"/>
       <c r="B134" s="36" t="inlineStr">
         <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C134" s="37" t="inlineStr">
+        <is>
           <t>16:25</t>
         </is>
       </c>
-      <c r="C134" s="37" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="D134" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35764,126 +35756,134 @@
       </c>
       <c r="E134" s="39" t="inlineStr">
         <is>
-          <t>A la Morgan: L desde 14 St-8 Av hasta Union Sq y 6 hasta 33 St, o A/C/E hasta 34 St-Penn y siete cuadras a pie (~30 min). Salir 16:25 deja margen para entrar 17:00 EN PUNTO.</t>
-        </is>
-      </c>
-      <c r="F134" s="37" t="inlineStr"/>
-      <c r="G134" s="40" t="inlineStr"/>
+          <t>Almuerzo en Chelsea Market — COMER FUERTE: es la comida grande del día, la cena de hoy es un bocado rápido entre el SUMMIT y el Vanguard. Los Tacos No.1 o Very Fresh Noodles. Ahora hay casi DOS HORAS: sin apuro, y si quedaron galerías de Chelsea sin ver, se vuelve.</t>
+        </is>
+      </c>
+      <c r="F134" s="37" t="inlineStr">
+        <is>
+          <t>Chelsea Market</t>
+        </is>
+      </c>
+      <c r="G134" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~7 min a pie · 0.5 km · estimado</t>
+        </is>
+      </c>
       <c r="H134" s="41" t="inlineStr"/>
       <c r="I134" s="41" t="inlineStr"/>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="35" t="n"/>
-      <c r="B135" s="42" t="inlineStr">
+      <c r="B135" s="36" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="C135" s="37" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="C135" s="43" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="D135" s="44" t="inlineStr">
+      <c r="D135" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E135" s="45" t="inlineStr">
-        <is>
-          <t>★ MORGAN LIBRARY — GRATIS los viernes 17-20h: entrar 17:00 EN PUNTO y hacerla en una hora — la biblioteca son tres salas gloriosas (estanterías de nogal, la Biblia de Gutenberg): alcanza. RESERVA OBLIGATORIA, se libera el viernes 28 de agosto. Está a 8 min a pie de One Vanderbilt.</t>
-        </is>
-      </c>
-      <c r="F135" s="43" t="inlineStr">
-        <is>
-          <t>The Morgan Library &amp; Museum</t>
-        </is>
-      </c>
+      <c r="E135" s="39" t="inlineStr">
+        <is>
+          <t>A la Morgan: L desde 14 St-8 Av hasta Union Sq y 6 hasta 33 St, o A/C/E hasta 34 St-Penn y siete cuadras a pie (~30 min). Salir 16:25 deja margen para entrar 17:00 EN PUNTO.</t>
+        </is>
+      </c>
+      <c r="F135" s="37" t="inlineStr"/>
       <c r="G135" s="40" t="inlineStr"/>
       <c r="H135" s="41" t="inlineStr"/>
       <c r="I135" s="41" t="inlineStr"/>
     </row>
-    <row r="136" ht="16" customHeight="1">
+    <row r="136" ht="30" customHeight="1">
       <c r="A136" s="35" t="n"/>
-      <c r="B136" s="36" t="inlineStr">
+      <c r="B136" s="42" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C136" s="43" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="C136" s="37" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="D136" s="38" t="inlineStr">
+      <c r="D136" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E136" s="39" t="inlineStr">
-        <is>
-          <t>Caminar las seis cuadras de la Morgan a One Vanderbilt (~8-10 min).</t>
-        </is>
-      </c>
-      <c r="F136" s="37" t="inlineStr"/>
+      <c r="E136" s="45" t="inlineStr">
+        <is>
+          <t>★ MORGAN LIBRARY — GRATIS los viernes 17-20h: entrar 17:00 EN PUNTO y hacerla en una hora — la biblioteca son tres salas gloriosas (estanterías de nogal, la Biblia de Gutenberg): alcanza. RESERVA OBLIGATORIA, se libera el viernes 28 de agosto. Está a 8 min a pie de One Vanderbilt.</t>
+        </is>
+      </c>
+      <c r="F136" s="43" t="inlineStr">
+        <is>
+          <t>The Morgan Library &amp; Museum</t>
+        </is>
+      </c>
       <c r="G136" s="40" t="inlineStr"/>
       <c r="H136" s="41" t="inlineStr"/>
       <c r="I136" s="41" t="inlineStr"/>
     </row>
-    <row r="137" ht="30" customHeight="1">
+    <row r="137" ht="16" customHeight="1">
       <c r="A137" s="35" t="n"/>
-      <c r="B137" s="42" t="inlineStr">
+      <c r="B137" s="36" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C137" s="37" t="inlineStr">
         <is>
           <t>18:10</t>
         </is>
       </c>
-      <c r="C137" s="43" t="inlineStr">
-        <is>
-          <t>20:20</t>
-        </is>
-      </c>
-      <c r="D137" s="44" t="inlineStr">
+      <c r="D137" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E137" s="45" t="inlineStr">
-        <is>
-          <t>★★ SUMMIT ONE VANDERBILT — EL ARCO COMPLETO: entrada 18:10 con luz, el atardecer ~19:21 multiplicado por los espejos infinitos de Kusama, y la noche encendida hasta ~20:15. Ticket ATARDECER $57-63 — es la franja que primero se agota: reservar YA. NO está en ningún pase.</t>
-        </is>
-      </c>
-      <c r="F137" s="43" t="inlineStr">
-        <is>
-          <t>SUMMIT One Vanderbilt</t>
-        </is>
-      </c>
+      <c r="E137" s="39" t="inlineStr">
+        <is>
+          <t>Caminar las seis cuadras de la Morgan a One Vanderbilt (~8-10 min).</t>
+        </is>
+      </c>
+      <c r="F137" s="37" t="inlineStr"/>
       <c r="G137" s="40" t="inlineStr"/>
       <c r="H137" s="41" t="inlineStr"/>
       <c r="I137" s="41" t="inlineStr"/>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="35" t="n"/>
-      <c r="B138" s="36" t="inlineStr">
+      <c r="B138" s="42" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="C138" s="43" t="inlineStr">
         <is>
           <t>20:20</t>
         </is>
       </c>
-      <c r="C138" s="37" t="inlineStr">
-        <is>
-          <t>20:50</t>
-        </is>
-      </c>
-      <c r="D138" s="38" t="inlineStr">
+      <c r="D138" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E138" s="39" t="inlineStr">
-        <is>
-          <t>Bajar AL VILLAGE PRIMERO y cenar allá: 4/5/6 o 7 hasta 14 St-Union Sq y 1 hasta Christopher St (~25 min). Cenar cerca de Grand Central y bajar después llega justo; hacerlo al revés deja margen.</t>
-        </is>
-      </c>
-      <c r="F138" s="37" t="inlineStr"/>
+      <c r="E138" s="45" t="inlineStr">
+        <is>
+          <t>★★ SUMMIT ONE VANDERBILT — EL ARCO COMPLETO: entrada 18:10 con luz, el atardecer ~19:21 multiplicado por los espejos infinitos de Kusama, y la noche encendida hasta ~20:15. Ticket ATARDECER $57-63 — es la franja que primero se agota: reservar YA. NO está en ningún pase.</t>
+        </is>
+      </c>
+      <c r="F138" s="43" t="inlineStr">
+        <is>
+          <t>SUMMIT One Vanderbilt</t>
+        </is>
+      </c>
       <c r="G138" s="40" t="inlineStr"/>
       <c r="H138" s="41" t="inlineStr"/>
       <c r="I138" s="41" t="inlineStr"/>
@@ -35892,14 +35892,14 @@
       <c r="A139" s="35" t="n"/>
       <c r="B139" s="36" t="inlineStr">
         <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="C139" s="37" t="inlineStr">
+        <is>
           <t>20:50</t>
         </is>
       </c>
-      <c r="C139" s="37" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
       <c r="D139" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35907,7 +35907,7 @@
       </c>
       <c r="E139" s="39" t="inlineStr">
         <is>
-          <t>Cena en el West Village, a cinco minutos del club. El Vanguard NO sirve NADA de comida (lo dicen así: 'ni un maní') y no se permite entrar comida: lo que no cenen ahora, no se cena. 40 minutos alcanzan.</t>
+          <t>Bajar AL VILLAGE PRIMERO y cenar allá: 4/5/6 o 7 hasta 14 St-Union Sq y 1 hasta Christopher St (~25 min). Cenar cerca de Grand Central y bajar después llega justo; hacerlo al revés deja margen.</t>
         </is>
       </c>
       <c r="F139" s="37" t="inlineStr"/>
@@ -35919,14 +35919,14 @@
       <c r="A140" s="35" t="n"/>
       <c r="B140" s="36" t="inlineStr">
         <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="C140" s="37" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C140" s="37" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
       <c r="D140" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35934,7 +35934,7 @@
       </c>
       <c r="E140" s="39" t="inlineStr">
         <is>
-          <t>EN LA PUERTA DEL VANGUARD a las 21:30 EN PUNTO: el acomodo del segundo set arranca a esa hora y los asientos son POR ORDEN DE LLEGADA — la entrada es General Admission, no numerada. Con 123 asientos, los diez minutos de diferencia son estar frente al piano o contra la columna. El ticket lo dice: el acomodo tardío, con entrada o sin ella, queda a criterio del encargado.</t>
+          <t>Cena en el West Village, a cinco minutos del club. El Vanguard NO sirve NADA de comida (lo dicen así: 'ni un maní') y no se permite entrar comida: lo que no cenen ahora, no se cena. 40 minutos alcanzan.</t>
         </is>
       </c>
       <c r="F140" s="37" t="inlineStr"/>
@@ -35944,199 +35944,199 @@
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="35" t="n"/>
-      <c r="B141" s="42" t="inlineStr">
+      <c r="B141" s="36" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C141" s="37" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C141" s="43" t="inlineStr"/>
-      <c r="D141" s="44" t="inlineStr">
+      <c r="D141" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E141" s="45" t="inlineStr">
-        <is>
-          <t>★★ VILLAGE VANGUARD — JOHN PATITUCCI TRIO con Chris Potter y Brian Blade, SET DE LAS 22:00. Movido acá desde el martes para que vayan LOS DOS (pedido de Juan). El sótano triangular de 1935, 123 asientos, la acústica que grabó a Coltrane. ✔ ENTRADAS COMPRADAS el 26/8: 2 × General Admission $45 (#18741454 y #18741456), a nombre de Juan Pablo Garicoïts. Falta solo el mínimo de UNA CONSUMICIÓN por cabeza en la mesa (vale gaseosa, jugo o agua) — se paga ahí, aceptan tarjeta.</t>
-        </is>
-      </c>
-      <c r="F141" s="43" t="inlineStr">
-        <is>
-          <t>Village Vanguard</t>
-        </is>
-      </c>
+      <c r="E141" s="39" t="inlineStr">
+        <is>
+          <t>EN LA PUERTA DEL VANGUARD a las 21:30 EN PUNTO: el acomodo del segundo set arranca a esa hora y los asientos son POR ORDEN DE LLEGADA — la entrada es General Admission, no numerada. Con 123 asientos, los diez minutos de diferencia son estar frente al piano o contra la columna. El ticket lo dice: el acomodo tardío, con entrada o sin ella, queda a criterio del encargado.</t>
+        </is>
+      </c>
+      <c r="F141" s="37" t="inlineStr"/>
       <c r="G141" s="40" t="inlineStr"/>
       <c r="H141" s="41" t="inlineStr"/>
       <c r="I141" s="41" t="inlineStr"/>
     </row>
-    <row r="142" ht="32" customHeight="1">
-      <c r="A142" s="46" t="inlineStr">
+    <row r="142" ht="30" customHeight="1">
+      <c r="A142" s="35" t="n"/>
+      <c r="B142" s="42" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C142" s="43" t="inlineStr"/>
+      <c r="D142" s="44" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E142" s="45" t="inlineStr">
+        <is>
+          <t>★★ VILLAGE VANGUARD — JOHN PATITUCCI TRIO con Chris Potter y Brian Blade, SET DE LAS 22:00. Movido acá desde el martes para que vayan LOS DOS (pedido de Juan). El sótano triangular de 1935, 123 asientos, la acústica que grabó a Coltrane. ✔ ENTRADAS COMPRADAS el 26/8: 2 × General Admission $45 (#18741454 y #18741456), a nombre de Juan Pablo Garicoïts. Falta solo el mínimo de UNA CONSUMICIÓN por cabeza en la mesa (vale gaseosa, jugo o agua) — se paga ahí, aceptan tarjeta.</t>
+        </is>
+      </c>
+      <c r="F142" s="43" t="inlineStr">
+        <is>
+          <t>Village Vanguard</t>
+        </is>
+      </c>
+      <c r="G142" s="40" t="inlineStr"/>
+      <c r="H142" s="41" t="inlineStr"/>
+      <c r="I142" s="41" t="inlineStr"/>
+    </row>
+    <row r="143" ht="32" customHeight="1">
+      <c r="A143" s="46" t="inlineStr">
         <is>
           <t>ALTERNATIVA / OJO:  EL CANJE DE ESTA NOCHE: para meter el Vanguard con Thais, SALIÓ BILL'S PLACE. No hay otra noche donde entre (Bill Saxton toca solo viernes y sábado, y el sábado está tomado por Peter Luger + el play + el Café Wha). Con las entradas ya compradas y sin cambios ni transferencias, el canje quedó CERRADO: Bill's Place sale del viaje. // EL WHITNEY, con los números verificados el 27/8: gratis todos los viernes de 17:00 a 22:00 (normal $30), y hoy pasan por Meatpacking, que es donde está. Coincide barrio, día y franja. El problema es el reloj y es serio: la Morgan también es hoy 17:00-20:00 y el SUMMIT entra 18:10. Meter el Whitney obliga a recortar el High Line o a soltar la Morgan, que ustedes tienen en 2 y el Whitney en 'quizás'. Si igual lo prefieren, el ticket gratis es OBLIGATORIO y hay que sacarlo antes. Si igual lo prefieren, el ticket gratis es OBLIGATORIO y el Whitney ahora cierra los martes. SI ALGO SALIERA MAL con el acomodo (llegar tarde y que no haya lugar): Mezzrow o Smalls quedan a cuatro cuadras ($25 con bebida, Smalls tiene jam de madrugada los viernes desde la 1:00), o el Blue Note — el 4 y 5 de septiembre toca Chief Adjuah.</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="22" customHeight="1">
-      <c r="A144" s="33" t="inlineStr">
+    <row r="145" ht="22" customHeight="1">
+      <c r="A145" s="33" t="inlineStr">
         <is>
           <t>DÍA 8 · Sábado 05/09 · Brooklyn, Peter Luger, un PLAY y Café Wha hasta la madrugada  —  base: The Beacon  ·  Ambos</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="32" customHeight="1">
-      <c r="A145" s="34" t="inlineStr">
+    <row r="146" ht="32" customHeight="1">
+      <c r="A146" s="34" t="inlineStr">
         <is>
           <t>La gran noche del viaje, rearmada a pedido: el musical SALIÓ y entraron un PLAY de Broadway a las 19:30 y el CAFÉ WHA a las 23:45 — el sótano del Village donde debutaron Dylan y Hendrix, con reserva gratis ya pedida por Eventbrite. La cena temprana en Peter Luger (17:00) ahora existe exactamente para esto: porterhouse → telón → medianoche de soul y funk. Frankel's sigue afuera (a un porterhouse no se llega con un pastrami encima) y Westlight sigue opcional. ⚠️ La noche termina ~1:15-1:30: el domingo no tiene NADA fijo hasta las 16:00.</t>
         </is>
       </c>
-    </row>
-    <row r="146" ht="30" customHeight="1">
-      <c r="A146" s="35" t="n"/>
-      <c r="B146" s="36" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="C146" s="37" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="D146" s="38" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="E146" s="39" t="inlineStr">
-        <is>
-          <t>Salir 8:15: 1/2/3 desde 72 St + transbordo a A/C hasta High St son ~40-45 min REALES. Llegar temprano a DUMBO es la diferencia entre la foto y la cola de fotos.</t>
-        </is>
-      </c>
-      <c r="F146" s="37" t="inlineStr"/>
-      <c r="G146" s="40" t="inlineStr"/>
-      <c r="H146" s="41" t="inlineStr"/>
-      <c r="I146" s="41" t="inlineStr"/>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="35" t="n"/>
-      <c r="B147" s="42" t="inlineStr">
+      <c r="B147" s="36" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="C147" s="37" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="C147" s="43" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="D147" s="44" t="inlineStr">
+      <c r="D147" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E147" s="45" t="inlineStr">
-        <is>
-          <t>★ Brooklyn Bridge Park y DUMBO — muelles reconvertidos con el skyline de Lower Manhattan de frente, y la foto del Manhattan Bridge encuadrado en Washington y Water.</t>
-        </is>
-      </c>
-      <c r="F147" s="43" t="inlineStr">
-        <is>
-          <t>Brooklyn Bridge Park</t>
-        </is>
-      </c>
+      <c r="E147" s="39" t="inlineStr">
+        <is>
+          <t>Salir 8:15: 1/2/3 desde 72 St + transbordo a A/C hasta High St son ~40-45 min REALES. Llegar temprano a DUMBO es la diferencia entre la foto y la cola de fotos.</t>
+        </is>
+      </c>
+      <c r="F147" s="37" t="inlineStr"/>
       <c r="G147" s="40" t="inlineStr"/>
       <c r="H147" s="41" t="inlineStr"/>
       <c r="I147" s="41" t="inlineStr"/>
     </row>
-    <row r="148" ht="16" customHeight="1">
+    <row r="148" ht="30" customHeight="1">
       <c r="A148" s="35" t="n"/>
-      <c r="B148" s="36" t="inlineStr">
+      <c r="B148" s="42" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C148" s="43" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="C148" s="37" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="D148" s="38" t="inlineStr">
+      <c r="D148" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E148" s="39" t="inlineStr">
-        <is>
-          <t>Brooklyn Heights Promenade — la postal clásica del skyline sobre el BQE.</t>
-        </is>
-      </c>
-      <c r="F148" s="37" t="inlineStr">
-        <is>
-          <t>Brooklyn Heights Promenade</t>
-        </is>
-      </c>
-      <c r="G148" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~8 min a pie · 0.6 km · estimado</t>
-        </is>
-      </c>
+      <c r="E148" s="45" t="inlineStr">
+        <is>
+          <t>★ Brooklyn Bridge Park y DUMBO — muelles reconvertidos con el skyline de Lower Manhattan de frente, y la foto del Manhattan Bridge encuadrado en Washington y Water.</t>
+        </is>
+      </c>
+      <c r="F148" s="43" t="inlineStr">
+        <is>
+          <t>Brooklyn Bridge Park</t>
+        </is>
+      </c>
+      <c r="G148" s="40" t="inlineStr"/>
       <c r="H148" s="41" t="inlineStr"/>
       <c r="I148" s="41" t="inlineStr"/>
     </row>
-    <row r="149" ht="30" customHeight="1">
+    <row r="149" ht="16" customHeight="1">
       <c r="A149" s="35" t="n"/>
-      <c r="B149" s="42" t="inlineStr">
+      <c r="B149" s="36" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C149" s="37" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="C149" s="43" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="D149" s="44" t="inlineStr">
+      <c r="D149" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E149" s="45" t="inlineStr">
-        <is>
-          <t>★ NEW YORK TRANSIT MUSEUM — una estación de subte clausurada de 1936 con 20 vagones históricos en las vías originales; se puede subir a todos. $10. Cierra lunes y martes, así que hoy es el día.</t>
-        </is>
-      </c>
-      <c r="F149" s="43" t="inlineStr">
-        <is>
-          <t>New York Transit Museum</t>
-        </is>
-      </c>
-      <c r="G149" s="40" t="inlineStr"/>
+      <c r="E149" s="39" t="inlineStr">
+        <is>
+          <t>Brooklyn Heights Promenade — la postal clásica del skyline sobre el BQE.</t>
+        </is>
+      </c>
+      <c r="F149" s="37" t="inlineStr">
+        <is>
+          <t>Brooklyn Heights Promenade</t>
+        </is>
+      </c>
+      <c r="G149" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~8 min a pie · 0.6 km · estimado</t>
+        </is>
+      </c>
       <c r="H149" s="41" t="inlineStr"/>
       <c r="I149" s="41" t="inlineStr"/>
     </row>
-    <row r="150" ht="16" customHeight="1">
+    <row r="150" ht="30" customHeight="1">
       <c r="A150" s="35" t="n"/>
-      <c r="B150" s="36" t="inlineStr">
+      <c r="B150" s="42" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C150" s="43" t="inlineStr">
         <is>
           <t>12:45</t>
         </is>
       </c>
-      <c r="C150" s="37" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="D150" s="38" t="inlineStr">
+      <c r="D150" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E150" s="39" t="inlineStr">
-        <is>
-          <t>Almuerzo en Downtown Brooklyn.</t>
-        </is>
-      </c>
-      <c r="F150" s="37" t="inlineStr"/>
+      <c r="E150" s="45" t="inlineStr">
+        <is>
+          <t>★ NEW YORK TRANSIT MUSEUM — una estación de subte clausurada de 1936 con 20 vagones históricos en las vías originales; se puede subir a todos. $10. Cierra lunes y martes, así que hoy es el día.</t>
+        </is>
+      </c>
+      <c r="F150" s="43" t="inlineStr">
+        <is>
+          <t>New York Transit Museum</t>
+        </is>
+      </c>
       <c r="G150" s="40" t="inlineStr"/>
       <c r="H150" s="41" t="inlineStr"/>
       <c r="I150" s="41" t="inlineStr"/>
@@ -36145,14 +36145,14 @@
       <c r="A151" s="35" t="n"/>
       <c r="B151" s="36" t="inlineStr">
         <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C151" s="37" t="inlineStr">
+        <is>
           <t>13:45</t>
         </is>
       </c>
-      <c r="C151" s="37" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="D151" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36160,7 +36160,7 @@
       </c>
       <c r="E151" s="39" t="inlineStr">
         <is>
-          <t>Subte a Williamsburg.</t>
+          <t>Almuerzo en Downtown Brooklyn.</t>
         </is>
       </c>
       <c r="F151" s="37" t="inlineStr"/>
@@ -36168,76 +36168,76 @@
       <c r="H151" s="41" t="inlineStr"/>
       <c r="I151" s="41" t="inlineStr"/>
     </row>
-    <row r="152" ht="30" customHeight="1">
+    <row r="152" ht="16" customHeight="1">
       <c r="A152" s="35" t="n"/>
-      <c r="B152" s="42" t="inlineStr">
+      <c r="B152" s="36" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="C152" s="37" t="inlineStr">
         <is>
           <t>14:15</t>
         </is>
       </c>
-      <c r="C152" s="43" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="D152" s="44" t="inlineStr">
+      <c r="D152" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E152" s="45" t="inlineStr">
-        <is>
-          <t>★ Domino Park — ex refinería de azúcar; el paseo elevado pasa entre la maquinaria industrial conservada, con el Williamsburg Bridge y Midtown enfrente.</t>
-        </is>
-      </c>
-      <c r="F152" s="43" t="inlineStr">
-        <is>
-          <t>Domino Park</t>
-        </is>
-      </c>
+      <c r="E152" s="39" t="inlineStr">
+        <is>
+          <t>Subte a Williamsburg.</t>
+        </is>
+      </c>
+      <c r="F152" s="37" t="inlineStr"/>
       <c r="G152" s="40" t="inlineStr"/>
       <c r="H152" s="41" t="inlineStr"/>
       <c r="I152" s="41" t="inlineStr"/>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="35" t="n"/>
-      <c r="B153" s="36" t="inlineStr">
+      <c r="B153" s="42" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="C153" s="43" t="inlineStr">
         <is>
           <t>15:15</t>
         </is>
       </c>
-      <c r="C153" s="37" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="D153" s="38" t="inlineStr">
+      <c r="D153" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E153" s="39" t="inlineStr">
-        <is>
-          <t>Paseo por Williamsburg: Bedford Ave, disquerías y vintage. OPCIONAL si quieren la panorámica: Westlight (piso 22, sin cover, un trago) — lo bajaron a 'quizás', así que es prescindible. NO comer nada: lo que viene lo merece.</t>
-        </is>
-      </c>
-      <c r="F153" s="37" t="inlineStr"/>
+      <c r="E153" s="45" t="inlineStr">
+        <is>
+          <t>★ Domino Park — ex refinería de azúcar; el paseo elevado pasa entre la maquinaria industrial conservada, con el Williamsburg Bridge y Midtown enfrente.</t>
+        </is>
+      </c>
+      <c r="F153" s="43" t="inlineStr">
+        <is>
+          <t>Domino Park</t>
+        </is>
+      </c>
       <c r="G153" s="40" t="inlineStr"/>
       <c r="H153" s="41" t="inlineStr"/>
       <c r="I153" s="41" t="inlineStr"/>
     </row>
-    <row r="154" ht="16" customHeight="1">
+    <row r="154" ht="30" customHeight="1">
       <c r="A154" s="35" t="n"/>
       <c r="B154" s="36" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C154" s="37" t="inlineStr">
+        <is>
           <t>16:45</t>
         </is>
       </c>
-      <c r="C154" s="37" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="D154" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36245,7 +36245,7 @@
       </c>
       <c r="E154" s="39" t="inlineStr">
         <is>
-          <t>Caminar por Bedford/Driggs hasta el pie del Williamsburg Bridge (~15 min).</t>
+          <t>Paseo por Williamsburg: Bedford Ave, disquerías y vintage. OPCIONAL si quieren la panorámica: Westlight (piso 22, sin cover, un trago) — lo bajaron a 'quizás', así que es prescindible. NO comer nada: lo que viene lo merece.</t>
         </is>
       </c>
       <c r="F154" s="37" t="inlineStr"/>
@@ -36253,134 +36253,134 @@
       <c r="H154" s="41" t="inlineStr"/>
       <c r="I154" s="41" t="inlineStr"/>
     </row>
-    <row r="155" ht="30" customHeight="1">
+    <row r="155" ht="16" customHeight="1">
       <c r="A155" s="35" t="n"/>
-      <c r="B155" s="42" t="inlineStr">
+      <c r="B155" s="36" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C155" s="37" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="C155" s="43" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="D155" s="44" t="inlineStr">
+      <c r="D155" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E155" s="45" t="inlineStr">
-        <is>
-          <t>★★ PETER LUGER (178 Broadway) — el porterhouse for two de 1887, dry-aged en el sótano, con la tocineta gruesa de entrada. ~$160-200 los dos con sides y propina. ⚠️ SIN TARJETAS DE CRÉDITO: efectivo, débito US o cheque — llevar cash. Cena temprana a propósito: el teatro espera. RESERVA EN RESY YA.</t>
-        </is>
-      </c>
-      <c r="F155" s="43" t="inlineStr">
-        <is>
-          <t>Peter Luger Steak House</t>
-        </is>
-      </c>
+      <c r="E155" s="39" t="inlineStr">
+        <is>
+          <t>Caminar por Bedford/Driggs hasta el pie del Williamsburg Bridge (~15 min).</t>
+        </is>
+      </c>
+      <c r="F155" s="37" t="inlineStr"/>
       <c r="G155" s="40" t="inlineStr"/>
       <c r="H155" s="41" t="inlineStr"/>
       <c r="I155" s="41" t="inlineStr"/>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="35" t="n"/>
-      <c r="B156" s="36" t="inlineStr">
+      <c r="B156" s="42" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C156" s="43" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="C156" s="37" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="D156" s="38" t="inlineStr">
+      <c r="D156" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E156" s="39" t="inlineStr">
-        <is>
-          <t>A la zona de teatros: subte J desde Marcy Av hasta Essex St y F hasta 42 St-Bryant Park (~35 min con transbordo), o directamente Uber al teatro (~20-25 min, $25-35 — un sábado a la noche el puente puede estar cargado).</t>
-        </is>
-      </c>
-      <c r="F156" s="37" t="inlineStr"/>
+      <c r="E156" s="45" t="inlineStr">
+        <is>
+          <t>★★ PETER LUGER (178 Broadway) — el porterhouse for two de 1887, dry-aged en el sótano, con la tocineta gruesa de entrada. ~$160-200 los dos con sides y propina. ⚠️ SIN TARJETAS DE CRÉDITO: efectivo, débito US o cheque — llevar cash. Cena temprana a propósito: el teatro espera. RESERVA EN RESY YA.</t>
+        </is>
+      </c>
+      <c r="F156" s="43" t="inlineStr">
+        <is>
+          <t>Peter Luger Steak House</t>
+        </is>
+      </c>
       <c r="G156" s="40" t="inlineStr"/>
       <c r="H156" s="41" t="inlineStr"/>
       <c r="I156" s="41" t="inlineStr"/>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="35" t="n"/>
-      <c r="B157" s="42" t="inlineStr">
+      <c r="B157" s="36" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C157" s="37" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="C157" s="43" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="D157" s="44" t="inlineStr">
+      <c r="D157" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E157" s="45" t="inlineStr">
-        <is>
-          <t>★★ PLAY DE BROADWAY — mi recomendación: STRANGER THINGS: THE FIRST SHADOW (Marquis, desde ~$76): la maquinaria escénica que ganó el Tony — para quien viene de Mercer Labs, el mismo músculo llevado al teatro. Alternativas esa semana: Harry Potter and the Cursed Child, Paranormal Activity, The Imaginary Invalid. COMPRA FIRME esta semana y verificar el horario real de la función (19:00/19:30/20:00): tiene que terminar ~22:00 para lo que sigue.</t>
-        </is>
-      </c>
-      <c r="F157" s="43" t="inlineStr">
-        <is>
-          <t>Stranger Things: The First Shadow (play)</t>
-        </is>
-      </c>
+      <c r="E157" s="39" t="inlineStr">
+        <is>
+          <t>A la zona de teatros: subte J desde Marcy Av hasta Essex St y F hasta 42 St-Bryant Park (~35 min con transbordo), o directamente Uber al teatro (~20-25 min, $25-35 — un sábado a la noche el puente puede estar cargado).</t>
+        </is>
+      </c>
+      <c r="F157" s="37" t="inlineStr"/>
       <c r="G157" s="40" t="inlineStr"/>
       <c r="H157" s="41" t="inlineStr"/>
       <c r="I157" s="41" t="inlineStr"/>
     </row>
-    <row r="158" ht="16" customHeight="1">
+    <row r="158" ht="30" customHeight="1">
       <c r="A158" s="35" t="n"/>
-      <c r="B158" s="36" t="inlineStr">
+      <c r="B158" s="42" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C158" s="43" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C158" s="37" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="D158" s="38" t="inlineStr">
+      <c r="D158" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E158" s="39" t="inlineStr">
-        <is>
-          <t>Subte 1 desde Times Sq hasta Christopher St (~15 min) y caminar al corazón del Village.</t>
-        </is>
-      </c>
-      <c r="F158" s="37" t="inlineStr"/>
+      <c r="E158" s="45" t="inlineStr">
+        <is>
+          <t>★★ PLAY DE BROADWAY — mi recomendación: STRANGER THINGS: THE FIRST SHADOW (Marquis, desde ~$76): la maquinaria escénica que ganó el Tony — para quien viene de Mercer Labs, el mismo músculo llevado al teatro. Alternativas esa semana: Harry Potter and the Cursed Child, Paranormal Activity, The Imaginary Invalid. COMPRA FIRME esta semana y verificar el horario real de la función (19:00/19:30/20:00): tiene que terminar ~22:00 para lo que sigue.</t>
+        </is>
+      </c>
+      <c r="F158" s="43" t="inlineStr">
+        <is>
+          <t>Stranger Things: The First Shadow (play)</t>
+        </is>
+      </c>
       <c r="G158" s="40" t="inlineStr"/>
       <c r="H158" s="41" t="inlineStr"/>
       <c r="I158" s="41" t="inlineStr"/>
     </row>
-    <row r="159" ht="30" customHeight="1">
+    <row r="159" ht="16" customHeight="1">
       <c r="A159" s="35" t="n"/>
       <c r="B159" s="36" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C159" s="37" t="inlineStr">
+        <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="C159" s="37" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
       <c r="D159" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36388,7 +36388,7 @@
       </c>
       <c r="E159" s="39" t="inlineStr">
         <is>
-          <t>Paseo sin apuro por Bleecker y MacDougal — la esquina folk de los 60s de noche, un café o un trago corto. El único objetivo real: estar en la puerta del Wha a las 23:10.</t>
+          <t>Subte 1 desde Times Sq hasta Christopher St (~15 min) y caminar al corazón del Village.</t>
         </is>
       </c>
       <c r="F159" s="37" t="inlineStr"/>
@@ -36398,106 +36398,102 @@
     </row>
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="35" t="n"/>
-      <c r="B160" s="42" t="inlineStr">
+      <c r="B160" s="36" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C160" s="37" t="inlineStr">
         <is>
           <t>23:15</t>
         </is>
       </c>
-      <c r="C160" s="43" t="inlineStr"/>
-      <c r="D160" s="44" t="inlineStr">
+      <c r="D160" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E160" s="45" t="inlineStr">
-        <is>
-          <t>★★ CAFÉ WHA — LLEGAR 23:10-23:15: la reserva de Eventbrite NO garantiza admisión y a las 23:30 EN PUNTO liberan los asientos vacíos al standby. TODOS los de la reserva presentes. Set 2 de la house band 23:45-~1:15: soul y funk a máquina en el sótano donde debutaron Dylan, Hendrix y Springsteen. $20 por cabeza van a la cuenta + consumo. Vuelta: subte 1 Christopher St → 72 St (~25 min) o taxi.</t>
-        </is>
-      </c>
-      <c r="F160" s="43" t="inlineStr">
-        <is>
-          <t>Cafe Wha?</t>
-        </is>
-      </c>
+      <c r="E160" s="39" t="inlineStr">
+        <is>
+          <t>Paseo sin apuro por Bleecker y MacDougal — la esquina folk de los 60s de noche, un café o un trago corto. El único objetivo real: estar en la puerta del Wha a las 23:10.</t>
+        </is>
+      </c>
+      <c r="F160" s="37" t="inlineStr"/>
       <c r="G160" s="40" t="inlineStr"/>
       <c r="H160" s="41" t="inlineStr"/>
       <c r="I160" s="41" t="inlineStr"/>
     </row>
-    <row r="161" ht="32" customHeight="1">
-      <c r="A161" s="46" t="inlineStr">
+    <row r="161" ht="30" customHeight="1">
+      <c r="A161" s="35" t="n"/>
+      <c r="B161" s="42" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="C161" s="43" t="inlineStr"/>
+      <c r="D161" s="44" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E161" s="45" t="inlineStr">
+        <is>
+          <t>★★ CAFÉ WHA — LLEGAR 23:10-23:15: la reserva de Eventbrite NO garantiza admisión y a las 23:30 EN PUNTO liberan los asientos vacíos al standby. TODOS los de la reserva presentes. Set 2 de la house band 23:45-~1:15: soul y funk a máquina en el sótano donde debutaron Dylan, Hendrix y Springsteen. $20 por cabeza van a la cuenta + consumo. Vuelta: subte 1 Christopher St → 72 St (~25 min) o taxi.</t>
+        </is>
+      </c>
+      <c r="F161" s="43" t="inlineStr">
+        <is>
+          <t>Cafe Wha?</t>
+        </is>
+      </c>
+      <c r="G161" s="40" t="inlineStr"/>
+      <c r="H161" s="41" t="inlineStr"/>
+      <c r="I161" s="41" t="inlineStr"/>
+    </row>
+    <row r="162" ht="32" customHeight="1">
+      <c r="A162" s="46" t="inlineStr">
         <is>
           <t>ALTERNATIVA / OJO:  SOBRE PETER LUGER: la mesa de las 17:00 es la realista — y ahora es la única que funciona: el play manda. PLAN B si no hay mesa: correr Peter Luger al ALMUERZO del mismo día (12:45). // SI EL CANSANCIO GANA A LAS 22:00: el Café Wha es la pieza sacrificable — la reserva es gratis y no penaliza no ir; el play, pagado, no. // Sigue afuera: Bar LunÀtico y Barbès (Bed-Stuy/Park Slope), sin noche posible.</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="22" customHeight="1">
-      <c r="A163" s="33" t="inlineStr">
+    <row r="164" ht="22" customHeight="1">
+      <c r="A164" s="33" t="inlineStr">
         <is>
           <t>DÍA 9 · Domingo 06/09 · Checkout, Central Park, Roosevelt Island, MoMA PS1 y vuelo  —  base: The Beacon (checkout) → EWR  ·  Ambos</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="32" customHeight="1">
-      <c r="A164" s="34" t="inlineStr">
+    <row r="165" ht="32" customHeight="1">
+      <c r="A165" s="34" t="inlineStr">
         <is>
           <t>El día arranca con el CHECKOUT de The Beacon: hacerlo temprano y dejar las valijas en el bell desk libera el día entero. El vuelo sale 23:40, así que hay margen — pero es el domingo del fin de semana largo de Labor Day, la noche de mayor tráfico del año, y EWR va a estar cargado. Por eso todo queda cerca y se sale con 2h45 de anticipación. EL CAMBIO DEL ÚLTIMO DÍA: entra MOMA PS1 y sale el Guggenheim. Se verificó el 27/8 que la rotonda del Guggenheim está cerrada hasta el 17/9 —no se camina la rampa, que es la razón para ir— y PS1 resultó ser gratis, abierto hasta las 18 los domingos, a 1,2 km de Roosevelt Island y con «Greater New York 2026» en pie hasta el 7/9. Era el último imprescindible que quedaba afuera del viaje. El Guggenheim queda escrito como alternativa por si cambian de idea.</t>
         </is>
       </c>
-    </row>
-    <row r="165" ht="30" customHeight="1">
-      <c r="A165" s="35" t="n"/>
-      <c r="B165" s="36" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="C165" s="37" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="D165" s="38" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="E165" s="39" t="inlineStr">
-        <is>
-          <t>Desayuno SIN despertador temprano: anoche terminó ~1:30 en el Village y lo único con hora fija hoy es el PS1, que cierra a las 18:00. Dormir un poco más está permitido.</t>
-        </is>
-      </c>
-      <c r="F165" s="37" t="inlineStr"/>
-      <c r="G165" s="40" t="inlineStr"/>
-      <c r="H165" s="41" t="inlineStr"/>
-      <c r="I165" s="41" t="inlineStr"/>
     </row>
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="35" t="n"/>
-      <c r="B166" s="42" t="inlineStr">
+      <c r="B166" s="36" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C166" s="37" t="inlineStr">
         <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="C166" s="43" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="D166" s="44" t="inlineStr">
+      <c r="D166" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E166" s="45" t="inlineStr">
-        <is>
-          <t>★ CHECKOUT de The Beacon y dejar las valijas en el bell desk. El checkout formal suele ser 11:00-12:00, pero hacerlo antes libera el día.</t>
-        </is>
-      </c>
-      <c r="F166" s="43" t="inlineStr">
-        <is>
-          <t>Hotel The Beacon (3-6 sep)</t>
-        </is>
-      </c>
+      <c r="E166" s="39" t="inlineStr">
+        <is>
+          <t>Desayuno SIN despertador temprano: anoche terminó ~1:30 en el Village y lo único con hora fija hoy es el PS1, que cierra a las 18:00. Dormir un poco más está permitido.</t>
+        </is>
+      </c>
+      <c r="F166" s="37" t="inlineStr"/>
       <c r="G166" s="40" t="inlineStr"/>
       <c r="H166" s="41" t="inlineStr"/>
       <c r="I166" s="41" t="inlineStr"/>
@@ -36506,14 +36502,14 @@
       <c r="A167" s="35" t="n"/>
       <c r="B167" s="42" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="C167" s="43" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="C167" s="43" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="D167" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36521,61 +36517,65 @@
       </c>
       <c r="E167" s="45" t="inlineStr">
         <is>
-          <t>★ CENTRAL PARK cruzando de oeste a este: Bethesda Terrace, el Ramble, Bow Bridge. Se entra por la 72 desde Broadway, a tres cuadras del hotel.</t>
+          <t>★ CHECKOUT de The Beacon y dejar las valijas en el bell desk. El checkout formal suele ser 11:00-12:00, pero hacerlo antes libera el día.</t>
         </is>
       </c>
       <c r="F167" s="43" t="inlineStr">
         <is>
-          <t>Central Park</t>
-        </is>
-      </c>
-      <c r="G167" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~20 min a pie (1.5 km) o 🚇 ~15 min · estimado</t>
-        </is>
-      </c>
+          <t>Hotel The Beacon (3-6 sep)</t>
+        </is>
+      </c>
+      <c r="G167" s="40" t="inlineStr"/>
       <c r="H167" s="41" t="inlineStr"/>
       <c r="I167" s="41" t="inlineStr"/>
     </row>
-    <row r="168" ht="16" customHeight="1">
+    <row r="168" ht="30" customHeight="1">
       <c r="A168" s="35" t="n"/>
-      <c r="B168" s="36" t="inlineStr">
+      <c r="B168" s="42" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="C168" s="43" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="C168" s="37" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="D168" s="38" t="inlineStr">
+      <c r="D168" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E168" s="39" t="inlineStr">
-        <is>
-          <t>Almuerzo en el Upper East Side, saliendo del parque por la Quinta.</t>
-        </is>
-      </c>
-      <c r="F168" s="37" t="inlineStr"/>
-      <c r="G168" s="40" t="inlineStr"/>
+      <c r="E168" s="45" t="inlineStr">
+        <is>
+          <t>★ CENTRAL PARK cruzando de oeste a este: Bethesda Terrace, el Ramble, Bow Bridge. Se entra por la 72 desde Broadway, a tres cuadras del hotel.</t>
+        </is>
+      </c>
+      <c r="F168" s="43" t="inlineStr">
+        <is>
+          <t>Central Park</t>
+        </is>
+      </c>
+      <c r="G168" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~20 min a pie (1.5 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H168" s="41" t="inlineStr"/>
       <c r="I168" s="41" t="inlineStr"/>
     </row>
-    <row r="169" ht="30" customHeight="1">
+    <row r="169" ht="16" customHeight="1">
       <c r="A169" s="35" t="n"/>
       <c r="B169" s="36" t="inlineStr">
         <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C169" s="37" t="inlineStr">
+        <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="C169" s="37" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="D169" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36583,7 +36583,7 @@
       </c>
       <c r="E169" s="39" t="inlineStr">
         <is>
-          <t>Bajar a 59 St y 2ª Av: subte 6 desde 68 St-Hunter College (el 4/5 exprés NO para ahí), o caminando por la Quinta si el día está lindo.</t>
+          <t>Almuerzo en el Upper East Side, saliendo del parque por la Quinta.</t>
         </is>
       </c>
       <c r="F169" s="37" t="inlineStr"/>
@@ -36593,60 +36593,56 @@
     </row>
     <row r="170" ht="30" customHeight="1">
       <c r="A170" s="35" t="n"/>
-      <c r="B170" s="42" t="inlineStr">
+      <c r="B170" s="36" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C170" s="37" t="inlineStr">
         <is>
           <t>13:50</t>
         </is>
       </c>
-      <c r="C170" s="43" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="D170" s="44" t="inlineStr">
+      <c r="D170" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E170" s="45" t="inlineStr">
-        <is>
-          <t>★ ROOSEVELT ISLAND TRAMWAY ($3, OMNY) — cruza el East River a 76 metros de altura con el Queensboro Bridge al lado. Es la vista de $50 por el precio de un viaje de subte.</t>
-        </is>
-      </c>
-      <c r="F170" s="43" t="inlineStr">
-        <is>
-          <t>Roosevelt Island Tramway</t>
-        </is>
-      </c>
+      <c r="E170" s="39" t="inlineStr">
+        <is>
+          <t>Bajar a 59 St y 2ª Av: subte 6 desde 68 St-Hunter College (el 4/5 exprés NO para ahí), o caminando por la Quinta si el día está lindo.</t>
+        </is>
+      </c>
+      <c r="F170" s="37" t="inlineStr"/>
       <c r="G170" s="40" t="inlineStr"/>
       <c r="H170" s="41" t="inlineStr"/>
       <c r="I170" s="41" t="inlineStr"/>
     </row>
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="35" t="n"/>
-      <c r="B171" s="36" t="inlineStr">
+      <c r="B171" s="42" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="C171" s="43" t="inlineStr">
         <is>
           <t>14:25</t>
         </is>
       </c>
-      <c r="C171" s="37" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="D171" s="38" t="inlineStr">
+      <c r="D171" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E171" s="39" t="inlineStr">
-        <is>
-          <t>FDR Four Freedoms Park — del teleférico son ~20 min a pie por el borde del río. La última obra de Louis Kahn: granito, plátanos y una sala abierta al río apuntando a Manhattan. Gratis y vacía. Se pasa por las ruinas del Smallpox Hospital.</t>
-        </is>
-      </c>
-      <c r="F171" s="37" t="inlineStr">
-        <is>
-          <t>FDR Four Freedoms Park</t>
+      <c r="E171" s="45" t="inlineStr">
+        <is>
+          <t>★ ROOSEVELT ISLAND TRAMWAY ($3, OMNY) — cruza el East River a 76 metros de altura con el Queensboro Bridge al lado. Es la vista de $50 por el precio de un viaje de subte.</t>
+        </is>
+      </c>
+      <c r="F171" s="43" t="inlineStr">
+        <is>
+          <t>Roosevelt Island Tramway</t>
         </is>
       </c>
       <c r="G171" s="40" t="inlineStr"/>
@@ -36657,14 +36653,14 @@
       <c r="A172" s="35" t="n"/>
       <c r="B172" s="36" t="inlineStr">
         <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="C172" s="37" t="inlineStr">
+        <is>
           <t>15:05</t>
         </is>
       </c>
-      <c r="C172" s="37" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="D172" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36672,10 +36668,14 @@
       </c>
       <c r="E172" s="39" t="inlineStr">
         <is>
-          <t>SALIR 15:05 de Four Freedoms Park y caminar 15 min al norte por el borde del río hasta la ESTACIÓN DEL F, que está en el medio de la isla (Main St y Roosevelt Island Bridge). Hoy NO se vuelve en teleférico: se cruza a Queens por abajo.</t>
-        </is>
-      </c>
-      <c r="F172" s="37" t="inlineStr"/>
+          <t>FDR Four Freedoms Park — del teleférico son ~20 min a pie por el borde del río. La última obra de Louis Kahn: granito, plátanos y una sala abierta al río apuntando a Manhattan. Gratis y vacía. Se pasa por las ruinas del Smallpox Hospital.</t>
+        </is>
+      </c>
+      <c r="F172" s="37" t="inlineStr">
+        <is>
+          <t>FDR Four Freedoms Park</t>
+        </is>
+      </c>
       <c r="G172" s="40" t="inlineStr"/>
       <c r="H172" s="41" t="inlineStr"/>
       <c r="I172" s="41" t="inlineStr"/>
@@ -36684,14 +36684,14 @@
       <c r="A173" s="35" t="n"/>
       <c r="B173" s="36" t="inlineStr">
         <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="C173" s="37" t="inlineStr">
+        <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="C173" s="37" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="D173" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36699,7 +36699,7 @@
       </c>
       <c r="E173" s="39" t="inlineStr">
         <is>
-          <t>Subte F, UNA parada: Roosevelt Island → 21 St-Queensbridge (~4 min). Salir y caminar 12-15 min al sur por 21st St / Jackson Ave.</t>
+          <t>SALIR 15:05 de Four Freedoms Park y caminar 15 min al norte por el borde del río hasta la ESTACIÓN DEL F, que está en el medio de la isla (Main St y Roosevelt Island Bridge). Hoy NO se vuelve en teleférico: se cruza a Queens por abajo.</t>
         </is>
       </c>
       <c r="F173" s="37" t="inlineStr"/>
@@ -36709,58 +36709,58 @@
     </row>
     <row r="174" ht="30" customHeight="1">
       <c r="A174" s="35" t="n"/>
-      <c r="B174" s="42" t="inlineStr">
+      <c r="B174" s="36" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C174" s="37" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="C174" s="43" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="D174" s="44" t="inlineStr">
+      <c r="D174" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E174" s="45" t="inlineStr">
-        <is>
-          <t>★★ MOMA PS1 — el último imprescindible del viaje, y entra gratis. Escuela pública de 1892 reconvertida en el laboratorio del MoMA: lo que no se anima a mostrar en la Quinta Avenida. VERIFICADO el 27/8: ENTRADA GRATUITA para todos, abre domingos 12:00-18:00, y «Greater New York 2026» —la encuesta insignia de la casa, que se hace cada cinco años— sigue en pie hasta el 7 de septiembre, o sea que la agarran por un día. Más el Courtyard Commission de Precious Okoyomon al aire libre. Dos horas holgadas hasta las 17:45.</t>
-        </is>
-      </c>
-      <c r="F174" s="43" t="inlineStr">
-        <is>
-          <t>MoMA PS1</t>
-        </is>
-      </c>
+      <c r="E174" s="39" t="inlineStr">
+        <is>
+          <t>Subte F, UNA parada: Roosevelt Island → 21 St-Queensbridge (~4 min). Salir y caminar 12-15 min al sur por 21st St / Jackson Ave.</t>
+        </is>
+      </c>
+      <c r="F174" s="37" t="inlineStr"/>
       <c r="G174" s="40" t="inlineStr"/>
       <c r="H174" s="41" t="inlineStr"/>
       <c r="I174" s="41" t="inlineStr"/>
     </row>
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="35" t="n"/>
-      <c r="B175" s="36" t="inlineStr">
+      <c r="B175" s="42" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C175" s="43" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="C175" s="37" t="inlineStr">
-        <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="D175" s="38" t="inlineStr">
+      <c r="D175" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E175" s="39" t="inlineStr">
-        <is>
-          <t>Del PS1 al hotel: subte 7 desde Court Sq hasta Times Sq y 1/2/3 hasta 72 St, o E/M hasta 53 St (~45 min). Llegan 18:30, justo para las valijas. El vuelo no se toca.</t>
-        </is>
-      </c>
-      <c r="F175" s="37" t="inlineStr"/>
+      <c r="E175" s="45" t="inlineStr">
+        <is>
+          <t>★★ MOMA PS1 — el último imprescindible del viaje, y entra gratis. Escuela pública de 1892 reconvertida en el laboratorio del MoMA: lo que no se anima a mostrar en la Quinta Avenida. VERIFICADO el 27/8: ENTRADA GRATUITA para todos, abre domingos 12:00-18:00, y «Greater New York 2026» —la encuesta insignia de la casa, que se hace cada cinco años— sigue en pie hasta el 7 de septiembre, o sea que la agarran por un día. Más el Courtyard Commission de Precious Okoyomon al aire libre. Dos horas holgadas hasta las 17:45.</t>
+        </is>
+      </c>
+      <c r="F175" s="43" t="inlineStr">
+        <is>
+          <t>MoMA PS1</t>
+        </is>
+      </c>
       <c r="G175" s="40" t="inlineStr"/>
       <c r="H175" s="41" t="inlineStr"/>
       <c r="I175" s="41" t="inlineStr"/>
@@ -36769,14 +36769,14 @@
       <c r="A176" s="35" t="n"/>
       <c r="B176" s="36" t="inlineStr">
         <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="C176" s="37" t="inlineStr">
+        <is>
           <t>18:20</t>
         </is>
       </c>
-      <c r="C176" s="37" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
       <c r="D176" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36784,7 +36784,7 @@
       </c>
       <c r="E176" s="39" t="inlineStr">
         <is>
-          <t>◇ SI PREFIEREN EL GUGGENHEIM, sigue estando y este bloque se ignora: pay-what-you-wish domingos 16:00-17:30 (mínimo $1) y entrada rebajada a $16 el resto del horario. ⚠️ PERO la rotonda está CERRADA del 3/8 al 17/9 por el montaje de Taryn Simon: no se camina la rampa —que es la razón para ir— y avisan que puede haber ruido de obra. Quedan las torres 4, 5 y 7 con «Guggenheim Pop» (Lichtenstein, Warhol, Oldenburg, Cattelan) y la colección Thannhauser. Para hacerlo: en vez de cruzar a Queens, teleférico de vuelta y subte 4/5/6 de 59 St a 86 St, y hay que salir del FDR Park 15:05 para entrar 16:00 — la ventana a voluntad va hasta las 17:30 y el museo cierra ahí.</t>
+          <t>Del PS1 al hotel: subte 7 desde Court Sq hasta Times Sq y 1/2/3 hasta 72 St, o E/M hasta 53 St (~45 min). Llegan 18:30, justo para las valijas. El vuelo no se toca.</t>
         </is>
       </c>
       <c r="F176" s="37" t="inlineStr"/>
@@ -36792,18 +36792,18 @@
       <c r="H176" s="41" t="inlineStr"/>
       <c r="I176" s="41" t="inlineStr"/>
     </row>
-    <row r="177" ht="16" customHeight="1">
+    <row r="177" ht="30" customHeight="1">
       <c r="A177" s="35" t="n"/>
       <c r="B177" s="36" t="inlineStr">
         <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="C177" s="37" t="inlineStr">
+        <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="C177" s="37" t="inlineStr">
-        <is>
-          <t>19:40</t>
-        </is>
-      </c>
       <c r="D177" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36811,7 +36811,7 @@
       </c>
       <c r="E177" s="39" t="inlineStr">
         <is>
-          <t>Retirar las valijas del bell desk. Cena tranquila cerca del hotel: es la última.</t>
+          <t>◇ SI PREFIEREN EL GUGGENHEIM, sigue estando y este bloque se ignora: pay-what-you-wish domingos 16:00-17:30 (mínimo $1) y entrada rebajada a $16 el resto del horario. ⚠️ PERO la rotonda está CERRADA del 3/8 al 17/9 por el montaje de Taryn Simon: no se camina la rampa —que es la razón para ir— y avisan que puede haber ruido de obra. Quedan las torres 4, 5 y 7 con «Guggenheim Pop» (Lichtenstein, Warhol, Oldenburg, Cattelan) y la colección Thannhauser. Para hacerlo: en vez de cruzar a Queens, teleférico de vuelta y subte 4/5/6 de 59 St a 86 St, y hay que salir del FDR Park 15:05 para entrar 16:00 — la ventana a voluntad va hasta las 17:30 y el museo cierra ahí.</t>
         </is>
       </c>
       <c r="F177" s="37" t="inlineStr"/>
@@ -36823,14 +36823,14 @@
       <c r="A178" s="35" t="n"/>
       <c r="B178" s="36" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C178" s="37" t="inlineStr">
+        <is>
           <t>19:40</t>
         </is>
       </c>
-      <c r="C178" s="37" t="inlineStr">
-        <is>
-          <t>20:14</t>
-        </is>
-      </c>
       <c r="D178" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36838,7 +36838,7 @@
       </c>
       <c r="E178" s="39" t="inlineStr">
         <is>
-          <t>Salir de The Beacon. Subte 1/2/3 desde 72 St hasta 34 St-Penn Station: ~10 min, $3.</t>
+          <t>Retirar las valijas del bell desk. Cena tranquila cerca del hotel: es la última.</t>
         </is>
       </c>
       <c r="F178" s="37" t="inlineStr"/>
@@ -36846,18 +36846,18 @@
       <c r="H178" s="41" t="inlineStr"/>
       <c r="I178" s="41" t="inlineStr"/>
     </row>
-    <row r="179" ht="30" customHeight="1">
+    <row r="179" ht="16" customHeight="1">
       <c r="A179" s="35" t="n"/>
       <c r="B179" s="36" t="inlineStr">
         <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="C179" s="37" t="inlineStr">
+        <is>
           <t>20:14</t>
         </is>
       </c>
-      <c r="C179" s="37" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
       <c r="D179" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36865,7 +36865,7 @@
       </c>
       <c r="E179" s="39" t="inlineStr">
         <is>
-          <t>NJ Transit Penn Station → EWR, llega 20:38. $17,25 (incluye el AirTrain). VERIFICAR el horario dominical en njtransit.com unos días antes.</t>
+          <t>Salir de The Beacon. Subte 1/2/3 desde 72 St hasta 34 St-Penn Station: ~10 min, $3.</t>
         </is>
       </c>
       <c r="F179" s="37" t="inlineStr"/>
@@ -36873,18 +36873,18 @@
       <c r="H179" s="41" t="inlineStr"/>
       <c r="I179" s="41" t="inlineStr"/>
     </row>
-    <row r="180" ht="16" customHeight="1">
+    <row r="180" ht="30" customHeight="1">
       <c r="A180" s="35" t="n"/>
       <c r="B180" s="36" t="inlineStr">
         <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="C180" s="37" t="inlineStr">
+        <is>
           <t>20:45</t>
         </is>
       </c>
-      <c r="C180" s="37" t="inlineStr">
-        <is>
-          <t>20:55</t>
-        </is>
-      </c>
       <c r="D180" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36892,7 +36892,7 @@
       </c>
       <c r="E180" s="39" t="inlineStr">
         <is>
-          <t>AirTrain hasta la terminal: 10-15 min.</t>
+          <t>NJ Transit Penn Station → EWR, llega 20:38. $17,25 (incluye el AirTrain). VERIFICAR el horario dominical en njtransit.com unos días antes.</t>
         </is>
       </c>
       <c r="F180" s="37" t="inlineStr"/>
@@ -36900,14 +36900,18 @@
       <c r="H180" s="41" t="inlineStr"/>
       <c r="I180" s="41" t="inlineStr"/>
     </row>
-    <row r="181" ht="30" customHeight="1">
+    <row r="181" ht="16" customHeight="1">
       <c r="A181" s="35" t="n"/>
       <c r="B181" s="36" t="inlineStr">
         <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C181" s="37" t="inlineStr">
+        <is>
           <t>20:55</t>
         </is>
       </c>
-      <c r="C181" s="37" t="inlineStr"/>
       <c r="D181" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36915,7 +36919,7 @@
       </c>
       <c r="E181" s="39" t="inlineStr">
         <is>
-          <t>En terminal. Faltan 2h45 para el vuelo de las 23:40 — correcto para un internacional en el domingo de Labor Day, que es la noche de más tráfico del año en EWR.</t>
+          <t>AirTrain hasta la terminal: 10-15 min.</t>
         </is>
       </c>
       <c r="F181" s="37" t="inlineStr"/>
@@ -36923,8 +36927,31 @@
       <c r="H181" s="41" t="inlineStr"/>
       <c r="I181" s="41" t="inlineStr"/>
     </row>
-    <row r="182" ht="32" customHeight="1">
-      <c r="A182" s="46" t="inlineStr">
+    <row r="182" ht="30" customHeight="1">
+      <c r="A182" s="35" t="n"/>
+      <c r="B182" s="36" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="C182" s="37" t="inlineStr"/>
+      <c r="D182" s="38" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E182" s="39" t="inlineStr">
+        <is>
+          <t>En terminal. Faltan 2h45 para el vuelo de las 23:40 — correcto para un internacional en el domingo de Labor Day, que es la noche de más tráfico del año en EWR.</t>
+        </is>
+      </c>
+      <c r="F182" s="37" t="inlineStr"/>
+      <c r="G182" s="40" t="inlineStr"/>
+      <c r="H182" s="41" t="inlineStr"/>
+      <c r="I182" s="41" t="inlineStr"/>
+    </row>
+    <row r="183" ht="32" customHeight="1">
+      <c r="A183" s="46" t="inlineStr">
         <is>
           <t>ALTERNATIVA / OJO:  COLCHÓN: si algo se atrasa, el tren siguiente sale 20:55 y llega a EWR 21:16, o sea terminal ~21:35 y 2h05 antes del vuelo. Es el último que yo tomaría. // Si prefieren un último día sin moverse, salteen el teleférico y estiren Central Park hasta el Guggenheim: el parque solo da para toda la mañana y la tarde. Lo que NO conviene hoy es meter algo nuevo y grande. // LO QUE SE PIERDEN POR EL VUELO, y duele: esta noche a las 20:00 el Met proyecta gratis en Lincoln Center «El Último Sueño de Frida y Diego» —la misma Frida de la muestra del MoMA del lunes— y ustedes salen del hotel 19:40 hacia Penn Station. Está a diez cuadras del Beacon. No hay forma de que entre sin poner en riesgo el vuelo. // SI QUIEREN VOLVER AL GUGGENHEIM en vez del PS1: está escrito en el bloque de las 18:20, con los tiempos hechos. Cuesta el último imprescindible del viaje y hay que aceptar que la rampa —la razón para ir— no se camina hasta el 17/9. Tercera opción si ninguna convence: el Whitney también abre los domingos.</t>
         </is>
@@ -36932,38 +36959,38 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A99:I99"/>
+    <mergeCell ref="A183:I183"/>
     <mergeCell ref="A164:I164"/>
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A84:I84"/>
+    <mergeCell ref="A66:I66"/>
     <mergeCell ref="A145:I145"/>
-    <mergeCell ref="A163:I163"/>
-    <mergeCell ref="A101:I101"/>
+    <mergeCell ref="A26:I26"/>
     <mergeCell ref="A86:I86"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A85:I85"/>
     <mergeCell ref="A126:I126"/>
-    <mergeCell ref="A144:I144"/>
-    <mergeCell ref="A125:I125"/>
+    <mergeCell ref="A100:I100"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A165:I165"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A68:I68"/>
     <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A161:I161"/>
-    <mergeCell ref="A44:I44"/>
     <mergeCell ref="A102:I102"/>
-    <mergeCell ref="A67:I67"/>
-    <mergeCell ref="A83:I83"/>
-    <mergeCell ref="A142:I142"/>
-    <mergeCell ref="A182:I182"/>
-    <mergeCell ref="A123:I123"/>
+    <mergeCell ref="A127:I127"/>
+    <mergeCell ref="A143:I143"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A103:I103"/>
+    <mergeCell ref="A45:I45"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A146:I146"/>
+    <mergeCell ref="A124:I124"/>
     <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A162:I162"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A87:I87"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H184" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H185" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,Reservado,Confirmado,Descartado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -37435,7 +37462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -37468,7 +37495,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>RECOMENDADO: AirTrain + NJ Transit</t>
+          <t>RECOMENDADO: Uber Shuttle</t>
         </is>
       </c>
     </row>
@@ -37497,56 +37524,56 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="39" t="inlineStr">
         <is>
-          <t>AirTrain + NJ Transit ✅</t>
+          <t>Uber Shuttle ✅</t>
         </is>
       </c>
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t>$17,25</t>
+          <t>$20,70 p/p · $41,40 los dos</t>
         </is>
       </c>
       <c r="C7" s="39" t="inlineStr">
         <is>
-          <t>~55-70 min desde terminal</t>
+          <t>~75 min terminal a hotel</t>
         </is>
       </c>
       <c r="D7" s="39" t="inlineStr">
         <is>
-          <t>Precio ÚNICO: ya incluye el fee de AirTrain de $8,75, no se compra aparte. Trenes sábado desde EWR: 6:00, 6:07, 6:43, 7:04, 7:15, 7:25, 7:39. Viaje 26-31 min. Comprar en la app MyTix o en máquina — a bordo cobran $5 de recargo.  ▸ ~$30-35 p/p con el taxi de Penn Station al hotel</t>
+          <t>UN SOLO transporte con las valijas: sin AirTrain, sin transbordo en Penn y sin taxi. Precio fijo por persona y asiento reservado, se pide en la app de Uber. Sale de Terminal B, Zona 5, a ~6 min a pie de llegadas. Horarios del sábado 29: 7:40 y 8:30 a Theatre District (50th y 8ª, 13 min a pie del Ink48); 7:50 y 8:35 a Port Authority (40th y 8ª, 17 min a pie). ⚠️ SALEN CADA 40-50 MIN: si migraciones se estira y pierden el de 7:40, el siguiente llega 9:57 y el día arranca tarde.  ▸ $41,40 los dos, sin nada más que pagar</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="39" t="inlineStr">
         <is>
-          <t>Taxi oficial de EWR</t>
+          <t>AirTrain + NJ Transit (el plan viejo)</t>
         </is>
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t>~$78-90</t>
+          <t>$17,25 p/p · $34,50 los dos</t>
         </is>
       </c>
       <c r="C8" s="39" t="inlineStr">
         <is>
-          <t>45-60 min</t>
+          <t>~55-70 min desde terminal</t>
         </is>
       </c>
       <c r="D8" s="39" t="inlineStr">
         <is>
-          <t>Tarifa fija por zona: Ink48 está en la calle 48 = Zona 2 = $65 fijo, + $2 de airport fee + $6,75-15,75 de peajes + $1 por valija. El recargo de hora pico ($10) rige sáb-dom 12-21h, así que a las 6-7 AM NO aplica.</t>
+          <t>Precio ÚNICO: ya incluye el fee de AirTrain de $8,75, no se compra aparte. Trenes sábado desde EWR: 6:00, 6:07, 6:43, 7:04, 7:15, 7:25, 7:39 — UNO CADA 10-15 MIN, que es su ventaja real sobre el shuttle. Viaje 26-31 min. Comprar en la app MyTix o en máquina — a bordo cobran $5 de recargo. Llegan al hotel 8:15-8:30, casi una hora antes.  ▸ $46,50-52,50 los dos con el taxi de Penn Station al hotel · ES EL PLAN B SI SALEN TARDE DE MIGRACIONES</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="39" t="inlineStr">
         <is>
-          <t>Uber / Lyft</t>
+          <t>Taxi oficial de EWR</t>
         </is>
       </c>
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t>$70-110 (estimado)</t>
+          <t>~$78-90</t>
         </is>
       </c>
       <c r="C9" s="39" t="inlineStr">
@@ -37556,698 +37583,720 @@
       </c>
       <c r="D9" s="39" t="inlineStr">
         <is>
-          <t>A las 7 AM de un sábado el tráfico es liviano. Ink48 está dentro de la zona de congestion pricing (sur de la calle 60): hay recargo adicional.</t>
+          <t>Tarifa fija por zona: Ink48 está en la calle 48 = Zona 2 = $65 fijo, + $2 de airport fee + $6,75-15,75 de peajes + $1 por valija. El recargo de hora pico ($10) rige sáb-dom 12-21h, así que a las 6-7 AM NO aplica.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="39" t="inlineStr">
         <is>
+          <t>Uber / Lyft</t>
+        </is>
+      </c>
+      <c r="B10" s="39" t="inlineStr">
+        <is>
+          <t>$70-110 (estimado)</t>
+        </is>
+      </c>
+      <c r="C10" s="39" t="inlineStr">
+        <is>
+          <t>45-60 min</t>
+        </is>
+      </c>
+      <c r="D10" s="39" t="inlineStr">
+        <is>
+          <t>A las 7 AM de un sábado el tráfico es liviano. Ink48 está dentro de la zona de congestion pricing (sur de la calle 60): hay recargo adicional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="39" t="inlineStr">
+        <is>
           <t>Newark Airport Express ❌</t>
         </is>
       </c>
-      <c r="B10" s="39" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>$18-19 (NO CONFIRMADO)</t>
         </is>
       </c>
-      <c r="C10" s="39" t="inlineStr">
+      <c r="C11" s="39" t="inlineStr">
         <is>
           <t>60-80 min</t>
         </is>
       </c>
-      <c r="D10" s="39" t="inlineStr">
+      <c r="D11" s="39" t="inlineStr">
         <is>
           <t>No aporta nada frente al tren: más caro, más lento, sujeto al tráfico del Lincoln Tunnel, y deja en Port Authority a 15 min caminando del hotel. Las fuentes se contradicen sobre el precio.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="58" t="inlineStr">
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="58" t="inlineStr">
         <is>
           <t>Secuencia realista</t>
         </is>
       </c>
-      <c r="B11" s="58" t="inlineStr"/>
-      <c r="C11" s="58" t="inlineStr"/>
-      <c r="D11" s="58" t="inlineStr">
-        <is>
-          <t>Aterrizan 6:00 → migraciones y equipaje 45-75 min → AirTrain ~10-12 min → tren de 7:25 o 7:39 → Penn Station 7:51/8:07 → hotel 8:15-8:30. Total ≈ 2h15-2h30 desde que tocan pista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="59" t="inlineStr">
+      <c r="B12" s="58" t="inlineStr"/>
+      <c r="C12" s="58" t="inlineStr"/>
+      <c r="D12" s="58" t="inlineStr">
+        <is>
+          <t>Aterrizan 6:00 → migraciones y equipaje 45-75 min → 6 min a pie a la Zona 5 de Terminal B → Uber Shuttle 7:40 → Theatre District 8:54 → 13 min a pie → hotel ~9:10. Total ≈ 3h desde que tocan pista, con UN solo transporte. Con el plan viejo llegaban 8:15-8:30 pero cambiando tres veces de vehículo con las valijas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="59" t="inlineStr">
         <is>
           <t>⚠ Alerta</t>
         </is>
       </c>
-      <c r="B12" s="59" t="inlineStr"/>
-      <c r="C12" s="59" t="inlineStr"/>
-      <c r="D12" s="59" t="inlineStr">
-        <is>
-          <t>El AirTrain de Newark está en obra de reemplazo hasta 2030. El servicio por bus solo aplica días de semana de 5:00 a 15:00 — sus dos vuelos caen en fin de semana, así que están cubiertos. Igual reverifiquen 2-3 días antes en njtransit.com.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="B13" s="59" t="inlineStr"/>
+      <c r="C13" s="59" t="inlineStr"/>
+      <c r="D13" s="59" t="inlineStr">
+        <is>
+          <t>El shuttle sale cada 40-50 minutos, no cada 10: mirá el horario en la app de Uber apenas aterricen y, si se estiró migraciones, pasate al tren sin dudar. El AirTrain de Newark está en obra de reemplazo hasta 2030. El servicio por bus solo aplica días de semana de 5:00 a 15:00 — sus dos vuelos caen en fin de semana, así que están cubiertos. Igual reverifiquen 2-3 días antes en njtransit.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>The Beacon → EWR · domingo 6 de septiembre, vuelo 23:40</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>RECOMENDADO: Subte 1/2/3 + NJ Transit — $20,25 total</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="57" t="inlineStr">
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="57" t="inlineStr">
         <is>
           <t>Opción</t>
         </is>
       </c>
-      <c r="B16" s="57" t="inlineStr">
+      <c r="B17" s="57" t="inlineStr">
         <is>
           <t>Costo</t>
         </is>
       </c>
-      <c r="C16" s="57" t="inlineStr">
+      <c r="C17" s="57" t="inlineStr">
         <is>
           <t>Tiempo</t>
         </is>
       </c>
-      <c r="D16" s="57" t="inlineStr">
+      <c r="D17" s="57" t="inlineStr">
         <is>
           <t>Detalle</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="39" t="inlineStr">
-        <is>
-          <t>Subte + NJ Transit ✅</t>
-        </is>
-      </c>
-      <c r="B17" s="39" t="inlineStr">
-        <is>
-          <t>$20,25</t>
-        </is>
-      </c>
-      <c r="C17" s="39" t="inlineStr">
-        <is>
-          <t>~55 min + AirTrain</t>
-        </is>
-      </c>
-      <c r="D17" s="39" t="inlineStr">
-        <is>
-          <t>1/2/3 desde 72 St (a 3 cuadras del hotel) hasta 34 St-Penn Station, directo, ~10 min, $3. Después NJ Transit a EWR, $17,25. Trenes domingo: 19:51→20:12, 20:03→20:26, 20:07→20:31, 20:14→20:38, 20:55→21:16.  ▸ Salir del hotel 19:40 → tren de 20:14 (llega 20:38) → AirTrain → en terminal ~20:55, con 2h45 de margen. Colchón: el de 20:55 deja en terminal ~21:35, 2h05 antes.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="39" t="inlineStr">
         <is>
-          <t>Taxi amarillo desde Manhattan</t>
+          <t>Subte + NJ Transit ✅</t>
         </is>
       </c>
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t>$95-120</t>
+          <t>$20,25</t>
         </is>
       </c>
       <c r="C18" s="39" t="inlineStr">
         <is>
-          <t>50-75 min</t>
+          <t>~55 min + AirTrain</t>
         </is>
       </c>
       <c r="D18" s="39" t="inlineStr">
         <is>
-          <t>OJO: saliendo de Manhattan NO rige la tarifa fija por zonas (esa es solo para taxis que salen de EWR). Se cobra medidor + recargo Newark de $20 + peajes + congestion charge.</t>
+          <t>1/2/3 desde 72 St (a 3 cuadras del hotel) hasta 34 St-Penn Station, directo, ~10 min, $3. Después NJ Transit a EWR, $17,25. Trenes domingo: 19:51→20:12, 20:03→20:26, 20:07→20:31, 20:14→20:38, 20:55→21:16.  ▸ Salir del hotel 19:40 → tren de 20:14 (llega 20:38) → AirTrain → en terminal ~20:55, con 2h45 de margen. Colchón: el de 20:55 deja en terminal ~21:35, 2h05 antes.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="39" t="inlineStr">
         <is>
+          <t>Taxi amarillo desde Manhattan</t>
+        </is>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>$95-120</t>
+        </is>
+      </c>
+      <c r="C19" s="39" t="inlineStr">
+        <is>
+          <t>50-75 min</t>
+        </is>
+      </c>
+      <c r="D19" s="39" t="inlineStr">
+        <is>
+          <t>OJO: saliendo de Manhattan NO rige la tarifa fija por zonas (esa es solo para taxis que salen de EWR). Se cobra medidor + recargo Newark de $20 + peajes + congestion charge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
           <t>Uber / Lyft</t>
         </is>
       </c>
-      <c r="B19" s="39" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>$70-110 + riesgo alto de surge</t>
         </is>
       </c>
-      <c r="C19" s="39" t="inlineStr">
+      <c r="C20" s="39" t="inlineStr">
         <is>
           <t>50-75 min</t>
         </is>
       </c>
-      <c r="D19" s="39" t="inlineStr">
+      <c r="D20" s="39" t="inlineStr">
         <is>
           <t>El domingo 6/9 es el domingo del fin de semana largo de Labor Day: el día de mayor tráfico de retorno del año. Riesgo real de surge y de demora.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="59" t="inlineStr">
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="59" t="inlineStr">
         <is>
           <t>⚠ Alerta</t>
         </is>
       </c>
-      <c r="B20" s="59" t="inlineStr"/>
-      <c r="C20" s="59" t="inlineStr"/>
-      <c r="D20" s="59" t="inlineStr">
+      <c r="B21" s="59" t="inlineStr"/>
+      <c r="C21" s="59" t="inlineStr"/>
+      <c r="D21" s="59" t="inlineStr">
         <is>
           <t>El domingo 6 es el domingo del fin de semana largo de Labor Day: la noche de mayor tráfico de retorno del año. Eso castiga fuerte a todo lo que vaya en auto y no afecta al tren, así que esta noche puntual el tren no es solo más barato sino más confiable. Pero EWR va a estar cargado: por eso salimos con 2h45 y no con las 2h de siempre.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="33" t="inlineStr">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t>Bridgewater/Branchburg NJ ↔ Manhattan · 31 ago al 3 sep</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>RECOMENDADO: Estación RARITAN + pasajes sueltos + Uber al tren</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="59" t="inlineStr">
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="59" t="inlineStr">
         <is>
           <t>Hotel</t>
         </is>
       </c>
-      <c r="B24" s="59" t="inlineStr"/>
-      <c r="C24" s="59" t="inlineStr"/>
-      <c r="D24" s="59" t="inlineStr">
+      <c r="B25" s="59" t="inlineStr"/>
+      <c r="C25" s="59" t="inlineStr"/>
+      <c r="D25" s="59" t="inlineStr">
         <is>
           <t>Residence Inn Bridgewater Branchburg, 3241 US-22 East. NO TIENE SHUTTLE (confirmado por Marriott). Estacionamiento propio gratis.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="57" t="inlineStr">
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="57" t="inlineStr">
         <is>
           <t>Estación</t>
         </is>
       </c>
-      <c r="B25" s="57" t="inlineStr">
+      <c r="B26" s="57" t="inlineStr">
         <is>
           <t>Distancia del hotel</t>
         </is>
       </c>
-      <c r="C25" s="57" t="inlineStr">
+      <c r="C26" s="57" t="inlineStr">
         <is>
           <t>Estacionamiento</t>
         </is>
       </c>
-      <c r="D25" s="57" t="inlineStr">
+      <c r="D26" s="57" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="58" t="inlineStr">
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="58" t="inlineStr">
         <is>
           <t>Raritan ✅</t>
         </is>
       </c>
-      <c r="B26" s="58" t="inlineStr">
+      <c r="B27" s="58" t="inlineStr">
         <is>
           <t>6,4 km / 4,0 mi</t>
         </is>
       </c>
-      <c r="C26" s="58" t="inlineStr">
+      <c r="C27" s="58" t="inlineStr">
         <is>
           <t>$4/día</t>
         </is>
       </c>
-      <c r="D26" s="58" t="inlineStr">
+      <c r="D27" s="58" t="inlineStr">
         <is>
           <t>Completo. Es cabecera: siempre hay asiento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="39" t="inlineStr">
-        <is>
-          <t>Somerville</t>
-        </is>
-      </c>
-      <c r="B27" s="39" t="inlineStr">
-        <is>
-          <t>8,1 km / 5,0 mi</t>
-        </is>
-      </c>
-      <c r="C27" s="39" t="inlineStr">
-        <is>
-          <t>$5/día (garage Robeson St)</t>
-        </is>
-      </c>
-      <c r="D27" s="39" t="inlineStr">
-        <is>
-          <t>Completo. Resta 3 min de viaje pero está 1 milla más lejos.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="39" t="inlineStr">
         <is>
-          <t>North Branch ❌</t>
+          <t>Somerville</t>
         </is>
       </c>
       <c r="B28" s="39" t="inlineStr">
         <is>
-          <t>1,7 km / 1,0 mi</t>
+          <t>8,1 km / 5,0 mi</t>
         </is>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
-          <t>GRATIS, 40 lugares</t>
+          <t>$5/día (garage Robeson St)</t>
         </is>
       </c>
       <c r="D28" s="39" t="inlineStr">
         <is>
-          <t>SOLO horas pico. Es la más cercana pero no sirve.</t>
+          <t>Completo. Resta 3 min de viaje pero está 1 milla más lejos.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="39" t="inlineStr">
         <is>
+          <t>North Branch ❌</t>
+        </is>
+      </c>
+      <c r="B29" s="39" t="inlineStr">
+        <is>
+          <t>1,7 km / 1,0 mi</t>
+        </is>
+      </c>
+      <c r="C29" s="39" t="inlineStr">
+        <is>
+          <t>GRATIS, 40 lugares</t>
+        </is>
+      </c>
+      <c r="D29" s="39" t="inlineStr">
+        <is>
+          <t>SOLO horas pico. Es la más cercana pero no sirve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="39" t="inlineStr">
+        <is>
           <t>Bridgewater</t>
         </is>
       </c>
-      <c r="B29" s="39" t="inlineStr">
+      <c r="B30" s="39" t="inlineStr">
         <is>
           <t>13,2 km / 8,2 mi</t>
         </is>
       </c>
-      <c r="C29" s="39" t="inlineStr">
+      <c r="C30" s="39" t="inlineStr">
         <is>
           <t>$4/día</t>
         </is>
       </c>
-      <c r="D29" s="39" t="inlineStr">
+      <c r="D30" s="39" t="inlineStr">
         <is>
           <t>Completo, pero es la más lejana del hotel.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="57" t="inlineStr">
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="57" t="inlineStr">
         <is>
           <t>Tipo de pasaje</t>
         </is>
       </c>
-      <c r="B31" s="57" t="inlineStr">
+      <c r="B32" s="57" t="inlineStr">
         <is>
           <t>Precio</t>
         </is>
       </c>
-      <c r="C31" s="57" t="inlineStr"/>
-      <c r="D31" s="57" t="inlineStr">
+      <c r="C32" s="57" t="inlineStr"/>
+      <c r="D32" s="57" t="inlineStr">
         <is>
           <t>Nota</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="58" t="inlineStr">
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="58" t="inlineStr">
         <is>
           <t>Pasaje suelto Raritan → NY Penn</t>
         </is>
       </c>
-      <c r="B32" s="58" t="inlineStr">
+      <c r="B33" s="58" t="inlineStr">
         <is>
           <t>$18,50</t>
         </is>
       </c>
-      <c r="C32" s="58" t="inlineStr"/>
-      <c r="D32" s="58" t="inlineStr">
+      <c r="C33" s="58" t="inlineStr"/>
+      <c r="D33" s="58" t="inlineStr">
         <is>
           <t>PLAN CONFIRMADO: JP hace 4 tramos = $74 (ida el 1, vuelta el 2, ida el 3, más la vuelta del 31). Thais hace 2 = $37. Total $111 ← LA OPCIÓN MÁS BARATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="39" t="inlineStr">
-        <is>
-          <t>Round-trip</t>
-        </is>
-      </c>
-      <c r="B33" s="39" t="inlineStr">
-        <is>
-          <t>$37,00</t>
-        </is>
-      </c>
-      <c r="C33" s="39" t="inlineStr"/>
-      <c r="D33" s="39" t="inlineStr">
-        <is>
-          <t>Exactamente 2 × $18,50. NO hay descuento.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="39" t="inlineStr">
         <is>
-          <t>10-trip</t>
+          <t>Round-trip</t>
         </is>
       </c>
       <c r="B34" s="39" t="inlineStr">
         <is>
-          <t>$185,00</t>
+          <t>$37,00</t>
         </is>
       </c>
       <c r="C34" s="39" t="inlineStr"/>
       <c r="D34" s="39" t="inlineStr">
         <is>
-          <t>Exactamente 10 × $18,50. Más caro y sobran 2 viajes.</t>
+          <t>Exactamente 2 × $18,50. NO hay descuento.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="39" t="inlineStr">
         <is>
-          <t>Pase semanal</t>
+          <t>10-trip</t>
         </is>
       </c>
       <c r="B35" s="39" t="inlineStr">
         <is>
-          <t>$164,00</t>
+          <t>$185,00</t>
         </is>
       </c>
       <c r="C35" s="39" t="inlineStr"/>
       <c r="D35" s="39" t="inlineStr">
         <is>
-          <t>Más caro que 8 pasajes sueltos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="40" customHeight="1">
+          <t>Exactamente 10 × $18,50. Más caro y sobran 2 viajes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
       <c r="A36" s="39" t="inlineStr">
         <is>
-          <t>FlexPass (20 viajes one-way)</t>
+          <t>Pase semanal</t>
         </is>
       </c>
       <c r="B36" s="39" t="inlineStr">
         <is>
-          <t>$314,50</t>
+          <t>$164,00</t>
         </is>
       </c>
       <c r="C36" s="39" t="inlineStr"/>
       <c r="D36" s="39" t="inlineStr">
         <is>
-          <t>El ÚNICO producto con descuento real: 15% off, válido 30 días. Pero son 20 viajes y ustedes hacen 8 — no sirve para este viaje.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="26" customHeight="1">
+          <t>Más caro que 8 pasajes sueltos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
       <c r="A37" s="39" t="inlineStr">
         <is>
-          <t>Bus 114/117 a Port Authority</t>
+          <t>FlexPass (20 viajes one-way)</t>
         </is>
       </c>
       <c r="B37" s="39" t="inlineStr">
         <is>
-          <t>$15,80</t>
+          <t>$314,50</t>
         </is>
       </c>
       <c r="C37" s="39" t="inlineStr"/>
       <c r="D37" s="39" t="inlineStr">
         <is>
+          <t>El ÚNICO producto con descuento real: 15% off, válido 30 días. Pero son 20 viajes y ustedes hacen 8 — no sirve para este viaje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="39" t="inlineStr">
+        <is>
+          <t>Bus 114/117 a Port Authority</t>
+        </is>
+      </c>
+      <c r="B38" s="39" t="inlineStr">
+        <is>
+          <t>$15,80</t>
+        </is>
+      </c>
+      <c r="C38" s="39" t="inlineStr"/>
+      <c r="D38" s="39" t="inlineStr">
+        <is>
           <t>$22 más barato en total, pero 45 min más por tramo. No compensa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="40" customHeight="1">
-      <c r="A39" s="39" t="inlineStr">
-        <is>
-          <t>Horarios</t>
-        </is>
-      </c>
-      <c r="B39" s="39" t="inlineStr"/>
-      <c r="C39" s="39" t="inlineStr"/>
-      <c r="D39" s="39" t="inlineStr">
-        <is>
-          <t>MAÑANA (Raritan → NY Penn, todos con transbordo en Newark): 4:31→5:59, 6:23→7:37, 6:42→8:05, 6:55→8:20, 7:13→8:31. NOCHE (NY Penn → Raritan), verificado para el miércoles 2/9/2026: 19:42 con transbordo → 21:12 · 20:48 DIRECTO → 22:04 · 21:48 DIRECTO → 23:10 · 22:48 DIRECTO → 00:04 · 00:05 con transbordo → 01:31 · 01:00 con transbordo → 02:35 (último). Viaje 75-90 min.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" s="39" t="inlineStr">
         <is>
-          <t>Trenes directos</t>
+          <t>Horarios</t>
         </is>
       </c>
       <c r="B40" s="39" t="inlineStr"/>
       <c r="C40" s="39" t="inlineStr"/>
       <c r="D40" s="39" t="inlineStr">
         <is>
+          <t>MAÑANA (Raritan → NY Penn, todos con transbordo en Newark): 4:31→5:59, 6:23→7:37, 6:42→8:05, 6:55→8:20, 7:13→8:31. NOCHE (NY Penn → Raritan), verificado para el miércoles 2/9/2026: 19:42 con transbordo → 21:12 · 20:48 DIRECTO → 22:04 · 21:48 DIRECTO → 23:10 · 22:48 DIRECTO → 00:04 · 00:05 con transbordo → 01:31 · 01:00 con transbordo → 02:35 (último). Viaje 75-90 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="39" t="inlineStr">
+        <is>
+          <t>Trenes directos</t>
+        </is>
+      </c>
+      <c r="B41" s="39" t="inlineStr"/>
+      <c r="C41" s="39" t="inlineStr"/>
+      <c r="D41" s="39" t="inlineStr">
+        <is>
           <t>8 trenes DIRECTOS por sentido, solo días hábiles. HACIA EL ESTE (Raritan → NY Penn), llegadas a Penn: 10:06, 11:11, 12:07, 13:08, 14:10, 20:14, 21:16, 22:10. HACIA EL OESTE (NY Penn → Raritan), salidas: 10:40, 11:40, 12:45, 13:40, 14:40 y 20:48, 21:48, 22:48. CORRECCIÓN: yo había dicho que los directos eran solo de valle — es falso, los TRES trenes de la noche son directos y son justo los que ustedes van a usar. El resto del día (pico y madrugada) todos los trenes del RVL nacen o terminan en Newark Penn y hay que transbordar. El motivo: el RVL no está electrificado al oeste de Newark. Los fines de semana NO hay directo. Verificado en el PDF oficial de NJ Transit y en el feed GTFS para el 2 de septiembre de 2026.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="57" t="inlineStr">
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="57" t="inlineStr">
         <is>
           <t>Escenario</t>
         </is>
       </c>
-      <c r="B42" s="57" t="inlineStr">
+      <c r="B43" s="57" t="inlineStr">
         <is>
           <t>Cálculo</t>
         </is>
       </c>
-      <c r="C42" s="57" t="inlineStr"/>
-      <c r="D42" s="57" t="inlineStr">
+      <c r="C43" s="57" t="inlineStr"/>
+      <c r="D43" s="57" t="inlineStr">
         <is>
           <t>Total 4 días</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="58" t="inlineStr">
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="58" t="inlineStr">
         <is>
           <t>① Uber ↔ Raritan + tren ✅ (PLAN REAL)</t>
         </is>
       </c>
-      <c r="B43" s="58" t="inlineStr">
+      <c r="B44" s="58" t="inlineStr">
         <is>
           <t>$111 tren (6 tramos entre los dos) + $108 Uber (6 tramos)</t>
         </is>
       </c>
-      <c r="C43" s="58" t="inlineStr"/>
-      <c r="D43" s="58" t="inlineStr">
+      <c r="C44" s="58" t="inlineStr"/>
+      <c r="D44" s="58" t="inlineStr">
         <is>
           <t>~$219 los dos</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="39" t="inlineStr">
-        <is>
-          <t>② Bus 114/117 + Uber</t>
-        </is>
-      </c>
-      <c r="B44" s="39" t="inlineStr">
-        <is>
-          <t>$126,40 bus + $128-176 Uber</t>
-        </is>
-      </c>
-      <c r="C44" s="39" t="inlineStr"/>
-      <c r="D44" s="39" t="inlineStr">
-        <is>
-          <t>$254-302 (pero +45 min por tramo)</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="39" t="inlineStr">
         <is>
-          <t>③ Auto de alquiler + park&amp;ride</t>
+          <t>② Bus 114/117 + Uber</t>
         </is>
       </c>
       <c r="B45" s="39" t="inlineStr">
         <is>
-          <t>$160-300 alquiler + $16 parking + nafta + $148 tren</t>
+          <t>$126,40 bus + $128-176 Uber</t>
         </is>
       </c>
       <c r="C45" s="39" t="inlineStr"/>
       <c r="D45" s="39" t="inlineStr">
         <is>
-          <t>$329-469 ❌</t>
+          <t>$254-302 (pero +45 min por tramo)</t>
         </is>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="39" t="inlineStr">
         <is>
-          <t>④ Auto hasta Newark Penn + PATH</t>
+          <t>③ Auto de alquiler + park&amp;ride</t>
         </is>
       </c>
       <c r="B46" s="39" t="inlineStr">
         <is>
-          <t>$160-300 alquiler + $80-120 parking + $26 PATH</t>
+          <t>$160-300 alquiler + $16 parking + nafta + $148 tren</t>
         </is>
       </c>
       <c r="C46" s="39" t="inlineStr"/>
       <c r="D46" s="39" t="inlineStr">
         <is>
+          <t>$329-469 ❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="39" t="inlineStr">
+        <is>
+          <t>④ Auto hasta Newark Penn + PATH</t>
+        </is>
+      </c>
+      <c r="B47" s="39" t="inlineStr">
+        <is>
+          <t>$160-300 alquiler + $80-120 parking + $26 PATH</t>
+        </is>
+      </c>
+      <c r="C47" s="39" t="inlineStr"/>
+      <c r="D47" s="39" t="inlineStr">
+        <is>
           <t>$266-446 ❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="40" customHeight="1">
-      <c r="A47" s="59" t="inlineStr">
-        <is>
-          <t>¿Conviene alquilar auto?</t>
-        </is>
-      </c>
-      <c r="B47" s="59" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C47" s="59" t="inlineStr"/>
-      <c r="D47" s="59" t="inlineStr">
-        <is>
-          <t>NO conviene alquilar auto solo para llegar a la estación: sale $70-160 más caro que el Uber y sumás manejar, estacionar y devolver. Solo tiene sentido si van a usar el auto para otra cosa. Y NO manejes hasta PATH: son ~35 millas por la Ruta 78/22 en hora pico (45-70 min por tramo, o sea 1,5-2,5 h diarias al volante) y PATH te deja en downtown, no en Midtown.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" s="59" t="inlineStr">
         <is>
-          <t>⚠ Riesgo</t>
-        </is>
-      </c>
-      <c r="B48" s="59" t="inlineStr"/>
+          <t>¿Conviene alquilar auto?</t>
+        </is>
+      </c>
+      <c r="B48" s="59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="C48" s="59" t="inlineStr"/>
       <c r="D48" s="59" t="inlineStr">
         <is>
+          <t>NO conviene alquilar auto solo para llegar a la estación: sale $70-160 más caro que el Uber y sumás manejar, estacionar y devolver. Solo tiene sentido si van a usar el auto para otra cosa. Y NO manejes hasta PATH: son ~35 millas por la Ruta 78/22 en hora pico (45-70 min por tramo, o sea 1,5-2,5 h diarias al volante) y PATH te deja en downtown, no en Midtown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" s="59" t="inlineStr">
+        <is>
+          <t>⚠ Riesgo</t>
+        </is>
+      </c>
+      <c r="B49" s="59" t="inlineStr"/>
+      <c r="C49" s="59" t="inlineStr"/>
+      <c r="D49" s="59" t="inlineStr">
+        <is>
           <t>DOS RIESGOS. (1) EL HUECO DE LAS 22:48: si perdés ese tren, la próxima llegada a Raritan es a la 01:31, o sea 87 minutos después. No hay NADA en el medio. El de las 22:48 es el tren crítico de las dos noches que volvés a New Jersey. (2) Branchburg es zona semi-rural: la disponibilidad de Uber a las 6-7 AM puede ser baja y las esperas largas. Pedí el auto la noche anterior y tené plan B. AVISO: NJ Transit publica cambios por obras con ~2 semanas de anticipación — revisá njtransit.com/travel-alerts-to unos días antes.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="33" t="inlineStr">
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="33" t="inlineStr">
         <is>
           <t>Moverse dentro de NYC</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="40" customHeight="1">
-      <c r="A51" s="60" t="inlineStr">
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" s="60" t="inlineStr">
         <is>
           <t>🔴 CAMBIO CLAVE 2026</t>
         </is>
       </c>
-      <c r="B51" s="60" t="inlineStr"/>
-      <c r="C51" s="60" t="inlineStr"/>
-      <c r="D51" s="60" t="inlineStr">
+      <c r="B52" s="60" t="inlineStr"/>
+      <c r="C52" s="60" t="inlineStr"/>
+      <c r="D52" s="60" t="inlineStr">
         <is>
           <t>EL METROCARD SE ELIMINÓ. Desde el 1 de enero de 2026 no se puede comprar ni recargar, y los pases de 7 y 30 días ilimitados ya no existen. No hay decisión que tomar: se usa OMNY.</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="26" customHeight="1">
-      <c r="A52" s="39" t="inlineStr">
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="39" t="inlineStr">
         <is>
           <t>Tarifa</t>
         </is>
       </c>
-      <c r="B52" s="39" t="inlineStr">
+      <c r="B53" s="39" t="inlineStr">
         <is>
           <t>$3,00</t>
         </is>
       </c>
-      <c r="C52" s="39" t="inlineStr"/>
-      <c r="D52" s="39" t="inlineStr">
+      <c r="C53" s="39" t="inlineStr"/>
+      <c r="D53" s="39" t="inlineStr">
         <is>
           <t>$3,00 por viaje de subte o bus local (subió de $2,90 en enero 2026). Bus express $7,25.</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="40" customHeight="1">
-      <c r="A53" s="58" t="inlineStr">
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" s="58" t="inlineStr">
         <is>
           <t>Fare capping OMNY</t>
         </is>
       </c>
-      <c r="B53" s="58" t="inlineStr">
+      <c r="B54" s="58" t="inlineStr">
         <is>
           <t>tope $35 / 7 días</t>
         </is>
       </c>
-      <c r="C53" s="58" t="inlineStr"/>
-      <c r="D53" s="58" t="inlineStr">
+      <c r="C54" s="58" t="inlineStr"/>
+      <c r="D54" s="58" t="inlineStr">
         <is>
           <t>Fare capping de OMNY: una vez que gastaste $35 en pasajes dentro de una ventana móvil de 7 días, el resto de esos 7 días viajás gratis. La regla es el MONTO ($35), no la cantidad de viajes — que den ~12 es aritmética ($3 × 11 = $33 y el viaje 12 cobra $2 hasta llegar a $35). La ventana arranca con el PRIMER tap, no el lunes. Los buses express, el AirTrain de JFK y los transbordos NO suman al tope.</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="40" customHeight="1">
-      <c r="A54" s="59" t="inlineStr">
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" s="59" t="inlineStr">
         <is>
           <t>⚠ CRÍTICO</t>
         </is>
       </c>
-      <c r="B54" s="59" t="inlineStr"/>
-      <c r="C54" s="59" t="inlineStr"/>
-      <c r="D54" s="59" t="inlineStr">
+      <c r="B55" s="59" t="inlineStr"/>
+      <c r="C55" s="59" t="inlineStr"/>
+      <c r="D55" s="59" t="inlineStr">
         <is>
           <t>Hay que usar SIEMPRE EL MISMO plástico o dispositivo los 7 días. Si un día tapean con el celular y otro con la tarjeta física, el contador se parte en dos y nunca llegan al tope. Cada persona necesita su propio medio: no se puede tapear dos veces con la misma tarjeta. Y ojo con la tarjeta extranjera: cada tap puede generar comisión por consumo en el exterior — conviene una tarjeta sin esa comisión, o crear una cuenta OMNY.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="40" customHeight="1">
-      <c r="A55" s="39" t="inlineStr">
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" s="39" t="inlineStr">
         <is>
           <t>Cuenta del viaje</t>
-        </is>
-      </c>
-      <c r="B55" s="39" t="inlineStr"/>
-      <c r="C55" s="39" t="inlineStr"/>
-      <c r="D55" s="39" t="inlineStr">
-        <is>
-          <t>9 días en NYC = dos períodos de 7 días. Con uso intensivo, el techo es $35 + $35 = $70 por persona en todo el viaje. Con uso liviano pagan solo lo que usan: OMNY nunca cobra de más.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="26" customHeight="1">
-      <c r="A56" s="39" t="inlineStr">
-        <is>
-          <t>Ink48 (48th &amp; 11th Ave)</t>
         </is>
       </c>
       <c r="B56" s="39" t="inlineStr"/>
       <c r="C56" s="39" t="inlineStr"/>
       <c r="D56" s="39" t="inlineStr">
         <is>
-          <t>50 St (C,E) a ~12 min caminando hacia el este. Es un hotel notoriamente lejos del subte.</t>
+          <t>9 días en NYC = dos períodos de 7 días. Con uso intensivo, el techo es $35 + $35 = $70 por persona en todo el viaje. Con uso liviano pagan solo lo que usan: OMNY nunca cobra de más.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="39" t="inlineStr">
         <is>
-          <t>The Beacon (Broadway &amp; 75th)</t>
+          <t>Ink48 (48th &amp; 11th Ave)</t>
         </is>
       </c>
       <c r="B57" s="39" t="inlineStr"/>
       <c r="C57" s="39" t="inlineStr"/>
       <c r="D57" s="39" t="inlineStr">
+        <is>
+          <t>50 St (C,E) a ~12 min caminando hacia el este. Es un hotel notoriamente lejos del subte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="39" t="inlineStr">
+        <is>
+          <t>The Beacon (Broadway &amp; 75th)</t>
+        </is>
+      </c>
+      <c r="B58" s="39" t="inlineStr"/>
+      <c r="C58" s="39" t="inlineStr"/>
+      <c r="D58" s="39" t="inlineStr">
         <is>
           <t>72 St (1,2,3) a 3 cuadras, 79 St (1) a 4. Directo a Penn Station en 10 min.</t>
         </is>
@@ -38258,12 +38307,12 @@
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A50:D50"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A51:D51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/NYC_2026_Planificador.xlsx
+++ b/NYC_2026_Planificador.xlsx
@@ -38627,7 +38627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -38935,17 +38935,17 @@
       <c r="A16" s="41" t="inlineStr"/>
       <c r="B16" s="60" t="inlineStr">
         <is>
-          <t>Guggenheim — llamar y preguntar DOS cosas: si la rotonda está abierta y si sigue el pay-what-you-wish</t>
+          <t>✅ RESUELTO — la rotonda del Guggenheim está CERRADA hasta el 17/9. Por eso el domingo entra MoMA PS1 en su lugar; el Guggenheim quedó como alternativa escrita en el bloque de las 18:20</t>
         </is>
       </c>
       <c r="C16" s="59" t="inlineStr">
         <is>
-          <t>La mañana del domingo 6, antes de salir del hotel</t>
+          <t>verificado el 27/8, ya no hay que llamar</t>
         </is>
       </c>
       <c r="D16" s="59" t="inlineStr">
         <is>
-          <t>guggenheim.org / +1 212-423-3500</t>
+          <t>guggenheim.org</t>
         </is>
       </c>
       <c r="E16" s="59" t="inlineStr">
@@ -38958,91 +38958,91 @@
       <c r="A17" s="41" t="inlineStr"/>
       <c r="B17" s="60" t="inlineStr">
         <is>
-          <t>Revisar travel alerts de NJ Transit para la noche del 2/9 y la mañana del 3/9</t>
+          <t>STUDIO MUSEUM sáb 29 — entrada con HORARIO ASIGNADO, sacarla antes. «Fade» cierra el 6/9: el sábado es la única pasada del viaje</t>
         </is>
       </c>
       <c r="C17" s="59" t="inlineStr">
         <is>
-          <t>2-3 días antes</t>
+          <t>HOY</t>
         </is>
       </c>
       <c r="D17" s="59" t="inlineStr">
         <is>
-          <t>njtransit.com/travel-alerts-to</t>
+          <t>studiomuseum.org</t>
         </is>
       </c>
       <c r="E17" s="59" t="inlineStr">
         <is>
-          <t>La ÚNICA noche que queda de vuelta a New Jersey (mié 2) depende del directo de las 22:48 — si se cae, la próxima llegada a Raritan es 01:31. Y el jueves 6:55 con las maletas también es NJT.</t>
+          <t>Reabrió este año tras siete cerrado, en el edificio nuevo de Adjaye. Sugerido $16, gratis los domingos. Lo detectó el barrido del 27/8: la entrada es con hora asignada, no se entra y ya.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="41" t="inlineStr"/>
-      <c r="B18" s="62" t="inlineStr">
-        <is>
-          <t>MO Lounge (Mandarin Oriental, piso 35) — JUEVES 3/9 ~20:30, antes de Dizzy's</t>
-        </is>
-      </c>
-      <c r="C18" s="39" t="inlineStr">
-        <is>
-          <t>1 semana antes</t>
-        </is>
-      </c>
-      <c r="D18" s="39" t="inlineStr">
-        <is>
-          <t>mandarinoriental.com (SevenRooms)</t>
-        </is>
-      </c>
-      <c r="E18" s="39" t="inlineStr">
-        <is>
-          <t>Ventanales sobre Central Park y está en el MISMO edificio que Dizzy's: se baja en ascensor. Coctel ~$26-32, sin cover. Alternativa en el mismo piso: The Bar (mar-sáb 17-1h, 45 asientos).</t>
+      <c r="B18" s="60" t="inlineStr">
+        <is>
+          <t>FRICK mié 2 — reservar la ventana a voluntad de 13:30 a 17:30</t>
+        </is>
+      </c>
+      <c r="C18" s="59" t="inlineStr">
+        <is>
+          <t>HOY</t>
+        </is>
+      </c>
+      <c r="D18" s="59" t="inlineStr">
+        <is>
+          <t>frick.org</t>
+        </is>
+      </c>
+      <c r="E18" s="59" t="inlineStr">
+        <is>
+          <t>Esa ventana es TODA: fuera de ella son $30 por cabeza. Online el mínimo es $5. El cupo en puerta existe pero no está garantizado, y son solo cuatro horas.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="41" t="inlineStr"/>
-      <c r="B19" s="62" t="inlineStr">
-        <is>
-          <t>Dos mails operativos: early check-in Ink48 (para el sáb 29) y luggage drop en The Beacon desde las 8:45 (jue 3)</t>
-        </is>
-      </c>
-      <c r="C19" s="39" t="inlineStr">
-        <is>
-          <t>esta semana</t>
-        </is>
-      </c>
-      <c r="D19" s="39" t="inlineStr">
-        <is>
-          <t>mail a cada hotel</t>
-        </is>
-      </c>
-      <c r="E19" s="39" t="inlineStr">
-        <is>
-          <t>El día 1 y el día 6 dependen de que los dos hoteles digan que sí. Un mail de dos líneas cada uno.</t>
+      <c r="B19" s="60" t="inlineStr">
+        <is>
+          <t>MORGAN LIBRARY vie 4 — las reservas del viernes gratis (17-20h) se liberan HOY, viernes 28</t>
+        </is>
+      </c>
+      <c r="C19" s="59" t="inlineStr">
+        <is>
+          <t>HOY, es el día</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="inlineStr">
+        <is>
+          <t>themorgan.org</t>
+        </is>
+      </c>
+      <c r="E19" s="59" t="inlineStr">
+        <is>
+          <t>Reserva obligatoria y se agota. Si no sale, el viernes queda un hueco de 17:00 a 18:10 antes del SUMMIT.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="41" t="inlineStr"/>
-      <c r="B20" s="62" t="inlineStr">
-        <is>
-          <t>Orden de artistas del festival Charlie Parker (¿a qué hora toca Joshua Redman?)</t>
-        </is>
-      </c>
-      <c r="C20" s="39" t="inlineStr">
-        <is>
-          <t>vie 28/8</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>cityparksfoundation.org</t>
-        </is>
-      </c>
-      <c r="E20" s="39" t="inlineStr">
-        <is>
-          <t>La salida obligada de las 18:30 puede o no cortar el set de cierre. Saberlo el día antes permite decidir el plan B del subte (salir 18:10) con datos.</t>
+      <c r="B20" s="60" t="inlineStr">
+        <is>
+          <t>Revisar travel alerts de NJ Transit para la noche del 2/9 y la mañana del 3/9</t>
+        </is>
+      </c>
+      <c r="C20" s="59" t="inlineStr">
+        <is>
+          <t>2-3 días antes</t>
+        </is>
+      </c>
+      <c r="D20" s="59" t="inlineStr">
+        <is>
+          <t>njtransit.com/travel-alerts-to</t>
+        </is>
+      </c>
+      <c r="E20" s="59" t="inlineStr">
+        <is>
+          <t>La ÚNICA noche que queda de vuelta a New Jersey (mié 2) depende del directo de las 22:48 — si se cae, la próxima llegada a Raritan es 01:31. Y el jueves 6:55 con las maletas también es NJT.</t>
         </is>
       </c>
     </row>
@@ -39050,22 +39050,22 @@
       <c r="A21" s="41" t="inlineStr"/>
       <c r="B21" s="62" t="inlineStr">
         <is>
-          <t>Broadway — loterías digitales</t>
+          <t>MO Lounge (Mandarin Oriental, piso 35) — JUEVES 3/9 ~20:30, antes de Dizzy's</t>
         </is>
       </c>
       <c r="C21" s="39" t="inlineStr">
         <is>
-          <t>TODOS LOS DÍAS desde ya</t>
+          <t>1 semana antes</t>
         </is>
       </c>
       <c r="D21" s="39" t="inlineStr">
         <is>
-          <t>Broadway Direct, Telecharge, LuckySeat, TodayTix</t>
+          <t>mandarinoriental.com (SevenRooms)</t>
         </is>
       </c>
       <c r="E21" s="39" t="inlineStr">
         <is>
-          <t>Entrar es GRATIS. Hamilton $10, Maybe Happy Ending $20,64, MJ/Hadestown/Moulin Rouge $49. Anotarse a 5-6 por día no cuesta nada.</t>
+          <t>Ventanales sobre Central Park y está en el MISMO edificio que Dizzy's: se baja en ascensor. Coctel ~$26-32, sin cover. Alternativa en el mismo piso: The Bar (mar-sáb 17-1h, 45 asientos).</t>
         </is>
       </c>
     </row>
@@ -39073,22 +39073,22 @@
       <c r="A22" s="41" t="inlineStr"/>
       <c r="B22" s="62" t="inlineStr">
         <is>
-          <t>One World Observatory — JUEVES 3/9 ~13:45</t>
+          <t>Dos mails operativos: early check-in Ink48 (para el sáb 29) y luggage drop en The Beacon desde las 8:45 (jue 3)</t>
         </is>
       </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
-          <t>1-2 semanas antes</t>
+          <t>esta semana</t>
         </is>
       </c>
       <c r="D22" s="39" t="inlineStr">
         <is>
-          <t>oneworldobservatory.com</t>
+          <t>mail a cada hotel</t>
         </is>
       </c>
       <c r="E22" s="39" t="inlineStr">
         <is>
-          <t>$44 + $3,50 fee, ventana de entrada de 15 min. Los slots de la tarde se agotan en verano.</t>
+          <t>El día 1 y el día 6 dependen de que los dos hoteles digan que sí. Un mail de dos líneas cada uno.</t>
         </is>
       </c>
     </row>
@@ -39096,22 +39096,22 @@
       <c r="A23" s="41" t="inlineStr"/>
       <c r="B23" s="62" t="inlineStr">
         <is>
-          <t>Mercer Labs — DOMINGO 30/8, slot 17:30 (Fever)</t>
+          <t>✅ RESUELTO — festival Charlie Parker: sáb 29, Marcus Garvey Park, 14:00 a 19:00, cierra JOSHUA REDMAN con Nat Adderley Jr., Catherine Russell y Nicole Glover</t>
         </is>
       </c>
       <c r="C23" s="39" t="inlineStr">
         <is>
-          <t>esta semana</t>
+          <t>verificado el 27/8</t>
         </is>
       </c>
       <c r="D23" s="39" t="inlineStr">
         <is>
-          <t>mercerlabs.com</t>
+          <t>cityparksfoundation.org</t>
         </is>
       </c>
       <c r="E23" s="39" t="inlineStr">
         <is>
-          <t>Hasta $57 por cabeza según franja; los slots del fin de semana se agotan en Fever. El domingo abre hasta las 22, así que si el 17:30 no está, cualquier slot 17:00-18:00 mantiene la cadena (Crown al atardecer 19:15).</t>
+          <t>La salida obligada de las 18:30 puede o no cortar el set de cierre. Saberlo el día antes permite decidir el plan B del subte (salir 18:10) con datos.</t>
         </is>
       </c>
     </row>
@@ -39119,22 +39119,22 @@
       <c r="A24" s="41" t="inlineStr"/>
       <c r="B24" s="62" t="inlineStr">
         <is>
-          <t>JGStay SoHo — RESUELTO (JP: 31/8 → 2/9). Confirmar la CONSIGNA de equipaje por mensaje</t>
+          <t>Broadway — loterías digitales</t>
         </is>
       </c>
       <c r="C24" s="39" t="inlineStr">
         <is>
-          <t>esta semana</t>
+          <t>TODOS LOS DÍAS desde ya</t>
         </is>
       </c>
       <c r="D24" s="39" t="inlineStr">
         <is>
-          <t>jgstay.com</t>
+          <t>Broadway Direct, Telecharge, LuckySeat, TodayTix</t>
         </is>
       </c>
       <c r="E24" s="39" t="inlineStr">
         <is>
-          <t>Ya reservado por Juan: adiós a dos de las tres vueltas nocturnas a NJ. Confirmar: dejar bolso lunes ~8:35 (antes del check-in) y consigna el miércoles post-checkout hasta ~17:00. Desayuno incluido 7-9 AM; recepción 24 h; Canal St (6, N/Q/R/W, J/Z) a pasos.</t>
+          <t>Entrar es GRATIS. Hamilton $10, Maybe Happy Ending $20,64, MJ/Hadestown/Moulin Rouge $49. Anotarse a 5-6 por día no cuesta nada.</t>
         </is>
       </c>
     </row>
@@ -39142,22 +39142,22 @@
       <c r="A25" s="41" t="inlineStr"/>
       <c r="B25" s="62" t="inlineStr">
         <is>
-          <t>Uber en Branchburg — quedó UNA sola mañana (jueves 3, 6:20)</t>
+          <t>One World Observatory — JUEVES 3/9 ~13:45</t>
         </is>
       </c>
       <c r="C25" s="39" t="inlineStr">
         <is>
-          <t>mié 2: pedir el de Raritan→hotel ANTES de subir al tren, y programar el del jueves 6:20</t>
+          <t>1-2 semanas antes</t>
         </is>
       </c>
       <c r="D25" s="39" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>oneworldobservatory.com</t>
         </is>
       </c>
       <c r="E25" s="39" t="inlineStr">
         <is>
-          <t>Zona semi-rural: a las 0:04 y a las 6:20 puede no haber conductores. Programar con anticipación y tener plan B.</t>
+          <t>$44 + $3,50 fee, ventana de entrada de 15 min. Los slots de la tarde se agotan en verano.</t>
         </is>
       </c>
     </row>
@@ -39165,22 +39165,22 @@
       <c r="A26" s="41" t="inlineStr"/>
       <c r="B26" s="62" t="inlineStr">
         <is>
-          <t>Birdland sáb 29/8 — RESERVAR set 21:30: David DeJesus &amp; the Boptet, 'Celebrating Charlie Parker'</t>
+          <t>Mercer Labs — DOMINGO 30/8, slot 17:30 (Fever)</t>
         </is>
       </c>
       <c r="C26" s="39" t="inlineStr">
         <is>
-          <t>YA</t>
+          <t>esta semana</t>
         </is>
       </c>
       <c r="D26" s="39" t="inlineStr">
         <is>
-          <t>birdlandjazz.com</t>
+          <t>mercerlabs.com</t>
         </is>
       </c>
       <c r="E26" s="39" t="inlineStr">
         <is>
-          <t>Cartelera verificada (22/8): tributo a Charlie Parker el día del cumpleaños de Bird, en el club que lleva su nombre, a 8 cuadras del Ink48 — encaja exacto tras los 90 min de mesa en Hudson VU (mesa cierra 21:00). Alternativa más tarde: Makoto Ozone Trio 22:30.</t>
+          <t>Hasta $57 por cabeza según franja; los slots del fin de semana se agotan en Fever. El domingo abre hasta las 22, así que si el 17:30 no está, cualquier slot 17:00-18:00 mantiene la cadena (Crown al atardecer 19:15).</t>
         </is>
       </c>
     </row>
@@ -39188,22 +39188,22 @@
       <c r="A27" s="41" t="inlineStr"/>
       <c r="B27" s="62" t="inlineStr">
         <is>
-          <t>Reverificar el AirTrain de Newark</t>
+          <t>JGStay SoHo — RESUELTO (JP: 31/8 → 2/9). Confirmar la CONSIGNA de equipaje por mensaje</t>
         </is>
       </c>
       <c r="C27" s="39" t="inlineStr">
         <is>
-          <t>2-3 días antes de cada vuelo</t>
+          <t>esta semana</t>
         </is>
       </c>
       <c r="D27" s="39" t="inlineStr">
         <is>
-          <t>njtransit.com</t>
+          <t>jgstay.com</t>
         </is>
       </c>
       <c r="E27" s="39" t="inlineStr">
         <is>
-          <t>Obra de reemplazo hasta 2030, con advisories que se renuevan mes a mes.</t>
+          <t>Ya reservado por Juan: adiós a dos de las tres vueltas nocturnas a NJ. Confirmar: dejar bolso lunes ~8:35 (antes del check-in) y consigna el miércoles post-checkout hasta ~17:00. Desayuno incluido 7-9 AM; recepción 24 h; Canal St (6, N/Q/R/W, J/Z) a pasos.</t>
         </is>
       </c>
     </row>
@@ -39211,22 +39211,22 @@
       <c r="A28" s="41" t="inlineStr"/>
       <c r="B28" s="62" t="inlineStr">
         <is>
-          <t>Dizzy's JUEVES 3/9 21:00 — solo si deciden mantenerlo</t>
+          <t>Uber en Branchburg — quedó UNA sola mañana (jueves 3, 6:20)</t>
         </is>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
-          <t>2-3 días antes</t>
+          <t>mié 2: pedir el de Raritan→hotel ANTES de subir al tren, y programar el del jueves 6:20</t>
         </is>
       </c>
       <c r="D28" s="39" t="inlineStr">
         <is>
-          <t>jazz.org/dizzys</t>
+          <t>app</t>
         </is>
       </c>
       <c r="E28" s="39" t="inlineStr">
         <is>
-          <t>Entradas con horario. CONDICIONAL: es la noche del día de ~17 horas con 5 de sueño — decidan a las 20:00 de ese día; la reserva flexible o el set Late Night (~22:45) son las opciones de bajo riesgo.</t>
+          <t>Zona semi-rural: a las 0:04 y a las 6:20 puede no haber conductores. Programar con anticipación y tener plan B.</t>
         </is>
       </c>
     </row>
@@ -39234,22 +39234,22 @@
       <c r="A29" s="41" t="inlineStr"/>
       <c r="B29" s="62" t="inlineStr">
         <is>
-          <t>Tenement Museum — SOLO SI deciden sumarlo (quedó FUERA del plan)</t>
+          <t>Birdland sáb 29/8 — RESERVAR set 21:30: David DeJesus &amp; the Boptet, 'Celebrating Charlie Parker'</t>
         </is>
       </c>
       <c r="C29" s="39" t="inlineStr">
         <is>
-          <t>solo si lo suman</t>
+          <t>YA</t>
         </is>
       </c>
       <c r="D29" s="39" t="inlineStr">
         <is>
-          <t>tenement.org</t>
+          <t>birdlandjazz.com</t>
         </is>
       </c>
       <c r="E29" s="39" t="inlineStr">
         <is>
-          <t>Los dos lo bajaron a 'quizás' y no está en ningún día. OJO: es sin reembolso — no reservar algo que no está agendado.</t>
+          <t>Cartelera verificada (22/8): tributo a Charlie Parker el día del cumpleaños de Bird, en el club que lleva su nombre, a 8 cuadras del Ink48 — encaja exacto tras los 90 min de mesa en Hudson VU (mesa cierra 21:00). Alternativa más tarde: Makoto Ozone Trio 22:30.</t>
         </is>
       </c>
     </row>
@@ -39257,22 +39257,22 @@
       <c r="A30" s="41" t="inlineStr"/>
       <c r="B30" s="62" t="inlineStr">
         <is>
-          <t>Edge — tarifa Advance Saver $34</t>
+          <t>AirTrain + NJ Transit — ahora es el PLAN B de la llegada (entró el Uber Shuttle). Igual conviene reverificarlo: es lo que salva el sábado si migraciones se estira</t>
         </is>
       </c>
       <c r="C30" s="39" t="inlineStr">
         <is>
-          <t>YA (exige 14+ días)</t>
+          <t>HOY, viernes 28</t>
         </is>
       </c>
       <c r="D30" s="39" t="inlineStr">
         <is>
-          <t>edgenyc.com</t>
+          <t>njtransit.com</t>
         </is>
       </c>
       <c r="E30" s="39" t="inlineStr">
         <is>
-          <t>FUERA del plan (lo marcaron 0/0 en la última pasada). Solo si cambian de idea; con SUMMIT y Top of the Rock ya se solapa mucho.</t>
+          <t>Obra de reemplazo hasta 2030, con advisories que se renuevan mes a mes.</t>
         </is>
       </c>
     </row>
@@ -39280,22 +39280,22 @@
       <c r="A31" s="41" t="inlineStr"/>
       <c r="B31" s="62" t="inlineStr">
         <is>
-          <t>Noguchi Museum — FUERA del plan (0/0)</t>
+          <t>Dizzy's JUEVES 3/9 21:00 — solo si deciden mantenerlo</t>
         </is>
       </c>
       <c r="C31" s="39" t="inlineStr">
         <is>
-          <t>solo si lo suman</t>
+          <t>2-3 días antes</t>
         </is>
       </c>
       <c r="D31" s="39" t="inlineStr">
         <is>
-          <t>noguchi.org</t>
+          <t>jazz.org/dizzys</t>
         </is>
       </c>
       <c r="E31" s="39" t="inlineStr">
         <is>
-          <t>Lo marcaron 0/0: no reservar salvo cambio de idea. (El primer viernes del mes es gratis hasta las 20h, por si acaso.)</t>
+          <t>Entradas con horario. CONDICIONAL: es la noche del día de ~17 horas con 5 de sueño — decidan a las 20:00 de ese día; la reserva flexible o el set Late Night (~22:45) son las opciones de bajo riesgo.</t>
         </is>
       </c>
     </row>
@@ -39303,22 +39303,22 @@
       <c r="A32" s="41" t="inlineStr"/>
       <c r="B32" s="62" t="inlineStr">
         <is>
-          <t>Lincoln Center — revisar calendario de la semana 3-6/9 (Atrium gratis, Film at Lincoln Center)</t>
+          <t>Tenement Museum — SOLO SI deciden sumarlo (quedó FUERA del plan)</t>
         </is>
       </c>
       <c r="C32" s="39" t="inlineStr">
         <is>
-          <t>1 semana antes</t>
+          <t>solo si lo suman</t>
         </is>
       </c>
       <c r="D32" s="39" t="inlineStr">
         <is>
-          <t>lincolncenter.org</t>
+          <t>tenement.org</t>
         </is>
       </c>
       <c r="E32" s="39" t="inlineStr">
         <is>
-          <t>Las salas grandes están entre temporadas (Filarmónica abre 10/9; Met Opera y Ballet después), pero el David Rubenstein Atrium suele tener shows GRATIS entre semana y Film at Lincoln Center proyecta todo el año. Si aparece algo bueno el jueves o viernes, la plaza ya está en el plan del jueves 20:30 y el cambio es trivial.</t>
+          <t>Los dos lo bajaron a 'quizás' y no está en ningún día. OJO: es sin reembolso — no reservar algo que no está agendado.</t>
         </is>
       </c>
     </row>
@@ -39326,22 +39326,22 @@
       <c r="A33" s="41" t="inlineStr"/>
       <c r="B33" s="62" t="inlineStr">
         <is>
-          <t>The Vessel — VIERNES 4/9 10:00</t>
+          <t>Edge — tarifa Advance Saver $34</t>
         </is>
       </c>
       <c r="C33" s="39" t="inlineStr">
         <is>
-          <t>2-3 días antes</t>
+          <t>YA (exige 14+ días)</t>
         </is>
       </c>
       <c r="D33" s="39" t="inlineStr">
         <is>
-          <t>hudsonyardsnewyork.com</t>
+          <t>edgenyc.com</t>
         </is>
       </c>
       <c r="E33" s="39" t="inlineStr">
         <is>
-          <t>$10 (flex $15). Suele haber en el día, pero el timed ticket de las 10:00 asegura el arranque sin fila.</t>
+          <t>FUERA del plan (lo marcaron 0/0 en la última pasada). Solo si cambian de idea; con SUMMIT y Top of the Rock ya se solapa mucho.</t>
         </is>
       </c>
     </row>
@@ -39349,22 +39349,22 @@
       <c r="A34" s="41" t="inlineStr"/>
       <c r="B34" s="62" t="inlineStr">
         <is>
-          <t>Estatua de la Libertad — corona o pedestal</t>
+          <t>Noguchi Museum — FUERA del plan (0/0)</t>
         </is>
       </c>
       <c r="C34" s="39" t="inlineStr">
         <is>
-          <t>YA, y probablemente sea tarde</t>
+          <t>solo si lo suman</t>
         </is>
       </c>
       <c r="D34" s="39" t="inlineStr">
         <is>
-          <t>statuecitycruises.com</t>
+          <t>noguchi.org</t>
         </is>
       </c>
       <c r="E34" s="39" t="inlineStr">
         <is>
-          <t>La corona se agota meses antes. SOLO por el sitio oficial: ninguna agencia vende corona.</t>
+          <t>Lo marcaron 0/0: no reservar salvo cambio de idea. (El primer viernes del mes es gratis hasta las 20h, por si acaso.)</t>
         </is>
       </c>
     </row>
@@ -39372,22 +39372,22 @@
       <c r="A35" s="41" t="inlineStr"/>
       <c r="B35" s="62" t="inlineStr">
         <is>
-          <t>Bill's Place — SALIÓ del plan (lo desplazó el Vanguard del viernes)</t>
+          <t>Lincoln Center — revisar calendario de la semana 3-6/9 (Atrium gratis, Film at Lincoln Center)</t>
         </is>
       </c>
       <c r="C35" s="39" t="inlineStr">
         <is>
-          <t>solo si cambian de idea</t>
+          <t>1 semana antes</t>
         </is>
       </c>
       <c r="D35" s="39" t="inlineStr">
         <is>
-          <t>billsplaceharlem.com</t>
+          <t>lincolncenter.org</t>
         </is>
       </c>
       <c r="E35" s="39" t="inlineStr">
         <is>
-          <t>Toca viernes y sábado nomás, y las dos noches están tomadas. Queda como la alternativa si prefieren el speakeasy de Harlem antes que el Vanguard: en ese caso el Vanguard vuelve al martes y Juan va solo.</t>
+          <t>Las salas grandes están entre temporadas (Filarmónica abre 10/9; Met Opera y Ballet después), pero el David Rubenstein Atrium suele tener shows GRATIS entre semana y Film at Lincoln Center proyecta todo el año. Si aparece algo bueno el jueves o viernes, la plaza ya está en el plan del jueves 20:30 y el cambio es trivial.</t>
         </is>
       </c>
     </row>
@@ -39395,20 +39395,89 @@
       <c r="A36" s="41" t="inlineStr"/>
       <c r="B36" s="62" t="inlineStr">
         <is>
+          <t>The Vessel — VIERNES 4/9 10:00</t>
+        </is>
+      </c>
+      <c r="C36" s="39" t="inlineStr">
+        <is>
+          <t>2-3 días antes</t>
+        </is>
+      </c>
+      <c r="D36" s="39" t="inlineStr">
+        <is>
+          <t>hudsonyardsnewyork.com</t>
+        </is>
+      </c>
+      <c r="E36" s="39" t="inlineStr">
+        <is>
+          <t>$10 (flex $15). Suele haber en el día, pero el timed ticket de las 10:00 asegura el arranque sin fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="41" t="inlineStr"/>
+      <c r="B37" s="62" t="inlineStr">
+        <is>
+          <t>Estatua de la Libertad — corona o pedestal</t>
+        </is>
+      </c>
+      <c r="C37" s="39" t="inlineStr">
+        <is>
+          <t>YA, y probablemente sea tarde</t>
+        </is>
+      </c>
+      <c r="D37" s="39" t="inlineStr">
+        <is>
+          <t>statuecitycruises.com</t>
+        </is>
+      </c>
+      <c r="E37" s="39" t="inlineStr">
+        <is>
+          <t>La corona se agota meses antes. SOLO por el sitio oficial: ninguna agencia vende corona.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="41" t="inlineStr"/>
+      <c r="B38" s="62" t="inlineStr">
+        <is>
+          <t>Bill's Place — SALIÓ del plan (lo desplazó el Vanguard del viernes)</t>
+        </is>
+      </c>
+      <c r="C38" s="39" t="inlineStr">
+        <is>
+          <t>solo si cambian de idea</t>
+        </is>
+      </c>
+      <c r="D38" s="39" t="inlineStr">
+        <is>
+          <t>billsplaceharlem.com</t>
+        </is>
+      </c>
+      <c r="E38" s="39" t="inlineStr">
+        <is>
+          <t>Toca viernes y sábado nomás, y las dos noches están tomadas. Queda como la alternativa si prefieren el speakeasy de Harlem antes que el Vanguard: en ese caso el Vanguard vuelve al martes y Juan va solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="41" t="inlineStr"/>
+      <c r="B39" s="62" t="inlineStr">
+        <is>
           <t>Village Vanguard — VIERNES 4/9, set de las 22:00 (Patitucci/Potter/Blade), DOS lugares</t>
         </is>
       </c>
-      <c r="C36" s="39" t="inlineStr">
+      <c r="C39" s="39" t="inlineStr">
         <is>
           <t>COMPRADAS 26/8</t>
         </is>
       </c>
-      <c r="D36" s="39" t="inlineStr">
+      <c r="D39" s="39" t="inlineStr">
         <is>
           <t>2 x GA $45 - #18741454 y #18741456</t>
         </is>
       </c>
-      <c r="E36" s="39" t="inlineStr">
+      <c r="E39" s="39" t="inlineStr">
         <is>
           <t>LISTO. A nombre de Juan Pablo Garicoits, $90 en total. Lo que queda del dia: son asientos POR ORDEN DE LLEGADA (el acomodo del 2do set abre 21:30, no 22:00) y hay minimo de una consumicion por cabeza. No sirven comida: cenar antes.</t>
         </is>
@@ -39420,7 +39489,7 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="A5:A37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SÍ,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NYC_2026_Planificador.xlsx
+++ b/NYC_2026_Planificador.xlsx
@@ -38351,7 +38351,7 @@
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="61" t="inlineStr">
         <is>
-          <t>VEREDICTO:  TICKETS INDIVIDUALES. Ningún pase les cierra con este itinerario, y el ahorro real está en el calendario gratuito, no en los pases.</t>
+          <t>VEREDICTO:  TICKETS INDIVIDUALES. Ningún pase les cierra, y ahora está calculado por separado para cada uno: a Juan la mejor ventana posible le hace perder $60 y a Thais $97. El ahorro real de este viaje está en el calendario gratuito, no en los pases.</t>
         </is>
       </c>
     </row>
@@ -38393,7 +38393,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>5.  Thais ya conoce los clásicos y va a hacer bastante menos atracciones pagas. Para ella ningún pase se acerca a amortizar.</t>
+          <t>5.  Thais no está en Nueva York del 31/8 al 2/9 —trabaja en New Jersey— así que sus días útiles NO son consecutivos, que es justo lo que el pase exige. En todo el viaje hace $82 de atracciones que el pase cubra, contra $169 del pase más barato.</t>
         </is>
       </c>
     </row>

--- a/NYC_2026_Planificador.xlsx
+++ b/NYC_2026_Planificador.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Decisiones" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lugares'!$A$4:$V$306</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lugares'!$A$4:$V$308</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1264,123 +1264,133 @@
 (coincide con lo que habíamos propuesto nosotros)</t>
       </text>
     </comment>
-    <comment ref="I265" authorId="0" shapeId="0">
+    <comment ref="I259" authorId="0" shapeId="0">
+      <text>
+        <t>una botella ronda $12-20; probar es gratis</t>
+      </text>
+    </comment>
+    <comment ref="I260" authorId="0" shapeId="0">
+      <text>
+        <t>una botella ronda $12-20; probar es gratis</t>
+      </text>
+    </comment>
+    <comment ref="I267" authorId="0" shapeId="0">
       <text>
         <t>Entrada libre 7-19h. Trolley tours con costo: sab 29/8 y sab 5/9, 13-15h.</t>
       </text>
     </comment>
-    <comment ref="I267" authorId="0" shapeId="0">
+    <comment ref="I269" authorId="0" shapeId="0">
       <text>
         <t>estimado, sin verificar contra la fuente</t>
       </text>
     </comment>
-    <comment ref="I268" authorId="0" shapeId="0">
+    <comment ref="I270" authorId="0" shapeId="0">
       <text>
         <t>$10. GRATIS todos los jueves.</t>
       </text>
     </comment>
-    <comment ref="U268" authorId="0" shapeId="0">
+    <comment ref="U270" authorId="0" shapeId="0">
       <text>
         <t>En la lista de Google figura como: Wave Hill Public Garden &amp; Cultural Center
 (coincide con lo que habíamos propuesto nosotros)</t>
       </text>
     </comment>
-    <comment ref="U285" authorId="0" shapeId="0">
+    <comment ref="U287" authorId="0" shapeId="0">
       <text>
         <t>En la lista de Google figura como: Washington Square Park
 (coincide con lo que habíamos propuesto nosotros)</t>
       </text>
     </comment>
-    <comment ref="U286" authorId="0" shapeId="0">
+    <comment ref="U288" authorId="0" shapeId="0">
       <text>
         <t>En la lista de Google figura como: High Line
 (coincide con lo que habíamos propuesto nosotros)</t>
       </text>
     </comment>
-    <comment ref="I287" authorId="0" shapeId="0">
+    <comment ref="I289" authorId="0" shapeId="0">
       <text>
         <t>Grounds pass desde ~$80 segun sesion</t>
       </text>
     </comment>
-    <comment ref="I288" authorId="0" shapeId="0">
+    <comment ref="I290" authorId="0" shapeId="0">
       <text>
         <t>GRATIS, sin reserva</t>
       </text>
     </comment>
-    <comment ref="I289" authorId="0" shapeId="0">
+    <comment ref="I291" authorId="0" shapeId="0">
       <text>
         <t>GRATIS, sin reserva</t>
       </text>
     </comment>
-    <comment ref="I290" authorId="0" shapeId="0">
+    <comment ref="I292" authorId="0" shapeId="0">
       <text>
         <t>GRATIS</t>
       </text>
     </comment>
-    <comment ref="I291" authorId="0" shapeId="0">
+    <comment ref="I293" authorId="0" shapeId="0">
       <text>
         <t>precios no publicados aun - VERIFICAR en wiadcacarnival.org</t>
       </text>
     </comment>
-    <comment ref="I294" authorId="0" shapeId="0">
+    <comment ref="I296" authorId="0" shapeId="0">
       <text>
         <t>precio no publicado - consultar green-wood.com</t>
       </text>
     </comment>
-    <comment ref="I295" authorId="0" shapeId="0">
+    <comment ref="I297" authorId="0" shapeId="0">
       <text>
         <t>Promedio real pagado $112. LOTERIA $10 (HamiltonMusical.com, cierra jueves 12h de la semana previa).</t>
       </text>
     </comment>
-    <comment ref="I296" authorId="0" shapeId="0">
+    <comment ref="I298" authorId="0" shapeId="0">
       <text>
         <t>Promedio real pagado $59. LOTERIA $20.64 (Telecharge, cierra 15h del dia previo). Rush $49.</t>
       </text>
     </comment>
-    <comment ref="I297" authorId="0" shapeId="0">
+    <comment ref="I299" authorId="0" shapeId="0">
       <text>
         <t>Loteria LuckySeat $49. Funciones de cierre suelen encarecerse.</t>
       </text>
     </comment>
-    <comment ref="I298" authorId="0" shapeId="0">
+    <comment ref="I300" authorId="0" shapeId="0">
       <text>
         <t>Promedio real $63. Rush $49 en boleteria a las 10h. TKTS ~40% off.</t>
       </text>
     </comment>
-    <comment ref="I299" authorId="0" shapeId="0">
+    <comment ref="I301" authorId="0" shapeId="0">
       <text>
         <t>Loteria digital $40 (Telecharge, sorteos 10h y 15h)</t>
       </text>
     </comment>
-    <comment ref="I300" authorId="0" shapeId="0">
+    <comment ref="I302" authorId="0" shapeId="0">
       <text>
         <t>Desde ~$76-100 segun funcion. Alternativas de play esa semana: Harry Potter and the Cursed Child (Lyric), Paranormal Activity (August Wilson), The Imaginary Invalid (Roundabout).</t>
       </text>
     </comment>
-    <comment ref="I301" authorId="0" shapeId="0">
+    <comment ref="I303" authorId="0" shapeId="0">
       <text>
         <t>Hasta 50% off (tipico 40%) + $8 de fee por ticket. Max 6 por persona.</t>
       </text>
     </comment>
-    <comment ref="U301" authorId="0" shapeId="0">
+    <comment ref="U303" authorId="0" shapeId="0">
       <text>
         <t>En la lista de Google figura como: TKTS Lincoln Center
 (coincide con lo que habíamos propuesto nosotros)</t>
       </text>
     </comment>
-    <comment ref="U303" authorId="0" shapeId="0">
+    <comment ref="U305" authorId="0" shapeId="0">
       <text>
         <t>En la lista de Google figura como: Ink 48 Hotel
 (coincide con lo que habíamos propuesto nosotros)</t>
       </text>
     </comment>
-    <comment ref="U304" authorId="0" shapeId="0">
+    <comment ref="U306" authorId="0" shapeId="0">
       <text>
         <t>En la lista de Google figura como: Hotel Beacon
 (coincide con lo que habíamos propuesto nosotros)</t>
       </text>
     </comment>
-    <comment ref="U306" authorId="0" shapeId="0">
+    <comment ref="U308" authorId="0" shapeId="0">
       <text>
         <t>En la lista de Google figura como: Residence Inn by Marriott Bridgewater Branchburg
 (coincide con lo que habíamos propuesto nosotros)</t>
@@ -2028,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V306"/>
+  <dimension ref="A1:V308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -27354,7 +27364,7 @@
     <row r="259" ht="46" customHeight="1">
       <c r="A259" s="9" t="inlineStr">
         <is>
-          <t>Hell's Kitchen Flea Market</t>
+          <t>HEATONIST Chelsea Market</t>
         </is>
       </c>
       <c r="B259" s="10" t="inlineStr">
@@ -27369,7 +27379,7 @@
       </c>
       <c r="D259" s="11" t="inlineStr">
         <is>
-          <t>Hell's Kitchen</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="E259" s="11" t="inlineStr">
@@ -27388,10 +27398,10 @@
         <v/>
       </c>
       <c r="I259" s="14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J259" s="15" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="K259" s="13" t="inlineStr">
         <is>
@@ -27400,7 +27410,7 @@
       </c>
       <c r="L259" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>lunes a domingo: 12:00–18:45</t>
         </is>
       </c>
       <c r="M259" s="11" t="inlineStr">
@@ -27420,17 +27430,17 @@
       </c>
       <c r="P259" s="16" t="inlineStr">
         <is>
-          <t>42 St-Port Authority (A,C,E)</t>
+          <t>14 St (A,C,E), 8 Av (L)</t>
         </is>
       </c>
       <c r="Q259" s="16" t="inlineStr">
         <is>
-          <t>Feria de antiguedades al aire libre, sabados y domingos. Vinilos, camaras y cosas que no vas a encontrar en otro lado.</t>
+          <t>La sucursal chica, ADENTRO del Chelsea Market donde ya almuerzan el viernes. Mismo catalogo de mas de 100 salsas y la misma cata, en menos metros y con mas gente.</t>
         </is>
       </c>
       <c r="R259" s="16" t="inlineStr">
         <is>
-          <t>W 39th St entre 9th y 10th Ave</t>
+          <t>75 9th Ave (dentro del Chelsea Market)</t>
         </is>
       </c>
       <c r="S259" s="16" t="inlineStr">
@@ -27453,7 +27463,7 @@
     <row r="260" ht="46" customHeight="1">
       <c r="A260" s="9" t="inlineStr">
         <is>
-          <t>Housing Works Bookstore</t>
+          <t>HEATONIST Williamsburg</t>
         </is>
       </c>
       <c r="B260" s="10" t="inlineStr">
@@ -27468,12 +27478,12 @@
       </c>
       <c r="D260" s="11" t="inlineStr">
         <is>
-          <t>SoHo</t>
+          <t>Williamsburg</t>
         </is>
       </c>
       <c r="E260" s="11" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="F260" s="12" t="n">
@@ -27487,10 +27497,10 @@
         <v/>
       </c>
       <c r="I260" s="14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J260" s="15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K260" s="13" t="inlineStr">
         <is>
@@ -27499,7 +27509,7 @@
       </c>
       <c r="L260" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>lunes a domingo: 12:00–19:00</t>
         </is>
       </c>
       <c r="M260" s="11" t="inlineStr">
@@ -27519,22 +27529,22 @@
       </c>
       <c r="P260" s="16" t="inlineStr">
         <is>
-          <t>Spring St (6)</t>
+          <t>Bedford Av (L)</t>
         </is>
       </c>
       <c r="Q260" s="16" t="inlineStr">
         <is>
-          <t>Librería de dos pisos con café: todo lo donado y toda la ganancia va a personas con VIH sin hogar.</t>
+          <t>La tienda insignia: mas de 100 salsas artesanales para PROBAR en el local, con el lineup completo de Hot Ones — las mismas diez que toman los invitados del programa, en orden de menor a mayor. El local es el grande de los dos.</t>
         </is>
       </c>
       <c r="R260" s="16" t="inlineStr">
         <is>
-          <t>126 Crosby St</t>
-        </is>
-      </c>
-      <c r="S260" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>121 Wythe Ave, Brooklyn</t>
+        </is>
+      </c>
+      <c r="S260" s="17" t="inlineStr">
+        <is>
+          <t>Día 8 · sáb 5/9</t>
         </is>
       </c>
       <c r="T260" s="18" t="inlineStr">
@@ -27542,9 +27552,9 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U260" s="19" t="inlineStr">
-        <is>
-          <t>lista google</t>
+      <c r="U260" s="21" t="inlineStr">
+        <is>
+          <t>otros</t>
         </is>
       </c>
       <c r="V260" s="20" t="inlineStr"/>
@@ -27552,7 +27562,7 @@
     <row r="261" ht="46" customHeight="1">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>Louis Vuitton</t>
+          <t>Hell's Kitchen Flea Market</t>
         </is>
       </c>
       <c r="B261" s="10" t="inlineStr">
@@ -27567,7 +27577,7 @@
       </c>
       <c r="D261" s="11" t="inlineStr">
         <is>
-          <t>Midtown</t>
+          <t>Hell's Kitchen</t>
         </is>
       </c>
       <c r="E261" s="11" t="inlineStr">
@@ -27579,7 +27589,7 @@
         <v>1</v>
       </c>
       <c r="G261" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H261" s="13">
         <f>IF(AND(F261=2,G261=2),"AMBOS",IF(AND(F261=2,G261&lt;2),"solo JP",IF(AND(F261&lt;2,G261=2),"solo Thais","-")))</f>
@@ -27589,11 +27599,11 @@
         <v>0</v>
       </c>
       <c r="J261" s="15" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K261" s="13" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L261" s="16" t="inlineStr">
@@ -27618,17 +27628,17 @@
       </c>
       <c r="P261" s="16" t="inlineStr">
         <is>
-          <t>5 Av/53 St (E,M)</t>
+          <t>42 St-Port Authority (A,C,E)</t>
         </is>
       </c>
       <c r="Q261" s="16" t="inlineStr">
         <is>
-          <t>Flagship de la Quinta. En la lista de Google, presumiblemente para compras.</t>
+          <t>Feria de antiguedades al aire libre, sabados y domingos. Vinilos, camaras y cosas que no vas a encontrar en otro lado.</t>
         </is>
       </c>
       <c r="R261" s="16" t="inlineStr">
         <is>
-          <t>1 E 57th St</t>
+          <t>W 39th St entre 9th y 10th Ave</t>
         </is>
       </c>
       <c r="S261" s="16" t="inlineStr">
@@ -27641,9 +27651,9 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U261" s="19" t="inlineStr">
-        <is>
-          <t>lista google</t>
+      <c r="U261" s="21" t="inlineStr">
+        <is>
+          <t>otros</t>
         </is>
       </c>
       <c r="V261" s="20" t="inlineStr"/>
@@ -27651,7 +27661,7 @@
     <row r="262" ht="46" customHeight="1">
       <c r="A262" s="9" t="inlineStr">
         <is>
-          <t>M&amp;M'S World New York</t>
+          <t>Housing Works Bookstore</t>
         </is>
       </c>
       <c r="B262" s="10" t="inlineStr">
@@ -27666,7 +27676,7 @@
       </c>
       <c r="D262" s="11" t="inlineStr">
         <is>
-          <t>Times Square</t>
+          <t>SoHo</t>
         </is>
       </c>
       <c r="E262" s="11" t="inlineStr">
@@ -27688,11 +27698,11 @@
         <v>0</v>
       </c>
       <c r="J262" s="15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K262" s="13" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L262" s="16" t="inlineStr">
@@ -27717,17 +27727,17 @@
       </c>
       <c r="P262" s="16" t="inlineStr">
         <is>
-          <t>42 St-Times Sq</t>
+          <t>Spring St (6)</t>
         </is>
       </c>
       <c r="Q262" s="16" t="inlineStr">
         <is>
-          <t>Tres pisos de merchandising en Times Square. Es lo que promete, ni más ni menos.</t>
+          <t>Librería de dos pisos con café: todo lo donado y toda la ganancia va a personas con VIH sin hogar.</t>
         </is>
       </c>
       <c r="R262" s="16" t="inlineStr">
         <is>
-          <t>1600 Broadway</t>
+          <t>126 Crosby St</t>
         </is>
       </c>
       <c r="S262" s="16" t="inlineStr">
@@ -27750,7 +27760,7 @@
     <row r="263" ht="46" customHeight="1">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>McNally Jackson Books</t>
+          <t>Louis Vuitton</t>
         </is>
       </c>
       <c r="B263" s="10" t="inlineStr">
@@ -27765,7 +27775,7 @@
       </c>
       <c r="D263" s="11" t="inlineStr">
         <is>
-          <t>SoHo</t>
+          <t>Midtown</t>
         </is>
       </c>
       <c r="E263" s="11" t="inlineStr">
@@ -27777,7 +27787,7 @@
         <v>1</v>
       </c>
       <c r="G263" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H263" s="13">
         <f>IF(AND(F263=2,G263=2),"AMBOS",IF(AND(F263=2,G263&lt;2),"solo JP",IF(AND(F263&lt;2,G263=2),"solo Thais","-")))</f>
@@ -27791,7 +27801,7 @@
       </c>
       <c r="K263" s="13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="L263" s="16" t="inlineStr">
@@ -27816,17 +27826,17 @@
       </c>
       <c r="P263" s="16" t="inlineStr">
         <is>
-          <t>Prince St (N,R,W)</t>
+          <t>5 Av/53 St (E,M)</t>
         </is>
       </c>
       <c r="Q263" s="16" t="inlineStr">
         <is>
-          <t>La libreria independiente que definio el SoHo literario: mesas curadas a mano y una seccion de traduccion que no tiene nadie.</t>
+          <t>Flagship de la Quinta. En la lista de Google, presumiblemente para compras.</t>
         </is>
       </c>
       <c r="R263" s="16" t="inlineStr">
         <is>
-          <t>134 Prince St</t>
+          <t>1 E 57th St</t>
         </is>
       </c>
       <c r="S263" s="16" t="inlineStr">
@@ -27839,9 +27849,9 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U263" s="21" t="inlineStr">
-        <is>
-          <t>otros</t>
+      <c r="U263" s="19" t="inlineStr">
+        <is>
+          <t>lista google</t>
         </is>
       </c>
       <c r="V263" s="20" t="inlineStr"/>
@@ -27849,7 +27859,7 @@
     <row r="264" ht="46" customHeight="1">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>The Mills at Jersey Gardens</t>
+          <t>M&amp;M'S World New York</t>
         </is>
       </c>
       <c r="B264" s="10" t="inlineStr">
@@ -27864,12 +27874,12 @@
       </c>
       <c r="D264" s="11" t="inlineStr">
         <is>
-          <t>Elizabeth</t>
+          <t>Times Square</t>
         </is>
       </c>
       <c r="E264" s="11" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="F264" s="12" t="n">
@@ -27886,11 +27896,11 @@
         <v>0</v>
       </c>
       <c r="J264" s="15" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="K264" s="13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="L264" s="16" t="inlineStr">
@@ -27915,17 +27925,17 @@
       </c>
       <c r="P264" s="16" t="inlineStr">
         <is>
-          <t>NJ Transit bus 40 o shuttle desde EWR</t>
+          <t>42 St-Times Sq</t>
         </is>
       </c>
       <c r="Q264" s="16" t="inlineStr">
         <is>
-          <t>El outlet mas grande de New Jersey, 200+ locales bajo techo y A CINCO MINUTOS DEL AEROPUERTO DE NEWARK, con shuttle propio desde la terminal. En New Jersey la ropa y el calzado NO pagan impuesto a las ventas. Sirve el domingo del vuelo si adelantan la salida, o cualquier dia que Thais este en NJ.</t>
+          <t>Tres pisos de merchandising en Times Square. Es lo que promete, ni más ni menos.</t>
         </is>
       </c>
       <c r="R264" s="16" t="inlineStr">
         <is>
-          <t>651 Kapkowski Rd, Elizabeth, NJ</t>
+          <t>1600 Broadway</t>
         </is>
       </c>
       <c r="S264" s="16" t="inlineStr">
@@ -27938,9 +27948,9 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U264" s="21" t="inlineStr">
-        <is>
-          <t>otros</t>
+      <c r="U264" s="19" t="inlineStr">
+        <is>
+          <t>lista google</t>
         </is>
       </c>
       <c r="V264" s="20" t="inlineStr"/>
@@ -27948,34 +27958,34 @@
     <row r="265" ht="46" customHeight="1">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>Green-Wood Cemetery</t>
+          <t>McNally Jackson Books</t>
         </is>
       </c>
       <c r="B265" s="10" t="inlineStr">
         <is>
-          <t>Cementerio-jardín</t>
+          <t>Tienda con historia</t>
         </is>
       </c>
       <c r="C265" s="11" t="inlineStr">
         <is>
-          <t>Parque</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D265" s="11" t="inlineStr">
         <is>
-          <t>Greenwood Heights</t>
+          <t>SoHo</t>
         </is>
       </c>
       <c r="E265" s="11" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="F265" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G265" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H265" s="13">
         <f>IF(AND(F265=2,G265=2),"AMBOS",IF(AND(F265=2,G265&lt;2),"solo JP",IF(AND(F265&lt;2,G265=2),"solo Thais","-")))</f>
@@ -27985,7 +27995,7 @@
         <v>0</v>
       </c>
       <c r="J265" s="15" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="K265" s="13" t="inlineStr">
         <is>
@@ -28014,17 +28024,17 @@
       </c>
       <c r="P265" s="16" t="inlineStr">
         <is>
-          <t>25 St (R)</t>
+          <t>Prince St (N,R,W)</t>
         </is>
       </c>
       <c r="Q265" s="16" t="inlineStr">
         <is>
-          <t>190 hectareas de cementerio-jardin victoriano de 1838, con la colina mas alta de Brooklyn y vista de Manhattan. Hay guia gratuita en la app Bloomberg Connects. Es un parque enorme donde no hay nadie.</t>
+          <t>La libreria independiente que definio el SoHo literario: mesas curadas a mano y una seccion de traduccion que no tiene nadie.</t>
         </is>
       </c>
       <c r="R265" s="16" t="inlineStr">
         <is>
-          <t>500 25th St, Brooklyn</t>
+          <t>134 Prince St</t>
         </is>
       </c>
       <c r="S265" s="16" t="inlineStr">
@@ -28047,34 +28057,34 @@
     <row r="266" ht="46" customHeight="1">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>Inwood Hill Park</t>
+          <t>The Mills at Jersey Gardens</t>
         </is>
       </c>
       <c r="B266" s="10" t="inlineStr">
         <is>
-          <t>Naturaleza</t>
+          <t>Tienda con historia</t>
         </is>
       </c>
       <c r="C266" s="11" t="inlineStr">
         <is>
-          <t>Parque</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D266" s="11" t="inlineStr">
         <is>
-          <t>Inwood</t>
+          <t>Elizabeth</t>
         </is>
       </c>
       <c r="E266" s="11" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="F266" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G266" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H266" s="13">
         <f>IF(AND(F266=2,G266=2),"AMBOS",IF(AND(F266=2,G266&lt;2),"solo JP",IF(AND(F266&lt;2,G266=2),"solo Thais","-")))</f>
@@ -28084,7 +28094,7 @@
         <v>0</v>
       </c>
       <c r="J266" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K266" s="13" t="inlineStr">
         <is>
@@ -28113,17 +28123,17 @@
       </c>
       <c r="P266" s="16" t="inlineStr">
         <is>
-          <t>Dyckman St o 207 St (A)</t>
+          <t>NJ Transit bus 40 o shuttle desde EWR</t>
         </is>
       </c>
       <c r="Q266" s="16" t="inlineStr">
         <is>
-          <t>El unico bosque primario que queda en Manhattan, con cuevas de roca usadas por los Lenape y vista del Hudson y los Palisades. Cuesta creer que sea la misma isla.</t>
+          <t>El outlet mas grande de New Jersey, 200+ locales bajo techo y A CINCO MINUTOS DEL AEROPUERTO DE NEWARK, con shuttle propio desde la terminal. En New Jersey la ropa y el calzado NO pagan impuesto a las ventas. Sirve el domingo del vuelo si adelantan la salida, o cualquier dia que Thais este en NJ.</t>
         </is>
       </c>
       <c r="R266" s="16" t="inlineStr">
         <is>
-          <t>Inwood Hill Park, Manhattan</t>
+          <t>651 Kapkowski Rd, Elizabeth, NJ</t>
         </is>
       </c>
       <c r="S266" s="16" t="inlineStr">
@@ -28146,12 +28156,12 @@
     <row r="267" ht="46" customHeight="1">
       <c r="A267" s="9" t="inlineStr">
         <is>
-          <t>New York Botanical Garden</t>
+          <t>Green-Wood Cemetery</t>
         </is>
       </c>
       <c r="B267" s="10" t="inlineStr">
         <is>
-          <t>Naturaleza</t>
+          <t>Cementerio-jardín</t>
         </is>
       </c>
       <c r="C267" s="11" t="inlineStr">
@@ -28161,29 +28171,29 @@
       </c>
       <c r="D267" s="11" t="inlineStr">
         <is>
-          <t>Bronx Park</t>
+          <t>Greenwood Heights</t>
         </is>
       </c>
       <c r="E267" s="11" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="F267" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G267" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H267" s="13">
         <f>IF(AND(F267=2,G267=2),"AMBOS",IF(AND(F267=2,G267&lt;2),"solo JP",IF(AND(F267&lt;2,G267=2),"solo Thais","-")))</f>
         <v/>
       </c>
       <c r="I267" s="14" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J267" s="15" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="K267" s="13" t="inlineStr">
         <is>
@@ -28212,17 +28222,17 @@
       </c>
       <c r="P267" s="16" t="inlineStr">
         <is>
-          <t>Metro-North a Botanical Garden, o Bx26</t>
+          <t>25 St (R)</t>
         </is>
       </c>
       <c r="Q267" s="16" t="inlineStr">
         <is>
-          <t>Un bosque original de 20 hectareas que nunca se talo, mas el invernadero victoriano. A diez cuadras de Arthur Avenue.</t>
+          <t>190 hectareas de cementerio-jardin victoriano de 1838, con la colina mas alta de Brooklyn y vista de Manhattan. Hay guia gratuita en la app Bloomberg Connects. Es un parque enorme donde no hay nadie.</t>
         </is>
       </c>
       <c r="R267" s="16" t="inlineStr">
         <is>
-          <t>2900 Southern Blvd, Bronx</t>
+          <t>500 25th St, Brooklyn</t>
         </is>
       </c>
       <c r="S267" s="16" t="inlineStr">
@@ -28245,7 +28255,7 @@
     <row r="268" ht="46" customHeight="1">
       <c r="A268" s="9" t="inlineStr">
         <is>
-          <t>Wave Hill</t>
+          <t>Inwood Hill Park</t>
         </is>
       </c>
       <c r="B268" s="10" t="inlineStr">
@@ -28260,29 +28270,29 @@
       </c>
       <c r="D268" s="11" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>Inwood</t>
         </is>
       </c>
       <c r="E268" s="11" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="F268" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G268" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H268" s="13">
         <f>IF(AND(F268=2,G268=2),"AMBOS",IF(AND(F268=2,G268&lt;2),"solo JP",IF(AND(F268&lt;2,G268=2),"solo Thais","-")))</f>
         <v/>
       </c>
       <c r="I268" s="14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J268" s="15" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K268" s="13" t="inlineStr">
         <is>
@@ -28296,7 +28306,7 @@
       </c>
       <c r="M268" s="11" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N268" s="16" t="inlineStr">
@@ -28311,17 +28321,17 @@
       </c>
       <c r="P268" s="16" t="inlineStr">
         <is>
-          <t>Metro-North a Riverdale + shuttle</t>
+          <t>Dyckman St o 207 St (A)</t>
         </is>
       </c>
       <c r="Q268" s="16" t="inlineStr">
         <is>
-          <t>Jardin botanico sobre un acantilado del Hudson, con los Palisades enfrente. Es el lugar mas tranquilo de los cinco boroughs.</t>
+          <t>El unico bosque primario que queda en Manhattan, con cuevas de roca usadas por los Lenape y vista del Hudson y los Palisades. Cuesta creer que sea la misma isla.</t>
         </is>
       </c>
       <c r="R268" s="16" t="inlineStr">
         <is>
-          <t>4900 Independence Ave, Bronx</t>
+          <t>Inwood Hill Park, Manhattan</t>
         </is>
       </c>
       <c r="S268" s="16" t="inlineStr">
@@ -28334,9 +28344,9 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U268" s="19" t="inlineStr">
-        <is>
-          <t>lista google</t>
+      <c r="U268" s="21" t="inlineStr">
+        <is>
+          <t>otros</t>
         </is>
       </c>
       <c r="V268" s="20" t="inlineStr"/>
@@ -28344,12 +28354,12 @@
     <row r="269" ht="46" customHeight="1">
       <c r="A269" s="9" t="inlineStr">
         <is>
-          <t>Elizabeth Street Garden</t>
+          <t>New York Botanical Garden</t>
         </is>
       </c>
       <c r="B269" s="10" t="inlineStr">
         <is>
-          <t>Parque de esculturas</t>
+          <t>Naturaleza</t>
         </is>
       </c>
       <c r="C269" s="11" t="inlineStr">
@@ -28359,12 +28369,12 @@
       </c>
       <c r="D269" s="11" t="inlineStr">
         <is>
-          <t>Nolita</t>
+          <t>Bronx Park</t>
         </is>
       </c>
       <c r="E269" s="11" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Bronx</t>
         </is>
       </c>
       <c r="F269" s="12" t="n">
@@ -28378,10 +28388,10 @@
         <v/>
       </c>
       <c r="I269" s="14" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J269" s="15" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="K269" s="13" t="inlineStr">
         <is>
@@ -28410,17 +28420,17 @@
       </c>
       <c r="P269" s="16" t="inlineStr">
         <is>
-          <t>Spring St (6)</t>
+          <t>Metro-North a Botanical Garden, o Bx26</t>
         </is>
       </c>
       <c r="Q269" s="16" t="inlineStr">
         <is>
-          <t>Jardin de esculturas metido entre edificios, con estatuas victorianas entre los yuyos. Gratis y lleno de vecinos, no de turistas.</t>
+          <t>Un bosque original de 20 hectareas que nunca se talo, mas el invernadero victoriano. A diez cuadras de Arthur Avenue.</t>
         </is>
       </c>
       <c r="R269" s="16" t="inlineStr">
         <is>
-          <t>Elizabeth St entre Prince y Spring</t>
+          <t>2900 Southern Blvd, Bronx</t>
         </is>
       </c>
       <c r="S269" s="16" t="inlineStr">
@@ -28443,12 +28453,12 @@
     <row r="270" ht="46" customHeight="1">
       <c r="A270" s="9" t="inlineStr">
         <is>
-          <t>Socrates Sculpture Park</t>
+          <t>Wave Hill</t>
         </is>
       </c>
       <c r="B270" s="10" t="inlineStr">
         <is>
-          <t>Parque de esculturas</t>
+          <t>Naturaleza</t>
         </is>
       </c>
       <c r="C270" s="11" t="inlineStr">
@@ -28458,29 +28468,29 @@
       </c>
       <c r="D270" s="11" t="inlineStr">
         <is>
-          <t>Long Island City</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="E270" s="11" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Bronx</t>
         </is>
       </c>
       <c r="F270" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G270" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H270" s="13">
         <f>IF(AND(F270=2,G270=2),"AMBOS",IF(AND(F270=2,G270&lt;2),"solo JP",IF(AND(F270&lt;2,G270=2),"solo Thais","-")))</f>
         <v/>
       </c>
       <c r="I270" s="14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J270" s="15" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="K270" s="13" t="inlineStr">
         <is>
@@ -28494,7 +28504,7 @@
       </c>
       <c r="M270" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="N270" s="16" t="inlineStr">
@@ -28509,17 +28519,17 @@
       </c>
       <c r="P270" s="16" t="inlineStr">
         <is>
-          <t>Broadway (N,W)</t>
+          <t>Metro-North a Riverdale + shuttle</t>
         </is>
       </c>
       <c r="Q270" s="16" t="inlineStr">
         <is>
-          <t>Ex basural convertido en parque de esculturas sobre el East River. 'Homecoming' de Chakaia Booker (esculturas de neumaticos) hasta abril 2027. A 5 minutos del Noguchi.</t>
+          <t>Jardin botanico sobre un acantilado del Hudson, con los Palisades enfrente. Es el lugar mas tranquilo de los cinco boroughs.</t>
         </is>
       </c>
       <c r="R270" s="16" t="inlineStr">
         <is>
-          <t>32-01 Vernon Blvd, LIC</t>
+          <t>4900 Independence Ave, Bronx</t>
         </is>
       </c>
       <c r="S270" s="16" t="inlineStr">
@@ -28532,9 +28542,9 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U270" s="21" t="inlineStr">
-        <is>
-          <t>otros</t>
+      <c r="U270" s="19" t="inlineStr">
+        <is>
+          <t>lista google</t>
         </is>
       </c>
       <c r="V270" s="20" t="inlineStr"/>
@@ -28542,12 +28552,12 @@
     <row r="271" ht="46" customHeight="1">
       <c r="A271" s="9" t="inlineStr">
         <is>
-          <t>Astoria Park</t>
+          <t>Elizabeth Street Garden</t>
         </is>
       </c>
       <c r="B271" s="10" t="inlineStr">
         <is>
-          <t>Parque urbano</t>
+          <t>Parque de esculturas</t>
         </is>
       </c>
       <c r="C271" s="11" t="inlineStr">
@@ -28557,12 +28567,12 @@
       </c>
       <c r="D271" s="11" t="inlineStr">
         <is>
-          <t>Astoria</t>
+          <t>Nolita</t>
         </is>
       </c>
       <c r="E271" s="11" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="F271" s="12" t="n">
@@ -28579,7 +28589,7 @@
         <v>0</v>
       </c>
       <c r="J271" s="15" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="K271" s="13" t="inlineStr">
         <is>
@@ -28608,17 +28618,17 @@
       </c>
       <c r="P271" s="16" t="inlineStr">
         <is>
-          <t>Astoria Blvd (N,W) + caminata</t>
+          <t>Spring St (6)</t>
         </is>
       </c>
       <c r="Q271" s="16" t="inlineStr">
         <is>
-          <t>Debajo del Hell Gate Bridge, con el Triborough al lado y Manhattan enfrente. Al atardecer es de los mejores lugares de la ciudad y solo hay vecinos corriendo.</t>
+          <t>Jardin de esculturas metido entre edificios, con estatuas victorianas entre los yuyos. Gratis y lleno de vecinos, no de turistas.</t>
         </is>
       </c>
       <c r="R271" s="16" t="inlineStr">
         <is>
-          <t>19th St &amp; 23rd Ave, Astoria</t>
+          <t>Elizabeth St entre Prince y Spring</t>
         </is>
       </c>
       <c r="S271" s="16" t="inlineStr">
@@ -28641,12 +28651,12 @@
     <row r="272" ht="46" customHeight="1">
       <c r="A272" s="9" t="inlineStr">
         <is>
-          <t>Battery Park</t>
+          <t>Socrates Sculpture Park</t>
         </is>
       </c>
       <c r="B272" s="10" t="inlineStr">
         <is>
-          <t>Parque urbano</t>
+          <t>Parque de esculturas</t>
         </is>
       </c>
       <c r="C272" s="11" t="inlineStr">
@@ -28656,19 +28666,19 @@
       </c>
       <c r="D272" s="11" t="inlineStr">
         <is>
-          <t>Financial District</t>
+          <t>Long Island City</t>
         </is>
       </c>
       <c r="E272" s="11" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="F272" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G272" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H272" s="13">
         <f>IF(AND(F272=2,G272=2),"AMBOS",IF(AND(F272=2,G272&lt;2),"solo JP",IF(AND(F272&lt;2,G272=2),"solo Thais","-")))</f>
@@ -28678,11 +28688,11 @@
         <v>0</v>
       </c>
       <c r="J272" s="15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K272" s="13" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L272" s="16" t="inlineStr">
@@ -28707,15 +28717,19 @@
       </c>
       <c r="P272" s="16" t="inlineStr">
         <is>
-          <t>Bowling Green (4,5), South Ferry (1)</t>
+          <t>Broadway (N,W)</t>
         </is>
       </c>
       <c r="Q272" s="16" t="inlineStr">
         <is>
-          <t>La punta sur de la isla: la bahía, la Estatua a lo lejos y el embarcadero del ferry. Gratis.</t>
-        </is>
-      </c>
-      <c r="R272" s="16" t="inlineStr"/>
+          <t>Ex basural convertido en parque de esculturas sobre el East River. 'Homecoming' de Chakaia Booker (esculturas de neumaticos) hasta abril 2027. A 5 minutos del Noguchi.</t>
+        </is>
+      </c>
+      <c r="R272" s="16" t="inlineStr">
+        <is>
+          <t>32-01 Vernon Blvd, LIC</t>
+        </is>
+      </c>
       <c r="S272" s="16" t="inlineStr">
         <is>
           <t>—</t>
@@ -28726,9 +28740,9 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U272" s="19" t="inlineStr">
-        <is>
-          <t>lista google</t>
+      <c r="U272" s="21" t="inlineStr">
+        <is>
+          <t>otros</t>
         </is>
       </c>
       <c r="V272" s="20" t="inlineStr"/>
@@ -28736,7 +28750,7 @@
     <row r="273" ht="46" customHeight="1">
       <c r="A273" s="9" t="inlineStr">
         <is>
-          <t>Brooklyn Bridge Park</t>
+          <t>Astoria Park</t>
         </is>
       </c>
       <c r="B273" s="10" t="inlineStr">
@@ -28751,19 +28765,19 @@
       </c>
       <c r="D273" s="11" t="inlineStr">
         <is>
-          <t>DUMBO / Brooklyn Heights</t>
+          <t>Astoria</t>
         </is>
       </c>
       <c r="E273" s="11" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="F273" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G273" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H273" s="13">
         <f>IF(AND(F273=2,G273=2),"AMBOS",IF(AND(F273=2,G273&lt;2),"solo JP",IF(AND(F273&lt;2,G273=2),"solo Thais","-")))</f>
@@ -28773,11 +28787,11 @@
         <v>0</v>
       </c>
       <c r="J273" s="15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K273" s="13" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L273" s="16" t="inlineStr">
@@ -28802,22 +28816,22 @@
       </c>
       <c r="P273" s="16" t="inlineStr">
         <is>
-          <t>York St (F), High St (A,C)</t>
+          <t>Astoria Blvd (N,W) + caminata</t>
         </is>
       </c>
       <c r="Q273" s="16" t="inlineStr">
         <is>
-          <t>Muelles reconvertidos con el skyline de Lower Manhattan de frente. Woody De Othello, 'Guardian Spirit', en el Pier 1 hasta marzo 2027.</t>
+          <t>Debajo del Hell Gate Bridge, con el Triborough al lado y Manhattan enfrente. Al atardecer es de los mejores lugares de la ciudad y solo hay vecinos corriendo.</t>
         </is>
       </c>
       <c r="R273" s="16" t="inlineStr">
         <is>
-          <t>334 Furman St, Brooklyn</t>
-        </is>
-      </c>
-      <c r="S273" s="17" t="inlineStr">
-        <is>
-          <t>Día 8 · sáb 5/9</t>
+          <t>19th St &amp; 23rd Ave, Astoria</t>
+        </is>
+      </c>
+      <c r="S273" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="T273" s="18" t="inlineStr">
@@ -28830,16 +28844,12 @@
           <t>otros</t>
         </is>
       </c>
-      <c r="V273" s="20" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="V273" s="20" t="inlineStr"/>
     </row>
     <row r="274" ht="46" customHeight="1">
       <c r="A274" s="9" t="inlineStr">
         <is>
-          <t>Bryant Park</t>
+          <t>Battery Park</t>
         </is>
       </c>
       <c r="B274" s="10" t="inlineStr">
@@ -28854,7 +28864,7 @@
       </c>
       <c r="D274" s="11" t="inlineStr">
         <is>
-          <t>Midtown</t>
+          <t>Financial District</t>
         </is>
       </c>
       <c r="E274" s="11" t="inlineStr">
@@ -28863,10 +28873,10 @@
         </is>
       </c>
       <c r="F274" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G274" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H274" s="13">
         <f>IF(AND(F274=2,G274=2),"AMBOS",IF(AND(F274=2,G274&lt;2),"solo JP",IF(AND(F274&lt;2,G274=2),"solo Thais","-")))</f>
@@ -28905,22 +28915,18 @@
       </c>
       <c r="P274" s="16" t="inlineStr">
         <is>
-          <t>5 Av-Bryant Pk (7,B,D,F,M)</t>
+          <t>Bowling Green (4,5), South Ferry (1)</t>
         </is>
       </c>
       <c r="Q274" s="16" t="inlineStr">
         <is>
-          <t>El patio trasero de la Biblioteca Publica. Picnic Performances gratis toda la temporada: sab 29/8 (Accordion Festival), jue 3 y vie 4/9 (Brass Festival).</t>
-        </is>
-      </c>
-      <c r="R274" s="16" t="inlineStr">
-        <is>
-          <t>Bryant Park, New York</t>
-        </is>
-      </c>
-      <c r="S274" s="17" t="inlineStr">
-        <is>
-          <t>Día 3 · lun 31/8</t>
+          <t>La punta sur de la isla: la bahía, la Estatua a lo lejos y el embarcadero del ferry. Gratis.</t>
+        </is>
+      </c>
+      <c r="R274" s="16" t="inlineStr"/>
+      <c r="S274" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="T274" s="18" t="inlineStr">
@@ -28928,21 +28934,17 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U274" s="21" t="inlineStr">
-        <is>
-          <t>otros</t>
-        </is>
-      </c>
-      <c r="V274" s="20" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="U274" s="19" t="inlineStr">
+        <is>
+          <t>lista google</t>
+        </is>
+      </c>
+      <c r="V274" s="20" t="inlineStr"/>
     </row>
     <row r="275" ht="46" customHeight="1">
       <c r="A275" s="9" t="inlineStr">
         <is>
-          <t>Carl Schurz Park</t>
+          <t>Brooklyn Bridge Park</t>
         </is>
       </c>
       <c r="B275" s="10" t="inlineStr">
@@ -28957,19 +28959,19 @@
       </c>
       <c r="D275" s="11" t="inlineStr">
         <is>
-          <t>Upper East Side</t>
+          <t>DUMBO / Brooklyn Heights</t>
         </is>
       </c>
       <c r="E275" s="11" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="F275" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G275" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H275" s="13">
         <f>IF(AND(F275=2,G275=2),"AMBOS",IF(AND(F275=2,G275&lt;2),"solo JP",IF(AND(F275&lt;2,G275=2),"solo Thais","-")))</f>
@@ -28979,11 +28981,11 @@
         <v>0</v>
       </c>
       <c r="J275" s="15" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="K275" s="13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="L275" s="16" t="inlineStr">
@@ -29008,22 +29010,22 @@
       </c>
       <c r="P275" s="16" t="inlineStr">
         <is>
-          <t>86 St (4,5,6) + M86 al este</t>
+          <t>York St (F), High St (A,C)</t>
         </is>
       </c>
       <c r="Q275" s="16" t="inlineStr">
         <is>
-          <t>Promenade sobre el East River con Gracie Mansion adentro, la casa del intendente. Lo usan los vecinos, no los turistas.</t>
+          <t>Muelles reconvertidos con el skyline de Lower Manhattan de frente. Woody De Othello, 'Guardian Spirit', en el Pier 1 hasta marzo 2027.</t>
         </is>
       </c>
       <c r="R275" s="16" t="inlineStr">
         <is>
-          <t>East End Ave y E 86th St</t>
-        </is>
-      </c>
-      <c r="S275" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>334 Furman St, Brooklyn</t>
+        </is>
+      </c>
+      <c r="S275" s="17" t="inlineStr">
+        <is>
+          <t>Día 8 · sáb 5/9</t>
         </is>
       </c>
       <c r="T275" s="18" t="inlineStr">
@@ -29036,12 +29038,16 @@
           <t>otros</t>
         </is>
       </c>
-      <c r="V275" s="20" t="inlineStr"/>
+      <c r="V275" s="20" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="46" customHeight="1">
       <c r="A276" s="9" t="inlineStr">
         <is>
-          <t>Central Park</t>
+          <t>Bryant Park</t>
         </is>
       </c>
       <c r="B276" s="10" t="inlineStr">
@@ -29056,7 +29062,7 @@
       </c>
       <c r="D276" s="11" t="inlineStr">
         <is>
-          <t>Central Park</t>
+          <t>Midtown</t>
         </is>
       </c>
       <c r="E276" s="11" t="inlineStr">
@@ -29068,7 +29074,7 @@
         <v>2</v>
       </c>
       <c r="G276" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H276" s="13">
         <f>IF(AND(F276=2,G276=2),"AMBOS",IF(AND(F276=2,G276&lt;2),"solo JP",IF(AND(F276&lt;2,G276=2),"solo Thais","-")))</f>
@@ -29078,7 +29084,7 @@
         <v>0</v>
       </c>
       <c r="J276" s="15" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="K276" s="13" t="inlineStr">
         <is>
@@ -29107,22 +29113,22 @@
       </c>
       <c r="P276" s="16" t="inlineStr">
         <is>
-          <t>multiples: 72 St (B,C), 59 St-Columbus Circle, 86 St</t>
+          <t>5 Av-Bryant Pk (7,B,D,F,M)</t>
         </is>
       </c>
       <c r="Q276" s="16" t="inlineStr">
         <is>
-          <t>Bethesda Terrace, el Ramble, Bow Bridge, el Reservoir. La mitad norte (arriba de la 96) esta casi vacia y es la mejor. A dos cuadras del hotel The Beacon.</t>
+          <t>El patio trasero de la Biblioteca Publica. Picnic Performances gratis toda la temporada: sab 29/8 (Accordion Festival), jue 3 y vie 4/9 (Brass Festival).</t>
         </is>
       </c>
       <c r="R276" s="16" t="inlineStr">
         <is>
-          <t>Central Park, New York</t>
+          <t>Bryant Park, New York</t>
         </is>
       </c>
       <c r="S276" s="17" t="inlineStr">
         <is>
-          <t>Día 9 · dom 6/9</t>
+          <t>Día 3 · lun 31/8</t>
         </is>
       </c>
       <c r="T276" s="18" t="inlineStr">
@@ -29144,7 +29150,7 @@
     <row r="277" ht="46" customHeight="1">
       <c r="A277" s="9" t="inlineStr">
         <is>
-          <t>Clinton Community Garden</t>
+          <t>Carl Schurz Park</t>
         </is>
       </c>
       <c r="B277" s="10" t="inlineStr">
@@ -29159,7 +29165,7 @@
       </c>
       <c r="D277" s="11" t="inlineStr">
         <is>
-          <t>Hell's Kitchen</t>
+          <t>Upper East Side</t>
         </is>
       </c>
       <c r="E277" s="11" t="inlineStr">
@@ -29181,7 +29187,7 @@
         <v>0</v>
       </c>
       <c r="J277" s="15" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K277" s="13" t="inlineStr">
         <is>
@@ -29210,17 +29216,17 @@
       </c>
       <c r="P277" s="16" t="inlineStr">
         <is>
-          <t>50 St (C,E)</t>
+          <t>86 St (4,5,6) + M86 al este</t>
         </is>
       </c>
       <c r="Q277" s="16" t="inlineStr">
         <is>
-          <t>1978, el barrio estaba lleno de terrenos baldíos y los vecinos ocuparon uno. Cuando la ciudad quiso rematarlo, juntaron US$ 1 el pie cuadrado vendiendo llaves del portón y se lo compraron. Fue el primer jardín comunitario de Nueva York que pasó a ser parque municipal.</t>
+          <t>Promenade sobre el East River con Gracie Mansion adentro, la casa del intendente. Lo usan los vecinos, no los turistas.</t>
         </is>
       </c>
       <c r="R277" s="16" t="inlineStr">
         <is>
-          <t>434 W 48th St</t>
+          <t>East End Ave y E 86th St</t>
         </is>
       </c>
       <c r="S277" s="16" t="inlineStr">
@@ -29243,7 +29249,7 @@
     <row r="278" ht="46" customHeight="1">
       <c r="A278" s="9" t="inlineStr">
         <is>
-          <t>Columbus Park</t>
+          <t>Central Park</t>
         </is>
       </c>
       <c r="B278" s="10" t="inlineStr">
@@ -29258,7 +29264,7 @@
       </c>
       <c r="D278" s="11" t="inlineStr">
         <is>
-          <t>Chinatown</t>
+          <t>Central Park</t>
         </is>
       </c>
       <c r="E278" s="11" t="inlineStr">
@@ -29267,10 +29273,10 @@
         </is>
       </c>
       <c r="F278" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G278" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H278" s="13">
         <f>IF(AND(F278=2,G278=2),"AMBOS",IF(AND(F278=2,G278&lt;2),"solo JP",IF(AND(F278&lt;2,G278=2),"solo Thais","-")))</f>
@@ -29280,11 +29286,11 @@
         <v>0</v>
       </c>
       <c r="J278" s="15" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="K278" s="13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="L278" s="16" t="inlineStr">
@@ -29309,22 +29315,22 @@
       </c>
       <c r="P278" s="16" t="inlineStr">
         <is>
-          <t>Canal St (J,N,Q,R,W,6)</t>
+          <t>multiples: 72 St (B,C), 59 St-Columbus Circle, 86 St</t>
         </is>
       </c>
       <c r="Q278" s="16" t="inlineStr">
         <is>
-          <t>acá estaba Mulberry Bend, el corazón de Five Points — el peor conventillo de la historia de Nueva York, al que Jacob Riis le dedicó un capítulo entero de *How the Other Half Lives* llamándolo "el núcleo podrido de los suburbios de Nueva York".</t>
+          <t>Bethesda Terrace, el Ramble, Bow Bridge, el Reservoir. La mitad norte (arriba de la 96) esta casi vacia y es la mejor. A dos cuadras del hotel The Beacon.</t>
         </is>
       </c>
       <c r="R278" s="16" t="inlineStr">
         <is>
-          <t>Columbus Park, Baxter St</t>
-        </is>
-      </c>
-      <c r="S278" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Central Park, New York</t>
+        </is>
+      </c>
+      <c r="S278" s="17" t="inlineStr">
+        <is>
+          <t>Día 9 · dom 6/9</t>
         </is>
       </c>
       <c r="T278" s="18" t="inlineStr">
@@ -29337,12 +29343,16 @@
           <t>otros</t>
         </is>
       </c>
-      <c r="V278" s="20" t="inlineStr"/>
+      <c r="V278" s="20" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="46" customHeight="1">
       <c r="A279" s="9" t="inlineStr">
         <is>
-          <t>Greenacre Park</t>
+          <t>Clinton Community Garden</t>
         </is>
       </c>
       <c r="B279" s="10" t="inlineStr">
@@ -29357,7 +29367,7 @@
       </c>
       <c r="D279" s="11" t="inlineStr">
         <is>
-          <t>Midtown East</t>
+          <t>Hell's Kitchen</t>
         </is>
       </c>
       <c r="E279" s="11" t="inlineStr">
@@ -29408,17 +29418,17 @@
       </c>
       <c r="P279" s="16" t="inlineStr">
         <is>
-          <t>51 St (6), Lexington Av-53 St (E,M)</t>
+          <t>50 St (C,E)</t>
         </is>
       </c>
       <c r="Q279" s="16" t="inlineStr">
         <is>
-          <t>El hermano escondido de Paley: cascada de 8 metros en un hueco entre edificios. Casi siempre vacio.</t>
+          <t>1978, el barrio estaba lleno de terrenos baldíos y los vecinos ocuparon uno. Cuando la ciudad quiso rematarlo, juntaron US$ 1 el pie cuadrado vendiendo llaves del portón y se lo compraron. Fue el primer jardín comunitario de Nueva York que pasó a ser parque municipal.</t>
         </is>
       </c>
       <c r="R279" s="16" t="inlineStr">
         <is>
-          <t>217 E 51st St</t>
+          <t>434 W 48th St</t>
         </is>
       </c>
       <c r="S279" s="16" t="inlineStr">
@@ -29441,7 +29451,7 @@
     <row r="280" ht="46" customHeight="1">
       <c r="A280" s="9" t="inlineStr">
         <is>
-          <t>Hudson River Park Pier 84</t>
+          <t>Columbus Park</t>
         </is>
       </c>
       <c r="B280" s="10" t="inlineStr">
@@ -29456,7 +29466,7 @@
       </c>
       <c r="D280" s="11" t="inlineStr">
         <is>
-          <t>Hell's Kitchen</t>
+          <t>Chinatown</t>
         </is>
       </c>
       <c r="E280" s="11" t="inlineStr">
@@ -29478,7 +29488,7 @@
         <v>0</v>
       </c>
       <c r="J280" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K280" s="13" t="inlineStr">
         <is>
@@ -29507,17 +29517,17 @@
       </c>
       <c r="P280" s="16" t="inlineStr">
         <is>
-          <t>42 St-Port Authority (A,C,E)</t>
+          <t>Canal St (J,N,Q,R,W,6)</t>
         </is>
       </c>
       <c r="Q280" s="16" t="inlineStr">
         <is>
-          <t>El muelle publico mas grande del rio, con el Intrepid al lado y el atardecer sobre New Jersey de frente.</t>
+          <t>acá estaba Mulberry Bend, el corazón de Five Points — el peor conventillo de la historia de Nueva York, al que Jacob Riis le dedicó un capítulo entero de *How the Other Half Lives* llamándolo "el núcleo podrido de los suburbios de Nueva York".</t>
         </is>
       </c>
       <c r="R280" s="16" t="inlineStr">
         <is>
-          <t>W 44th St y 12th Ave</t>
+          <t>Columbus Park, Baxter St</t>
         </is>
       </c>
       <c r="S280" s="16" t="inlineStr">
@@ -29540,7 +29550,7 @@
     <row r="281" ht="46" customHeight="1">
       <c r="A281" s="9" t="inlineStr">
         <is>
-          <t>Paley Park</t>
+          <t>Greenacre Park</t>
         </is>
       </c>
       <c r="B281" s="10" t="inlineStr">
@@ -29555,7 +29565,7 @@
       </c>
       <c r="D281" s="11" t="inlineStr">
         <is>
-          <t>Midtown</t>
+          <t>Midtown East</t>
         </is>
       </c>
       <c r="E281" s="11" t="inlineStr">
@@ -29606,17 +29616,17 @@
       </c>
       <c r="P281" s="16" t="inlineStr">
         <is>
-          <t>5 Av-53 St (E,M)</t>
+          <t>51 St (6), Lexington Av-53 St (E,M)</t>
         </is>
       </c>
       <c r="Q281" s="16" t="inlineStr">
         <is>
-          <t>Pocket park de 1967 con una cascada que tapa el ruido de la calle. El mejor invento urbano de Nueva York y entra en media cuadra.</t>
+          <t>El hermano escondido de Paley: cascada de 8 metros en un hueco entre edificios. Casi siempre vacio.</t>
         </is>
       </c>
       <c r="R281" s="16" t="inlineStr">
         <is>
-          <t>3 E 53rd St</t>
+          <t>217 E 51st St</t>
         </is>
       </c>
       <c r="S281" s="16" t="inlineStr">
@@ -29639,7 +29649,7 @@
     <row r="282" ht="46" customHeight="1">
       <c r="A282" s="9" t="inlineStr">
         <is>
-          <t>Prospect Park</t>
+          <t>Hudson River Park Pier 84</t>
         </is>
       </c>
       <c r="B282" s="10" t="inlineStr">
@@ -29654,12 +29664,12 @@
       </c>
       <c r="D282" s="11" t="inlineStr">
         <is>
-          <t>Park Slope</t>
+          <t>Hell's Kitchen</t>
         </is>
       </c>
       <c r="E282" s="11" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="F282" s="12" t="n">
@@ -29676,7 +29686,7 @@
         <v>0</v>
       </c>
       <c r="J282" s="15" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="K282" s="13" t="inlineStr">
         <is>
@@ -29705,15 +29715,19 @@
       </c>
       <c r="P282" s="16" t="inlineStr">
         <is>
-          <t>Grand Army Plaza (2,3)</t>
+          <t>42 St-Port Authority (A,C,E)</t>
         </is>
       </c>
       <c r="Q282" s="16" t="inlineStr">
         <is>
-          <t>El parque que Olmsted y Vaux consideraban SU obra maestra, mejor que Central Park: más bosque y menos turistas.</t>
-        </is>
-      </c>
-      <c r="R282" s="16" t="inlineStr"/>
+          <t>El muelle publico mas grande del rio, con el Intrepid al lado y el atardecer sobre New Jersey de frente.</t>
+        </is>
+      </c>
+      <c r="R282" s="16" t="inlineStr">
+        <is>
+          <t>W 44th St y 12th Ave</t>
+        </is>
+      </c>
       <c r="S282" s="16" t="inlineStr">
         <is>
           <t>—</t>
@@ -29724,9 +29738,9 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U282" s="19" t="inlineStr">
-        <is>
-          <t>lista google</t>
+      <c r="U282" s="21" t="inlineStr">
+        <is>
+          <t>otros</t>
         </is>
       </c>
       <c r="V282" s="20" t="inlineStr"/>
@@ -29734,7 +29748,7 @@
     <row r="283" ht="46" customHeight="1">
       <c r="A283" s="9" t="inlineStr">
         <is>
-          <t>Straus Park</t>
+          <t>Paley Park</t>
         </is>
       </c>
       <c r="B283" s="10" t="inlineStr">
@@ -29749,7 +29763,7 @@
       </c>
       <c r="D283" s="11" t="inlineStr">
         <is>
-          <t>Upper West Side</t>
+          <t>Midtown</t>
         </is>
       </c>
       <c r="E283" s="11" t="inlineStr">
@@ -29800,17 +29814,17 @@
       </c>
       <c r="P283" s="16" t="inlineStr">
         <is>
-          <t>103 St (1)</t>
+          <t>5 Av-53 St (E,M)</t>
         </is>
       </c>
       <c r="Q283" s="16" t="inlineStr">
         <is>
-          <t>Isidor Straus era dueño de Macy's y murió en el Titanic. Su mujer Ida se negó a subir al bote salvavidas y se quedó con él.</t>
+          <t>Pocket park de 1967 con una cascada que tapa el ruido de la calle. El mejor invento urbano de Nueva York y entra en media cuadra.</t>
         </is>
       </c>
       <c r="R283" s="16" t="inlineStr">
         <is>
-          <t>Broadway &amp; W 106th St</t>
+          <t>3 E 53rd St</t>
         </is>
       </c>
       <c r="S283" s="16" t="inlineStr">
@@ -29833,7 +29847,7 @@
     <row r="284" ht="46" customHeight="1">
       <c r="A284" s="9" t="inlineStr">
         <is>
-          <t>Tudor City Greens</t>
+          <t>Prospect Park</t>
         </is>
       </c>
       <c r="B284" s="10" t="inlineStr">
@@ -29848,12 +29862,12 @@
       </c>
       <c r="D284" s="11" t="inlineStr">
         <is>
-          <t>Midtown East</t>
+          <t>Park Slope</t>
         </is>
       </c>
       <c r="E284" s="11" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="F284" s="12" t="n">
@@ -29870,7 +29884,7 @@
         <v>0</v>
       </c>
       <c r="J284" s="15" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="K284" s="13" t="inlineStr">
         <is>
@@ -29899,19 +29913,15 @@
       </c>
       <c r="P284" s="16" t="inlineStr">
         <is>
-          <t>Grand Central-42 St (4,5,6,7,S)</t>
+          <t>Grand Army Plaza (2,3)</t>
         </is>
       </c>
       <c r="Q284" s="16" t="inlineStr">
         <is>
-          <t>dos parques privados abiertos al público arriba de un barranco, con el mirador que da directo sobre la 42 hacia el este — es la postal del puente de la 42 sobre el cañón de la calle.</t>
-        </is>
-      </c>
-      <c r="R284" s="16" t="inlineStr">
-        <is>
-          <t>Tudor City Pl</t>
-        </is>
-      </c>
+          <t>El parque que Olmsted y Vaux consideraban SU obra maestra, mejor que Central Park: más bosque y menos turistas.</t>
+        </is>
+      </c>
+      <c r="R284" s="16" t="inlineStr"/>
       <c r="S284" s="16" t="inlineStr">
         <is>
           <t>—</t>
@@ -29922,9 +29932,9 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U284" s="21" t="inlineStr">
-        <is>
-          <t>otros</t>
+      <c r="U284" s="19" t="inlineStr">
+        <is>
+          <t>lista google</t>
         </is>
       </c>
       <c r="V284" s="20" t="inlineStr"/>
@@ -29932,7 +29942,7 @@
     <row r="285" ht="46" customHeight="1">
       <c r="A285" s="9" t="inlineStr">
         <is>
-          <t>Washington Square Park</t>
+          <t>Straus Park</t>
         </is>
       </c>
       <c r="B285" s="10" t="inlineStr">
@@ -29947,7 +29957,7 @@
       </c>
       <c r="D285" s="11" t="inlineStr">
         <is>
-          <t>Greenwich Village</t>
+          <t>Upper West Side</t>
         </is>
       </c>
       <c r="E285" s="11" t="inlineStr">
@@ -29956,10 +29966,10 @@
         </is>
       </c>
       <c r="F285" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G285" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H285" s="13">
         <f>IF(AND(F285=2,G285=2),"AMBOS",IF(AND(F285=2,G285&lt;2),"solo JP",IF(AND(F285&lt;2,G285=2),"solo Thais","-")))</f>
@@ -29969,11 +29979,11 @@
         <v>0</v>
       </c>
       <c r="J285" s="15" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="K285" s="13" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L285" s="16" t="inlineStr">
@@ -29998,22 +30008,22 @@
       </c>
       <c r="P285" s="16" t="inlineStr">
         <is>
-          <t>W 4 St (A,B,C,D,E,F,M), 8 St-NYU (R,W)</t>
+          <t>103 St (1)</t>
         </is>
       </c>
       <c r="Q285" s="16" t="inlineStr">
         <is>
-          <t>El arco, el piano ambulante, los ajedrecistas y NYU alrededor. Es el mejor lugar de la ciudad para sentarse una hora a mirar gente.</t>
+          <t>Isidor Straus era dueño de Macy's y murió en el Titanic. Su mujer Ida se negó a subir al bote salvavidas y se quedó con él.</t>
         </is>
       </c>
       <c r="R285" s="16" t="inlineStr">
         <is>
-          <t>Washington Square Park</t>
-        </is>
-      </c>
-      <c r="S285" s="17" t="inlineStr">
-        <is>
-          <t>Día 4 · mar 1/9</t>
+          <t>Broadway &amp; W 106th St</t>
+        </is>
+      </c>
+      <c r="S285" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="T285" s="18" t="inlineStr">
@@ -30021,9 +30031,9 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U285" s="19" t="inlineStr">
-        <is>
-          <t>lista google</t>
+      <c r="U285" s="21" t="inlineStr">
+        <is>
+          <t>otros</t>
         </is>
       </c>
       <c r="V285" s="20" t="inlineStr"/>
@@ -30031,12 +30041,12 @@
     <row r="286" ht="46" customHeight="1">
       <c r="A286" s="9" t="inlineStr">
         <is>
-          <t>The High Line</t>
+          <t>Tudor City Greens</t>
         </is>
       </c>
       <c r="B286" s="10" t="inlineStr">
         <is>
-          <t>Paseo elevado</t>
+          <t>Parque urbano</t>
         </is>
       </c>
       <c r="C286" s="11" t="inlineStr">
@@ -30046,7 +30056,7 @@
       </c>
       <c r="D286" s="11" t="inlineStr">
         <is>
-          <t>Chelsea / Meatpacking</t>
+          <t>Midtown East</t>
         </is>
       </c>
       <c r="E286" s="11" t="inlineStr">
@@ -30055,10 +30065,10 @@
         </is>
       </c>
       <c r="F286" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G286" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H286" s="13">
         <f>IF(AND(F286=2,G286=2),"AMBOS",IF(AND(F286=2,G286&lt;2),"solo JP",IF(AND(F286&lt;2,G286=2),"solo Thais","-")))</f>
@@ -30068,11 +30078,11 @@
         <v>0</v>
       </c>
       <c r="J286" s="15" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="K286" s="13" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L286" s="16" t="inlineStr">
@@ -30097,22 +30107,22 @@
       </c>
       <c r="P286" s="16" t="inlineStr">
         <is>
-          <t>14 St (A,C,E), 34 St-Hudson Yards (7)</t>
+          <t>Grand Central-42 St (4,5,6,7,S)</t>
         </is>
       </c>
       <c r="Q286" s="16" t="inlineStr">
         <is>
-          <t>Via ferroviaria elevada convertida en parque lineal de 2,3 km. Recorrer de sur a norte por la luz. Incluye 'The Light That Shines Through the Universe' de Tuan Andrew Nguyen, un Buda de arenisca de 9 metros.</t>
+          <t>dos parques privados abiertos al público arriba de un barranco, con el mirador que da directo sobre la 42 hacia el este — es la postal del puente de la 42 sobre el cañón de la calle.</t>
         </is>
       </c>
       <c r="R286" s="16" t="inlineStr">
         <is>
-          <t>High Line, Gansevoort St a W 34th St</t>
-        </is>
-      </c>
-      <c r="S286" s="17" t="inlineStr">
-        <is>
-          <t>Día 7 · vie 4/9</t>
+          <t>Tudor City Pl</t>
+        </is>
+      </c>
+      <c r="S286" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="T286" s="18" t="inlineStr">
@@ -30120,224 +30130,224 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U286" s="19" t="inlineStr">
-        <is>
-          <t>lista google</t>
-        </is>
-      </c>
-      <c r="V286" s="20" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="U286" s="21" t="inlineStr">
+        <is>
+          <t>otros</t>
+        </is>
+      </c>
+      <c r="V286" s="20" t="inlineStr"/>
     </row>
     <row r="287" ht="46" customHeight="1">
-      <c r="A287" s="23" t="inlineStr">
-        <is>
-          <t>US Open (primeras rondas)</t>
-        </is>
-      </c>
-      <c r="B287" s="24" t="inlineStr">
-        <is>
-          <t>Deporte</t>
-        </is>
-      </c>
-      <c r="C287" s="25" t="inlineStr">
-        <is>
-          <t>Evento</t>
-        </is>
-      </c>
-      <c r="D287" s="25" t="inlineStr">
-        <is>
-          <t>Flushing Meadows</t>
-        </is>
-      </c>
-      <c r="E287" s="25" t="inlineStr">
-        <is>
-          <t>Queens</t>
+      <c r="A287" s="9" t="inlineStr">
+        <is>
+          <t>Washington Square Park</t>
+        </is>
+      </c>
+      <c r="B287" s="10" t="inlineStr">
+        <is>
+          <t>Parque urbano</t>
+        </is>
+      </c>
+      <c r="C287" s="11" t="inlineStr">
+        <is>
+          <t>Parque</t>
+        </is>
+      </c>
+      <c r="D287" s="11" t="inlineStr">
+        <is>
+          <t>Greenwich Village</t>
+        </is>
+      </c>
+      <c r="E287" s="11" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="F287" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G287" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H287" s="26">
+      <c r="H287" s="13">
         <f>IF(AND(F287=2,G287=2),"AMBOS",IF(AND(F287=2,G287&lt;2),"solo JP",IF(AND(F287&lt;2,G287=2),"solo Thais","-")))</f>
         <v/>
       </c>
-      <c r="I287" s="27" t="n">
-        <v>80</v>
-      </c>
-      <c r="J287" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="K287" s="26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L287" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M287" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N287" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O287" s="29" t="inlineStr">
-        <is>
-          <t>Ticketmaster</t>
-        </is>
-      </c>
-      <c r="P287" s="29" t="inlineStr">
-        <is>
-          <t>Mets-Willets Point (7)</t>
-        </is>
-      </c>
-      <c r="Q287" s="29" t="inlineStr">
-        <is>
-          <t>Cuadro principal del 30 de agosto al 13 de septiembre. Las primeras rondas (30 ago - 2 sep) son cuando mas partidos simultaneos hay y el grounds pass rinde mas: se ve a metros en las canchas exteriores. Se come un dia entero.</t>
-        </is>
-      </c>
-      <c r="R287" s="29" t="inlineStr">
-        <is>
-          <t>USTA Billie Jean King NTC, Flushing</t>
-        </is>
-      </c>
-      <c r="S287" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T287" s="30" t="inlineStr">
+      <c r="I287" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J287" s="15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K287" s="13" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="L287" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M287" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N287" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O287" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P287" s="16" t="inlineStr">
+        <is>
+          <t>W 4 St (A,B,C,D,E,F,M), 8 St-NYU (R,W)</t>
+        </is>
+      </c>
+      <c r="Q287" s="16" t="inlineStr">
+        <is>
+          <t>El arco, el piano ambulante, los ajedrecistas y NYU alrededor. Es el mejor lugar de la ciudad para sentarse una hora a mirar gente.</t>
+        </is>
+      </c>
+      <c r="R287" s="16" t="inlineStr">
+        <is>
+          <t>Washington Square Park</t>
+        </is>
+      </c>
+      <c r="S287" s="17" t="inlineStr">
+        <is>
+          <t>Día 4 · mar 1/9</t>
+        </is>
+      </c>
+      <c r="T287" s="18" t="inlineStr">
         <is>
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U287" s="31" t="inlineStr">
-        <is>
-          <t>otros</t>
+      <c r="U287" s="19" t="inlineStr">
+        <is>
+          <t>lista google</t>
         </is>
       </c>
       <c r="V287" s="20" t="inlineStr"/>
     </row>
     <row r="288" ht="46" customHeight="1">
-      <c r="A288" s="23" t="inlineStr">
-        <is>
-          <t>Charlie Parker Jazz Festival - East Village</t>
-        </is>
-      </c>
-      <c r="B288" s="24" t="inlineStr">
-        <is>
-          <t>Festival gratis</t>
-        </is>
-      </c>
-      <c r="C288" s="25" t="inlineStr">
-        <is>
-          <t>Evento</t>
-        </is>
-      </c>
-      <c r="D288" s="25" t="inlineStr">
-        <is>
-          <t>East Village</t>
-        </is>
-      </c>
-      <c r="E288" s="25" t="inlineStr">
+      <c r="A288" s="9" t="inlineStr">
+        <is>
+          <t>The High Line</t>
+        </is>
+      </c>
+      <c r="B288" s="10" t="inlineStr">
+        <is>
+          <t>Paseo elevado</t>
+        </is>
+      </c>
+      <c r="C288" s="11" t="inlineStr">
+        <is>
+          <t>Parque</t>
+        </is>
+      </c>
+      <c r="D288" s="11" t="inlineStr">
+        <is>
+          <t>Chelsea / Meatpacking</t>
+        </is>
+      </c>
+      <c r="E288" s="11" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
       <c r="F288" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G288" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H288" s="26">
+        <v>2</v>
+      </c>
+      <c r="H288" s="13">
         <f>IF(AND(F288=2,G288=2),"AMBOS",IF(AND(F288=2,G288&lt;2),"solo JP",IF(AND(F288&lt;2,G288=2),"solo Thais","-")))</f>
         <v/>
       </c>
-      <c r="I288" s="27" t="n">
+      <c r="I288" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J288" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="K288" s="26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L288" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M288" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N288" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O288" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P288" s="29" t="inlineStr">
-        <is>
-          <t>1 Av (L), Astor Pl (6)</t>
-        </is>
-      </c>
-      <c r="Q288" s="29" t="inlineStr">
-        <is>
-          <t>DOMINGO 30 DE AGOSTO, 15-19h. Ravi Coltrane (headliner), Billy Hart Quartet, Kassa Overall, Vanisha Gould. Segundo dia del festival, en el East Village.</t>
-        </is>
-      </c>
-      <c r="R288" s="29" t="inlineStr">
-        <is>
-          <t>Tompkins Square Park</t>
-        </is>
-      </c>
-      <c r="S288" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T288" s="30" t="inlineStr">
+      <c r="J288" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K288" s="13" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="L288" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M288" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N288" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O288" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P288" s="16" t="inlineStr">
+        <is>
+          <t>14 St (A,C,E), 34 St-Hudson Yards (7)</t>
+        </is>
+      </c>
+      <c r="Q288" s="16" t="inlineStr">
+        <is>
+          <t>Via ferroviaria elevada convertida en parque lineal de 2,3 km. Recorrer de sur a norte por la luz. Incluye 'The Light That Shines Through the Universe' de Tuan Andrew Nguyen, un Buda de arenisca de 9 metros.</t>
+        </is>
+      </c>
+      <c r="R288" s="16" t="inlineStr">
+        <is>
+          <t>High Line, Gansevoort St a W 34th St</t>
+        </is>
+      </c>
+      <c r="S288" s="17" t="inlineStr">
+        <is>
+          <t>Día 7 · vie 4/9</t>
+        </is>
+      </c>
+      <c r="T288" s="18" t="inlineStr">
         <is>
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U288" s="31" t="inlineStr">
-        <is>
-          <t>otros</t>
-        </is>
-      </c>
-      <c r="V288" s="20" t="inlineStr"/>
+      <c r="U288" s="19" t="inlineStr">
+        <is>
+          <t>lista google</t>
+        </is>
+      </c>
+      <c r="V288" s="20" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="46" customHeight="1">
       <c r="A289" s="23" t="inlineStr">
         <is>
-          <t>Charlie Parker Jazz Festival - Harlem</t>
+          <t>US Open (primeras rondas)</t>
         </is>
       </c>
       <c r="B289" s="24" t="inlineStr">
         <is>
-          <t>Festival gratis</t>
+          <t>Deporte</t>
         </is>
       </c>
       <c r="C289" s="25" t="inlineStr">
@@ -30347,29 +30357,29 @@
       </c>
       <c r="D289" s="25" t="inlineStr">
         <is>
-          <t>Harlem</t>
+          <t>Flushing Meadows</t>
         </is>
       </c>
       <c r="E289" s="25" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="F289" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G289" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H289" s="26">
         <f>IF(AND(F289=2,G289=2),"AMBOS",IF(AND(F289=2,G289&lt;2),"solo JP",IF(AND(F289&lt;2,G289=2),"solo Thais","-")))</f>
         <v/>
       </c>
       <c r="I289" s="27" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J289" s="28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K289" s="26" t="inlineStr">
         <is>
@@ -30393,27 +30403,27 @@
       </c>
       <c r="O289" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ticketmaster</t>
         </is>
       </c>
       <c r="P289" s="29" t="inlineStr">
         <is>
-          <t>125 St (2,3)</t>
+          <t>Mets-Willets Point (7)</t>
         </is>
       </c>
       <c r="Q289" s="29" t="inlineStr">
         <is>
-          <t>SABADO 29 DE AGOSTO, 14-19h. Joshua Redman (headliner), Nat Adderley Jr., Catherine Russell, Nicole Glover. Gratis, al aire libre, con el mismo nivel artistico que se paga $60-80 en un club. Llevar manta y llegar 1-2 h antes del headliner.</t>
+          <t>Cuadro principal del 30 de agosto al 13 de septiembre. Las primeras rondas (30 ago - 2 sep) son cuando mas partidos simultaneos hay y el grounds pass rinde mas: se ve a metros en las canchas exteriores. Se come un dia entero.</t>
         </is>
       </c>
       <c r="R289" s="29" t="inlineStr">
         <is>
-          <t>Marcus Garvey Park, Harlem</t>
-        </is>
-      </c>
-      <c r="S289" s="17" t="inlineStr">
-        <is>
-          <t>Día 1 · sáb 29/8</t>
+          <t>USTA Billie Jean King NTC, Flushing</t>
+        </is>
+      </c>
+      <c r="S289" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="T289" s="30" t="inlineStr">
@@ -30426,16 +30436,12 @@
           <t>otros</t>
         </is>
       </c>
-      <c r="V289" s="20" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="V289" s="20" t="inlineStr"/>
     </row>
     <row r="290" ht="46" customHeight="1">
       <c r="A290" s="23" t="inlineStr">
         <is>
-          <t>SummerStage: Christian McBride (gratis)</t>
+          <t>Charlie Parker Jazz Festival - East Village</t>
         </is>
       </c>
       <c r="B290" s="24" t="inlineStr">
@@ -30450,7 +30456,7 @@
       </c>
       <c r="D290" s="25" t="inlineStr">
         <is>
-          <t>Central Park</t>
+          <t>East Village</t>
         </is>
       </c>
       <c r="E290" s="25" t="inlineStr">
@@ -30459,7 +30465,7 @@
         </is>
       </c>
       <c r="F290" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G290" s="12" t="n">
         <v>0</v>
@@ -30472,7 +30478,7 @@
         <v>0</v>
       </c>
       <c r="J290" s="28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K290" s="26" t="inlineStr">
         <is>
@@ -30501,22 +30507,22 @@
       </c>
       <c r="P290" s="29" t="inlineStr">
         <is>
-          <t>72 St (B,C)</t>
+          <t>1 Av (L), Astor Pl (6)</t>
         </is>
       </c>
       <c r="Q290" s="29" t="inlineStr">
         <is>
-          <t>MIERCOLES 2 DE SEPTIEMBRE. Christian McBride + SAMARA JOY (Verve 70 aniversario) + Mei Semones &amp; Friends tocando Getz/Gilberto. Puertas 18:00, show 19:00-22:00. Gratis, sin ticket, por orden de llegada: con ese cartel hay que llegar bastante antes de las 18:00.</t>
+          <t>DOMINGO 30 DE AGOSTO, 15-19h. Ravi Coltrane (headliner), Billy Hart Quartet, Kassa Overall, Vanisha Gould. Segundo dia del festival, en el East Village.</t>
         </is>
       </c>
       <c r="R290" s="29" t="inlineStr">
         <is>
-          <t>Rumsey Playfield, Central Park</t>
-        </is>
-      </c>
-      <c r="S290" s="17" t="inlineStr">
-        <is>
-          <t>Día 5 · mié 2/9</t>
+          <t>Tompkins Square Park</t>
+        </is>
+      </c>
+      <c r="S290" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="T290" s="30" t="inlineStr">
@@ -30529,21 +30535,17 @@
           <t>otros</t>
         </is>
       </c>
-      <c r="V290" s="20" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="V290" s="20" t="inlineStr"/>
     </row>
     <row r="291" ht="46" customHeight="1">
       <c r="A291" s="23" t="inlineStr">
         <is>
-          <t>NY Caribbean Carnival Week (Panorama)</t>
+          <t>Charlie Parker Jazz Festival - Harlem</t>
         </is>
       </c>
       <c r="B291" s="24" t="inlineStr">
         <is>
-          <t>Festival pago</t>
+          <t>Festival gratis</t>
         </is>
       </c>
       <c r="C291" s="25" t="inlineStr">
@@ -30553,26 +30555,26 @@
       </c>
       <c r="D291" s="25" t="inlineStr">
         <is>
-          <t>Prospect Heights</t>
+          <t>Harlem</t>
         </is>
       </c>
       <c r="E291" s="25" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="F291" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G291" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H291" s="26">
         <f>IF(AND(F291=2,G291=2),"AMBOS",IF(AND(F291=2,G291&lt;2),"solo JP",IF(AND(F291&lt;2,G291=2),"solo Thais","-")))</f>
         <v/>
       </c>
       <c r="I291" s="27" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J291" s="28" t="n">
         <v>4</v>
@@ -30604,22 +30606,22 @@
       </c>
       <c r="P291" s="29" t="inlineStr">
         <is>
-          <t>Eastern Pkwy-Brooklyn Museum (2,3)</t>
+          <t>125 St (2,3)</t>
         </is>
       </c>
       <c r="Q291" s="29" t="inlineStr">
         <is>
-          <t>Del 3 al 7 de septiembre en el Brooklyn Museum: Blocko Mania (jue 3), Soca Fest (vie 4), Junior Carnival y Panorama (sab 5 / dom 6). El Panorama es la competencia de steel pan mas grande de Norteamerica. Fechas de fuente secundaria: VERIFICAR.</t>
+          <t>SABADO 29 DE AGOSTO, 14-19h. Joshua Redman (headliner), Nat Adderley Jr., Catherine Russell, Nicole Glover. Gratis, al aire libre, con el mismo nivel artistico que se paga $60-80 en un club. Llevar manta y llegar 1-2 h antes del headliner.</t>
         </is>
       </c>
       <c r="R291" s="29" t="inlineStr">
         <is>
-          <t>Brooklyn Museum, 200 Eastern Pkwy</t>
-        </is>
-      </c>
-      <c r="S291" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Marcus Garvey Park, Harlem</t>
+        </is>
+      </c>
+      <c r="S291" s="17" t="inlineStr">
+        <is>
+          <t>Día 1 · sáb 29/8</t>
         </is>
       </c>
       <c r="T291" s="30" t="inlineStr">
@@ -30632,17 +30634,21 @@
           <t>otros</t>
         </is>
       </c>
-      <c r="V291" s="20" t="inlineStr"/>
+      <c r="V291" s="20" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="46" customHeight="1">
       <c r="A292" s="23" t="inlineStr">
         <is>
-          <t>Paint 'N Pour</t>
+          <t>SummerStage: Christian McBride (gratis)</t>
         </is>
       </c>
       <c r="B292" s="24" t="inlineStr">
         <is>
-          <t>Taller y experiencia</t>
+          <t>Festival gratis</t>
         </is>
       </c>
       <c r="C292" s="25" t="inlineStr">
@@ -30652,29 +30658,29 @@
       </c>
       <c r="D292" s="25" t="inlineStr">
         <is>
+          <t>Central Park</t>
+        </is>
+      </c>
+      <c r="E292" s="25" t="inlineStr">
+        <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="E292" s="25" t="inlineStr">
-        <is>
-          <t>Manhattan</t>
-        </is>
-      </c>
       <c r="F292" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G292" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H292" s="26">
         <f>IF(AND(F292=2,G292=2),"AMBOS",IF(AND(F292=2,G292&lt;2),"solo JP",IF(AND(F292&lt;2,G292=2),"solo Thais","-")))</f>
         <v/>
       </c>
       <c r="I292" s="27" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J292" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K292" s="26" t="inlineStr">
         <is>
@@ -30703,18 +30709,22 @@
       </c>
       <c r="P292" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>72 St (B,C)</t>
         </is>
       </c>
       <c r="Q292" s="29" t="inlineStr">
         <is>
-          <t>Taller de pintura con copa de vino. Se reserva por sesión.</t>
-        </is>
-      </c>
-      <c r="R292" s="29" t="inlineStr"/>
-      <c r="S292" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>MIERCOLES 2 DE SEPTIEMBRE. Christian McBride + SAMARA JOY (Verve 70 aniversario) + Mei Semones &amp; Friends tocando Getz/Gilberto. Puertas 18:00, show 19:00-22:00. Gratis, sin ticket, por orden de llegada: con ese cartel hay que llegar bastante antes de las 18:00.</t>
+        </is>
+      </c>
+      <c r="R292" s="29" t="inlineStr">
+        <is>
+          <t>Rumsey Playfield, Central Park</t>
+        </is>
+      </c>
+      <c r="S292" s="17" t="inlineStr">
+        <is>
+          <t>Día 5 · mié 2/9</t>
         </is>
       </c>
       <c r="T292" s="30" t="inlineStr">
@@ -30722,22 +30732,26 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U292" s="32" t="inlineStr">
-        <is>
-          <t>lista google</t>
-        </is>
-      </c>
-      <c r="V292" s="20" t="inlineStr"/>
+      <c r="U292" s="31" t="inlineStr">
+        <is>
+          <t>otros</t>
+        </is>
+      </c>
+      <c r="V292" s="20" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="46" customHeight="1">
       <c r="A293" s="23" t="inlineStr">
         <is>
-          <t>Time To Paint - Painting Studio</t>
+          <t>NY Caribbean Carnival Week (Panorama)</t>
         </is>
       </c>
       <c r="B293" s="24" t="inlineStr">
         <is>
-          <t>Taller y experiencia</t>
+          <t>Festival pago</t>
         </is>
       </c>
       <c r="C293" s="25" t="inlineStr">
@@ -30747,12 +30761,12 @@
       </c>
       <c r="D293" s="25" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Prospect Heights</t>
         </is>
       </c>
       <c r="E293" s="25" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="F293" s="12" t="n">
@@ -30766,10 +30780,10 @@
         <v/>
       </c>
       <c r="I293" s="27" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J293" s="28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K293" s="26" t="inlineStr">
         <is>
@@ -30798,15 +30812,19 @@
       </c>
       <c r="P293" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Eastern Pkwy-Brooklyn Museum (2,3)</t>
         </is>
       </c>
       <c r="Q293" s="29" t="inlineStr">
         <is>
-          <t>Estudio para pintar por sesión, mismo formato que Paint 'N Pour.</t>
-        </is>
-      </c>
-      <c r="R293" s="29" t="inlineStr"/>
+          <t>Del 3 al 7 de septiembre en el Brooklyn Museum: Blocko Mania (jue 3), Soca Fest (vie 4), Junior Carnival y Panorama (sab 5 / dom 6). El Panorama es la competencia de steel pan mas grande de Norteamerica. Fechas de fuente secundaria: VERIFICAR.</t>
+        </is>
+      </c>
+      <c r="R293" s="29" t="inlineStr">
+        <is>
+          <t>Brooklyn Museum, 200 Eastern Pkwy</t>
+        </is>
+      </c>
       <c r="S293" s="29" t="inlineStr">
         <is>
           <t>—</t>
@@ -30817,9 +30835,9 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U293" s="32" t="inlineStr">
-        <is>
-          <t>lista google</t>
+      <c r="U293" s="31" t="inlineStr">
+        <is>
+          <t>otros</t>
         </is>
       </c>
       <c r="V293" s="20" t="inlineStr"/>
@@ -30827,12 +30845,12 @@
     <row r="294" ht="46" customHeight="1">
       <c r="A294" s="23" t="inlineStr">
         <is>
-          <t>Green-Wood Discover Trolley Tour</t>
+          <t>Paint 'N Pour</t>
         </is>
       </c>
       <c r="B294" s="24" t="inlineStr">
         <is>
-          <t>Tour guiado</t>
+          <t>Taller y experiencia</t>
         </is>
       </c>
       <c r="C294" s="25" t="inlineStr">
@@ -30842,26 +30860,26 @@
       </c>
       <c r="D294" s="25" t="inlineStr">
         <is>
-          <t>Greenwood Heights</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E294" s="25" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="F294" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G294" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H294" s="26">
         <f>IF(AND(F294=2,G294=2),"AMBOS",IF(AND(F294=2,G294&lt;2),"solo JP",IF(AND(F294&lt;2,G294=2),"solo Thais","-")))</f>
         <v/>
       </c>
       <c r="I294" s="27" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="J294" s="28" t="n">
         <v>2</v>
@@ -30888,24 +30906,20 @@
       </c>
       <c r="O294" s="29" t="inlineStr">
         <is>
-          <t>reservar</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P294" s="29" t="inlineStr">
         <is>
-          <t>25 St (R)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q294" s="29" t="inlineStr">
         <is>
-          <t>SABADO 29 DE AGOSTO y SABADO 5 DE SEPTIEMBRE, 13-15h. Recorrido en trolley por las 190 hectareas con guia. Es la forma de ver el cementerio entero sin caminar seis horas.</t>
-        </is>
-      </c>
-      <c r="R294" s="29" t="inlineStr">
-        <is>
-          <t>500 25th St, Brooklyn</t>
-        </is>
-      </c>
+          <t>Taller de pintura con copa de vino. Se reserva por sesión.</t>
+        </is>
+      </c>
+      <c r="R294" s="29" t="inlineStr"/>
       <c r="S294" s="29" t="inlineStr">
         <is>
           <t>—</t>
@@ -30916,9 +30930,9 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U294" s="31" t="inlineStr">
-        <is>
-          <t>otros</t>
+      <c r="U294" s="32" t="inlineStr">
+        <is>
+          <t>lista google</t>
         </is>
       </c>
       <c r="V294" s="20" t="inlineStr"/>
@@ -30926,22 +30940,22 @@
     <row r="295" ht="46" customHeight="1">
       <c r="A295" s="23" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Time To Paint - Painting Studio</t>
         </is>
       </c>
       <c r="B295" s="24" t="inlineStr">
         <is>
-          <t>Musical de Broadway</t>
+          <t>Taller y experiencia</t>
         </is>
       </c>
       <c r="C295" s="25" t="inlineStr">
         <is>
-          <t>Teatro</t>
+          <t>Evento</t>
         </is>
       </c>
       <c r="D295" s="25" t="inlineStr">
         <is>
-          <t>Theater District</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E295" s="25" t="inlineStr">
@@ -30950,24 +30964,24 @@
         </is>
       </c>
       <c r="F295" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G295" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H295" s="26">
         <f>IF(AND(F295=2,G295=2),"AMBOS",IF(AND(F295=2,G295&lt;2),"solo JP",IF(AND(F295&lt;2,G295=2),"solo Thais","-")))</f>
         <v/>
       </c>
       <c r="I295" s="27" t="n">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="J295" s="28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K295" s="26" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L295" s="29" t="inlineStr">
@@ -30992,19 +31006,15 @@
       </c>
       <c r="P295" s="29" t="inlineStr">
         <is>
-          <t>50 St (1), 49 St (N,R,W)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q295" s="29" t="inlineStr">
         <is>
-          <t>Sigue siendo el show mas dificil de conseguir barato, pero la loteria de $10 es gratis de intentar y asigna butacas de primera fila. Anotarse todos los dias desde ya.</t>
-        </is>
-      </c>
-      <c r="R295" s="29" t="inlineStr">
-        <is>
-          <t>Richard Rodgers Theatre, 226 W 46th St</t>
-        </is>
-      </c>
+          <t>Estudio para pintar por sesión, mismo formato que Paint 'N Pour.</t>
+        </is>
+      </c>
+      <c r="R295" s="29" t="inlineStr"/>
       <c r="S295" s="29" t="inlineStr">
         <is>
           <t>—</t>
@@ -31015,9 +31025,9 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U295" s="31" t="inlineStr">
-        <is>
-          <t>otros</t>
+      <c r="U295" s="32" t="inlineStr">
+        <is>
+          <t>lista google</t>
         </is>
       </c>
       <c r="V295" s="20" t="inlineStr"/>
@@ -31025,27 +31035,27 @@
     <row r="296" ht="46" customHeight="1">
       <c r="A296" s="23" t="inlineStr">
         <is>
-          <t>Maybe Happy Ending</t>
+          <t>Green-Wood Discover Trolley Tour</t>
         </is>
       </c>
       <c r="B296" s="24" t="inlineStr">
         <is>
-          <t>Musical de Broadway</t>
+          <t>Tour guiado</t>
         </is>
       </c>
       <c r="C296" s="25" t="inlineStr">
         <is>
-          <t>Teatro</t>
+          <t>Evento</t>
         </is>
       </c>
       <c r="D296" s="25" t="inlineStr">
         <is>
-          <t>Theater District</t>
+          <t>Greenwood Heights</t>
         </is>
       </c>
       <c r="E296" s="25" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="F296" s="12" t="n">
@@ -31059,10 +31069,10 @@
         <v/>
       </c>
       <c r="I296" s="27" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="J296" s="28" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K296" s="26" t="inlineStr">
         <is>
@@ -31086,22 +31096,22 @@
       </c>
       <c r="O296" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>reservar</t>
         </is>
       </c>
       <c r="P296" s="29" t="inlineStr">
         <is>
-          <t>49 St (N,R,W)</t>
+          <t>25 St (R)</t>
         </is>
       </c>
       <c r="Q296" s="29" t="inlineStr">
         <is>
-          <t>Musical sobre dos robots obsoletos en Seul. Es la mejor relacion calidad/precio de la cartelera actual y la loteria de $20 es de las mas accesibles.</t>
+          <t>SABADO 29 DE AGOSTO y SABADO 5 DE SEPTIEMBRE, 13-15h. Recorrido en trolley por las 190 hectareas con guia. Es la forma de ver el cementerio entero sin caminar seis horas.</t>
         </is>
       </c>
       <c r="R296" s="29" t="inlineStr">
         <is>
-          <t>Belasco Theatre, 111 W 44th St</t>
+          <t>500 25th St, Brooklyn</t>
         </is>
       </c>
       <c r="S296" s="29" t="inlineStr">
@@ -31124,7 +31134,7 @@
     <row r="297" ht="46" customHeight="1">
       <c r="A297" s="23" t="inlineStr">
         <is>
-          <t>Moulin Rouge! (ULTIMAS FUNCIONES)</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="B297" s="24" t="inlineStr">
@@ -31148,24 +31158,24 @@
         </is>
       </c>
       <c r="F297" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G297" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H297" s="26">
         <f>IF(AND(F297=2,G297=2),"AMBOS",IF(AND(F297=2,G297&lt;2),"solo JP",IF(AND(F297&lt;2,G297=2),"solo Thais","-")))</f>
         <v/>
       </c>
       <c r="I297" s="27" t="n">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="J297" s="28" t="n">
         <v>3</v>
       </c>
       <c r="K297" s="26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="L297" s="29" t="inlineStr">
@@ -31185,22 +31195,22 @@
       </c>
       <c r="O297" s="29" t="inlineStr">
         <is>
-          <t>urgente si lo quieren</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P297" s="29" t="inlineStr">
         <is>
-          <t>42 St-Port Authority (A,C,E)</t>
+          <t>50 St (1), 49 St (N,R,W)</t>
         </is>
       </c>
       <c r="Q297" s="29" t="inlineStr">
         <is>
-          <t>CIERRA EL 30 DE AGOSTO DE 2026 (ya postergo el cierre una vez, de julio a agosto: puede volver a extender). Las dos ultimas funciones caen en el fin de semana de llegada, con demanda y precios en pico. Aaron Tveit protagoniza del 18 al 29 de agosto.</t>
+          <t>Sigue siendo el show mas dificil de conseguir barato, pero la loteria de $10 es gratis de intentar y asigna butacas de primera fila. Anotarse todos los dias desde ya.</t>
         </is>
       </c>
       <c r="R297" s="29" t="inlineStr">
         <is>
-          <t>Al Hirschfeld Theatre, 302 W 45th St</t>
+          <t>Richard Rodgers Theatre, 226 W 46th St</t>
         </is>
       </c>
       <c r="S297" s="29" t="inlineStr">
@@ -31223,7 +31233,7 @@
     <row r="298" ht="46" customHeight="1">
       <c r="A298" s="23" t="inlineStr">
         <is>
-          <t>Operation Mincemeat</t>
+          <t>Maybe Happy Ending</t>
         </is>
       </c>
       <c r="B298" s="24" t="inlineStr">
@@ -31257,7 +31267,7 @@
         <v/>
       </c>
       <c r="I298" s="27" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J298" s="28" t="n">
         <v>2.5</v>
@@ -31294,12 +31304,12 @@
       </c>
       <c r="Q298" s="29" t="inlineStr">
         <is>
-          <t>Comedia musical britanica sobre una operacion de contrainteligencia real de la Segunda Guerra. Cinco actores haciendo ochenta personajes. Muy bien recibida y mas barata que los grandes musicales.</t>
+          <t>Musical sobre dos robots obsoletos en Seul. Es la mejor relacion calidad/precio de la cartelera actual y la loteria de $20 es de las mas accesibles.</t>
         </is>
       </c>
       <c r="R298" s="29" t="inlineStr">
         <is>
-          <t>John Golden Theatre, 252 W 45th St</t>
+          <t>Belasco Theatre, 111 W 44th St</t>
         </is>
       </c>
       <c r="S298" s="29" t="inlineStr">
@@ -31322,12 +31332,12 @@
     <row r="299" ht="46" customHeight="1">
       <c r="A299" s="23" t="inlineStr">
         <is>
-          <t>Little Shop of Horrors (Off-Broadway)</t>
+          <t>Moulin Rouge! (ULTIMAS FUNCIONES)</t>
         </is>
       </c>
       <c r="B299" s="24" t="inlineStr">
         <is>
-          <t>Off-Broadway</t>
+          <t>Musical de Broadway</t>
         </is>
       </c>
       <c r="C299" s="25" t="inlineStr">
@@ -31346,20 +31356,20 @@
         </is>
       </c>
       <c r="F299" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G299" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H299" s="26">
         <f>IF(AND(F299=2,G299=2),"AMBOS",IF(AND(F299=2,G299&lt;2),"solo JP",IF(AND(F299&lt;2,G299=2),"solo Thais","-")))</f>
         <v/>
       </c>
       <c r="I299" s="27" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="J299" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K299" s="26" t="inlineStr">
         <is>
@@ -31383,22 +31393,22 @@
       </c>
       <c r="O299" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>urgente si lo quieren</t>
         </is>
       </c>
       <c r="P299" s="29" t="inlineStr">
         <is>
-          <t>50 St (C,E)</t>
+          <t>42 St-Port Authority (A,C,E)</t>
         </is>
       </c>
       <c r="Q299" s="29" t="inlineStr">
         <is>
-          <t>Sala chica, produccion excelente, y a un cuarto del precio de un musical grande. Off-Broadway hecho bien.</t>
+          <t>CIERRA EL 30 DE AGOSTO DE 2026 (ya postergo el cierre una vez, de julio a agosto: puede volver a extender). Las dos ultimas funciones caen en el fin de semana de llegada, con demanda y precios en pico. Aaron Tveit protagoniza del 18 al 29 de agosto.</t>
         </is>
       </c>
       <c r="R299" s="29" t="inlineStr">
         <is>
-          <t>Westside Theatre, 407 W 43rd St</t>
+          <t>Al Hirschfeld Theatre, 302 W 45th St</t>
         </is>
       </c>
       <c r="S299" s="29" t="inlineStr">
@@ -31421,12 +31431,12 @@
     <row r="300" ht="46" customHeight="1">
       <c r="A300" s="23" t="inlineStr">
         <is>
-          <t>Stranger Things: The First Shadow (play)</t>
+          <t>Operation Mincemeat</t>
         </is>
       </c>
       <c r="B300" s="24" t="inlineStr">
         <is>
-          <t>Play de Broadway</t>
+          <t>Musical de Broadway</t>
         </is>
       </c>
       <c r="C300" s="25" t="inlineStr">
@@ -31436,7 +31446,7 @@
       </c>
       <c r="D300" s="25" t="inlineStr">
         <is>
-          <t>Midtown</t>
+          <t>Theater District</t>
         </is>
       </c>
       <c r="E300" s="25" t="inlineStr">
@@ -31445,24 +31455,24 @@
         </is>
       </c>
       <c r="F300" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G300" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H300" s="26">
         <f>IF(AND(F300=2,G300=2),"AMBOS",IF(AND(F300=2,G300&lt;2),"solo JP",IF(AND(F300&lt;2,G300=2),"solo Thais","-")))</f>
         <v/>
       </c>
       <c r="I300" s="27" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="J300" s="28" t="n">
         <v>2.5</v>
       </c>
       <c r="K300" s="26" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L300" s="29" t="inlineStr">
@@ -31482,27 +31492,27 @@
       </c>
       <c r="O300" s="29" t="inlineStr">
         <is>
-          <t>compra firme esta semana - verificar horario de funcion (19:00/19:30/20:00)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P300" s="29" t="inlineStr">
         <is>
-          <t>Times Sq-42 St</t>
+          <t>49 St (N,R,W)</t>
         </is>
       </c>
       <c r="Q300" s="29" t="inlineStr">
         <is>
-          <t>EL play-espectaculo de Broadway: la precuela de Stranger Things con la maquinaria escenica que gano el Tony. Para quien viene de Mercer Labs, es el mismo musculo llevado al teatro.</t>
+          <t>Comedia musical britanica sobre una operacion de contrainteligencia real de la Segunda Guerra. Cinco actores haciendo ochenta personajes. Muy bien recibida y mas barata que los grandes musicales.</t>
         </is>
       </c>
       <c r="R300" s="29" t="inlineStr">
         <is>
-          <t>Marquis Theatre, 210 W 46th St</t>
-        </is>
-      </c>
-      <c r="S300" s="17" t="inlineStr">
-        <is>
-          <t>Día 8 · sáb 5/9</t>
+          <t>John Golden Theatre, 252 W 45th St</t>
+        </is>
+      </c>
+      <c r="S300" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="T300" s="30" t="inlineStr">
@@ -31520,12 +31530,12 @@
     <row r="301" ht="46" customHeight="1">
       <c r="A301" s="23" t="inlineStr">
         <is>
-          <t>TKTS Lincoln Center</t>
+          <t>Little Shop of Horrors (Off-Broadway)</t>
         </is>
       </c>
       <c r="B301" s="24" t="inlineStr">
         <is>
-          <t>Tickets con descuento</t>
+          <t>Off-Broadway</t>
         </is>
       </c>
       <c r="C301" s="25" t="inlineStr">
@@ -31535,7 +31545,7 @@
       </c>
       <c r="D301" s="25" t="inlineStr">
         <is>
-          <t>Lincoln Square</t>
+          <t>Theater District</t>
         </is>
       </c>
       <c r="E301" s="25" t="inlineStr">
@@ -31554,10 +31564,10 @@
         <v/>
       </c>
       <c r="I301" s="27" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J301" s="28" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="K301" s="26" t="inlineStr">
         <is>
@@ -31566,12 +31576,12 @@
       </c>
       <c r="L301" s="29" t="inlineStr">
         <is>
-          <t>lunes: cerrado · martes a sábado: 11:00–18:00 · domingo: cerrado</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M301" s="25" t="inlineStr">
         <is>
-          <t>lunes y domingos</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N301" s="29" t="inlineStr">
@@ -31586,17 +31596,17 @@
       </c>
       <c r="P301" s="29" t="inlineStr">
         <is>
-          <t>66 St-Lincoln Center (1)</t>
+          <t>50 St (C,E)</t>
         </is>
       </c>
       <c r="Q301" s="29" t="inlineStr">
         <is>
-          <t>Mismo inventario que el booth de Times Square y casi siempre sin cola. Mar-sab 11-18h. Usar la app de TKTS para ver el inventario en tiempo real ANTES de ir. A 10 cuadras del hotel The Beacon.</t>
+          <t>Sala chica, produccion excelente, y a un cuarto del precio de un musical grande. Off-Broadway hecho bien.</t>
         </is>
       </c>
       <c r="R301" s="29" t="inlineStr">
         <is>
-          <t>61 W 62nd St</t>
+          <t>Westside Theatre, 407 W 43rd St</t>
         </is>
       </c>
       <c r="S301" s="29" t="inlineStr">
@@ -31609,201 +31619,205 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U301" s="32" t="inlineStr">
-        <is>
-          <t>lista google</t>
+      <c r="U301" s="31" t="inlineStr">
+        <is>
+          <t>otros</t>
         </is>
       </c>
       <c r="V301" s="20" t="inlineStr"/>
     </row>
     <row r="302" ht="46" customHeight="1">
-      <c r="A302" s="9" t="inlineStr">
-        <is>
-          <t>NYC Ferry DUMBO → Wall St</t>
-        </is>
-      </c>
-      <c r="B302" s="10" t="inlineStr">
-        <is>
-          <t>Ferry y teleférico</t>
-        </is>
-      </c>
-      <c r="C302" s="11" t="inlineStr">
-        <is>
-          <t>Logística</t>
-        </is>
-      </c>
-      <c r="D302" s="11" t="inlineStr">
-        <is>
-          <t>East River</t>
-        </is>
-      </c>
-      <c r="E302" s="11" t="inlineStr">
+      <c r="A302" s="23" t="inlineStr">
+        <is>
+          <t>Stranger Things: The First Shadow (play)</t>
+        </is>
+      </c>
+      <c r="B302" s="24" t="inlineStr">
+        <is>
+          <t>Play de Broadway</t>
+        </is>
+      </c>
+      <c r="C302" s="25" t="inlineStr">
+        <is>
+          <t>Teatro</t>
+        </is>
+      </c>
+      <c r="D302" s="25" t="inlineStr">
+        <is>
+          <t>Midtown</t>
+        </is>
+      </c>
+      <c r="E302" s="25" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
       <c r="F302" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G302" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H302" s="13">
+        <v>2</v>
+      </c>
+      <c r="H302" s="26">
         <f>IF(AND(F302=2,G302=2),"AMBOS",IF(AND(F302=2,G302&lt;2),"solo JP",IF(AND(F302&lt;2,G302=2),"solo Thais","-")))</f>
         <v/>
       </c>
-      <c r="I302" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J302" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K302" s="13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L302" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M302" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N302" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O302" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P302" s="16" t="inlineStr">
-        <is>
-          <t>Pier 1 DUMBO / Pier 11 Wall St</t>
-        </is>
-      </c>
-      <c r="Q302" s="16" t="inlineStr">
-        <is>
-          <t>$4,50 y cruza el East River con el puente de Brooklyn de frente: la vista del crucero turístico por precio de subte.</t>
-        </is>
-      </c>
-      <c r="R302" s="16" t="inlineStr"/>
-      <c r="S302" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T302" s="18" t="inlineStr">
+      <c r="I302" s="27" t="n">
+        <v>90</v>
+      </c>
+      <c r="J302" s="28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K302" s="26" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="L302" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M302" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N302" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O302" s="29" t="inlineStr">
+        <is>
+          <t>compra firme esta semana - verificar horario de funcion (19:00/19:30/20:00)</t>
+        </is>
+      </c>
+      <c r="P302" s="29" t="inlineStr">
+        <is>
+          <t>Times Sq-42 St</t>
+        </is>
+      </c>
+      <c r="Q302" s="29" t="inlineStr">
+        <is>
+          <t>EL play-espectaculo de Broadway: la precuela de Stranger Things con la maquinaria escenica que gano el Tony. Para quien viene de Mercer Labs, es el mismo musculo llevado al teatro.</t>
+        </is>
+      </c>
+      <c r="R302" s="29" t="inlineStr">
+        <is>
+          <t>Marquis Theatre, 210 W 46th St</t>
+        </is>
+      </c>
+      <c r="S302" s="17" t="inlineStr">
+        <is>
+          <t>Día 8 · sáb 5/9</t>
+        </is>
+      </c>
+      <c r="T302" s="30" t="inlineStr">
         <is>
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U302" s="19" t="inlineStr">
-        <is>
-          <t>lista google</t>
+      <c r="U302" s="31" t="inlineStr">
+        <is>
+          <t>otros</t>
         </is>
       </c>
       <c r="V302" s="20" t="inlineStr"/>
     </row>
     <row r="303" ht="46" customHeight="1">
-      <c r="A303" s="9" t="inlineStr">
-        <is>
-          <t>Hotel Ink48 (29-31 ago)</t>
-        </is>
-      </c>
-      <c r="B303" s="10" t="inlineStr">
-        <is>
-          <t>Hotel</t>
-        </is>
-      </c>
-      <c r="C303" s="11" t="inlineStr">
-        <is>
-          <t>Logística</t>
-        </is>
-      </c>
-      <c r="D303" s="11" t="inlineStr">
-        <is>
-          <t>Hell's Kitchen</t>
-        </is>
-      </c>
-      <c r="E303" s="11" t="inlineStr">
+      <c r="A303" s="23" t="inlineStr">
+        <is>
+          <t>TKTS Lincoln Center</t>
+        </is>
+      </c>
+      <c r="B303" s="24" t="inlineStr">
+        <is>
+          <t>Tickets con descuento</t>
+        </is>
+      </c>
+      <c r="C303" s="25" t="inlineStr">
+        <is>
+          <t>Teatro</t>
+        </is>
+      </c>
+      <c r="D303" s="25" t="inlineStr">
+        <is>
+          <t>Lincoln Square</t>
+        </is>
+      </c>
+      <c r="E303" s="25" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
       <c r="F303" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G303" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H303" s="13">
+        <v>0</v>
+      </c>
+      <c r="H303" s="26">
         <f>IF(AND(F303=2,G303=2),"AMBOS",IF(AND(F303=2,G303&lt;2),"solo JP",IF(AND(F303&lt;2,G303=2),"solo Thais","-")))</f>
         <v/>
       </c>
-      <c r="I303" s="14" t="n">
+      <c r="I303" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="J303" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K303" s="13" t="inlineStr">
+      <c r="J303" s="28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K303" s="26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="L303" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M303" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N303" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O303" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P303" s="16" t="inlineStr">
-        <is>
-          <t>50 St (C,E) a ~12 min caminando</t>
-        </is>
-      </c>
-      <c r="Q303" s="16" t="inlineStr">
-        <is>
-          <t>Base 29-31 de agosto. Esta lejos del subte (12 min al este hasta la 8va Av). Cerca: Intrepid, High Line norte, Hudson Yards, Birdland.</t>
-        </is>
-      </c>
-      <c r="R303" s="16" t="inlineStr">
-        <is>
-          <t>653 11th Ave</t>
-        </is>
-      </c>
-      <c r="S303" s="17" t="inlineStr">
-        <is>
-          <t>Día 1 · sáb 29/8, Día 3 · lun 31/8</t>
-        </is>
-      </c>
-      <c r="T303" s="18" t="inlineStr">
+      <c r="L303" s="29" t="inlineStr">
+        <is>
+          <t>lunes: cerrado · martes a sábado: 11:00–18:00 · domingo: cerrado</t>
+        </is>
+      </c>
+      <c r="M303" s="25" t="inlineStr">
+        <is>
+          <t>lunes y domingos</t>
+        </is>
+      </c>
+      <c r="N303" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O303" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P303" s="29" t="inlineStr">
+        <is>
+          <t>66 St-Lincoln Center (1)</t>
+        </is>
+      </c>
+      <c r="Q303" s="29" t="inlineStr">
+        <is>
+          <t>Mismo inventario que el booth de Times Square y casi siempre sin cola. Mar-sab 11-18h. Usar la app de TKTS para ver el inventario en tiempo real ANTES de ir. A 10 cuadras del hotel The Beacon.</t>
+        </is>
+      </c>
+      <c r="R303" s="29" t="inlineStr">
+        <is>
+          <t>61 W 62nd St</t>
+        </is>
+      </c>
+      <c r="S303" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T303" s="30" t="inlineStr">
         <is>
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U303" s="19" t="inlineStr">
+      <c r="U303" s="32" t="inlineStr">
         <is>
           <t>lista google</t>
         </is>
@@ -31813,12 +31827,12 @@
     <row r="304" ht="46" customHeight="1">
       <c r="A304" s="9" t="inlineStr">
         <is>
-          <t>Hotel The Beacon (3-6 sep)</t>
+          <t>NYC Ferry DUMBO → Wall St</t>
         </is>
       </c>
       <c r="B304" s="10" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Ferry y teleférico</t>
         </is>
       </c>
       <c r="C304" s="11" t="inlineStr">
@@ -31828,7 +31842,7 @@
       </c>
       <c r="D304" s="11" t="inlineStr">
         <is>
-          <t>Upper West Side</t>
+          <t>East River</t>
         </is>
       </c>
       <c r="E304" s="11" t="inlineStr">
@@ -31837,20 +31851,20 @@
         </is>
       </c>
       <c r="F304" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G304" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H304" s="13">
         <f>IF(AND(F304=2,G304=2),"AMBOS",IF(AND(F304=2,G304&lt;2),"solo JP",IF(AND(F304&lt;2,G304=2),"solo Thais","-")))</f>
         <v/>
       </c>
       <c r="I304" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J304" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K304" s="13" t="inlineStr">
         <is>
@@ -31879,22 +31893,18 @@
       </c>
       <c r="P304" s="16" t="inlineStr">
         <is>
-          <t>72 St (1,2,3) a 3 cuadras</t>
+          <t>Pier 1 DUMBO / Pier 11 Wall St</t>
         </is>
       </c>
       <c r="Q304" s="16" t="inlineStr">
         <is>
-          <t>Base 3-6 de septiembre. Ubicacion excelente: la 1/2/3 llega a Penn Station en 10 min. Cerca: Central Park, AMNH, TKTS Lincoln Center, Dizzy's.</t>
-        </is>
-      </c>
-      <c r="R304" s="16" t="inlineStr">
-        <is>
-          <t>2130 Broadway</t>
-        </is>
-      </c>
-      <c r="S304" s="17" t="inlineStr">
-        <is>
-          <t>Día 6 · jue 3/9, Día 9 · dom 6/9</t>
+          <t>$4,50 y cruza el East River con el puente de Brooklyn de frente: la vista del crucero turístico por precio de subte.</t>
+        </is>
+      </c>
+      <c r="R304" s="16" t="inlineStr"/>
+      <c r="S304" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="T304" s="18" t="inlineStr">
@@ -31912,7 +31922,7 @@
     <row r="305" ht="46" customHeight="1">
       <c r="A305" s="9" t="inlineStr">
         <is>
-          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
+          <t>Hotel Ink48 (29-31 ago)</t>
         </is>
       </c>
       <c r="B305" s="10" t="inlineStr">
@@ -31927,7 +31937,7 @@
       </c>
       <c r="D305" s="11" t="inlineStr">
         <is>
-          <t>SoHo</t>
+          <t>Hell's Kitchen</t>
         </is>
       </c>
       <c r="E305" s="11" t="inlineStr">
@@ -31939,7 +31949,7 @@
         <v>2</v>
       </c>
       <c r="G305" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H305" s="13">
         <f>IF(AND(F305=2,G305=2),"AMBOS",IF(AND(F305=2,G305&lt;2),"solo JP",IF(AND(F305&lt;2,G305=2),"solo Thais","-")))</f>
@@ -31978,22 +31988,22 @@
       </c>
       <c r="P305" s="16" t="inlineStr">
         <is>
-          <t>Canal St: la del 6/J/Z esta EN la esquina (Lafayette y Canal); N/Q/R/W a 2 cuadras</t>
+          <t>50 St (C,E) a ~12 min caminando</t>
         </is>
       </c>
       <c r="Q305" s="16" t="inlineStr">
         <is>
-          <t>Base de JP lunes y martes a la noche: se acabaron las dos vueltas nocturnas a New Jersey. Recepcion 24 h, CONSIGNA de equipaje y desayuno incluido 7-9 AM. Canal St al lado = 6 directo al MET y Grand Central, A/C al AMNH, y el Village a 15-20 min a pie.</t>
+          <t>Base 29-31 de agosto. Esta lejos del subte (12 min al este hasta la 8va Av). Cerca: Intrepid, High Line norte, Hudson Yards, Birdland.</t>
         </is>
       </c>
       <c r="R305" s="16" t="inlineStr">
         <is>
-          <t>120 Lafayette St, NY 10013</t>
+          <t>653 11th Ave</t>
         </is>
       </c>
       <c r="S305" s="17" t="inlineStr">
         <is>
-          <t>Día 3 · lun 31/8, Día 4 · mar 1/9, Día 5 · mié 2/9</t>
+          <t>Día 1 · sáb 29/8, Día 3 · lun 31/8</t>
         </is>
       </c>
       <c r="T305" s="18" t="inlineStr">
@@ -32001,9 +32011,9 @@
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U305" s="21" t="inlineStr">
-        <is>
-          <t>otros</t>
+      <c r="U305" s="19" t="inlineStr">
+        <is>
+          <t>lista google</t>
         </is>
       </c>
       <c r="V305" s="20" t="inlineStr"/>
@@ -32011,7 +32021,7 @@
     <row r="306" ht="46" customHeight="1">
       <c r="A306" s="9" t="inlineStr">
         <is>
-          <t>Residence Inn Branchburg (Thais 31/8-3/9 · JP solo la noche del 2)</t>
+          <t>Hotel The Beacon (3-6 sep)</t>
         </is>
       </c>
       <c r="B306" s="10" t="inlineStr">
@@ -32026,12 +32036,12 @@
       </c>
       <c r="D306" s="11" t="inlineStr">
         <is>
-          <t>Branchburg</t>
+          <t>Upper West Side</t>
         </is>
       </c>
       <c r="E306" s="11" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="F306" s="12" t="n">
@@ -32077,52 +32087,250 @@
       </c>
       <c r="P306" s="16" t="inlineStr">
         <is>
+          <t>72 St (1,2,3) a 3 cuadras</t>
+        </is>
+      </c>
+      <c r="Q306" s="16" t="inlineStr">
+        <is>
+          <t>Base 3-6 de septiembre. Ubicacion excelente: la 1/2/3 llega a Penn Station en 10 min. Cerca: Central Park, AMNH, TKTS Lincoln Center, Dizzy's.</t>
+        </is>
+      </c>
+      <c r="R306" s="16" t="inlineStr">
+        <is>
+          <t>2130 Broadway</t>
+        </is>
+      </c>
+      <c r="S306" s="17" t="inlineStr">
+        <is>
+          <t>Día 6 · jue 3/9, Día 9 · dom 6/9</t>
+        </is>
+      </c>
+      <c r="T306" s="18" t="inlineStr">
+        <is>
+          <t>Abrir ↗</t>
+        </is>
+      </c>
+      <c r="U306" s="19" t="inlineStr">
+        <is>
+          <t>lista google</t>
+        </is>
+      </c>
+      <c r="V306" s="20" t="inlineStr"/>
+    </row>
+    <row r="307" ht="46" customHeight="1">
+      <c r="A307" s="9" t="inlineStr">
+        <is>
+          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
+        </is>
+      </c>
+      <c r="B307" s="10" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+      <c r="C307" s="11" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D307" s="11" t="inlineStr">
+        <is>
+          <t>SoHo</t>
+        </is>
+      </c>
+      <c r="E307" s="11" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="F307" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G307" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H307" s="13">
+        <f>IF(AND(F307=2,G307=2),"AMBOS",IF(AND(F307=2,G307&lt;2),"solo JP",IF(AND(F307&lt;2,G307=2),"solo Thais","-")))</f>
+        <v/>
+      </c>
+      <c r="I307" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J307" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K307" s="13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L307" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M307" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N307" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O307" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P307" s="16" t="inlineStr">
+        <is>
+          <t>Canal St: la del 6/J/Z esta EN la esquina (Lafayette y Canal); N/Q/R/W a 2 cuadras</t>
+        </is>
+      </c>
+      <c r="Q307" s="16" t="inlineStr">
+        <is>
+          <t>Base de JP lunes y martes a la noche: se acabaron las dos vueltas nocturnas a New Jersey. Recepcion 24 h, CONSIGNA de equipaje y desayuno incluido 7-9 AM. Canal St al lado = 6 directo al MET y Grand Central, A/C al AMNH, y el Village a 15-20 min a pie.</t>
+        </is>
+      </c>
+      <c r="R307" s="16" t="inlineStr">
+        <is>
+          <t>120 Lafayette St, NY 10013</t>
+        </is>
+      </c>
+      <c r="S307" s="17" t="inlineStr">
+        <is>
+          <t>Día 3 · lun 31/8, Día 4 · mar 1/9, Día 5 · mié 2/9</t>
+        </is>
+      </c>
+      <c r="T307" s="18" t="inlineStr">
+        <is>
+          <t>Abrir ↗</t>
+        </is>
+      </c>
+      <c r="U307" s="21" t="inlineStr">
+        <is>
+          <t>otros</t>
+        </is>
+      </c>
+      <c r="V307" s="20" t="inlineStr"/>
+    </row>
+    <row r="308" ht="46" customHeight="1">
+      <c r="A308" s="9" t="inlineStr">
+        <is>
+          <t>Residence Inn Branchburg (Thais 31/8-3/9 · JP solo la noche del 2)</t>
+        </is>
+      </c>
+      <c r="B308" s="10" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+      <c r="C308" s="11" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D308" s="11" t="inlineStr">
+        <is>
+          <t>Branchburg</t>
+        </is>
+      </c>
+      <c r="E308" s="11" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="F308" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G308" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H308" s="13">
+        <f>IF(AND(F308=2,G308=2),"AMBOS",IF(AND(F308=2,G308&lt;2),"solo JP",IF(AND(F308&lt;2,G308=2),"solo Thais","-")))</f>
+        <v/>
+      </c>
+      <c r="I308" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K308" s="13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L308" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M308" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N308" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O308" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P308" s="16" t="inlineStr">
+        <is>
           <t>Estacion Raritan (NJ Transit RVL) a 6,4 km</t>
         </is>
       </c>
-      <c r="Q306" s="16" t="inlineStr">
+      <c r="Q308" s="16" t="inlineStr">
         <is>
           <t>Base en NJ. NO tiene shuttle (confirmado por Marriott). Estacionamiento propio gratis. Para llegar al tren hay que tomar Uber (~$14-20 por tramo a Raritan).</t>
         </is>
       </c>
-      <c r="R306" s="16" t="inlineStr">
+      <c r="R308" s="16" t="inlineStr">
         <is>
           <t>3241 US Highway 22 East, Branchburg NJ</t>
         </is>
       </c>
-      <c r="S306" s="17" t="inlineStr">
+      <c r="S308" s="17" t="inlineStr">
         <is>
           <t>Día 5 · mié 2/9, Día 6 · jue 3/9</t>
         </is>
       </c>
-      <c r="T306" s="18" t="inlineStr">
+      <c r="T308" s="18" t="inlineStr">
         <is>
           <t>Abrir ↗</t>
         </is>
       </c>
-      <c r="U306" s="19" t="inlineStr">
+      <c r="U308" s="19" t="inlineStr">
         <is>
           <t>lista google</t>
         </is>
       </c>
-      <c r="V306" s="20" t="inlineStr"/>
+      <c r="V308" s="20" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:V306"/>
+  <autoFilter ref="A4:V308"/>
   <mergeCells count="2">
     <mergeCell ref="A2:V2"/>
     <mergeCell ref="A1:V1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H306">
+  <conditionalFormatting sqref="H5:H308">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"AMBOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="F5:G306" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Valor inválido" error="Solo 0, 1 o 2" promptTitle="Nivel de interés" prompt="0 = no me interesa · 1 = quizás · 2 = sí quiero" type="list">
+    <dataValidation sqref="F5:G308" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Valor inválido" error="Solo 0, 1 o 2" promptTitle="Nivel de interés" prompt="0 = no me interesa · 1 = quizás · 2 = sí quiero" type="list">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
-    <dataValidation sqref="V5:V306" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escribí SÍ, NO, o dejalo vacío" promptTitle="Imprescindible" prompt="SÍ = tiene que entrar sí o sí. NO = lo descartás a propósito. Vacío = sin decidir." type="list">
+    <dataValidation sqref="V5:V308" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escribí SÍ, NO, o dejalo vacío" promptTitle="Imprescindible" prompt="SÍ = tiene que entrar sí o sí. NO = lo descartás a propósito. Vacío = sin decidir." type="list">
       <formula1>"SÍ,NO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -32429,6 +32637,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T304" r:id="rId300"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T305" r:id="rId301"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T306" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T307" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T308" r:id="rId304"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -35756,7 +35966,7 @@
       </c>
       <c r="E134" s="39" t="inlineStr">
         <is>
-          <t>Almuerzo en Chelsea Market — COMER FUERTE: es la comida grande del día, la cena de hoy es un bocado rápido entre el SUMMIT y el Vanguard. Los Tacos No.1 o Very Fresh Noodles. Ahora hay casi DOS HORAS: sin apuro, y si quedaron galerías de Chelsea sin ver, se vuelve.</t>
+          <t>Almuerzo en Chelsea Market — COMER FUERTE: es la comida grande del día, la cena de hoy es un bocado rápido entre el SUMMIT y el Vanguard. Los Tacos No.1 o Very Fresh Noodles. Ahora hay casi DOS HORAS: sin apuro, y si quedaron galerías de Chelsea sin ver, se vuelve. ★ HEATONIST está ADENTRO de este mismo mercado (12-18:45): más de 100 salsas picantes para probar, con el lineup de Hot Ones. Si el sábado no llegan a la de Williamsburg, esta es la misma cata en menos metros.</t>
         </is>
       </c>
       <c r="F134" s="37" t="inlineStr">
@@ -36245,11 +36455,19 @@
       </c>
       <c r="E154" s="39" t="inlineStr">
         <is>
-          <t>Paseo por Williamsburg: Bedford Ave, disquerías y vintage. OPCIONAL si quieren la panorámica: Westlight (piso 22, sin cover, un trago) — lo bajaron a 'quizás', así que es prescindible. NO comer nada: lo que viene lo merece.</t>
-        </is>
-      </c>
-      <c r="F154" s="37" t="inlineStr"/>
-      <c r="G154" s="40" t="inlineStr"/>
+          <t>Paseo por Williamsburg: Bedford Ave, disquerías y vintage. ★ ACÁ ENTRA HEATONIST (121 Wythe Ave, a una cuadra de Bedford): la tienda insignia de salsas picantes, con más de 100 para probar en el local y el lineup completo de Hot Ones. Abre 12-19 todos los días, así que a esta hora está abierta y les queda de camino al Williamsburg Bridge. OPCIONAL si quieren la panorámica: Westlight (piso 22, sin cover, un trago) — lo bajaron a 'quizás'. NO comer nada: lo que viene lo merece.</t>
+        </is>
+      </c>
+      <c r="F154" s="37" t="inlineStr">
+        <is>
+          <t>HEATONIST Williamsburg</t>
+        </is>
+      </c>
+      <c r="G154" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~20 min a pie (1.2 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H154" s="41" t="inlineStr"/>
       <c r="I154" s="41" t="inlineStr"/>
     </row>
@@ -37064,11 +37282,11 @@
         </is>
       </c>
       <c r="B5" s="48">
-        <f>SUMIF(Lugares!$F$5:$F$306,2,Lugares!$I$5:$I$306)-SUMIFS(Lugares!$I$5:$I$306,Lugares!$F$5:$F$306,2,Lugares!$C$5:$C$306,"Comida")-SUMIFS(Lugares!$I$5:$I$306,Lugares!$F$5:$F$306,2,Lugares!$C$5:$C$306,"Música")</f>
+        <f>SUMIF(Lugares!$F$5:$F$308,2,Lugares!$I$5:$I$308)-SUMIFS(Lugares!$I$5:$I$308,Lugares!$F$5:$F$308,2,Lugares!$C$5:$C$308,"Comida")-SUMIFS(Lugares!$I$5:$I$308,Lugares!$F$5:$F$308,2,Lugares!$C$5:$C$308,"Música")</f>
         <v/>
       </c>
       <c r="C5" s="48">
-        <f>SUMIF(Lugares!$G$5:$G$306,2,Lugares!$I$5:$I$306)-SUMIFS(Lugares!$I$5:$I$306,Lugares!$G$5:$G$306,2,Lugares!$C$5:$C$306,"Comida")-SUMIFS(Lugares!$I$5:$I$306,Lugares!$G$5:$G$306,2,Lugares!$C$5:$C$306,"Música")</f>
+        <f>SUMIF(Lugares!$G$5:$G$308,2,Lugares!$I$5:$I$308)-SUMIFS(Lugares!$I$5:$I$308,Lugares!$G$5:$G$308,2,Lugares!$C$5:$C$308,"Comida")-SUMIFS(Lugares!$I$5:$I$308,Lugares!$G$5:$G$308,2,Lugares!$C$5:$C$308,"Música")</f>
         <v/>
       </c>
       <c r="D5" s="49">

--- a/NYC_2026_Planificador.xlsx
+++ b/NYC_2026_Planificador.xlsx
@@ -5170,7 +5170,7 @@
       </c>
       <c r="S34" s="17" t="inlineStr">
         <is>
-          <t>Día 3 · lun 31/8</t>
+          <t>Día 3 · lun 31/8, Día 5 · mié 2/9</t>
         </is>
       </c>
       <c r="T34" s="18" t="inlineStr">
@@ -5572,9 +5572,9 @@
           <t>1 E 70th St</t>
         </is>
       </c>
-      <c r="S38" s="17" t="inlineStr">
-        <is>
-          <t>Día 5 · mié 2/9</t>
+      <c r="S38" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="T38" s="18" t="inlineStr">
@@ -21115,9 +21115,9 @@
           <t>20 Hudson Yards</t>
         </is>
       </c>
-      <c r="S195" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S195" s="17" t="inlineStr">
+        <is>
+          <t>Día 5 · mié 2/9</t>
         </is>
       </c>
       <c r="T195" s="18" t="inlineStr">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="S198" s="17" t="inlineStr">
         <is>
-          <t>Día 7 · vie 4/9</t>
+          <t>Día 5 · mié 2/9, Día 7 · vie 4/9</t>
         </is>
       </c>
       <c r="T198" s="18" t="inlineStr">
@@ -21913,7 +21913,7 @@
       </c>
       <c r="S203" s="17" t="inlineStr">
         <is>
-          <t>Día 7 · vie 4/9</t>
+          <t>Día 5 · mié 2/9, Día 7 · vie 4/9</t>
         </is>
       </c>
       <c r="T203" s="18" t="inlineStr">
@@ -30320,7 +30320,7 @@
       </c>
       <c r="S288" s="17" t="inlineStr">
         <is>
-          <t>Día 7 · vie 4/9</t>
+          <t>Día 5 · mié 2/9, Día 7 · vie 4/9</t>
         </is>
       </c>
       <c r="T288" s="18" t="inlineStr">
@@ -32201,7 +32201,7 @@
       </c>
       <c r="S307" s="17" t="inlineStr">
         <is>
-          <t>Día 3 · lun 31/8, Día 4 · mar 1/9, Día 5 · mié 2/9</t>
+          <t>Día 3 · lun 31/8, Día 4 · mar 1/9, Día 5 · mié 2/9, Día 6 · jue 3/9</t>
         </is>
       </c>
       <c r="T307" s="18" t="inlineStr">
@@ -32298,9 +32298,9 @@
           <t>3241 US Highway 22 East, Branchburg NJ</t>
         </is>
       </c>
-      <c r="S308" s="17" t="inlineStr">
-        <is>
-          <t>Día 5 · mié 2/9, Día 6 · jue 3/9</t>
+      <c r="S308" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="T308" s="18" t="inlineStr">
@@ -32651,7 +32651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I183"/>
+  <dimension ref="A1:I184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -34764,14 +34764,14 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="33" t="inlineStr">
         <is>
-          <t>DÍA 5 · Miércoles 02/09 · JP solo · Historia Natural, Frick gratis y McBride en Central Park  —  base: JGStay SoHo → New Jersey (la ÚNICA vuelta nocturna)  ·  Solo JP</t>
+          <t>DÍA 5 · Miércoles 02/09 · JP solo · High Line al amanecer, Vessel, Historia Natural, MoMA y McBride en Central Park  —  base: JGStay SoHo (YA NO se vuelve a New Jersey)  ·  Solo JP</t>
         </is>
       </c>
     </row>
     <row r="87" ht="32" customHeight="1">
       <c r="A87" s="34" t="inlineStr">
         <is>
-          <t>Thais trabaja en New Jersey hasta mañana, así que sigue siendo día de JP solo, y se aprovecha para lo que ella marcó 0: el Museo de Historia Natural y el Frick. El miércoles el Frick es pay-what-you-wish de 13:30 a 17:30, así que sale casi nada. Cierra el MET, pero hoy no hace falta: ya se hizo ayer. El teleférico a Roosevelt Island se fue al domingo: lo marcaron 2 los dos, así que corresponde a un día de a dos. ⚠️ OJO CON LA NOCHE: hoy es LA ÚNICA vuelta a New Jersey que quedó en el viaje (para volver mañana con las maletas), y mañana se madruga 5:45. Cenar TEMPRANO y no perder el tren de las 22:48.</t>
+          <t>REARMADO EL 1/9 con dos cambios de Juan. UNO: ya no vuelve a New Jersey — se queda en el JGStay SoHo hasta el jueves y de ahí lleva las maletas a The Beacon. Eso borra la única vuelta nocturna del viaje, o sea que hoy NO hay tren que atrapar: el SummerStage se ve entero y sin mirar el reloj, y mañana se arranca a las 7:30 desde SoHo en vez de a las 5:45 desde Branchburg. DOS: Juan quiere el HIGH LINE A LAS 7 DE LA MAÑANA, cuando abre y está vacío. ⚠️ EL ENGANCHE QUE NO CIERRA SOLO: el Vessel abre a las 10:00, así que entre el final del High Line y el Vessel hay un hueco de una hora larga — se llena con el desayuno en Hudson Yards, que además reemplaza al del hotel (7-9 AM), que hoy se pierde por salir temprano. Y entra el MoMA, que quedó pendiente del lunes: cierra 17:30 y encaja justo antes del SummerStage. CERRADOS hoy: el MET (por eso fue ayer) y el Frick pierde su ventana a voluntad — ver alternativas.</t>
         </is>
       </c>
     </row>
@@ -34779,12 +34779,12 @@
       <c r="A88" s="35" t="n"/>
       <c r="B88" s="36" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="C88" s="37" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D88" s="38" t="inlineStr">
@@ -34794,7 +34794,7 @@
       </c>
       <c r="E88" s="39" t="inlineStr">
         <is>
-          <t>Desayuno incluido en el JGStay y CHECKOUT: el bolso queda en la CONSIGNA — se retira a la tarde, en el hueco libre del día.</t>
+          <t>Salir del JGStay. Subte 1 desde Canal St hasta Christopher St, o A/C/E hasta 14 St (~12 min). Hoy se pierde el desayuno incluido del hotel (7-9 AM): se desayuna a media mañana en Hudson Yards.</t>
         </is>
       </c>
       <c r="F88" s="37" t="inlineStr">
@@ -34806,74 +34806,82 @@
       <c r="H88" s="41" t="inlineStr"/>
       <c r="I88" s="41" t="inlineStr"/>
     </row>
-    <row r="89" ht="16" customHeight="1">
+    <row r="89" ht="30" customHeight="1">
       <c r="A89" s="35" t="n"/>
-      <c r="B89" s="36" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="C89" s="37" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D89" s="38" t="inlineStr">
+      <c r="B89" s="42" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C89" s="43" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="D89" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E89" s="39" t="inlineStr">
-        <is>
-          <t>Subte A o C desde Canal St hasta 81 St-Museum of Natural History (~30 min).</t>
-        </is>
-      </c>
-      <c r="F89" s="37" t="inlineStr"/>
+      <c r="E89" s="45" t="inlineStr">
+        <is>
+          <t>★★ THE HIGH LINE AL AMANECER — abre 7:00 y esta es LA hora: vacío, con el sol bajo entre los edificios y sin las hordas de la tarde. Entrar por Gansevoort St (extremo SUR) y caminar los 2,3 km hacia el norte, sin apuro. Incluye el Buda de arenisca de 9 metros de Tuan Andrew Nguyen.</t>
+        </is>
+      </c>
+      <c r="F89" s="43" t="inlineStr">
+        <is>
+          <t>The High Line</t>
+        </is>
+      </c>
       <c r="G89" s="40" t="inlineStr"/>
       <c r="H89" s="41" t="inlineStr"/>
       <c r="I89" s="41" t="inlineStr"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="35" t="n"/>
-      <c r="B90" s="42" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="C90" s="43" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="D90" s="44" t="inlineStr">
+      <c r="B90" s="36" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="C90" s="37" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="D90" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E90" s="45" t="inlineStr">
-        <is>
-          <t>★ AMERICAN MUSEUM OF NATURAL HISTORY — dinosaurios, la ballena azul y el Gilder Center nuevo de Studio Gang. $37. Thais lo marcó 0: es de hoy.</t>
-        </is>
-      </c>
-      <c r="F90" s="43" t="inlineStr">
-        <is>
-          <t>American Museum of Natural History</t>
-        </is>
-      </c>
-      <c r="G90" s="40" t="inlineStr"/>
+      <c r="E90" s="39" t="inlineStr">
+        <is>
+          <t>Little Island — el parque flotante de Heatherwick sobre 132 macetas de hormigón, a la altura de la calle 13. Abre 6:00, así que a esta hora también está vacío. Media hora y se sigue al norte.</t>
+        </is>
+      </c>
+      <c r="F90" s="37" t="inlineStr">
+        <is>
+          <t>Little Island</t>
+        </is>
+      </c>
+      <c r="G90" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~15 min a pie · 1.1 km · estimado</t>
+        </is>
+      </c>
       <c r="H90" s="41" t="inlineStr"/>
       <c r="I90" s="41" t="inlineStr"/>
     </row>
-    <row r="91" ht="16" customHeight="1">
+    <row r="91" ht="30" customHeight="1">
       <c r="A91" s="35" t="n"/>
       <c r="B91" s="36" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C91" s="37" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D91" s="38" t="inlineStr">
@@ -34883,11 +34891,19 @@
       </c>
       <c r="E91" s="39" t="inlineStr">
         <is>
-          <t>Almuerzo y cruzar Central Park de oeste a este (20 min a pie).</t>
-        </is>
-      </c>
-      <c r="F91" s="37" t="inlineStr"/>
-      <c r="G91" s="40" t="inlineStr"/>
+          <t>Desayuno en Hudson Yards, al pie del Vessel — acá se llena el hueco hasta que abra. The Shops tiene opciones rápidas; si prefieren algo mejor, Mercado Little Spain de José Andrés está en la planta baja.</t>
+        </is>
+      </c>
+      <c r="F91" s="37" t="inlineStr">
+        <is>
+          <t>Hudson Yards</t>
+        </is>
+      </c>
+      <c r="G91" s="40" t="inlineStr">
+        <is>
+          <t>🚇 ~15 min en subte · 2.5 km (a pie 35 min) · estimado</t>
+        </is>
+      </c>
       <c r="H91" s="41" t="inlineStr"/>
       <c r="I91" s="41" t="inlineStr"/>
     </row>
@@ -34895,12 +34911,12 @@
       <c r="A92" s="35" t="n"/>
       <c r="B92" s="42" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C92" s="43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="D92" s="44" t="inlineStr">
@@ -34910,17 +34926,17 @@
       </c>
       <c r="E92" s="45" t="inlineStr">
         <is>
-          <t>★ THE FRICK COLLECTION — pay-what-you-wish los miércoles 13:30-17:30, y ESA VENTANA ES TODA: fuera de ahí son $30. Vermeer, Rembrandt y Bellini colgados como en una casa, porque era una casa. Online el mínimo es $5 y CONVIENE RESERVAR: el cupo en puerta existe pero no está garantizado. Llegar 13:45 como está planeado deja las cuatro horas justas.</t>
+          <t>★ THE VESSEL — abre 10:00 EN PUNTO y conviene ser de los primeros: la escalera infinita de Heatherwick, 154 tramos y 2.500 escalones, $10. Reabierto con redes; hay ascensor cada 15 min. Subir es la única forma de entenderla.</t>
         </is>
       </c>
       <c r="F92" s="43" t="inlineStr">
         <is>
-          <t>The Frick Collection</t>
+          <t>The Vessel</t>
         </is>
       </c>
       <c r="G92" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~25 min a pie (1.6 km) o 🚇 ~15 min · estimado</t>
+          <t>🚶 ~7 min a pie · 0.5 km · estimado</t>
         </is>
       </c>
       <c r="H92" s="41" t="inlineStr"/>
@@ -34930,12 +34946,12 @@
       <c r="A93" s="35" t="n"/>
       <c r="B93" s="36" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="C93" s="37" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="D93" s="38" t="inlineStr">
@@ -34945,55 +34961,55 @@
       </c>
       <c r="E93" s="39" t="inlineStr">
         <is>
-          <t>El hueco libre ahora tiene una función: subte 6 desde 68 St hasta Canal St, RETIRAR EL BOLSO de la consigna del JGStay, y 6 de vuelta hasta 68 St (~1h10 el circuito completo). El bolso viaja esta noche a New Jersey. La cena temprana de las 17:45 sigue en pie.</t>
-        </is>
-      </c>
-      <c r="F93" s="37" t="inlineStr">
-        <is>
-          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
-        </is>
-      </c>
+          <t>Subte a Historia Natural: 7 desde 34 St-Hudson Yards hasta Times Sq y 1/2/3 hasta 79 St, o A/C desde 34 St-Penn hasta 81 St (~30 min).</t>
+        </is>
+      </c>
+      <c r="F93" s="37" t="inlineStr"/>
       <c r="G93" s="40" t="inlineStr"/>
       <c r="H93" s="41" t="inlineStr"/>
       <c r="I93" s="41" t="inlineStr"/>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="35" t="n"/>
-      <c r="B94" s="36" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="C94" s="37" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="D94" s="38" t="inlineStr">
+      <c r="B94" s="42" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C94" s="43" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="D94" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E94" s="39" t="inlineStr">
-        <is>
-          <t>Subte 6 al sur. Cena TEMPRANA cerca de Central Park: hoy no hay cena tardía posible, el tren manda.</t>
-        </is>
-      </c>
-      <c r="F94" s="37" t="inlineStr"/>
+      <c r="E94" s="45" t="inlineStr">
+        <is>
+          <t>★ AMERICAN MUSEUM OF NATURAL HISTORY — dinosaurios, la ballena azul y el Gilder Center nuevo de Studio Gang. $37. Abre 10-17:30. Thais lo marcó 0: es de hoy.</t>
+        </is>
+      </c>
+      <c r="F94" s="43" t="inlineStr">
+        <is>
+          <t>American Museum of Natural History</t>
+        </is>
+      </c>
       <c r="G94" s="40" t="inlineStr"/>
       <c r="H94" s="41" t="inlineStr"/>
       <c r="I94" s="41" t="inlineStr"/>
     </row>
-    <row r="95" ht="16" customHeight="1">
+    <row r="95" ht="30" customHeight="1">
       <c r="A95" s="35" t="n"/>
       <c r="B95" s="36" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C95" s="37" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="D95" s="38" t="inlineStr">
@@ -35003,7 +35019,7 @@
       </c>
       <c r="E95" s="39" t="inlineStr">
         <is>
-          <t>Entrar a Rumsey Playfield. Puertas 18:00 y con este cartel se llena: cuanto antes, mejor lugar.</t>
+          <t>Almuerzo en el Upper West Side, saliendo del museo. Amsterdam o Columbus tienen de todo; Gray's Papaya está en Broadway y 72 si quieren el pancho de parado.</t>
         </is>
       </c>
       <c r="F95" s="37" t="inlineStr"/>
@@ -35011,60 +35027,60 @@
       <c r="H95" s="41" t="inlineStr"/>
       <c r="I95" s="41" t="inlineStr"/>
     </row>
-    <row r="96" ht="30" customHeight="1">
+    <row r="96" ht="16" customHeight="1">
       <c r="A96" s="35" t="n"/>
-      <c r="B96" s="42" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C96" s="43" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="D96" s="44" t="inlineStr">
+      <c r="B96" s="36" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C96" s="37" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="D96" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E96" s="45" t="inlineStr">
-        <is>
-          <t>★★ SUMMERSTAGE: Christian McBride + SAMARA JOY + Mei Semones — Verve 70 aniversario y Getz/Gilberto. GRATIS, sin ticket, Rumsey Playfield, 19:00-22:00.</t>
-        </is>
-      </c>
-      <c r="F96" s="43" t="inlineStr">
-        <is>
-          <t>SummerStage: Christian McBride (gratis)</t>
-        </is>
-      </c>
+      <c r="E96" s="39" t="inlineStr">
+        <is>
+          <t>Subte B/C o D desde 81 St hasta 7 Av / 47-50 Sts (~15 min). Caminar al MoMA.</t>
+        </is>
+      </c>
+      <c r="F96" s="37" t="inlineStr"/>
       <c r="G96" s="40" t="inlineStr"/>
       <c r="H96" s="41" t="inlineStr"/>
       <c r="I96" s="41" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="35" t="n"/>
-      <c r="B97" s="36" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C97" s="37" t="inlineStr">
-        <is>
-          <t>22:48</t>
-        </is>
-      </c>
-      <c r="D97" s="38" t="inlineStr">
+      <c r="B97" s="42" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="C97" s="43" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="D97" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E97" s="39" t="inlineStr">
-        <is>
-          <t>Salir del parque por la 72 y subte 1/2/3 hasta 34 St-Penn Station. Son 25-30 min puerta a puerta: llegás a Penn 22:25-22:30, con 18-23 min de colchón.</t>
-        </is>
-      </c>
-      <c r="F97" s="37" t="inlineStr"/>
+      <c r="E97" s="45" t="inlineStr">
+        <is>
+          <t>★ MoMA — QUEDÓ PENDIENTE DEL LUNES y hoy es el día: cierra 17:30, así que entrando 15:40 quedan casi dos horas, que alcanzan para las salas de arriba. Van Gogh, Picasso, Rothko, Warhol. QUÉ HAY AHORA: «Frida and Diego: The Last Dream», que cierra el 12 de septiembre. El cine está incluido en la entrada. $30.</t>
+        </is>
+      </c>
+      <c r="F97" s="43" t="inlineStr">
+        <is>
+          <t>MoMA</t>
+        </is>
+      </c>
       <c r="G97" s="40" t="inlineStr"/>
       <c r="H97" s="41" t="inlineStr"/>
       <c r="I97" s="41" t="inlineStr"/>
@@ -35073,12 +35089,12 @@
       <c r="A98" s="35" t="n"/>
       <c r="B98" s="36" t="inlineStr">
         <is>
-          <t>22:48</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="C98" s="37" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D98" s="38" t="inlineStr">
@@ -35088,7 +35104,7 @@
       </c>
       <c r="E98" s="39" t="inlineStr">
         <is>
-          <t>NJ Transit DIRECTO Penn → Raritan (tren 5197), llega 00:04. $18,50. ⚠️ ES EL TREN CRÍTICO: si lo perdés, la próxima llegada a Raritan es 01:31.</t>
+          <t>Del MoMA a Rumsey Playfield: subte F desde 57 St hasta 63 St-Lexington y caminar, o los 20 minutos a pie por la Quinta y entrando por la 69. Con el cartel de hoy conviene estar temprano.</t>
         </is>
       </c>
       <c r="F98" s="37" t="inlineStr"/>
@@ -35100,10 +35116,14 @@
       <c r="A99" s="35" t="n"/>
       <c r="B99" s="36" t="inlineStr">
         <is>
-          <t>00:15</t>
-        </is>
-      </c>
-      <c r="C99" s="37" t="inlineStr"/>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="C99" s="37" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
       <c r="D99" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -35111,107 +35131,103 @@
       </c>
       <c r="E99" s="39" t="inlineStr">
         <is>
-          <t>Uber Raritan → Residence Inn (pedirlo antes de subir al tren). Mañana: despertador 5:45 para el tren de las 6:55 con las maletas.</t>
-        </is>
-      </c>
-      <c r="F99" s="37" t="inlineStr">
-        <is>
-          <t>Residence Inn Branchburg (Thais 31/8-3/9 · JP solo la noche del 2)</t>
-        </is>
-      </c>
+          <t>Entrar a Rumsey Playfield y buscar lugar. Puertas 18:00 y con este cartel se llena: cuanto antes, mejor lugar. Comer algo acá o de camino — hoy la cena es lo que se consiga.</t>
+        </is>
+      </c>
+      <c r="F99" s="37" t="inlineStr"/>
       <c r="G99" s="40" t="inlineStr"/>
       <c r="H99" s="41" t="inlineStr"/>
       <c r="I99" s="41" t="inlineStr"/>
     </row>
-    <row r="100" ht="32" customHeight="1">
-      <c r="A100" s="46" t="inlineStr">
-        <is>
-          <t>ALTERNATIVA / OJO:  Si el AMNH es demasiado museo dos días seguidos (ayer fueron el MET y The Cloisters), salteálo y usá la mañana para Inwood Hill Park o para caminar el Upper West Side sin plan. El Frick y el SummerStage son los dos anclas del día: uno es casi gratis solo hoy, el otro pasa una sola vez. // ⚠️ LA DECISIÓN DE LA NOCHE, con los horarios ya verificados: el directo de las 21:48 llega a Raritan 23:10 y al hotel ~23:30, o sea UNA HORA MÁS DE SUEÑO antes de un jueves que arranca 5:45 con maletas. Pero para tomarlo hay que salir del SummerStage a las 21:05 — el colchón es de 3 a 8 minutos, no hay margen — y te perdés el final de Christian McBride y Samara Joy, que es el plato fuerte y pasa una sola vez. Mi recomendación: quedate hasta el final y tomá el de las 22:48. La hora de sueño no convierte el jueves en un día fácil, y el show no se repite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="22" customHeight="1">
-      <c r="A102" s="33" t="inlineStr">
-        <is>
-          <t>DÍA 6 · Jueves 03/09 · Traslado + World Trade Center completo + ferry con Thais  —  base: New Jersey → The Beacon  ·  Solo JP</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="32" customHeight="1">
-      <c r="A103" s="34" t="inlineStr">
-        <is>
-          <t>La mañana y la primera tarde son el World Trade Center completo — memorial, museo y One World Observatory en una sola bajada. OJO: One World es EL MIRADOR DE DÍA a propósito — su vista es el puerto y el agua, que de noche es negra; los arcos de atardecer van en Top of the Rock (lunes) y SUMMIT (viernes). THAIS ESTÁ EN NYC CON SU EQUIPO este jueves y SE LIBERA A LAS 16:00: se encuentran por Manhattan y se van juntos al Museum of the Moving Image, que es GRATIS los jueves de 14 a 18 — estaba caído del plan y ustedes lo tienen 2/2: RECUPERADO. El día cierra con check-in, cena y Dizzy's. Siguen afuera MoMA PS1, Astoria y Gantry (no hay hueco), y el Staten Island Ferry pasó a la alternativa nocturna de hoy. ENTRA STONE ST, que era imprescindible y no estaba en ningún día: el almuerzo se corre de Brookfield Place a la calle adoquinada, a 10 minutos del museo y 12 de One World. Se pagan 22 minutos de caminata y quedan 38 para comer — alcanza para un mediodía, aunque su mejor hora sea el after office de 5 a 8 y no la del almuerzo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="30" customHeight="1">
-      <c r="A104" s="35" t="n"/>
-      <c r="B104" s="36" t="inlineStr">
-        <is>
-          <t>06:20</t>
-        </is>
-      </c>
-      <c r="C104" s="37" t="inlineStr">
-        <is>
-          <t>06:55</t>
-        </is>
-      </c>
-      <c r="D104" s="38" t="inlineStr">
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="35" t="n"/>
+      <c r="B100" s="42" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C100" s="43" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="D100" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E104" s="39" t="inlineStr">
-        <is>
-          <t>Uber desde el Residence Inn a la estación Raritan (~20 min, $14-20). PEDIRLO LA NOCHE ANTERIOR: Branchburg es semi-rural y a esa hora puede no haber autos.</t>
-        </is>
-      </c>
-      <c r="F104" s="37" t="inlineStr">
-        <is>
-          <t>Residence Inn Branchburg (Thais 31/8-3/9 · JP solo la noche del 2)</t>
-        </is>
-      </c>
-      <c r="G104" s="40" t="inlineStr"/>
-      <c r="H104" s="41" t="inlineStr"/>
-      <c r="I104" s="41" t="inlineStr"/>
-    </row>
-    <row r="105" ht="30" customHeight="1">
-      <c r="A105" s="35" t="n"/>
-      <c r="B105" s="36" t="inlineStr">
-        <is>
-          <t>06:55</t>
-        </is>
-      </c>
-      <c r="C105" s="37" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="D105" s="38" t="inlineStr">
+      <c r="E100" s="45" t="inlineStr">
+        <is>
+          <t>★★ SUMMERSTAGE: Christian McBride + SAMARA JOY + Mei Semones — Verve 70 aniversario y Getz/Gilberto. GRATIS, sin ticket, Rumsey Playfield, 19:00-22:00. Y AHORA SE VE ENTERO: ya no hay tren a New Jersey que atrapar, que era lo que obligaba a salir corriendo.</t>
+        </is>
+      </c>
+      <c r="F100" s="43" t="inlineStr">
+        <is>
+          <t>SummerStage: Christian McBride (gratis)</t>
+        </is>
+      </c>
+      <c r="G100" s="40" t="inlineStr"/>
+      <c r="H100" s="41" t="inlineStr"/>
+      <c r="I100" s="41" t="inlineStr"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="35" t="n"/>
+      <c r="B101" s="36" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="C101" s="37" t="inlineStr"/>
+      <c r="D101" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E105" s="39" t="inlineStr">
-        <is>
-          <t>NJ Transit Raritan → NY Penn Station. Llega 8:20. $18,50. Con maletas, ir al vagón con espacio de equipaje.</t>
-        </is>
-      </c>
-      <c r="F105" s="37" t="inlineStr"/>
-      <c r="G105" s="40" t="inlineStr"/>
-      <c r="H105" s="41" t="inlineStr"/>
-      <c r="I105" s="41" t="inlineStr"/>
-    </row>
-    <row r="106" ht="16" customHeight="1">
+      <c r="E101" s="39" t="inlineStr">
+        <is>
+          <t>Al JGStay sin apuro: subte B/C desde 72 St hasta W 4 St y caminar, o 1 hasta Canal (~35 min). Dormir en SoHo y no en Branchburg cambia el jueves entero.</t>
+        </is>
+      </c>
+      <c r="F101" s="37" t="inlineStr">
+        <is>
+          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
+        </is>
+      </c>
+      <c r="G101" s="40" t="inlineStr"/>
+      <c r="H101" s="41" t="inlineStr"/>
+      <c r="I101" s="41" t="inlineStr"/>
+    </row>
+    <row r="102" ht="32" customHeight="1">
+      <c r="A102" s="46" t="inlineStr">
+        <is>
+          <t>ALTERNATIVA / OJO:  EL FRICK SE CAE, y hay que decirlo: hoy era su ventana pay-what-you-wish de 13:30 a 17:30, la única de la semana, y el día quedó lleno con el High Line temprano, el Vessel y el MoMA pendiente. Si lo quieren recuperar, la única forma es soltar el MoMA o el AMNH — el Frick fuera de esa ventana son $30 por cabeza. // SI PREFIEREN EL TOP OF THE ROCK EN VEZ DEL MoMA: abre 8:00-24:00, así que entra en el mismo hueco de las 15:40. PERO su gracia es el atardecer (hoy ~19:26) y a esa hora están en el SummerStage, así que sería subir con luz plana. El MoMA cierra 17:30 y hoy es su única chance del viaje; el Top of the Rock, en cambio, compite con el SUMMIT del viernes, que ya tiene el atardecer reservado y es mejor mirador. Por eso el plan pone el MoMA. // Si el High Line a las 7 resulta demasiado madrugón después de anoche, se puede entrar 8:30 y correr todo una hora: el Vessel abre 10:00 igual y el resto del día no se mueve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="33" t="inlineStr">
+        <is>
+          <t>DÍA 6 · Jueves 03/09 · Traslado + World Trade Center completo + ferry con Thais  —  base: JGStay SoHo → The Beacon  ·  Solo JP</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="32" customHeight="1">
+      <c r="A105" s="34" t="inlineStr">
+        <is>
+          <t>REARMADO EL 1/9: Juan ya no duerme en New Jersey, así que el día arranca en el JGStay SoHo a las 7:30 con desayuno incluido en vez de a las 6:20 en Branchburg — hora y media más de sueño, un Uber menos y un tren menos. Las maletas van en el subte 1, directo de Canal St a 72 St, y quedan en el bell desk del Beacon antes de las 9. La mañana y la primera tarde son el World Trade Center completo — memorial, museo y One World Observatory en una sola bajada. OJO: One World es EL MIRADOR DE DÍA a propósito — su vista es el puerto y el agua, que de noche es negra; los arcos de atardecer van en Top of the Rock (lunes) y SUMMIT (viernes). THAIS ESTÁ EN NYC CON SU EQUIPO este jueves y SE LIBERA A LAS 16:00: se encuentran por Manhattan y se van juntos al Museum of the Moving Image, que es GRATIS los jueves de 14 a 18 — estaba caído del plan y ustedes lo tienen 2/2: RECUPERADO. El día cierra con check-in, cena y Dizzy's. Siguen afuera MoMA PS1, Astoria y Gantry (no hay hueco), y el Staten Island Ferry pasó a la alternativa nocturna de hoy. ENTRA STONE ST, que era imprescindible y no estaba en ningún día: el almuerzo se corre de Brookfield Place a la calle adoquinada, a 10 minutos del museo y 12 de One World. Se pagan 22 minutos de caminata y quedan 38 para comer — alcanza para un mediodía, aunque su mejor hora sea el after office de 5 a 8 y no la del almuerzo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="30" customHeight="1">
       <c r="A106" s="35" t="n"/>
       <c r="B106" s="36" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C106" s="37" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="D106" s="38" t="inlineStr">
@@ -35221,95 +35237,99 @@
       </c>
       <c r="E106" s="39" t="inlineStr">
         <is>
-          <t>Subte 1/2/3 desde 34 St-Penn Station hasta 72 St. Diez minutos, directo.</t>
-        </is>
-      </c>
-      <c r="F106" s="37" t="inlineStr"/>
+          <t>Desayuno incluido en el JGStay (7-9 AM) y CHECKOUT con las maletas. Hoy ya no se madruga a las 5:45 en Branchburg: se duerme en SoHo y se sale a las 7:30. Una hora y media más de sueño y un tren menos.</t>
+        </is>
+      </c>
+      <c r="F106" s="37" t="inlineStr">
+        <is>
+          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
+        </is>
+      </c>
       <c r="G106" s="40" t="inlineStr"/>
       <c r="H106" s="41" t="inlineStr"/>
       <c r="I106" s="41" t="inlineStr"/>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="35" t="n"/>
-      <c r="B107" s="42" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="C107" s="43" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="D107" s="44" t="inlineStr">
+      <c r="B107" s="36" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="C107" s="37" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="D107" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E107" s="45" t="inlineStr">
-        <is>
-          <t>★ THE BEACON — dejar las maletas en el bell desk. El check-in formal es a la tarde, con Thais, pero el equipaje se puede dejar desde temprano. Confirmalo por mail antes de viajar.</t>
-        </is>
-      </c>
-      <c r="F107" s="43" t="inlineStr">
-        <is>
-          <t>Hotel The Beacon (3-6 sep)</t>
-        </is>
-      </c>
+      <c r="E107" s="39" t="inlineStr">
+        <is>
+          <t>Subte 1 desde Canal St derecho hasta 72 St (~25 min). Con maletas, el 1 es el que conviene: es directo y no hay que hacer transbordo.</t>
+        </is>
+      </c>
+      <c r="F107" s="37" t="inlineStr"/>
       <c r="G107" s="40" t="inlineStr"/>
       <c r="H107" s="41" t="inlineStr"/>
       <c r="I107" s="41" t="inlineStr"/>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="35" t="n"/>
-      <c r="B108" s="36" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="C108" s="37" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="D108" s="38" t="inlineStr">
+      <c r="B108" s="42" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="C108" s="43" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="D108" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E108" s="39" t="inlineStr">
-        <is>
-          <t>Subte 1 directo desde 72 St hasta WTC Cortlandt (~30 min). Alternativa: 2/3 express hasta Chambers St y 5 min a pie.</t>
-        </is>
-      </c>
-      <c r="F108" s="37" t="inlineStr"/>
+      <c r="E108" s="45" t="inlineStr">
+        <is>
+          <t>★ THE BEACON — dejar las maletas en el bell desk. El check-in formal es a la tarde, con Thais, pero el equipaje se recibe desde temprano. Confirmalo por mail.</t>
+        </is>
+      </c>
+      <c r="F108" s="43" t="inlineStr">
+        <is>
+          <t>Hotel The Beacon (3-6 sep)</t>
+        </is>
+      </c>
       <c r="G108" s="40" t="inlineStr"/>
       <c r="H108" s="41" t="inlineStr"/>
       <c r="I108" s="41" t="inlineStr"/>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="35" t="n"/>
-      <c r="B109" s="42" t="inlineStr">
+      <c r="B109" s="36" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="C109" s="37" t="inlineStr">
         <is>
           <t>09:50</t>
         </is>
       </c>
-      <c r="C109" s="43" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="D109" s="44" t="inlineStr">
+      <c r="D109" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E109" s="45" t="inlineStr">
-        <is>
-          <t>★ 9/11 MEMORIAL (la plaza) — las dos fuentes en las huellas de las torres y el Survivor Tree. Gratis, abierto desde las 8:00. Verlo ANTES del museo ordena la visita.</t>
-        </is>
-      </c>
-      <c r="F109" s="43" t="inlineStr"/>
+      <c r="E109" s="39" t="inlineStr">
+        <is>
+          <t>Subte 1 directo desde 72 St hasta WTC Cortlandt (~30 min), otra vez sin transbordo. Alternativa: 2/3 express hasta Chambers St y 5 min a pie.</t>
+        </is>
+      </c>
+      <c r="F109" s="37" t="inlineStr"/>
       <c r="G109" s="40" t="inlineStr"/>
       <c r="H109" s="41" t="inlineStr"/>
       <c r="I109" s="41" t="inlineStr"/>
@@ -35318,14 +35338,14 @@
       <c r="A110" s="35" t="n"/>
       <c r="B110" s="42" t="inlineStr">
         <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="C110" s="43" t="inlineStr">
+        <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="C110" s="43" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="D110" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
@@ -35333,83 +35353,75 @@
       </c>
       <c r="E110" s="45" t="inlineStr">
         <is>
-          <t>★★ 9/11 MEMORIAL MUSEUM — $36, TIMED TICKET OBLIGATORIO comprado online antes (el museo no vende en puerta sin reserva). 2 horas largas; es duro y muy bien hecho. Thais lo marcó 0: por eso va en la mañana de JP solo.</t>
-        </is>
-      </c>
-      <c r="F110" s="43" t="inlineStr">
-        <is>
-          <t>9/11 Memorial Museum</t>
-        </is>
-      </c>
+          <t>★ 9/11 MEMORIAL (la plaza) — las dos fuentes en las huellas de las torres y el Survivor Tree. Gratis, abierto desde las 8:00. Verlo ANTES del museo ordena la visita.</t>
+        </is>
+      </c>
+      <c r="F110" s="43" t="inlineStr"/>
       <c r="G110" s="40" t="inlineStr"/>
       <c r="H110" s="41" t="inlineStr"/>
       <c r="I110" s="41" t="inlineStr"/>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="35" t="n"/>
-      <c r="B111" s="36" t="inlineStr">
+      <c r="B111" s="42" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C111" s="43" t="inlineStr">
         <is>
           <t>12:45</t>
         </is>
       </c>
-      <c r="C111" s="37" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="D111" s="38" t="inlineStr">
+      <c r="D111" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E111" s="39" t="inlineStr">
-        <is>
-          <t>★ ALMUERZO EN STONE ST — 10 min a pie desde el museo, hacia el sureste. Calle adoquinada peatonal de 1660, la traza holandesa que sobrevivió al fuego de 1835: mesas afuera, sin autos, entre edificios de piedra. Se come rápido y se sigue: One World es a las 13:45 y son 12 min de vuelta. Plan B si llueve o no hay mesa: Hudson Eats o Le District en Brookfield Place, cruzando West St.</t>
-        </is>
-      </c>
-      <c r="F111" s="37" t="inlineStr">
-        <is>
-          <t>Stone St</t>
-        </is>
-      </c>
-      <c r="G111" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~14 min a pie · 1.1 km · estimado</t>
-        </is>
-      </c>
+      <c r="E111" s="45" t="inlineStr">
+        <is>
+          <t>★★ 9/11 MEMORIAL MUSEUM — $36, TIMED TICKET OBLIGATORIO comprado online antes (el museo no vende en puerta sin reserva). 2 horas largas; es duro y muy bien hecho. Thais lo marcó 0: por eso va en la mañana de JP solo.</t>
+        </is>
+      </c>
+      <c r="F111" s="43" t="inlineStr">
+        <is>
+          <t>9/11 Memorial Museum</t>
+        </is>
+      </c>
+      <c r="G111" s="40" t="inlineStr"/>
       <c r="H111" s="41" t="inlineStr"/>
       <c r="I111" s="41" t="inlineStr"/>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="35" t="n"/>
-      <c r="B112" s="42" t="inlineStr">
+      <c r="B112" s="36" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C112" s="37" t="inlineStr">
         <is>
           <t>13:45</t>
         </is>
       </c>
-      <c r="C112" s="43" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="D112" s="44" t="inlineStr">
+      <c r="D112" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E112" s="45" t="inlineStr">
-        <is>
-          <t>★★ ONE WORLD OBSERVATORY — piso 102, el punto más alto del hemisferio occidental, con el puerto y Brooklyn dominando la vista. $44+fee, ventana de entrada de 15 min: sacar el timed ticket online. JP lo subió a 2 en la última pasada.</t>
-        </is>
-      </c>
-      <c r="F112" s="43" t="inlineStr">
-        <is>
-          <t>One World Observatory</t>
+      <c r="E112" s="39" t="inlineStr">
+        <is>
+          <t>★ ALMUERZO EN STONE ST — 10 min a pie desde el museo, hacia el sureste. Calle adoquinada peatonal de 1660, la traza holandesa que sobrevivió al fuego de 1835: mesas afuera, sin autos, entre edificios de piedra. Se come rápido y se sigue: One World es a las 13:45 y son 12 min de vuelta. Plan B si llueve o no hay mesa: Hudson Eats o Le District en Brookfield Place, cruzando West St.</t>
+        </is>
+      </c>
+      <c r="F112" s="37" t="inlineStr">
+        <is>
+          <t>Stone St</t>
         </is>
       </c>
       <c r="G112" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~20 min a pie (1.2 km) o 🚇 ~15 min · estimado</t>
+          <t>🚶 ~14 min a pie · 1.1 km · estimado</t>
         </is>
       </c>
       <c r="H112" s="41" t="inlineStr"/>
@@ -35417,34 +35429,34 @@
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="35" t="n"/>
-      <c r="B113" s="36" t="inlineStr">
+      <c r="B113" s="42" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="C113" s="43" t="inlineStr">
         <is>
           <t>15:15</t>
         </is>
       </c>
-      <c r="C113" s="37" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D113" s="38" t="inlineStr">
+      <c r="D113" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E113" s="39" t="inlineStr">
-        <is>
-          <t>El Oculus en un VISTAZO (5 min — ya estás ahí, y el tiempo no da para más) y R/W desde Cortlandt St hacia el norte.</t>
-        </is>
-      </c>
-      <c r="F113" s="37" t="inlineStr">
-        <is>
-          <t>Oculus / WTC Transportation Hub</t>
+      <c r="E113" s="45" t="inlineStr">
+        <is>
+          <t>★★ ONE WORLD OBSERVATORY — piso 102, el punto más alto del hemisferio occidental, con el puerto y Brooklyn dominando la vista. $44+fee, ventana de entrada de 15 min: sacar el timed ticket online. JP lo subió a 2 en la última pasada.</t>
+        </is>
+      </c>
+      <c r="F113" s="43" t="inlineStr">
+        <is>
+          <t>One World Observatory</t>
         </is>
       </c>
       <c r="G113" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~4 min a pie · 0.3 km · estimado</t>
+          <t>🚶 ~20 min a pie (1.2 km) o 🚇 ~15 min · estimado</t>
         </is>
       </c>
       <c r="H113" s="41" t="inlineStr"/>
@@ -35452,28 +35464,36 @@
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="35" t="n"/>
-      <c r="B114" s="42" t="inlineStr">
+      <c r="B114" s="36" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C114" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="C114" s="43" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="D114" s="44" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="E114" s="45" t="inlineStr">
-        <is>
-          <t>★ ENCUENTRO CON THAIS. Lo que MÁS rinde: verse DIRECTO en la puerta del MoMI a las 16:20 (36-01 35 Ave, N/W hasta 36 Av) — cada uno llega por su lado y el museo gana 10-15 min. Si prefieren encontrarse antes en Manhattan: Lexington Av-59 St 16:00 y N/W juntos (JP puede llegar 16:05-16:10 si el WTC se estiró: avisale que es ±10).</t>
-        </is>
-      </c>
-      <c r="F114" s="43" t="inlineStr"/>
-      <c r="G114" s="40" t="inlineStr"/>
+      <c r="D114" s="38" t="inlineStr">
+        <is>
+          <t>Solo JP</t>
+        </is>
+      </c>
+      <c r="E114" s="39" t="inlineStr">
+        <is>
+          <t>El Oculus en un VISTAZO (5 min — ya estás ahí, y el tiempo no da para más) y R/W desde Cortlandt St hacia el norte.</t>
+        </is>
+      </c>
+      <c r="F114" s="37" t="inlineStr">
+        <is>
+          <t>Oculus / WTC Transportation Hub</t>
+        </is>
+      </c>
+      <c r="G114" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~4 min a pie · 0.3 km · estimado</t>
+        </is>
+      </c>
       <c r="H114" s="41" t="inlineStr"/>
       <c r="I114" s="41" t="inlineStr"/>
     </row>
@@ -35481,14 +35501,14 @@
       <c r="A115" s="35" t="n"/>
       <c r="B115" s="42" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C115" s="43" t="inlineStr">
+        <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="C115" s="43" t="inlineStr">
-        <is>
-          <t>18:05</t>
-        </is>
-      </c>
       <c r="D115" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35496,46 +35516,46 @@
       </c>
       <c r="E115" s="45" t="inlineStr">
         <is>
-          <t>★★ MUSEUM OF THE MOVING IMAGE — GRATIS los jueves 14-18, sus únicas horas del jueves. RECUPERADO: había quedado afuera del plan y ustedes lo tienen 2/2. Una hora y media alcanza para Behind the Screen y los Muppets originales de Jim Henson. Cierra 18:00 EN PUNTO. (N/W hasta 36 Av + 8 min a pie.)</t>
-        </is>
-      </c>
-      <c r="F115" s="43" t="inlineStr">
-        <is>
-          <t>Museum of the Moving Image</t>
-        </is>
-      </c>
-      <c r="G115" s="40" t="inlineStr">
-        <is>
-          <t>🚇 ~40 min en subte · 11.5 km (a pie 155 min) · estimado</t>
-        </is>
-      </c>
+          <t>★ ENCUENTRO CON THAIS. Lo que MÁS rinde: verse DIRECTO en la puerta del MoMI a las 16:20 (36-01 35 Ave, N/W hasta 36 Av) — cada uno llega por su lado y el museo gana 10-15 min. Si prefieren encontrarse antes en Manhattan: Lexington Av-59 St 16:00 y N/W juntos (JP puede llegar 16:05-16:10 si el WTC se estiró: avisale que es ±10).</t>
+        </is>
+      </c>
+      <c r="F115" s="43" t="inlineStr"/>
+      <c r="G115" s="40" t="inlineStr"/>
       <c r="H115" s="41" t="inlineStr"/>
       <c r="I115" s="41" t="inlineStr"/>
     </row>
-    <row r="116" ht="16" customHeight="1">
+    <row r="116" ht="30" customHeight="1">
       <c r="A116" s="35" t="n"/>
-      <c r="B116" s="36" t="inlineStr">
+      <c r="B116" s="42" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C116" s="43" t="inlineStr">
         <is>
           <t>18:05</t>
         </is>
       </c>
-      <c r="C116" s="37" t="inlineStr">
-        <is>
-          <t>18:55</t>
-        </is>
-      </c>
-      <c r="D116" s="38" t="inlineStr">
+      <c r="D116" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E116" s="39" t="inlineStr">
-        <is>
-          <t>Subte N/W desde 36 Av hasta Times Sq y 1/2/3 hasta 72 St (~45 min).</t>
-        </is>
-      </c>
-      <c r="F116" s="37" t="inlineStr"/>
-      <c r="G116" s="40" t="inlineStr"/>
+      <c r="E116" s="45" t="inlineStr">
+        <is>
+          <t>★★ MUSEUM OF THE MOVING IMAGE — GRATIS los jueves 14-18, sus únicas horas del jueves. RECUPERADO: había quedado afuera del plan y ustedes lo tienen 2/2. Una hora y media alcanza para Behind the Screen y los Muppets originales de Jim Henson. Cierra 18:00 EN PUNTO. (N/W hasta 36 Av + 8 min a pie.)</t>
+        </is>
+      </c>
+      <c r="F116" s="43" t="inlineStr">
+        <is>
+          <t>Museum of the Moving Image</t>
+        </is>
+      </c>
+      <c r="G116" s="40" t="inlineStr">
+        <is>
+          <t>🚇 ~40 min en subte · 11.5 km (a pie 155 min) · estimado</t>
+        </is>
+      </c>
       <c r="H116" s="41" t="inlineStr"/>
       <c r="I116" s="41" t="inlineStr"/>
     </row>
@@ -35543,14 +35563,14 @@
       <c r="A117" s="35" t="n"/>
       <c r="B117" s="36" t="inlineStr">
         <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="C117" s="37" t="inlineStr">
+        <is>
           <t>18:55</t>
         </is>
       </c>
-      <c r="C117" s="37" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
       <c r="D117" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35558,30 +35578,26 @@
       </c>
       <c r="E117" s="39" t="inlineStr">
         <is>
-          <t>The Beacon: check-in formal y subir las maletas.</t>
-        </is>
-      </c>
-      <c r="F117" s="37" t="inlineStr">
-        <is>
-          <t>Hotel The Beacon (3-6 sep)</t>
-        </is>
-      </c>
+          <t>Subte N/W desde 36 Av hasta Times Sq y 1/2/3 hasta 72 St (~45 min).</t>
+        </is>
+      </c>
+      <c r="F117" s="37" t="inlineStr"/>
       <c r="G117" s="40" t="inlineStr"/>
       <c r="H117" s="41" t="inlineStr"/>
       <c r="I117" s="41" t="inlineStr"/>
     </row>
-    <row r="118" ht="30" customHeight="1">
+    <row r="118" ht="16" customHeight="1">
       <c r="A118" s="35" t="n"/>
       <c r="B118" s="36" t="inlineStr">
         <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="C118" s="37" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="C118" s="37" t="inlineStr">
-        <is>
-          <t>19:55</t>
-        </is>
-      </c>
       <c r="D118" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35589,130 +35605,134 @@
       </c>
       <c r="E118" s="39" t="inlineStr">
         <is>
-          <t>Cena RÁPIDA en el Upper West Side, bajando por Broadway o Columbus. Hoy se come temprano y liviano: la noche tiene tres paradas y todas valen.</t>
-        </is>
-      </c>
-      <c r="F118" s="37" t="inlineStr"/>
+          <t>The Beacon: check-in formal y subir las maletas.</t>
+        </is>
+      </c>
+      <c r="F118" s="37" t="inlineStr">
+        <is>
+          <t>Hotel The Beacon (3-6 sep)</t>
+        </is>
+      </c>
       <c r="G118" s="40" t="inlineStr"/>
       <c r="H118" s="41" t="inlineStr"/>
       <c r="I118" s="41" t="inlineStr"/>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="35" t="n"/>
-      <c r="B119" s="42" t="inlineStr">
+      <c r="B119" s="36" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C119" s="37" t="inlineStr">
         <is>
           <t>19:55</t>
         </is>
       </c>
-      <c r="C119" s="43" t="inlineStr">
-        <is>
-          <t>20:20</t>
-        </is>
-      </c>
-      <c r="D119" s="44" t="inlineStr">
+      <c r="D119" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E119" s="45" t="inlineStr">
-        <is>
-          <t>★ LINCOLN CENTER DE NOCHE (gratis, 20 min) — OJO, VERIFICADO el 27/8 y cambia lo que van a encontrar: esta noche la Josie Robertson Plaza NO está tranquila. El Met proyecta Tristan und Isolde (actos II y III) a las 20:00 en pantalla gigante, gratis y sin reserva, y despejan la plaza desde las 18:00 para armar 2.500 sillas. O sea: llegan justo cuando se está llenando. La fuente y los chandeliers siguen ahí, pero con multitud y pantalla. Puede ser mejor que el plan original —hay ambiente de estreno— o puede ser un quilombo: decidan en el momento. Si prefieren el Lincoln Center vacío, el espejo de agua con el Henry Moore está del lado norte, detrás del Vivian Beaumont, y ahí no hay nadie.</t>
-        </is>
-      </c>
-      <c r="F119" s="43" t="inlineStr">
-        <is>
-          <t>Lincoln Center (campus y plaza)</t>
-        </is>
-      </c>
-      <c r="G119" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~20 min a pie (1.3 km) o 🚇 ~15 min · estimado</t>
-        </is>
-      </c>
+      <c r="E119" s="39" t="inlineStr">
+        <is>
+          <t>Cena RÁPIDA en el Upper West Side, bajando por Broadway o Columbus. Hoy se come temprano y liviano: la noche tiene tres paradas y todas valen.</t>
+        </is>
+      </c>
+      <c r="F119" s="37" t="inlineStr"/>
+      <c r="G119" s="40" t="inlineStr"/>
       <c r="H119" s="41" t="inlineStr"/>
       <c r="I119" s="41" t="inlineStr"/>
     </row>
-    <row r="120" ht="16" customHeight="1">
+    <row r="120" ht="30" customHeight="1">
       <c r="A120" s="35" t="n"/>
-      <c r="B120" s="36" t="inlineStr">
+      <c r="B120" s="42" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="C120" s="43" t="inlineStr">
         <is>
           <t>20:20</t>
         </is>
       </c>
-      <c r="C120" s="37" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="D120" s="38" t="inlineStr">
+      <c r="D120" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E120" s="39" t="inlineStr">
-        <is>
-          <t>Caminar seis cuadras por Broadway hasta Columbus Circle (~8 min).</t>
-        </is>
-      </c>
-      <c r="F120" s="37" t="inlineStr"/>
-      <c r="G120" s="40" t="inlineStr"/>
+      <c r="E120" s="45" t="inlineStr">
+        <is>
+          <t>★ LINCOLN CENTER DE NOCHE (gratis, 20 min) — OJO, VERIFICADO el 27/8 y cambia lo que van a encontrar: esta noche la Josie Robertson Plaza NO está tranquila. El Met proyecta Tristan und Isolde (actos II y III) a las 20:00 en pantalla gigante, gratis y sin reserva, y despejan la plaza desde las 18:00 para armar 2.500 sillas. O sea: llegan justo cuando se está llenando. La fuente y los chandeliers siguen ahí, pero con multitud y pantalla. Puede ser mejor que el plan original —hay ambiente de estreno— o puede ser un quilombo: decidan en el momento. Si prefieren el Lincoln Center vacío, el espejo de agua con el Henry Moore está del lado norte, detrás del Vivian Beaumont, y ahí no hay nadie.</t>
+        </is>
+      </c>
+      <c r="F120" s="43" t="inlineStr">
+        <is>
+          <t>Lincoln Center (campus y plaza)</t>
+        </is>
+      </c>
+      <c r="G120" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~20 min a pie (1.3 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H120" s="41" t="inlineStr"/>
       <c r="I120" s="41" t="inlineStr"/>
     </row>
-    <row r="121" ht="30" customHeight="1">
+    <row r="121" ht="16" customHeight="1">
       <c r="A121" s="35" t="n"/>
-      <c r="B121" s="42" t="inlineStr">
+      <c r="B121" s="36" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="C121" s="37" t="inlineStr">
         <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="C121" s="43" t="inlineStr">
-        <is>
-          <t>20:55</t>
-        </is>
-      </c>
-      <c r="D121" s="44" t="inlineStr">
+      <c r="D121" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E121" s="45" t="inlineStr">
-        <is>
-          <t>★★ MO LOUNGE, PISO 35 DEL MANDARIN ORIENTAL (80 Columbus Circle) — el dato del amigo de Juan, con una corrección: es el piso 35, no el 60 (el hotel ocupa del 35 al 54). Ventanales de piso a techo sobre Central Park con la ciudad encendida abajo. Coctel ~$26-32, sin cover. RESERVAR por SevenRooms desde su web. Si prefieren algo más íntimo, en ese MISMO piso está The Bar (ex speakeasy The Office, 45 asientos, mar-sáb 17-1h).</t>
-        </is>
-      </c>
-      <c r="F121" s="43" t="inlineStr">
-        <is>
-          <t>MO Lounge — Mandarin Oriental (piso 35)</t>
-        </is>
-      </c>
+      <c r="E121" s="39" t="inlineStr">
+        <is>
+          <t>Caminar seis cuadras por Broadway hasta Columbus Circle (~8 min).</t>
+        </is>
+      </c>
+      <c r="F121" s="37" t="inlineStr"/>
       <c r="G121" s="40" t="inlineStr"/>
       <c r="H121" s="41" t="inlineStr"/>
       <c r="I121" s="41" t="inlineStr"/>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="35" t="n"/>
-      <c r="B122" s="36" t="inlineStr">
+      <c r="B122" s="42" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C122" s="43" t="inlineStr">
         <is>
           <t>20:55</t>
         </is>
       </c>
-      <c r="C122" s="37" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="D122" s="38" t="inlineStr">
+      <c r="D122" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E122" s="39" t="inlineStr">
-        <is>
-          <t>Bajar en ascensor: Dizzy's está EN EL MISMO EDIFICIO (10 Columbus Circle, piso 5). Cero calle, cero frío.</t>
-        </is>
-      </c>
-      <c r="F122" s="37" t="inlineStr"/>
+      <c r="E122" s="45" t="inlineStr">
+        <is>
+          <t>★★ MO LOUNGE, PISO 35 DEL MANDARIN ORIENTAL (80 Columbus Circle) — el dato del amigo de Juan, con una corrección: es el piso 35, no el 60 (el hotel ocupa del 35 al 54). Ventanales de piso a techo sobre Central Park con la ciudad encendida abajo. Coctel ~$26-32, sin cover. RESERVAR por SevenRooms desde su web. Si prefieren algo más íntimo, en ese MISMO piso está The Bar (ex speakeasy The Office, 45 asientos, mar-sáb 17-1h).</t>
+        </is>
+      </c>
+      <c r="F122" s="43" t="inlineStr">
+        <is>
+          <t>MO Lounge — Mandarin Oriental (piso 35)</t>
+        </is>
+      </c>
       <c r="G122" s="40" t="inlineStr"/>
       <c r="H122" s="41" t="inlineStr"/>
       <c r="I122" s="41" t="inlineStr"/>
@@ -35721,10 +35741,14 @@
       <c r="A123" s="35" t="n"/>
       <c r="B123" s="36" t="inlineStr">
         <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="C123" s="37" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C123" s="37" t="inlineStr"/>
       <c r="D123" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35732,78 +35756,74 @@
       </c>
       <c r="E123" s="39" t="inlineStr">
         <is>
-          <t>★ Dizzy's Club — ventanales sobre Central Park detrás del escenario, un piso abajo del cóctel. SEAMOS HONESTOS: JP lleva ~17 horas en pie con 5 de sueño. Decidan A LAS 20:00, arriba en el Mandarin: si están enteros, bajan; si no, se quedan con la vista y el trago, que ya es un cierre precioso. El set Late Night (~22:45) cuesta una fracción — variante para valientes.</t>
-        </is>
-      </c>
-      <c r="F123" s="37" t="inlineStr">
-        <is>
-          <t>Dizzy's Club (Jazz at Lincoln Center)</t>
-        </is>
-      </c>
+          <t>Bajar en ascensor: Dizzy's está EN EL MISMO EDIFICIO (10 Columbus Circle, piso 5). Cero calle, cero frío.</t>
+        </is>
+      </c>
+      <c r="F123" s="37" t="inlineStr"/>
       <c r="G123" s="40" t="inlineStr"/>
       <c r="H123" s="41" t="inlineStr"/>
       <c r="I123" s="41" t="inlineStr"/>
     </row>
-    <row r="124" ht="32" customHeight="1">
-      <c r="A124" s="46" t="inlineStr">
+    <row r="124" ht="30" customHeight="1">
+      <c r="A124" s="35" t="n"/>
+      <c r="B124" s="36" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C124" s="37" t="inlineStr"/>
+      <c r="D124" s="38" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E124" s="39" t="inlineStr">
+        <is>
+          <t>★ Dizzy's Club — ventanales sobre Central Park detrás del escenario, un piso abajo del cóctel. SEAMOS HONESTOS: JP lleva ~17 horas en pie con 5 de sueño. Decidan A LAS 20:00, arriba en el Mandarin: si están enteros, bajan; si no, se quedan con la vista y el trago, que ya es un cierre precioso. El set Late Night (~22:45) cuesta una fracción — variante para valientes.</t>
+        </is>
+      </c>
+      <c r="F124" s="37" t="inlineStr">
+        <is>
+          <t>Dizzy's Club (Jazz at Lincoln Center)</t>
+        </is>
+      </c>
+      <c r="G124" s="40" t="inlineStr"/>
+      <c r="H124" s="41" t="inlineStr"/>
+      <c r="I124" s="41" t="inlineStr"/>
+    </row>
+    <row r="125" ht="32" customHeight="1">
+      <c r="A125" s="46" t="inlineStr">
         <is>
           <t>ALTERNATIVA / OJO:  ⚠️ EL PROBLEMA DE LA NOCHE ANTERIOR: si JP viaja desde New Jersey el jueves, significa que durmió allá el miércoles — y el miércoles el SummerStage termina a las 22:00 en Central Park. Llegando a Penn ~22:25 se toma el directo de las 22:48, que deja en Raritan ~0:04, más Uber: llegada al hotel ~0:25 y despertador a las 5:45. Son cinco horas de sueño antes de un día completo. Tres salidas: (a) salir del SummerStage a las 21:15, después del set principal; (b) quedarse una noche más en el JGStay y que Thais lleve las maletas el jueves (implica tocar la reserva); (c) tomar el tren de las 7:13 en vez del de 6:55 y arrancar 20 minutos más tarde. Verificá los horarios exactos de la tarde-noche en njtransit.com: solo tengo confirmado el directo de las 22:48. // EL FERRY, SI LES DUELE (lo tienen 2/2): al salir del MoMI, W directo hasta Whitehall (~50 min), ferry ~19:15 — el atardecer (~19:22) de ida y la Estatua y el skyline ILUMINADOS de vuelta; check-in ~21:15, cena tarde cerca del hotel, y Dizzy's tiene set Late Night los jueves ~22:45 como consuelo. Es MÁS día: elíjanlo solo si llegan enteros. // Siguen afuera: MoMA PS1, Astoria y Gantry (sin hueco); ya habían salido Noguchi, Astoria Park y Socrates por interés bajo.</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="22" customHeight="1">
-      <c r="A126" s="33" t="inlineStr">
+    <row r="127" ht="22" customHeight="1">
+      <c r="A127" s="33" t="inlineStr">
         <is>
           <t>DÍA 7 · Viernes 04/09 · Vessel + High Line, SUMMIT al atardecer y el VANGUARD de a dos  —  base: The Beacon  ·  Ambos</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="32" customHeight="1">
-      <c r="A127" s="34" t="inlineStr">
+    <row r="128" ht="32" customHeight="1">
+      <c r="A128" s="34" t="inlineStr">
         <is>
           <t>Salieron el West Village, Washington Square y el Whitney; entraron el High Line, THE VESSEL (al pie del arranque, $10 y 45 min), la Morgan (hoy GRATIS 17-20) y SUMMIT — que se movió AL ATARDECER por el pedido de ustedes: entrada 18:10, luz plena, la puesta ~19:21 multiplicada por los espejos de Kusama (es EL lugar de la ciudad para ese momento) y la noche encendida hasta las 20:15. EL PAGO, dicho honesto: la Morgan se hace en una hora entrando 17:00 en punto, y la cena de hoy es un bocado rápido — por eso el almuerzo en Chelsea Market es EL fuerte del día. SALIÓ GRAND CENTRAL: estaba a las 16:20 con el argumento de que JP ya lo vio el lunes y Thais no — pero ella lo tiene en 0, así que eran 40 minutos para alguien que no lo quiere. Sin esa parada tampoco hace falta cortar Chelsea a las 15:50: se sale 16:25 derecho a la Morgan y la tarde de galerías y almuerzo gana una hora larga.</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="35" t="n"/>
-      <c r="B128" s="36" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="C128" s="37" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="D128" s="38" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="E128" s="39" t="inlineStr">
-        <is>
-          <t>Subte a Hudson Yards.</t>
-        </is>
-      </c>
-      <c r="F128" s="37" t="inlineStr"/>
-      <c r="G128" s="40" t="inlineStr"/>
-      <c r="H128" s="41" t="inlineStr"/>
-      <c r="I128" s="41" t="inlineStr"/>
-    </row>
-    <row r="129" ht="30" customHeight="1">
+    <row r="129" ht="16" customHeight="1">
       <c r="A129" s="35" t="n"/>
       <c r="B129" s="36" t="inlineStr">
         <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C129" s="37" t="inlineStr">
+        <is>
           <t>09:40</t>
         </is>
       </c>
-      <c r="C129" s="37" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="D129" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35811,7 +35831,7 @@
       </c>
       <c r="E129" s="39" t="inlineStr">
         <is>
-          <t>La plaza de Hudson Yards mientras abre el Vessel: The Shops y el Shed desde afuera. Sacar el timed ticket de las 10:00 online antes.</t>
+          <t>Subte a Hudson Yards.</t>
         </is>
       </c>
       <c r="F129" s="37" t="inlineStr"/>
@@ -35821,31 +35841,27 @@
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="35" t="n"/>
-      <c r="B130" s="42" t="inlineStr">
+      <c r="B130" s="36" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="C130" s="37" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="C130" s="43" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="D130" s="44" t="inlineStr">
+      <c r="D130" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E130" s="45" t="inlineStr">
-        <is>
-          <t>★ THE VESSEL — la escalera infinita de Heatherwick: 154 tramos, 2.500 escalones, $10. Reabierto con redes; algunos tramos altos hacia el Hudson siguen cerrados, y hay ascensor cada 15 min. Subir es la única forma de entenderla. Si Thais prefiere no subir, la plaza está al pie.</t>
-        </is>
-      </c>
-      <c r="F130" s="43" t="inlineStr">
-        <is>
-          <t>The Vessel</t>
-        </is>
-      </c>
+      <c r="E130" s="39" t="inlineStr">
+        <is>
+          <t>La plaza de Hudson Yards mientras abre el Vessel: The Shops y el Shed desde afuera. Sacar el timed ticket de las 10:00 online antes.</t>
+        </is>
+      </c>
+      <c r="F130" s="37" t="inlineStr"/>
       <c r="G130" s="40" t="inlineStr"/>
       <c r="H130" s="41" t="inlineStr"/>
       <c r="I130" s="41" t="inlineStr"/>
@@ -35854,14 +35870,14 @@
       <c r="A131" s="35" t="n"/>
       <c r="B131" s="42" t="inlineStr">
         <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C131" s="43" t="inlineStr">
+        <is>
           <t>10:50</t>
         </is>
       </c>
-      <c r="C131" s="43" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="D131" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35869,52 +35885,48 @@
       </c>
       <c r="E131" s="45" t="inlineStr">
         <is>
-          <t>★ THE HIGH LINE completo, de norte a sur (2,3 km) — arranca ahí mismo, en 30th y 10ª. Vía ferroviaria elevada convertida en parque lineal. Incluye el Buda de arenisca de 9 metros de Tuan Andrew Nguyen.</t>
+          <t>★ THE VESSEL — la escalera infinita de Heatherwick: 154 tramos, 2.500 escalones, $10. Reabierto con redes; algunos tramos altos hacia el Hudson siguen cerrados, y hay ascensor cada 15 min. Subir es la única forma de entenderla. Si Thais prefiere no subir, la plaza está al pie.</t>
         </is>
       </c>
       <c r="F131" s="43" t="inlineStr">
         <is>
-          <t>The High Line</t>
-        </is>
-      </c>
-      <c r="G131" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~12 min a pie · 0.9 km · estimado</t>
-        </is>
-      </c>
+          <t>The Vessel</t>
+        </is>
+      </c>
+      <c r="G131" s="40" t="inlineStr"/>
       <c r="H131" s="41" t="inlineStr"/>
       <c r="I131" s="41" t="inlineStr"/>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="35" t="n"/>
-      <c r="B132" s="36" t="inlineStr">
+      <c r="B132" s="42" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="C132" s="43" t="inlineStr">
         <is>
           <t>12:20</t>
         </is>
       </c>
-      <c r="C132" s="37" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="D132" s="38" t="inlineStr">
+      <c r="D132" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E132" s="39" t="inlineStr">
-        <is>
-          <t>Little Island — el parque flotante de Heatherwick sobre 132 macetas de hormigón, al final del High Line. Gratis.</t>
-        </is>
-      </c>
-      <c r="F132" s="37" t="inlineStr">
-        <is>
-          <t>Little Island</t>
+      <c r="E132" s="45" t="inlineStr">
+        <is>
+          <t>★ THE HIGH LINE completo, de norte a sur (2,3 km) — arranca ahí mismo, en 30th y 10ª. Vía ferroviaria elevada convertida en parque lineal. Incluye el Buda de arenisca de 9 metros de Tuan Andrew Nguyen.</t>
+        </is>
+      </c>
+      <c r="F132" s="43" t="inlineStr">
+        <is>
+          <t>The High Line</t>
         </is>
       </c>
       <c r="G132" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~15 min a pie · 1.1 km · estimado</t>
+          <t>🚶 ~12 min a pie · 0.9 km · estimado</t>
         </is>
       </c>
       <c r="H132" s="41" t="inlineStr"/>
@@ -35922,63 +35934,63 @@
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="35" t="n"/>
-      <c r="B133" s="42" t="inlineStr">
+      <c r="B133" s="36" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="C133" s="37" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="C133" s="43" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="D133" s="44" t="inlineStr">
+      <c r="D133" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E133" s="45" t="inlineStr">
-        <is>
-          <t>Galerías de Chelsea COMPLETAS — W 19th a W 27th entre la 10ª y la 11ª, concentradas en W 24th y W 21st (Gagosian, Pace, Zwirner). Gratis, se entra y se sale. El recorte del Vessel se devolvió: SUMMIT pasó al atardecer y la tarde se estiró.</t>
-        </is>
-      </c>
-      <c r="F133" s="43" t="inlineStr"/>
-      <c r="G133" s="40" t="inlineStr"/>
+      <c r="E133" s="39" t="inlineStr">
+        <is>
+          <t>Little Island — el parque flotante de Heatherwick sobre 132 macetas de hormigón, al final del High Line. Gratis.</t>
+        </is>
+      </c>
+      <c r="F133" s="37" t="inlineStr">
+        <is>
+          <t>Little Island</t>
+        </is>
+      </c>
+      <c r="G133" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~15 min a pie · 1.1 km · estimado</t>
+        </is>
+      </c>
       <c r="H133" s="41" t="inlineStr"/>
       <c r="I133" s="41" t="inlineStr"/>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="35" t="n"/>
-      <c r="B134" s="36" t="inlineStr">
+      <c r="B134" s="42" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C134" s="43" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="C134" s="37" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="D134" s="38" t="inlineStr">
+      <c r="D134" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E134" s="39" t="inlineStr">
-        <is>
-          <t>Almuerzo en Chelsea Market — COMER FUERTE: es la comida grande del día, la cena de hoy es un bocado rápido entre el SUMMIT y el Vanguard. Los Tacos No.1 o Very Fresh Noodles. Ahora hay casi DOS HORAS: sin apuro, y si quedaron galerías de Chelsea sin ver, se vuelve. ★ HEATONIST está ADENTRO de este mismo mercado (12-18:45): más de 100 salsas picantes para probar, con el lineup de Hot Ones. Si el sábado no llegan a la de Williamsburg, esta es la misma cata en menos metros.</t>
-        </is>
-      </c>
-      <c r="F134" s="37" t="inlineStr">
-        <is>
-          <t>Chelsea Market</t>
-        </is>
-      </c>
-      <c r="G134" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~7 min a pie · 0.5 km · estimado</t>
-        </is>
-      </c>
+      <c r="E134" s="45" t="inlineStr">
+        <is>
+          <t>Galerías de Chelsea COMPLETAS — W 19th a W 27th entre la 10ª y la 11ª, concentradas en W 24th y W 21st (Gagosian, Pace, Zwirner). Gratis, se entra y se sale. El recorte del Vessel se devolvió: SUMMIT pasó al atardecer y la tarde se estiró.</t>
+        </is>
+      </c>
+      <c r="F134" s="43" t="inlineStr"/>
+      <c r="G134" s="40" t="inlineStr"/>
       <c r="H134" s="41" t="inlineStr"/>
       <c r="I134" s="41" t="inlineStr"/>
     </row>
@@ -35986,14 +35998,14 @@
       <c r="A135" s="35" t="n"/>
       <c r="B135" s="36" t="inlineStr">
         <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C135" s="37" t="inlineStr">
+        <is>
           <t>16:25</t>
         </is>
       </c>
-      <c r="C135" s="37" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="D135" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36001,126 +36013,134 @@
       </c>
       <c r="E135" s="39" t="inlineStr">
         <is>
-          <t>A la Morgan: L desde 14 St-8 Av hasta Union Sq y 6 hasta 33 St, o A/C/E hasta 34 St-Penn y siete cuadras a pie (~30 min). Salir 16:25 deja margen para entrar 17:00 EN PUNTO.</t>
-        </is>
-      </c>
-      <c r="F135" s="37" t="inlineStr"/>
-      <c r="G135" s="40" t="inlineStr"/>
+          <t>Almuerzo en Chelsea Market — COMER FUERTE: es la comida grande del día, la cena de hoy es un bocado rápido entre el SUMMIT y el Vanguard. Los Tacos No.1 o Very Fresh Noodles. Ahora hay casi DOS HORAS: sin apuro, y si quedaron galerías de Chelsea sin ver, se vuelve. ★ HEATONIST está ADENTRO de este mismo mercado (12-18:45): más de 100 salsas picantes para probar, con el lineup de Hot Ones. Si el sábado no llegan a la de Williamsburg, esta es la misma cata en menos metros.</t>
+        </is>
+      </c>
+      <c r="F135" s="37" t="inlineStr">
+        <is>
+          <t>Chelsea Market</t>
+        </is>
+      </c>
+      <c r="G135" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~7 min a pie · 0.5 km · estimado</t>
+        </is>
+      </c>
       <c r="H135" s="41" t="inlineStr"/>
       <c r="I135" s="41" t="inlineStr"/>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="35" t="n"/>
-      <c r="B136" s="42" t="inlineStr">
+      <c r="B136" s="36" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="C136" s="37" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="C136" s="43" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="D136" s="44" t="inlineStr">
+      <c r="D136" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E136" s="45" t="inlineStr">
-        <is>
-          <t>★ MORGAN LIBRARY — GRATIS los viernes 17-20h: entrar 17:00 EN PUNTO y hacerla en una hora — la biblioteca son tres salas gloriosas (estanterías de nogal, la Biblia de Gutenberg): alcanza. RESERVA OBLIGATORIA, se libera el viernes 28 de agosto. Está a 8 min a pie de One Vanderbilt.</t>
-        </is>
-      </c>
-      <c r="F136" s="43" t="inlineStr">
-        <is>
-          <t>The Morgan Library &amp; Museum</t>
-        </is>
-      </c>
+      <c r="E136" s="39" t="inlineStr">
+        <is>
+          <t>A la Morgan: L desde 14 St-8 Av hasta Union Sq y 6 hasta 33 St, o A/C/E hasta 34 St-Penn y siete cuadras a pie (~30 min). Salir 16:25 deja margen para entrar 17:00 EN PUNTO.</t>
+        </is>
+      </c>
+      <c r="F136" s="37" t="inlineStr"/>
       <c r="G136" s="40" t="inlineStr"/>
       <c r="H136" s="41" t="inlineStr"/>
       <c r="I136" s="41" t="inlineStr"/>
     </row>
-    <row r="137" ht="16" customHeight="1">
+    <row r="137" ht="30" customHeight="1">
       <c r="A137" s="35" t="n"/>
-      <c r="B137" s="36" t="inlineStr">
+      <c r="B137" s="42" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C137" s="43" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="C137" s="37" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="D137" s="38" t="inlineStr">
+      <c r="D137" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E137" s="39" t="inlineStr">
-        <is>
-          <t>Caminar las seis cuadras de la Morgan a One Vanderbilt (~8-10 min).</t>
-        </is>
-      </c>
-      <c r="F137" s="37" t="inlineStr"/>
+      <c r="E137" s="45" t="inlineStr">
+        <is>
+          <t>★ MORGAN LIBRARY — GRATIS los viernes 17-20h: entrar 17:00 EN PUNTO y hacerla en una hora — la biblioteca son tres salas gloriosas (estanterías de nogal, la Biblia de Gutenberg): alcanza. RESERVA OBLIGATORIA, se libera el viernes 28 de agosto. Está a 8 min a pie de One Vanderbilt.</t>
+        </is>
+      </c>
+      <c r="F137" s="43" t="inlineStr">
+        <is>
+          <t>The Morgan Library &amp; Museum</t>
+        </is>
+      </c>
       <c r="G137" s="40" t="inlineStr"/>
       <c r="H137" s="41" t="inlineStr"/>
       <c r="I137" s="41" t="inlineStr"/>
     </row>
-    <row r="138" ht="30" customHeight="1">
+    <row r="138" ht="16" customHeight="1">
       <c r="A138" s="35" t="n"/>
-      <c r="B138" s="42" t="inlineStr">
+      <c r="B138" s="36" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C138" s="37" t="inlineStr">
         <is>
           <t>18:10</t>
         </is>
       </c>
-      <c r="C138" s="43" t="inlineStr">
-        <is>
-          <t>20:20</t>
-        </is>
-      </c>
-      <c r="D138" s="44" t="inlineStr">
+      <c r="D138" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E138" s="45" t="inlineStr">
-        <is>
-          <t>★★ SUMMIT ONE VANDERBILT — EL ARCO COMPLETO: entrada 18:10 con luz, el atardecer ~19:21 multiplicado por los espejos infinitos de Kusama, y la noche encendida hasta ~20:15. Ticket ATARDECER $57-63 — es la franja que primero se agota: reservar YA. NO está en ningún pase.</t>
-        </is>
-      </c>
-      <c r="F138" s="43" t="inlineStr">
-        <is>
-          <t>SUMMIT One Vanderbilt</t>
-        </is>
-      </c>
+      <c r="E138" s="39" t="inlineStr">
+        <is>
+          <t>Caminar las seis cuadras de la Morgan a One Vanderbilt (~8-10 min).</t>
+        </is>
+      </c>
+      <c r="F138" s="37" t="inlineStr"/>
       <c r="G138" s="40" t="inlineStr"/>
       <c r="H138" s="41" t="inlineStr"/>
       <c r="I138" s="41" t="inlineStr"/>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="35" t="n"/>
-      <c r="B139" s="36" t="inlineStr">
+      <c r="B139" s="42" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="C139" s="43" t="inlineStr">
         <is>
           <t>20:20</t>
         </is>
       </c>
-      <c r="C139" s="37" t="inlineStr">
-        <is>
-          <t>20:50</t>
-        </is>
-      </c>
-      <c r="D139" s="38" t="inlineStr">
+      <c r="D139" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E139" s="39" t="inlineStr">
-        <is>
-          <t>Bajar AL VILLAGE PRIMERO y cenar allá: 4/5/6 o 7 hasta 14 St-Union Sq y 1 hasta Christopher St (~25 min). Cenar cerca de Grand Central y bajar después llega justo; hacerlo al revés deja margen.</t>
-        </is>
-      </c>
-      <c r="F139" s="37" t="inlineStr"/>
+      <c r="E139" s="45" t="inlineStr">
+        <is>
+          <t>★★ SUMMIT ONE VANDERBILT — EL ARCO COMPLETO: entrada 18:10 con luz, el atardecer ~19:21 multiplicado por los espejos infinitos de Kusama, y la noche encendida hasta ~20:15. Ticket ATARDECER $57-63 — es la franja que primero se agota: reservar YA. NO está en ningún pase.</t>
+        </is>
+      </c>
+      <c r="F139" s="43" t="inlineStr">
+        <is>
+          <t>SUMMIT One Vanderbilt</t>
+        </is>
+      </c>
       <c r="G139" s="40" t="inlineStr"/>
       <c r="H139" s="41" t="inlineStr"/>
       <c r="I139" s="41" t="inlineStr"/>
@@ -36129,14 +36149,14 @@
       <c r="A140" s="35" t="n"/>
       <c r="B140" s="36" t="inlineStr">
         <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="C140" s="37" t="inlineStr">
+        <is>
           <t>20:50</t>
         </is>
       </c>
-      <c r="C140" s="37" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
       <c r="D140" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36144,7 +36164,7 @@
       </c>
       <c r="E140" s="39" t="inlineStr">
         <is>
-          <t>Cena en el West Village, a cinco minutos del club. El Vanguard NO sirve NADA de comida (lo dicen así: 'ni un maní') y no se permite entrar comida: lo que no cenen ahora, no se cena. 40 minutos alcanzan.</t>
+          <t>Bajar AL VILLAGE PRIMERO y cenar allá: 4/5/6 o 7 hasta 14 St-Union Sq y 1 hasta Christopher St (~25 min). Cenar cerca de Grand Central y bajar después llega justo; hacerlo al revés deja margen.</t>
         </is>
       </c>
       <c r="F140" s="37" t="inlineStr"/>
@@ -36156,14 +36176,14 @@
       <c r="A141" s="35" t="n"/>
       <c r="B141" s="36" t="inlineStr">
         <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="C141" s="37" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C141" s="37" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
       <c r="D141" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36171,7 +36191,7 @@
       </c>
       <c r="E141" s="39" t="inlineStr">
         <is>
-          <t>EN LA PUERTA DEL VANGUARD a las 21:30 EN PUNTO: el acomodo del segundo set arranca a esa hora y los asientos son POR ORDEN DE LLEGADA — la entrada es General Admission, no numerada. Con 123 asientos, los diez minutos de diferencia son estar frente al piano o contra la columna. El ticket lo dice: el acomodo tardío, con entrada o sin ella, queda a criterio del encargado.</t>
+          <t>Cena en el West Village, a cinco minutos del club. El Vanguard NO sirve NADA de comida (lo dicen así: 'ni un maní') y no se permite entrar comida: lo que no cenen ahora, no se cena. 40 minutos alcanzan.</t>
         </is>
       </c>
       <c r="F141" s="37" t="inlineStr"/>
@@ -36181,199 +36201,199 @@
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="35" t="n"/>
-      <c r="B142" s="42" t="inlineStr">
+      <c r="B142" s="36" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C142" s="37" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C142" s="43" t="inlineStr"/>
-      <c r="D142" s="44" t="inlineStr">
+      <c r="D142" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E142" s="45" t="inlineStr">
-        <is>
-          <t>★★ VILLAGE VANGUARD — JOHN PATITUCCI TRIO con Chris Potter y Brian Blade, SET DE LAS 22:00. Movido acá desde el martes para que vayan LOS DOS (pedido de Juan). El sótano triangular de 1935, 123 asientos, la acústica que grabó a Coltrane. ✔ ENTRADAS COMPRADAS el 26/8: 2 × General Admission $45 (#18741454 y #18741456), a nombre de Juan Pablo Garicoïts. Falta solo el mínimo de UNA CONSUMICIÓN por cabeza en la mesa (vale gaseosa, jugo o agua) — se paga ahí, aceptan tarjeta.</t>
-        </is>
-      </c>
-      <c r="F142" s="43" t="inlineStr">
-        <is>
-          <t>Village Vanguard</t>
-        </is>
-      </c>
+      <c r="E142" s="39" t="inlineStr">
+        <is>
+          <t>EN LA PUERTA DEL VANGUARD a las 21:30 EN PUNTO: el acomodo del segundo set arranca a esa hora y los asientos son POR ORDEN DE LLEGADA — la entrada es General Admission, no numerada. Con 123 asientos, los diez minutos de diferencia son estar frente al piano o contra la columna. El ticket lo dice: el acomodo tardío, con entrada o sin ella, queda a criterio del encargado.</t>
+        </is>
+      </c>
+      <c r="F142" s="37" t="inlineStr"/>
       <c r="G142" s="40" t="inlineStr"/>
       <c r="H142" s="41" t="inlineStr"/>
       <c r="I142" s="41" t="inlineStr"/>
     </row>
-    <row r="143" ht="32" customHeight="1">
-      <c r="A143" s="46" t="inlineStr">
-        <is>
-          <t>ALTERNATIVA / OJO:  EL CANJE DE ESTA NOCHE: para meter el Vanguard con Thais, SALIÓ BILL'S PLACE. No hay otra noche donde entre (Bill Saxton toca solo viernes y sábado, y el sábado está tomado por Peter Luger + el play + el Café Wha). Con las entradas ya compradas y sin cambios ni transferencias, el canje quedó CERRADO: Bill's Place sale del viaje. // EL WHITNEY, con los números verificados el 27/8: gratis todos los viernes de 17:00 a 22:00 (normal $30), y hoy pasan por Meatpacking, que es donde está. Coincide barrio, día y franja. El problema es el reloj y es serio: la Morgan también es hoy 17:00-20:00 y el SUMMIT entra 18:10. Meter el Whitney obliga a recortar el High Line o a soltar la Morgan, que ustedes tienen en 2 y el Whitney en 'quizás'. Si igual lo prefieren, el ticket gratis es OBLIGATORIO y hay que sacarlo antes. Si igual lo prefieren, el ticket gratis es OBLIGATORIO y el Whitney ahora cierra los martes. SI ALGO SALIERA MAL con el acomodo (llegar tarde y que no haya lugar): Mezzrow o Smalls quedan a cuatro cuadras ($25 con bebida, Smalls tiene jam de madrugada los viernes desde la 1:00), o el Blue Note — el 4 y 5 de septiembre toca Chief Adjuah.</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="22" customHeight="1">
-      <c r="A145" s="33" t="inlineStr">
+    <row r="143" ht="30" customHeight="1">
+      <c r="A143" s="35" t="n"/>
+      <c r="B143" s="42" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C143" s="43" t="inlineStr"/>
+      <c r="D143" s="44" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E143" s="45" t="inlineStr">
+        <is>
+          <t>★★ VILLAGE VANGUARD — JOHN PATITUCCI TRIO con Chris Potter y Brian Blade, SET DE LAS 22:00. Movido acá desde el martes para que vayan LOS DOS (pedido de Juan). El sótano triangular de 1935, 123 asientos, la acústica que grabó a Coltrane. ✔ ENTRADAS COMPRADAS el 26/8: 2 × General Admission $45 (#18741454 y #18741456), a nombre de Juan Pablo Garicoïts. Falta solo el mínimo de UNA CONSUMICIÓN por cabeza en la mesa (vale gaseosa, jugo o agua) — se paga ahí, aceptan tarjeta.</t>
+        </is>
+      </c>
+      <c r="F143" s="43" t="inlineStr">
+        <is>
+          <t>Village Vanguard</t>
+        </is>
+      </c>
+      <c r="G143" s="40" t="inlineStr"/>
+      <c r="H143" s="41" t="inlineStr"/>
+      <c r="I143" s="41" t="inlineStr"/>
+    </row>
+    <row r="144" ht="32" customHeight="1">
+      <c r="A144" s="46" t="inlineStr">
+        <is>
+          <t>ALTERNATIVA / OJO:  ⚠️ OJO CON LA MAÑANA, y es nuevo: Juan hizo el HIGH LINE, LITTLE ISLAND y el VESSEL el miércoles temprano, solo. Los tres siguen en el plan de hoy porque THAIS NO LOS VIO —el Vessel además lo tienen 2/2 y es imprescindible— así que sacarlos la perjudica a ella. Decidan en el momento: si Juan la acompaña igual, el High Line de día con ella es otro paseo y no se pierde nada; si prefieren no repetir, esa mañana libera de 9:15 a 13:00 y ahí entran las galerías de Chelsea con calma, o el Whitney, que hoy es gratis de 17 a 22 pero abre 10:30. // EL CANJE DE ESTA NOCHE: para meter el Vanguard con Thais, SALIÓ BILL'S PLACE. No hay otra noche donde entre (Bill Saxton toca solo viernes y sábado, y el sábado está tomado por Peter Luger + el play + el Café Wha). Con las entradas ya compradas y sin cambios ni transferencias, el canje quedó CERRADO: Bill's Place sale del viaje. // EL WHITNEY, con los números verificados el 27/8: gratis todos los viernes de 17:00 a 22:00 (normal $30), y hoy pasan por Meatpacking, que es donde está. Coincide barrio, día y franja. El problema es el reloj y es serio: la Morgan también es hoy 17:00-20:00 y el SUMMIT entra 18:10. Meter el Whitney obliga a recortar el High Line o a soltar la Morgan, que ustedes tienen en 2 y el Whitney en 'quizás'. Si igual lo prefieren, el ticket gratis es OBLIGATORIO y hay que sacarlo antes. Si igual lo prefieren, el ticket gratis es OBLIGATORIO y el Whitney ahora cierra los martes. SI ALGO SALIERA MAL con el acomodo (llegar tarde y que no haya lugar): Mezzrow o Smalls quedan a cuatro cuadras ($25 con bebida, Smalls tiene jam de madrugada los viernes desde la 1:00), o el Blue Note — el 4 y 5 de septiembre toca Chief Adjuah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="22" customHeight="1">
+      <c r="A146" s="33" t="inlineStr">
         <is>
           <t>DÍA 8 · Sábado 05/09 · Brooklyn, Peter Luger, un PLAY y Café Wha hasta la madrugada  —  base: The Beacon  ·  Ambos</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="32" customHeight="1">
-      <c r="A146" s="34" t="inlineStr">
+    <row r="147" ht="32" customHeight="1">
+      <c r="A147" s="34" t="inlineStr">
         <is>
           <t>La gran noche del viaje, rearmada a pedido: el musical SALIÓ y entraron un PLAY de Broadway a las 19:30 y el CAFÉ WHA a las 23:45 — el sótano del Village donde debutaron Dylan y Hendrix, con reserva gratis ya pedida por Eventbrite. La cena temprana en Peter Luger (17:00) ahora existe exactamente para esto: porterhouse → telón → medianoche de soul y funk. Frankel's sigue afuera (a un porterhouse no se llega con un pastrami encima) y Westlight sigue opcional. ⚠️ La noche termina ~1:15-1:30: el domingo no tiene NADA fijo hasta las 16:00.</t>
         </is>
       </c>
-    </row>
-    <row r="147" ht="30" customHeight="1">
-      <c r="A147" s="35" t="n"/>
-      <c r="B147" s="36" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="C147" s="37" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="D147" s="38" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="E147" s="39" t="inlineStr">
-        <is>
-          <t>Salir 8:15: 1/2/3 desde 72 St + transbordo a A/C hasta High St son ~40-45 min REALES. Llegar temprano a DUMBO es la diferencia entre la foto y la cola de fotos.</t>
-        </is>
-      </c>
-      <c r="F147" s="37" t="inlineStr"/>
-      <c r="G147" s="40" t="inlineStr"/>
-      <c r="H147" s="41" t="inlineStr"/>
-      <c r="I147" s="41" t="inlineStr"/>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="35" t="n"/>
-      <c r="B148" s="42" t="inlineStr">
+      <c r="B148" s="36" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="C148" s="37" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="C148" s="43" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="D148" s="44" t="inlineStr">
+      <c r="D148" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E148" s="45" t="inlineStr">
-        <is>
-          <t>★ Brooklyn Bridge Park y DUMBO — muelles reconvertidos con el skyline de Lower Manhattan de frente, y la foto del Manhattan Bridge encuadrado en Washington y Water.</t>
-        </is>
-      </c>
-      <c r="F148" s="43" t="inlineStr">
-        <is>
-          <t>Brooklyn Bridge Park</t>
-        </is>
-      </c>
+      <c r="E148" s="39" t="inlineStr">
+        <is>
+          <t>Salir 8:15: 1/2/3 desde 72 St + transbordo a A/C hasta High St son ~40-45 min REALES. Llegar temprano a DUMBO es la diferencia entre la foto y la cola de fotos.</t>
+        </is>
+      </c>
+      <c r="F148" s="37" t="inlineStr"/>
       <c r="G148" s="40" t="inlineStr"/>
       <c r="H148" s="41" t="inlineStr"/>
       <c r="I148" s="41" t="inlineStr"/>
     </row>
-    <row r="149" ht="16" customHeight="1">
+    <row r="149" ht="30" customHeight="1">
       <c r="A149" s="35" t="n"/>
-      <c r="B149" s="36" t="inlineStr">
+      <c r="B149" s="42" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C149" s="43" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="C149" s="37" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="D149" s="38" t="inlineStr">
+      <c r="D149" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E149" s="39" t="inlineStr">
-        <is>
-          <t>Brooklyn Heights Promenade — la postal clásica del skyline sobre el BQE.</t>
-        </is>
-      </c>
-      <c r="F149" s="37" t="inlineStr">
-        <is>
-          <t>Brooklyn Heights Promenade</t>
-        </is>
-      </c>
-      <c r="G149" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~8 min a pie · 0.6 km · estimado</t>
-        </is>
-      </c>
+      <c r="E149" s="45" t="inlineStr">
+        <is>
+          <t>★ Brooklyn Bridge Park y DUMBO — muelles reconvertidos con el skyline de Lower Manhattan de frente, y la foto del Manhattan Bridge encuadrado en Washington y Water.</t>
+        </is>
+      </c>
+      <c r="F149" s="43" t="inlineStr">
+        <is>
+          <t>Brooklyn Bridge Park</t>
+        </is>
+      </c>
+      <c r="G149" s="40" t="inlineStr"/>
       <c r="H149" s="41" t="inlineStr"/>
       <c r="I149" s="41" t="inlineStr"/>
     </row>
-    <row r="150" ht="30" customHeight="1">
+    <row r="150" ht="16" customHeight="1">
       <c r="A150" s="35" t="n"/>
-      <c r="B150" s="42" t="inlineStr">
+      <c r="B150" s="36" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C150" s="37" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="C150" s="43" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="D150" s="44" t="inlineStr">
+      <c r="D150" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E150" s="45" t="inlineStr">
-        <is>
-          <t>★ NEW YORK TRANSIT MUSEUM — una estación de subte clausurada de 1936 con 20 vagones históricos en las vías originales; se puede subir a todos. $10. Cierra lunes y martes, así que hoy es el día.</t>
-        </is>
-      </c>
-      <c r="F150" s="43" t="inlineStr">
-        <is>
-          <t>New York Transit Museum</t>
-        </is>
-      </c>
-      <c r="G150" s="40" t="inlineStr"/>
+      <c r="E150" s="39" t="inlineStr">
+        <is>
+          <t>Brooklyn Heights Promenade — la postal clásica del skyline sobre el BQE.</t>
+        </is>
+      </c>
+      <c r="F150" s="37" t="inlineStr">
+        <is>
+          <t>Brooklyn Heights Promenade</t>
+        </is>
+      </c>
+      <c r="G150" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~8 min a pie · 0.6 km · estimado</t>
+        </is>
+      </c>
       <c r="H150" s="41" t="inlineStr"/>
       <c r="I150" s="41" t="inlineStr"/>
     </row>
-    <row r="151" ht="16" customHeight="1">
+    <row r="151" ht="30" customHeight="1">
       <c r="A151" s="35" t="n"/>
-      <c r="B151" s="36" t="inlineStr">
+      <c r="B151" s="42" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C151" s="43" t="inlineStr">
         <is>
           <t>12:45</t>
         </is>
       </c>
-      <c r="C151" s="37" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="D151" s="38" t="inlineStr">
+      <c r="D151" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E151" s="39" t="inlineStr">
-        <is>
-          <t>Almuerzo en Downtown Brooklyn.</t>
-        </is>
-      </c>
-      <c r="F151" s="37" t="inlineStr"/>
+      <c r="E151" s="45" t="inlineStr">
+        <is>
+          <t>★ NEW YORK TRANSIT MUSEUM — una estación de subte clausurada de 1936 con 20 vagones históricos en las vías originales; se puede subir a todos. $10. Cierra lunes y martes, así que hoy es el día.</t>
+        </is>
+      </c>
+      <c r="F151" s="43" t="inlineStr">
+        <is>
+          <t>New York Transit Museum</t>
+        </is>
+      </c>
       <c r="G151" s="40" t="inlineStr"/>
       <c r="H151" s="41" t="inlineStr"/>
       <c r="I151" s="41" t="inlineStr"/>
@@ -36382,14 +36402,14 @@
       <c r="A152" s="35" t="n"/>
       <c r="B152" s="36" t="inlineStr">
         <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C152" s="37" t="inlineStr">
+        <is>
           <t>13:45</t>
         </is>
       </c>
-      <c r="C152" s="37" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="D152" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36397,7 +36417,7 @@
       </c>
       <c r="E152" s="39" t="inlineStr">
         <is>
-          <t>Subte a Williamsburg.</t>
+          <t>Almuerzo en Downtown Brooklyn.</t>
         </is>
       </c>
       <c r="F152" s="37" t="inlineStr"/>
@@ -36405,84 +36425,76 @@
       <c r="H152" s="41" t="inlineStr"/>
       <c r="I152" s="41" t="inlineStr"/>
     </row>
-    <row r="153" ht="30" customHeight="1">
+    <row r="153" ht="16" customHeight="1">
       <c r="A153" s="35" t="n"/>
-      <c r="B153" s="42" t="inlineStr">
+      <c r="B153" s="36" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="C153" s="37" t="inlineStr">
         <is>
           <t>14:15</t>
         </is>
       </c>
-      <c r="C153" s="43" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="D153" s="44" t="inlineStr">
+      <c r="D153" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E153" s="45" t="inlineStr">
-        <is>
-          <t>★ Domino Park — ex refinería de azúcar; el paseo elevado pasa entre la maquinaria industrial conservada, con el Williamsburg Bridge y Midtown enfrente.</t>
-        </is>
-      </c>
-      <c r="F153" s="43" t="inlineStr">
-        <is>
-          <t>Domino Park</t>
-        </is>
-      </c>
+      <c r="E153" s="39" t="inlineStr">
+        <is>
+          <t>Subte a Williamsburg.</t>
+        </is>
+      </c>
+      <c r="F153" s="37" t="inlineStr"/>
       <c r="G153" s="40" t="inlineStr"/>
       <c r="H153" s="41" t="inlineStr"/>
       <c r="I153" s="41" t="inlineStr"/>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="35" t="n"/>
-      <c r="B154" s="36" t="inlineStr">
+      <c r="B154" s="42" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="C154" s="43" t="inlineStr">
         <is>
           <t>15:15</t>
         </is>
       </c>
-      <c r="C154" s="37" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="D154" s="38" t="inlineStr">
+      <c r="D154" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E154" s="39" t="inlineStr">
-        <is>
-          <t>Paseo por Williamsburg: Bedford Ave, disquerías y vintage. ★ ACÁ ENTRA HEATONIST (121 Wythe Ave, a una cuadra de Bedford): la tienda insignia de salsas picantes, con más de 100 para probar en el local y el lineup completo de Hot Ones. Abre 12-19 todos los días, así que a esta hora está abierta y les queda de camino al Williamsburg Bridge. OPCIONAL si quieren la panorámica: Westlight (piso 22, sin cover, un trago) — lo bajaron a 'quizás'. NO comer nada: lo que viene lo merece.</t>
-        </is>
-      </c>
-      <c r="F154" s="37" t="inlineStr">
-        <is>
-          <t>HEATONIST Williamsburg</t>
-        </is>
-      </c>
-      <c r="G154" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~20 min a pie (1.2 km) o 🚇 ~15 min · estimado</t>
-        </is>
-      </c>
+      <c r="E154" s="45" t="inlineStr">
+        <is>
+          <t>★ Domino Park — ex refinería de azúcar; el paseo elevado pasa entre la maquinaria industrial conservada, con el Williamsburg Bridge y Midtown enfrente.</t>
+        </is>
+      </c>
+      <c r="F154" s="43" t="inlineStr">
+        <is>
+          <t>Domino Park</t>
+        </is>
+      </c>
+      <c r="G154" s="40" t="inlineStr"/>
       <c r="H154" s="41" t="inlineStr"/>
       <c r="I154" s="41" t="inlineStr"/>
     </row>
-    <row r="155" ht="16" customHeight="1">
+    <row r="155" ht="30" customHeight="1">
       <c r="A155" s="35" t="n"/>
       <c r="B155" s="36" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C155" s="37" t="inlineStr">
+        <is>
           <t>16:45</t>
         </is>
       </c>
-      <c r="C155" s="37" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="D155" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36490,142 +36502,150 @@
       </c>
       <c r="E155" s="39" t="inlineStr">
         <is>
-          <t>Caminar por Bedford/Driggs hasta el pie del Williamsburg Bridge (~15 min).</t>
-        </is>
-      </c>
-      <c r="F155" s="37" t="inlineStr"/>
-      <c r="G155" s="40" t="inlineStr"/>
+          <t>Paseo por Williamsburg: Bedford Ave, disquerías y vintage. ★ ACÁ ENTRA HEATONIST (121 Wythe Ave, a una cuadra de Bedford): la tienda insignia de salsas picantes, con más de 100 para probar en el local y el lineup completo de Hot Ones. Abre 12-19 todos los días, así que a esta hora está abierta y les queda de camino al Williamsburg Bridge. OPCIONAL si quieren la panorámica: Westlight (piso 22, sin cover, un trago) — lo bajaron a 'quizás'. NO comer nada: lo que viene lo merece.</t>
+        </is>
+      </c>
+      <c r="F155" s="37" t="inlineStr">
+        <is>
+          <t>HEATONIST Williamsburg</t>
+        </is>
+      </c>
+      <c r="G155" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~20 min a pie (1.2 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H155" s="41" t="inlineStr"/>
       <c r="I155" s="41" t="inlineStr"/>
     </row>
-    <row r="156" ht="30" customHeight="1">
+    <row r="156" ht="16" customHeight="1">
       <c r="A156" s="35" t="n"/>
-      <c r="B156" s="42" t="inlineStr">
+      <c r="B156" s="36" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C156" s="37" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="C156" s="43" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="D156" s="44" t="inlineStr">
+      <c r="D156" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E156" s="45" t="inlineStr">
-        <is>
-          <t>★★ PETER LUGER (178 Broadway) — el porterhouse for two de 1887, dry-aged en el sótano, con la tocineta gruesa de entrada. ~$160-200 los dos con sides y propina. ⚠️ SIN TARJETAS DE CRÉDITO: efectivo, débito US o cheque — llevar cash. Cena temprana a propósito: el teatro espera. RESERVA EN RESY YA.</t>
-        </is>
-      </c>
-      <c r="F156" s="43" t="inlineStr">
-        <is>
-          <t>Peter Luger Steak House</t>
-        </is>
-      </c>
+      <c r="E156" s="39" t="inlineStr">
+        <is>
+          <t>Caminar por Bedford/Driggs hasta el pie del Williamsburg Bridge (~15 min).</t>
+        </is>
+      </c>
+      <c r="F156" s="37" t="inlineStr"/>
       <c r="G156" s="40" t="inlineStr"/>
       <c r="H156" s="41" t="inlineStr"/>
       <c r="I156" s="41" t="inlineStr"/>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="35" t="n"/>
-      <c r="B157" s="36" t="inlineStr">
+      <c r="B157" s="42" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C157" s="43" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="C157" s="37" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="D157" s="38" t="inlineStr">
+      <c r="D157" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E157" s="39" t="inlineStr">
-        <is>
-          <t>A la zona de teatros: subte J desde Marcy Av hasta Essex St y F hasta 42 St-Bryant Park (~35 min con transbordo), o directamente Uber al teatro (~20-25 min, $25-35 — un sábado a la noche el puente puede estar cargado).</t>
-        </is>
-      </c>
-      <c r="F157" s="37" t="inlineStr"/>
+      <c r="E157" s="45" t="inlineStr">
+        <is>
+          <t>★★ PETER LUGER (178 Broadway) — el porterhouse for two de 1887, dry-aged en el sótano, con la tocineta gruesa de entrada. ~$160-200 los dos con sides y propina. ⚠️ SIN TARJETAS DE CRÉDITO: efectivo, débito US o cheque — llevar cash. Cena temprana a propósito: el teatro espera. RESERVA EN RESY YA.</t>
+        </is>
+      </c>
+      <c r="F157" s="43" t="inlineStr">
+        <is>
+          <t>Peter Luger Steak House</t>
+        </is>
+      </c>
       <c r="G157" s="40" t="inlineStr"/>
       <c r="H157" s="41" t="inlineStr"/>
       <c r="I157" s="41" t="inlineStr"/>
     </row>
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="35" t="n"/>
-      <c r="B158" s="42" t="inlineStr">
+      <c r="B158" s="36" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C158" s="37" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="C158" s="43" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="D158" s="44" t="inlineStr">
+      <c r="D158" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E158" s="45" t="inlineStr">
-        <is>
-          <t>★★ PLAY DE BROADWAY — mi recomendación: STRANGER THINGS: THE FIRST SHADOW (Marquis, desde ~$76): la maquinaria escénica que ganó el Tony — para quien viene de Mercer Labs, el mismo músculo llevado al teatro. Alternativas esa semana: Harry Potter and the Cursed Child, Paranormal Activity, The Imaginary Invalid. COMPRA FIRME esta semana y verificar el horario real de la función (19:00/19:30/20:00): tiene que terminar ~22:00 para lo que sigue.</t>
-        </is>
-      </c>
-      <c r="F158" s="43" t="inlineStr">
-        <is>
-          <t>Stranger Things: The First Shadow (play)</t>
-        </is>
-      </c>
+      <c r="E158" s="39" t="inlineStr">
+        <is>
+          <t>A la zona de teatros: subte J desde Marcy Av hasta Essex St y F hasta 42 St-Bryant Park (~35 min con transbordo), o directamente Uber al teatro (~20-25 min, $25-35 — un sábado a la noche el puente puede estar cargado).</t>
+        </is>
+      </c>
+      <c r="F158" s="37" t="inlineStr"/>
       <c r="G158" s="40" t="inlineStr"/>
       <c r="H158" s="41" t="inlineStr"/>
       <c r="I158" s="41" t="inlineStr"/>
     </row>
-    <row r="159" ht="16" customHeight="1">
+    <row r="159" ht="30" customHeight="1">
       <c r="A159" s="35" t="n"/>
-      <c r="B159" s="36" t="inlineStr">
+      <c r="B159" s="42" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C159" s="43" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C159" s="37" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="D159" s="38" t="inlineStr">
+      <c r="D159" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E159" s="39" t="inlineStr">
-        <is>
-          <t>Subte 1 desde Times Sq hasta Christopher St (~15 min) y caminar al corazón del Village.</t>
-        </is>
-      </c>
-      <c r="F159" s="37" t="inlineStr"/>
+      <c r="E159" s="45" t="inlineStr">
+        <is>
+          <t>★★ PLAY DE BROADWAY — mi recomendación: STRANGER THINGS: THE FIRST SHADOW (Marquis, desde ~$76): la maquinaria escénica que ganó el Tony — para quien viene de Mercer Labs, el mismo músculo llevado al teatro. Alternativas esa semana: Harry Potter and the Cursed Child, Paranormal Activity, The Imaginary Invalid. COMPRA FIRME esta semana y verificar el horario real de la función (19:00/19:30/20:00): tiene que terminar ~22:00 para lo que sigue.</t>
+        </is>
+      </c>
+      <c r="F159" s="43" t="inlineStr">
+        <is>
+          <t>Stranger Things: The First Shadow (play)</t>
+        </is>
+      </c>
       <c r="G159" s="40" t="inlineStr"/>
       <c r="H159" s="41" t="inlineStr"/>
       <c r="I159" s="41" t="inlineStr"/>
     </row>
-    <row r="160" ht="30" customHeight="1">
+    <row r="160" ht="16" customHeight="1">
       <c r="A160" s="35" t="n"/>
       <c r="B160" s="36" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C160" s="37" t="inlineStr">
+        <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="C160" s="37" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
       <c r="D160" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36633,7 +36653,7 @@
       </c>
       <c r="E160" s="39" t="inlineStr">
         <is>
-          <t>Paseo sin apuro por Bleecker y MacDougal — la esquina folk de los 60s de noche, un café o un trago corto. El único objetivo real: estar en la puerta del Wha a las 23:10.</t>
+          <t>Subte 1 desde Times Sq hasta Christopher St (~15 min) y caminar al corazón del Village.</t>
         </is>
       </c>
       <c r="F160" s="37" t="inlineStr"/>
@@ -36643,106 +36663,102 @@
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="35" t="n"/>
-      <c r="B161" s="42" t="inlineStr">
+      <c r="B161" s="36" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C161" s="37" t="inlineStr">
         <is>
           <t>23:15</t>
         </is>
       </c>
-      <c r="C161" s="43" t="inlineStr"/>
-      <c r="D161" s="44" t="inlineStr">
+      <c r="D161" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E161" s="45" t="inlineStr">
-        <is>
-          <t>★★ CAFÉ WHA — LLEGAR 23:10-23:15: la reserva de Eventbrite NO garantiza admisión y a las 23:30 EN PUNTO liberan los asientos vacíos al standby. TODOS los de la reserva presentes. Set 2 de la house band 23:45-~1:15: soul y funk a máquina en el sótano donde debutaron Dylan, Hendrix y Springsteen. $20 por cabeza van a la cuenta + consumo. Vuelta: subte 1 Christopher St → 72 St (~25 min) o taxi.</t>
-        </is>
-      </c>
-      <c r="F161" s="43" t="inlineStr">
-        <is>
-          <t>Cafe Wha?</t>
-        </is>
-      </c>
+      <c r="E161" s="39" t="inlineStr">
+        <is>
+          <t>Paseo sin apuro por Bleecker y MacDougal — la esquina folk de los 60s de noche, un café o un trago corto. El único objetivo real: estar en la puerta del Wha a las 23:10.</t>
+        </is>
+      </c>
+      <c r="F161" s="37" t="inlineStr"/>
       <c r="G161" s="40" t="inlineStr"/>
       <c r="H161" s="41" t="inlineStr"/>
       <c r="I161" s="41" t="inlineStr"/>
     </row>
-    <row r="162" ht="32" customHeight="1">
-      <c r="A162" s="46" t="inlineStr">
+    <row r="162" ht="30" customHeight="1">
+      <c r="A162" s="35" t="n"/>
+      <c r="B162" s="42" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="C162" s="43" t="inlineStr"/>
+      <c r="D162" s="44" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E162" s="45" t="inlineStr">
+        <is>
+          <t>★★ CAFÉ WHA — LLEGAR 23:10-23:15: la reserva de Eventbrite NO garantiza admisión y a las 23:30 EN PUNTO liberan los asientos vacíos al standby. TODOS los de la reserva presentes. Set 2 de la house band 23:45-~1:15: soul y funk a máquina en el sótano donde debutaron Dylan, Hendrix y Springsteen. $20 por cabeza van a la cuenta + consumo. Vuelta: subte 1 Christopher St → 72 St (~25 min) o taxi.</t>
+        </is>
+      </c>
+      <c r="F162" s="43" t="inlineStr">
+        <is>
+          <t>Cafe Wha?</t>
+        </is>
+      </c>
+      <c r="G162" s="40" t="inlineStr"/>
+      <c r="H162" s="41" t="inlineStr"/>
+      <c r="I162" s="41" t="inlineStr"/>
+    </row>
+    <row r="163" ht="32" customHeight="1">
+      <c r="A163" s="46" t="inlineStr">
         <is>
           <t>ALTERNATIVA / OJO:  SOBRE PETER LUGER: la mesa de las 17:00 es la realista — y ahora es la única que funciona: el play manda. PLAN B si no hay mesa: correr Peter Luger al ALMUERZO del mismo día (12:45). // SI EL CANSANCIO GANA A LAS 22:00: el Café Wha es la pieza sacrificable — la reserva es gratis y no penaliza no ir; el play, pagado, no. // Sigue afuera: Bar LunÀtico y Barbès (Bed-Stuy/Park Slope), sin noche posible.</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="22" customHeight="1">
-      <c r="A164" s="33" t="inlineStr">
+    <row r="165" ht="22" customHeight="1">
+      <c r="A165" s="33" t="inlineStr">
         <is>
           <t>DÍA 9 · Domingo 06/09 · Checkout, Central Park, Roosevelt Island, MoMA PS1 y vuelo  —  base: The Beacon (checkout) → EWR  ·  Ambos</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="32" customHeight="1">
-      <c r="A165" s="34" t="inlineStr">
+    <row r="166" ht="32" customHeight="1">
+      <c r="A166" s="34" t="inlineStr">
         <is>
           <t>El día arranca con el CHECKOUT de The Beacon: hacerlo temprano y dejar las valijas en el bell desk libera el día entero. El vuelo sale 23:40, así que hay margen — pero es el domingo del fin de semana largo de Labor Day, la noche de mayor tráfico del año, y EWR va a estar cargado. Por eso todo queda cerca y se sale con 2h45 de anticipación. EL CAMBIO DEL ÚLTIMO DÍA: entra MOMA PS1 y sale el Guggenheim. Se verificó el 27/8 que la rotonda del Guggenheim está cerrada hasta el 17/9 —no se camina la rampa, que es la razón para ir— y PS1 resultó ser gratis, abierto hasta las 18 los domingos, a 1,2 km de Roosevelt Island y con «Greater New York 2026» en pie hasta el 7/9. Era el último imprescindible que quedaba afuera del viaje. El Guggenheim queda escrito como alternativa por si cambian de idea.</t>
         </is>
       </c>
-    </row>
-    <row r="166" ht="30" customHeight="1">
-      <c r="A166" s="35" t="n"/>
-      <c r="B166" s="36" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="C166" s="37" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="D166" s="38" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="E166" s="39" t="inlineStr">
-        <is>
-          <t>Desayuno SIN despertador temprano: anoche terminó ~1:30 en el Village y lo único con hora fija hoy es el PS1, que cierra a las 18:00. Dormir un poco más está permitido.</t>
-        </is>
-      </c>
-      <c r="F166" s="37" t="inlineStr"/>
-      <c r="G166" s="40" t="inlineStr"/>
-      <c r="H166" s="41" t="inlineStr"/>
-      <c r="I166" s="41" t="inlineStr"/>
     </row>
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="35" t="n"/>
-      <c r="B167" s="42" t="inlineStr">
+      <c r="B167" s="36" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C167" s="37" t="inlineStr">
         <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="C167" s="43" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="D167" s="44" t="inlineStr">
+      <c r="D167" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E167" s="45" t="inlineStr">
-        <is>
-          <t>★ CHECKOUT de The Beacon y dejar las valijas en el bell desk. El checkout formal suele ser 11:00-12:00, pero hacerlo antes libera el día.</t>
-        </is>
-      </c>
-      <c r="F167" s="43" t="inlineStr">
-        <is>
-          <t>Hotel The Beacon (3-6 sep)</t>
-        </is>
-      </c>
+      <c r="E167" s="39" t="inlineStr">
+        <is>
+          <t>Desayuno SIN despertador temprano: anoche terminó ~1:30 en el Village y lo único con hora fija hoy es el PS1, que cierra a las 18:00. Dormir un poco más está permitido.</t>
+        </is>
+      </c>
+      <c r="F167" s="37" t="inlineStr"/>
       <c r="G167" s="40" t="inlineStr"/>
       <c r="H167" s="41" t="inlineStr"/>
       <c r="I167" s="41" t="inlineStr"/>
@@ -36751,14 +36767,14 @@
       <c r="A168" s="35" t="n"/>
       <c r="B168" s="42" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="C168" s="43" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="C168" s="43" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="D168" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36766,61 +36782,65 @@
       </c>
       <c r="E168" s="45" t="inlineStr">
         <is>
-          <t>★ CENTRAL PARK cruzando de oeste a este: Bethesda Terrace, el Ramble, Bow Bridge. Se entra por la 72 desde Broadway, a tres cuadras del hotel.</t>
+          <t>★ CHECKOUT de The Beacon y dejar las valijas en el bell desk. El checkout formal suele ser 11:00-12:00, pero hacerlo antes libera el día.</t>
         </is>
       </c>
       <c r="F168" s="43" t="inlineStr">
         <is>
-          <t>Central Park</t>
-        </is>
-      </c>
-      <c r="G168" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~20 min a pie (1.5 km) o 🚇 ~15 min · estimado</t>
-        </is>
-      </c>
+          <t>Hotel The Beacon (3-6 sep)</t>
+        </is>
+      </c>
+      <c r="G168" s="40" t="inlineStr"/>
       <c r="H168" s="41" t="inlineStr"/>
       <c r="I168" s="41" t="inlineStr"/>
     </row>
-    <row r="169" ht="16" customHeight="1">
+    <row r="169" ht="30" customHeight="1">
       <c r="A169" s="35" t="n"/>
-      <c r="B169" s="36" t="inlineStr">
+      <c r="B169" s="42" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="C169" s="43" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="C169" s="37" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="D169" s="38" t="inlineStr">
+      <c r="D169" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E169" s="39" t="inlineStr">
-        <is>
-          <t>Almuerzo en el Upper East Side, saliendo del parque por la Quinta.</t>
-        </is>
-      </c>
-      <c r="F169" s="37" t="inlineStr"/>
-      <c r="G169" s="40" t="inlineStr"/>
+      <c r="E169" s="45" t="inlineStr">
+        <is>
+          <t>★ CENTRAL PARK cruzando de oeste a este: Bethesda Terrace, el Ramble, Bow Bridge. Se entra por la 72 desde Broadway, a tres cuadras del hotel.</t>
+        </is>
+      </c>
+      <c r="F169" s="43" t="inlineStr">
+        <is>
+          <t>Central Park</t>
+        </is>
+      </c>
+      <c r="G169" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~20 min a pie (1.5 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H169" s="41" t="inlineStr"/>
       <c r="I169" s="41" t="inlineStr"/>
     </row>
-    <row r="170" ht="30" customHeight="1">
+    <row r="170" ht="16" customHeight="1">
       <c r="A170" s="35" t="n"/>
       <c r="B170" s="36" t="inlineStr">
         <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C170" s="37" t="inlineStr">
+        <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="C170" s="37" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="D170" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36828,7 +36848,7 @@
       </c>
       <c r="E170" s="39" t="inlineStr">
         <is>
-          <t>Bajar a 59 St y 2ª Av: subte 6 desde 68 St-Hunter College (el 4/5 exprés NO para ahí), o caminando por la Quinta si el día está lindo.</t>
+          <t>Almuerzo en el Upper East Side, saliendo del parque por la Quinta.</t>
         </is>
       </c>
       <c r="F170" s="37" t="inlineStr"/>
@@ -36838,60 +36858,56 @@
     </row>
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="35" t="n"/>
-      <c r="B171" s="42" t="inlineStr">
+      <c r="B171" s="36" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C171" s="37" t="inlineStr">
         <is>
           <t>13:50</t>
         </is>
       </c>
-      <c r="C171" s="43" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="D171" s="44" t="inlineStr">
+      <c r="D171" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E171" s="45" t="inlineStr">
-        <is>
-          <t>★ ROOSEVELT ISLAND TRAMWAY ($3, OMNY) — cruza el East River a 76 metros de altura con el Queensboro Bridge al lado. Es la vista de $50 por el precio de un viaje de subte.</t>
-        </is>
-      </c>
-      <c r="F171" s="43" t="inlineStr">
-        <is>
-          <t>Roosevelt Island Tramway</t>
-        </is>
-      </c>
+      <c r="E171" s="39" t="inlineStr">
+        <is>
+          <t>Bajar a 59 St y 2ª Av: subte 6 desde 68 St-Hunter College (el 4/5 exprés NO para ahí), o caminando por la Quinta si el día está lindo.</t>
+        </is>
+      </c>
+      <c r="F171" s="37" t="inlineStr"/>
       <c r="G171" s="40" t="inlineStr"/>
       <c r="H171" s="41" t="inlineStr"/>
       <c r="I171" s="41" t="inlineStr"/>
     </row>
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="35" t="n"/>
-      <c r="B172" s="36" t="inlineStr">
+      <c r="B172" s="42" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="C172" s="43" t="inlineStr">
         <is>
           <t>14:25</t>
         </is>
       </c>
-      <c r="C172" s="37" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="D172" s="38" t="inlineStr">
+      <c r="D172" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E172" s="39" t="inlineStr">
-        <is>
-          <t>FDR Four Freedoms Park — del teleférico son ~20 min a pie por el borde del río. La última obra de Louis Kahn: granito, plátanos y una sala abierta al río apuntando a Manhattan. Gratis y vacía. Se pasa por las ruinas del Smallpox Hospital.</t>
-        </is>
-      </c>
-      <c r="F172" s="37" t="inlineStr">
-        <is>
-          <t>FDR Four Freedoms Park</t>
+      <c r="E172" s="45" t="inlineStr">
+        <is>
+          <t>★ ROOSEVELT ISLAND TRAMWAY ($3, OMNY) — cruza el East River a 76 metros de altura con el Queensboro Bridge al lado. Es la vista de $50 por el precio de un viaje de subte.</t>
+        </is>
+      </c>
+      <c r="F172" s="43" t="inlineStr">
+        <is>
+          <t>Roosevelt Island Tramway</t>
         </is>
       </c>
       <c r="G172" s="40" t="inlineStr"/>
@@ -36902,14 +36918,14 @@
       <c r="A173" s="35" t="n"/>
       <c r="B173" s="36" t="inlineStr">
         <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="C173" s="37" t="inlineStr">
+        <is>
           <t>15:05</t>
         </is>
       </c>
-      <c r="C173" s="37" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="D173" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36917,10 +36933,14 @@
       </c>
       <c r="E173" s="39" t="inlineStr">
         <is>
-          <t>SALIR 15:05 de Four Freedoms Park y caminar 15 min al norte por el borde del río hasta la ESTACIÓN DEL F, que está en el medio de la isla (Main St y Roosevelt Island Bridge). Hoy NO se vuelve en teleférico: se cruza a Queens por abajo.</t>
-        </is>
-      </c>
-      <c r="F173" s="37" t="inlineStr"/>
+          <t>FDR Four Freedoms Park — del teleférico son ~20 min a pie por el borde del río. La última obra de Louis Kahn: granito, plátanos y una sala abierta al río apuntando a Manhattan. Gratis y vacía. Se pasa por las ruinas del Smallpox Hospital.</t>
+        </is>
+      </c>
+      <c r="F173" s="37" t="inlineStr">
+        <is>
+          <t>FDR Four Freedoms Park</t>
+        </is>
+      </c>
       <c r="G173" s="40" t="inlineStr"/>
       <c r="H173" s="41" t="inlineStr"/>
       <c r="I173" s="41" t="inlineStr"/>
@@ -36929,14 +36949,14 @@
       <c r="A174" s="35" t="n"/>
       <c r="B174" s="36" t="inlineStr">
         <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="C174" s="37" t="inlineStr">
+        <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="C174" s="37" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="D174" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36944,7 +36964,7 @@
       </c>
       <c r="E174" s="39" t="inlineStr">
         <is>
-          <t>Subte F, UNA parada: Roosevelt Island → 21 St-Queensbridge (~4 min). Salir y caminar 12-15 min al sur por 21st St / Jackson Ave.</t>
+          <t>SALIR 15:05 de Four Freedoms Park y caminar 15 min al norte por el borde del río hasta la ESTACIÓN DEL F, que está en el medio de la isla (Main St y Roosevelt Island Bridge). Hoy NO se vuelve en teleférico: se cruza a Queens por abajo.</t>
         </is>
       </c>
       <c r="F174" s="37" t="inlineStr"/>
@@ -36954,58 +36974,58 @@
     </row>
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="35" t="n"/>
-      <c r="B175" s="42" t="inlineStr">
+      <c r="B175" s="36" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C175" s="37" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="C175" s="43" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="D175" s="44" t="inlineStr">
+      <c r="D175" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E175" s="45" t="inlineStr">
-        <is>
-          <t>★★ MOMA PS1 — el último imprescindible del viaje, y entra gratis. Escuela pública de 1892 reconvertida en el laboratorio del MoMA: lo que no se anima a mostrar en la Quinta Avenida. VERIFICADO el 27/8: ENTRADA GRATUITA para todos, abre domingos 12:00-18:00, y «Greater New York 2026» —la encuesta insignia de la casa, que se hace cada cinco años— sigue en pie hasta el 7 de septiembre, o sea que la agarran por un día. Más el Courtyard Commission de Precious Okoyomon al aire libre. Dos horas holgadas hasta las 17:45.</t>
-        </is>
-      </c>
-      <c r="F175" s="43" t="inlineStr">
-        <is>
-          <t>MoMA PS1</t>
-        </is>
-      </c>
+      <c r="E175" s="39" t="inlineStr">
+        <is>
+          <t>Subte F, UNA parada: Roosevelt Island → 21 St-Queensbridge (~4 min). Salir y caminar 12-15 min al sur por 21st St / Jackson Ave.</t>
+        </is>
+      </c>
+      <c r="F175" s="37" t="inlineStr"/>
       <c r="G175" s="40" t="inlineStr"/>
       <c r="H175" s="41" t="inlineStr"/>
       <c r="I175" s="41" t="inlineStr"/>
     </row>
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="35" t="n"/>
-      <c r="B176" s="36" t="inlineStr">
+      <c r="B176" s="42" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C176" s="43" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="C176" s="37" t="inlineStr">
-        <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="D176" s="38" t="inlineStr">
+      <c r="D176" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E176" s="39" t="inlineStr">
-        <is>
-          <t>Del PS1 al hotel: subte 7 desde Court Sq hasta Times Sq y 1/2/3 hasta 72 St, o E/M hasta 53 St (~45 min). Llegan 18:30, justo para las valijas. El vuelo no se toca.</t>
-        </is>
-      </c>
-      <c r="F176" s="37" t="inlineStr"/>
+      <c r="E176" s="45" t="inlineStr">
+        <is>
+          <t>★★ MOMA PS1 — el último imprescindible del viaje, y entra gratis. Escuela pública de 1892 reconvertida en el laboratorio del MoMA: lo que no se anima a mostrar en la Quinta Avenida. VERIFICADO el 27/8: ENTRADA GRATUITA para todos, abre domingos 12:00-18:00, y «Greater New York 2026» —la encuesta insignia de la casa, que se hace cada cinco años— sigue en pie hasta el 7 de septiembre, o sea que la agarran por un día. Más el Courtyard Commission de Precious Okoyomon al aire libre. Dos horas holgadas hasta las 17:45.</t>
+        </is>
+      </c>
+      <c r="F176" s="43" t="inlineStr">
+        <is>
+          <t>MoMA PS1</t>
+        </is>
+      </c>
       <c r="G176" s="40" t="inlineStr"/>
       <c r="H176" s="41" t="inlineStr"/>
       <c r="I176" s="41" t="inlineStr"/>
@@ -37014,14 +37034,14 @@
       <c r="A177" s="35" t="n"/>
       <c r="B177" s="36" t="inlineStr">
         <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="C177" s="37" t="inlineStr">
+        <is>
           <t>18:20</t>
         </is>
       </c>
-      <c r="C177" s="37" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
       <c r="D177" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -37029,7 +37049,7 @@
       </c>
       <c r="E177" s="39" t="inlineStr">
         <is>
-          <t>◇ SI PREFIEREN EL GUGGENHEIM, sigue estando y este bloque se ignora: pay-what-you-wish domingos 16:00-17:30 (mínimo $1) y entrada rebajada a $16 el resto del horario. ⚠️ PERO la rotonda está CERRADA del 3/8 al 17/9 por el montaje de Taryn Simon: no se camina la rampa —que es la razón para ir— y avisan que puede haber ruido de obra. Quedan las torres 4, 5 y 7 con «Guggenheim Pop» (Lichtenstein, Warhol, Oldenburg, Cattelan) y la colección Thannhauser. Para hacerlo: en vez de cruzar a Queens, teleférico de vuelta y subte 4/5/6 de 59 St a 86 St, y hay que salir del FDR Park 15:05 para entrar 16:00 — la ventana a voluntad va hasta las 17:30 y el museo cierra ahí.</t>
+          <t>Del PS1 al hotel: subte 7 desde Court Sq hasta Times Sq y 1/2/3 hasta 72 St, o E/M hasta 53 St (~45 min). Llegan 18:30, justo para las valijas. El vuelo no se toca.</t>
         </is>
       </c>
       <c r="F177" s="37" t="inlineStr"/>
@@ -37037,18 +37057,18 @@
       <c r="H177" s="41" t="inlineStr"/>
       <c r="I177" s="41" t="inlineStr"/>
     </row>
-    <row r="178" ht="16" customHeight="1">
+    <row r="178" ht="30" customHeight="1">
       <c r="A178" s="35" t="n"/>
       <c r="B178" s="36" t="inlineStr">
         <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="C178" s="37" t="inlineStr">
+        <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="C178" s="37" t="inlineStr">
-        <is>
-          <t>19:40</t>
-        </is>
-      </c>
       <c r="D178" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -37056,7 +37076,7 @@
       </c>
       <c r="E178" s="39" t="inlineStr">
         <is>
-          <t>Retirar las valijas del bell desk. Cena tranquila cerca del hotel: es la última.</t>
+          <t>◇ SI PREFIEREN EL GUGGENHEIM, sigue estando y este bloque se ignora: pay-what-you-wish domingos 16:00-17:30 (mínimo $1) y entrada rebajada a $16 el resto del horario. ⚠️ PERO la rotonda está CERRADA del 3/8 al 17/9 por el montaje de Taryn Simon: no se camina la rampa —que es la razón para ir— y avisan que puede haber ruido de obra. Quedan las torres 4, 5 y 7 con «Guggenheim Pop» (Lichtenstein, Warhol, Oldenburg, Cattelan) y la colección Thannhauser. Para hacerlo: en vez de cruzar a Queens, teleférico de vuelta y subte 4/5/6 de 59 St a 86 St, y hay que salir del FDR Park 15:05 para entrar 16:00 — la ventana a voluntad va hasta las 17:30 y el museo cierra ahí.</t>
         </is>
       </c>
       <c r="F178" s="37" t="inlineStr"/>
@@ -37068,14 +37088,14 @@
       <c r="A179" s="35" t="n"/>
       <c r="B179" s="36" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C179" s="37" t="inlineStr">
+        <is>
           <t>19:40</t>
         </is>
       </c>
-      <c r="C179" s="37" t="inlineStr">
-        <is>
-          <t>20:14</t>
-        </is>
-      </c>
       <c r="D179" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -37083,7 +37103,7 @@
       </c>
       <c r="E179" s="39" t="inlineStr">
         <is>
-          <t>Salir de The Beacon. Subte 1/2/3 desde 72 St hasta 34 St-Penn Station: ~10 min, $3.</t>
+          <t>Retirar las valijas del bell desk. Cena tranquila cerca del hotel: es la última.</t>
         </is>
       </c>
       <c r="F179" s="37" t="inlineStr"/>
@@ -37091,18 +37111,18 @@
       <c r="H179" s="41" t="inlineStr"/>
       <c r="I179" s="41" t="inlineStr"/>
     </row>
-    <row r="180" ht="30" customHeight="1">
+    <row r="180" ht="16" customHeight="1">
       <c r="A180" s="35" t="n"/>
       <c r="B180" s="36" t="inlineStr">
         <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="C180" s="37" t="inlineStr">
+        <is>
           <t>20:14</t>
         </is>
       </c>
-      <c r="C180" s="37" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
       <c r="D180" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -37110,7 +37130,7 @@
       </c>
       <c r="E180" s="39" t="inlineStr">
         <is>
-          <t>NJ Transit Penn Station → EWR, llega 20:38. $17,25 (incluye el AirTrain). VERIFICAR el horario dominical en njtransit.com unos días antes.</t>
+          <t>Salir de The Beacon. Subte 1/2/3 desde 72 St hasta 34 St-Penn Station: ~10 min, $3.</t>
         </is>
       </c>
       <c r="F180" s="37" t="inlineStr"/>
@@ -37118,18 +37138,18 @@
       <c r="H180" s="41" t="inlineStr"/>
       <c r="I180" s="41" t="inlineStr"/>
     </row>
-    <row r="181" ht="16" customHeight="1">
+    <row r="181" ht="30" customHeight="1">
       <c r="A181" s="35" t="n"/>
       <c r="B181" s="36" t="inlineStr">
         <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="C181" s="37" t="inlineStr">
+        <is>
           <t>20:45</t>
         </is>
       </c>
-      <c r="C181" s="37" t="inlineStr">
-        <is>
-          <t>20:55</t>
-        </is>
-      </c>
       <c r="D181" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -37137,7 +37157,7 @@
       </c>
       <c r="E181" s="39" t="inlineStr">
         <is>
-          <t>AirTrain hasta la terminal: 10-15 min.</t>
+          <t>NJ Transit Penn Station → EWR, llega 20:38. $17,25 (incluye el AirTrain). VERIFICAR el horario dominical en njtransit.com unos días antes.</t>
         </is>
       </c>
       <c r="F181" s="37" t="inlineStr"/>
@@ -37145,14 +37165,18 @@
       <c r="H181" s="41" t="inlineStr"/>
       <c r="I181" s="41" t="inlineStr"/>
     </row>
-    <row r="182" ht="30" customHeight="1">
+    <row r="182" ht="16" customHeight="1">
       <c r="A182" s="35" t="n"/>
       <c r="B182" s="36" t="inlineStr">
         <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C182" s="37" t="inlineStr">
+        <is>
           <t>20:55</t>
         </is>
       </c>
-      <c r="C182" s="37" t="inlineStr"/>
       <c r="D182" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -37160,7 +37184,7 @@
       </c>
       <c r="E182" s="39" t="inlineStr">
         <is>
-          <t>En terminal. Faltan 2h45 para el vuelo de las 23:40 — correcto para un internacional en el domingo de Labor Day, que es la noche de más tráfico del año en EWR.</t>
+          <t>AirTrain hasta la terminal: 10-15 min.</t>
         </is>
       </c>
       <c r="F182" s="37" t="inlineStr"/>
@@ -37168,8 +37192,31 @@
       <c r="H182" s="41" t="inlineStr"/>
       <c r="I182" s="41" t="inlineStr"/>
     </row>
-    <row r="183" ht="32" customHeight="1">
-      <c r="A183" s="46" t="inlineStr">
+    <row r="183" ht="30" customHeight="1">
+      <c r="A183" s="35" t="n"/>
+      <c r="B183" s="36" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="C183" s="37" t="inlineStr"/>
+      <c r="D183" s="38" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E183" s="39" t="inlineStr">
+        <is>
+          <t>En terminal. Faltan 2h45 para el vuelo de las 23:40 — correcto para un internacional en el domingo de Labor Day, que es la noche de más tráfico del año en EWR.</t>
+        </is>
+      </c>
+      <c r="F183" s="37" t="inlineStr"/>
+      <c r="G183" s="40" t="inlineStr"/>
+      <c r="H183" s="41" t="inlineStr"/>
+      <c r="I183" s="41" t="inlineStr"/>
+    </row>
+    <row r="184" ht="32" customHeight="1">
+      <c r="A184" s="46" t="inlineStr">
         <is>
           <t>ALTERNATIVA / OJO:  COLCHÓN: si algo se atrasa, el tren siguiente sale 20:55 y llega a EWR 21:16, o sea terminal ~21:35 y 2h05 antes del vuelo. Es el último que yo tomaría. // Si prefieren un último día sin moverse, salteen el teleférico y estiren Central Park hasta el Guggenheim: el parque solo da para toda la mañana y la tarde. Lo que NO conviene hoy es meter algo nuevo y grande. // LO QUE SE PIERDEN POR EL VUELO, y duele: esta noche a las 20:00 el Met proyecta gratis en Lincoln Center «El Último Sueño de Frida y Diego» —la misma Frida de la muestra del MoMA del lunes— y ustedes salen del hotel 19:40 hacia Penn Station. Está a diez cuadras del Beacon. No hay forma de que entre sin poner en riesgo el vuelo. // SI QUIEREN VOLVER AL GUGGENHEIM en vez del PS1: está escrito en el bloque de las 18:20, con los tiempos hechos. Cuesta el último imprescindible del viaje y hay que aceptar que la rampa —la razón para ir— no se camina hasta el 17/9. Tercera opción si ninguna convence: el Whitney también abre los domingos.</t>
         </is>
@@ -37177,17 +37224,20 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A183:I183"/>
-    <mergeCell ref="A164:I164"/>
+    <mergeCell ref="A128:I128"/>
     <mergeCell ref="A84:I84"/>
     <mergeCell ref="A66:I66"/>
-    <mergeCell ref="A145:I145"/>
+    <mergeCell ref="A105:I105"/>
+    <mergeCell ref="A163:I163"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="A86:I86"/>
+    <mergeCell ref="A104:I104"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A126:I126"/>
-    <mergeCell ref="A100:I100"/>
+    <mergeCell ref="A144:I144"/>
+    <mergeCell ref="A184:I184"/>
+    <mergeCell ref="A125:I125"/>
+    <mergeCell ref="A147:I147"/>
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A165:I165"/>
     <mergeCell ref="A1:G1"/>
@@ -37195,20 +37245,17 @@
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="A102:I102"/>
     <mergeCell ref="A127:I127"/>
-    <mergeCell ref="A143:I143"/>
     <mergeCell ref="A48:I48"/>
-    <mergeCell ref="A103:I103"/>
+    <mergeCell ref="A166:I166"/>
     <mergeCell ref="A45:I45"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A146:I146"/>
-    <mergeCell ref="A124:I124"/>
     <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A162:I162"/>
     <mergeCell ref="A69:I69"/>
     <mergeCell ref="A87:I87"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H185" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H186" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,Reservado,Confirmado,Descartado"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NYC_2026_Planificador.xlsx
+++ b/NYC_2026_Planificador.xlsx
@@ -5572,9 +5572,9 @@
           <t>1 E 70th St</t>
         </is>
       </c>
-      <c r="S38" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S38" s="17" t="inlineStr">
+        <is>
+          <t>Día 5 · mié 2/9</t>
         </is>
       </c>
       <c r="T38" s="18" t="inlineStr">
@@ -21115,9 +21115,9 @@
           <t>20 Hudson Yards</t>
         </is>
       </c>
-      <c r="S195" s="17" t="inlineStr">
-        <is>
-          <t>Día 5 · mié 2/9</t>
+      <c r="S195" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="T195" s="18" t="inlineStr">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="S198" s="17" t="inlineStr">
         <is>
-          <t>Día 5 · mié 2/9, Día 7 · vie 4/9</t>
+          <t>Día 7 · vie 4/9</t>
         </is>
       </c>
       <c r="T198" s="18" t="inlineStr">
@@ -21913,7 +21913,7 @@
       </c>
       <c r="S203" s="17" t="inlineStr">
         <is>
-          <t>Día 5 · mié 2/9, Día 7 · vie 4/9</t>
+          <t>Día 7 · vie 4/9</t>
         </is>
       </c>
       <c r="T203" s="18" t="inlineStr">
@@ -32651,7 +32651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I184"/>
+  <dimension ref="A1:I183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -34764,14 +34764,14 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="33" t="inlineStr">
         <is>
-          <t>DÍA 5 · Miércoles 02/09 · JP solo · High Line al amanecer, Vessel, Historia Natural, MoMA y McBride en Central Park  —  base: JGStay SoHo (YA NO se vuelve a New Jersey)  ·  Solo JP</t>
+          <t>DÍA 5 · Miércoles 02/09 · JP solo · High Line al amanecer, Historia Natural, Frick a voluntad, MoMA y McBride en Central Park  —  base: JGStay SoHo (YA NO se vuelve a New Jersey)  ·  Solo JP</t>
         </is>
       </c>
     </row>
     <row r="87" ht="32" customHeight="1">
       <c r="A87" s="34" t="inlineStr">
         <is>
-          <t>REARMADO EL 1/9 con dos cambios de Juan. UNO: ya no vuelve a New Jersey — se queda en el JGStay SoHo hasta el jueves y de ahí lleva las maletas a The Beacon. Eso borra la única vuelta nocturna del viaje, o sea que hoy NO hay tren que atrapar: el SummerStage se ve entero y sin mirar el reloj, y mañana se arranca a las 7:30 desde SoHo en vez de a las 5:45 desde Branchburg. DOS: Juan quiere el HIGH LINE A LAS 7 DE LA MAÑANA, cuando abre y está vacío. ⚠️ EL ENGANCHE QUE NO CIERRA SOLO: el Vessel abre a las 10:00, así que entre el final del High Line y el Vessel hay un hueco de una hora larga — se llena con el desayuno en Hudson Yards, que además reemplaza al del hotel (7-9 AM), que hoy se pierde por salir temprano. Y entra el MoMA, que quedó pendiente del lunes: cierra 17:30 y encaja justo antes del SummerStage. CERRADOS hoy: el MET (por eso fue ayer) y el Frick pierde su ventana a voluntad — ver alternativas.</t>
+          <t>REARMADO EL 1/9, SEGUNDA PASADA. Juan sacó el Vessel (del High Line quiere SOLO la caminata) y con eso se liberaron casi dos horas: ahora entran los TRES museos que no se podían soltar. El día pasó de apretado a encastrado, y el que lo hace posible es el Vessel que se fue. LA LLAVE DEL DÍA es la ventana pay-what-you-wish del FRICK, miércoles 13:30-17:30, la única de la semana: el plan la toma a las 13:30 EN PUNTO, apenas abre, y de ahí sale con tiempo para el MoMA antes de que cierre a las 17:30. Los tres horarios encajan sin margen para improvisar: AMNH abre 10:00, Frick a voluntad 13:30, MoMA cierra 17:30. Correrse media hora en el primero se paga en el último. ⚠️ HAY QUE COMPRAR EL TICKET DEL FRICK HOY: online el mínimo son $5 y GARANTIZA la entrada; en persona se puede pagar menos pero sin garantía de lugar, y un miércoles de septiembre a las 13:30 es la hora pico de la ventana. Por $5 no vale el riesgo de quedarse afuera. EL ALMUERZO SE RESIGNA, por decisión de Juan: se come algo de parado cruzando Central Park entre el museo y el Frick. Es la media hora que hace entrar todo. EL VESSEL NO SE PIERDE: está el viernes con Thais, que lo tiene 2/2 — sacarlo hoy lo mueve, no lo borra. Y como ya no hay tren a New Jersey, el SummerStage se ve entero. CERRADO hoy: el MET (por eso fue ayer).</t>
         </is>
       </c>
     </row>
@@ -34794,7 +34794,7 @@
       </c>
       <c r="E88" s="39" t="inlineStr">
         <is>
-          <t>Salir del JGStay. Subte 1 desde Canal St hasta Christopher St, o A/C/E hasta 14 St (~12 min). Hoy se pierde el desayuno incluido del hotel (7-9 AM): se desayuna a media mañana en Hudson Yards.</t>
+          <t>Salir del JGStay. Subte 1 desde Canal St hasta Christopher St, o A/C/E hasta 14 St (~12 min). Hoy se pierde el desayuno incluido del hotel (7-9 AM): se desayuna a media mañana en el Upper West Side, antes de que abra el museo.</t>
         </is>
       </c>
       <c r="F88" s="37" t="inlineStr">
@@ -34815,7 +34815,7 @@
       </c>
       <c r="C89" s="43" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="D89" s="44" t="inlineStr">
@@ -34825,7 +34825,7 @@
       </c>
       <c r="E89" s="45" t="inlineStr">
         <is>
-          <t>★★ THE HIGH LINE AL AMANECER — abre 7:00 y esta es LA hora: vacío, con el sol bajo entre los edificios y sin las hordas de la tarde. Entrar por Gansevoort St (extremo SUR) y caminar los 2,3 km hacia el norte, sin apuro. Incluye el Buda de arenisca de 9 metros de Tuan Andrew Nguyen.</t>
+          <t>★★ THE HIGH LINE AL AMANECER — abre 7:00 y esta es LA hora: vacío, con el sol bajo entre los edificios y sin las hordas de la tarde. Entrar por Gansevoort St (extremo SUR) y caminar los 2,3 km hacia el norte, sin apuro: hoy hay casi dos horas para hacerlo lento. Incluye el Buda de arenisca de 9 metros de Tuan Andrew Nguyen. SI QUIERE SUMAR 20 MINUTOS: Little Island está a 5 min de la entrada de Gansevoort y también abre temprano (6:00).</t>
         </is>
       </c>
       <c r="F89" s="43" t="inlineStr">
@@ -34841,12 +34841,12 @@
       <c r="A90" s="35" t="n"/>
       <c r="B90" s="36" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="C90" s="37" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="D90" s="38" t="inlineStr">
@@ -34856,19 +34856,11 @@
       </c>
       <c r="E90" s="39" t="inlineStr">
         <is>
-          <t>Little Island — el parque flotante de Heatherwick sobre 132 macetas de hormigón, a la altura de la calle 13. Abre 6:00, así que a esta hora también está vacío. Media hora y se sigue al norte.</t>
-        </is>
-      </c>
-      <c r="F90" s="37" t="inlineStr">
-        <is>
-          <t>Little Island</t>
-        </is>
-      </c>
-      <c r="G90" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~15 min a pie · 1.1 km · estimado</t>
-        </is>
-      </c>
+          <t>Subte al Upper West Side: A/C desde 34 St-Penn Station hasta 81 St-Museum of Natural History, directo y sin transbordo (~20 min). El High Line termina justo ahí arriba.</t>
+        </is>
+      </c>
+      <c r="F90" s="37" t="inlineStr"/>
+      <c r="G90" s="40" t="inlineStr"/>
       <c r="H90" s="41" t="inlineStr"/>
       <c r="I90" s="41" t="inlineStr"/>
     </row>
@@ -34876,7 +34868,7 @@
       <c r="A91" s="35" t="n"/>
       <c r="B91" s="36" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="C91" s="37" t="inlineStr">
@@ -34891,19 +34883,11 @@
       </c>
       <c r="E91" s="39" t="inlineStr">
         <is>
-          <t>Desayuno en Hudson Yards, al pie del Vessel — acá se llena el hueco hasta que abra. The Shops tiene opciones rápidas; si prefieren algo mejor, Mercado Little Spain de José Andrés está en la planta baja.</t>
-        </is>
-      </c>
-      <c r="F91" s="37" t="inlineStr">
-        <is>
-          <t>Hudson Yards</t>
-        </is>
-      </c>
-      <c r="G91" s="40" t="inlineStr">
-        <is>
-          <t>🚇 ~15 min en subte · 2.5 km (a pie 35 min) · estimado</t>
-        </is>
-      </c>
+          <t>Desayuno en el Upper West Side, sobre Amsterdam o Columbus, a metros del museo. Acá se llena el hueco hasta que abra el AMNH y se recupera el desayuno del hotel que se perdió por madrugar.</t>
+        </is>
+      </c>
+      <c r="F91" s="37" t="inlineStr"/>
+      <c r="G91" s="40" t="inlineStr"/>
       <c r="H91" s="41" t="inlineStr"/>
       <c r="I91" s="41" t="inlineStr"/>
     </row>
@@ -34916,7 +34900,7 @@
       </c>
       <c r="C92" s="43" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="D92" s="44" t="inlineStr">
@@ -34926,19 +34910,15 @@
       </c>
       <c r="E92" s="45" t="inlineStr">
         <is>
-          <t>★ THE VESSEL — abre 10:00 EN PUNTO y conviene ser de los primeros: la escalera infinita de Heatherwick, 154 tramos y 2.500 escalones, $10. Reabierto con redes; hay ascensor cada 15 min. Subir es la única forma de entenderla.</t>
+          <t>★ AMERICAN MUSEUM OF NATURAL HISTORY — ENTRAR A LA APERTURA, 10:00 en punto: son 2h45 y el día no da más. Dinosaurios (4º piso, lo mejor), la ballena azul y el Gilder Center nuevo de Studio Gang. $37. Thais lo marcó 0: es de hoy o no es. A las 12:45 hay que estar saliendo.</t>
         </is>
       </c>
       <c r="F92" s="43" t="inlineStr">
         <is>
-          <t>The Vessel</t>
-        </is>
-      </c>
-      <c r="G92" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~7 min a pie · 0.5 km · estimado</t>
-        </is>
-      </c>
+          <t>American Museum of Natural History</t>
+        </is>
+      </c>
+      <c r="G92" s="40" t="inlineStr"/>
       <c r="H92" s="41" t="inlineStr"/>
       <c r="I92" s="41" t="inlineStr"/>
     </row>
@@ -34946,12 +34926,12 @@
       <c r="A93" s="35" t="n"/>
       <c r="B93" s="36" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C93" s="37" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="D93" s="38" t="inlineStr">
@@ -34961,7 +34941,7 @@
       </c>
       <c r="E93" s="39" t="inlineStr">
         <is>
-          <t>Subte a Historia Natural: 7 desde 34 St-Hudson Yards hasta Times Sq y 1/2/3 hasta 79 St, o A/C desde 34 St-Penn hasta 81 St (~30 min).</t>
+          <t>ALMUERZO DE PARADO cruzando Central Park — 1,3 km a pie, unos 18 min: bajar por Central Park West hasta la 72, cruzar el parque por Terrace Drive y salir a la Quinta. Comprar algo antes de entrar (hay carritos en CPW, o el café del propio museo) y comerlo caminando: esta media hora es la que hace entrar los tres museos. Al Frick no se entra con comida.</t>
         </is>
       </c>
       <c r="F93" s="37" t="inlineStr"/>
@@ -34973,12 +34953,12 @@
       <c r="A94" s="35" t="n"/>
       <c r="B94" s="42" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C94" s="43" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="D94" s="44" t="inlineStr">
@@ -34988,15 +34968,19 @@
       </c>
       <c r="E94" s="45" t="inlineStr">
         <is>
-          <t>★ AMERICAN MUSEUM OF NATURAL HISTORY — dinosaurios, la ballena azul y el Gilder Center nuevo de Studio Gang. $37. Abre 10-17:30. Thais lo marcó 0: es de hoy.</t>
+          <t>★ THE FRICK COLLECTION, A VOLUNTAD — 13:30 EN PUNTO, cuando arranca la ventana pay-what-you-wish de los miércoles, la única de la semana. Reabrió en 2025 tras cinco años de obra: Vermeer, Rembrandt y Bellini colgados en la mansión del magnate, como en una casa. Es el museo más placentero de NYC. TICKET COMPRADO ONLINE ($5 mínimo, garantiza la entrada). 1h45 alcanza bien: es chico a propósito.</t>
         </is>
       </c>
       <c r="F94" s="43" t="inlineStr">
         <is>
-          <t>American Museum of Natural History</t>
-        </is>
-      </c>
-      <c r="G94" s="40" t="inlineStr"/>
+          <t>The Frick Collection</t>
+        </is>
+      </c>
+      <c r="G94" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~25 min a pie (1.6 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H94" s="41" t="inlineStr"/>
       <c r="I94" s="41" t="inlineStr"/>
     </row>
@@ -35004,12 +34988,12 @@
       <c r="A95" s="35" t="n"/>
       <c r="B95" s="36" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C95" s="37" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="D95" s="38" t="inlineStr">
@@ -35019,7 +35003,7 @@
       </c>
       <c r="E95" s="39" t="inlineStr">
         <is>
-          <t>Almuerzo en el Upper West Side, saliendo del museo. Amsterdam o Columbus tienen de todo; Gray's Papaya está en Broadway y 72 si quieren el pancho de parado.</t>
+          <t>Del Frick al MoMA: 1,4 km bajando por la Quinta Avenida, ~18 min a pie, con el Central Park a la derecha y las vidrieras a la izquierda. Es de los mejores paseos de Manhattan y va cuesta abajo. Alternativa si están las piernas cansadas: subte 6 desde 68 St hasta 51 St.</t>
         </is>
       </c>
       <c r="F95" s="37" t="inlineStr"/>
@@ -35027,60 +35011,60 @@
       <c r="H95" s="41" t="inlineStr"/>
       <c r="I95" s="41" t="inlineStr"/>
     </row>
-    <row r="96" ht="16" customHeight="1">
+    <row r="96" ht="30" customHeight="1">
       <c r="A96" s="35" t="n"/>
-      <c r="B96" s="36" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="C96" s="37" t="inlineStr">
+      <c r="B96" s="42" t="inlineStr">
         <is>
           <t>15:40</t>
         </is>
       </c>
-      <c r="D96" s="38" t="inlineStr">
+      <c r="C96" s="43" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="D96" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E96" s="39" t="inlineStr">
-        <is>
-          <t>Subte B/C o D desde 81 St hasta 7 Av / 47-50 Sts (~15 min). Caminar al MoMA.</t>
-        </is>
-      </c>
-      <c r="F96" s="37" t="inlineStr"/>
+      <c r="E96" s="45" t="inlineStr">
+        <is>
+          <t>★ MoMA — QUEDÓ PENDIENTE DEL LUNES y hoy es su última chance del viaje: cierra 17:30, así que son 1h50. SIN VUELTAS, DERECHO AL 5º PISO: ahí están la noche estrellada de Van Gogh, Les Demoiselles d'Avignon y los Monet grandes. Si sobra tiempo, el 4º (Warhol, Rothko). QUÉ HAY AHORA: «Frida and Diego: The Last Dream», que cierra el 12 de septiembre. $30. (El viernes gratis de UNIQLO es SOLO para residentes del Estado de NY: no aplica.)</t>
+        </is>
+      </c>
+      <c r="F96" s="43" t="inlineStr">
+        <is>
+          <t>MoMA</t>
+        </is>
+      </c>
       <c r="G96" s="40" t="inlineStr"/>
       <c r="H96" s="41" t="inlineStr"/>
       <c r="I96" s="41" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="35" t="n"/>
-      <c r="B97" s="42" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="C97" s="43" t="inlineStr">
+      <c r="B97" s="36" t="inlineStr">
         <is>
           <t>17:35</t>
         </is>
       </c>
-      <c r="D97" s="44" t="inlineStr">
+      <c r="C97" s="37" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D97" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E97" s="45" t="inlineStr">
-        <is>
-          <t>★ MoMA — QUEDÓ PENDIENTE DEL LUNES y hoy es el día: cierra 17:30, así que entrando 15:40 quedan casi dos horas, que alcanzan para las salas de arriba. Van Gogh, Picasso, Rothko, Warhol. QUÉ HAY AHORA: «Frida and Diego: The Last Dream», que cierra el 12 de septiembre. El cine está incluido en la entrada. $30.</t>
-        </is>
-      </c>
-      <c r="F97" s="43" t="inlineStr">
-        <is>
-          <t>MoMA</t>
-        </is>
-      </c>
+      <c r="E97" s="39" t="inlineStr">
+        <is>
+          <t>Del MoMA a Rumsey Playfield: 1,3 km, ~16 min a pie subiendo por la Quinta y entrando al parque por la 69. Con el cartel de hoy conviene estar temprano.</t>
+        </is>
+      </c>
+      <c r="F97" s="37" t="inlineStr"/>
       <c r="G97" s="40" t="inlineStr"/>
       <c r="H97" s="41" t="inlineStr"/>
       <c r="I97" s="41" t="inlineStr"/>
@@ -35089,12 +35073,12 @@
       <c r="A98" s="35" t="n"/>
       <c r="B98" s="36" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="C98" s="37" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D98" s="38" t="inlineStr">
@@ -35104,7 +35088,7 @@
       </c>
       <c r="E98" s="39" t="inlineStr">
         <is>
-          <t>Del MoMA a Rumsey Playfield: subte F desde 57 St hasta 63 St-Lexington y caminar, o los 20 minutos a pie por la Quinta y entrando por la 69. Con el cartel de hoy conviene estar temprano.</t>
+          <t>Entrar a Rumsey Playfield y buscar lugar. Puertas 18:00 y con este cartel se llena: cuanto antes, mejor lugar. LA CENA ES ACÁ — hoy el almuerzo fue de parado, así que esta es la comida de verdad del día: hay puestos adentro, o se compra algo en el camino por la Quinta.</t>
         </is>
       </c>
       <c r="F98" s="37" t="inlineStr"/>
@@ -35114,120 +35098,124 @@
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="35" t="n"/>
-      <c r="B99" s="36" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="C99" s="37" t="inlineStr">
+      <c r="B99" s="42" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D99" s="38" t="inlineStr">
+      <c r="C99" s="43" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="D99" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E99" s="39" t="inlineStr">
-        <is>
-          <t>Entrar a Rumsey Playfield y buscar lugar. Puertas 18:00 y con este cartel se llena: cuanto antes, mejor lugar. Comer algo acá o de camino — hoy la cena es lo que se consiga.</t>
-        </is>
-      </c>
-      <c r="F99" s="37" t="inlineStr"/>
+      <c r="E99" s="45" t="inlineStr">
+        <is>
+          <t>★★ SUMMERSTAGE: Christian McBride + SAMARA JOY + Mei Semones — Verve 70 aniversario y Getz/Gilberto. GRATIS, sin ticket, Rumsey Playfield, 19:00-22:00. Y SE VE ENTERO: ya no hay tren a New Jersey que atrapar, que era lo que obligaba a salir corriendo.</t>
+        </is>
+      </c>
+      <c r="F99" s="43" t="inlineStr">
+        <is>
+          <t>SummerStage: Christian McBride (gratis)</t>
+        </is>
+      </c>
       <c r="G99" s="40" t="inlineStr"/>
       <c r="H99" s="41" t="inlineStr"/>
       <c r="I99" s="41" t="inlineStr"/>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="35" t="n"/>
-      <c r="B100" s="42" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C100" s="43" t="inlineStr">
+      <c r="B100" s="36" t="inlineStr">
         <is>
           <t>22:05</t>
         </is>
       </c>
-      <c r="D100" s="44" t="inlineStr">
+      <c r="C100" s="37" t="inlineStr"/>
+      <c r="D100" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E100" s="45" t="inlineStr">
-        <is>
-          <t>★★ SUMMERSTAGE: Christian McBride + SAMARA JOY + Mei Semones — Verve 70 aniversario y Getz/Gilberto. GRATIS, sin ticket, Rumsey Playfield, 19:00-22:00. Y AHORA SE VE ENTERO: ya no hay tren a New Jersey que atrapar, que era lo que obligaba a salir corriendo.</t>
-        </is>
-      </c>
-      <c r="F100" s="43" t="inlineStr">
-        <is>
-          <t>SummerStage: Christian McBride (gratis)</t>
+      <c r="E100" s="39" t="inlineStr">
+        <is>
+          <t>Al JGStay sin apuro: subte B/C desde 72 St hasta W 4 St y caminar, o 1 hasta Canal (~35 min). Dormir en SoHo y no en Branchburg cambia el jueves entero.</t>
+        </is>
+      </c>
+      <c r="F100" s="37" t="inlineStr">
+        <is>
+          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
         </is>
       </c>
       <c r="G100" s="40" t="inlineStr"/>
       <c r="H100" s="41" t="inlineStr"/>
       <c r="I100" s="41" t="inlineStr"/>
     </row>
-    <row r="101" ht="30" customHeight="1">
-      <c r="A101" s="35" t="n"/>
-      <c r="B101" s="36" t="inlineStr">
-        <is>
-          <t>22:05</t>
-        </is>
-      </c>
-      <c r="C101" s="37" t="inlineStr"/>
-      <c r="D101" s="38" t="inlineStr">
+    <row r="101" ht="32" customHeight="1">
+      <c r="A101" s="46" t="inlineStr">
+        <is>
+          <t>ALTERNATIVA / OJO:  LO QUE HAY QUE HACER HOY, ANTES DE DORMIR: comprar el ticket del Frick para mañana 13:30. Son $5 (el mínimo online del pay-what-you-wish) y es lo único que garantiza la entrada. Sin eso, hay que hacer la cola en persona y jugarse a que haya lugar en la hora más pedida de la única ventana semanal. // EL DÍA NO TIENE COLCHÓN, y conviene saber dónde se corta si algo se estira: el que se achica es el MoMA, porque es el último y cierra a las 17:30 pase lo que pase. Salir del AMNH 12:45 no es negociable; salir del Frick 15:15 tampoco. Si el High Line a las 7 resulta demasiado madrugón después de anoche, se puede entrar 8:30 y empezar el día en el museo: el AMNH abre 10:00 igual y nada se mueve — lo único que se acorta es el desayuno. // EL VESSEL SE FUE DE HOY y está bien que así sea: Thais lo tiene 2/2 y está en el plan del viernes, con el High Line y Little Island. Hoy Juan hace solo la caminata, que es lo que quería. // TOP OF THE ROCK: ya no entra en ningún lado. Su gracia es el atardecer y el viernes el SUMMIT —mejor mirador— ya lo tiene reservado. Si igual lo quieren, la única forma es soltar el MoMA de hoy, y el MoMA no tiene otra fecha. // Si el Frick resulta corto y sobran 20 minutos, el Guggenheim está 14 cuadras al norte por la Quinta — pero OJO, la rotonda está en montaje hasta el 17 de septiembre: es entrar a ver el edificio a medio armar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="33" t="inlineStr">
+        <is>
+          <t>DÍA 6 · Jueves 03/09 · Traslado + World Trade Center completo + ferry con Thais  —  base: JGStay SoHo → The Beacon  ·  Solo JP</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="34" t="inlineStr">
+        <is>
+          <t>REARMADO EL 1/9: Juan ya no duerme en New Jersey, así que el día arranca en el JGStay SoHo a las 7:30 con desayuno incluido en vez de a las 6:20 en Branchburg — hora y media más de sueño, un Uber menos y un tren menos. Las maletas van en el subte 1, directo de Canal St a 72 St, y quedan en el bell desk del Beacon antes de las 9. La mañana y la primera tarde son el World Trade Center completo — memorial, museo y One World Observatory en una sola bajada. OJO: One World es EL MIRADOR DE DÍA a propósito — su vista es el puerto y el agua, que de noche es negra; los arcos de atardecer van en Top of the Rock (lunes) y SUMMIT (viernes). THAIS ESTÁ EN NYC CON SU EQUIPO este jueves y SE LIBERA A LAS 16:00: se encuentran por Manhattan y se van juntos al Museum of the Moving Image, que es GRATIS los jueves de 14 a 18 — estaba caído del plan y ustedes lo tienen 2/2: RECUPERADO. El día cierra con check-in, cena y Dizzy's. Siguen afuera MoMA PS1, Astoria y Gantry (no hay hueco), y el Staten Island Ferry pasó a la alternativa nocturna de hoy. ENTRA STONE ST, que era imprescindible y no estaba en ningún día: el almuerzo se corre de Brookfield Place a la calle adoquinada, a 10 minutos del museo y 12 de One World. Se pagan 22 minutos de caminata y quedan 38 para comer — alcanza para un mediodía, aunque su mejor hora sea el after office de 5 a 8 y no la del almuerzo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="35" t="n"/>
+      <c r="B105" s="36" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="C105" s="37" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="D105" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E101" s="39" t="inlineStr">
-        <is>
-          <t>Al JGStay sin apuro: subte B/C desde 72 St hasta W 4 St y caminar, o 1 hasta Canal (~35 min). Dormir en SoHo y no en Branchburg cambia el jueves entero.</t>
-        </is>
-      </c>
-      <c r="F101" s="37" t="inlineStr">
+      <c r="E105" s="39" t="inlineStr">
+        <is>
+          <t>Desayuno incluido en el JGStay (7-9 AM) y CHECKOUT con las maletas. Hoy ya no se madruga a las 5:45 en Branchburg: se duerme en SoHo y se sale a las 7:30. Una hora y media más de sueño y un tren menos.</t>
+        </is>
+      </c>
+      <c r="F105" s="37" t="inlineStr">
         <is>
           <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
         </is>
       </c>
-      <c r="G101" s="40" t="inlineStr"/>
-      <c r="H101" s="41" t="inlineStr"/>
-      <c r="I101" s="41" t="inlineStr"/>
-    </row>
-    <row r="102" ht="32" customHeight="1">
-      <c r="A102" s="46" t="inlineStr">
-        <is>
-          <t>ALTERNATIVA / OJO:  EL FRICK SE CAE, y hay que decirlo: hoy era su ventana pay-what-you-wish de 13:30 a 17:30, la única de la semana, y el día quedó lleno con el High Line temprano, el Vessel y el MoMA pendiente. Si lo quieren recuperar, la única forma es soltar el MoMA o el AMNH — el Frick fuera de esa ventana son $30 por cabeza. // SI PREFIEREN EL TOP OF THE ROCK EN VEZ DEL MoMA: abre 8:00-24:00, así que entra en el mismo hueco de las 15:40. PERO su gracia es el atardecer (hoy ~19:26) y a esa hora están en el SummerStage, así que sería subir con luz plana. El MoMA cierra 17:30 y hoy es su única chance del viaje; el Top of the Rock, en cambio, compite con el SUMMIT del viernes, que ya tiene el atardecer reservado y es mejor mirador. Por eso el plan pone el MoMA. // Si el High Line a las 7 resulta demasiado madrugón después de anoche, se puede entrar 8:30 y correr todo una hora: el Vessel abre 10:00 igual y el resto del día no se mueve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="22" customHeight="1">
-      <c r="A104" s="33" t="inlineStr">
-        <is>
-          <t>DÍA 6 · Jueves 03/09 · Traslado + World Trade Center completo + ferry con Thais  —  base: JGStay SoHo → The Beacon  ·  Solo JP</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="32" customHeight="1">
-      <c r="A105" s="34" t="inlineStr">
-        <is>
-          <t>REARMADO EL 1/9: Juan ya no duerme en New Jersey, así que el día arranca en el JGStay SoHo a las 7:30 con desayuno incluido en vez de a las 6:20 en Branchburg — hora y media más de sueño, un Uber menos y un tren menos. Las maletas van en el subte 1, directo de Canal St a 72 St, y quedan en el bell desk del Beacon antes de las 9. La mañana y la primera tarde son el World Trade Center completo — memorial, museo y One World Observatory en una sola bajada. OJO: One World es EL MIRADOR DE DÍA a propósito — su vista es el puerto y el agua, que de noche es negra; los arcos de atardecer van en Top of the Rock (lunes) y SUMMIT (viernes). THAIS ESTÁ EN NYC CON SU EQUIPO este jueves y SE LIBERA A LAS 16:00: se encuentran por Manhattan y se van juntos al Museum of the Moving Image, que es GRATIS los jueves de 14 a 18 — estaba caído del plan y ustedes lo tienen 2/2: RECUPERADO. El día cierra con check-in, cena y Dizzy's. Siguen afuera MoMA PS1, Astoria y Gantry (no hay hueco), y el Staten Island Ferry pasó a la alternativa nocturna de hoy. ENTRA STONE ST, que era imprescindible y no estaba en ningún día: el almuerzo se corre de Brookfield Place a la calle adoquinada, a 10 minutos del museo y 12 de One World. Se pagan 22 minutos de caminata y quedan 38 para comer — alcanza para un mediodía, aunque su mejor hora sea el after office de 5 a 8 y no la del almuerzo.</t>
-        </is>
-      </c>
+      <c r="G105" s="40" t="inlineStr"/>
+      <c r="H105" s="41" t="inlineStr"/>
+      <c r="I105" s="41" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="35" t="n"/>
       <c r="B106" s="36" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="C106" s="37" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="D106" s="38" t="inlineStr">
@@ -35237,99 +35225,95 @@
       </c>
       <c r="E106" s="39" t="inlineStr">
         <is>
-          <t>Desayuno incluido en el JGStay (7-9 AM) y CHECKOUT con las maletas. Hoy ya no se madruga a las 5:45 en Branchburg: se duerme en SoHo y se sale a las 7:30. Una hora y media más de sueño y un tren menos.</t>
-        </is>
-      </c>
-      <c r="F106" s="37" t="inlineStr">
-        <is>
-          <t>JGSTAY SoHo (JP: 31 ago-2 sep)</t>
-        </is>
-      </c>
+          <t>Subte 1 desde Canal St derecho hasta 72 St (~25 min). Con maletas, el 1 es el que conviene: es directo y no hay que hacer transbordo.</t>
+        </is>
+      </c>
+      <c r="F106" s="37" t="inlineStr"/>
       <c r="G106" s="40" t="inlineStr"/>
       <c r="H106" s="41" t="inlineStr"/>
       <c r="I106" s="41" t="inlineStr"/>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="35" t="n"/>
-      <c r="B107" s="36" t="inlineStr">
-        <is>
-          <t>08:05</t>
-        </is>
-      </c>
-      <c r="C107" s="37" t="inlineStr">
+      <c r="B107" s="42" t="inlineStr">
         <is>
           <t>08:35</t>
         </is>
       </c>
-      <c r="D107" s="38" t="inlineStr">
+      <c r="C107" s="43" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="D107" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E107" s="39" t="inlineStr">
-        <is>
-          <t>Subte 1 desde Canal St derecho hasta 72 St (~25 min). Con maletas, el 1 es el que conviene: es directo y no hay que hacer transbordo.</t>
-        </is>
-      </c>
-      <c r="F107" s="37" t="inlineStr"/>
+      <c r="E107" s="45" t="inlineStr">
+        <is>
+          <t>★ THE BEACON — dejar las maletas en el bell desk. El check-in formal es a la tarde, con Thais, pero el equipaje se recibe desde temprano. Confirmalo por mail.</t>
+        </is>
+      </c>
+      <c r="F107" s="43" t="inlineStr">
+        <is>
+          <t>Hotel The Beacon (3-6 sep)</t>
+        </is>
+      </c>
       <c r="G107" s="40" t="inlineStr"/>
       <c r="H107" s="41" t="inlineStr"/>
       <c r="I107" s="41" t="inlineStr"/>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="35" t="n"/>
-      <c r="B108" s="42" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="C108" s="43" t="inlineStr">
+      <c r="B108" s="36" t="inlineStr">
         <is>
           <t>09:05</t>
         </is>
       </c>
-      <c r="D108" s="44" t="inlineStr">
+      <c r="C108" s="37" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="D108" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E108" s="45" t="inlineStr">
-        <is>
-          <t>★ THE BEACON — dejar las maletas en el bell desk. El check-in formal es a la tarde, con Thais, pero el equipaje se recibe desde temprano. Confirmalo por mail.</t>
-        </is>
-      </c>
-      <c r="F108" s="43" t="inlineStr">
-        <is>
-          <t>Hotel The Beacon (3-6 sep)</t>
-        </is>
-      </c>
+      <c r="E108" s="39" t="inlineStr">
+        <is>
+          <t>Subte 1 directo desde 72 St hasta WTC Cortlandt (~30 min), otra vez sin transbordo. Alternativa: 2/3 express hasta Chambers St y 5 min a pie.</t>
+        </is>
+      </c>
+      <c r="F108" s="37" t="inlineStr"/>
       <c r="G108" s="40" t="inlineStr"/>
       <c r="H108" s="41" t="inlineStr"/>
       <c r="I108" s="41" t="inlineStr"/>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="35" t="n"/>
-      <c r="B109" s="36" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="C109" s="37" t="inlineStr">
+      <c r="B109" s="42" t="inlineStr">
         <is>
           <t>09:50</t>
         </is>
       </c>
-      <c r="D109" s="38" t="inlineStr">
+      <c r="C109" s="43" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D109" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E109" s="39" t="inlineStr">
-        <is>
-          <t>Subte 1 directo desde 72 St hasta WTC Cortlandt (~30 min), otra vez sin transbordo. Alternativa: 2/3 express hasta Chambers St y 5 min a pie.</t>
-        </is>
-      </c>
-      <c r="F109" s="37" t="inlineStr"/>
+      <c r="E109" s="45" t="inlineStr">
+        <is>
+          <t>★ 9/11 MEMORIAL (la plaza) — las dos fuentes en las huellas de las torres y el Survivor Tree. Gratis, abierto desde las 8:00. Verlo ANTES del museo ordena la visita.</t>
+        </is>
+      </c>
+      <c r="F109" s="43" t="inlineStr"/>
       <c r="G109" s="40" t="inlineStr"/>
       <c r="H109" s="41" t="inlineStr"/>
       <c r="I109" s="41" t="inlineStr"/>
@@ -35338,12 +35322,12 @@
       <c r="A110" s="35" t="n"/>
       <c r="B110" s="42" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C110" s="43" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="D110" s="44" t="inlineStr">
@@ -35353,75 +35337,83 @@
       </c>
       <c r="E110" s="45" t="inlineStr">
         <is>
-          <t>★ 9/11 MEMORIAL (la plaza) — las dos fuentes en las huellas de las torres y el Survivor Tree. Gratis, abierto desde las 8:00. Verlo ANTES del museo ordena la visita.</t>
-        </is>
-      </c>
-      <c r="F110" s="43" t="inlineStr"/>
+          <t>★★ 9/11 MEMORIAL MUSEUM — $36, TIMED TICKET OBLIGATORIO comprado online antes (el museo no vende en puerta sin reserva). 2 horas largas; es duro y muy bien hecho. Thais lo marcó 0: por eso va en la mañana de JP solo.</t>
+        </is>
+      </c>
+      <c r="F110" s="43" t="inlineStr">
+        <is>
+          <t>9/11 Memorial Museum</t>
+        </is>
+      </c>
       <c r="G110" s="40" t="inlineStr"/>
       <c r="H110" s="41" t="inlineStr"/>
       <c r="I110" s="41" t="inlineStr"/>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="35" t="n"/>
-      <c r="B111" s="42" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="C111" s="43" t="inlineStr">
+      <c r="B111" s="36" t="inlineStr">
         <is>
           <t>12:45</t>
         </is>
       </c>
-      <c r="D111" s="44" t="inlineStr">
+      <c r="C111" s="37" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="D111" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E111" s="45" t="inlineStr">
-        <is>
-          <t>★★ 9/11 MEMORIAL MUSEUM — $36, TIMED TICKET OBLIGATORIO comprado online antes (el museo no vende en puerta sin reserva). 2 horas largas; es duro y muy bien hecho. Thais lo marcó 0: por eso va en la mañana de JP solo.</t>
-        </is>
-      </c>
-      <c r="F111" s="43" t="inlineStr">
-        <is>
-          <t>9/11 Memorial Museum</t>
-        </is>
-      </c>
-      <c r="G111" s="40" t="inlineStr"/>
+      <c r="E111" s="39" t="inlineStr">
+        <is>
+          <t>★ ALMUERZO EN STONE ST — 10 min a pie desde el museo, hacia el sureste. Calle adoquinada peatonal de 1660, la traza holandesa que sobrevivió al fuego de 1835: mesas afuera, sin autos, entre edificios de piedra. Se come rápido y se sigue: One World es a las 13:45 y son 12 min de vuelta. Plan B si llueve o no hay mesa: Hudson Eats o Le District en Brookfield Place, cruzando West St.</t>
+        </is>
+      </c>
+      <c r="F111" s="37" t="inlineStr">
+        <is>
+          <t>Stone St</t>
+        </is>
+      </c>
+      <c r="G111" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~14 min a pie · 1.1 km · estimado</t>
+        </is>
+      </c>
       <c r="H111" s="41" t="inlineStr"/>
       <c r="I111" s="41" t="inlineStr"/>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="35" t="n"/>
-      <c r="B112" s="36" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="C112" s="37" t="inlineStr">
+      <c r="B112" s="42" t="inlineStr">
         <is>
           <t>13:45</t>
         </is>
       </c>
-      <c r="D112" s="38" t="inlineStr">
+      <c r="C112" s="43" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="D112" s="44" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E112" s="39" t="inlineStr">
-        <is>
-          <t>★ ALMUERZO EN STONE ST — 10 min a pie desde el museo, hacia el sureste. Calle adoquinada peatonal de 1660, la traza holandesa que sobrevivió al fuego de 1835: mesas afuera, sin autos, entre edificios de piedra. Se come rápido y se sigue: One World es a las 13:45 y son 12 min de vuelta. Plan B si llueve o no hay mesa: Hudson Eats o Le District en Brookfield Place, cruzando West St.</t>
-        </is>
-      </c>
-      <c r="F112" s="37" t="inlineStr">
-        <is>
-          <t>Stone St</t>
+      <c r="E112" s="45" t="inlineStr">
+        <is>
+          <t>★★ ONE WORLD OBSERVATORY — piso 102, el punto más alto del hemisferio occidental, con el puerto y Brooklyn dominando la vista. $44+fee, ventana de entrada de 15 min: sacar el timed ticket online. JP lo subió a 2 en la última pasada.</t>
+        </is>
+      </c>
+      <c r="F112" s="43" t="inlineStr">
+        <is>
+          <t>One World Observatory</t>
         </is>
       </c>
       <c r="G112" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~14 min a pie · 1.1 km · estimado</t>
+          <t>🚶 ~20 min a pie (1.2 km) o 🚇 ~15 min · estimado</t>
         </is>
       </c>
       <c r="H112" s="41" t="inlineStr"/>
@@ -35429,34 +35421,34 @@
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="35" t="n"/>
-      <c r="B113" s="42" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="C113" s="43" t="inlineStr">
+      <c r="B113" s="36" t="inlineStr">
         <is>
           <t>15:15</t>
         </is>
       </c>
-      <c r="D113" s="44" t="inlineStr">
+      <c r="C113" s="37" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D113" s="38" t="inlineStr">
         <is>
           <t>Solo JP</t>
         </is>
       </c>
-      <c r="E113" s="45" t="inlineStr">
-        <is>
-          <t>★★ ONE WORLD OBSERVATORY — piso 102, el punto más alto del hemisferio occidental, con el puerto y Brooklyn dominando la vista. $44+fee, ventana de entrada de 15 min: sacar el timed ticket online. JP lo subió a 2 en la última pasada.</t>
-        </is>
-      </c>
-      <c r="F113" s="43" t="inlineStr">
-        <is>
-          <t>One World Observatory</t>
+      <c r="E113" s="39" t="inlineStr">
+        <is>
+          <t>El Oculus en un VISTAZO (5 min — ya estás ahí, y el tiempo no da para más) y R/W desde Cortlandt St hacia el norte.</t>
+        </is>
+      </c>
+      <c r="F113" s="37" t="inlineStr">
+        <is>
+          <t>Oculus / WTC Transportation Hub</t>
         </is>
       </c>
       <c r="G113" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~20 min a pie (1.2 km) o 🚇 ~15 min · estimado</t>
+          <t>🚶 ~4 min a pie · 0.3 km · estimado</t>
         </is>
       </c>
       <c r="H113" s="41" t="inlineStr"/>
@@ -35464,36 +35456,28 @@
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="35" t="n"/>
-      <c r="B114" s="36" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="C114" s="37" t="inlineStr">
+      <c r="B114" s="42" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D114" s="38" t="inlineStr">
-        <is>
-          <t>Solo JP</t>
-        </is>
-      </c>
-      <c r="E114" s="39" t="inlineStr">
-        <is>
-          <t>El Oculus en un VISTAZO (5 min — ya estás ahí, y el tiempo no da para más) y R/W desde Cortlandt St hacia el norte.</t>
-        </is>
-      </c>
-      <c r="F114" s="37" t="inlineStr">
-        <is>
-          <t>Oculus / WTC Transportation Hub</t>
-        </is>
-      </c>
-      <c r="G114" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~4 min a pie · 0.3 km · estimado</t>
-        </is>
-      </c>
+      <c r="C114" s="43" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="D114" s="44" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E114" s="45" t="inlineStr">
+        <is>
+          <t>★ ENCUENTRO CON THAIS. Lo que MÁS rinde: verse DIRECTO en la puerta del MoMI a las 16:20 (36-01 35 Ave, N/W hasta 36 Av) — cada uno llega por su lado y el museo gana 10-15 min. Si prefieren encontrarse antes en Manhattan: Lexington Av-59 St 16:00 y N/W juntos (JP puede llegar 16:05-16:10 si el WTC se estiró: avisale que es ±10).</t>
+        </is>
+      </c>
+      <c r="F114" s="43" t="inlineStr"/>
+      <c r="G114" s="40" t="inlineStr"/>
       <c r="H114" s="41" t="inlineStr"/>
       <c r="I114" s="41" t="inlineStr"/>
     </row>
@@ -35501,12 +35485,12 @@
       <c r="A115" s="35" t="n"/>
       <c r="B115" s="42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C115" s="43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="D115" s="44" t="inlineStr">
@@ -35516,46 +35500,46 @@
       </c>
       <c r="E115" s="45" t="inlineStr">
         <is>
-          <t>★ ENCUENTRO CON THAIS. Lo que MÁS rinde: verse DIRECTO en la puerta del MoMI a las 16:20 (36-01 35 Ave, N/W hasta 36 Av) — cada uno llega por su lado y el museo gana 10-15 min. Si prefieren encontrarse antes en Manhattan: Lexington Av-59 St 16:00 y N/W juntos (JP puede llegar 16:05-16:10 si el WTC se estiró: avisale que es ±10).</t>
-        </is>
-      </c>
-      <c r="F115" s="43" t="inlineStr"/>
-      <c r="G115" s="40" t="inlineStr"/>
+          <t>★★ MUSEUM OF THE MOVING IMAGE — GRATIS los jueves 14-18, sus únicas horas del jueves. RECUPERADO: había quedado afuera del plan y ustedes lo tienen 2/2. Una hora y media alcanza para Behind the Screen y los Muppets originales de Jim Henson. Cierra 18:00 EN PUNTO. (N/W hasta 36 Av + 8 min a pie.)</t>
+        </is>
+      </c>
+      <c r="F115" s="43" t="inlineStr">
+        <is>
+          <t>Museum of the Moving Image</t>
+        </is>
+      </c>
+      <c r="G115" s="40" t="inlineStr">
+        <is>
+          <t>🚇 ~40 min en subte · 11.5 km (a pie 155 min) · estimado</t>
+        </is>
+      </c>
       <c r="H115" s="41" t="inlineStr"/>
       <c r="I115" s="41" t="inlineStr"/>
     </row>
-    <row r="116" ht="30" customHeight="1">
+    <row r="116" ht="16" customHeight="1">
       <c r="A116" s="35" t="n"/>
-      <c r="B116" s="42" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C116" s="43" t="inlineStr">
+      <c r="B116" s="36" t="inlineStr">
         <is>
           <t>18:05</t>
         </is>
       </c>
-      <c r="D116" s="44" t="inlineStr">
+      <c r="C116" s="37" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="D116" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E116" s="45" t="inlineStr">
-        <is>
-          <t>★★ MUSEUM OF THE MOVING IMAGE — GRATIS los jueves 14-18, sus únicas horas del jueves. RECUPERADO: había quedado afuera del plan y ustedes lo tienen 2/2. Una hora y media alcanza para Behind the Screen y los Muppets originales de Jim Henson. Cierra 18:00 EN PUNTO. (N/W hasta 36 Av + 8 min a pie.)</t>
-        </is>
-      </c>
-      <c r="F116" s="43" t="inlineStr">
-        <is>
-          <t>Museum of the Moving Image</t>
-        </is>
-      </c>
-      <c r="G116" s="40" t="inlineStr">
-        <is>
-          <t>🚇 ~40 min en subte · 11.5 km (a pie 155 min) · estimado</t>
-        </is>
-      </c>
+      <c r="E116" s="39" t="inlineStr">
+        <is>
+          <t>Subte N/W desde 36 Av hasta Times Sq y 1/2/3 hasta 72 St (~45 min).</t>
+        </is>
+      </c>
+      <c r="F116" s="37" t="inlineStr"/>
+      <c r="G116" s="40" t="inlineStr"/>
       <c r="H116" s="41" t="inlineStr"/>
       <c r="I116" s="41" t="inlineStr"/>
     </row>
@@ -35563,12 +35547,12 @@
       <c r="A117" s="35" t="n"/>
       <c r="B117" s="36" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="C117" s="37" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="D117" s="38" t="inlineStr">
@@ -35578,24 +35562,28 @@
       </c>
       <c r="E117" s="39" t="inlineStr">
         <is>
-          <t>Subte N/W desde 36 Av hasta Times Sq y 1/2/3 hasta 72 St (~45 min).</t>
-        </is>
-      </c>
-      <c r="F117" s="37" t="inlineStr"/>
+          <t>The Beacon: check-in formal y subir las maletas.</t>
+        </is>
+      </c>
+      <c r="F117" s="37" t="inlineStr">
+        <is>
+          <t>Hotel The Beacon (3-6 sep)</t>
+        </is>
+      </c>
       <c r="G117" s="40" t="inlineStr"/>
       <c r="H117" s="41" t="inlineStr"/>
       <c r="I117" s="41" t="inlineStr"/>
     </row>
-    <row r="118" ht="16" customHeight="1">
+    <row r="118" ht="30" customHeight="1">
       <c r="A118" s="35" t="n"/>
       <c r="B118" s="36" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="C118" s="37" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="D118" s="38" t="inlineStr">
@@ -35605,134 +35593,130 @@
       </c>
       <c r="E118" s="39" t="inlineStr">
         <is>
-          <t>The Beacon: check-in formal y subir las maletas.</t>
-        </is>
-      </c>
-      <c r="F118" s="37" t="inlineStr">
-        <is>
-          <t>Hotel The Beacon (3-6 sep)</t>
-        </is>
-      </c>
+          <t>Cena RÁPIDA en el Upper West Side, bajando por Broadway o Columbus. Hoy se come temprano y liviano: la noche tiene tres paradas y todas valen.</t>
+        </is>
+      </c>
+      <c r="F118" s="37" t="inlineStr"/>
       <c r="G118" s="40" t="inlineStr"/>
       <c r="H118" s="41" t="inlineStr"/>
       <c r="I118" s="41" t="inlineStr"/>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="35" t="n"/>
-      <c r="B119" s="36" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="C119" s="37" t="inlineStr">
+      <c r="B119" s="42" t="inlineStr">
         <is>
           <t>19:55</t>
         </is>
       </c>
-      <c r="D119" s="38" t="inlineStr">
+      <c r="C119" s="43" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="D119" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E119" s="39" t="inlineStr">
-        <is>
-          <t>Cena RÁPIDA en el Upper West Side, bajando por Broadway o Columbus. Hoy se come temprano y liviano: la noche tiene tres paradas y todas valen.</t>
-        </is>
-      </c>
-      <c r="F119" s="37" t="inlineStr"/>
-      <c r="G119" s="40" t="inlineStr"/>
+      <c r="E119" s="45" t="inlineStr">
+        <is>
+          <t>★ LINCOLN CENTER DE NOCHE (gratis, 20 min) — OJO, VERIFICADO el 27/8 y cambia lo que van a encontrar: esta noche la Josie Robertson Plaza NO está tranquila. El Met proyecta Tristan und Isolde (actos II y III) a las 20:00 en pantalla gigante, gratis y sin reserva, y despejan la plaza desde las 18:00 para armar 2.500 sillas. O sea: llegan justo cuando se está llenando. La fuente y los chandeliers siguen ahí, pero con multitud y pantalla. Puede ser mejor que el plan original —hay ambiente de estreno— o puede ser un quilombo: decidan en el momento. Si prefieren el Lincoln Center vacío, el espejo de agua con el Henry Moore está del lado norte, detrás del Vivian Beaumont, y ahí no hay nadie.</t>
+        </is>
+      </c>
+      <c r="F119" s="43" t="inlineStr">
+        <is>
+          <t>Lincoln Center (campus y plaza)</t>
+        </is>
+      </c>
+      <c r="G119" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~20 min a pie (1.3 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H119" s="41" t="inlineStr"/>
       <c r="I119" s="41" t="inlineStr"/>
     </row>
-    <row r="120" ht="30" customHeight="1">
+    <row r="120" ht="16" customHeight="1">
       <c r="A120" s="35" t="n"/>
-      <c r="B120" s="42" t="inlineStr">
-        <is>
-          <t>19:55</t>
-        </is>
-      </c>
-      <c r="C120" s="43" t="inlineStr">
+      <c r="B120" s="36" t="inlineStr">
         <is>
           <t>20:20</t>
         </is>
       </c>
-      <c r="D120" s="44" t="inlineStr">
+      <c r="C120" s="37" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="D120" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E120" s="45" t="inlineStr">
-        <is>
-          <t>★ LINCOLN CENTER DE NOCHE (gratis, 20 min) — OJO, VERIFICADO el 27/8 y cambia lo que van a encontrar: esta noche la Josie Robertson Plaza NO está tranquila. El Met proyecta Tristan und Isolde (actos II y III) a las 20:00 en pantalla gigante, gratis y sin reserva, y despejan la plaza desde las 18:00 para armar 2.500 sillas. O sea: llegan justo cuando se está llenando. La fuente y los chandeliers siguen ahí, pero con multitud y pantalla. Puede ser mejor que el plan original —hay ambiente de estreno— o puede ser un quilombo: decidan en el momento. Si prefieren el Lincoln Center vacío, el espejo de agua con el Henry Moore está del lado norte, detrás del Vivian Beaumont, y ahí no hay nadie.</t>
-        </is>
-      </c>
-      <c r="F120" s="43" t="inlineStr">
-        <is>
-          <t>Lincoln Center (campus y plaza)</t>
-        </is>
-      </c>
-      <c r="G120" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~20 min a pie (1.3 km) o 🚇 ~15 min · estimado</t>
-        </is>
-      </c>
+      <c r="E120" s="39" t="inlineStr">
+        <is>
+          <t>Caminar seis cuadras por Broadway hasta Columbus Circle (~8 min).</t>
+        </is>
+      </c>
+      <c r="F120" s="37" t="inlineStr"/>
+      <c r="G120" s="40" t="inlineStr"/>
       <c r="H120" s="41" t="inlineStr"/>
       <c r="I120" s="41" t="inlineStr"/>
     </row>
-    <row r="121" ht="16" customHeight="1">
+    <row r="121" ht="30" customHeight="1">
       <c r="A121" s="35" t="n"/>
-      <c r="B121" s="36" t="inlineStr">
-        <is>
-          <t>20:20</t>
-        </is>
-      </c>
-      <c r="C121" s="37" t="inlineStr">
+      <c r="B121" s="42" t="inlineStr">
         <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="D121" s="38" t="inlineStr">
+      <c r="C121" s="43" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="D121" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E121" s="39" t="inlineStr">
-        <is>
-          <t>Caminar seis cuadras por Broadway hasta Columbus Circle (~8 min).</t>
-        </is>
-      </c>
-      <c r="F121" s="37" t="inlineStr"/>
+      <c r="E121" s="45" t="inlineStr">
+        <is>
+          <t>★★ MO LOUNGE, PISO 35 DEL MANDARIN ORIENTAL (80 Columbus Circle) — el dato del amigo de Juan, con una corrección: es el piso 35, no el 60 (el hotel ocupa del 35 al 54). Ventanales de piso a techo sobre Central Park con la ciudad encendida abajo. Coctel ~$26-32, sin cover. RESERVAR por SevenRooms desde su web. Si prefieren algo más íntimo, en ese MISMO piso está The Bar (ex speakeasy The Office, 45 asientos, mar-sáb 17-1h).</t>
+        </is>
+      </c>
+      <c r="F121" s="43" t="inlineStr">
+        <is>
+          <t>MO Lounge — Mandarin Oriental (piso 35)</t>
+        </is>
+      </c>
       <c r="G121" s="40" t="inlineStr"/>
       <c r="H121" s="41" t="inlineStr"/>
       <c r="I121" s="41" t="inlineStr"/>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="35" t="n"/>
-      <c r="B122" s="42" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C122" s="43" t="inlineStr">
+      <c r="B122" s="36" t="inlineStr">
         <is>
           <t>20:55</t>
         </is>
       </c>
-      <c r="D122" s="44" t="inlineStr">
+      <c r="C122" s="37" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="D122" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E122" s="45" t="inlineStr">
-        <is>
-          <t>★★ MO LOUNGE, PISO 35 DEL MANDARIN ORIENTAL (80 Columbus Circle) — el dato del amigo de Juan, con una corrección: es el piso 35, no el 60 (el hotel ocupa del 35 al 54). Ventanales de piso a techo sobre Central Park con la ciudad encendida abajo. Coctel ~$26-32, sin cover. RESERVAR por SevenRooms desde su web. Si prefieren algo más íntimo, en ese MISMO piso está The Bar (ex speakeasy The Office, 45 asientos, mar-sáb 17-1h).</t>
-        </is>
-      </c>
-      <c r="F122" s="43" t="inlineStr">
-        <is>
-          <t>MO Lounge — Mandarin Oriental (piso 35)</t>
-        </is>
-      </c>
+      <c r="E122" s="39" t="inlineStr">
+        <is>
+          <t>Bajar en ascensor: Dizzy's está EN EL MISMO EDIFICIO (10 Columbus Circle, piso 5). Cero calle, cero frío.</t>
+        </is>
+      </c>
+      <c r="F122" s="37" t="inlineStr"/>
       <c r="G122" s="40" t="inlineStr"/>
       <c r="H122" s="41" t="inlineStr"/>
       <c r="I122" s="41" t="inlineStr"/>
@@ -35741,14 +35725,10 @@
       <c r="A123" s="35" t="n"/>
       <c r="B123" s="36" t="inlineStr">
         <is>
-          <t>20:55</t>
-        </is>
-      </c>
-      <c r="C123" s="37" t="inlineStr">
-        <is>
           <t>21:00</t>
         </is>
       </c>
+      <c r="C123" s="37" t="inlineStr"/>
       <c r="D123" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35756,72 +35736,76 @@
       </c>
       <c r="E123" s="39" t="inlineStr">
         <is>
-          <t>Bajar en ascensor: Dizzy's está EN EL MISMO EDIFICIO (10 Columbus Circle, piso 5). Cero calle, cero frío.</t>
-        </is>
-      </c>
-      <c r="F123" s="37" t="inlineStr"/>
+          <t>★ Dizzy's Club — ventanales sobre Central Park detrás del escenario, un piso abajo del cóctel. SEAMOS HONESTOS: JP lleva ~17 horas en pie con 5 de sueño. Decidan A LAS 20:00, arriba en el Mandarin: si están enteros, bajan; si no, se quedan con la vista y el trago, que ya es un cierre precioso. El set Late Night (~22:45) cuesta una fracción — variante para valientes.</t>
+        </is>
+      </c>
+      <c r="F123" s="37" t="inlineStr">
+        <is>
+          <t>Dizzy's Club (Jazz at Lincoln Center)</t>
+        </is>
+      </c>
       <c r="G123" s="40" t="inlineStr"/>
       <c r="H123" s="41" t="inlineStr"/>
       <c r="I123" s="41" t="inlineStr"/>
     </row>
-    <row r="124" ht="30" customHeight="1">
-      <c r="A124" s="35" t="n"/>
-      <c r="B124" s="36" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C124" s="37" t="inlineStr"/>
-      <c r="D124" s="38" t="inlineStr">
+    <row r="124" ht="32" customHeight="1">
+      <c r="A124" s="46" t="inlineStr">
+        <is>
+          <t>ALTERNATIVA / OJO:  ⚠️ EL PROBLEMA DE LA NOCHE ANTERIOR: si JP viaja desde New Jersey el jueves, significa que durmió allá el miércoles — y el miércoles el SummerStage termina a las 22:00 en Central Park. Llegando a Penn ~22:25 se toma el directo de las 22:48, que deja en Raritan ~0:04, más Uber: llegada al hotel ~0:25 y despertador a las 5:45. Son cinco horas de sueño antes de un día completo. Tres salidas: (a) salir del SummerStage a las 21:15, después del set principal; (b) quedarse una noche más en el JGStay y que Thais lleve las maletas el jueves (implica tocar la reserva); (c) tomar el tren de las 7:13 en vez del de 6:55 y arrancar 20 minutos más tarde. Verificá los horarios exactos de la tarde-noche en njtransit.com: solo tengo confirmado el directo de las 22:48. // EL FERRY, SI LES DUELE (lo tienen 2/2): al salir del MoMI, W directo hasta Whitehall (~50 min), ferry ~19:15 — el atardecer (~19:22) de ida y la Estatua y el skyline ILUMINADOS de vuelta; check-in ~21:15, cena tarde cerca del hotel, y Dizzy's tiene set Late Night los jueves ~22:45 como consuelo. Es MÁS día: elíjanlo solo si llegan enteros. // Siguen afuera: MoMA PS1, Astoria y Gantry (sin hueco); ya habían salido Noguchi, Astoria Park y Socrates por interés bajo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="33" t="inlineStr">
+        <is>
+          <t>DÍA 7 · Viernes 04/09 · Vessel + High Line, SUMMIT al atardecer y el VANGUARD de a dos  —  base: The Beacon  ·  Ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="32" customHeight="1">
+      <c r="A127" s="34" t="inlineStr">
+        <is>
+          <t>Salieron el West Village, Washington Square y el Whitney; entraron el High Line, THE VESSEL (al pie del arranque, $10 y 45 min), la Morgan (hoy GRATIS 17-20) y SUMMIT — que se movió AL ATARDECER por el pedido de ustedes: entrada 18:10, luz plena, la puesta ~19:21 multiplicada por los espejos de Kusama (es EL lugar de la ciudad para ese momento) y la noche encendida hasta las 20:15. EL PAGO, dicho honesto: la Morgan se hace en una hora entrando 17:00 en punto, y la cena de hoy es un bocado rápido — por eso el almuerzo en Chelsea Market es EL fuerte del día. SALIÓ GRAND CENTRAL: estaba a las 16:20 con el argumento de que JP ya lo vio el lunes y Thais no — pero ella lo tiene en 0, así que eran 40 minutos para alguien que no lo quiere. Sin esa parada tampoco hace falta cortar Chelsea a las 15:50: se sale 16:25 derecho a la Morgan y la tarde de galerías y almuerzo gana una hora larga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="16" customHeight="1">
+      <c r="A128" s="35" t="n"/>
+      <c r="B128" s="36" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C128" s="37" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="D128" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E124" s="39" t="inlineStr">
-        <is>
-          <t>★ Dizzy's Club — ventanales sobre Central Park detrás del escenario, un piso abajo del cóctel. SEAMOS HONESTOS: JP lleva ~17 horas en pie con 5 de sueño. Decidan A LAS 20:00, arriba en el Mandarin: si están enteros, bajan; si no, se quedan con la vista y el trago, que ya es un cierre precioso. El set Late Night (~22:45) cuesta una fracción — variante para valientes.</t>
-        </is>
-      </c>
-      <c r="F124" s="37" t="inlineStr">
-        <is>
-          <t>Dizzy's Club (Jazz at Lincoln Center)</t>
-        </is>
-      </c>
-      <c r="G124" s="40" t="inlineStr"/>
-      <c r="H124" s="41" t="inlineStr"/>
-      <c r="I124" s="41" t="inlineStr"/>
-    </row>
-    <row r="125" ht="32" customHeight="1">
-      <c r="A125" s="46" t="inlineStr">
-        <is>
-          <t>ALTERNATIVA / OJO:  ⚠️ EL PROBLEMA DE LA NOCHE ANTERIOR: si JP viaja desde New Jersey el jueves, significa que durmió allá el miércoles — y el miércoles el SummerStage termina a las 22:00 en Central Park. Llegando a Penn ~22:25 se toma el directo de las 22:48, que deja en Raritan ~0:04, más Uber: llegada al hotel ~0:25 y despertador a las 5:45. Son cinco horas de sueño antes de un día completo. Tres salidas: (a) salir del SummerStage a las 21:15, después del set principal; (b) quedarse una noche más en el JGStay y que Thais lleve las maletas el jueves (implica tocar la reserva); (c) tomar el tren de las 7:13 en vez del de 6:55 y arrancar 20 minutos más tarde. Verificá los horarios exactos de la tarde-noche en njtransit.com: solo tengo confirmado el directo de las 22:48. // EL FERRY, SI LES DUELE (lo tienen 2/2): al salir del MoMI, W directo hasta Whitehall (~50 min), ferry ~19:15 — el atardecer (~19:22) de ida y la Estatua y el skyline ILUMINADOS de vuelta; check-in ~21:15, cena tarde cerca del hotel, y Dizzy's tiene set Late Night los jueves ~22:45 como consuelo. Es MÁS día: elíjanlo solo si llegan enteros. // Siguen afuera: MoMA PS1, Astoria y Gantry (sin hueco); ya habían salido Noguchi, Astoria Park y Socrates por interés bajo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="22" customHeight="1">
-      <c r="A127" s="33" t="inlineStr">
-        <is>
-          <t>DÍA 7 · Viernes 04/09 · Vessel + High Line, SUMMIT al atardecer y el VANGUARD de a dos  —  base: The Beacon  ·  Ambos</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="32" customHeight="1">
-      <c r="A128" s="34" t="inlineStr">
-        <is>
-          <t>Salieron el West Village, Washington Square y el Whitney; entraron el High Line, THE VESSEL (al pie del arranque, $10 y 45 min), la Morgan (hoy GRATIS 17-20) y SUMMIT — que se movió AL ATARDECER por el pedido de ustedes: entrada 18:10, luz plena, la puesta ~19:21 multiplicada por los espejos de Kusama (es EL lugar de la ciudad para ese momento) y la noche encendida hasta las 20:15. EL PAGO, dicho honesto: la Morgan se hace en una hora entrando 17:00 en punto, y la cena de hoy es un bocado rápido — por eso el almuerzo en Chelsea Market es EL fuerte del día. SALIÓ GRAND CENTRAL: estaba a las 16:20 con el argumento de que JP ya lo vio el lunes y Thais no — pero ella lo tiene en 0, así que eran 40 minutos para alguien que no lo quiere. Sin esa parada tampoco hace falta cortar Chelsea a las 15:50: se sale 16:25 derecho a la Morgan y la tarde de galerías y almuerzo gana una hora larga.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="16" customHeight="1">
+      <c r="E128" s="39" t="inlineStr">
+        <is>
+          <t>Subte a Hudson Yards.</t>
+        </is>
+      </c>
+      <c r="F128" s="37" t="inlineStr"/>
+      <c r="G128" s="40" t="inlineStr"/>
+      <c r="H128" s="41" t="inlineStr"/>
+      <c r="I128" s="41" t="inlineStr"/>
+    </row>
+    <row r="129" ht="30" customHeight="1">
       <c r="A129" s="35" t="n"/>
       <c r="B129" s="36" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="C129" s="37" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D129" s="38" t="inlineStr">
@@ -35831,7 +35815,7 @@
       </c>
       <c r="E129" s="39" t="inlineStr">
         <is>
-          <t>Subte a Hudson Yards.</t>
+          <t>La plaza de Hudson Yards mientras abre el Vessel: The Shops y el Shed desde afuera. Sacar el timed ticket de las 10:00 online antes.</t>
         </is>
       </c>
       <c r="F129" s="37" t="inlineStr"/>
@@ -35841,27 +35825,31 @@
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="35" t="n"/>
-      <c r="B130" s="36" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="C130" s="37" t="inlineStr">
+      <c r="B130" s="42" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D130" s="38" t="inlineStr">
+      <c r="C130" s="43" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="D130" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E130" s="39" t="inlineStr">
-        <is>
-          <t>La plaza de Hudson Yards mientras abre el Vessel: The Shops y el Shed desde afuera. Sacar el timed ticket de las 10:00 online antes.</t>
-        </is>
-      </c>
-      <c r="F130" s="37" t="inlineStr"/>
+      <c r="E130" s="45" t="inlineStr">
+        <is>
+          <t>★ THE VESSEL — la escalera infinita de Heatherwick: 154 tramos, 2.500 escalones, $10. Reabierto con redes; algunos tramos altos hacia el Hudson siguen cerrados, y hay ascensor cada 15 min. Subir es la única forma de entenderla. Si Thais prefiere no subir, la plaza está al pie.</t>
+        </is>
+      </c>
+      <c r="F130" s="43" t="inlineStr">
+        <is>
+          <t>The Vessel</t>
+        </is>
+      </c>
       <c r="G130" s="40" t="inlineStr"/>
       <c r="H130" s="41" t="inlineStr"/>
       <c r="I130" s="41" t="inlineStr"/>
@@ -35870,12 +35858,12 @@
       <c r="A131" s="35" t="n"/>
       <c r="B131" s="42" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="C131" s="43" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="D131" s="44" t="inlineStr">
@@ -35885,48 +35873,52 @@
       </c>
       <c r="E131" s="45" t="inlineStr">
         <is>
-          <t>★ THE VESSEL — la escalera infinita de Heatherwick: 154 tramos, 2.500 escalones, $10. Reabierto con redes; algunos tramos altos hacia el Hudson siguen cerrados, y hay ascensor cada 15 min. Subir es la única forma de entenderla. Si Thais prefiere no subir, la plaza está al pie.</t>
+          <t>★ THE HIGH LINE completo, de norte a sur (2,3 km) — arranca ahí mismo, en 30th y 10ª. Vía ferroviaria elevada convertida en parque lineal. Incluye el Buda de arenisca de 9 metros de Tuan Andrew Nguyen.</t>
         </is>
       </c>
       <c r="F131" s="43" t="inlineStr">
         <is>
-          <t>The Vessel</t>
-        </is>
-      </c>
-      <c r="G131" s="40" t="inlineStr"/>
+          <t>The High Line</t>
+        </is>
+      </c>
+      <c r="G131" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~12 min a pie · 0.9 km · estimado</t>
+        </is>
+      </c>
       <c r="H131" s="41" t="inlineStr"/>
       <c r="I131" s="41" t="inlineStr"/>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="35" t="n"/>
-      <c r="B132" s="42" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="C132" s="43" t="inlineStr">
+      <c r="B132" s="36" t="inlineStr">
         <is>
           <t>12:20</t>
         </is>
       </c>
-      <c r="D132" s="44" t="inlineStr">
+      <c r="C132" s="37" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D132" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E132" s="45" t="inlineStr">
-        <is>
-          <t>★ THE HIGH LINE completo, de norte a sur (2,3 km) — arranca ahí mismo, en 30th y 10ª. Vía ferroviaria elevada convertida en parque lineal. Incluye el Buda de arenisca de 9 metros de Tuan Andrew Nguyen.</t>
-        </is>
-      </c>
-      <c r="F132" s="43" t="inlineStr">
-        <is>
-          <t>The High Line</t>
+      <c r="E132" s="39" t="inlineStr">
+        <is>
+          <t>Little Island — el parque flotante de Heatherwick sobre 132 macetas de hormigón, al final del High Line. Gratis.</t>
+        </is>
+      </c>
+      <c r="F132" s="37" t="inlineStr">
+        <is>
+          <t>Little Island</t>
         </is>
       </c>
       <c r="G132" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~12 min a pie · 0.9 km · estimado</t>
+          <t>🚶 ~15 min a pie · 1.1 km · estimado</t>
         </is>
       </c>
       <c r="H132" s="41" t="inlineStr"/>
@@ -35934,63 +35926,63 @@
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="35" t="n"/>
-      <c r="B133" s="36" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="C133" s="37" t="inlineStr">
+      <c r="B133" s="42" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="D133" s="38" t="inlineStr">
+      <c r="C133" s="43" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D133" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E133" s="39" t="inlineStr">
-        <is>
-          <t>Little Island — el parque flotante de Heatherwick sobre 132 macetas de hormigón, al final del High Line. Gratis.</t>
-        </is>
-      </c>
-      <c r="F133" s="37" t="inlineStr">
-        <is>
-          <t>Little Island</t>
-        </is>
-      </c>
-      <c r="G133" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~15 min a pie · 1.1 km · estimado</t>
-        </is>
-      </c>
+      <c r="E133" s="45" t="inlineStr">
+        <is>
+          <t>Galerías de Chelsea COMPLETAS — W 19th a W 27th entre la 10ª y la 11ª, concentradas en W 24th y W 21st (Gagosian, Pace, Zwirner). Gratis, se entra y se sale. El recorte del Vessel se devolvió: SUMMIT pasó al atardecer y la tarde se estiró.</t>
+        </is>
+      </c>
+      <c r="F133" s="43" t="inlineStr"/>
+      <c r="G133" s="40" t="inlineStr"/>
       <c r="H133" s="41" t="inlineStr"/>
       <c r="I133" s="41" t="inlineStr"/>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="35" t="n"/>
-      <c r="B134" s="42" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C134" s="43" t="inlineStr">
+      <c r="B134" s="36" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="D134" s="44" t="inlineStr">
+      <c r="C134" s="37" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="D134" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E134" s="45" t="inlineStr">
-        <is>
-          <t>Galerías de Chelsea COMPLETAS — W 19th a W 27th entre la 10ª y la 11ª, concentradas en W 24th y W 21st (Gagosian, Pace, Zwirner). Gratis, se entra y se sale. El recorte del Vessel se devolvió: SUMMIT pasó al atardecer y la tarde se estiró.</t>
-        </is>
-      </c>
-      <c r="F134" s="43" t="inlineStr"/>
-      <c r="G134" s="40" t="inlineStr"/>
+      <c r="E134" s="39" t="inlineStr">
+        <is>
+          <t>Almuerzo en Chelsea Market — COMER FUERTE: es la comida grande del día, la cena de hoy es un bocado rápido entre el SUMMIT y el Vanguard. Los Tacos No.1 o Very Fresh Noodles. Ahora hay casi DOS HORAS: sin apuro, y si quedaron galerías de Chelsea sin ver, se vuelve. ★ HEATONIST está ADENTRO de este mismo mercado (12-18:45): más de 100 salsas picantes para probar, con el lineup de Hot Ones. Si el sábado no llegan a la de Williamsburg, esta es la misma cata en menos metros.</t>
+        </is>
+      </c>
+      <c r="F134" s="37" t="inlineStr">
+        <is>
+          <t>Chelsea Market</t>
+        </is>
+      </c>
+      <c r="G134" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~7 min a pie · 0.5 km · estimado</t>
+        </is>
+      </c>
       <c r="H134" s="41" t="inlineStr"/>
       <c r="I134" s="41" t="inlineStr"/>
     </row>
@@ -35998,12 +35990,12 @@
       <c r="A135" s="35" t="n"/>
       <c r="B135" s="36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="C135" s="37" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D135" s="38" t="inlineStr">
@@ -36013,134 +36005,126 @@
       </c>
       <c r="E135" s="39" t="inlineStr">
         <is>
-          <t>Almuerzo en Chelsea Market — COMER FUERTE: es la comida grande del día, la cena de hoy es un bocado rápido entre el SUMMIT y el Vanguard. Los Tacos No.1 o Very Fresh Noodles. Ahora hay casi DOS HORAS: sin apuro, y si quedaron galerías de Chelsea sin ver, se vuelve. ★ HEATONIST está ADENTRO de este mismo mercado (12-18:45): más de 100 salsas picantes para probar, con el lineup de Hot Ones. Si el sábado no llegan a la de Williamsburg, esta es la misma cata en menos metros.</t>
-        </is>
-      </c>
-      <c r="F135" s="37" t="inlineStr">
-        <is>
-          <t>Chelsea Market</t>
-        </is>
-      </c>
-      <c r="G135" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~7 min a pie · 0.5 km · estimado</t>
-        </is>
-      </c>
+          <t>A la Morgan: L desde 14 St-8 Av hasta Union Sq y 6 hasta 33 St, o A/C/E hasta 34 St-Penn y siete cuadras a pie (~30 min). Salir 16:25 deja margen para entrar 17:00 EN PUNTO.</t>
+        </is>
+      </c>
+      <c r="F135" s="37" t="inlineStr"/>
+      <c r="G135" s="40" t="inlineStr"/>
       <c r="H135" s="41" t="inlineStr"/>
       <c r="I135" s="41" t="inlineStr"/>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="35" t="n"/>
-      <c r="B136" s="36" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="C136" s="37" t="inlineStr">
+      <c r="B136" s="42" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D136" s="38" t="inlineStr">
+      <c r="C136" s="43" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D136" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E136" s="39" t="inlineStr">
-        <is>
-          <t>A la Morgan: L desde 14 St-8 Av hasta Union Sq y 6 hasta 33 St, o A/C/E hasta 34 St-Penn y siete cuadras a pie (~30 min). Salir 16:25 deja margen para entrar 17:00 EN PUNTO.</t>
-        </is>
-      </c>
-      <c r="F136" s="37" t="inlineStr"/>
+      <c r="E136" s="45" t="inlineStr">
+        <is>
+          <t>★ MORGAN LIBRARY — GRATIS los viernes 17-20h: entrar 17:00 EN PUNTO y hacerla en una hora — la biblioteca son tres salas gloriosas (estanterías de nogal, la Biblia de Gutenberg): alcanza. RESERVA OBLIGATORIA, se libera el viernes 28 de agosto. Está a 8 min a pie de One Vanderbilt.</t>
+        </is>
+      </c>
+      <c r="F136" s="43" t="inlineStr">
+        <is>
+          <t>The Morgan Library &amp; Museum</t>
+        </is>
+      </c>
       <c r="G136" s="40" t="inlineStr"/>
       <c r="H136" s="41" t="inlineStr"/>
       <c r="I136" s="41" t="inlineStr"/>
     </row>
-    <row r="137" ht="30" customHeight="1">
+    <row r="137" ht="16" customHeight="1">
       <c r="A137" s="35" t="n"/>
-      <c r="B137" s="42" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C137" s="43" t="inlineStr">
+      <c r="B137" s="36" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D137" s="44" t="inlineStr">
+      <c r="C137" s="37" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D137" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E137" s="45" t="inlineStr">
-        <is>
-          <t>★ MORGAN LIBRARY — GRATIS los viernes 17-20h: entrar 17:00 EN PUNTO y hacerla en una hora — la biblioteca son tres salas gloriosas (estanterías de nogal, la Biblia de Gutenberg): alcanza. RESERVA OBLIGATORIA, se libera el viernes 28 de agosto. Está a 8 min a pie de One Vanderbilt.</t>
-        </is>
-      </c>
-      <c r="F137" s="43" t="inlineStr">
-        <is>
-          <t>The Morgan Library &amp; Museum</t>
-        </is>
-      </c>
+      <c r="E137" s="39" t="inlineStr">
+        <is>
+          <t>Caminar las seis cuadras de la Morgan a One Vanderbilt (~8-10 min).</t>
+        </is>
+      </c>
+      <c r="F137" s="37" t="inlineStr"/>
       <c r="G137" s="40" t="inlineStr"/>
       <c r="H137" s="41" t="inlineStr"/>
       <c r="I137" s="41" t="inlineStr"/>
     </row>
-    <row r="138" ht="16" customHeight="1">
+    <row r="138" ht="30" customHeight="1">
       <c r="A138" s="35" t="n"/>
-      <c r="B138" s="36" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C138" s="37" t="inlineStr">
+      <c r="B138" s="42" t="inlineStr">
         <is>
           <t>18:10</t>
         </is>
       </c>
-      <c r="D138" s="38" t="inlineStr">
+      <c r="C138" s="43" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="D138" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E138" s="39" t="inlineStr">
-        <is>
-          <t>Caminar las seis cuadras de la Morgan a One Vanderbilt (~8-10 min).</t>
-        </is>
-      </c>
-      <c r="F138" s="37" t="inlineStr"/>
+      <c r="E138" s="45" t="inlineStr">
+        <is>
+          <t>★★ SUMMIT ONE VANDERBILT — EL ARCO COMPLETO: entrada 18:10 con luz, el atardecer ~19:21 multiplicado por los espejos infinitos de Kusama, y la noche encendida hasta ~20:15. Ticket ATARDECER $57-63 — es la franja que primero se agota: reservar YA. NO está en ningún pase.</t>
+        </is>
+      </c>
+      <c r="F138" s="43" t="inlineStr">
+        <is>
+          <t>SUMMIT One Vanderbilt</t>
+        </is>
+      </c>
       <c r="G138" s="40" t="inlineStr"/>
       <c r="H138" s="41" t="inlineStr"/>
       <c r="I138" s="41" t="inlineStr"/>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="35" t="n"/>
-      <c r="B139" s="42" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="C139" s="43" t="inlineStr">
+      <c r="B139" s="36" t="inlineStr">
         <is>
           <t>20:20</t>
         </is>
       </c>
-      <c r="D139" s="44" t="inlineStr">
+      <c r="C139" s="37" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="D139" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E139" s="45" t="inlineStr">
-        <is>
-          <t>★★ SUMMIT ONE VANDERBILT — EL ARCO COMPLETO: entrada 18:10 con luz, el atardecer ~19:21 multiplicado por los espejos infinitos de Kusama, y la noche encendida hasta ~20:15. Ticket ATARDECER $57-63 — es la franja que primero se agota: reservar YA. NO está en ningún pase.</t>
-        </is>
-      </c>
-      <c r="F139" s="43" t="inlineStr">
-        <is>
-          <t>SUMMIT One Vanderbilt</t>
-        </is>
-      </c>
+      <c r="E139" s="39" t="inlineStr">
+        <is>
+          <t>Bajar AL VILLAGE PRIMERO y cenar allá: 4/5/6 o 7 hasta 14 St-Union Sq y 1 hasta Christopher St (~25 min). Cenar cerca de Grand Central y bajar después llega justo; hacerlo al revés deja margen.</t>
+        </is>
+      </c>
+      <c r="F139" s="37" t="inlineStr"/>
       <c r="G139" s="40" t="inlineStr"/>
       <c r="H139" s="41" t="inlineStr"/>
       <c r="I139" s="41" t="inlineStr"/>
@@ -36149,12 +36133,12 @@
       <c r="A140" s="35" t="n"/>
       <c r="B140" s="36" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="C140" s="37" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="D140" s="38" t="inlineStr">
@@ -36164,7 +36148,7 @@
       </c>
       <c r="E140" s="39" t="inlineStr">
         <is>
-          <t>Bajar AL VILLAGE PRIMERO y cenar allá: 4/5/6 o 7 hasta 14 St-Union Sq y 1 hasta Christopher St (~25 min). Cenar cerca de Grand Central y bajar después llega justo; hacerlo al revés deja margen.</t>
+          <t>Cena en el West Village, a cinco minutos del club. El Vanguard NO sirve NADA de comida (lo dicen así: 'ni un maní') y no se permite entrar comida: lo que no cenen ahora, no se cena. 40 minutos alcanzan.</t>
         </is>
       </c>
       <c r="F140" s="37" t="inlineStr"/>
@@ -36176,12 +36160,12 @@
       <c r="A141" s="35" t="n"/>
       <c r="B141" s="36" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C141" s="37" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D141" s="38" t="inlineStr">
@@ -36191,7 +36175,7 @@
       </c>
       <c r="E141" s="39" t="inlineStr">
         <is>
-          <t>Cena en el West Village, a cinco minutos del club. El Vanguard NO sirve NADA de comida (lo dicen así: 'ni un maní') y no se permite entrar comida: lo que no cenen ahora, no se cena. 40 minutos alcanzan.</t>
+          <t>EN LA PUERTA DEL VANGUARD a las 21:30 EN PUNTO: el acomodo del segundo set arranca a esa hora y los asientos son POR ORDEN DE LLEGADA — la entrada es General Admission, no numerada. Con 123 asientos, los diez minutos de diferencia son estar frente al piano o contra la columna. El ticket lo dice: el acomodo tardío, con entrada o sin ella, queda a criterio del encargado.</t>
         </is>
       </c>
       <c r="F141" s="37" t="inlineStr"/>
@@ -36201,199 +36185,199 @@
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="35" t="n"/>
-      <c r="B142" s="36" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C142" s="37" t="inlineStr">
+      <c r="B142" s="42" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="D142" s="38" t="inlineStr">
+      <c r="C142" s="43" t="inlineStr"/>
+      <c r="D142" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E142" s="39" t="inlineStr">
-        <is>
-          <t>EN LA PUERTA DEL VANGUARD a las 21:30 EN PUNTO: el acomodo del segundo set arranca a esa hora y los asientos son POR ORDEN DE LLEGADA — la entrada es General Admission, no numerada. Con 123 asientos, los diez minutos de diferencia son estar frente al piano o contra la columna. El ticket lo dice: el acomodo tardío, con entrada o sin ella, queda a criterio del encargado.</t>
-        </is>
-      </c>
-      <c r="F142" s="37" t="inlineStr"/>
+      <c r="E142" s="45" t="inlineStr">
+        <is>
+          <t>★★ VILLAGE VANGUARD — JOHN PATITUCCI TRIO con Chris Potter y Brian Blade, SET DE LAS 22:00. Movido acá desde el martes para que vayan LOS DOS (pedido de Juan). El sótano triangular de 1935, 123 asientos, la acústica que grabó a Coltrane. ✔ ENTRADAS COMPRADAS el 26/8: 2 × General Admission $45 (#18741454 y #18741456), a nombre de Juan Pablo Garicoïts. Falta solo el mínimo de UNA CONSUMICIÓN por cabeza en la mesa (vale gaseosa, jugo o agua) — se paga ahí, aceptan tarjeta.</t>
+        </is>
+      </c>
+      <c r="F142" s="43" t="inlineStr">
+        <is>
+          <t>Village Vanguard</t>
+        </is>
+      </c>
       <c r="G142" s="40" t="inlineStr"/>
       <c r="H142" s="41" t="inlineStr"/>
       <c r="I142" s="41" t="inlineStr"/>
     </row>
-    <row r="143" ht="30" customHeight="1">
-      <c r="A143" s="35" t="n"/>
-      <c r="B143" s="42" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C143" s="43" t="inlineStr"/>
-      <c r="D143" s="44" t="inlineStr">
+    <row r="143" ht="32" customHeight="1">
+      <c r="A143" s="46" t="inlineStr">
+        <is>
+          <t>ALTERNATIVA / OJO:  ⚠️ OJO CON LA MAÑANA, y es nuevo: Juan hizo el HIGH LINE, LITTLE ISLAND y el VESSEL el miércoles temprano, solo. Los tres siguen en el plan de hoy porque THAIS NO LOS VIO —el Vessel además lo tienen 2/2 y es imprescindible— así que sacarlos la perjudica a ella. Decidan en el momento: si Juan la acompaña igual, el High Line de día con ella es otro paseo y no se pierde nada; si prefieren no repetir, esa mañana libera de 9:15 a 13:00 y ahí entran las galerías de Chelsea con calma, o el Whitney, que hoy es gratis de 17 a 22 pero abre 10:30. // EL CANJE DE ESTA NOCHE: para meter el Vanguard con Thais, SALIÓ BILL'S PLACE. No hay otra noche donde entre (Bill Saxton toca solo viernes y sábado, y el sábado está tomado por Peter Luger + el play + el Café Wha). Con las entradas ya compradas y sin cambios ni transferencias, el canje quedó CERRADO: Bill's Place sale del viaje. // EL WHITNEY, con los números verificados el 27/8: gratis todos los viernes de 17:00 a 22:00 (normal $30), y hoy pasan por Meatpacking, que es donde está. Coincide barrio, día y franja. El problema es el reloj y es serio: la Morgan también es hoy 17:00-20:00 y el SUMMIT entra 18:10. Meter el Whitney obliga a recortar el High Line o a soltar la Morgan, que ustedes tienen en 2 y el Whitney en 'quizás'. Si igual lo prefieren, el ticket gratis es OBLIGATORIO y hay que sacarlo antes. Si igual lo prefieren, el ticket gratis es OBLIGATORIO y el Whitney ahora cierra los martes. SI ALGO SALIERA MAL con el acomodo (llegar tarde y que no haya lugar): Mezzrow o Smalls quedan a cuatro cuadras ($25 con bebida, Smalls tiene jam de madrugada los viernes desde la 1:00), o el Blue Note — el 4 y 5 de septiembre toca Chief Adjuah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="22" customHeight="1">
+      <c r="A145" s="33" t="inlineStr">
+        <is>
+          <t>DÍA 8 · Sábado 05/09 · Brooklyn, Peter Luger, un PLAY y Café Wha hasta la madrugada  —  base: The Beacon  ·  Ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="32" customHeight="1">
+      <c r="A146" s="34" t="inlineStr">
+        <is>
+          <t>La gran noche del viaje, rearmada a pedido: el musical SALIÓ y entraron un PLAY de Broadway a las 19:30 y el CAFÉ WHA a las 23:45 — el sótano del Village donde debutaron Dylan y Hendrix, con reserva gratis ya pedida por Eventbrite. La cena temprana en Peter Luger (17:00) ahora existe exactamente para esto: porterhouse → telón → medianoche de soul y funk. Frankel's sigue afuera (a un porterhouse no se llega con un pastrami encima) y Westlight sigue opcional. ⚠️ La noche termina ~1:15-1:30: el domingo no tiene NADA fijo hasta las 16:00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="30" customHeight="1">
+      <c r="A147" s="35" t="n"/>
+      <c r="B147" s="36" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="C147" s="37" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D147" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E143" s="45" t="inlineStr">
-        <is>
-          <t>★★ VILLAGE VANGUARD — JOHN PATITUCCI TRIO con Chris Potter y Brian Blade, SET DE LAS 22:00. Movido acá desde el martes para que vayan LOS DOS (pedido de Juan). El sótano triangular de 1935, 123 asientos, la acústica que grabó a Coltrane. ✔ ENTRADAS COMPRADAS el 26/8: 2 × General Admission $45 (#18741454 y #18741456), a nombre de Juan Pablo Garicoïts. Falta solo el mínimo de UNA CONSUMICIÓN por cabeza en la mesa (vale gaseosa, jugo o agua) — se paga ahí, aceptan tarjeta.</t>
-        </is>
-      </c>
-      <c r="F143" s="43" t="inlineStr">
-        <is>
-          <t>Village Vanguard</t>
-        </is>
-      </c>
-      <c r="G143" s="40" t="inlineStr"/>
-      <c r="H143" s="41" t="inlineStr"/>
-      <c r="I143" s="41" t="inlineStr"/>
-    </row>
-    <row r="144" ht="32" customHeight="1">
-      <c r="A144" s="46" t="inlineStr">
-        <is>
-          <t>ALTERNATIVA / OJO:  ⚠️ OJO CON LA MAÑANA, y es nuevo: Juan hizo el HIGH LINE, LITTLE ISLAND y el VESSEL el miércoles temprano, solo. Los tres siguen en el plan de hoy porque THAIS NO LOS VIO —el Vessel además lo tienen 2/2 y es imprescindible— así que sacarlos la perjudica a ella. Decidan en el momento: si Juan la acompaña igual, el High Line de día con ella es otro paseo y no se pierde nada; si prefieren no repetir, esa mañana libera de 9:15 a 13:00 y ahí entran las galerías de Chelsea con calma, o el Whitney, que hoy es gratis de 17 a 22 pero abre 10:30. // EL CANJE DE ESTA NOCHE: para meter el Vanguard con Thais, SALIÓ BILL'S PLACE. No hay otra noche donde entre (Bill Saxton toca solo viernes y sábado, y el sábado está tomado por Peter Luger + el play + el Café Wha). Con las entradas ya compradas y sin cambios ni transferencias, el canje quedó CERRADO: Bill's Place sale del viaje. // EL WHITNEY, con los números verificados el 27/8: gratis todos los viernes de 17:00 a 22:00 (normal $30), y hoy pasan por Meatpacking, que es donde está. Coincide barrio, día y franja. El problema es el reloj y es serio: la Morgan también es hoy 17:00-20:00 y el SUMMIT entra 18:10. Meter el Whitney obliga a recortar el High Line o a soltar la Morgan, que ustedes tienen en 2 y el Whitney en 'quizás'. Si igual lo prefieren, el ticket gratis es OBLIGATORIO y hay que sacarlo antes. Si igual lo prefieren, el ticket gratis es OBLIGATORIO y el Whitney ahora cierra los martes. SI ALGO SALIERA MAL con el acomodo (llegar tarde y que no haya lugar): Mezzrow o Smalls quedan a cuatro cuadras ($25 con bebida, Smalls tiene jam de madrugada los viernes desde la 1:00), o el Blue Note — el 4 y 5 de septiembre toca Chief Adjuah.</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="22" customHeight="1">
-      <c r="A146" s="33" t="inlineStr">
-        <is>
-          <t>DÍA 8 · Sábado 05/09 · Brooklyn, Peter Luger, un PLAY y Café Wha hasta la madrugada  —  base: The Beacon  ·  Ambos</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="32" customHeight="1">
-      <c r="A147" s="34" t="inlineStr">
-        <is>
-          <t>La gran noche del viaje, rearmada a pedido: el musical SALIÓ y entraron un PLAY de Broadway a las 19:30 y el CAFÉ WHA a las 23:45 — el sótano del Village donde debutaron Dylan y Hendrix, con reserva gratis ya pedida por Eventbrite. La cena temprana en Peter Luger (17:00) ahora existe exactamente para esto: porterhouse → telón → medianoche de soul y funk. Frankel's sigue afuera (a un porterhouse no se llega con un pastrami encima) y Westlight sigue opcional. ⚠️ La noche termina ~1:15-1:30: el domingo no tiene NADA fijo hasta las 16:00.</t>
-        </is>
-      </c>
+      <c r="E147" s="39" t="inlineStr">
+        <is>
+          <t>Salir 8:15: 1/2/3 desde 72 St + transbordo a A/C hasta High St son ~40-45 min REALES. Llegar temprano a DUMBO es la diferencia entre la foto y la cola de fotos.</t>
+        </is>
+      </c>
+      <c r="F147" s="37" t="inlineStr"/>
+      <c r="G147" s="40" t="inlineStr"/>
+      <c r="H147" s="41" t="inlineStr"/>
+      <c r="I147" s="41" t="inlineStr"/>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="35" t="n"/>
-      <c r="B148" s="36" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="C148" s="37" t="inlineStr">
+      <c r="B148" s="42" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D148" s="38" t="inlineStr">
+      <c r="C148" s="43" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D148" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E148" s="39" t="inlineStr">
-        <is>
-          <t>Salir 8:15: 1/2/3 desde 72 St + transbordo a A/C hasta High St son ~40-45 min REALES. Llegar temprano a DUMBO es la diferencia entre la foto y la cola de fotos.</t>
-        </is>
-      </c>
-      <c r="F148" s="37" t="inlineStr"/>
+      <c r="E148" s="45" t="inlineStr">
+        <is>
+          <t>★ Brooklyn Bridge Park y DUMBO — muelles reconvertidos con el skyline de Lower Manhattan de frente, y la foto del Manhattan Bridge encuadrado en Washington y Water.</t>
+        </is>
+      </c>
+      <c r="F148" s="43" t="inlineStr">
+        <is>
+          <t>Brooklyn Bridge Park</t>
+        </is>
+      </c>
       <c r="G148" s="40" t="inlineStr"/>
       <c r="H148" s="41" t="inlineStr"/>
       <c r="I148" s="41" t="inlineStr"/>
     </row>
-    <row r="149" ht="30" customHeight="1">
+    <row r="149" ht="16" customHeight="1">
       <c r="A149" s="35" t="n"/>
-      <c r="B149" s="42" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="C149" s="43" t="inlineStr">
+      <c r="B149" s="36" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="D149" s="44" t="inlineStr">
+      <c r="C149" s="37" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="D149" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E149" s="45" t="inlineStr">
-        <is>
-          <t>★ Brooklyn Bridge Park y DUMBO — muelles reconvertidos con el skyline de Lower Manhattan de frente, y la foto del Manhattan Bridge encuadrado en Washington y Water.</t>
-        </is>
-      </c>
-      <c r="F149" s="43" t="inlineStr">
-        <is>
-          <t>Brooklyn Bridge Park</t>
-        </is>
-      </c>
-      <c r="G149" s="40" t="inlineStr"/>
+      <c r="E149" s="39" t="inlineStr">
+        <is>
+          <t>Brooklyn Heights Promenade — la postal clásica del skyline sobre el BQE.</t>
+        </is>
+      </c>
+      <c r="F149" s="37" t="inlineStr">
+        <is>
+          <t>Brooklyn Heights Promenade</t>
+        </is>
+      </c>
+      <c r="G149" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~8 min a pie · 0.6 km · estimado</t>
+        </is>
+      </c>
       <c r="H149" s="41" t="inlineStr"/>
       <c r="I149" s="41" t="inlineStr"/>
     </row>
-    <row r="150" ht="16" customHeight="1">
+    <row r="150" ht="30" customHeight="1">
       <c r="A150" s="35" t="n"/>
-      <c r="B150" s="36" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="C150" s="37" t="inlineStr">
+      <c r="B150" s="42" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="D150" s="38" t="inlineStr">
+      <c r="C150" s="43" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="D150" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E150" s="39" t="inlineStr">
-        <is>
-          <t>Brooklyn Heights Promenade — la postal clásica del skyline sobre el BQE.</t>
-        </is>
-      </c>
-      <c r="F150" s="37" t="inlineStr">
-        <is>
-          <t>Brooklyn Heights Promenade</t>
-        </is>
-      </c>
-      <c r="G150" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~8 min a pie · 0.6 km · estimado</t>
-        </is>
-      </c>
+      <c r="E150" s="45" t="inlineStr">
+        <is>
+          <t>★ NEW YORK TRANSIT MUSEUM — una estación de subte clausurada de 1936 con 20 vagones históricos en las vías originales; se puede subir a todos. $10. Cierra lunes y martes, así que hoy es el día.</t>
+        </is>
+      </c>
+      <c r="F150" s="43" t="inlineStr">
+        <is>
+          <t>New York Transit Museum</t>
+        </is>
+      </c>
+      <c r="G150" s="40" t="inlineStr"/>
       <c r="H150" s="41" t="inlineStr"/>
       <c r="I150" s="41" t="inlineStr"/>
     </row>
-    <row r="151" ht="30" customHeight="1">
+    <row r="151" ht="16" customHeight="1">
       <c r="A151" s="35" t="n"/>
-      <c r="B151" s="42" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="C151" s="43" t="inlineStr">
+      <c r="B151" s="36" t="inlineStr">
         <is>
           <t>12:45</t>
         </is>
       </c>
-      <c r="D151" s="44" t="inlineStr">
+      <c r="C151" s="37" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="D151" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E151" s="45" t="inlineStr">
-        <is>
-          <t>★ NEW YORK TRANSIT MUSEUM — una estación de subte clausurada de 1936 con 20 vagones históricos en las vías originales; se puede subir a todos. $10. Cierra lunes y martes, así que hoy es el día.</t>
-        </is>
-      </c>
-      <c r="F151" s="43" t="inlineStr">
-        <is>
-          <t>New York Transit Museum</t>
-        </is>
-      </c>
+      <c r="E151" s="39" t="inlineStr">
+        <is>
+          <t>Almuerzo en Downtown Brooklyn.</t>
+        </is>
+      </c>
+      <c r="F151" s="37" t="inlineStr"/>
       <c r="G151" s="40" t="inlineStr"/>
       <c r="H151" s="41" t="inlineStr"/>
       <c r="I151" s="41" t="inlineStr"/>
@@ -36402,12 +36386,12 @@
       <c r="A152" s="35" t="n"/>
       <c r="B152" s="36" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C152" s="37" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="D152" s="38" t="inlineStr">
@@ -36417,7 +36401,7 @@
       </c>
       <c r="E152" s="39" t="inlineStr">
         <is>
-          <t>Almuerzo en Downtown Brooklyn.</t>
+          <t>Subte a Williamsburg.</t>
         </is>
       </c>
       <c r="F152" s="37" t="inlineStr"/>
@@ -36425,74 +36409,82 @@
       <c r="H152" s="41" t="inlineStr"/>
       <c r="I152" s="41" t="inlineStr"/>
     </row>
-    <row r="153" ht="16" customHeight="1">
+    <row r="153" ht="30" customHeight="1">
       <c r="A153" s="35" t="n"/>
-      <c r="B153" s="36" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="C153" s="37" t="inlineStr">
+      <c r="B153" s="42" t="inlineStr">
         <is>
           <t>14:15</t>
         </is>
       </c>
-      <c r="D153" s="38" t="inlineStr">
+      <c r="C153" s="43" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="D153" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E153" s="39" t="inlineStr">
-        <is>
-          <t>Subte a Williamsburg.</t>
-        </is>
-      </c>
-      <c r="F153" s="37" t="inlineStr"/>
+      <c r="E153" s="45" t="inlineStr">
+        <is>
+          <t>★ Domino Park — ex refinería de azúcar; el paseo elevado pasa entre la maquinaria industrial conservada, con el Williamsburg Bridge y Midtown enfrente.</t>
+        </is>
+      </c>
+      <c r="F153" s="43" t="inlineStr">
+        <is>
+          <t>Domino Park</t>
+        </is>
+      </c>
       <c r="G153" s="40" t="inlineStr"/>
       <c r="H153" s="41" t="inlineStr"/>
       <c r="I153" s="41" t="inlineStr"/>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="35" t="n"/>
-      <c r="B154" s="42" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="C154" s="43" t="inlineStr">
+      <c r="B154" s="36" t="inlineStr">
         <is>
           <t>15:15</t>
         </is>
       </c>
-      <c r="D154" s="44" t="inlineStr">
+      <c r="C154" s="37" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="D154" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E154" s="45" t="inlineStr">
-        <is>
-          <t>★ Domino Park — ex refinería de azúcar; el paseo elevado pasa entre la maquinaria industrial conservada, con el Williamsburg Bridge y Midtown enfrente.</t>
-        </is>
-      </c>
-      <c r="F154" s="43" t="inlineStr">
-        <is>
-          <t>Domino Park</t>
-        </is>
-      </c>
-      <c r="G154" s="40" t="inlineStr"/>
+      <c r="E154" s="39" t="inlineStr">
+        <is>
+          <t>Paseo por Williamsburg: Bedford Ave, disquerías y vintage. ★ ACÁ ENTRA HEATONIST (121 Wythe Ave, a una cuadra de Bedford): la tienda insignia de salsas picantes, con más de 100 para probar en el local y el lineup completo de Hot Ones. Abre 12-19 todos los días, así que a esta hora está abierta y les queda de camino al Williamsburg Bridge. OPCIONAL si quieren la panorámica: Westlight (piso 22, sin cover, un trago) — lo bajaron a 'quizás'. NO comer nada: lo que viene lo merece.</t>
+        </is>
+      </c>
+      <c r="F154" s="37" t="inlineStr">
+        <is>
+          <t>HEATONIST Williamsburg</t>
+        </is>
+      </c>
+      <c r="G154" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~20 min a pie (1.2 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H154" s="41" t="inlineStr"/>
       <c r="I154" s="41" t="inlineStr"/>
     </row>
-    <row r="155" ht="30" customHeight="1">
+    <row r="155" ht="16" customHeight="1">
       <c r="A155" s="35" t="n"/>
       <c r="B155" s="36" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C155" s="37" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D155" s="38" t="inlineStr">
@@ -36502,148 +36494,140 @@
       </c>
       <c r="E155" s="39" t="inlineStr">
         <is>
-          <t>Paseo por Williamsburg: Bedford Ave, disquerías y vintage. ★ ACÁ ENTRA HEATONIST (121 Wythe Ave, a una cuadra de Bedford): la tienda insignia de salsas picantes, con más de 100 para probar en el local y el lineup completo de Hot Ones. Abre 12-19 todos los días, así que a esta hora está abierta y les queda de camino al Williamsburg Bridge. OPCIONAL si quieren la panorámica: Westlight (piso 22, sin cover, un trago) — lo bajaron a 'quizás'. NO comer nada: lo que viene lo merece.</t>
-        </is>
-      </c>
-      <c r="F155" s="37" t="inlineStr">
-        <is>
-          <t>HEATONIST Williamsburg</t>
-        </is>
-      </c>
-      <c r="G155" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~20 min a pie (1.2 km) o 🚇 ~15 min · estimado</t>
-        </is>
-      </c>
+          <t>Caminar por Bedford/Driggs hasta el pie del Williamsburg Bridge (~15 min).</t>
+        </is>
+      </c>
+      <c r="F155" s="37" t="inlineStr"/>
+      <c r="G155" s="40" t="inlineStr"/>
       <c r="H155" s="41" t="inlineStr"/>
       <c r="I155" s="41" t="inlineStr"/>
     </row>
-    <row r="156" ht="16" customHeight="1">
+    <row r="156" ht="30" customHeight="1">
       <c r="A156" s="35" t="n"/>
-      <c r="B156" s="36" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="C156" s="37" t="inlineStr">
+      <c r="B156" s="42" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D156" s="38" t="inlineStr">
+      <c r="C156" s="43" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="D156" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E156" s="39" t="inlineStr">
-        <is>
-          <t>Caminar por Bedford/Driggs hasta el pie del Williamsburg Bridge (~15 min).</t>
-        </is>
-      </c>
-      <c r="F156" s="37" t="inlineStr"/>
+      <c r="E156" s="45" t="inlineStr">
+        <is>
+          <t>★★ PETER LUGER (178 Broadway) — el porterhouse for two de 1887, dry-aged en el sótano, con la tocineta gruesa de entrada. ~$160-200 los dos con sides y propina. ⚠️ SIN TARJETAS DE CRÉDITO: efectivo, débito US o cheque — llevar cash. Cena temprana a propósito: el teatro espera. RESERVA EN RESY YA.</t>
+        </is>
+      </c>
+      <c r="F156" s="43" t="inlineStr">
+        <is>
+          <t>Peter Luger Steak House</t>
+        </is>
+      </c>
       <c r="G156" s="40" t="inlineStr"/>
       <c r="H156" s="41" t="inlineStr"/>
       <c r="I156" s="41" t="inlineStr"/>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="35" t="n"/>
-      <c r="B157" s="42" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C157" s="43" t="inlineStr">
+      <c r="B157" s="36" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="D157" s="44" t="inlineStr">
+      <c r="C157" s="37" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="D157" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E157" s="45" t="inlineStr">
-        <is>
-          <t>★★ PETER LUGER (178 Broadway) — el porterhouse for two de 1887, dry-aged en el sótano, con la tocineta gruesa de entrada. ~$160-200 los dos con sides y propina. ⚠️ SIN TARJETAS DE CRÉDITO: efectivo, débito US o cheque — llevar cash. Cena temprana a propósito: el teatro espera. RESERVA EN RESY YA.</t>
-        </is>
-      </c>
-      <c r="F157" s="43" t="inlineStr">
-        <is>
-          <t>Peter Luger Steak House</t>
-        </is>
-      </c>
+      <c r="E157" s="39" t="inlineStr">
+        <is>
+          <t>A la zona de teatros: subte J desde Marcy Av hasta Essex St y F hasta 42 St-Bryant Park (~35 min con transbordo), o directamente Uber al teatro (~20-25 min, $25-35 — un sábado a la noche el puente puede estar cargado).</t>
+        </is>
+      </c>
+      <c r="F157" s="37" t="inlineStr"/>
       <c r="G157" s="40" t="inlineStr"/>
       <c r="H157" s="41" t="inlineStr"/>
       <c r="I157" s="41" t="inlineStr"/>
     </row>
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="35" t="n"/>
-      <c r="B158" s="36" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="C158" s="37" t="inlineStr">
+      <c r="B158" s="42" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D158" s="38" t="inlineStr">
+      <c r="C158" s="43" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="D158" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E158" s="39" t="inlineStr">
-        <is>
-          <t>A la zona de teatros: subte J desde Marcy Av hasta Essex St y F hasta 42 St-Bryant Park (~35 min con transbordo), o directamente Uber al teatro (~20-25 min, $25-35 — un sábado a la noche el puente puede estar cargado).</t>
-        </is>
-      </c>
-      <c r="F158" s="37" t="inlineStr"/>
+      <c r="E158" s="45" t="inlineStr">
+        <is>
+          <t>★★ PLAY DE BROADWAY — mi recomendación: STRANGER THINGS: THE FIRST SHADOW (Marquis, desde ~$76): la maquinaria escénica que ganó el Tony — para quien viene de Mercer Labs, el mismo músculo llevado al teatro. Alternativas esa semana: Harry Potter and the Cursed Child, Paranormal Activity, The Imaginary Invalid. COMPRA FIRME esta semana y verificar el horario real de la función (19:00/19:30/20:00): tiene que terminar ~22:00 para lo que sigue.</t>
+        </is>
+      </c>
+      <c r="F158" s="43" t="inlineStr">
+        <is>
+          <t>Stranger Things: The First Shadow (play)</t>
+        </is>
+      </c>
       <c r="G158" s="40" t="inlineStr"/>
       <c r="H158" s="41" t="inlineStr"/>
       <c r="I158" s="41" t="inlineStr"/>
     </row>
-    <row r="159" ht="30" customHeight="1">
+    <row r="159" ht="16" customHeight="1">
       <c r="A159" s="35" t="n"/>
-      <c r="B159" s="42" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C159" s="43" t="inlineStr">
+      <c r="B159" s="36" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="D159" s="44" t="inlineStr">
+      <c r="C159" s="37" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="D159" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E159" s="45" t="inlineStr">
-        <is>
-          <t>★★ PLAY DE BROADWAY — mi recomendación: STRANGER THINGS: THE FIRST SHADOW (Marquis, desde ~$76): la maquinaria escénica que ganó el Tony — para quien viene de Mercer Labs, el mismo músculo llevado al teatro. Alternativas esa semana: Harry Potter and the Cursed Child, Paranormal Activity, The Imaginary Invalid. COMPRA FIRME esta semana y verificar el horario real de la función (19:00/19:30/20:00): tiene que terminar ~22:00 para lo que sigue.</t>
-        </is>
-      </c>
-      <c r="F159" s="43" t="inlineStr">
-        <is>
-          <t>Stranger Things: The First Shadow (play)</t>
-        </is>
-      </c>
+      <c r="E159" s="39" t="inlineStr">
+        <is>
+          <t>Subte 1 desde Times Sq hasta Christopher St (~15 min) y caminar al corazón del Village.</t>
+        </is>
+      </c>
+      <c r="F159" s="37" t="inlineStr"/>
       <c r="G159" s="40" t="inlineStr"/>
       <c r="H159" s="41" t="inlineStr"/>
       <c r="I159" s="41" t="inlineStr"/>
     </row>
-    <row r="160" ht="16" customHeight="1">
+    <row r="160" ht="30" customHeight="1">
       <c r="A160" s="35" t="n"/>
       <c r="B160" s="36" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C160" s="37" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D160" s="38" t="inlineStr">
@@ -36653,7 +36637,7 @@
       </c>
       <c r="E160" s="39" t="inlineStr">
         <is>
-          <t>Subte 1 desde Times Sq hasta Christopher St (~15 min) y caminar al corazón del Village.</t>
+          <t>Paseo sin apuro por Bleecker y MacDougal — la esquina folk de los 60s de noche, un café o un trago corto. El único objetivo real: estar en la puerta del Wha a las 23:10.</t>
         </is>
       </c>
       <c r="F160" s="37" t="inlineStr"/>
@@ -36663,102 +36647,106 @@
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="35" t="n"/>
-      <c r="B161" s="36" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C161" s="37" t="inlineStr">
+      <c r="B161" s="42" t="inlineStr">
         <is>
           <t>23:15</t>
         </is>
       </c>
-      <c r="D161" s="38" t="inlineStr">
+      <c r="C161" s="43" t="inlineStr"/>
+      <c r="D161" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E161" s="39" t="inlineStr">
-        <is>
-          <t>Paseo sin apuro por Bleecker y MacDougal — la esquina folk de los 60s de noche, un café o un trago corto. El único objetivo real: estar en la puerta del Wha a las 23:10.</t>
-        </is>
-      </c>
-      <c r="F161" s="37" t="inlineStr"/>
+      <c r="E161" s="45" t="inlineStr">
+        <is>
+          <t>★★ CAFÉ WHA — LLEGAR 23:10-23:15: la reserva de Eventbrite NO garantiza admisión y a las 23:30 EN PUNTO liberan los asientos vacíos al standby. TODOS los de la reserva presentes. Set 2 de la house band 23:45-~1:15: soul y funk a máquina en el sótano donde debutaron Dylan, Hendrix y Springsteen. $20 por cabeza van a la cuenta + consumo. Vuelta: subte 1 Christopher St → 72 St (~25 min) o taxi.</t>
+        </is>
+      </c>
+      <c r="F161" s="43" t="inlineStr">
+        <is>
+          <t>Cafe Wha?</t>
+        </is>
+      </c>
       <c r="G161" s="40" t="inlineStr"/>
       <c r="H161" s="41" t="inlineStr"/>
       <c r="I161" s="41" t="inlineStr"/>
     </row>
-    <row r="162" ht="30" customHeight="1">
-      <c r="A162" s="35" t="n"/>
-      <c r="B162" s="42" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C162" s="43" t="inlineStr"/>
-      <c r="D162" s="44" t="inlineStr">
+    <row r="162" ht="32" customHeight="1">
+      <c r="A162" s="46" t="inlineStr">
+        <is>
+          <t>ALTERNATIVA / OJO:  SOBRE PETER LUGER: la mesa de las 17:00 es la realista — y ahora es la única que funciona: el play manda. PLAN B si no hay mesa: correr Peter Luger al ALMUERZO del mismo día (12:45). // SI EL CANSANCIO GANA A LAS 22:00: el Café Wha es la pieza sacrificable — la reserva es gratis y no penaliza no ir; el play, pagado, no. // Sigue afuera: Bar LunÀtico y Barbès (Bed-Stuy/Park Slope), sin noche posible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="22" customHeight="1">
+      <c r="A164" s="33" t="inlineStr">
+        <is>
+          <t>DÍA 9 · Domingo 06/09 · Checkout, Central Park, Roosevelt Island, MoMA PS1 y vuelo  —  base: The Beacon (checkout) → EWR  ·  Ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="32" customHeight="1">
+      <c r="A165" s="34" t="inlineStr">
+        <is>
+          <t>El día arranca con el CHECKOUT de The Beacon: hacerlo temprano y dejar las valijas en el bell desk libera el día entero. El vuelo sale 23:40, así que hay margen — pero es el domingo del fin de semana largo de Labor Day, la noche de mayor tráfico del año, y EWR va a estar cargado. Por eso todo queda cerca y se sale con 2h45 de anticipación. EL CAMBIO DEL ÚLTIMO DÍA: entra MOMA PS1 y sale el Guggenheim. Se verificó el 27/8 que la rotonda del Guggenheim está cerrada hasta el 17/9 —no se camina la rampa, que es la razón para ir— y PS1 resultó ser gratis, abierto hasta las 18 los domingos, a 1,2 km de Roosevelt Island y con «Greater New York 2026» en pie hasta el 7/9. Era el último imprescindible que quedaba afuera del viaje. El Guggenheim queda escrito como alternativa por si cambian de idea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="30" customHeight="1">
+      <c r="A166" s="35" t="n"/>
+      <c r="B166" s="36" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C166" s="37" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="D166" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E162" s="45" t="inlineStr">
-        <is>
-          <t>★★ CAFÉ WHA — LLEGAR 23:10-23:15: la reserva de Eventbrite NO garantiza admisión y a las 23:30 EN PUNTO liberan los asientos vacíos al standby. TODOS los de la reserva presentes. Set 2 de la house band 23:45-~1:15: soul y funk a máquina en el sótano donde debutaron Dylan, Hendrix y Springsteen. $20 por cabeza van a la cuenta + consumo. Vuelta: subte 1 Christopher St → 72 St (~25 min) o taxi.</t>
-        </is>
-      </c>
-      <c r="F162" s="43" t="inlineStr">
-        <is>
-          <t>Cafe Wha?</t>
-        </is>
-      </c>
-      <c r="G162" s="40" t="inlineStr"/>
-      <c r="H162" s="41" t="inlineStr"/>
-      <c r="I162" s="41" t="inlineStr"/>
-    </row>
-    <row r="163" ht="32" customHeight="1">
-      <c r="A163" s="46" t="inlineStr">
-        <is>
-          <t>ALTERNATIVA / OJO:  SOBRE PETER LUGER: la mesa de las 17:00 es la realista — y ahora es la única que funciona: el play manda. PLAN B si no hay mesa: correr Peter Luger al ALMUERZO del mismo día (12:45). // SI EL CANSANCIO GANA A LAS 22:00: el Café Wha es la pieza sacrificable — la reserva es gratis y no penaliza no ir; el play, pagado, no. // Sigue afuera: Bar LunÀtico y Barbès (Bed-Stuy/Park Slope), sin noche posible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="22" customHeight="1">
-      <c r="A165" s="33" t="inlineStr">
-        <is>
-          <t>DÍA 9 · Domingo 06/09 · Checkout, Central Park, Roosevelt Island, MoMA PS1 y vuelo  —  base: The Beacon (checkout) → EWR  ·  Ambos</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="32" customHeight="1">
-      <c r="A166" s="34" t="inlineStr">
-        <is>
-          <t>El día arranca con el CHECKOUT de The Beacon: hacerlo temprano y dejar las valijas en el bell desk libera el día entero. El vuelo sale 23:40, así que hay margen — pero es el domingo del fin de semana largo de Labor Day, la noche de mayor tráfico del año, y EWR va a estar cargado. Por eso todo queda cerca y se sale con 2h45 de anticipación. EL CAMBIO DEL ÚLTIMO DÍA: entra MOMA PS1 y sale el Guggenheim. Se verificó el 27/8 que la rotonda del Guggenheim está cerrada hasta el 17/9 —no se camina la rampa, que es la razón para ir— y PS1 resultó ser gratis, abierto hasta las 18 los domingos, a 1,2 km de Roosevelt Island y con «Greater New York 2026» en pie hasta el 7/9. Era el último imprescindible que quedaba afuera del viaje. El Guggenheim queda escrito como alternativa por si cambian de idea.</t>
-        </is>
-      </c>
+      <c r="E166" s="39" t="inlineStr">
+        <is>
+          <t>Desayuno SIN despertador temprano: anoche terminó ~1:30 en el Village y lo único con hora fija hoy es el PS1, que cierra a las 18:00. Dormir un poco más está permitido.</t>
+        </is>
+      </c>
+      <c r="F166" s="37" t="inlineStr"/>
+      <c r="G166" s="40" t="inlineStr"/>
+      <c r="H166" s="41" t="inlineStr"/>
+      <c r="I166" s="41" t="inlineStr"/>
     </row>
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="35" t="n"/>
-      <c r="B167" s="36" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="C167" s="37" t="inlineStr">
+      <c r="B167" s="42" t="inlineStr">
         <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="D167" s="38" t="inlineStr">
+      <c r="C167" s="43" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="D167" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E167" s="39" t="inlineStr">
-        <is>
-          <t>Desayuno SIN despertador temprano: anoche terminó ~1:30 en el Village y lo único con hora fija hoy es el PS1, que cierra a las 18:00. Dormir un poco más está permitido.</t>
-        </is>
-      </c>
-      <c r="F167" s="37" t="inlineStr"/>
+      <c r="E167" s="45" t="inlineStr">
+        <is>
+          <t>★ CHECKOUT de The Beacon y dejar las valijas en el bell desk. El checkout formal suele ser 11:00-12:00, pero hacerlo antes libera el día.</t>
+        </is>
+      </c>
+      <c r="F167" s="43" t="inlineStr">
+        <is>
+          <t>Hotel The Beacon (3-6 sep)</t>
+        </is>
+      </c>
       <c r="G167" s="40" t="inlineStr"/>
       <c r="H167" s="41" t="inlineStr"/>
       <c r="I167" s="41" t="inlineStr"/>
@@ -36767,12 +36755,12 @@
       <c r="A168" s="35" t="n"/>
       <c r="B168" s="42" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C168" s="43" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="D168" s="44" t="inlineStr">
@@ -36782,63 +36770,59 @@
       </c>
       <c r="E168" s="45" t="inlineStr">
         <is>
-          <t>★ CHECKOUT de The Beacon y dejar las valijas en el bell desk. El checkout formal suele ser 11:00-12:00, pero hacerlo antes libera el día.</t>
+          <t>★ CENTRAL PARK cruzando de oeste a este: Bethesda Terrace, el Ramble, Bow Bridge. Se entra por la 72 desde Broadway, a tres cuadras del hotel.</t>
         </is>
       </c>
       <c r="F168" s="43" t="inlineStr">
         <is>
-          <t>Hotel The Beacon (3-6 sep)</t>
-        </is>
-      </c>
-      <c r="G168" s="40" t="inlineStr"/>
+          <t>Central Park</t>
+        </is>
+      </c>
+      <c r="G168" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~20 min a pie (1.5 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H168" s="41" t="inlineStr"/>
       <c r="I168" s="41" t="inlineStr"/>
     </row>
-    <row r="169" ht="30" customHeight="1">
+    <row r="169" ht="16" customHeight="1">
       <c r="A169" s="35" t="n"/>
-      <c r="B169" s="42" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="C169" s="43" t="inlineStr">
+      <c r="B169" s="36" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="D169" s="44" t="inlineStr">
+      <c r="C169" s="37" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="D169" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E169" s="45" t="inlineStr">
-        <is>
-          <t>★ CENTRAL PARK cruzando de oeste a este: Bethesda Terrace, el Ramble, Bow Bridge. Se entra por la 72 desde Broadway, a tres cuadras del hotel.</t>
-        </is>
-      </c>
-      <c r="F169" s="43" t="inlineStr">
-        <is>
-          <t>Central Park</t>
-        </is>
-      </c>
-      <c r="G169" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~20 min a pie (1.5 km) o 🚇 ~15 min · estimado</t>
-        </is>
-      </c>
+      <c r="E169" s="39" t="inlineStr">
+        <is>
+          <t>Almuerzo en el Upper East Side, saliendo del parque por la Quinta.</t>
+        </is>
+      </c>
+      <c r="F169" s="37" t="inlineStr"/>
+      <c r="G169" s="40" t="inlineStr"/>
       <c r="H169" s="41" t="inlineStr"/>
       <c r="I169" s="41" t="inlineStr"/>
     </row>
-    <row r="170" ht="16" customHeight="1">
+    <row r="170" ht="30" customHeight="1">
       <c r="A170" s="35" t="n"/>
       <c r="B170" s="36" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C170" s="37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="D170" s="38" t="inlineStr">
@@ -36848,7 +36832,7 @@
       </c>
       <c r="E170" s="39" t="inlineStr">
         <is>
-          <t>Almuerzo en el Upper East Side, saliendo del parque por la Quinta.</t>
+          <t>Bajar a 59 St y 2ª Av: subte 6 desde 68 St-Hunter College (el 4/5 exprés NO para ahí), o caminando por la Quinta si el día está lindo.</t>
         </is>
       </c>
       <c r="F170" s="37" t="inlineStr"/>
@@ -36858,56 +36842,60 @@
     </row>
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="35" t="n"/>
-      <c r="B171" s="36" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C171" s="37" t="inlineStr">
+      <c r="B171" s="42" t="inlineStr">
         <is>
           <t>13:50</t>
         </is>
       </c>
-      <c r="D171" s="38" t="inlineStr">
+      <c r="C171" s="43" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="D171" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E171" s="39" t="inlineStr">
-        <is>
-          <t>Bajar a 59 St y 2ª Av: subte 6 desde 68 St-Hunter College (el 4/5 exprés NO para ahí), o caminando por la Quinta si el día está lindo.</t>
-        </is>
-      </c>
-      <c r="F171" s="37" t="inlineStr"/>
+      <c r="E171" s="45" t="inlineStr">
+        <is>
+          <t>★ ROOSEVELT ISLAND TRAMWAY ($3, OMNY) — cruza el East River a 76 metros de altura con el Queensboro Bridge al lado. Es la vista de $50 por el precio de un viaje de subte.</t>
+        </is>
+      </c>
+      <c r="F171" s="43" t="inlineStr">
+        <is>
+          <t>Roosevelt Island Tramway</t>
+        </is>
+      </c>
       <c r="G171" s="40" t="inlineStr"/>
       <c r="H171" s="41" t="inlineStr"/>
       <c r="I171" s="41" t="inlineStr"/>
     </row>
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="35" t="n"/>
-      <c r="B172" s="42" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="C172" s="43" t="inlineStr">
+      <c r="B172" s="36" t="inlineStr">
         <is>
           <t>14:25</t>
         </is>
       </c>
-      <c r="D172" s="44" t="inlineStr">
+      <c r="C172" s="37" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="D172" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E172" s="45" t="inlineStr">
-        <is>
-          <t>★ ROOSEVELT ISLAND TRAMWAY ($3, OMNY) — cruza el East River a 76 metros de altura con el Queensboro Bridge al lado. Es la vista de $50 por el precio de un viaje de subte.</t>
-        </is>
-      </c>
-      <c r="F172" s="43" t="inlineStr">
-        <is>
-          <t>Roosevelt Island Tramway</t>
+      <c r="E172" s="39" t="inlineStr">
+        <is>
+          <t>FDR Four Freedoms Park — del teleférico son ~20 min a pie por el borde del río. La última obra de Louis Kahn: granito, plátanos y una sala abierta al río apuntando a Manhattan. Gratis y vacía. Se pasa por las ruinas del Smallpox Hospital.</t>
+        </is>
+      </c>
+      <c r="F172" s="37" t="inlineStr">
+        <is>
+          <t>FDR Four Freedoms Park</t>
         </is>
       </c>
       <c r="G172" s="40" t="inlineStr"/>
@@ -36918,12 +36906,12 @@
       <c r="A173" s="35" t="n"/>
       <c r="B173" s="36" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="C173" s="37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="D173" s="38" t="inlineStr">
@@ -36933,14 +36921,10 @@
       </c>
       <c r="E173" s="39" t="inlineStr">
         <is>
-          <t>FDR Four Freedoms Park — del teleférico son ~20 min a pie por el borde del río. La última obra de Louis Kahn: granito, plátanos y una sala abierta al río apuntando a Manhattan. Gratis y vacía. Se pasa por las ruinas del Smallpox Hospital.</t>
-        </is>
-      </c>
-      <c r="F173" s="37" t="inlineStr">
-        <is>
-          <t>FDR Four Freedoms Park</t>
-        </is>
-      </c>
+          <t>SALIR 15:05 de Four Freedoms Park y caminar 15 min al norte por el borde del río hasta la ESTACIÓN DEL F, que está en el medio de la isla (Main St y Roosevelt Island Bridge). Hoy NO se vuelve en teleférico: se cruza a Queens por abajo.</t>
+        </is>
+      </c>
+      <c r="F173" s="37" t="inlineStr"/>
       <c r="G173" s="40" t="inlineStr"/>
       <c r="H173" s="41" t="inlineStr"/>
       <c r="I173" s="41" t="inlineStr"/>
@@ -36949,12 +36933,12 @@
       <c r="A174" s="35" t="n"/>
       <c r="B174" s="36" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C174" s="37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="D174" s="38" t="inlineStr">
@@ -36964,7 +36948,7 @@
       </c>
       <c r="E174" s="39" t="inlineStr">
         <is>
-          <t>SALIR 15:05 de Four Freedoms Park y caminar 15 min al norte por el borde del río hasta la ESTACIÓN DEL F, que está en el medio de la isla (Main St y Roosevelt Island Bridge). Hoy NO se vuelve en teleférico: se cruza a Queens por abajo.</t>
+          <t>Subte F, UNA parada: Roosevelt Island → 21 St-Queensbridge (~4 min). Salir y caminar 12-15 min al sur por 21st St / Jackson Ave.</t>
         </is>
       </c>
       <c r="F174" s="37" t="inlineStr"/>
@@ -36974,58 +36958,58 @@
     </row>
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="35" t="n"/>
-      <c r="B175" s="36" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="C175" s="37" t="inlineStr">
+      <c r="B175" s="42" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="D175" s="38" t="inlineStr">
+      <c r="C175" s="43" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="D175" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E175" s="39" t="inlineStr">
-        <is>
-          <t>Subte F, UNA parada: Roosevelt Island → 21 St-Queensbridge (~4 min). Salir y caminar 12-15 min al sur por 21st St / Jackson Ave.</t>
-        </is>
-      </c>
-      <c r="F175" s="37" t="inlineStr"/>
+      <c r="E175" s="45" t="inlineStr">
+        <is>
+          <t>★★ MOMA PS1 — el último imprescindible del viaje, y entra gratis. Escuela pública de 1892 reconvertida en el laboratorio del MoMA: lo que no se anima a mostrar en la Quinta Avenida. VERIFICADO el 27/8: ENTRADA GRATUITA para todos, abre domingos 12:00-18:00, y «Greater New York 2026» —la encuesta insignia de la casa, que se hace cada cinco años— sigue en pie hasta el 7 de septiembre, o sea que la agarran por un día. Más el Courtyard Commission de Precious Okoyomon al aire libre. Dos horas holgadas hasta las 17:45.</t>
+        </is>
+      </c>
+      <c r="F175" s="43" t="inlineStr">
+        <is>
+          <t>MoMA PS1</t>
+        </is>
+      </c>
       <c r="G175" s="40" t="inlineStr"/>
       <c r="H175" s="41" t="inlineStr"/>
       <c r="I175" s="41" t="inlineStr"/>
     </row>
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="35" t="n"/>
-      <c r="B176" s="42" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="C176" s="43" t="inlineStr">
+      <c r="B176" s="36" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="D176" s="44" t="inlineStr">
+      <c r="C176" s="37" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="D176" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E176" s="45" t="inlineStr">
-        <is>
-          <t>★★ MOMA PS1 — el último imprescindible del viaje, y entra gratis. Escuela pública de 1892 reconvertida en el laboratorio del MoMA: lo que no se anima a mostrar en la Quinta Avenida. VERIFICADO el 27/8: ENTRADA GRATUITA para todos, abre domingos 12:00-18:00, y «Greater New York 2026» —la encuesta insignia de la casa, que se hace cada cinco años— sigue en pie hasta el 7 de septiembre, o sea que la agarran por un día. Más el Courtyard Commission de Precious Okoyomon al aire libre. Dos horas holgadas hasta las 17:45.</t>
-        </is>
-      </c>
-      <c r="F176" s="43" t="inlineStr">
-        <is>
-          <t>MoMA PS1</t>
-        </is>
-      </c>
+      <c r="E176" s="39" t="inlineStr">
+        <is>
+          <t>Del PS1 al hotel: subte 7 desde Court Sq hasta Times Sq y 1/2/3 hasta 72 St, o E/M hasta 53 St (~45 min). Llegan 18:30, justo para las valijas. El vuelo no se toca.</t>
+        </is>
+      </c>
+      <c r="F176" s="37" t="inlineStr"/>
       <c r="G176" s="40" t="inlineStr"/>
       <c r="H176" s="41" t="inlineStr"/>
       <c r="I176" s="41" t="inlineStr"/>
@@ -37034,12 +37018,12 @@
       <c r="A177" s="35" t="n"/>
       <c r="B177" s="36" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="C177" s="37" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D177" s="38" t="inlineStr">
@@ -37049,7 +37033,7 @@
       </c>
       <c r="E177" s="39" t="inlineStr">
         <is>
-          <t>Del PS1 al hotel: subte 7 desde Court Sq hasta Times Sq y 1/2/3 hasta 72 St, o E/M hasta 53 St (~45 min). Llegan 18:30, justo para las valijas. El vuelo no se toca.</t>
+          <t>◇ SI PREFIEREN EL GUGGENHEIM, sigue estando y este bloque se ignora: pay-what-you-wish domingos 16:00-17:30 (mínimo $1) y entrada rebajada a $16 el resto del horario. ⚠️ PERO la rotonda está CERRADA del 3/8 al 17/9 por el montaje de Taryn Simon: no se camina la rampa —que es la razón para ir— y avisan que puede haber ruido de obra. Quedan las torres 4, 5 y 7 con «Guggenheim Pop» (Lichtenstein, Warhol, Oldenburg, Cattelan) y la colección Thannhauser. Para hacerlo: en vez de cruzar a Queens, teleférico de vuelta y subte 4/5/6 de 59 St a 86 St, y hay que salir del FDR Park 15:05 para entrar 16:00 — la ventana a voluntad va hasta las 17:30 y el museo cierra ahí.</t>
         </is>
       </c>
       <c r="F177" s="37" t="inlineStr"/>
@@ -37057,16 +37041,16 @@
       <c r="H177" s="41" t="inlineStr"/>
       <c r="I177" s="41" t="inlineStr"/>
     </row>
-    <row r="178" ht="30" customHeight="1">
+    <row r="178" ht="16" customHeight="1">
       <c r="A178" s="35" t="n"/>
       <c r="B178" s="36" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C178" s="37" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="D178" s="38" t="inlineStr">
@@ -37076,7 +37060,7 @@
       </c>
       <c r="E178" s="39" t="inlineStr">
         <is>
-          <t>◇ SI PREFIEREN EL GUGGENHEIM, sigue estando y este bloque se ignora: pay-what-you-wish domingos 16:00-17:30 (mínimo $1) y entrada rebajada a $16 el resto del horario. ⚠️ PERO la rotonda está CERRADA del 3/8 al 17/9 por el montaje de Taryn Simon: no se camina la rampa —que es la razón para ir— y avisan que puede haber ruido de obra. Quedan las torres 4, 5 y 7 con «Guggenheim Pop» (Lichtenstein, Warhol, Oldenburg, Cattelan) y la colección Thannhauser. Para hacerlo: en vez de cruzar a Queens, teleférico de vuelta y subte 4/5/6 de 59 St a 86 St, y hay que salir del FDR Park 15:05 para entrar 16:00 — la ventana a voluntad va hasta las 17:30 y el museo cierra ahí.</t>
+          <t>Retirar las valijas del bell desk. Cena tranquila cerca del hotel: es la última.</t>
         </is>
       </c>
       <c r="F178" s="37" t="inlineStr"/>
@@ -37088,12 +37072,12 @@
       <c r="A179" s="35" t="n"/>
       <c r="B179" s="36" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="C179" s="37" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="D179" s="38" t="inlineStr">
@@ -37103,7 +37087,7 @@
       </c>
       <c r="E179" s="39" t="inlineStr">
         <is>
-          <t>Retirar las valijas del bell desk. Cena tranquila cerca del hotel: es la última.</t>
+          <t>Salir de The Beacon. Subte 1/2/3 desde 72 St hasta 34 St-Penn Station: ~10 min, $3.</t>
         </is>
       </c>
       <c r="F179" s="37" t="inlineStr"/>
@@ -37111,16 +37095,16 @@
       <c r="H179" s="41" t="inlineStr"/>
       <c r="I179" s="41" t="inlineStr"/>
     </row>
-    <row r="180" ht="16" customHeight="1">
+    <row r="180" ht="30" customHeight="1">
       <c r="A180" s="35" t="n"/>
       <c r="B180" s="36" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="C180" s="37" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="D180" s="38" t="inlineStr">
@@ -37130,7 +37114,7 @@
       </c>
       <c r="E180" s="39" t="inlineStr">
         <is>
-          <t>Salir de The Beacon. Subte 1/2/3 desde 72 St hasta 34 St-Penn Station: ~10 min, $3.</t>
+          <t>NJ Transit Penn Station → EWR, llega 20:38. $17,25 (incluye el AirTrain). VERIFICAR el horario dominical en njtransit.com unos días antes.</t>
         </is>
       </c>
       <c r="F180" s="37" t="inlineStr"/>
@@ -37138,16 +37122,16 @@
       <c r="H180" s="41" t="inlineStr"/>
       <c r="I180" s="41" t="inlineStr"/>
     </row>
-    <row r="181" ht="30" customHeight="1">
+    <row r="181" ht="16" customHeight="1">
       <c r="A181" s="35" t="n"/>
       <c r="B181" s="36" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="C181" s="37" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="D181" s="38" t="inlineStr">
@@ -37157,7 +37141,7 @@
       </c>
       <c r="E181" s="39" t="inlineStr">
         <is>
-          <t>NJ Transit Penn Station → EWR, llega 20:38. $17,25 (incluye el AirTrain). VERIFICAR el horario dominical en njtransit.com unos días antes.</t>
+          <t>AirTrain hasta la terminal: 10-15 min.</t>
         </is>
       </c>
       <c r="F181" s="37" t="inlineStr"/>
@@ -37165,18 +37149,14 @@
       <c r="H181" s="41" t="inlineStr"/>
       <c r="I181" s="41" t="inlineStr"/>
     </row>
-    <row r="182" ht="16" customHeight="1">
+    <row r="182" ht="30" customHeight="1">
       <c r="A182" s="35" t="n"/>
       <c r="B182" s="36" t="inlineStr">
         <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C182" s="37" t="inlineStr">
-        <is>
           <t>20:55</t>
         </is>
       </c>
+      <c r="C182" s="37" t="inlineStr"/>
       <c r="D182" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -37184,7 +37164,7 @@
       </c>
       <c r="E182" s="39" t="inlineStr">
         <is>
-          <t>AirTrain hasta la terminal: 10-15 min.</t>
+          <t>En terminal. Faltan 2h45 para el vuelo de las 23:40 — correcto para un internacional en el domingo de Labor Day, que es la noche de más tráfico del año en EWR.</t>
         </is>
       </c>
       <c r="F182" s="37" t="inlineStr"/>
@@ -37192,31 +37172,8 @@
       <c r="H182" s="41" t="inlineStr"/>
       <c r="I182" s="41" t="inlineStr"/>
     </row>
-    <row r="183" ht="30" customHeight="1">
-      <c r="A183" s="35" t="n"/>
-      <c r="B183" s="36" t="inlineStr">
-        <is>
-          <t>20:55</t>
-        </is>
-      </c>
-      <c r="C183" s="37" t="inlineStr"/>
-      <c r="D183" s="38" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="E183" s="39" t="inlineStr">
-        <is>
-          <t>En terminal. Faltan 2h45 para el vuelo de las 23:40 — correcto para un internacional en el domingo de Labor Day, que es la noche de más tráfico del año en EWR.</t>
-        </is>
-      </c>
-      <c r="F183" s="37" t="inlineStr"/>
-      <c r="G183" s="40" t="inlineStr"/>
-      <c r="H183" s="41" t="inlineStr"/>
-      <c r="I183" s="41" t="inlineStr"/>
-    </row>
-    <row r="184" ht="32" customHeight="1">
-      <c r="A184" s="46" t="inlineStr">
+    <row r="183" ht="32" customHeight="1">
+      <c r="A183" s="46" t="inlineStr">
         <is>
           <t>ALTERNATIVA / OJO:  COLCHÓN: si algo se atrasa, el tren siguiente sale 20:55 y llega a EWR 21:16, o sea terminal ~21:35 y 2h05 antes del vuelo. Es el último que yo tomaría. // Si prefieren un último día sin moverse, salteen el teleférico y estiren Central Park hasta el Guggenheim: el parque solo da para toda la mañana y la tarde. Lo que NO conviene hoy es meter algo nuevo y grande. // LO QUE SE PIERDEN POR EL VUELO, y duele: esta noche a las 20:00 el Met proyecta gratis en Lincoln Center «El Último Sueño de Frida y Diego» —la misma Frida de la muestra del MoMA del lunes— y ustedes salen del hotel 19:40 hacia Penn Station. Está a diez cuadras del Beacon. No hay forma de que entre sin poner en riesgo el vuelo. // SI QUIEREN VOLVER AL GUGGENHEIM en vez del PS1: está escrito en el bloque de las 18:20, con los tiempos hechos. Cuesta el último imprescindible del viaje y hay que aceptar que la rampa —la razón para ir— no se camina hasta el 17/9. Tercera opción si ninguna convence: el Whitney también abre los domingos.</t>
         </is>
@@ -37224,38 +37181,38 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A128:I128"/>
+    <mergeCell ref="A183:I183"/>
+    <mergeCell ref="A164:I164"/>
     <mergeCell ref="A84:I84"/>
     <mergeCell ref="A66:I66"/>
-    <mergeCell ref="A105:I105"/>
-    <mergeCell ref="A163:I163"/>
+    <mergeCell ref="A145:I145"/>
     <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A101:I101"/>
     <mergeCell ref="A86:I86"/>
     <mergeCell ref="A104:I104"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A144:I144"/>
-    <mergeCell ref="A184:I184"/>
-    <mergeCell ref="A125:I125"/>
-    <mergeCell ref="A147:I147"/>
+    <mergeCell ref="A126:I126"/>
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A165:I165"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A68:I68"/>
     <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A102:I102"/>
     <mergeCell ref="A127:I127"/>
+    <mergeCell ref="A143:I143"/>
     <mergeCell ref="A48:I48"/>
-    <mergeCell ref="A166:I166"/>
+    <mergeCell ref="A103:I103"/>
     <mergeCell ref="A45:I45"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A146:I146"/>
+    <mergeCell ref="A124:I124"/>
     <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A162:I162"/>
     <mergeCell ref="A69:I69"/>
     <mergeCell ref="A87:I87"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H186" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H185" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,Reservado,Confirmado,Descartado"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NYC_2026_Planificador.xlsx
+++ b/NYC_2026_Planificador.xlsx
@@ -7758,9 +7758,9 @@
           <t>36-01 35th Ave, Astoria</t>
         </is>
       </c>
-      <c r="S60" s="17" t="inlineStr">
-        <is>
-          <t>Día 6 · jue 3/9</t>
+      <c r="S60" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="T60" s="18" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="S125" s="17" t="inlineStr">
         <is>
-          <t>Día 7 · vie 4/9</t>
+          <t>Día 6 · jue 3/9, Día 7 · vie 4/9</t>
         </is>
       </c>
       <c r="T125" s="18" t="inlineStr">
@@ -27443,9 +27443,9 @@
           <t>75 9th Ave (dentro del Chelsea Market)</t>
         </is>
       </c>
-      <c r="S259" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S259" s="17" t="inlineStr">
+        <is>
+          <t>Día 6 · jue 3/9</t>
         </is>
       </c>
       <c r="T259" s="18" t="inlineStr">
@@ -32651,7 +32651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I183"/>
+  <dimension ref="A1:I184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -35164,14 +35164,14 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="33" t="inlineStr">
         <is>
-          <t>DÍA 6 · Jueves 03/09 · Traslado + World Trade Center completo + ferry con Thais  —  base: JGStay SoHo → The Beacon  ·  Solo JP</t>
+          <t>DÍA 6 · Jueves 03/09 · World Trade Center completo · encuentro con Thais en Chelsea Market · check-in y noche de jazz  —  base: JGStay SoHo → The Beacon  ·  Solo JP</t>
         </is>
       </c>
     </row>
     <row r="104" ht="32" customHeight="1">
       <c r="A104" s="34" t="inlineStr">
         <is>
-          <t>REARMADO EL 1/9: Juan ya no duerme en New Jersey, así que el día arranca en el JGStay SoHo a las 7:30 con desayuno incluido en vez de a las 6:20 en Branchburg — hora y media más de sueño, un Uber menos y un tren menos. Las maletas van en el subte 1, directo de Canal St a 72 St, y quedan en el bell desk del Beacon antes de las 9. La mañana y la primera tarde son el World Trade Center completo — memorial, museo y One World Observatory en una sola bajada. OJO: One World es EL MIRADOR DE DÍA a propósito — su vista es el puerto y el agua, que de noche es negra; los arcos de atardecer van en Top of the Rock (lunes) y SUMMIT (viernes). THAIS ESTÁ EN NYC CON SU EQUIPO este jueves y SE LIBERA A LAS 16:00: se encuentran por Manhattan y se van juntos al Museum of the Moving Image, que es GRATIS los jueves de 14 a 18 — estaba caído del plan y ustedes lo tienen 2/2: RECUPERADO. El día cierra con check-in, cena y Dizzy's. Siguen afuera MoMA PS1, Astoria y Gantry (no hay hueco), y el Staten Island Ferry pasó a la alternativa nocturna de hoy. ENTRA STONE ST, que era imprescindible y no estaba en ningún día: el almuerzo se corre de Brookfield Place a la calle adoquinada, a 10 minutos del museo y 12 de One World. Se pagan 22 minutos de caminata y quedan 38 para comer — alcanza para un mediodía, aunque su mejor hora sea el after office de 5 a 8 y no la del almuerzo.</t>
+          <t>REARMADO EL 2/9 A LA NOCHE: el encuentro con Thais pasa a las 15:30 EN CHELSEA MARKET, y de ahí van juntos a dejar la valija de ella en The Beacon. Eso reordena toda la tarde. LA MAÑANA NO CAMBIA: Juan sale del JGStay a las 7:30 con desayuno incluido, deja sus maletas en el Beacon antes de las 9 y baja al World Trade Center — memorial, museo y One World Observatory en una sola bajada. OJO: One World es EL MIRADOR DE DÍA a propósito — su vista es el puerto y el agua, que de noche es negra; los arcos de atardecer van en el SUMMIT del viernes. ⚠️ LO QUE SE CAE, Y HAY QUE DECIRLO: el MUSEUM OF THE MOVING IMAGE. Estaba a las 16:30 porque los jueves es gratis de 14 a 18, y era su única ventana del viaje. Desde Chelsea Market son 45 min hasta Astoria y desde el Beacon son 50: con el encuentro a las 15:30 y la valija de por medio, llegarían 25 minutos antes de que cierre. No hay forma de salvarlo sin arrastrar la valija de Thais toda la tarde. Fuera del jueves cuesta $20 por cabeza y no queda otro jueves en el viaje. LO QUE SE GANA: el check-in pasa de las 18:55 a las 16:50, y con eso la tarde deja de ser una carrera. Aparecen tres horas libres en el Upper West Side, que es exactamente donde estaba el cuello de botella: la cena era «rápida y liviana» de 19:15 a 19:55 y ahora es una cena de verdad, con Central Park al atardecer antes. Y EL PENDIENTE DE LAS SALSAS SE RESUELVE SOLO: HEATONIST está DENTRO del Chelsea Market, abierto hasta las 18:45. Se compran en el encuentro, sin desviarse un metro.</t>
         </is>
       </c>
     </row>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="E111" s="39" t="inlineStr">
         <is>
-          <t>★ ALMUERZO EN STONE ST — 10 min a pie desde el museo, hacia el sureste. Calle adoquinada peatonal de 1660, la traza holandesa que sobrevivió al fuego de 1835: mesas afuera, sin autos, entre edificios de piedra. Se come rápido y se sigue: One World es a las 13:45 y son 12 min de vuelta. Plan B si llueve o no hay mesa: Hudson Eats o Le District en Brookfield Place, cruzando West St.</t>
+          <t>★ ALMUERZO EN STONE ST — 10 min a pie desde el museo, hacia el sureste. Calle adoquinada peatonal de 1660, la traza holandesa que sobrevivió al fuego de 1835: mesas afuera, sin autos, entre edificios de piedra. Se come rápido y se sigue. Plan B si llueve o no hay mesa: Hudson Eats o Le District en Brookfield Place, cruzando West St.</t>
         </is>
       </c>
       <c r="F111" s="37" t="inlineStr">
@@ -35393,7 +35393,7 @@
       </c>
       <c r="C112" s="43" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="D112" s="44" t="inlineStr">
@@ -35403,7 +35403,7 @@
       </c>
       <c r="E112" s="45" t="inlineStr">
         <is>
-          <t>★★ ONE WORLD OBSERVATORY — piso 102, el punto más alto del hemisferio occidental, con el puerto y Brooklyn dominando la vista. $44+fee, ventana de entrada de 15 min: sacar el timed ticket online. JP lo subió a 2 en la última pasada.</t>
+          <t>★★ ONE WORLD OBSERVATORY — piso 102, el punto más alto del hemisferio occidental, con el puerto y Brooklyn dominando la vista. $44+fee, ventana de entrada de 15 min: sacar el timed ticket online. HOY SON 65 MINUTOS, no más: a las 14:50 hay que estar bajando, porque el encuentro con Thais es a las 15:30 del otro lado de la ciudad.</t>
         </is>
       </c>
       <c r="F112" s="43" t="inlineStr">
@@ -35423,12 +35423,12 @@
       <c r="A113" s="35" t="n"/>
       <c r="B113" s="36" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="C113" s="37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="D113" s="38" t="inlineStr">
@@ -35438,7 +35438,7 @@
       </c>
       <c r="E113" s="39" t="inlineStr">
         <is>
-          <t>El Oculus en un VISTAZO (5 min — ya estás ahí, y el tiempo no da para más) y R/W desde Cortlandt St hacia el norte.</t>
+          <t>El Oculus en un VISTAZO (5 min) — está de camino al subte, así que no cuesta nada. Después, subte 1 desde WTC Cortlandt hasta 18 St (~12 min) y cuatro cuadras al oeste hasta la Novena.</t>
         </is>
       </c>
       <c r="F113" s="37" t="inlineStr">
@@ -35446,11 +35446,7 @@
           <t>Oculus / WTC Transportation Hub</t>
         </is>
       </c>
-      <c r="G113" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~4 min a pie · 0.3 km · estimado</t>
-        </is>
-      </c>
+      <c r="G113" s="40" t="inlineStr"/>
       <c r="H113" s="41" t="inlineStr"/>
       <c r="I113" s="41" t="inlineStr"/>
     </row>
@@ -35458,12 +35454,12 @@
       <c r="A114" s="35" t="n"/>
       <c r="B114" s="42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C114" s="43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="D114" s="44" t="inlineStr">
@@ -35473,59 +35469,63 @@
       </c>
       <c r="E114" s="45" t="inlineStr">
         <is>
-          <t>★ ENCUENTRO CON THAIS. Lo que MÁS rinde: verse DIRECTO en la puerta del MoMI a las 16:20 (36-01 35 Ave, N/W hasta 36 Av) — cada uno llega por su lado y el museo gana 10-15 min. Si prefieren encontrarse antes en Manhattan: Lexington Av-59 St 16:00 y N/W juntos (JP puede llegar 16:05-16:10 si el WTC se estiró: avisale que es ±10).</t>
-        </is>
-      </c>
-      <c r="F114" s="43" t="inlineStr"/>
-      <c r="G114" s="40" t="inlineStr"/>
+          <t>★★ ENCUENTRO CON THAIS — CHELSEA MARKET (75 Ninth Ave, entre las calles 15 y 16). La antigua fábrica de galletitas Nabisco, donde se inventó el Oreo, convertida en mercado techado de ladrillo. Thais llega con su valija: acá se juntan y de acá se van derecho al hotel. Si ella viene sin almorzar, este es el lugar — hay de todo y se come parado.</t>
+        </is>
+      </c>
+      <c r="F114" s="43" t="inlineStr">
+        <is>
+          <t>Chelsea Market</t>
+        </is>
+      </c>
+      <c r="G114" s="40" t="inlineStr">
+        <is>
+          <t>🚇 ~20 min en subte · 4.5 km (a pie 60 min) · estimado</t>
+        </is>
+      </c>
       <c r="H114" s="41" t="inlineStr"/>
       <c r="I114" s="41" t="inlineStr"/>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="35" t="n"/>
-      <c r="B115" s="42" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C115" s="43" t="inlineStr">
-        <is>
-          <t>18:05</t>
-        </is>
-      </c>
-      <c r="D115" s="44" t="inlineStr">
+      <c r="B115" s="36" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C115" s="37" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="D115" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E115" s="45" t="inlineStr">
-        <is>
-          <t>★★ MUSEUM OF THE MOVING IMAGE — GRATIS los jueves 14-18, sus únicas horas del jueves. RECUPERADO: había quedado afuera del plan y ustedes lo tienen 2/2. Una hora y media alcanza para Behind the Screen y los Muppets originales de Jim Henson. Cierra 18:00 EN PUNTO. (N/W hasta 36 Av + 8 min a pie.)</t>
-        </is>
-      </c>
-      <c r="F115" s="43" t="inlineStr">
-        <is>
-          <t>Museum of the Moving Image</t>
-        </is>
-      </c>
-      <c r="G115" s="40" t="inlineStr">
-        <is>
-          <t>🚇 ~40 min en subte · 11.5 km (a pie 155 min) · estimado</t>
-        </is>
-      </c>
+      <c r="E115" s="39" t="inlineStr">
+        <is>
+          <t>★ HEATONIST — LAS SALSAS PICANTES, y está DENTRO del Chelsea Market: cero desvío. Es la tienda de las salsas de Hot Ones, con barra de degustación para probar antes de comprar. Abierto hasta 18:45. Este era un pendiente de Juan y se resuelve sin mover un dedo del plan.</t>
+        </is>
+      </c>
+      <c r="F115" s="37" t="inlineStr">
+        <is>
+          <t>HEATONIST Chelsea Market</t>
+        </is>
+      </c>
+      <c r="G115" s="40" t="inlineStr"/>
       <c r="H115" s="41" t="inlineStr"/>
       <c r="I115" s="41" t="inlineStr"/>
     </row>
-    <row r="116" ht="16" customHeight="1">
+    <row r="116" ht="30" customHeight="1">
       <c r="A116" s="35" t="n"/>
       <c r="B116" s="36" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C116" s="37" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="D116" s="38" t="inlineStr">
@@ -35535,7 +35535,7 @@
       </c>
       <c r="E116" s="39" t="inlineStr">
         <is>
-          <t>Subte N/W desde 36 Av hasta Times Sq y 1/2/3 hasta 72 St (~45 min).</t>
+          <t>Al hotel con la valija: caminar cuatro cuadras al este hasta 18 St y subte 1 directo hasta 72 St (~20 min). El 1 es el que conviene con equipaje — directo, sin transbordo, y para a tres cuadras del Beacon.</t>
         </is>
       </c>
       <c r="F116" s="37" t="inlineStr"/>
@@ -35543,29 +35543,29 @@
       <c r="H116" s="41" t="inlineStr"/>
       <c r="I116" s="41" t="inlineStr"/>
     </row>
-    <row r="117" ht="16" customHeight="1">
+    <row r="117" ht="30" customHeight="1">
       <c r="A117" s="35" t="n"/>
-      <c r="B117" s="36" t="inlineStr">
-        <is>
-          <t>18:55</t>
-        </is>
-      </c>
-      <c r="C117" s="37" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="D117" s="38" t="inlineStr">
+      <c r="B117" s="42" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="C117" s="43" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="D117" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E117" s="39" t="inlineStr">
-        <is>
-          <t>The Beacon: check-in formal y subir las maletas.</t>
-        </is>
-      </c>
-      <c r="F117" s="37" t="inlineStr">
+      <c r="E117" s="45" t="inlineStr">
+        <is>
+          <t>★ THE BEACON — CHECK-IN FORMAL con Thais, la valija de ella y las maletas de Juan que quedaron a la mañana. Dos horas antes que en el plan viejo: de acá en adelante el día deja de ser una carrera.</t>
+        </is>
+      </c>
+      <c r="F117" s="43" t="inlineStr">
         <is>
           <t>Hotel The Beacon (3-6 sep)</t>
         </is>
@@ -35576,147 +35576,147 @@
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="35" t="n"/>
-      <c r="B118" s="36" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="C118" s="37" t="inlineStr">
-        <is>
-          <t>19:55</t>
-        </is>
-      </c>
-      <c r="D118" s="38" t="inlineStr">
+      <c r="B118" s="42" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="C118" s="43" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="D118" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E118" s="39" t="inlineStr">
-        <is>
-          <t>Cena RÁPIDA en el Upper West Side, bajando por Broadway o Columbus. Hoy se come temprano y liviano: la noche tiene tres paradas y todas valen.</t>
-        </is>
-      </c>
-      <c r="F118" s="37" t="inlineStr"/>
+      <c r="E118" s="45" t="inlineStr">
+        <is>
+          <t>★ CENTRAL PARK AL ATARDECER — cuatro cuadras al este y ya estás adentro. Entrar por la 72 y Central Park West: Strawberry Fields (el mosaico IMAGINE, a metros del Dakota donde vivía Lennon), bajar a Bethesda Terrace y el lago con los botes. El sol se pone ~19:24, así que esta es la hora buena. Gratis. SI THAIS LLEGA CANSADA de trabajar todo el día, el hotel está a cuatro cuadras: se corta cuando quieran y se pasa derecho a la cena.</t>
+        </is>
+      </c>
+      <c r="F118" s="43" t="inlineStr"/>
       <c r="G118" s="40" t="inlineStr"/>
       <c r="H118" s="41" t="inlineStr"/>
       <c r="I118" s="41" t="inlineStr"/>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="35" t="n"/>
-      <c r="B119" s="42" t="inlineStr">
+      <c r="B119" s="36" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C119" s="37" t="inlineStr">
         <is>
           <t>19:55</t>
         </is>
       </c>
-      <c r="C119" s="43" t="inlineStr">
-        <is>
-          <t>20:20</t>
-        </is>
-      </c>
-      <c r="D119" s="44" t="inlineStr">
+      <c r="D119" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E119" s="45" t="inlineStr">
-        <is>
-          <t>★ LINCOLN CENTER DE NOCHE (gratis, 20 min) — OJO, VERIFICADO el 27/8 y cambia lo que van a encontrar: esta noche la Josie Robertson Plaza NO está tranquila. El Met proyecta Tristan und Isolde (actos II y III) a las 20:00 en pantalla gigante, gratis y sin reserva, y despejan la plaza desde las 18:00 para armar 2.500 sillas. O sea: llegan justo cuando se está llenando. La fuente y los chandeliers siguen ahí, pero con multitud y pantalla. Puede ser mejor que el plan original —hay ambiente de estreno— o puede ser un quilombo: decidan en el momento. Si prefieren el Lincoln Center vacío, el espejo de agua con el Henry Moore está del lado norte, detrás del Vivian Beaumont, y ahí no hay nadie.</t>
-        </is>
-      </c>
-      <c r="F119" s="43" t="inlineStr">
-        <is>
-          <t>Lincoln Center (campus y plaza)</t>
-        </is>
-      </c>
-      <c r="G119" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~20 min a pie (1.3 km) o 🚇 ~15 min · estimado</t>
-        </is>
-      </c>
+      <c r="E119" s="39" t="inlineStr">
+        <is>
+          <t>CENA SIN APURO en el Upper West Side, sobre Broadway, Columbus o Amsterdam. HOY SE PUEDE COMER TRANQUILO: en el plan viejo esto eran 40 minutos de trámite antes de salir corriendo. Ahora hay una hora larga y el Lincoln Center está a diez cuadras caminando.</t>
+        </is>
+      </c>
+      <c r="F119" s="37" t="inlineStr"/>
+      <c r="G119" s="40" t="inlineStr"/>
       <c r="H119" s="41" t="inlineStr"/>
       <c r="I119" s="41" t="inlineStr"/>
     </row>
-    <row r="120" ht="16" customHeight="1">
+    <row r="120" ht="30" customHeight="1">
       <c r="A120" s="35" t="n"/>
-      <c r="B120" s="36" t="inlineStr">
+      <c r="B120" s="42" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="C120" s="43" t="inlineStr">
         <is>
           <t>20:20</t>
         </is>
       </c>
-      <c r="C120" s="37" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="D120" s="38" t="inlineStr">
+      <c r="D120" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E120" s="39" t="inlineStr">
-        <is>
-          <t>Caminar seis cuadras por Broadway hasta Columbus Circle (~8 min).</t>
-        </is>
-      </c>
-      <c r="F120" s="37" t="inlineStr"/>
-      <c r="G120" s="40" t="inlineStr"/>
+      <c r="E120" s="45" t="inlineStr">
+        <is>
+          <t>★ LINCOLN CENTER DE NOCHE (gratis, 20 min) — OJO, VERIFICADO el 27/8 y cambia lo que van a encontrar: esta noche la Josie Robertson Plaza NO está tranquila. El Met proyecta Tristan und Isolde (actos II y III) a las 20:00 en pantalla gigante, gratis y sin reserva, y despejan la plaza desde las 18:00 para armar 2.500 sillas. Llegan justo cuando arranca. La fuente y los chandeliers siguen ahí, pero con multitud y pantalla. Si prefieren el Lincoln Center vacío, el espejo de agua con el Henry Moore está del lado norte, detrás del Vivian Beaumont, y ahí no hay nadie.</t>
+        </is>
+      </c>
+      <c r="F120" s="43" t="inlineStr">
+        <is>
+          <t>Lincoln Center (campus y plaza)</t>
+        </is>
+      </c>
+      <c r="G120" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~20 min a pie (1.3 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H120" s="41" t="inlineStr"/>
       <c r="I120" s="41" t="inlineStr"/>
     </row>
-    <row r="121" ht="30" customHeight="1">
+    <row r="121" ht="16" customHeight="1">
       <c r="A121" s="35" t="n"/>
-      <c r="B121" s="42" t="inlineStr">
+      <c r="B121" s="36" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="C121" s="37" t="inlineStr">
         <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="C121" s="43" t="inlineStr">
-        <is>
-          <t>20:55</t>
-        </is>
-      </c>
-      <c r="D121" s="44" t="inlineStr">
+      <c r="D121" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E121" s="45" t="inlineStr">
-        <is>
-          <t>★★ MO LOUNGE, PISO 35 DEL MANDARIN ORIENTAL (80 Columbus Circle) — el dato del amigo de Juan, con una corrección: es el piso 35, no el 60 (el hotel ocupa del 35 al 54). Ventanales de piso a techo sobre Central Park con la ciudad encendida abajo. Coctel ~$26-32, sin cover. RESERVAR por SevenRooms desde su web. Si prefieren algo más íntimo, en ese MISMO piso está The Bar (ex speakeasy The Office, 45 asientos, mar-sáb 17-1h).</t>
-        </is>
-      </c>
-      <c r="F121" s="43" t="inlineStr">
-        <is>
-          <t>MO Lounge — Mandarin Oriental (piso 35)</t>
-        </is>
-      </c>
+      <c r="E121" s="39" t="inlineStr">
+        <is>
+          <t>Caminar seis cuadras por Broadway hasta Columbus Circle (~8 min).</t>
+        </is>
+      </c>
+      <c r="F121" s="37" t="inlineStr"/>
       <c r="G121" s="40" t="inlineStr"/>
       <c r="H121" s="41" t="inlineStr"/>
       <c r="I121" s="41" t="inlineStr"/>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="35" t="n"/>
-      <c r="B122" s="36" t="inlineStr">
+      <c r="B122" s="42" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C122" s="43" t="inlineStr">
         <is>
           <t>20:55</t>
         </is>
       </c>
-      <c r="C122" s="37" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="D122" s="38" t="inlineStr">
+      <c r="D122" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E122" s="39" t="inlineStr">
-        <is>
-          <t>Bajar en ascensor: Dizzy's está EN EL MISMO EDIFICIO (10 Columbus Circle, piso 5). Cero calle, cero frío.</t>
-        </is>
-      </c>
-      <c r="F122" s="37" t="inlineStr"/>
+      <c r="E122" s="45" t="inlineStr">
+        <is>
+          <t>★★ MO LOUNGE, PISO 35 DEL MANDARIN ORIENTAL (80 Columbus Circle) — el dato del amigo de Juan, con la vista de Central Park entero desde arriba y los cócteles caros que la pagan. Sin reserva se entra, pero temprano es más fácil.</t>
+        </is>
+      </c>
+      <c r="F122" s="43" t="inlineStr">
+        <is>
+          <t>MO Lounge — Mandarin Oriental (piso 35)</t>
+        </is>
+      </c>
       <c r="G122" s="40" t="inlineStr"/>
       <c r="H122" s="41" t="inlineStr"/>
       <c r="I122" s="41" t="inlineStr"/>
@@ -35725,10 +35725,14 @@
       <c r="A123" s="35" t="n"/>
       <c r="B123" s="36" t="inlineStr">
         <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="C123" s="37" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C123" s="37" t="inlineStr"/>
       <c r="D123" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35736,78 +35740,74 @@
       </c>
       <c r="E123" s="39" t="inlineStr">
         <is>
-          <t>★ Dizzy's Club — ventanales sobre Central Park detrás del escenario, un piso abajo del cóctel. SEAMOS HONESTOS: JP lleva ~17 horas en pie con 5 de sueño. Decidan A LAS 20:00, arriba en el Mandarin: si están enteros, bajan; si no, se quedan con la vista y el trago, que ya es un cierre precioso. El set Late Night (~22:45) cuesta una fracción — variante para valientes.</t>
-        </is>
-      </c>
-      <c r="F123" s="37" t="inlineStr">
-        <is>
-          <t>Dizzy's Club (Jazz at Lincoln Center)</t>
-        </is>
-      </c>
+          <t>Bajar en ascensor: Dizzy's está EN EL MISMO EDIFICIO (10 Columbus Circle, piso 5). Cero calle, cero subte.</t>
+        </is>
+      </c>
+      <c r="F123" s="37" t="inlineStr"/>
       <c r="G123" s="40" t="inlineStr"/>
       <c r="H123" s="41" t="inlineStr"/>
       <c r="I123" s="41" t="inlineStr"/>
     </row>
-    <row r="124" ht="32" customHeight="1">
-      <c r="A124" s="46" t="inlineStr">
-        <is>
-          <t>ALTERNATIVA / OJO:  ⚠️ EL PROBLEMA DE LA NOCHE ANTERIOR: si JP viaja desde New Jersey el jueves, significa que durmió allá el miércoles — y el miércoles el SummerStage termina a las 22:00 en Central Park. Llegando a Penn ~22:25 se toma el directo de las 22:48, que deja en Raritan ~0:04, más Uber: llegada al hotel ~0:25 y despertador a las 5:45. Son cinco horas de sueño antes de un día completo. Tres salidas: (a) salir del SummerStage a las 21:15, después del set principal; (b) quedarse una noche más en el JGStay y que Thais lleve las maletas el jueves (implica tocar la reserva); (c) tomar el tren de las 7:13 en vez del de 6:55 y arrancar 20 minutos más tarde. Verificá los horarios exactos de la tarde-noche en njtransit.com: solo tengo confirmado el directo de las 22:48. // EL FERRY, SI LES DUELE (lo tienen 2/2): al salir del MoMI, W directo hasta Whitehall (~50 min), ferry ~19:15 — el atardecer (~19:22) de ida y la Estatua y el skyline ILUMINADOS de vuelta; check-in ~21:15, cena tarde cerca del hotel, y Dizzy's tiene set Late Night los jueves ~22:45 como consuelo. Es MÁS día: elíjanlo solo si llegan enteros. // Siguen afuera: MoMA PS1, Astoria y Gantry (sin hueco); ya habían salido Noguchi, Astoria Park y Socrates por interés bajo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="22" customHeight="1">
-      <c r="A126" s="33" t="inlineStr">
+    <row r="124" ht="30" customHeight="1">
+      <c r="A124" s="35" t="n"/>
+      <c r="B124" s="36" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C124" s="37" t="inlineStr"/>
+      <c r="D124" s="38" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E124" s="39" t="inlineStr">
+        <is>
+          <t>★ Dizzy's Club — ventanales sobre Central Park detrás del escenario, un piso abajo del cóctel. Set de las 21:00, ~$45. Es el cierre perfecto del primer día de Thais en la ciudad.</t>
+        </is>
+      </c>
+      <c r="F124" s="37" t="inlineStr">
+        <is>
+          <t>Dizzy's Club (Jazz at Lincoln Center)</t>
+        </is>
+      </c>
+      <c r="G124" s="40" t="inlineStr"/>
+      <c r="H124" s="41" t="inlineStr"/>
+      <c r="I124" s="41" t="inlineStr"/>
+    </row>
+    <row r="125" ht="32" customHeight="1">
+      <c r="A125" s="46" t="inlineStr">
+        <is>
+          <t>ALTERNATIVA / OJO:  EL MoMI SE PIERDE DEL VIAJE, y conviene tenerlo claro en vez de descubrirlo el sábado. Los jueves es gratis de 14 a 18 y hoy era el único jueves; fuera de eso son $20 por cabeza y no hay hueco en viernes, sábado ni domingo (el domingo es checkout y vuelo). LA ÚNICA FORMA DE SALVARLO sería ir de Chelsea Market derecho a Astoria con la valija de Thais a cuestas: salen 16:15, llegan ~17:00, tienen una hora justa, y después son 50 minutos más hasta el Beacon para llegar 18:50 sin tiempo de nada antes del MO Lounge. Es posible y es feo: cuatro horas de subte con equipaje el primer día de ella. Por eso el plan no lo hace. // SI EL WTC SE ESTIRA: lo primero que se recorta es el One World, que hoy tiene 65 minutos en vez de 85. Llegar tarde al Chelsea Market es lo único que no se puede hacer. // SI PREFIEREN QUEDARSE A LA ÓPERA: el Met proyecta Tristan und Isolde gratis a las 20:00 en la plaza del Lincoln Center, con 2.500 sillas. Verla en serio significa soltar el MO Lounge y Dizzy's, que están en el mismo edificio y ya tienen set a las 21:00. El plan elige el jazz; la ópera queda como opción si el día viene cansado y prefieren sentarse. // LAS SALSAS DE HEATONIST YA ESTÁN RESUELTAS acá dentro, así que la sucursal de Williamsburg deja de ser necesaria: si el sábado en Brooklyn no da el tiempo, no se pierde nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="22" customHeight="1">
+      <c r="A127" s="33" t="inlineStr">
         <is>
           <t>DÍA 7 · Viernes 04/09 · Vessel + High Line, SUMMIT al atardecer y el VANGUARD de a dos  —  base: The Beacon  ·  Ambos</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="32" customHeight="1">
-      <c r="A127" s="34" t="inlineStr">
+    <row r="128" ht="32" customHeight="1">
+      <c r="A128" s="34" t="inlineStr">
         <is>
           <t>Salieron el West Village, Washington Square y el Whitney; entraron el High Line, THE VESSEL (al pie del arranque, $10 y 45 min), la Morgan (hoy GRATIS 17-20) y SUMMIT — que se movió AL ATARDECER por el pedido de ustedes: entrada 18:10, luz plena, la puesta ~19:21 multiplicada por los espejos de Kusama (es EL lugar de la ciudad para ese momento) y la noche encendida hasta las 20:15. EL PAGO, dicho honesto: la Morgan se hace en una hora entrando 17:00 en punto, y la cena de hoy es un bocado rápido — por eso el almuerzo en Chelsea Market es EL fuerte del día. SALIÓ GRAND CENTRAL: estaba a las 16:20 con el argumento de que JP ya lo vio el lunes y Thais no — pero ella lo tiene en 0, así que eran 40 minutos para alguien que no lo quiere. Sin esa parada tampoco hace falta cortar Chelsea a las 15:50: se sale 16:25 derecho a la Morgan y la tarde de galerías y almuerzo gana una hora larga.</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="35" t="n"/>
-      <c r="B128" s="36" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="C128" s="37" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="D128" s="38" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="E128" s="39" t="inlineStr">
-        <is>
-          <t>Subte a Hudson Yards.</t>
-        </is>
-      </c>
-      <c r="F128" s="37" t="inlineStr"/>
-      <c r="G128" s="40" t="inlineStr"/>
-      <c r="H128" s="41" t="inlineStr"/>
-      <c r="I128" s="41" t="inlineStr"/>
-    </row>
-    <row r="129" ht="30" customHeight="1">
+    <row r="129" ht="16" customHeight="1">
       <c r="A129" s="35" t="n"/>
       <c r="B129" s="36" t="inlineStr">
         <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C129" s="37" t="inlineStr">
+        <is>
           <t>09:40</t>
         </is>
       </c>
-      <c r="C129" s="37" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="D129" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35815,7 +35815,7 @@
       </c>
       <c r="E129" s="39" t="inlineStr">
         <is>
-          <t>La plaza de Hudson Yards mientras abre el Vessel: The Shops y el Shed desde afuera. Sacar el timed ticket de las 10:00 online antes.</t>
+          <t>Subte a Hudson Yards.</t>
         </is>
       </c>
       <c r="F129" s="37" t="inlineStr"/>
@@ -35825,31 +35825,27 @@
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="35" t="n"/>
-      <c r="B130" s="42" t="inlineStr">
+      <c r="B130" s="36" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="C130" s="37" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="C130" s="43" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="D130" s="44" t="inlineStr">
+      <c r="D130" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E130" s="45" t="inlineStr">
-        <is>
-          <t>★ THE VESSEL — la escalera infinita de Heatherwick: 154 tramos, 2.500 escalones, $10. Reabierto con redes; algunos tramos altos hacia el Hudson siguen cerrados, y hay ascensor cada 15 min. Subir es la única forma de entenderla. Si Thais prefiere no subir, la plaza está al pie.</t>
-        </is>
-      </c>
-      <c r="F130" s="43" t="inlineStr">
-        <is>
-          <t>The Vessel</t>
-        </is>
-      </c>
+      <c r="E130" s="39" t="inlineStr">
+        <is>
+          <t>La plaza de Hudson Yards mientras abre el Vessel: The Shops y el Shed desde afuera. Sacar el timed ticket de las 10:00 online antes.</t>
+        </is>
+      </c>
+      <c r="F130" s="37" t="inlineStr"/>
       <c r="G130" s="40" t="inlineStr"/>
       <c r="H130" s="41" t="inlineStr"/>
       <c r="I130" s="41" t="inlineStr"/>
@@ -35858,14 +35854,14 @@
       <c r="A131" s="35" t="n"/>
       <c r="B131" s="42" t="inlineStr">
         <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C131" s="43" t="inlineStr">
+        <is>
           <t>10:50</t>
         </is>
       </c>
-      <c r="C131" s="43" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="D131" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -35873,52 +35869,48 @@
       </c>
       <c r="E131" s="45" t="inlineStr">
         <is>
-          <t>★ THE HIGH LINE completo, de norte a sur (2,3 km) — arranca ahí mismo, en 30th y 10ª. Vía ferroviaria elevada convertida en parque lineal. Incluye el Buda de arenisca de 9 metros de Tuan Andrew Nguyen.</t>
+          <t>★ THE VESSEL — la escalera infinita de Heatherwick: 154 tramos, 2.500 escalones, $10. Reabierto con redes; algunos tramos altos hacia el Hudson siguen cerrados, y hay ascensor cada 15 min. Subir es la única forma de entenderla. Si Thais prefiere no subir, la plaza está al pie.</t>
         </is>
       </c>
       <c r="F131" s="43" t="inlineStr">
         <is>
-          <t>The High Line</t>
-        </is>
-      </c>
-      <c r="G131" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~12 min a pie · 0.9 km · estimado</t>
-        </is>
-      </c>
+          <t>The Vessel</t>
+        </is>
+      </c>
+      <c r="G131" s="40" t="inlineStr"/>
       <c r="H131" s="41" t="inlineStr"/>
       <c r="I131" s="41" t="inlineStr"/>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="35" t="n"/>
-      <c r="B132" s="36" t="inlineStr">
+      <c r="B132" s="42" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="C132" s="43" t="inlineStr">
         <is>
           <t>12:20</t>
         </is>
       </c>
-      <c r="C132" s="37" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="D132" s="38" t="inlineStr">
+      <c r="D132" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E132" s="39" t="inlineStr">
-        <is>
-          <t>Little Island — el parque flotante de Heatherwick sobre 132 macetas de hormigón, al final del High Line. Gratis.</t>
-        </is>
-      </c>
-      <c r="F132" s="37" t="inlineStr">
-        <is>
-          <t>Little Island</t>
+      <c r="E132" s="45" t="inlineStr">
+        <is>
+          <t>★ THE HIGH LINE completo, de norte a sur (2,3 km) — arranca ahí mismo, en 30th y 10ª. Vía ferroviaria elevada convertida en parque lineal. Incluye el Buda de arenisca de 9 metros de Tuan Andrew Nguyen.</t>
+        </is>
+      </c>
+      <c r="F132" s="43" t="inlineStr">
+        <is>
+          <t>The High Line</t>
         </is>
       </c>
       <c r="G132" s="40" t="inlineStr">
         <is>
-          <t>🚶 ~15 min a pie · 1.1 km · estimado</t>
+          <t>🚶 ~12 min a pie · 0.9 km · estimado</t>
         </is>
       </c>
       <c r="H132" s="41" t="inlineStr"/>
@@ -35926,63 +35918,63 @@
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="35" t="n"/>
-      <c r="B133" s="42" t="inlineStr">
+      <c r="B133" s="36" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="C133" s="37" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="C133" s="43" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="D133" s="44" t="inlineStr">
+      <c r="D133" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E133" s="45" t="inlineStr">
-        <is>
-          <t>Galerías de Chelsea COMPLETAS — W 19th a W 27th entre la 10ª y la 11ª, concentradas en W 24th y W 21st (Gagosian, Pace, Zwirner). Gratis, se entra y se sale. El recorte del Vessel se devolvió: SUMMIT pasó al atardecer y la tarde se estiró.</t>
-        </is>
-      </c>
-      <c r="F133" s="43" t="inlineStr"/>
-      <c r="G133" s="40" t="inlineStr"/>
+      <c r="E133" s="39" t="inlineStr">
+        <is>
+          <t>Little Island — el parque flotante de Heatherwick sobre 132 macetas de hormigón, al final del High Line. Gratis.</t>
+        </is>
+      </c>
+      <c r="F133" s="37" t="inlineStr">
+        <is>
+          <t>Little Island</t>
+        </is>
+      </c>
+      <c r="G133" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~15 min a pie · 1.1 km · estimado</t>
+        </is>
+      </c>
       <c r="H133" s="41" t="inlineStr"/>
       <c r="I133" s="41" t="inlineStr"/>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="35" t="n"/>
-      <c r="B134" s="36" t="inlineStr">
+      <c r="B134" s="42" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C134" s="43" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="C134" s="37" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="D134" s="38" t="inlineStr">
+      <c r="D134" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E134" s="39" t="inlineStr">
-        <is>
-          <t>Almuerzo en Chelsea Market — COMER FUERTE: es la comida grande del día, la cena de hoy es un bocado rápido entre el SUMMIT y el Vanguard. Los Tacos No.1 o Very Fresh Noodles. Ahora hay casi DOS HORAS: sin apuro, y si quedaron galerías de Chelsea sin ver, se vuelve. ★ HEATONIST está ADENTRO de este mismo mercado (12-18:45): más de 100 salsas picantes para probar, con el lineup de Hot Ones. Si el sábado no llegan a la de Williamsburg, esta es la misma cata en menos metros.</t>
-        </is>
-      </c>
-      <c r="F134" s="37" t="inlineStr">
-        <is>
-          <t>Chelsea Market</t>
-        </is>
-      </c>
-      <c r="G134" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~7 min a pie · 0.5 km · estimado</t>
-        </is>
-      </c>
+      <c r="E134" s="45" t="inlineStr">
+        <is>
+          <t>Galerías de Chelsea COMPLETAS — W 19th a W 27th entre la 10ª y la 11ª, concentradas en W 24th y W 21st (Gagosian, Pace, Zwirner). Gratis, se entra y se sale. El recorte del Vessel se devolvió: SUMMIT pasó al atardecer y la tarde se estiró.</t>
+        </is>
+      </c>
+      <c r="F134" s="43" t="inlineStr"/>
+      <c r="G134" s="40" t="inlineStr"/>
       <c r="H134" s="41" t="inlineStr"/>
       <c r="I134" s="41" t="inlineStr"/>
     </row>
@@ -35990,14 +35982,14 @@
       <c r="A135" s="35" t="n"/>
       <c r="B135" s="36" t="inlineStr">
         <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C135" s="37" t="inlineStr">
+        <is>
           <t>16:25</t>
         </is>
       </c>
-      <c r="C135" s="37" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="D135" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36005,126 +35997,134 @@
       </c>
       <c r="E135" s="39" t="inlineStr">
         <is>
-          <t>A la Morgan: L desde 14 St-8 Av hasta Union Sq y 6 hasta 33 St, o A/C/E hasta 34 St-Penn y siete cuadras a pie (~30 min). Salir 16:25 deja margen para entrar 17:00 EN PUNTO.</t>
-        </is>
-      </c>
-      <c r="F135" s="37" t="inlineStr"/>
-      <c r="G135" s="40" t="inlineStr"/>
+          <t>Almuerzo en Chelsea Market — COMER FUERTE: es la comida grande del día, la cena de hoy es un bocado rápido entre el SUMMIT y el Vanguard. Los Tacos No.1 o Very Fresh Noodles. Ahora hay casi DOS HORAS: sin apuro, y si quedaron galerías de Chelsea sin ver, se vuelve. ★ HEATONIST está ADENTRO de este mismo mercado (12-18:45): más de 100 salsas picantes para probar, con el lineup de Hot Ones. Si el sábado no llegan a la de Williamsburg, esta es la misma cata en menos metros.</t>
+        </is>
+      </c>
+      <c r="F135" s="37" t="inlineStr">
+        <is>
+          <t>Chelsea Market</t>
+        </is>
+      </c>
+      <c r="G135" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~7 min a pie · 0.5 km · estimado</t>
+        </is>
+      </c>
       <c r="H135" s="41" t="inlineStr"/>
       <c r="I135" s="41" t="inlineStr"/>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="35" t="n"/>
-      <c r="B136" s="42" t="inlineStr">
+      <c r="B136" s="36" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="C136" s="37" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="C136" s="43" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="D136" s="44" t="inlineStr">
+      <c r="D136" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E136" s="45" t="inlineStr">
-        <is>
-          <t>★ MORGAN LIBRARY — GRATIS los viernes 17-20h: entrar 17:00 EN PUNTO y hacerla en una hora — la biblioteca son tres salas gloriosas (estanterías de nogal, la Biblia de Gutenberg): alcanza. RESERVA OBLIGATORIA, se libera el viernes 28 de agosto. Está a 8 min a pie de One Vanderbilt.</t>
-        </is>
-      </c>
-      <c r="F136" s="43" t="inlineStr">
-        <is>
-          <t>The Morgan Library &amp; Museum</t>
-        </is>
-      </c>
+      <c r="E136" s="39" t="inlineStr">
+        <is>
+          <t>A la Morgan: L desde 14 St-8 Av hasta Union Sq y 6 hasta 33 St, o A/C/E hasta 34 St-Penn y siete cuadras a pie (~30 min). Salir 16:25 deja margen para entrar 17:00 EN PUNTO.</t>
+        </is>
+      </c>
+      <c r="F136" s="37" t="inlineStr"/>
       <c r="G136" s="40" t="inlineStr"/>
       <c r="H136" s="41" t="inlineStr"/>
       <c r="I136" s="41" t="inlineStr"/>
     </row>
-    <row r="137" ht="16" customHeight="1">
+    <row r="137" ht="30" customHeight="1">
       <c r="A137" s="35" t="n"/>
-      <c r="B137" s="36" t="inlineStr">
+      <c r="B137" s="42" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C137" s="43" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="C137" s="37" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="D137" s="38" t="inlineStr">
+      <c r="D137" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E137" s="39" t="inlineStr">
-        <is>
-          <t>Caminar las seis cuadras de la Morgan a One Vanderbilt (~8-10 min).</t>
-        </is>
-      </c>
-      <c r="F137" s="37" t="inlineStr"/>
+      <c r="E137" s="45" t="inlineStr">
+        <is>
+          <t>★ MORGAN LIBRARY — GRATIS los viernes 17-20h: entrar 17:00 EN PUNTO y hacerla en una hora — la biblioteca son tres salas gloriosas (estanterías de nogal, la Biblia de Gutenberg): alcanza. RESERVA OBLIGATORIA, se libera el viernes 28 de agosto. Está a 8 min a pie de One Vanderbilt.</t>
+        </is>
+      </c>
+      <c r="F137" s="43" t="inlineStr">
+        <is>
+          <t>The Morgan Library &amp; Museum</t>
+        </is>
+      </c>
       <c r="G137" s="40" t="inlineStr"/>
       <c r="H137" s="41" t="inlineStr"/>
       <c r="I137" s="41" t="inlineStr"/>
     </row>
-    <row r="138" ht="30" customHeight="1">
+    <row r="138" ht="16" customHeight="1">
       <c r="A138" s="35" t="n"/>
-      <c r="B138" s="42" t="inlineStr">
+      <c r="B138" s="36" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C138" s="37" t="inlineStr">
         <is>
           <t>18:10</t>
         </is>
       </c>
-      <c r="C138" s="43" t="inlineStr">
-        <is>
-          <t>20:20</t>
-        </is>
-      </c>
-      <c r="D138" s="44" t="inlineStr">
+      <c r="D138" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E138" s="45" t="inlineStr">
-        <is>
-          <t>★★ SUMMIT ONE VANDERBILT — EL ARCO COMPLETO: entrada 18:10 con luz, el atardecer ~19:21 multiplicado por los espejos infinitos de Kusama, y la noche encendida hasta ~20:15. Ticket ATARDECER $57-63 — es la franja que primero se agota: reservar YA. NO está en ningún pase.</t>
-        </is>
-      </c>
-      <c r="F138" s="43" t="inlineStr">
-        <is>
-          <t>SUMMIT One Vanderbilt</t>
-        </is>
-      </c>
+      <c r="E138" s="39" t="inlineStr">
+        <is>
+          <t>Caminar las seis cuadras de la Morgan a One Vanderbilt (~8-10 min).</t>
+        </is>
+      </c>
+      <c r="F138" s="37" t="inlineStr"/>
       <c r="G138" s="40" t="inlineStr"/>
       <c r="H138" s="41" t="inlineStr"/>
       <c r="I138" s="41" t="inlineStr"/>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="35" t="n"/>
-      <c r="B139" s="36" t="inlineStr">
+      <c r="B139" s="42" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="C139" s="43" t="inlineStr">
         <is>
           <t>20:20</t>
         </is>
       </c>
-      <c r="C139" s="37" t="inlineStr">
-        <is>
-          <t>20:50</t>
-        </is>
-      </c>
-      <c r="D139" s="38" t="inlineStr">
+      <c r="D139" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E139" s="39" t="inlineStr">
-        <is>
-          <t>Bajar AL VILLAGE PRIMERO y cenar allá: 4/5/6 o 7 hasta 14 St-Union Sq y 1 hasta Christopher St (~25 min). Cenar cerca de Grand Central y bajar después llega justo; hacerlo al revés deja margen.</t>
-        </is>
-      </c>
-      <c r="F139" s="37" t="inlineStr"/>
+      <c r="E139" s="45" t="inlineStr">
+        <is>
+          <t>★★ SUMMIT ONE VANDERBILT — EL ARCO COMPLETO: entrada 18:10 con luz, el atardecer ~19:21 multiplicado por los espejos infinitos de Kusama, y la noche encendida hasta ~20:15. Ticket ATARDECER $57-63 — es la franja que primero se agota: reservar YA. NO está en ningún pase.</t>
+        </is>
+      </c>
+      <c r="F139" s="43" t="inlineStr">
+        <is>
+          <t>SUMMIT One Vanderbilt</t>
+        </is>
+      </c>
       <c r="G139" s="40" t="inlineStr"/>
       <c r="H139" s="41" t="inlineStr"/>
       <c r="I139" s="41" t="inlineStr"/>
@@ -36133,14 +36133,14 @@
       <c r="A140" s="35" t="n"/>
       <c r="B140" s="36" t="inlineStr">
         <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="C140" s="37" t="inlineStr">
+        <is>
           <t>20:50</t>
         </is>
       </c>
-      <c r="C140" s="37" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
       <c r="D140" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36148,7 +36148,7 @@
       </c>
       <c r="E140" s="39" t="inlineStr">
         <is>
-          <t>Cena en el West Village, a cinco minutos del club. El Vanguard NO sirve NADA de comida (lo dicen así: 'ni un maní') y no se permite entrar comida: lo que no cenen ahora, no se cena. 40 minutos alcanzan.</t>
+          <t>Bajar AL VILLAGE PRIMERO y cenar allá: 4/5/6 o 7 hasta 14 St-Union Sq y 1 hasta Christopher St (~25 min). Cenar cerca de Grand Central y bajar después llega justo; hacerlo al revés deja margen.</t>
         </is>
       </c>
       <c r="F140" s="37" t="inlineStr"/>
@@ -36160,14 +36160,14 @@
       <c r="A141" s="35" t="n"/>
       <c r="B141" s="36" t="inlineStr">
         <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="C141" s="37" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C141" s="37" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
       <c r="D141" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36175,7 +36175,7 @@
       </c>
       <c r="E141" s="39" t="inlineStr">
         <is>
-          <t>EN LA PUERTA DEL VANGUARD a las 21:30 EN PUNTO: el acomodo del segundo set arranca a esa hora y los asientos son POR ORDEN DE LLEGADA — la entrada es General Admission, no numerada. Con 123 asientos, los diez minutos de diferencia son estar frente al piano o contra la columna. El ticket lo dice: el acomodo tardío, con entrada o sin ella, queda a criterio del encargado.</t>
+          <t>Cena en el West Village, a cinco minutos del club. El Vanguard NO sirve NADA de comida (lo dicen así: 'ni un maní') y no se permite entrar comida: lo que no cenen ahora, no se cena. 40 minutos alcanzan.</t>
         </is>
       </c>
       <c r="F141" s="37" t="inlineStr"/>
@@ -36185,199 +36185,199 @@
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="35" t="n"/>
-      <c r="B142" s="42" t="inlineStr">
+      <c r="B142" s="36" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C142" s="37" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C142" s="43" t="inlineStr"/>
-      <c r="D142" s="44" t="inlineStr">
+      <c r="D142" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E142" s="45" t="inlineStr">
-        <is>
-          <t>★★ VILLAGE VANGUARD — JOHN PATITUCCI TRIO con Chris Potter y Brian Blade, SET DE LAS 22:00. Movido acá desde el martes para que vayan LOS DOS (pedido de Juan). El sótano triangular de 1935, 123 asientos, la acústica que grabó a Coltrane. ✔ ENTRADAS COMPRADAS el 26/8: 2 × General Admission $45 (#18741454 y #18741456), a nombre de Juan Pablo Garicoïts. Falta solo el mínimo de UNA CONSUMICIÓN por cabeza en la mesa (vale gaseosa, jugo o agua) — se paga ahí, aceptan tarjeta.</t>
-        </is>
-      </c>
-      <c r="F142" s="43" t="inlineStr">
-        <is>
-          <t>Village Vanguard</t>
-        </is>
-      </c>
+      <c r="E142" s="39" t="inlineStr">
+        <is>
+          <t>EN LA PUERTA DEL VANGUARD a las 21:30 EN PUNTO: el acomodo del segundo set arranca a esa hora y los asientos son POR ORDEN DE LLEGADA — la entrada es General Admission, no numerada. Con 123 asientos, los diez minutos de diferencia son estar frente al piano o contra la columna. El ticket lo dice: el acomodo tardío, con entrada o sin ella, queda a criterio del encargado.</t>
+        </is>
+      </c>
+      <c r="F142" s="37" t="inlineStr"/>
       <c r="G142" s="40" t="inlineStr"/>
       <c r="H142" s="41" t="inlineStr"/>
       <c r="I142" s="41" t="inlineStr"/>
     </row>
-    <row r="143" ht="32" customHeight="1">
-      <c r="A143" s="46" t="inlineStr">
+    <row r="143" ht="30" customHeight="1">
+      <c r="A143" s="35" t="n"/>
+      <c r="B143" s="42" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C143" s="43" t="inlineStr"/>
+      <c r="D143" s="44" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E143" s="45" t="inlineStr">
+        <is>
+          <t>★★ VILLAGE VANGUARD — JOHN PATITUCCI TRIO con Chris Potter y Brian Blade, SET DE LAS 22:00. Movido acá desde el martes para que vayan LOS DOS (pedido de Juan). El sótano triangular de 1935, 123 asientos, la acústica que grabó a Coltrane. ✔ ENTRADAS COMPRADAS el 26/8: 2 × General Admission $45 (#18741454 y #18741456), a nombre de Juan Pablo Garicoïts. Falta solo el mínimo de UNA CONSUMICIÓN por cabeza en la mesa (vale gaseosa, jugo o agua) — se paga ahí, aceptan tarjeta.</t>
+        </is>
+      </c>
+      <c r="F143" s="43" t="inlineStr">
+        <is>
+          <t>Village Vanguard</t>
+        </is>
+      </c>
+      <c r="G143" s="40" t="inlineStr"/>
+      <c r="H143" s="41" t="inlineStr"/>
+      <c r="I143" s="41" t="inlineStr"/>
+    </row>
+    <row r="144" ht="32" customHeight="1">
+      <c r="A144" s="46" t="inlineStr">
         <is>
           <t>ALTERNATIVA / OJO:  ⚠️ OJO CON LA MAÑANA, y es nuevo: Juan hizo el HIGH LINE, LITTLE ISLAND y el VESSEL el miércoles temprano, solo. Los tres siguen en el plan de hoy porque THAIS NO LOS VIO —el Vessel además lo tienen 2/2 y es imprescindible— así que sacarlos la perjudica a ella. Decidan en el momento: si Juan la acompaña igual, el High Line de día con ella es otro paseo y no se pierde nada; si prefieren no repetir, esa mañana libera de 9:15 a 13:00 y ahí entran las galerías de Chelsea con calma, o el Whitney, que hoy es gratis de 17 a 22 pero abre 10:30. // EL CANJE DE ESTA NOCHE: para meter el Vanguard con Thais, SALIÓ BILL'S PLACE. No hay otra noche donde entre (Bill Saxton toca solo viernes y sábado, y el sábado está tomado por Peter Luger + el play + el Café Wha). Con las entradas ya compradas y sin cambios ni transferencias, el canje quedó CERRADO: Bill's Place sale del viaje. // EL WHITNEY, con los números verificados el 27/8: gratis todos los viernes de 17:00 a 22:00 (normal $30), y hoy pasan por Meatpacking, que es donde está. Coincide barrio, día y franja. El problema es el reloj y es serio: la Morgan también es hoy 17:00-20:00 y el SUMMIT entra 18:10. Meter el Whitney obliga a recortar el High Line o a soltar la Morgan, que ustedes tienen en 2 y el Whitney en 'quizás'. Si igual lo prefieren, el ticket gratis es OBLIGATORIO y hay que sacarlo antes. Si igual lo prefieren, el ticket gratis es OBLIGATORIO y el Whitney ahora cierra los martes. SI ALGO SALIERA MAL con el acomodo (llegar tarde y que no haya lugar): Mezzrow o Smalls quedan a cuatro cuadras ($25 con bebida, Smalls tiene jam de madrugada los viernes desde la 1:00), o el Blue Note — el 4 y 5 de septiembre toca Chief Adjuah.</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="22" customHeight="1">
-      <c r="A145" s="33" t="inlineStr">
+    <row r="146" ht="22" customHeight="1">
+      <c r="A146" s="33" t="inlineStr">
         <is>
           <t>DÍA 8 · Sábado 05/09 · Brooklyn, Peter Luger, un PLAY y Café Wha hasta la madrugada  —  base: The Beacon  ·  Ambos</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="32" customHeight="1">
-      <c r="A146" s="34" t="inlineStr">
+    <row r="147" ht="32" customHeight="1">
+      <c r="A147" s="34" t="inlineStr">
         <is>
           <t>La gran noche del viaje, rearmada a pedido: el musical SALIÓ y entraron un PLAY de Broadway a las 19:30 y el CAFÉ WHA a las 23:45 — el sótano del Village donde debutaron Dylan y Hendrix, con reserva gratis ya pedida por Eventbrite. La cena temprana en Peter Luger (17:00) ahora existe exactamente para esto: porterhouse → telón → medianoche de soul y funk. Frankel's sigue afuera (a un porterhouse no se llega con un pastrami encima) y Westlight sigue opcional. ⚠️ La noche termina ~1:15-1:30: el domingo no tiene NADA fijo hasta las 16:00.</t>
         </is>
       </c>
-    </row>
-    <row r="147" ht="30" customHeight="1">
-      <c r="A147" s="35" t="n"/>
-      <c r="B147" s="36" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="C147" s="37" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="D147" s="38" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="E147" s="39" t="inlineStr">
-        <is>
-          <t>Salir 8:15: 1/2/3 desde 72 St + transbordo a A/C hasta High St son ~40-45 min REALES. Llegar temprano a DUMBO es la diferencia entre la foto y la cola de fotos.</t>
-        </is>
-      </c>
-      <c r="F147" s="37" t="inlineStr"/>
-      <c r="G147" s="40" t="inlineStr"/>
-      <c r="H147" s="41" t="inlineStr"/>
-      <c r="I147" s="41" t="inlineStr"/>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="35" t="n"/>
-      <c r="B148" s="42" t="inlineStr">
+      <c r="B148" s="36" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="C148" s="37" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="C148" s="43" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="D148" s="44" t="inlineStr">
+      <c r="D148" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E148" s="45" t="inlineStr">
-        <is>
-          <t>★ Brooklyn Bridge Park y DUMBO — muelles reconvertidos con el skyline de Lower Manhattan de frente, y la foto del Manhattan Bridge encuadrado en Washington y Water.</t>
-        </is>
-      </c>
-      <c r="F148" s="43" t="inlineStr">
-        <is>
-          <t>Brooklyn Bridge Park</t>
-        </is>
-      </c>
+      <c r="E148" s="39" t="inlineStr">
+        <is>
+          <t>Salir 8:15: 1/2/3 desde 72 St + transbordo a A/C hasta High St son ~40-45 min REALES. Llegar temprano a DUMBO es la diferencia entre la foto y la cola de fotos.</t>
+        </is>
+      </c>
+      <c r="F148" s="37" t="inlineStr"/>
       <c r="G148" s="40" t="inlineStr"/>
       <c r="H148" s="41" t="inlineStr"/>
       <c r="I148" s="41" t="inlineStr"/>
     </row>
-    <row r="149" ht="16" customHeight="1">
+    <row r="149" ht="30" customHeight="1">
       <c r="A149" s="35" t="n"/>
-      <c r="B149" s="36" t="inlineStr">
+      <c r="B149" s="42" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C149" s="43" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="C149" s="37" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="D149" s="38" t="inlineStr">
+      <c r="D149" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E149" s="39" t="inlineStr">
-        <is>
-          <t>Brooklyn Heights Promenade — la postal clásica del skyline sobre el BQE.</t>
-        </is>
-      </c>
-      <c r="F149" s="37" t="inlineStr">
-        <is>
-          <t>Brooklyn Heights Promenade</t>
-        </is>
-      </c>
-      <c r="G149" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~8 min a pie · 0.6 km · estimado</t>
-        </is>
-      </c>
+      <c r="E149" s="45" t="inlineStr">
+        <is>
+          <t>★ Brooklyn Bridge Park y DUMBO — muelles reconvertidos con el skyline de Lower Manhattan de frente, y la foto del Manhattan Bridge encuadrado en Washington y Water.</t>
+        </is>
+      </c>
+      <c r="F149" s="43" t="inlineStr">
+        <is>
+          <t>Brooklyn Bridge Park</t>
+        </is>
+      </c>
+      <c r="G149" s="40" t="inlineStr"/>
       <c r="H149" s="41" t="inlineStr"/>
       <c r="I149" s="41" t="inlineStr"/>
     </row>
-    <row r="150" ht="30" customHeight="1">
+    <row r="150" ht="16" customHeight="1">
       <c r="A150" s="35" t="n"/>
-      <c r="B150" s="42" t="inlineStr">
+      <c r="B150" s="36" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C150" s="37" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="C150" s="43" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="D150" s="44" t="inlineStr">
+      <c r="D150" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E150" s="45" t="inlineStr">
-        <is>
-          <t>★ NEW YORK TRANSIT MUSEUM — una estación de subte clausurada de 1936 con 20 vagones históricos en las vías originales; se puede subir a todos. $10. Cierra lunes y martes, así que hoy es el día.</t>
-        </is>
-      </c>
-      <c r="F150" s="43" t="inlineStr">
-        <is>
-          <t>New York Transit Museum</t>
-        </is>
-      </c>
-      <c r="G150" s="40" t="inlineStr"/>
+      <c r="E150" s="39" t="inlineStr">
+        <is>
+          <t>Brooklyn Heights Promenade — la postal clásica del skyline sobre el BQE.</t>
+        </is>
+      </c>
+      <c r="F150" s="37" t="inlineStr">
+        <is>
+          <t>Brooklyn Heights Promenade</t>
+        </is>
+      </c>
+      <c r="G150" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~8 min a pie · 0.6 km · estimado</t>
+        </is>
+      </c>
       <c r="H150" s="41" t="inlineStr"/>
       <c r="I150" s="41" t="inlineStr"/>
     </row>
-    <row r="151" ht="16" customHeight="1">
+    <row r="151" ht="30" customHeight="1">
       <c r="A151" s="35" t="n"/>
-      <c r="B151" s="36" t="inlineStr">
+      <c r="B151" s="42" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C151" s="43" t="inlineStr">
         <is>
           <t>12:45</t>
         </is>
       </c>
-      <c r="C151" s="37" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="D151" s="38" t="inlineStr">
+      <c r="D151" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E151" s="39" t="inlineStr">
-        <is>
-          <t>Almuerzo en Downtown Brooklyn.</t>
-        </is>
-      </c>
-      <c r="F151" s="37" t="inlineStr"/>
+      <c r="E151" s="45" t="inlineStr">
+        <is>
+          <t>★ NEW YORK TRANSIT MUSEUM — una estación de subte clausurada de 1936 con 20 vagones históricos en las vías originales; se puede subir a todos. $10. Cierra lunes y martes, así que hoy es el día.</t>
+        </is>
+      </c>
+      <c r="F151" s="43" t="inlineStr">
+        <is>
+          <t>New York Transit Museum</t>
+        </is>
+      </c>
       <c r="G151" s="40" t="inlineStr"/>
       <c r="H151" s="41" t="inlineStr"/>
       <c r="I151" s="41" t="inlineStr"/>
@@ -36386,14 +36386,14 @@
       <c r="A152" s="35" t="n"/>
       <c r="B152" s="36" t="inlineStr">
         <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C152" s="37" t="inlineStr">
+        <is>
           <t>13:45</t>
         </is>
       </c>
-      <c r="C152" s="37" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="D152" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36401,7 +36401,7 @@
       </c>
       <c r="E152" s="39" t="inlineStr">
         <is>
-          <t>Subte a Williamsburg.</t>
+          <t>Almuerzo en Downtown Brooklyn.</t>
         </is>
       </c>
       <c r="F152" s="37" t="inlineStr"/>
@@ -36409,84 +36409,76 @@
       <c r="H152" s="41" t="inlineStr"/>
       <c r="I152" s="41" t="inlineStr"/>
     </row>
-    <row r="153" ht="30" customHeight="1">
+    <row r="153" ht="16" customHeight="1">
       <c r="A153" s="35" t="n"/>
-      <c r="B153" s="42" t="inlineStr">
+      <c r="B153" s="36" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="C153" s="37" t="inlineStr">
         <is>
           <t>14:15</t>
         </is>
       </c>
-      <c r="C153" s="43" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="D153" s="44" t="inlineStr">
+      <c r="D153" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E153" s="45" t="inlineStr">
-        <is>
-          <t>★ Domino Park — ex refinería de azúcar; el paseo elevado pasa entre la maquinaria industrial conservada, con el Williamsburg Bridge y Midtown enfrente.</t>
-        </is>
-      </c>
-      <c r="F153" s="43" t="inlineStr">
-        <is>
-          <t>Domino Park</t>
-        </is>
-      </c>
+      <c r="E153" s="39" t="inlineStr">
+        <is>
+          <t>Subte a Williamsburg.</t>
+        </is>
+      </c>
+      <c r="F153" s="37" t="inlineStr"/>
       <c r="G153" s="40" t="inlineStr"/>
       <c r="H153" s="41" t="inlineStr"/>
       <c r="I153" s="41" t="inlineStr"/>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="35" t="n"/>
-      <c r="B154" s="36" t="inlineStr">
+      <c r="B154" s="42" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="C154" s="43" t="inlineStr">
         <is>
           <t>15:15</t>
         </is>
       </c>
-      <c r="C154" s="37" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="D154" s="38" t="inlineStr">
+      <c r="D154" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E154" s="39" t="inlineStr">
-        <is>
-          <t>Paseo por Williamsburg: Bedford Ave, disquerías y vintage. ★ ACÁ ENTRA HEATONIST (121 Wythe Ave, a una cuadra de Bedford): la tienda insignia de salsas picantes, con más de 100 para probar en el local y el lineup completo de Hot Ones. Abre 12-19 todos los días, así que a esta hora está abierta y les queda de camino al Williamsburg Bridge. OPCIONAL si quieren la panorámica: Westlight (piso 22, sin cover, un trago) — lo bajaron a 'quizás'. NO comer nada: lo que viene lo merece.</t>
-        </is>
-      </c>
-      <c r="F154" s="37" t="inlineStr">
-        <is>
-          <t>HEATONIST Williamsburg</t>
-        </is>
-      </c>
-      <c r="G154" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~20 min a pie (1.2 km) o 🚇 ~15 min · estimado</t>
-        </is>
-      </c>
+      <c r="E154" s="45" t="inlineStr">
+        <is>
+          <t>★ Domino Park — ex refinería de azúcar; el paseo elevado pasa entre la maquinaria industrial conservada, con el Williamsburg Bridge y Midtown enfrente.</t>
+        </is>
+      </c>
+      <c r="F154" s="43" t="inlineStr">
+        <is>
+          <t>Domino Park</t>
+        </is>
+      </c>
+      <c r="G154" s="40" t="inlineStr"/>
       <c r="H154" s="41" t="inlineStr"/>
       <c r="I154" s="41" t="inlineStr"/>
     </row>
-    <row r="155" ht="16" customHeight="1">
+    <row r="155" ht="30" customHeight="1">
       <c r="A155" s="35" t="n"/>
       <c r="B155" s="36" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C155" s="37" t="inlineStr">
+        <is>
           <t>16:45</t>
         </is>
       </c>
-      <c r="C155" s="37" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="D155" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36494,142 +36486,150 @@
       </c>
       <c r="E155" s="39" t="inlineStr">
         <is>
-          <t>Caminar por Bedford/Driggs hasta el pie del Williamsburg Bridge (~15 min).</t>
-        </is>
-      </c>
-      <c r="F155" s="37" t="inlineStr"/>
-      <c r="G155" s="40" t="inlineStr"/>
+          <t>Paseo por Williamsburg: Bedford Ave, disquerías y vintage. ★ ACÁ ENTRA HEATONIST (121 Wythe Ave, a una cuadra de Bedford): la tienda insignia de salsas picantes, con más de 100 para probar en el local y el lineup completo de Hot Ones. Abre 12-19 todos los días, así que a esta hora está abierta y les queda de camino al Williamsburg Bridge. OPCIONAL si quieren la panorámica: Westlight (piso 22, sin cover, un trago) — lo bajaron a 'quizás'. NO comer nada: lo que viene lo merece.</t>
+        </is>
+      </c>
+      <c r="F155" s="37" t="inlineStr">
+        <is>
+          <t>HEATONIST Williamsburg</t>
+        </is>
+      </c>
+      <c r="G155" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~20 min a pie (1.2 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H155" s="41" t="inlineStr"/>
       <c r="I155" s="41" t="inlineStr"/>
     </row>
-    <row r="156" ht="30" customHeight="1">
+    <row r="156" ht="16" customHeight="1">
       <c r="A156" s="35" t="n"/>
-      <c r="B156" s="42" t="inlineStr">
+      <c r="B156" s="36" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C156" s="37" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="C156" s="43" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="D156" s="44" t="inlineStr">
+      <c r="D156" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E156" s="45" t="inlineStr">
-        <is>
-          <t>★★ PETER LUGER (178 Broadway) — el porterhouse for two de 1887, dry-aged en el sótano, con la tocineta gruesa de entrada. ~$160-200 los dos con sides y propina. ⚠️ SIN TARJETAS DE CRÉDITO: efectivo, débito US o cheque — llevar cash. Cena temprana a propósito: el teatro espera. RESERVA EN RESY YA.</t>
-        </is>
-      </c>
-      <c r="F156" s="43" t="inlineStr">
-        <is>
-          <t>Peter Luger Steak House</t>
-        </is>
-      </c>
+      <c r="E156" s="39" t="inlineStr">
+        <is>
+          <t>Caminar por Bedford/Driggs hasta el pie del Williamsburg Bridge (~15 min).</t>
+        </is>
+      </c>
+      <c r="F156" s="37" t="inlineStr"/>
       <c r="G156" s="40" t="inlineStr"/>
       <c r="H156" s="41" t="inlineStr"/>
       <c r="I156" s="41" t="inlineStr"/>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="35" t="n"/>
-      <c r="B157" s="36" t="inlineStr">
+      <c r="B157" s="42" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C157" s="43" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="C157" s="37" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="D157" s="38" t="inlineStr">
+      <c r="D157" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E157" s="39" t="inlineStr">
-        <is>
-          <t>A la zona de teatros: subte J desde Marcy Av hasta Essex St y F hasta 42 St-Bryant Park (~35 min con transbordo), o directamente Uber al teatro (~20-25 min, $25-35 — un sábado a la noche el puente puede estar cargado).</t>
-        </is>
-      </c>
-      <c r="F157" s="37" t="inlineStr"/>
+      <c r="E157" s="45" t="inlineStr">
+        <is>
+          <t>★★ PETER LUGER (178 Broadway) — el porterhouse for two de 1887, dry-aged en el sótano, con la tocineta gruesa de entrada. ~$160-200 los dos con sides y propina. ⚠️ SIN TARJETAS DE CRÉDITO: efectivo, débito US o cheque — llevar cash. Cena temprana a propósito: el teatro espera. RESERVA EN RESY YA.</t>
+        </is>
+      </c>
+      <c r="F157" s="43" t="inlineStr">
+        <is>
+          <t>Peter Luger Steak House</t>
+        </is>
+      </c>
       <c r="G157" s="40" t="inlineStr"/>
       <c r="H157" s="41" t="inlineStr"/>
       <c r="I157" s="41" t="inlineStr"/>
     </row>
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="35" t="n"/>
-      <c r="B158" s="42" t="inlineStr">
+      <c r="B158" s="36" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C158" s="37" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="C158" s="43" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="D158" s="44" t="inlineStr">
+      <c r="D158" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E158" s="45" t="inlineStr">
-        <is>
-          <t>★★ PLAY DE BROADWAY — mi recomendación: STRANGER THINGS: THE FIRST SHADOW (Marquis, desde ~$76): la maquinaria escénica que ganó el Tony — para quien viene de Mercer Labs, el mismo músculo llevado al teatro. Alternativas esa semana: Harry Potter and the Cursed Child, Paranormal Activity, The Imaginary Invalid. COMPRA FIRME esta semana y verificar el horario real de la función (19:00/19:30/20:00): tiene que terminar ~22:00 para lo que sigue.</t>
-        </is>
-      </c>
-      <c r="F158" s="43" t="inlineStr">
-        <is>
-          <t>Stranger Things: The First Shadow (play)</t>
-        </is>
-      </c>
+      <c r="E158" s="39" t="inlineStr">
+        <is>
+          <t>A la zona de teatros: subte J desde Marcy Av hasta Essex St y F hasta 42 St-Bryant Park (~35 min con transbordo), o directamente Uber al teatro (~20-25 min, $25-35 — un sábado a la noche el puente puede estar cargado).</t>
+        </is>
+      </c>
+      <c r="F158" s="37" t="inlineStr"/>
       <c r="G158" s="40" t="inlineStr"/>
       <c r="H158" s="41" t="inlineStr"/>
       <c r="I158" s="41" t="inlineStr"/>
     </row>
-    <row r="159" ht="16" customHeight="1">
+    <row r="159" ht="30" customHeight="1">
       <c r="A159" s="35" t="n"/>
-      <c r="B159" s="36" t="inlineStr">
+      <c r="B159" s="42" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C159" s="43" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C159" s="37" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="D159" s="38" t="inlineStr">
+      <c r="D159" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E159" s="39" t="inlineStr">
-        <is>
-          <t>Subte 1 desde Times Sq hasta Christopher St (~15 min) y caminar al corazón del Village.</t>
-        </is>
-      </c>
-      <c r="F159" s="37" t="inlineStr"/>
+      <c r="E159" s="45" t="inlineStr">
+        <is>
+          <t>★★ PLAY DE BROADWAY — mi recomendación: STRANGER THINGS: THE FIRST SHADOW (Marquis, desde ~$76): la maquinaria escénica que ganó el Tony — para quien viene de Mercer Labs, el mismo músculo llevado al teatro. Alternativas esa semana: Harry Potter and the Cursed Child, Paranormal Activity, The Imaginary Invalid. COMPRA FIRME esta semana y verificar el horario real de la función (19:00/19:30/20:00): tiene que terminar ~22:00 para lo que sigue.</t>
+        </is>
+      </c>
+      <c r="F159" s="43" t="inlineStr">
+        <is>
+          <t>Stranger Things: The First Shadow (play)</t>
+        </is>
+      </c>
       <c r="G159" s="40" t="inlineStr"/>
       <c r="H159" s="41" t="inlineStr"/>
       <c r="I159" s="41" t="inlineStr"/>
     </row>
-    <row r="160" ht="30" customHeight="1">
+    <row r="160" ht="16" customHeight="1">
       <c r="A160" s="35" t="n"/>
       <c r="B160" s="36" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C160" s="37" t="inlineStr">
+        <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="C160" s="37" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
       <c r="D160" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36637,7 +36637,7 @@
       </c>
       <c r="E160" s="39" t="inlineStr">
         <is>
-          <t>Paseo sin apuro por Bleecker y MacDougal — la esquina folk de los 60s de noche, un café o un trago corto. El único objetivo real: estar en la puerta del Wha a las 23:10.</t>
+          <t>Subte 1 desde Times Sq hasta Christopher St (~15 min) y caminar al corazón del Village.</t>
         </is>
       </c>
       <c r="F160" s="37" t="inlineStr"/>
@@ -36647,106 +36647,102 @@
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="35" t="n"/>
-      <c r="B161" s="42" t="inlineStr">
+      <c r="B161" s="36" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C161" s="37" t="inlineStr">
         <is>
           <t>23:15</t>
         </is>
       </c>
-      <c r="C161" s="43" t="inlineStr"/>
-      <c r="D161" s="44" t="inlineStr">
+      <c r="D161" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E161" s="45" t="inlineStr">
-        <is>
-          <t>★★ CAFÉ WHA — LLEGAR 23:10-23:15: la reserva de Eventbrite NO garantiza admisión y a las 23:30 EN PUNTO liberan los asientos vacíos al standby. TODOS los de la reserva presentes. Set 2 de la house band 23:45-~1:15: soul y funk a máquina en el sótano donde debutaron Dylan, Hendrix y Springsteen. $20 por cabeza van a la cuenta + consumo. Vuelta: subte 1 Christopher St → 72 St (~25 min) o taxi.</t>
-        </is>
-      </c>
-      <c r="F161" s="43" t="inlineStr">
-        <is>
-          <t>Cafe Wha?</t>
-        </is>
-      </c>
+      <c r="E161" s="39" t="inlineStr">
+        <is>
+          <t>Paseo sin apuro por Bleecker y MacDougal — la esquina folk de los 60s de noche, un café o un trago corto. El único objetivo real: estar en la puerta del Wha a las 23:10.</t>
+        </is>
+      </c>
+      <c r="F161" s="37" t="inlineStr"/>
       <c r="G161" s="40" t="inlineStr"/>
       <c r="H161" s="41" t="inlineStr"/>
       <c r="I161" s="41" t="inlineStr"/>
     </row>
-    <row r="162" ht="32" customHeight="1">
-      <c r="A162" s="46" t="inlineStr">
+    <row r="162" ht="30" customHeight="1">
+      <c r="A162" s="35" t="n"/>
+      <c r="B162" s="42" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="C162" s="43" t="inlineStr"/>
+      <c r="D162" s="44" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E162" s="45" t="inlineStr">
+        <is>
+          <t>★★ CAFÉ WHA — LLEGAR 23:10-23:15: la reserva de Eventbrite NO garantiza admisión y a las 23:30 EN PUNTO liberan los asientos vacíos al standby. TODOS los de la reserva presentes. Set 2 de la house band 23:45-~1:15: soul y funk a máquina en el sótano donde debutaron Dylan, Hendrix y Springsteen. $20 por cabeza van a la cuenta + consumo. Vuelta: subte 1 Christopher St → 72 St (~25 min) o taxi.</t>
+        </is>
+      </c>
+      <c r="F162" s="43" t="inlineStr">
+        <is>
+          <t>Cafe Wha?</t>
+        </is>
+      </c>
+      <c r="G162" s="40" t="inlineStr"/>
+      <c r="H162" s="41" t="inlineStr"/>
+      <c r="I162" s="41" t="inlineStr"/>
+    </row>
+    <row r="163" ht="32" customHeight="1">
+      <c r="A163" s="46" t="inlineStr">
         <is>
           <t>ALTERNATIVA / OJO:  SOBRE PETER LUGER: la mesa de las 17:00 es la realista — y ahora es la única que funciona: el play manda. PLAN B si no hay mesa: correr Peter Luger al ALMUERZO del mismo día (12:45). // SI EL CANSANCIO GANA A LAS 22:00: el Café Wha es la pieza sacrificable — la reserva es gratis y no penaliza no ir; el play, pagado, no. // Sigue afuera: Bar LunÀtico y Barbès (Bed-Stuy/Park Slope), sin noche posible.</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="22" customHeight="1">
-      <c r="A164" s="33" t="inlineStr">
+    <row r="165" ht="22" customHeight="1">
+      <c r="A165" s="33" t="inlineStr">
         <is>
           <t>DÍA 9 · Domingo 06/09 · Checkout, Central Park, Roosevelt Island, MoMA PS1 y vuelo  —  base: The Beacon (checkout) → EWR  ·  Ambos</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="32" customHeight="1">
-      <c r="A165" s="34" t="inlineStr">
+    <row r="166" ht="32" customHeight="1">
+      <c r="A166" s="34" t="inlineStr">
         <is>
           <t>El día arranca con el CHECKOUT de The Beacon: hacerlo temprano y dejar las valijas en el bell desk libera el día entero. El vuelo sale 23:40, así que hay margen — pero es el domingo del fin de semana largo de Labor Day, la noche de mayor tráfico del año, y EWR va a estar cargado. Por eso todo queda cerca y se sale con 2h45 de anticipación. EL CAMBIO DEL ÚLTIMO DÍA: entra MOMA PS1 y sale el Guggenheim. Se verificó el 27/8 que la rotonda del Guggenheim está cerrada hasta el 17/9 —no se camina la rampa, que es la razón para ir— y PS1 resultó ser gratis, abierto hasta las 18 los domingos, a 1,2 km de Roosevelt Island y con «Greater New York 2026» en pie hasta el 7/9. Era el último imprescindible que quedaba afuera del viaje. El Guggenheim queda escrito como alternativa por si cambian de idea.</t>
         </is>
       </c>
-    </row>
-    <row r="166" ht="30" customHeight="1">
-      <c r="A166" s="35" t="n"/>
-      <c r="B166" s="36" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="C166" s="37" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="D166" s="38" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="E166" s="39" t="inlineStr">
-        <is>
-          <t>Desayuno SIN despertador temprano: anoche terminó ~1:30 en el Village y lo único con hora fija hoy es el PS1, que cierra a las 18:00. Dormir un poco más está permitido.</t>
-        </is>
-      </c>
-      <c r="F166" s="37" t="inlineStr"/>
-      <c r="G166" s="40" t="inlineStr"/>
-      <c r="H166" s="41" t="inlineStr"/>
-      <c r="I166" s="41" t="inlineStr"/>
     </row>
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="35" t="n"/>
-      <c r="B167" s="42" t="inlineStr">
+      <c r="B167" s="36" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C167" s="37" t="inlineStr">
         <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="C167" s="43" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="D167" s="44" t="inlineStr">
+      <c r="D167" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E167" s="45" t="inlineStr">
-        <is>
-          <t>★ CHECKOUT de The Beacon y dejar las valijas en el bell desk. El checkout formal suele ser 11:00-12:00, pero hacerlo antes libera el día.</t>
-        </is>
-      </c>
-      <c r="F167" s="43" t="inlineStr">
-        <is>
-          <t>Hotel The Beacon (3-6 sep)</t>
-        </is>
-      </c>
+      <c r="E167" s="39" t="inlineStr">
+        <is>
+          <t>Desayuno SIN despertador temprano: anoche terminó ~1:30 en el Village y lo único con hora fija hoy es el PS1, que cierra a las 18:00. Dormir un poco más está permitido.</t>
+        </is>
+      </c>
+      <c r="F167" s="37" t="inlineStr"/>
       <c r="G167" s="40" t="inlineStr"/>
       <c r="H167" s="41" t="inlineStr"/>
       <c r="I167" s="41" t="inlineStr"/>
@@ -36755,14 +36751,14 @@
       <c r="A168" s="35" t="n"/>
       <c r="B168" s="42" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="C168" s="43" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="C168" s="43" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="D168" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36770,61 +36766,65 @@
       </c>
       <c r="E168" s="45" t="inlineStr">
         <is>
-          <t>★ CENTRAL PARK cruzando de oeste a este: Bethesda Terrace, el Ramble, Bow Bridge. Se entra por la 72 desde Broadway, a tres cuadras del hotel.</t>
+          <t>★ CHECKOUT de The Beacon y dejar las valijas en el bell desk. El checkout formal suele ser 11:00-12:00, pero hacerlo antes libera el día.</t>
         </is>
       </c>
       <c r="F168" s="43" t="inlineStr">
         <is>
-          <t>Central Park</t>
-        </is>
-      </c>
-      <c r="G168" s="40" t="inlineStr">
-        <is>
-          <t>🚶 ~20 min a pie (1.5 km) o 🚇 ~15 min · estimado</t>
-        </is>
-      </c>
+          <t>Hotel The Beacon (3-6 sep)</t>
+        </is>
+      </c>
+      <c r="G168" s="40" t="inlineStr"/>
       <c r="H168" s="41" t="inlineStr"/>
       <c r="I168" s="41" t="inlineStr"/>
     </row>
-    <row r="169" ht="16" customHeight="1">
+    <row r="169" ht="30" customHeight="1">
       <c r="A169" s="35" t="n"/>
-      <c r="B169" s="36" t="inlineStr">
+      <c r="B169" s="42" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="C169" s="43" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="C169" s="37" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="D169" s="38" t="inlineStr">
+      <c r="D169" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E169" s="39" t="inlineStr">
-        <is>
-          <t>Almuerzo en el Upper East Side, saliendo del parque por la Quinta.</t>
-        </is>
-      </c>
-      <c r="F169" s="37" t="inlineStr"/>
-      <c r="G169" s="40" t="inlineStr"/>
+      <c r="E169" s="45" t="inlineStr">
+        <is>
+          <t>★ CENTRAL PARK cruzando de oeste a este: Bethesda Terrace, el Ramble, Bow Bridge. Se entra por la 72 desde Broadway, a tres cuadras del hotel.</t>
+        </is>
+      </c>
+      <c r="F169" s="43" t="inlineStr">
+        <is>
+          <t>Central Park</t>
+        </is>
+      </c>
+      <c r="G169" s="40" t="inlineStr">
+        <is>
+          <t>🚶 ~20 min a pie (1.5 km) o 🚇 ~15 min · estimado</t>
+        </is>
+      </c>
       <c r="H169" s="41" t="inlineStr"/>
       <c r="I169" s="41" t="inlineStr"/>
     </row>
-    <row r="170" ht="30" customHeight="1">
+    <row r="170" ht="16" customHeight="1">
       <c r="A170" s="35" t="n"/>
       <c r="B170" s="36" t="inlineStr">
         <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C170" s="37" t="inlineStr">
+        <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="C170" s="37" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="D170" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36832,7 +36832,7 @@
       </c>
       <c r="E170" s="39" t="inlineStr">
         <is>
-          <t>Bajar a 59 St y 2ª Av: subte 6 desde 68 St-Hunter College (el 4/5 exprés NO para ahí), o caminando por la Quinta si el día está lindo.</t>
+          <t>Almuerzo en el Upper East Side, saliendo del parque por la Quinta.</t>
         </is>
       </c>
       <c r="F170" s="37" t="inlineStr"/>
@@ -36842,60 +36842,56 @@
     </row>
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="35" t="n"/>
-      <c r="B171" s="42" t="inlineStr">
+      <c r="B171" s="36" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C171" s="37" t="inlineStr">
         <is>
           <t>13:50</t>
         </is>
       </c>
-      <c r="C171" s="43" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="D171" s="44" t="inlineStr">
+      <c r="D171" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E171" s="45" t="inlineStr">
-        <is>
-          <t>★ ROOSEVELT ISLAND TRAMWAY ($3, OMNY) — cruza el East River a 76 metros de altura con el Queensboro Bridge al lado. Es la vista de $50 por el precio de un viaje de subte.</t>
-        </is>
-      </c>
-      <c r="F171" s="43" t="inlineStr">
-        <is>
-          <t>Roosevelt Island Tramway</t>
-        </is>
-      </c>
+      <c r="E171" s="39" t="inlineStr">
+        <is>
+          <t>Bajar a 59 St y 2ª Av: subte 6 desde 68 St-Hunter College (el 4/5 exprés NO para ahí), o caminando por la Quinta si el día está lindo.</t>
+        </is>
+      </c>
+      <c r="F171" s="37" t="inlineStr"/>
       <c r="G171" s="40" t="inlineStr"/>
       <c r="H171" s="41" t="inlineStr"/>
       <c r="I171" s="41" t="inlineStr"/>
     </row>
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="35" t="n"/>
-      <c r="B172" s="36" t="inlineStr">
+      <c r="B172" s="42" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="C172" s="43" t="inlineStr">
         <is>
           <t>14:25</t>
         </is>
       </c>
-      <c r="C172" s="37" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="D172" s="38" t="inlineStr">
+      <c r="D172" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E172" s="39" t="inlineStr">
-        <is>
-          <t>FDR Four Freedoms Park — del teleférico son ~20 min a pie por el borde del río. La última obra de Louis Kahn: granito, plátanos y una sala abierta al río apuntando a Manhattan. Gratis y vacía. Se pasa por las ruinas del Smallpox Hospital.</t>
-        </is>
-      </c>
-      <c r="F172" s="37" t="inlineStr">
-        <is>
-          <t>FDR Four Freedoms Park</t>
+      <c r="E172" s="45" t="inlineStr">
+        <is>
+          <t>★ ROOSEVELT ISLAND TRAMWAY ($3, OMNY) — cruza el East River a 76 metros de altura con el Queensboro Bridge al lado. Es la vista de $50 por el precio de un viaje de subte.</t>
+        </is>
+      </c>
+      <c r="F172" s="43" t="inlineStr">
+        <is>
+          <t>Roosevelt Island Tramway</t>
         </is>
       </c>
       <c r="G172" s="40" t="inlineStr"/>
@@ -36906,14 +36902,14 @@
       <c r="A173" s="35" t="n"/>
       <c r="B173" s="36" t="inlineStr">
         <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="C173" s="37" t="inlineStr">
+        <is>
           <t>15:05</t>
         </is>
       </c>
-      <c r="C173" s="37" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="D173" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36921,10 +36917,14 @@
       </c>
       <c r="E173" s="39" t="inlineStr">
         <is>
-          <t>SALIR 15:05 de Four Freedoms Park y caminar 15 min al norte por el borde del río hasta la ESTACIÓN DEL F, que está en el medio de la isla (Main St y Roosevelt Island Bridge). Hoy NO se vuelve en teleférico: se cruza a Queens por abajo.</t>
-        </is>
-      </c>
-      <c r="F173" s="37" t="inlineStr"/>
+          <t>FDR Four Freedoms Park — del teleférico son ~20 min a pie por el borde del río. La última obra de Louis Kahn: granito, plátanos y una sala abierta al río apuntando a Manhattan. Gratis y vacía. Se pasa por las ruinas del Smallpox Hospital.</t>
+        </is>
+      </c>
+      <c r="F173" s="37" t="inlineStr">
+        <is>
+          <t>FDR Four Freedoms Park</t>
+        </is>
+      </c>
       <c r="G173" s="40" t="inlineStr"/>
       <c r="H173" s="41" t="inlineStr"/>
       <c r="I173" s="41" t="inlineStr"/>
@@ -36933,14 +36933,14 @@
       <c r="A174" s="35" t="n"/>
       <c r="B174" s="36" t="inlineStr">
         <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="C174" s="37" t="inlineStr">
+        <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="C174" s="37" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="D174" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -36948,7 +36948,7 @@
       </c>
       <c r="E174" s="39" t="inlineStr">
         <is>
-          <t>Subte F, UNA parada: Roosevelt Island → 21 St-Queensbridge (~4 min). Salir y caminar 12-15 min al sur por 21st St / Jackson Ave.</t>
+          <t>SALIR 15:05 de Four Freedoms Park y caminar 15 min al norte por el borde del río hasta la ESTACIÓN DEL F, que está en el medio de la isla (Main St y Roosevelt Island Bridge). Hoy NO se vuelve en teleférico: se cruza a Queens por abajo.</t>
         </is>
       </c>
       <c r="F174" s="37" t="inlineStr"/>
@@ -36958,58 +36958,58 @@
     </row>
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="35" t="n"/>
-      <c r="B175" s="42" t="inlineStr">
+      <c r="B175" s="36" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C175" s="37" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="C175" s="43" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="D175" s="44" t="inlineStr">
+      <c r="D175" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E175" s="45" t="inlineStr">
-        <is>
-          <t>★★ MOMA PS1 — el último imprescindible del viaje, y entra gratis. Escuela pública de 1892 reconvertida en el laboratorio del MoMA: lo que no se anima a mostrar en la Quinta Avenida. VERIFICADO el 27/8: ENTRADA GRATUITA para todos, abre domingos 12:00-18:00, y «Greater New York 2026» —la encuesta insignia de la casa, que se hace cada cinco años— sigue en pie hasta el 7 de septiembre, o sea que la agarran por un día. Más el Courtyard Commission de Precious Okoyomon al aire libre. Dos horas holgadas hasta las 17:45.</t>
-        </is>
-      </c>
-      <c r="F175" s="43" t="inlineStr">
-        <is>
-          <t>MoMA PS1</t>
-        </is>
-      </c>
+      <c r="E175" s="39" t="inlineStr">
+        <is>
+          <t>Subte F, UNA parada: Roosevelt Island → 21 St-Queensbridge (~4 min). Salir y caminar 12-15 min al sur por 21st St / Jackson Ave.</t>
+        </is>
+      </c>
+      <c r="F175" s="37" t="inlineStr"/>
       <c r="G175" s="40" t="inlineStr"/>
       <c r="H175" s="41" t="inlineStr"/>
       <c r="I175" s="41" t="inlineStr"/>
     </row>
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="35" t="n"/>
-      <c r="B176" s="36" t="inlineStr">
+      <c r="B176" s="42" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C176" s="43" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="C176" s="37" t="inlineStr">
-        <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="D176" s="38" t="inlineStr">
+      <c r="D176" s="44" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E176" s="39" t="inlineStr">
-        <is>
-          <t>Del PS1 al hotel: subte 7 desde Court Sq hasta Times Sq y 1/2/3 hasta 72 St, o E/M hasta 53 St (~45 min). Llegan 18:30, justo para las valijas. El vuelo no se toca.</t>
-        </is>
-      </c>
-      <c r="F176" s="37" t="inlineStr"/>
+      <c r="E176" s="45" t="inlineStr">
+        <is>
+          <t>★★ MOMA PS1 — el último imprescindible del viaje, y entra gratis. Escuela pública de 1892 reconvertida en el laboratorio del MoMA: lo que no se anima a mostrar en la Quinta Avenida. VERIFICADO el 27/8: ENTRADA GRATUITA para todos, abre domingos 12:00-18:00, y «Greater New York 2026» —la encuesta insignia de la casa, que se hace cada cinco años— sigue en pie hasta el 7 de septiembre, o sea que la agarran por un día. Más el Courtyard Commission de Precious Okoyomon al aire libre. Dos horas holgadas hasta las 17:45.</t>
+        </is>
+      </c>
+      <c r="F176" s="43" t="inlineStr">
+        <is>
+          <t>MoMA PS1</t>
+        </is>
+      </c>
       <c r="G176" s="40" t="inlineStr"/>
       <c r="H176" s="41" t="inlineStr"/>
       <c r="I176" s="41" t="inlineStr"/>
@@ -37018,14 +37018,14 @@
       <c r="A177" s="35" t="n"/>
       <c r="B177" s="36" t="inlineStr">
         <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="C177" s="37" t="inlineStr">
+        <is>
           <t>18:20</t>
         </is>
       </c>
-      <c r="C177" s="37" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
       <c r="D177" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -37033,7 +37033,7 @@
       </c>
       <c r="E177" s="39" t="inlineStr">
         <is>
-          <t>◇ SI PREFIEREN EL GUGGENHEIM, sigue estando y este bloque se ignora: pay-what-you-wish domingos 16:00-17:30 (mínimo $1) y entrada rebajada a $16 el resto del horario. ⚠️ PERO la rotonda está CERRADA del 3/8 al 17/9 por el montaje de Taryn Simon: no se camina la rampa —que es la razón para ir— y avisan que puede haber ruido de obra. Quedan las torres 4, 5 y 7 con «Guggenheim Pop» (Lichtenstein, Warhol, Oldenburg, Cattelan) y la colección Thannhauser. Para hacerlo: en vez de cruzar a Queens, teleférico de vuelta y subte 4/5/6 de 59 St a 86 St, y hay que salir del FDR Park 15:05 para entrar 16:00 — la ventana a voluntad va hasta las 17:30 y el museo cierra ahí.</t>
+          <t>Del PS1 al hotel: subte 7 desde Court Sq hasta Times Sq y 1/2/3 hasta 72 St, o E/M hasta 53 St (~45 min). Llegan 18:30, justo para las valijas. El vuelo no se toca.</t>
         </is>
       </c>
       <c r="F177" s="37" t="inlineStr"/>
@@ -37041,18 +37041,18 @@
       <c r="H177" s="41" t="inlineStr"/>
       <c r="I177" s="41" t="inlineStr"/>
     </row>
-    <row r="178" ht="16" customHeight="1">
+    <row r="178" ht="30" customHeight="1">
       <c r="A178" s="35" t="n"/>
       <c r="B178" s="36" t="inlineStr">
         <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="C178" s="37" t="inlineStr">
+        <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="C178" s="37" t="inlineStr">
-        <is>
-          <t>19:40</t>
-        </is>
-      </c>
       <c r="D178" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -37060,7 +37060,7 @@
       </c>
       <c r="E178" s="39" t="inlineStr">
         <is>
-          <t>Retirar las valijas del bell desk. Cena tranquila cerca del hotel: es la última.</t>
+          <t>◇ SI PREFIEREN EL GUGGENHEIM, sigue estando y este bloque se ignora: pay-what-you-wish domingos 16:00-17:30 (mínimo $1) y entrada rebajada a $16 el resto del horario. ⚠️ PERO la rotonda está CERRADA del 3/8 al 17/9 por el montaje de Taryn Simon: no se camina la rampa —que es la razón para ir— y avisan que puede haber ruido de obra. Quedan las torres 4, 5 y 7 con «Guggenheim Pop» (Lichtenstein, Warhol, Oldenburg, Cattelan) y la colección Thannhauser. Para hacerlo: en vez de cruzar a Queens, teleférico de vuelta y subte 4/5/6 de 59 St a 86 St, y hay que salir del FDR Park 15:05 para entrar 16:00 — la ventana a voluntad va hasta las 17:30 y el museo cierra ahí.</t>
         </is>
       </c>
       <c r="F178" s="37" t="inlineStr"/>
@@ -37072,14 +37072,14 @@
       <c r="A179" s="35" t="n"/>
       <c r="B179" s="36" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C179" s="37" t="inlineStr">
+        <is>
           <t>19:40</t>
         </is>
       </c>
-      <c r="C179" s="37" t="inlineStr">
-        <is>
-          <t>20:14</t>
-        </is>
-      </c>
       <c r="D179" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -37087,7 +37087,7 @@
       </c>
       <c r="E179" s="39" t="inlineStr">
         <is>
-          <t>Salir de The Beacon. Subte 1/2/3 desde 72 St hasta 34 St-Penn Station: ~10 min, $3.</t>
+          <t>Retirar las valijas del bell desk. Cena tranquila cerca del hotel: es la última.</t>
         </is>
       </c>
       <c r="F179" s="37" t="inlineStr"/>
@@ -37095,18 +37095,18 @@
       <c r="H179" s="41" t="inlineStr"/>
       <c r="I179" s="41" t="inlineStr"/>
     </row>
-    <row r="180" ht="30" customHeight="1">
+    <row r="180" ht="16" customHeight="1">
       <c r="A180" s="35" t="n"/>
       <c r="B180" s="36" t="inlineStr">
         <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="C180" s="37" t="inlineStr">
+        <is>
           <t>20:14</t>
         </is>
       </c>
-      <c r="C180" s="37" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
       <c r="D180" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -37114,7 +37114,7 @@
       </c>
       <c r="E180" s="39" t="inlineStr">
         <is>
-          <t>NJ Transit Penn Station → EWR, llega 20:38. $17,25 (incluye el AirTrain). VERIFICAR el horario dominical en njtransit.com unos días antes.</t>
+          <t>Salir de The Beacon. Subte 1/2/3 desde 72 St hasta 34 St-Penn Station: ~10 min, $3.</t>
         </is>
       </c>
       <c r="F180" s="37" t="inlineStr"/>
@@ -37122,18 +37122,18 @@
       <c r="H180" s="41" t="inlineStr"/>
       <c r="I180" s="41" t="inlineStr"/>
     </row>
-    <row r="181" ht="16" customHeight="1">
+    <row r="181" ht="30" customHeight="1">
       <c r="A181" s="35" t="n"/>
       <c r="B181" s="36" t="inlineStr">
         <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="C181" s="37" t="inlineStr">
+        <is>
           <t>20:45</t>
         </is>
       </c>
-      <c r="C181" s="37" t="inlineStr">
-        <is>
-          <t>20:55</t>
-        </is>
-      </c>
       <c r="D181" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -37141,7 +37141,7 @@
       </c>
       <c r="E181" s="39" t="inlineStr">
         <is>
-          <t>AirTrain hasta la terminal: 10-15 min.</t>
+          <t>NJ Transit Penn Station → EWR, llega 20:38. $17,25 (incluye el AirTrain). VERIFICAR el horario dominical en njtransit.com unos días antes.</t>
         </is>
       </c>
       <c r="F181" s="37" t="inlineStr"/>
@@ -37149,14 +37149,18 @@
       <c r="H181" s="41" t="inlineStr"/>
       <c r="I181" s="41" t="inlineStr"/>
     </row>
-    <row r="182" ht="30" customHeight="1">
+    <row r="182" ht="16" customHeight="1">
       <c r="A182" s="35" t="n"/>
       <c r="B182" s="36" t="inlineStr">
         <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C182" s="37" t="inlineStr">
+        <is>
           <t>20:55</t>
         </is>
       </c>
-      <c r="C182" s="37" t="inlineStr"/>
       <c r="D182" s="38" t="inlineStr">
         <is>
           <t>Ambos</t>
@@ -37164,7 +37168,7 @@
       </c>
       <c r="E182" s="39" t="inlineStr">
         <is>
-          <t>En terminal. Faltan 2h45 para el vuelo de las 23:40 — correcto para un internacional en el domingo de Labor Day, que es la noche de más tráfico del año en EWR.</t>
+          <t>AirTrain hasta la terminal: 10-15 min.</t>
         </is>
       </c>
       <c r="F182" s="37" t="inlineStr"/>
@@ -37172,8 +37176,31 @@
       <c r="H182" s="41" t="inlineStr"/>
       <c r="I182" s="41" t="inlineStr"/>
     </row>
-    <row r="183" ht="32" customHeight="1">
-      <c r="A183" s="46" t="inlineStr">
+    <row r="183" ht="30" customHeight="1">
+      <c r="A183" s="35" t="n"/>
+      <c r="B183" s="36" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="C183" s="37" t="inlineStr"/>
+      <c r="D183" s="38" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="E183" s="39" t="inlineStr">
+        <is>
+          <t>En terminal. Faltan 2h45 para el vuelo de las 23:40 — correcto para un internacional en el domingo de Labor Day, que es la noche de más tráfico del año en EWR.</t>
+        </is>
+      </c>
+      <c r="F183" s="37" t="inlineStr"/>
+      <c r="G183" s="40" t="inlineStr"/>
+      <c r="H183" s="41" t="inlineStr"/>
+      <c r="I183" s="41" t="inlineStr"/>
+    </row>
+    <row r="184" ht="32" customHeight="1">
+      <c r="A184" s="46" t="inlineStr">
         <is>
           <t>ALTERNATIVA / OJO:  COLCHÓN: si algo se atrasa, el tren siguiente sale 20:55 y llega a EWR 21:16, o sea terminal ~21:35 y 2h05 antes del vuelo. Es el último que yo tomaría. // Si prefieren un último día sin moverse, salteen el teleférico y estiren Central Park hasta el Guggenheim: el parque solo da para toda la mañana y la tarde. Lo que NO conviene hoy es meter algo nuevo y grande. // LO QUE SE PIERDEN POR EL VUELO, y duele: esta noche a las 20:00 el Met proyecta gratis en Lincoln Center «El Último Sueño de Frida y Diego» —la misma Frida de la muestra del MoMA del lunes— y ustedes salen del hotel 19:40 hacia Penn Station. Está a diez cuadras del Beacon. No hay forma de que entre sin poner en riesgo el vuelo. // SI QUIEREN VOLVER AL GUGGENHEIM en vez del PS1: está escrito en el bloque de las 18:20, con los tiempos hechos. Cuesta el último imprescindible del viaje y hay que aceptar que la rampa —la razón para ir— no se camina hasta el 17/9. Tercera opción si ninguna convence: el Whitney también abre los domingos.</t>
         </is>
@@ -37181,38 +37208,38 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A183:I183"/>
-    <mergeCell ref="A164:I164"/>
+    <mergeCell ref="A128:I128"/>
     <mergeCell ref="A84:I84"/>
     <mergeCell ref="A66:I66"/>
-    <mergeCell ref="A145:I145"/>
+    <mergeCell ref="A163:I163"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="A101:I101"/>
     <mergeCell ref="A86:I86"/>
     <mergeCell ref="A104:I104"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A126:I126"/>
+    <mergeCell ref="A144:I144"/>
+    <mergeCell ref="A184:I184"/>
+    <mergeCell ref="A125:I125"/>
+    <mergeCell ref="A147:I147"/>
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A165:I165"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A68:I68"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="A127:I127"/>
-    <mergeCell ref="A143:I143"/>
     <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A166:I166"/>
     <mergeCell ref="A103:I103"/>
     <mergeCell ref="A45:I45"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A146:I146"/>
-    <mergeCell ref="A124:I124"/>
     <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A162:I162"/>
     <mergeCell ref="A69:I69"/>
     <mergeCell ref="A87:I87"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H185" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H186" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,Reservado,Confirmado,Descartado"</formula1>
     </dataValidation>
   </dataValidations>
